--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,20 +476,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K92"/>
+  <dimension ref="A1:K95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="148" customWidth="1" min="3" max="3"/>
+    <col width="104" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="507" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="275" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -552,2582 +552,2565 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>3.05</v>
+        <v>4.43</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>消息面上，节后钨原料价格持续飙升，钨粉已突破1800元/公斤。</t>
+          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>sz002378</t>
+          <t>sh600759</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>章源钨业</t>
+          <t>洲际油气</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>40.6</v>
+        <v>6.83</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>7天5板</t>
+          <t>5天3板</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>有色钨|公司建立了从钨上游采矿、选矿，中游冶炼至下游精深加工的完整一体化生产体系，是国内钨行业产业链完整的厂商之一，拥有淘锡坑钨矿、新安子钨锡矿、大余石雷钨矿、天井窝钨矿、长流坑铜矿5座采矿权矿山，以及东峰、西坑口、碧坑、泥坑、龙潭面、石咀脑6个钨锡矿详查探矿权矿区，主要从事以钨为原料的钨精矿、仲钨酸铵（APT）、氧化钨、钨粉、碳化钨粉、热喷涂粉、硬质合金的生产及销售。公司APT、钨粉、碳化钨粉和硬质合金产能每年分别为10000吨、8000吨、6000吨和1500吨，“高性能钨粉体智能制造技术改造（二期）”项目投产后预计可新增7000吨钨粉和4600吨碳化钨粉的产能（2019年9月）。</t>
+          <t>油气|公司是以勘探开发为主的国际化独立石油公司，目前公司的运营区块主要集中在哈萨克斯坦，主力在产项目马腾油田和克山油田均位于哈萨克斯坦滨里海盆地，是国际公认的油气富集的区域之一。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>有色钨</t>
+          <t>油气</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>3.05</v>
+        <v>4.43</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>消息面上，节后钨原料价格持续飙升，钨粉已突破1800元/公斤。</t>
+          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sh600397</t>
+          <t>sz002207</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>江钨装备</t>
+          <t>准油股份</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>21.53</v>
+        <v>12.42</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>7天5板</t>
-        </is>
-      </c>
+        <v>10.01</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>选矿装备|2025年4月2日公告，公司控股股东江钨控股拟将控股子公司江钨发展持有的金环磁选57%股份，与公司所持有的煤炭业务相关资产及负债进行置换，拟置入资产与拟置出资产交易价格的差额由一方向另一方以现金等方式补足。本次交易构成关联交易，预计将构成重大资产重组。金环磁选的SCT永磁筒式磁选机适用于于磁铁矿、磁黄铁矿、磁赤铁矿、钛磁铁矿、焙烧物料的粗选、扫选、精选作业，也适用于各种非金属矿物的磨后除铁作业。</t>
+          <t>油气|公司是为石油、天然气开采企业提供油田动态监测和提高采收率技术服务的专业化企业，已形成油田动态监测资料录取、资料解释研究和应用、治理方案编制、增产措施施工及效果评价等综合技术服务能力，是西部地区实力较强的一体化油田稳产、增产技术服务企业，能够提供油田增产、油田管理和配套建设等“一站式”技术服务。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>选矿装备</t>
+          <t>油气</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3.05</v>
+        <v>4.43</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>消息面上，节后钨原料价格持续飙升，钨粉已突破1800元/公斤。</t>
+          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sz000657</t>
+          <t>sz002490</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>中钨高新</t>
+          <t>山东墨龙</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>66.22</v>
+        <v>9.68</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3天2板</t>
-        </is>
-      </c>
+      <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">有色钨|公司作为中国五矿唯一钨产业管控平台，具有钨全产业链优势，打通了钨产业上游资源、中游冶炼、下游硬质合金产品的全流程环节。公司依托完整产业链优势，现在是全球第一大硬质合金生产商，全球第一大钨资源开发供应商，在国内市场份额超三成，是国内钨产业领域龙头。
-2024年1月9日公告，公司拟通过发行股份及支付现金的方式，购买五矿钨业、沃溪矿业合计持有的柿竹园公司100%股权，此次股票发行价格敲定为7.05元/股，标的资产最终价格亦尚未确定。柿竹园公司主营业务为钨、钼、铋、萤石等多金属矿的采选、钨精矿冶炼加工和铋系新材料研发。本次交易有助于中钨高新形成集钨矿山、钨冶炼、硬质合金及深加工的完整钨产业链，整合资源，促进产业转型升级，增强上市公司抵御经营风险的能力。
-</t>
+          <t>油气|全产业链石油钻采装备制造商，主要产品包括油气开采用管、流体及结构用管、抽油机、抽油泵、抽油杆、钻机用缸套、阀门散件及大型铸锻件等。公司产品主要用于石油、天然气、煤层气、页岩气等行业。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>有色钨</t>
+          <t>油气</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>3.05</v>
+        <v>4.43</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>消息面上，节后钨原料价格持续飙升，钨粉已突破1800元/公斤。</t>
+          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sh600301</t>
+          <t>sz002828</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>华锡有色</t>
+          <t>贝肯能源</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>64.76000000000001</v>
+        <v>14.88</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3天2板</t>
-        </is>
-      </c>
+        <v>9.98</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>有色锡|公司是亚洲最大的锡多金属矿选矿基地、国内唯一的铟锡锑资源综合利用示范基地，拥有的多项关键战略性资源储量位居全球前列，主要金属矿产资源包括锡、锑、铟、锌、铅、银等，是国内主要的锡、锑金属生产企业之一。</t>
+          <t>油气|公司主要从事油气勘探和开发过程中的钻井工程技术服务及其他油田技术服务，具体包括钻井、固井、钻井液、定向井、欠平衡等，是国内规模较大的、能够提供一体化钻井工程技术服务的独立油田服务供应商。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>有色锡</t>
+          <t>油气</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>3.05</v>
+        <v>4.43</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>消息面上，节后钨原料价格持续飙升，钨粉已突破1800元/公斤。</t>
+          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sz002842</t>
+          <t>sz300164</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>翔鹭钨业</t>
+          <t>通源石油</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>41.56</v>
+        <v>18.08</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>10.01</v>
+        <v>19.97</v>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>有色钨|公司一直专注于钨制品的开发、生产与销售，主要产品包括各种规格的氧化钨、钨粉、碳化钨粉、钨合金粉及钨硬质合金等。公司是国内钨行业具备完整产业链的企业之一，从钨精矿采选、仲钨酸铵冶炼、氧化钨、钨粉、碳化钨粉、硬质合金及其工具等全系列钨产品的生产。公司是商务部批准的14家"钨品国营贸易出口资格企业"之一。</t>
+          <t>油气|公司是以油田增产为核心的国际油服企业，业务涵盖钻井、定向、完井压裂、测井、射孔、带压作业、连续油管和采油、油田化学等整个油气服务产业链，其中，公司是我国复合射孔行业的领军企业、行业国家标准制定的参与者。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>有色钨</t>
+          <t>油气</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>3.05</v>
+        <v>4.43</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>消息面上，节后钨原料价格持续飙升，钨粉已突破1800元/公斤。</t>
+          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sz002182</t>
+          <t>sh600871</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>宝武镁业</t>
+          <t>石化油服</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>21.79</v>
+        <v>3.53</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>9.99</v>
+        <v>9.969999999999999</v>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>有色镁|公司是集矿业开采、有色金属材料和深加工产品为一体的高新技术企业，主营业务为镁、铝合金材料的生产及深加工业务，主要产品包括镁合金、镁合金深加工产品、铝合金、铝合金深加工产品、中间合金和金属锶等，拥有“白云石开采-原镁冶炼-镁合金熔炼-镁合金精密铸造、变形加工-镁合金再生回收”的完整产业链。</t>
+          <t>油气|最大的综合油气工程与技术服务专业公司，全球油服行业第四，在中国的20多个省，76个盆地，561个区块开展油气工程技术服务；同时海外业务规模不断提高，在38个国家和地区执行364个项目。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>有色镁</t>
+          <t>油气</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>3.05</v>
+        <v>4.43</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>消息面上，节后钨原料价格持续飙升，钨粉已突破1800元/公斤。</t>
+          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sz002167</t>
+          <t>sh603619</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>东方锆业</t>
+          <t>中曼石油</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>15.58</v>
+        <v>39.99</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>10.03</v>
+        <v>10.01</v>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>有色锆|全球锆产品品种最齐全的制造商之一，公司产品包括锆矿砂、硅酸锆、氯氧化锆、电熔锆、二氧化锆、复合氧化锆、氧化锆陶瓷结构件及海绵锆八大系列共一百多个品种规格。
-公司于2021年6月21日晚公告，拟出资设立子公司汕头东里新材料有限公司，投资金额合计2亿元，并由该子公司负责投资建设年产6万吨高纯超细硅酸锆项目。另外，公司同意全资子公司云南东锆投资建设年产3万吨电熔氧化锆产业基地，投资预算2亿元。此外，公司拟重启铭瑞锆业Mindarie项目，投资预算2000-2600万澳元。铭瑞锆业Mindarie项目基础扎实，当前的矿权覆盖下，还有6条矿带可供开采。以年产重矿物12.5万吨来计算，剩余可开采年限为7-10年。</t>
+          <t>油气|国内最具实力的国际化钻井工程大包服务承包商和高端石油装备制造商。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>有色锆</t>
+          <t>油气</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>3.05</v>
+        <v>4.43</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>消息面上，节后钨原料价格持续飙升，钨粉已突破1800元/公斤。</t>
+          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sh600108</t>
+          <t>sz300191</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>亚盛集团</t>
+          <t>潜能恒信</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>3.97</v>
+        <v>44.23</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>9.969999999999999</v>
+        <v>19.99</v>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>有色钨|子公司甘肃亚盛鱼儿红矿业拟对鱼儿红牧场境内矿产资源进行开发，其中塔尔沟钨矿区拥有C+D 级三氧化钨22.42万吨(其中黑钨矿12.98万吨)，其中C级3773吨。</t>
+          <t>油气|石油勘探开发综合性公司，公司已具备了提供勘探开发一体化高端油气工程服务能力，服务内容涵盖地震采集、数据处理和解释、地球物理和地质综合分析研究、石油区块评价、井位部署、油藏描述、油气成藏模拟、钻完井服务、水平井压裂设计及施工以及智能化油田管理及相关软件开发等。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>有色钨</t>
+          <t>油气</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>3.05</v>
+        <v>4.43</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>消息面上，节后钨原料价格持续飙升，钨粉已突破1800元/公斤。</t>
+          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sh600259</t>
+          <t>sh600339</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>中稀有色</t>
+          <t>中油工程</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>102.08</v>
+        <v>4.66</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>10</v>
+        <v>9.91</v>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>有色钨|广东省稀土龙头，在粤北地区控股及参股5个钨矿山。</t>
+          <t>油气|公司主要从事以油气田地面工程服务、储运工程服务、炼化工程服务、环境工程服务、项目管理服务为核心的石油工程设计、施工及总承包等相关石油工程建设业务，公司面向国内外石油化工工程市场提供全产业链的“一站式”综合服务。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>有色钨</t>
+          <t>油气</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>3.05</v>
+        <v>4.43</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>消息面上，节后钨原料价格持续飙升，钨粉已突破1800元/公斤。</t>
+          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sh600549</t>
+          <t>sh600968</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>厦门钨业</t>
+          <t>海油发展</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>70.15000000000001</v>
+        <v>5.04</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>10</v>
+        <v>10.04</v>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>有色钨|旗下厦门三虹主要从事钨钼矿资源投资。</t>
+          <t>油气|公司业务以海洋石油生产服务为核心，重点发展FPSO生产技术服务、油田化学服务、多功能生活支持平台、油田装备运维、数据信息、监督监理等业务。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>有色钨</t>
+          <t>油气</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>3.05</v>
+        <v>4.43</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>消息面上，节后钨原料价格持续飙升，钨粉已突破1800元/公斤。</t>
+          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sz000960</t>
+          <t>sz002554</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>锡业股份</t>
+          <t>惠博普</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>44.36</v>
+        <v>4.66</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>9.99</v>
+        <v>9.91</v>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>有色锡|公司作为全球锡铟行业的龙头企业，拥有着国际先进水平的采、选、冶及深加工成套技术，及全行业最完整的产业链，主要产品为锡锭、阴极铜、锌锭、铟锭、锡材和锡化工产品等1000多个规格品种，现有锡冶炼产能8万吨/年，锡材产能4.1万吨/年、锡化工产能2.4万吨/年、阴极铜产能12.5万吨/年、锌冶炼产能10万吨/年、铟冶炼产能60吨/年。</t>
+          <t>油气|公司专注于油气水高效分离技术的研发，业务主要分为油气处理成套系统装备、油气开采系统装备、油田环保系统装备、油田工程技术服务四个领域。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>有色锡</t>
+          <t>油气</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>3.05</v>
+        <v>4.43</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>消息面上，节后钨原料价格持续飙升，钨粉已突破1800元/公斤。</t>
+          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sh600459</t>
+          <t>920088.BJ</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>贵研铂业</t>
+          <t>科力股份</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>25.85</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>有色铂|公司是国内在贵金属材料领域拥有系列核心技术和完整创新体系、集产学研用为一体的上市公司，已建立较完整的贵金属产业链体系，能够在贵金属全产业链上为客户提供从贵金属原料供给到新材料制造、资源回收利用的一站式综合服务。</t>
+          <t>油气|公司主营业务为提供油田化学技术服务、油田专用化学品和油田专用设备的研发、生产与销售。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>有色铂</t>
+          <t>油气</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>3.05</v>
+        <v>4.43</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>消息面上，节后钨原料价格持续飙升，钨粉已突破1800元/公斤。</t>
+          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sh603257</t>
+          <t>sh603727</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>中国瑞林</t>
+          <t xml:space="preserve">博迈科  </t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>66.43000000000001</v>
+        <v>19.81</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>矿业工程|在铜、钴资源开发上，公司在全球铜冶炼领域保持技术优势，承接设计了多个标志性项目，如非洲刚果（金）的卡莫阿铜冶炼厂和洛钼集团Tenke Fungurume铜钴矿项目。
-2025年10月15日公告，公司与江西省国有资本运营控股集团有限公司、江西江钨私募基金管理有限公司、农银金融资产投资有限公司、交银金融资产投资有限公司、江西钨业控股集团有限公司共同签署《合作意向书》。公司拟作为有限合伙人，参与设立江钨矿业基金。江钨矿业基金总规模暂定为20亿元，投资领域聚焦钨、稀土、钽铌、钼、锡等稀有金属项目。公司拟以自有资金出资3000万元。</t>
+          <t>油气|公司主要产品大类分为海洋油气开发模块、矿业开采模块、天然气液化模块等，产品具体涉及十多种子类别。公司为海洋油气开发、矿业开采和天然气液化领域中的国内外高端客户提供能源资源设施开发的专业分包服务。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>矿业工程</t>
+          <t>油气</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>3.05</v>
+        <v>4.43</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>消息面上，节后钨原料价格持续飙升，钨粉已突破1800元/公斤。</t>
+          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sh601958</t>
+          <t>sz301158</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>金钼股份</t>
+          <t>德石股份</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>24.53</v>
+        <v>31.2</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">有色钼|公司是生产规模排名全球前三位的钼金属生产运营商，是钼行业产业链最完整、产品线最丰富、整体工装技术先进的大型钼企业之一。公司主要业务包括钼金属采矿、选矿、冶炼、深加工、科研、贸易一体化运营和相关有色金属贸易业务。公司及公司的子公司正在运营两座世界级钼矿山，分别为金堆城钼矿和汝阳东沟钼矿，同时公司参股的安徽金寨县沙坪沟钼矿为世界第一大单体钼矿床。
-公司于2022年5月5日披露2022年非公开发行A股股票预案，拟定增募资19亿元，用于金堆城钼矿总体选矿升级改造项目、钼焙烧低浓度烟气制酸升级改造项目及补充流动资金。其中金堆城钼矿总体选矿升级改造项目总投资12.5亿元，项目通过新建3万吨/天选矿能力的葵花园选矿厂以及对现有选矿厂总体升级改造，实现设备大型化、高效化、管理精细化、智能化，致使整体选矿成本降低，生产效率提高。
-</t>
+          <t>油气|公司主要从事油气钻井专用工具及设备的研发、生产、销售及租赁，开展定向钻井、水平钻井的工程技术服务，业务涵盖石油、天然气、页岩气、煤层气、地热能钻井及定向穿越工程。公司是国内重要的螺杆钻具制造商之一，国内重要的井口装置制造商之一，产品已覆盖国内陆上及海上油气田。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>有色钼</t>
+          <t>油气</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>3.05</v>
+        <v>4.43</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>消息面上，节后钨原料价格持续飙升，钨粉已突破1800元/公斤。</t>
+          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sz002756</t>
+          <t>sh600583</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>永兴材料</t>
+          <t>海油工程</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>64.90000000000001</v>
+        <v>7.93</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>有色锂|公司拥有上游优质锂矿资源，控股子公司花桥矿业拥有的化山瓷石矿矿权面积1.8714平方公里，采矿证范围内累计查明陶瓷土矿资源储量49225.21万吨，其中，累计查明Li2O≥0.20%陶瓷土矿矿石量41000.80万吨，是公司锂云母和碳酸锂生产原材料的主要保障渠道。公司联营公司花锂矿业拥有白水洞高岭土矿矿权面积0.7614平方公里，累计查明控制的经济资源量矿石量730.74万吨。</t>
+          <t>油气|国内惟一一家集海洋石油、天然气开发工程设计、陆地制造和海上安装、调试、维修以及液化天然气工程于一体的大型工程总承包公司，是亚太地区最大的海洋石油工程EPCI（设计、采办、建造、安装）总承包商之一。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>有色锂</t>
+          <t>油气</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>3.05</v>
+        <v>4.43</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>消息面上，节后钨原料价格持续飙升，钨粉已突破1800元/公斤。</t>
+          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sz002155</t>
+          <t>sz002629</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>湖南黄金</t>
+          <t>仁智股份</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>37.7</v>
+        <v>7.37</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>有色锑|公司拥有规模化的生产线，拥有3万吨/年精锑冶炼生产线、3.2万吨/年多品种氧化锑生产线。截止2019年末，公司锑金属储量25.75万吨。</t>
+          <t>油气|公司系具有钻井液技术服务、井下作业技术服务、环保治理技术服务等多个油服产业的综合性油服公司。公司从事油田化学品与功能新材料的研发、生产与销售，产品广泛应用于石油天然气开发多个领域，已取得中石化、中石油市场准入资质。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>有色锑</t>
+          <t>油气</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>3.05</v>
+        <v>4.43</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>消息面上，节后钨原料价格持续飙升，钨粉已突破1800元/公斤。</t>
+          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sh600456</t>
+          <t>sz300157</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>宝钛股份</t>
+          <t>新锦动力</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>44.35</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>10</v>
+        <v>20.03</v>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>金属钛|钛行业国内领先，主要从事钛及钛合金的生产、加工和销售，是中国最大的钛及钛合金生产、科研基地，主导产品钛材年产量位居世界同类企业前列。公司主要产品为各种规格的钛及钛合金板、带、箔、管、棒、线、锻件、铸件等加工材和各种金属复合材产品，是美国波音、法国空客、法国斯奈克玛、美国古德里奇、加拿大庞巴迪、英国罗尔斯－罗伊斯等公司的战略合作伙伴。</t>
+          <t>油气+甲醇|1.公司主要从事油气资源的勘探开发技术服务，利用自主研发油气勘探开发软件和相关技术帮助石油公司寻找油气资源。公司拥有4大类、20套勘探开发软件产品。
+2.公司自主研发生产的"NEWICM"品牌离心式压缩机是国内外生产合成氨、尿素、烧碱、甲醇等化工产品的关键装备，在合成气压缩机组、CO2压缩机组、氯气压缩机组领域处于国际第一梯队。</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>金属钛</t>
+          <t>油气, 甲醇</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>1.41</v>
+        <v>4.43</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>消息面上，华为技术有限公司董事长梁华表示，目前已有43个业界主流大模型基于昇腾预训练，200多个开源模型适配昇腾生态，推动6000多个解决方案落地应用。</t>
+          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sz001896</t>
+          <t>sh601808</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>豫能控股</t>
+          <t>中海油服</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>13.34</v>
+        <v>18.56</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>7天7板</t>
-        </is>
-      </c>
+        <v>10.02</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>算力工程|2026年2月11日公告，公司正在筹划参股投资控股股东河南投资集团下属控股企业先天算力(河南)科技有限公司，并联合河南投资集团以先天算力为收购主体，收购郑州合盈数据有限责任公司控股权相关事项。郑州合盈数据主要从事第三方超大规模数据中心业务，下属数据中心主要分布于河北省张家口市怀来县、廊坊市，位于京津冀节点，定位服务首都及周边地区实时算力需求。</t>
+          <t>油气|公司是全球最具规模的油田服务供应商之一，拥有完整的服务链条和强大的海上石油服务装备群。</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>油气</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1.41</v>
+        <v>4.43</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>消息面上，华为技术有限公司董事长梁华表示，目前已有43个业界主流大模型基于昇腾预训练，200多个开源模型适配昇腾生态，推动6000多个解决方案落地应用。</t>
+          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sz002843</t>
+          <t>sz300084</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>泰嘉股份</t>
+          <t>海默科技</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>25.27</v>
+        <v>13.45</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5天3板</t>
-        </is>
-      </c>
+        <v>19.98</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>服务器电源|公司大功率电源业务包含部分数据中心电源业务，主要为客户代工服务器电源模块产品。</t>
+          <t>油气|公司是国际领先的油气田多相计量和生产优化解决方案提供商，国内最大的压裂泵液力端制造商、国内领先的油气增产工程专用仪器制造商、国内油气田环保技术引领者和首家投资海外非常规油气资源的民营上市公司。</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>服务器电源</t>
+          <t>油气</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>消息面上，华为技术有限公司董事长梁华表示，目前已有43个业界主流大模型基于昇腾预训练，200多个开源模型适配昇腾生态，推动6000多个解决方案落地应用。</t>
+          <t>银河证券表示，供需格局改善与行业盈利修复带动的“反内卷”概念，以及估值具备安全边际的红利资产，配置逻辑依然清晰，建议关注受益于价格上涨的有色金属板块。</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>sz002261</t>
+          <t>sh600301</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>拓维信息</t>
+          <t>华锡有色</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>36.52</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
+        <v>10.01</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>4天3板</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>华为算力|公司2020年先后在贵州、兰州与地方政府成立贵州云上鲲鹏科技有限公司与甘肃九霄鲲鹏科技有限责任公司发展鲲鹏计算机产业。</t>
+          <t>铟锡锑|公司是亚洲最大的锡多金属矿选矿基地、国内唯一的铟锡锑资源综合利用示范基地，拥有的多项关键战略性资源储量位居全球前列，主要金属矿产资源包括锡、锑、铟、锌、铅、银等，是国内主要的锡、锑金属生产企业之一。</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>华为算力</t>
+          <t>铟锡锑</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>消息面上，华为技术有限公司董事长梁华表示，目前已有43个业界主流大模型基于昇腾预训练，200多个开源模型适配昇腾生态，推动6000多个解决方案落地应用。</t>
+          <t>银河证券表示，供需格局改善与行业盈利修复带动的“反内卷”概念，以及估值具备安全边际的红利资产，配置逻辑依然清晰，建议关注受益于价格上涨的有色金属板块。</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>sh600126</t>
+          <t>sh600108</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>杭钢股份</t>
+          <t>亚盛集团</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>9.94</v>
+        <v>4.37</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>9.959999999999999</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr"/>
+        <v>10.08</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>算力租赁|公司与浙江天猫合作建设浙江云计算数据中心项目，由浙江天猫承租数据中心机柜资源。</t>
+          <t>钨矿|子公司甘肃亚盛鱼儿红矿业拟对鱼儿红牧场境内矿产资源进行开发，其中塔尔沟钨矿区拥有C+D 级三氧化钨22.42万吨(其中黑钨矿12.98万吨)，其中C级3773吨。</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>算力租赁</t>
+          <t>钨矿</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>消息面上，华为技术有限公司董事长梁华表示，目前已有43个业界主流大模型基于昇腾预训练，200多个开源模型适配昇腾生态，推动6000多个解决方案落地应用。</t>
+          <t>银河证券表示，供需格局改善与行业盈利修复带动的“反内卷”概念，以及估值具备安全边际的红利资产，配置逻辑依然清晰，建议关注受益于价格上涨的有色金属板块。</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>sz002015</t>
+          <t>sz002842</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>协鑫能科</t>
+          <t>翔鹭钨业</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>14.16</v>
+        <v>45.72</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
+        <v>10.01</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>算力|公司在上海、苏州投运两个智算中心，已投运超千P的算力资源。</t>
+          <t>钨|公司一直专注于钨制品的开发、生产与销售，主要产品包括各种规格的氧化钨、钨粉、碳化钨粉、钨合金粉及钨硬质合金等。公司是国内钨行业具备完整产业链的企业之一，从钨精矿采选、仲钨酸铵冶炼、氧化钨、钨粉、碳化钨粉、硬质合金及其工具等全系列钨产品的生产。公司是商务部批准的14家"钨品国营贸易出口资格企业"之一。</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>算力</t>
+          <t>钨</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>消息面上，华为技术有限公司董事长梁华表示，目前已有43个业界主流大模型基于昇腾预训练，200多个开源模型适配昇腾生态，推动6000多个解决方案落地应用。</t>
+          <t>银河证券表示，供需格局改善与行业盈利修复带动的“反内卷”概念，以及估值具备安全边际的红利资产，配置逻辑依然清晰，建议关注受益于价格上涨的有色金属板块。</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>sh600821</t>
+          <t>sh603257</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>金开新能</t>
+          <t>中国瑞林</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>7.39</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>9.969999999999999</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">算力租赁|2024年10月8日公告，公司全资子公司金开新能科技有限公司拟于新疆昌吉市投资建设国家超算广州中心新疆分中心昌吉智算中心项目，算力总规模达到5,000PFlops，项目采取分期报建方式推进，首批建设规模2,000PFlops，分两期建设完毕，每期1,000PFlops，首批项目投资预计为4.51亿元，项目建设期预计2个月，运营周期为6年，预计年营业收入1亿元。
-</t>
+          <t>铜钴+钨|1.在铜、钴资源开发上，公司在全球铜冶炼领域保持技术优势，承接设计了多个标志性项目，如非洲刚果（金）的卡莫阿铜冶炼厂和洛钼集团Tenke Fungurume铜钴矿项目。
+2.2025年10月15日公告，公司与江西省国有资本运营控股集团有限公司、江西江钨私募基金管理有限公司、农银金融资产投资有限公司、交银金融资产投资有限公司、江西钨业控股集团有限公司共同签署《合作意向书》。公司拟作为有限合伙人，参与设立江钨矿业基金。江钨矿业基金总规模暂定为20亿元，投资领域聚焦钨、稀土、钽铌、钼、锡等稀有金属项目。公司拟以自有资金出资3000万元。</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>算力租赁</t>
+          <t>铜钴, 钨</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>消息面上，华为技术有限公司董事长梁华表示，目前已有43个业界主流大模型基于昇腾预训练，200多个开源模型适配昇腾生态，推动6000多个解决方案落地应用。</t>
+          <t>银河证券表示，供需格局改善与行业盈利修复带动的“反内卷”概念，以及估值具备安全边际的红利资产，配置逻辑依然清晰，建议关注受益于价格上涨的有色金属板块。</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>sh603629</t>
+          <t>sz002155</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>利通电子</t>
+          <t>湖南黄金</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>58.52</v>
+        <v>41.47</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>算力租赁|公司目前对外出租AI算力规模已达10000P以上，其中，约4000P是以自有算力（报表中在固定资产科目列示）出租，其余是转租算力（在使用权资产科目列示）出租。</t>
+          <t>黄金+锑+钨|公司长期专注于黄金、锑和钨三种金属的矿山开采和深加工，拥有集矿山勘探、开采、选矿、冶炼、精炼、深加工及销售于一体的完整产业链，拥有100吨/年黄金生产线。</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>算力租赁</t>
+          <t>黄金, 锑, 钨</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>消息面上，华为技术有限公司董事长梁华表示，目前已有43个业界主流大模型基于昇腾预训练，200多个开源模型适配昇腾生态，推动6000多个解决方案落地应用。</t>
+          <t>银河证券表示，供需格局改善与行业盈利修复带动的“反内卷”概念，以及估值具备安全边际的红利资产，配置逻辑依然清晰，建议关注受益于价格上涨的有色金属板块。</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>sh688343</t>
+          <t>sh600259</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>云天励飞-U</t>
+          <t>中稀有色</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>110.26</v>
+        <v>112.29</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">算力芯片|公司自研芯片DeepEye1000已于2019年起实现独立商用，已与海康威视、阿里巴巴平头哥等建立了业务合作关系。DeepEye1000单芯片提供2Tops可编程运算能力，该芯片具有可编程、高效率、智升级等特点，应用DeepEye1000的厂商不仅能够直接应用云天励飞自研的上百种计算机视觉算法，也能够通过公司的开放的工具链，搭载自研或第三方厂商的算法。
-</t>
+          <t>稀土+钨|广东省稀土龙头，在粤北地区控股及参股5个钨矿山。</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>算力芯片</t>
+          <t>稀土, 钨</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>0.61</v>
+        <v>1.2</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>消息面上，美国将磷元素及草甘膦除草剂提升至国家安全优先事项，指出这两种物资的短缺将对国家安全构成直接威胁。</t>
+          <t>银河证券表示，供需格局改善与行业盈利修复带动的“反内卷”概念，以及估值具备安全边际的红利资产，配置逻辑依然清晰，建议关注受益于价格上涨的有色金属板块。</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>sz002470</t>
+          <t>sz000960</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>金正大</t>
+          <t>锡业股份</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>3.1</v>
+        <v>48.8</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>9.93</v>
+        <v>10.01</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7天5板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>化肥|公司的复合肥、缓控释肥、硝基复合肥、水溶肥及其他新型肥料在技术和市场占有率方面居国内领先地位，具有较强的竞争优势。公司复合肥产销量连续八年居国内第一位；是缓控释肥行业标准和国家标准的起草单位，拥有全球最大的缓控释生产基地，缓控释肥的产销量连续十年居行业第一位，市场份额超过50%。作为复合肥的领军企业，公司一直保持持续、快速发展。公司先后在山东临沭、山东菏泽、安徽长丰、河南郸城、河南驻马店、辽宁铁岭、贵州瓮安、云南晋宁、山东德州、广东英德、新疆阿克苏、湖北潜江、新疆阜康等地建有生产基地，具有年产各类新型肥料720万吨的生产能力。公司的产品覆盖普通复合肥、缓控释肥、硝基复合肥、水溶性肥、生物菌肥、有机肥、有机-无机复混肥料、植物生长调理剂、土壤调理剂等，覆盖12大类100多种产品，在我国肥料企业中，肥料品种最为丰富。公司坚持以市场为导向，采取“以销定产”生产模式，生产部门严格按照公司销售计划制定生产计划，并根据销售情况，对生产计划及时进行调整。在销售模式上，以“金正大”、“沃夫特”、“金大地”等实行多品牌进行覆盖。目前公司拥有传统渠道一级代理商5000余家，二级代理商10万余家，营销渠道遍</t>
+          <t>锡铟|公司作为全球锡铟行业的龙头企业，拥有着国际先进水平的采、选、冶及深加工成套技术，及全行业最完整的产业链，主要产品为锡锭、阴极铜、锌锭、铟锭、锡材和锡化工产品等1000多个规格品种，现有锡冶炼产能8万吨/年，锡材产能4.1万吨/年、锡化工产能2.4万吨/年、阴极铜产能12.5万吨/年、锌冶炼产能10万吨/年、铟冶炼产能60吨/年。</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>化肥</t>
+          <t>锡铟</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>0.61</v>
+        <v>1.2</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>消息面上，美国将磷元素及草甘膦除草剂提升至国家安全优先事项，指出这两种物资的短缺将对国家安全构成直接威胁。</t>
+          <t>银河证券表示，供需格局改善与行业盈利修复带动的“反内卷”概念，以及估值具备安全边际的红利资产，配置逻辑依然清晰，建议关注受益于价格上涨的有色金属板块。</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>sh600230</t>
+          <t>sz002667</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>沧州大化</t>
+          <t>威领股份</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>24.76</v>
+        <v>23.35</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>3天2板</t>
-        </is>
-      </c>
+        <v>9.99</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>化工|公司是我国首家规模生产TDI的公司，拥有年产15万吨TDI、10万吨PC、及配套的16万吨烧碱、造气原料气、20万吨双酚A等相关产品链相衔接、上下游原料相配套的生产规模。</t>
+          <t>锂矿+有色|1.公司主要以新能源锂电材料产业链为主体，包括锂矿选矿、基础性锂电原料锂盐加工及冶炼业务，主要产品包括锂化合物及衍生品、锂精矿及伴生品和振动筛及PC生产线等。旗下领辉科技具备锂云母年选矿产能120万吨。
+2.2025年5月20日公告，控股孙公司天津长领矿业以2.2亿元成功竞得湖南临武嘉宇矿业74.3%股权。嘉宇矿业拥有锡矿石247万吨、铅矿石119万吨、锌矿石117万吨，年开采规模30万吨，可迅速形成稳定的采选产能。</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>锂矿, 有色</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>0.61</v>
+        <v>1.2</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>消息面上，美国将磷元素及草甘膦除草剂提升至国家安全优先事项，指出这两种物资的短缺将对国家安全构成直接威胁。</t>
+          <t>银河证券表示，供需格局改善与行业盈利修复带动的“反内卷”概念，以及估值具备安全边际的红利资产，配置逻辑依然清晰，建议关注受益于价格上涨的有色金属板块。</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>sh600725</t>
+          <t>sh601069</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>云维股份</t>
+          <t>西部黄金</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>5.39</v>
+        <v>39.89</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>煤化工|1.公司已经形成了较完整的煤化工细分行业产业链条，产业布局涵盖了传统煤化工的三个领域，即煤焦化、煤电石化和煤气化。
-2.2025年12月11日公告，公司拟通过发行股份及支付现金方式收购云南能投红河发电有限公司100%股权，重大资产重组事项持续推进中。红河发电系滇南地区主要的火力发电厂之一，核定装机容量1300MW。</t>
+          <t>黄金|公司长期专注于黄金矿山开采与冶炼，拥有集矿山勘探、开采、选矿、冶炼、精炼、销售于一体的完整产业链，拥有哈图金矿、伊犁公司所属阿希金矿和哈密金矿等主要黄金生产矿山。</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>煤化工</t>
+          <t>黄金</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0.61</v>
+        <v>1.2</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>消息面上，美国将磷元素及草甘膦除草剂提升至国家安全优先事项，指出这两种物资的短缺将对国家安全构成直接威胁。</t>
+          <t>银河证券表示，供需格局改善与行业盈利修复带动的“反内卷”概念，以及估值具备安全边际的红利资产，配置逻辑依然清晰，建议关注受益于价格上涨的有色金属板块。</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>sz002628</t>
+          <t>sz001337</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>成都路桥</t>
+          <t>四川黄金</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>5.27</v>
+        <v>55.74</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>10.02</v>
+        <v>10.01</v>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>化工|2024年8月1日公告，公司与内蒙古自治区赤峰市喀喇沁旗人民政府于近日拟签订战略合作意向协议，公司作为喀喇沁旗萤石矿资源整合主体，将充分发挥自身人才、资金、技术等资源优势，对喀喇沁旗范围内萤石矿产进行资源整合并打造氟化工产业集群项目。</t>
+          <t>黄金|公司是一家长期专注于金矿资源开发及综合利用的企业，主要从事金矿的采选及销售，产品为金精矿和合质金，已成为国内主要的金矿采选企业之一。公司拥有梭罗沟金矿采矿权和梭罗-挖金沟详查金矿探矿权，梭罗沟金矿矿区采矿许可证范围内保有资源储量为金金属量44862kg，梭罗沟金矿区挖金沟矿段查明资源储量为金金属量1332kg。</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>黄金</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0.61</v>
+        <v>1.2</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>消息面上，美国将磷元素及草甘膦除草剂提升至国家安全优先事项，指出这两种物资的短缺将对国家安全构成直接威胁。</t>
+          <t>银河证券表示，供需格局改善与行业盈利修复带动的“反内卷”概念，以及估值具备安全边际的红利资产，配置逻辑依然清晰，建议关注受益于价格上涨的有色金属板块。</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>sz000510</t>
+          <t>sz300139</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>新金路</t>
+          <t>晓程科技</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>20.41</v>
+        <v>79.78</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>10.03</v>
+        <v>20.01</v>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>化工|公司主要从事氯碱化工、电石、PVC软制品的生产经营及仓储、物流等经营、运输业务，其中，氯碱化工是公司核心业务，主要产品包括PVC树脂、烧碱、钾碱、电石等，其中电石作为主要生产原材料销售至公司主体企业树脂公司。公司目前氢氧化钾产能为5万吨/年（2021年3月）。</t>
+          <t>黄金|公司的黄金开采及销售业务已形成黄金勘探、采矿、选冶、冶炼、销售于一体的完整产业链条。截至2023年6月30日，公司拥有三座金矿，分别为AKROMA金矿、AKOASE金矿和FGM（NAFORMAN_NOYEM）金矿，已探明的黄金储量分别为5.8吨、16.8吨和32.2吨，合计54.8吨。</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>黄金</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>0.61</v>
+        <v>1.2</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>消息面上，美国将磷元素及草甘膦除草剂提升至国家安全优先事项，指出这两种物资的短缺将对国家安全构成直接威胁。</t>
+          <t>银河证券表示，供需格局改善与行业盈利修复带动的“反内卷”概念，以及估值具备安全边际的红利资产，配置逻辑依然清晰，建议关注受益于价格上涨的有色金属板块。</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>sz000731</t>
+          <t>sz000506</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>四川美丰</t>
+          <t>招金黄金</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>7.89</v>
+        <v>22.33</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>10.04</v>
+        <v>10</v>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>化工|作为中国百万吨级大型化工生产企业之一，公司现拥有尿素、复合肥、三聚氰胺、硝酸、硝铵、塑编制品、重载膜包装、柴油车尾气处理液、液体二氧化碳和LNG等化工产品300余万吨生产规模，涉及农业、环保、能源三大领域。公司“美丰及图”商标被依法认定为“中国驰名商标”，荣获“全国五一劳动奖状”、“中国十大诚信企业”、“全国质量管理先进企业”、“中国企业文化建设先进单位”、“中国最佳董事会50强”、“上市公司信息披露优秀企业”、“银行AAA级信誉企业”、“农资经销商最佳合作厂家”等荣誉称号。</t>
+          <t>黄金|公司主要业务包括以黄金为主要品种的矿业开采，子公司斐济瓦图科拉金矿有限公司所拥有的斐济瓦图科拉金矿已有90年的开采历史，已采出黄金240多吨，是全球少有的长寿大型矿山，地质勘探潜力较大。</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>黄金</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>0.61</v>
+        <v>1.2</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>消息面上，美国将磷元素及草甘膦除草剂提升至国家安全优先事项，指出这两种物资的短缺将对国家安全构成直接威胁。</t>
+          <t>银河证券表示，供需格局改善与行业盈利修复带动的“反内卷”概念，以及估值具备安全边际的红利资产，配置逻辑依然清晰，建议关注受益于价格上涨的有色金属板块。</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>sh603217</t>
+          <t>sh600988</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>元利科技</t>
+          <t>赤峰黄金</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>28.33</v>
+        <v>43.91</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>10.02</v>
+        <v>9.99</v>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>化工+光伏|1.公司在2022年年报中披露，公司完成了太阳能电池所需原料金属银粉项目关键性技术的开发。
-2.公司主要从事二元酸二甲酯系列（混合二元酸二甲酯、丁二酸二甲酯、戊二酸二甲酯、己二酸二甲酯等）、脂肪醇系列（1,6-己二醇、1,5-戊二醇）等</t>
+          <t>黄金|公司的主营业务为黄金的采选及销售业务，主要通过下属子公司开展，公司拥有并经营7个黄金及多金属矿山，分布于中国、东南亚和西非等世界各地。子公司吉隆矿业、五龙矿业、华泰矿业及锦泰矿业从事黄金采选业务；子公司瀚丰矿业从事锌、铅、铜、钼采选业务；位于老挝的控股子公司万象矿业目前主要从事金、铜矿开采和冶炼；位于加纳的控股子公司金星瓦萨主要从事黄金采选业务。</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>化工, 光伏</t>
+          <t>黄金</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>石油</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>0.61</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>消息面上，美国将磷元素及草甘膦除草剂提升至国家安全优先事项，指出这两种物资的短缺将对国家安全构成直接威胁。</t>
+          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>sz002734</t>
+          <t>sh603353</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>利民股份</t>
+          <t>和顺石油</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>22.48</v>
+        <v>46.34</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
+        <v>9.99</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>化工|公司是国家定点农药制造骨干企业、中国农药工业50强企业和国家高新技术企业，主要从事农药原药、制剂的研发、生产和销售。产品包括杀菌剂、杀虫剂和除草剂三大系列共12种原药、66种制剂以及部分化工中间体，公司控股子公司河北双吉产品共有5种原药和36种制剂。杀菌剂产品主要包括代森类、霜脲氰、三乙膦酸铝、嘧霉胺、威百亩等原药及制剂，杀虫剂产品包括噻虫啉及其他复配制剂，除草剂包括硝磺草酮等原药及制剂。公司主要产品均为“高效、低毒、低残留”的农药产品。公司注重国内外市场开发，市场覆盖80多个国家和地区，位列中国农药出口额30强。公司原药和大包装制剂产品主要销售到大型跨国公司和贸易代理商，公司小包装制剂产品主要通过经销商实现销售，对于大农场和种植基地采用直销模式。</t>
+          <t>石油+半导体|1.公司是湖南省第一家获国家商务部批准取得成品油批发资质的民营石油企业，主营成品油批发零售，业务涵盖成品油采购、仓储、物流、批发、零售环节，在成品油流通领域形成完整产业链。
+2.2025年11月16日晚公告，公司拟以现金收购及增资方式取得上海奎芯集成电路设计有限公司不低于34%股权并通过表决权委托合计控制其51%表决权，交易完成后奎芯科技将纳入合并报表，布局高速接口IP及Chiplet解决方案。</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>石油, 半导体</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>石油</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>1.28</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">消息面上，华为云码道（CodeArts）代码智能体公测版2月26日发布，覆盖代码生成等AI编程技术。
-</t>
+          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sh605398</t>
+          <t>sz000554</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>新炬网络</t>
+          <t>泰山石油</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>33.41</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>10.01</v>
+        <v>10.04</v>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>低代码平台|公司自主研发的低代码开发平台可开放企业现有数字化运维/运营基础能力，实现敏捷业务创新，并面向运维、运营人员提供个性场景快速构建能力。</t>
+          <t>成品油经营|中石化旗下上市公司，主要从事成品油批发零售，车用天然气加气业务以及非油品业务。公司是山东省泰安市成油品、车用天然气的最大经销商。</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>低代码平台</t>
+          <t>成品油经营</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>石油</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>1.28</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">消息面上，华为云码道（CodeArts）代码智能体公测版2月26日发布，覆盖代码生成等AI编程技术。
-</t>
+          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sh688118</t>
+          <t>sh600938</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>普元信息</t>
+          <t>中国海油</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>35.5</v>
+        <v>39.46</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>20.01</v>
+        <v>10.01</v>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>低代码|公司新一代低代码平台结合人工智能技术，提供了丰富的编程助手，用于应用模板构建、代码片段生成、实时语法检查、实体智能推荐等场景。</t>
+          <t>油气|公司为中国最大之海上原油及天然气生产商，亦为全球最大之独立油气勘探及生产企业之一，主要业务为勘探、开发、生产及销售原油和天然气。</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>低代码</t>
+          <t>油气</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>石油</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>1.28</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">消息面上，华为云码道（CodeArts）代码智能体公测版2月26日发布，覆盖代码生成等AI编程技术。
-</t>
+          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sz300830</t>
+          <t>sh600688</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>金现代</t>
+          <t>上海石化</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>14.88</v>
+        <v>3.49</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>20</v>
+        <v>10.09</v>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>AI编程|公司发展以“AI低代码”开发平台为代表的标准化、通用软件产品业务。在轻骑兵低代码开发平台中，通过使用智谱华章ChatGLM4基础大模型并训练软件开发领域的垂直行业大模型，结合自然语言处理（NLP）技术，为平台开发推荐所需要的功能模块、数据模型、片段代码、页面布局。</t>
+          <t>石油化工|中国最大的炼油化工一体化综合性石油化工企业之一，具有较强的整体规模实力，是中国重要的成品油、中间石化产品、合成树脂和合成纤维生产企业。</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>AI编程</t>
+          <t>石油化工</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>石油</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>1.28</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">消息面上，华为云码道（CodeArts）代码智能体公测版2月26日发布，覆盖代码生成等AI编程技术。
-</t>
+          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>sz002980</t>
+          <t>sz000096</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>华盛昌</t>
+          <t>广聚能源</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>28.97</v>
+        <v>12.06</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>9.98</v>
+        <v>10.04</v>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>AI应用|公司最新发布的AI-7760电能质量分析仪是基于该大模型创新性集成多个AI智能体，深度整合了行业知识图谱，涵盖产品手册、行业标准文档、学术论文、期刊文献以及丰富的行业问答数据等多维度信息，可结合RAG检索增强技术为行业用户提供专业的场景化的解答，该仪器可实时监测设备状态、深度理解用户指令、生成诊断分析报告、智能决策、自动高效执行。</t>
+          <t>成品油经营|深圳市唯一的大型液体化工品仓储企业，公司具有成品油、液化石油气、危险化学品特许经营资质。</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>成品油经营</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>石油</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>1.28</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">消息面上，华为云码道（CodeArts）代码智能体公测版2月26日发布，覆盖代码生成等AI编程技术。
-</t>
+          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>sz002973</t>
+          <t>sh600256</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>侨银股份</t>
+          <t>广汇能源</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>15.59</v>
+        <v>6.47</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>10.02</v>
+        <v>10.03</v>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI应用+机器人|2024年1月30日公告，公司的全资子公司侨银数智及控股孙公司西部数智与东北大学机器人科学与工程学院、合肥市智能机器人研究院、国研新经济咨询（北京）有限公司、睿戈智能科技（沈阳）有限公司分别签署了关于人工智能相关的战略协议。根据相关合作协议，合作各方将以“人工智能”为主要合作方向，坚持产业协同与科技协作，在智能网联、无人驾驶、智能服务机器人的技术攻克、行业标准体系建立、产业生态打造等领域开展深度合作，共建数智城市研究体系和产业体系，共同打造“AI全维度全场景赋能城市综合管理服务”的新模式。
-</t>
+          <t>油气+煤炭|公司已形成以煤炭、LNG、醇醚、煤焦油、石油为核心产品，以能源物流为支撑的天然气液化、煤炭开采、煤化工转换、油气勘探开发四大业务板块，是国内唯一一家同时拥有煤、气、油三种资源的民营企业。</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>AI应用, 机器人</t>
+          <t>油气, 煤炭</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>光伏</t>
+          <t>石油</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>1.26</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>消息面上，广发证券表示，AI巨头群雄逐鹿，“算力上天”已成共识。“算力上天”的共识推动下，太空光伏作为主要供能形式有望深度受益。预计未来有望累计为光伏设备累计带来千亿级市场空间。</t>
+          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>sh603381</t>
+          <t>sh601857</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>永臻股份</t>
+          <t>中国石油</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>29.5</v>
+        <v>11.95</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>9.99</v>
+        <v>10.04</v>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>光伏|公司主要从事绿色能源结构材料的研发、生产、销售及应用，已成为国内领先的铝合金光伏结构件制造商之一。公司主营产品包括光伏边框产品、光伏建筑一体化产品（BIPV）、光伏支架结构件。目前公司拥有江苏常州、辽宁营口、安徽滁州、安徽芜湖四大生产基地，总占地规模近1250亩，可年产24万吨光伏边框，拥有近9000万套光伏边框的产能。2023年公司光伏边框市场占有率约为10.73%。公司主要BIPV产品包括：光伏幕墙、光伏百叶窗、BIPV别墅屋顶解决方案。公司生产的光伏边框已进入天合光能、晶澳科技、隆基绿能、阿特斯、晶科能源、通威股份等头部组件制造商的供应链体系并建立了长期稳定的合作关系。</t>
+          <t>油气|集团是我国油气行业占主导地位的最大的油气生产和销售商，世界最大的石油公司之一。</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>光伏</t>
+          <t>油气</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>光伏</t>
+          <t>军工</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>1.26</v>
+        <v>0.27</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>消息面上，广发证券表示，AI巨头群雄逐鹿，“算力上天”已成共识。“算力上天”的共识推动下，太空光伏作为主要供能形式有望深度受益。预计未来有望累计为光伏设备累计带来千亿级市场空间。</t>
+          <t>华泰证券发布航天军工板块2026年度展望研报称，复盘“十四五”，军工体量迈上新台阶；展望“十五五”，或将由“量”的增值转向“质”的提升。</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>sz002865</t>
+          <t>sz301302</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>钧达股份</t>
+          <t>华如科技</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>92.94</v>
+        <v>29.72</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>10</v>
+        <v>19.98</v>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>太空光伏|公司深耕光伏赛道多年，提前启动钙钛矿叠层电池研发，目前小面积钙钛矿-TOPCon叠层电池转换效率已突破33.53%；尚翼光电依托中科院上海光机所技术背景，是国内稀缺的卫星电池生产商，其核心团队深耕钙钛矿航天应用多年，建有独有的太空仿真研发平台，目前已完成太空环境下钙钛矿材料的第一性原理验证。公司与尚翼光电正在根据下游客户需求，积极推动产品量产，加强产品服务能力，开拓布局国内及北美商业航天及太空算力市场，致力于以技术及成本优势服务全球商业航天及太空算力客户，致力成为全球太空光伏引领者。</t>
+          <t>军工信息化|公司以建模仿真为主业，致力于军用仿真、虚拟现实和数据应用技术研发与产品推广，为政府、军队、教育和科研部门，以及国防工业、交通物流、应急安全、能源化工等行业企业提供优质的仿真产品和技术服务。</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>太空光伏</t>
+          <t>军工信息化</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>光伏</t>
+          <t>军工</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>1.26</v>
+        <v>0.27</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>消息面上，广发证券表示，AI巨头群雄逐鹿，“算力上天”已成共识。“算力上天”的共识推动下，太空光伏作为主要供能形式有望深度受益。预计未来有望累计为光伏设备累计带来千亿级市场空间。</t>
+          <t>华泰证券发布航天军工板块2026年度展望研报称，复盘“十四五”，军工体量迈上新台阶；展望“十五五”，或将由“量”的增值转向“质”的提升。</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>sz002394</t>
+          <t>sh603488</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>联发股份</t>
+          <t>展鹏科技</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>15.66</v>
+        <v>10.91</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>9.969999999999999</v>
+        <v>9.98</v>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>光伏|子公司环保新能源的主营业务是供应电力、蒸汽、压缩空气，其中产生电力的方式分为火力发电和分布式光伏发电，电力是自发自用。</t>
+          <t>军工信息化|公司于2023年11月18日公告，拟以6.47元/股的价格发行股份及支付现金购买领为军融100%股权并以6.87元/股的价格发行股份募集配套资金，本次交易预计构成重大资产重组。标的公司主营军事航空仿真系列产品的研制、生产和技术服务，核心产品为面向航空兵作战训练的便携式“通用数字空战仿真系统”。</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>光伏</t>
+          <t>军工信息化</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>光伏</t>
+          <t>军工</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>1.26</v>
+        <v>0.27</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>消息面上，广发证券表示，AI巨头群雄逐鹿，“算力上天”已成共识。“算力上天”的共识推动下，太空光伏作为主要供能形式有望深度受益。预计未来有望累计为光伏设备累计带来千亿级市场空间。</t>
+          <t>华泰证券发布航天军工板块2026年度展望研报称，复盘“十四五”，军工体量迈上新台阶；展望“十五五”，或将由“量”的增值转向“质”的提升。</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>sz300317</t>
+          <t>sz002413</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>珈伟新能</t>
+          <t>雷科防务</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>5.36</v>
+        <v>16.36</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>19.91</v>
+        <v>10.02</v>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">光伏|子公司华源新能源是国内领先的光伏发电企业之一，从事光伏电站EPC业务和光伏电站投资运营业务。
-</t>
+          <t>军工|公司主要业务包括雷达系统业务群、智能弹药业务群、卫星应用业务群、安全存储业务群、智能网联业务群的相关产品研发、制造和销售。公司致力于相控阵雷达、合成孔径雷达和毫米波雷达等技术方面的研究，主要应用于国防军工和国民经济各个领域。</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>光伏</t>
+          <t>军工</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>光伏</t>
+          <t>军工</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>1.26</v>
+        <v>0.27</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>消息面上，广发证券表示，AI巨头群雄逐鹿，“算力上天”已成共识。“算力上天”的共识推动下，太空光伏作为主要供能形式有望深度受益。预计未来有望累计为光伏设备累计带来千亿级市场空间。</t>
+          <t>华泰证券发布航天军工板块2026年度展望研报称，复盘“十四五”，军工体量迈上新台阶；展望“十五五”，或将由“量”的增值转向“质”的提升。</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>sh603578</t>
+          <t>sz301213</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>三星新材</t>
+          <t>观想科技</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>15.98</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>9.98</v>
+        <v>20.01</v>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>光伏玻璃|公司以国华金泰为经营主体，向光伏玻璃等新能源应用领域拓展，既可生产常规硅晶电池的盖板玻璃，也可生产薄钢化光伏玻璃。</t>
+          <t>军工信息化|公司为客户提供装备全寿命周期管理系统、智能武器装备管控模块等相关产品及服务。公司产品和服务广泛应用于陆军、海军、空军、火箭军等国防信息化领域。</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>光伏玻璃</t>
+          <t>军工信息化</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>军工</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>2.9</v>
+        <v>0.27</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>消息面上，近日国家能源局公布新型电力系统建设能力提升试点名单（第一批）。</t>
+          <t>华泰证券发布航天军工板块2026年度展望研报称，复盘“十四五”，军工体量迈上新台阶；展望“十五五”，或将由“量”的增值转向“质”的提升。</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>sz000899</t>
+          <t>sz003009</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>赣能股份</t>
+          <t>中天火箭</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>14.61</v>
+        <v>75.13</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>电力|公司主营业务为火力、水力发电，目前公司所属已投产运营火电厂一家、水电厂两家，总装机容量为150万千瓦。公司所属火电厂丰城二期发电厂装机容量2×70万千瓦，位于江西省丰城市，两家水电厂居龙潭水电厂、抱子石水电厂装机容量分别为2×3万千瓦和2×2万千瓦，分别位于江西省赣州市和九江市修水县。公司尚有丰城三期发电厂项目，设计装机容量为2×100万千瓦超超临界发电机组；另外，公司受托管理控股股东江投集团下辖江西东津发电有限责任公司，装机容量为2×3万千瓦。</t>
+          <t>军工+商业航天|公司是国内少数掌握固体火箭发动机复合材料核心技术的主要企业之一，研制的固体火箭发动机耐烧蚀组件先后为国内多个型号的固体火箭产品成功配套，商业航天业务主要集中在军用耐烧蚀组件产品板块。</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>军工, 商业航天</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>军工</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>2.9</v>
+        <v>0.27</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>消息面上，近日国家能源局公布新型电力系统建设能力提升试点名单（第一批）。</t>
+          <t>华泰证券发布航天军工板块2026年度展望研报称，复盘“十四五”，军工体量迈上新台阶；展望“十五五”，或将由“量”的增值转向“质”的提升。</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>sh600744</t>
+          <t>sz002389</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>华银电力</t>
+          <t>航天彩虹</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>7.94</v>
+        <v>26.54</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>9.969999999999999</v>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.99</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>电力|作为湖南省火电装机主要发电企业，公司主要从事火力发电业务，同时经营水电、风电、太阳能业务以及电力销售业务。</t>
+          <t>无人机|中国航天科技集团旗下上市公司，是我国首家以无人机为主营业务的上市公司，产品在原有新材料产品的基础上，增加彩虹-3、彩虹-4和彩虹-5等中大型察打一体无人机产品以及射手系列导弹，形成多元化的产品结构。</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>无人机</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>军工</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>2.9</v>
+        <v>0.27</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>消息面上，近日国家能源局公布新型电力系统建设能力提升试点名单（第一批）。</t>
+          <t>华泰证券发布航天军工板块2026年度展望研报称，复盘“十四五”，军工体量迈上新台阶；展望“十五五”，或将由“量”的增值转向“质”的提升。</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>sz000993</t>
+          <t>sh600435</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>北方导航</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>14.43</v>
+        <v>18.87</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>9.98</v>
+        <v>10.03</v>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>电力|公司致力于清洁能源、新能源等领域的发展。发电业务是公司业务的核心业务，主要包括水力发电和风力发电。是电力产业链的发电环节，相对电网企业，处于弱势地位，由于水电、风电生产均属清洁能源，电调顺序靠前，与火电相比，来自电网的竞争压力相对较小。公司目前是宁德市唯一以经营清洁能源发电为主营业务的国有控股上市公司。</t>
+          <t>军工|中国兵器工业集团旗下上市公司，军民两用产品业务以“导航控制和弹药信息化技术”为主，涵盖制导控制、导航控制、探测控制、环境控制、稳定控制、电台及卫星通信、电连接器等产品和技术。公司是以军品二三四级配套为主的制造型企业，军品以导航控制、弹药信息化系统、短波电台和卫星通信系统、军用电连接器等领域的整机、核心部件为主要产品。</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>军工</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>甲醇</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>2.9</v>
+        <v>3.97</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>消息面上，近日国家能源局公布新型电力系统建设能力提升试点名单（第一批）。</t>
+          <t>美伊冲突对全球化工行业形成重大影响，伊朗是全球重要的化肥生产国和出口国，甲醇供应占全球10%，尿素出口量位居世界前列。</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>sh600452</t>
+          <t>sz000035</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>涪陵电力</t>
+          <t>中国天楹</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>13.28</v>
+        <v>7.71</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
+        <v>9.99</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>电力|公司主营业务为电力供应业务、配电网节能业务。公司作为一家从事输、配、售电业务一体化经营的电力企业，公司在现有的供电区域内拥有完善的供电网网络，能够为供电辖区提供优质、可靠的供电服务，保证了对辖区电力供应的市场优势，具有较强的竞争优势。</t>
+          <t>绿色甲醇|公司依托吉林辽源和黑龙江安达等风光储氢氨醇一体化项目投资建设，打造涵盖绿色甲醇、绿氨、SAF 等多元化氢基能源产品生产线，形成规模化的绿色燃料供应能力。
+2026年2月26日公司在投资者关系活动记录表中透露，公司目前已与国际头部能源巨头签订了全球首单电制甲醇供货订单，标志着公司绿色甲醇产品正式进入国际主流能源企业供应体系。</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>绿色甲醇</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>甲醇</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>0.5</v>
+        <v>3.97</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>消息面上，谷歌表示，Xcel Energy将为新的数据中心供电，谷歌将承担所有与电力服务相关的费用。谷歌称，新协议将把Form Energy提供的1400兆瓦风能、200兆瓦太阳能和300兆瓦电池储能系统并入Xcel的电网。</t>
+          <t>美伊冲突对全球化工行业形成重大影响，伊朗是全球重要的化肥生产国和出口国，甲醇供应占全球10%，尿素出口量位居世界前列。</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>sz002350</t>
+          <t>sh600227</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>北京科锐</t>
+          <t xml:space="preserve">赤天化  </t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>12.32</v>
+        <v>3.17</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>10</v>
+        <v>10.07</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>4天2板</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>智能电网|公司是技术导向型配电设备制造企业，主营业务为12kV及以下配电及控制设备的研发、生产与销售。公司成立30年以来，专注于配电系统技术进步，崇尚技术创新，曾率先推出智能节电器、故障指示器、美式箱变、户外环网柜、永磁机构真空开关、GRC环保箱体和高过载变压器等新技术或产品，上述技术或产品都获得了广泛应用。目前，公司的产品基本涵盖了配电系统的一次设备，并形成了四大系列产品，如中低压开关系列产品（中置柜、柱上开关等）、配电变压器系列产品（美式箱变、欧式箱变、硅钢变压器以及非晶变压器等）、配电网自动化系列产品（环网柜、重合器、模块化变电站等）、配电设备元器件系列产品（GRC外壳、电缆附件等）；也涵盖了部分二次设备，如故障定位类系列产品（故障指示器等）、电力电子系列产品（无功补偿、超级电容等）。公司产品大部分通过招投标方式供应给国家电网公司和南方电网公司，另外部分产品应用于铁路、冶金、石化、煤炭领域以及用户工程领域。随着电力体制改革的持续推进，公司在稳步耕耘配电设备产品的同时，利用多年来在配网市场建立的产品与渠道等资源优势，通过和电网以及地方政府的合作共享为主导，自主研发智慧能源管控与服务云平台和智</t>
+          <t>甲醇|煤制甲醇，全资子公司桐梓化工拥有甲醇产能30万吨/年。</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>甲醇</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>甲醇</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>0.5</v>
+        <v>3.97</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>消息面上，谷歌表示，Xcel Energy将为新的数据中心供电，谷歌将承担所有与电力服务相关的费用。谷歌称，新协议将把Form Energy提供的1400兆瓦风能、200兆瓦太阳能和300兆瓦电池储能系统并入Xcel的电网。</t>
+          <t>美伊冲突对全球化工行业形成重大影响，伊朗是全球重要的化肥生产国和出口国，甲醇供应占全球10%，尿素出口量位居世界前列。</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>sh603530</t>
+          <t>sh600722</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>神马电力</t>
+          <t>金牛化工</t>
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>60.17</v>
+        <v>10.32</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.02</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>智能电网|国际知名的电力系统复合外绝缘产品研制企业与国内电力设备用橡胶密封件龙头企业，从事电力系统变电站复合外绝缘、输配电线路复合外绝缘和橡胶密封件等产品的研发、生产与销售。</t>
+          <t>甲醇|公司的主要业务为甲醇的生产和销售，产品方式为焦炉气制甲醇。公司的主要业务由持股50%的控股子公司金牛旭阳经营，金牛旭阳拥有的甲醇生产能力为20万吨/年。</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>甲醇</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>甲醇</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>0.5</v>
+        <v>3.97</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>消息面上，谷歌表示，Xcel Energy将为新的数据中心供电，谷歌将承担所有与电力服务相关的费用。谷歌称，新协议将把Form Energy提供的1400兆瓦风能、200兆瓦太阳能和300兆瓦电池储能系统并入Xcel的电网。</t>
+          <t>美伊冲突对全球化工行业形成重大影响，伊朗是全球重要的化肥生产国和出口国，甲醇供应占全球10%，尿素出口量位居世界前列。</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>sz003035</t>
+          <t>sz002109</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>南网能源</t>
+          <t>兴化股份</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>8.220000000000001</v>
+        <v>4.84</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>10.04</v>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>智能电网|公司主要从事节能服务,为客户能源使用提供诊断、设计、改造、综合能源项目投资及运营维护等一站式综合节能服务。公司协同电网公司为智能电网提供区域清洁能源的规划、投资、建设、运营等相关服务。</t>
+          <t>甲醇|全资子公司兴化化工主营煤制甲醇，产能30万吨/年。</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>甲醇</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>甲醇</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>0.5</v>
+        <v>3.97</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>消息面上，谷歌表示，Xcel Energy将为新的数据中心供电，谷歌将承担所有与电力服务相关的费用。谷歌称，新协议将把Form Energy提供的1400兆瓦风能、200兆瓦太阳能和300兆瓦电池储能系统并入Xcel的电网。</t>
+          <t>美伊冲突对全球化工行业形成重大影响，伊朗是全球重要的化肥生产国和出口国，甲醇供应占全球10%，尿素出口量位居世界前列。</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>sz001216</t>
+          <t>sz000912</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>华瓷股份</t>
+          <t>泸天化</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>20.66</v>
+        <v>5.35</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>10.01</v>
+        <v>10.08</v>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">智能电网|子公司华联火炬的支柱绝缘子、穿墙套管等产品可用于柔性直流输电，有向国网、南网等客户供货。
-</t>
+          <t>甲醇|天然气制甲醇，子公司绿源醇从事甲醇业务，拥有甲醇产能70万吨/年。</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>甲醇</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>发电机概念</t>
+          <t>甲醇</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>1.23</v>
+        <v>3.97</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>消息面上，华泰证券研报称，海外整机厂商产能已普遍排满至2029年末，随产能释放有望实现新签订单确收的量利齐升。头部重燃扩产仍待2027年后释放，30%+的供需缺口下需求外溢趋势短期内仍将加强。</t>
+          <t>美伊冲突对全球化工行业形成重大影响，伊朗是全球重要的化肥生产国和出口国，甲醇供应占全球10%，尿素出口量位居世界前列。</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>sh603950</t>
+          <t>sh600989</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>长源东谷</t>
+          <t>宝丰能源</t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>44.51</v>
+        <v>26.32</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>6天3板</t>
-        </is>
-      </c>
+        <v>9.99</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>发电机|2025年1月10日公告，公司与玉柴集团子公司金创公司共同出资成立合资公司玉柴长源科技，玉柴长源科技将聚焦算力中心发动机缸体零部件、船电、汽车零部件等核心业务的制造加工与研发。</t>
+          <t>甲醇|公司于2019年10月8日公告，募投项目焦炭气化制60万吨/年烯烃产品段一次开车成功；焦炭气化制220万吨/年甲醇项目进度已达80%，预计于2019年底前投产。</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>发电机</t>
+          <t>甲醇</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>发电机概念</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>1.23</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>消息面上，华泰证券研报称，海外整机厂商产能已普遍排满至2029年末，随产能释放有望实现新签订单确收的量利齐升。头部重燃扩产仍待2027年后释放，30%+的供需缺口下需求外溢趋势短期内仍将加强。</t>
+          <t>LightCounting上调了对800G和1.6T光模块出货量的预测——2026年800G光模块出货量将增长一倍以上，1.6T光模块出货量则从2025年的小基数增长至数千万端口。</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>sz002633</t>
+          <t>sz002980</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>申科股份</t>
+          <t>华盛昌</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>19.35</v>
+        <v>31.87</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>10.01</v>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>燃气轮机|公司主导产品为厚壁滑动轴承，主要配套于汽轮机、燃气轮机、水轮机、发动机、电动机、鼓风机、水泵、压缩机、风机等各类旋转机械。</t>
+          <t>并购重组+光通信|华盛昌公告称，公司拟以现金方式收购深圳市伽蓝特科技有限公司100%股权，整体估值暂定为4.6亿元。伽蓝特专注于仪器仪表测试测量行业中的光通信模块和光芯片测试领域。</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>燃气轮机</t>
+          <t>并购重组, 光通信</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>发电机概念</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>1.23</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>消息面上，华泰证券研报称，海外整机厂商产能已普遍排满至2029年末，随产能释放有望实现新签订单确收的量利齐升。头部重燃扩产仍待2027年后释放，30%+的供需缺口下需求外溢趋势短期内仍将加强。</t>
+          <t>LightCounting上调了对800G和1.6T光模块出货量的预测——2026年800G光模块出货量将增长一倍以上，1.6T光模块出货量则从2025年的小基数增长至数千万端口。</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>sh603318</t>
+          <t>sh603738</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>水发燃气</t>
+          <t>泰晶科技</t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>8.02</v>
+        <v>23.96</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>10.01</v>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>燃气轮机|子公司大连派思设备作为燃气电厂配套企业，有燃气轮机相关配套业务，客户包括GE、西门子等行业领先企业。</t>
+          <t>光通信|公司针对光通信200G、400G、800G、1.6T市场推出了高基频、高精度、低相噪CMOS、LVDS差分输出时钟解决方案，随着光模块传输速率升级，对应使用超高频、差分时钟产品，在技术上提出更高性能匹配要求。</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>燃气轮机</t>
+          <t>光通信</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>0.98</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>消息面上，2026年1月，中国市场G.652.D单模光纤价格平均价格超40元/芯公里，创下近七年来新高，部分厂商报价达到50元/芯公里。</t>
+          <t>LightCounting上调了对800G和1.6T光模块出货量的预测——2026年800G光模块出货量将增长一倍以上，1.6T光模块出货量则从2025年的小基数增长至数千万端口。</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>sh600498</t>
+          <t>sz301338</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>烽火通信</t>
+          <t>凯格精机</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>51.55</v>
+        <v>179.65</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>10.01</v>
+        <v>20</v>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>光纤+商业航天|1.公司系光通信行业领先企业，产品围绕光通信全产业链布局，是我国最早从事光通信传输设备、光纤光缆科研、生产的企业，已跻身全球光传输与网络接入设备、光纤光缆最具竞争力企业10强。
-2.公司全面进军卫星光通信领域，低轨星载路由(天基IP网)与星间激光通信（天基传送网）已成为公司布局卫星互联网的关键突破口，成功研发面向低轨卫星平台的高集成度、低功耗星上路由交换系统。</t>
+          <t>PCB+光模块设备|1.公司的锡膏印刷设备、点胶设备及柔性自动化设备应用于电子工业制造领域的电子装联环节，一般用到PCB、FPC和电子元器件的地方均会涉及到电子装联，下游可应用于消费电子、汽车电子、网络通讯、航空航天、医疗器械、智能家居等行业的生产制造。
+2.2024年2月26日公司在互动平台表示，公司主要从事自动化精密装备的研发、生产、销售及技术支持服务，公司产品可以应用于光模块领域部分电子装联环节和封装环节。</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>光纤, 商业航天</t>
+          <t>PCB, 光模块设备</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>0.98</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>消息面上，2026年1月，中国市场G.652.D单模光纤价格平均价格超40元/芯公里，创下近七年来新高，部分厂商报价达到50元/芯公里。</t>
+          <t>LightCounting上调了对800G和1.6T光模块出货量的预测——2026年800G光模块出货量将增长一倍以上，1.6T光模块出货量则从2025年的小基数增长至数千万端口。</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>sh603618</t>
+          <t>sz001267</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>杭电股份</t>
+          <t>汇绿生态</t>
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>18.15</v>
+        <v>33.55</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>10</v>
@@ -3135,90 +3118,90 @@
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">光纤|公司光通信板块主要由富春江光电及其子公司从事经营，其主要从事光通信产业链中光纤预制棒、光纤、光缆、光通信相关设备等产品研发、生产、销售和服务。公司具备光通信“光棒—光纤—光缆”一体化产业链。
-</t>
+          <t>光通信|公司旗下钧恒科技是专业从事高端光通信产品的研制、生产及推广的高新技术企业，拥有从光学组件，光电转换模块，光端机及子系统的行业垂直整合能力，能够为客户提供各种特定应用的定制化产品，包括PLCC、Mini SFF、Micro Pod等各种形态及各种复合协议的光端机及波分复用子系统。</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>光纤</t>
+          <t>光通信</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>超硬材料</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>3.45</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>消息面上，Akash Systems宣布，全球首批搭载Diamond Cooling技术的英伟达GPU服务器正式交付给印度主权云服务商NxtGen AI Pvt Ltd。这批产品基于NVIDIA H200平台，是全球首次将“金刚石导热技术”应用于商用AI服务器体系，实现了材料层面的创新突破。</t>
+          <t>LightCounting上调了对800G和1.6T光模块出货量的预测——2026年800G光模块出货量将增长一倍以上，1.6T光模块出货量则从2025年的小基数增长至数千万端口。</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>sh688028</t>
+          <t>sh603011</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">沃尔德  </t>
+          <t>合锻智能</t>
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>114.13</v>
+        <v>28.28</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>金刚石散热|公司是国内领先的刀具综合解决方案商，为客户提供超硬、硬质合金刀具产品；金刚石功能材料业务定位于全球高端新材料市场，是少数能够全部掌握CVD金刚石生长技术的公司之一，主要产品包括金刚石膜声学器件、金刚石热沉材料、金刚石光学窗口、金刚石工具材料、硼掺杂金刚石膜涂层电极及制品、CVD培育钻石等。</t>
+          <t>核聚变+光通信|1.公司在聚变堆核心部件制造领域取得突破性进展，顺利启动BEST真空室制造工作，在成型、焊接及检测工艺取得阶段性成果。
+2.参股27.18%的合肥汇智提供400G及以下光模块的结构件给光通信厂商 。</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>金刚石散热</t>
+          <t>核聚变, 光通信</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>超硬材料</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>3.45</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>消息面上，Akash Systems宣布，全球首批搭载Diamond Cooling技术的英伟达GPU服务器正式交付给印度主权云服务商NxtGen AI Pvt Ltd。这批产品基于NVIDIA H200平台，是全球首次将“金刚石导热技术”应用于商用AI服务器体系，实现了材料层面的创新突破。</t>
+          <t>LightCounting上调了对800G和1.6T光模块出货量的预测——2026年800G光模块出货量将增长一倍以上，1.6T光模块出货量则从2025年的小基数增长至数千万端口。</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>sz002046</t>
+          <t>sh603083</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>国机精工</t>
+          <t>剑桥科技</t>
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>52.57</v>
+        <v>113.74</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>10</v>
@@ -3226,805 +3209,930 @@
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>金刚石材料|公司磨料磨具业务领域主要分为超硬材料磨具产品、复合超硬材料产品、金刚石功能化应用产品，在金刚石/金属复合材料制备及加工技术、MPCVD散热功能材料长晶及加工技术领域深耕多年，已构建起贯穿“设备研发-材料制备-精密加工”的全技术链产业能力。公司散热类产品矩阵涵盖金刚石/铜复合材料、CVD热沉片及GaN键合用金刚石材料等。</t>
+          <t>光模块|公司系全球高速光组件和光模块技术领先企业，2019年通过收购美国Lumentum公司旗下的Oclaro日本公司的部分资产及技术转移，加上在上海和美国培养发展的两个光电子研发中心，公司又进一步在高速光模块，特别是基于最新PAM4调制技术的400G和800G以及硅光技术的光模块、400G和800G LPO线性直驱光模块领域成为领先公司之一。</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>金刚石材料</t>
+          <t>光模块</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>AI眼镜</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>0.45</v>
+        <v>-0.9299999999999999</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>阿里千问将在2026年世界移动通信大会（MWC）上发布AI眼镜，并于3月2日开启线上线下全渠道预约。</t>
+          <t>美伊冲突对全球化工行业形成重大影响，伊朗是全球重要的化肥生产国和出口国，甲醇供应占全球10%，尿素出口量位居世界前列。</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>sz002655</t>
+          <t>sz000510</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>共达电声</t>
+          <t>新金路</t>
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>17.12</v>
+        <v>22.45</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="I60" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>AI眼镜|公司专注在声学领域的发展，公司产品可用于AI眼镜方向。</t>
+          <t>化工+有色|1.公司主要从事氯碱化工、电石、PVC软制品的生产经营及仓储、物流等经营、运输业务，其中，氯碱化工是公司核心业务，主要产品包括PVC树脂、烧碱、钾碱、电石等。
+2.旗下栗木矿业已取得了广西壮族自治区应急管理厅出具的《关于广西有色栗木矿业有限公司桂林矿产地质研究院栗木钽铌锡多金属矿（60万t/a采矿改建项目）安全设施设计审查意见书》，同意公司栗木钽铌锡多金属矿一期60万t/a采矿改建项目安全设施设计。</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>AI眼镜</t>
+          <t>化工, 有色</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="C61" s="2" t="inlineStr"/>
+        <v>-0.9299999999999999</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>美伊冲突对全球化工行业形成重大影响，伊朗是全球重要的化肥生产国和出口国，甲醇供应占全球10%，尿素出口量位居世界前列。</t>
+        </is>
+      </c>
       <c r="D61" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>sh603268</t>
+          <t>sh600714</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST松发 </t>
+          <t>金瑞矿业</t>
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>110.09</v>
+        <v>19.76</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>8天6板</t>
-        </is>
-      </c>
+        <v>10.02</v>
+      </c>
+      <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 拟收购恒力重工主营船舶及高端装备的研发、生产及销售，已确定排产新造船舶140艘，货值约108亿美元，船型包含散货船、VLCC、VLOC 和集装箱船等。</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr"/>
+          <t>锶盐|公司主营业务为锶盐系列产品的生产和销售。主要产品包括碳酸锶（含工业级碳酸锶、电子级碳酸锶）、金属锶、铝锶合金、硝酸锶、氢氧化锶和副产品硫磺、亚硫酸钠。</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>锶盐</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="C62" s="2" t="inlineStr"/>
+        <v>-0.9299999999999999</v>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>美伊冲突对全球化工行业形成重大影响，伊朗是全球重要的化肥生产国和出口国，甲醇供应占全球10%，尿素出口量位居世界前列。</t>
+        </is>
+      </c>
       <c r="D62" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>sh600753</t>
+          <t>sh600367</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST海钦 </t>
+          <t>红星发展</t>
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>10.46</v>
+        <v>23.55</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>4天4板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司目前的主营业务为煤炭（含焦炭）、天然气等大宗商品供应链管理业务。</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr"/>
+          <t>钡盐+锶盐|公司主要业务是钡盐、锶盐和锰系产品的研发、生产和销售。公司钡盐、锶盐生产能力在全国排名第一，碳酸钡和碳酸锶市场占有率分别达到40%和30%。</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>钡盐, 锶盐</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="C63" s="2" t="inlineStr"/>
+        <v>-0.9299999999999999</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>美伊冲突对全球化工行业形成重大影响，伊朗是全球重要的化肥生产国和出口国，甲醇供应占全球10%，尿素出口量位居世界前列。</t>
+        </is>
+      </c>
       <c r="D63" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>sh603580</t>
+          <t>sz000637</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST艾艾 </t>
+          <t>茂化实华</t>
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>17.19</v>
+        <v>5.42</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>9.94</v>
+      </c>
+      <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司是专业从事为轻型输送带的研发、生产及销售，境外营业收入大于50%。</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr"/>
+          <t>石油化工|公司属于石油化工行业，主要经营范围是石油化工产品的生产及销售，主要产品是液化石油气、聚丙烯、醋酸仲丁酯、MTBE、特种白油、乙醇胺、聚合级异丁烷、丙烷等。</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>石油化工</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="C64" s="2" t="inlineStr"/>
+        <v>-0.9299999999999999</v>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>美伊冲突对全球化工行业形成重大影响，伊朗是全球重要的化肥生产国和出口国，甲醇供应占全球10%，尿素出口量位居世界前列。</t>
+        </is>
+      </c>
       <c r="D64" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>sh600243</t>
+          <t>sz002545</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST海华 </t>
+          <t>东方铁塔</t>
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>3.78</v>
+        <v>29.96</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>9.99</v>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 青海华鼎与源鑫隆昌、茫崖源鑫签署增资协议，约定青海华鼎以现金增资5083.88万元取得茫崖源鑫51%的股权。上市公司称，茫崖源鑫所处的天然气行业具有良好的发展前景。</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr"/>
+          <t>化肥|四川省汇元达钾肥有限责任公司之全资子公司老挝开元矿业有限公司在老挝境内拥有141平方公里的钾盐矿开采权，其中已经开采中的老挝甘蒙省龙湖矿区西段41.69平方公里矿区保有资源储量矿石量119,902.75万吨，氯化钾资源储量21,763.10万吨，矿藏储量十分丰富。老挝开元目前的产能为年产50万吨氯化钾，为老挝境内现存产能最大的氯化钾生产企业，产品主要销往中国、印度和越南、泰国、马来西亚、新加坡等东南亚国家。</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>化肥</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>航运港口</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="C65" s="2" t="inlineStr"/>
+        <v>3.23</v>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>近期，油运市场火爆，VLCC日租金冲高，已突破20万美元/天，创近六年新高。</t>
+        </is>
+      </c>
       <c r="D65" s="2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>sz002047</t>
+          <t>sh601872</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>*ST宝鹰</t>
+          <t>招商轮船</t>
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>4.96</v>
+        <v>17.86</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>5.08</v>
+        <v>9.98</v>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>4天3板</t>
+          <t>7天4板</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 宝鹰股份公告，公司正在筹划重大资产出售事项，拟向控股股东大横琴集团出售所持有的宝鹰建设100%股权。本次交易构成关联交易，预计构成重大资产重组。</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr"/>
+          <t>油运|公司主要从事国际原油运输、国际干散货运输业务，并通过持股50%的CLNG公司（另一持股50%的股东为中远海能下属的大连中远海运油品运输有限公司）投资经营国际LNG运输业务。</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>油运</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>航运港口</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="C66" s="2" t="inlineStr"/>
+        <v>3.23</v>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>近期，油运市场火爆，VLCC日租金冲高，已突破20万美元/天，创近六年新高。</t>
+        </is>
+      </c>
       <c r="D66" s="2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>sh603021</t>
+          <t>sz002040</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST华鹏  </t>
+          <t>南 京 港</t>
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>7.12</v>
+        <v>11.97</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>5天3板</t>
-        </is>
-      </c>
+        <v>10.02</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司是国内日用玻璃行业的企业之一，主营业务为研发、生产和销售玻璃器皿产品和玻璃瓶罐。</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr"/>
+          <t>港口|中国内河最大的石油、液体化工产品中转港之一。本集团的主要经营业务为：提供原油、成品油、液体化工产品及普通货物的装卸、仓储服务。</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>港口</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>航运港口</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="C67" s="2" t="inlineStr"/>
+        <v>3.23</v>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>近期，油运市场火爆，VLCC日租金冲高，已突破20万美元/天，创近六年新高。</t>
+        </is>
+      </c>
       <c r="D67" s="2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>sh600525</t>
+          <t>sh601975</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST长园  </t>
+          <t>招商南油</t>
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>5.16</v>
+        <v>4.52</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>3天2板</t>
-        </is>
-      </c>
+        <v>9.98</v>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 子公司长园光波导技术（珠海）有限公司主要从事光学方案相关检测设备及制程设备的市场与技术布局。</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr"/>
+          <t>油运|公司是招商局集团旗下从事油轮运输的专业化公司，市场定位为全球石化产品的运输服务商。</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>油运</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>航运港口</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="C68" s="2" t="inlineStr"/>
+        <v>3.23</v>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>近期，油运市场火爆，VLCC日租金冲高，已突破20万美元/天，创近六年新高。</t>
+        </is>
+      </c>
       <c r="D68" s="2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>sh603559</t>
+          <t>sh600026</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST通脉  </t>
+          <t>中远海能</t>
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>7.52</v>
+        <v>22.64</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>5.029999999999999</v>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>10.01</v>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司是国内专业通信技术服务商，主营业务是为基础电信运营商和通信设备商提供涵盖核心网、传输网和接入网等全网络层次的通信网络工程建设和维护综合技术服务。</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr"/>
+          <t>油运|公司主营业务为从事国际和中国沿海原油及成品油运输、国际液化天然气(LNG)运输以及国际化学品运输，是中国沿海原油和成品油运输领域的龙头企业。</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>油运</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="C69" s="2" t="inlineStr"/>
+        <v>4.41</v>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>在美国和以色列袭击伊朗后，伊朗宣布关闭霍尔木兹海峡航道，多个油轮船东、交易商已暂停经这一海峡运输原油、燃料及液化天然气。</t>
+        </is>
+      </c>
       <c r="D69" s="2" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>sz002485</t>
+          <t>sh603318</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>ST雪发</t>
+          <t>水发燃气</t>
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>5.09</v>
+        <v>8.82</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="I69" s="2" t="inlineStr"/>
+        <v>9.98</v>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司文旅项目地处一线旅游目的地黄金地段，历史文化底蕴深厚，旅游资源丰富，市场潜力较大。</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr"/>
+          <t>天然气|公司是燃气输配和燃气应用领域（以天然气发电为主）的成套设备供应商，未来公司将实现从上游液化天然气生产，到中游燃气装备为主的高端制造，再到下游燃气应用领域的分布式能源和城镇燃气供应的全产业链，多维度发展。</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>天然气</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="C70" s="2" t="inlineStr"/>
+        <v>4.41</v>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>在美国和以色列袭击伊朗后，伊朗宣布关闭霍尔木兹海峡航道，多个油轮船东、交易商已暂停经这一海峡运输原油、燃料及液化天然气。</t>
+        </is>
+      </c>
       <c r="D70" s="2" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>sh600777</t>
+          <t>sz000968</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST新潮 </t>
+          <t>蓝焰控股</t>
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>4.45</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>4.95</v>
+        <v>10</v>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司在美国德克萨斯州拥有Hoople油田资产（常规油田）、Howard和Borden油田资产（页岩油藏）两处油田资产；公司主营业务为：石油及天然气的勘探、开采和销售。</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr"/>
+          <t>天然气|山西煤层气龙头，A股唯一煤层气标的，市占率第二，煤层气抽采量14.33亿方，销售量7亿方，运营近3400口煤层井。</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>天然气</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="C71" s="2" t="inlineStr"/>
+        <v>4.41</v>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>在美国和以色列袭击伊朗后，伊朗宣布关闭霍尔木兹海峡航道，多个油轮船东、交易商已暂停经这一海峡运输原油、燃料及液化天然气。</t>
+        </is>
+      </c>
       <c r="D71" s="2" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>sh603838</t>
+          <t>sh603393</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST四通 </t>
+          <t>新天然气</t>
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>8.07</v>
+        <v>37.48</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>4.94</v>
+        <v>10.01</v>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司是一家集研发、设计、生产、销售于一体的新型家居生活陶瓷供应商，产品覆盖日用陶瓷、卫生陶瓷、艺术陶瓷、建筑装饰等全系列家居生活用瓷。</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr"/>
+          <t>天然气|公司是新疆主要的城镇燃气经营企业，主要从事城市天然气的输配、销售、入户安装以及煤层气开采业务。公司取得了乌鲁木齐市高新区（新市区）、库车市、焉耆县、博湖县及和硕县等五个市（区、县）天然气市场的长期经营权。</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>天然气</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>光纤光缆</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="C72" s="2" t="inlineStr"/>
+        <v>0.9299999999999999</v>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>在AI算力需求驱动下，光纤行业正步入景气周期，市场出现明显涨价现象。以G.652.D单模光纤为例，其价格已从去年低点的18至19元/芯公里，上涨至目前最高约50元/芯公里。</t>
+        </is>
+      </c>
       <c r="D72" s="2" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>sz000697</t>
+          <t>sz000890</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>ST炼石</t>
+          <t>法尔胜</t>
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>9.57</v>
+        <v>8.43</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>5.050000000000001</v>
-      </c>
-      <c r="I72" s="2" t="inlineStr"/>
+        <v>10.05</v>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>6天5板</t>
+        </is>
+      </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST股 | 公司主要业务为航空制造业，构建“铼元素-高温合金-单晶叶片-航空零部件-航空发动机-大型无人机整机”完整的产业链。 </t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr"/>
+          <t>光纤光缆|公司参股的普天法尔胜光通信有限公司主要产品为光纤预制棒、光纤、光缆，上述产品可以应用于在运营商基础网络通信及广播电视通信领域。</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>光纤光缆</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>光纤光缆</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="C73" s="2" t="inlineStr"/>
+        <v>0.9299999999999999</v>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>在AI算力需求驱动下，光纤行业正步入景气周期，市场出现明显涨价现象。以G.652.D单模光纤为例，其价格已从去年低点的18至19元/芯公里，上涨至目前最高约50元/芯公里。</t>
+        </is>
+      </c>
       <c r="D73" s="2" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>sz000972</t>
+          <t>sh600498</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>*ST中基</t>
+          <t>烽火通信</t>
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>3.8</v>
+        <v>56.71</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="I73" s="2" t="inlineStr"/>
+        <v>10.01</v>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司依托新疆得天独厚的地域和自然优势，致力于发展番茄“红色产业”，产业规模居于前列，产品行销世界数十国家和地区，是全球主要食品企业长期、固定的原料供应商。</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr"/>
+          <t>光纤光缆+商业航天|1.公司系光通信行业领先企业，产品围绕光通信全产业链布局，是我国最早从事光通信传输设备、光纤光缆科研、生产的企业，已跻身全球光传输与网络接入设备、光纤光缆最具竞争力企业10强。
+2.公司全面进军卫星光通信领域，低轨星载路由(天基IP网)与星间激光通信（天基传送网）已成为公司布局卫星互联网的关键突破口，成功研发面向低轨卫星平台的高集成度、低功耗星上路由交换系统。</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>光纤光缆, 商业航天</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>光纤光缆</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="C74" s="2" t="inlineStr"/>
+        <v>0.9299999999999999</v>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>在AI算力需求驱动下，光纤行业正步入景气周期，市场出现明显涨价现象。以G.652.D单模光纤为例，其价格已从去年低点的18至19元/芯公里，上涨至目前最高约50元/芯公里。</t>
+        </is>
+      </c>
       <c r="D74" s="2" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>sz002650</t>
+          <t>sz000070</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>ST加加</t>
+          <t>特发信息</t>
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>6.6</v>
+        <v>19.66</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>4.93</v>
+        <v>10.02</v>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 主营业务涉及酱油、植物油、食醋、味精、鸡精、蚝油等的生产及销售。</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr"/>
+          <t>光纤光缆+算力租赁|1.公司拥有华南地区规模最大的光纤光缆研制、生产及检测基地，在海外市场方面，谷歌是其客户。
+2.公司除自营数据中心项目外，还曾承接鹏城云脑二期项目Atlas900 AI计算集群及通用计算与存储系统的建设集成项目、许昌市中原人工智能计算中心项目工程总承包项目以及国家超级计算深圳中心（深圳云计算中心）一楼机房建设设备购置项目等。</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>光纤光缆, 算力租赁</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>智能电网</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="C75" s="2" t="inlineStr"/>
+        <v>-1.34</v>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>国家电网宣布“十五五”期间将投运15项特高压直流工程，较“十四五”期间近乎翻倍。</t>
+        </is>
+      </c>
       <c r="D75" s="2" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>sz002581</t>
+          <t>sh603897</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>ST未名</t>
+          <t>长城科技</t>
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>8.4</v>
+        <v>33.7</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I75" s="2" t="inlineStr"/>
+        <v>9.99</v>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司全资子公司山东衍渡以自主创新建立的高表达重组蛋白平台为依托，构建了多个生物制品药物研发体系，涵盖眼科、儿科、神内科等等。</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr"/>
+          <t>电网设备|公司自成立以来专注于电磁线业务领域，是目前国内同类产品的主要制造商之一。</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>电网设备</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>智能电网</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="C76" s="2" t="inlineStr"/>
+        <v>-1.34</v>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>国家电网宣布“十五五”期间将投运15项特高压直流工程，较“十四五”期间近乎翻倍。</t>
+        </is>
+      </c>
       <c r="D76" s="2" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>sz002620</t>
+          <t>sz002380</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>ST瑞和</t>
+          <t>科远智慧</t>
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>7.07</v>
+        <v>35.74</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>5.050000000000001</v>
+        <v>10</v>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司主要从事政府机构、房地产开发商、大型企业、高档酒店、交通枢纽、园林绿化等综合性专业化装饰设计、工程施工业务以及光伏电站运营、光伏项目施工安装等。</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr"/>
+          <t>智能电网|公司控股子公司南京磐控微型电网技术有限公司从事微型电网工程规划、设计、调试、技术咨询、技术服务；微型电网专用设备研发、生产等业务。</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>智能电网</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr"/>
+          <t>智能电网</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>国家电网宣布“十五五”期间将投运15项特高压直流工程，较“十四五”期间近乎翻倍。</t>
+        </is>
+      </c>
       <c r="D77" s="2" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>sz001209</t>
+          <t>sh603861</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>洪兴股份</t>
+          <t>白云电器</t>
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>32.52</v>
+        <v>20.49</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>9.98</v>
+      </c>
+      <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>家居|公司主营家居服饰的研发、设计、生产及销售，主要产品包括家居服、内衣内裤及其他相关产品。公司旗下千线艺品牌是专业的儿童内衣品牌。</t>
+          <t>数据中心电源|公司长期为数据中心行业提供产品和服务,已经形成服务智能算力领域领先的电力能源解决方案能力,主要产品包括中低压开关柜、UPS 配电、变压器、母线槽、动力配电箱、精密列头柜等供配电系统设备,产品已经应用于中国联通粤港澳大湾区枢纽(韶关)数据中心、佛山开普勒数据中心、腾龙亦庄云计算数据中心、明蔚京西云计算数据中心等众多项目。</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>家居</t>
+          <t>数据中心电源</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr"/>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>国家能源局发布通知，决定将安徽省淮南市风光热储融合系统友好型新能源电站项目等43个项目、河北省张家口市等10个城市列为新型电力系统建设能力提升试点（第一批）。</t>
+        </is>
+      </c>
       <c r="D78" s="2" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>sz000593</t>
+          <t>sh600452</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>德龙汇能</t>
+          <t>涪陵电力</t>
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>15.74</v>
+        <v>14.61</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>9.99</v>
+        <v>10.02</v>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>3天2板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>股权转让|德龙汇能公告称，公司控股股东顶信瑞通与诺信芯材签订了《股份转让协议》，拟通过协议转让方式向诺信芯材转让公司股份1.06亿股，占公司总股本的29.64%。本次股份转让价格为9.41元/股，股份转让的交易价款合计为10亿元。若本次交易顺利推进并实施完成，公司控股股东及实际控制人将发生变更，公司控股股东将变更为诺信芯材，公司实际控制人将变更为孙维佳。</t>
+          <t>电力|公司主营业务为电力供应业务、配电网节能业务。公司作为一家从事输、配、售电业务一体化经营的电力企业，公司在现有的供电区域内拥有完善的供电网网络，能够为供电辖区提供优质、可靠的供电服务，保证了对辖区电力供应的市场优势，具有较强的竞争优势。</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>股权转让</t>
+          <t>电力</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr"/>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>国家能源局发布通知，决定将安徽省淮南市风光热储融合系统友好型新能源电站项目等43个项目、河北省张家口市等10个城市列为新型电力系统建设能力提升试点（第一批）。</t>
+        </is>
+      </c>
       <c r="D79" s="2" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>sh603232</t>
+          <t>sh600236</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>格尔软件</t>
+          <t>桂冠电力</t>
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>26.05</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="H79" s="2" t="n">
         <v>10.01</v>
@@ -4032,360 +4140,356 @@
       <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>量子|公司旗下控股企业泓格科技致力于抗量子密码领域技术研究、标准制定、产品研发，在政务、金融、军队等领域开展试点、和应用推广工作，其与复旦大学联合成立密码技术与工程实验室，聚焦抗量子领域。银河证券联合格尔、泓格申报的“抗量子密码技术在证券业的创新研究与应用”课题被评为中国证券业协会2023年重点课题研究优秀课题。</t>
+          <t>电力|公司主要投资建设、经营以电力生产、销售为主业的电力能源项目，水电、风电、光伏等清洁能源占公司在役装机容量的89.79%，水电装机容量达1023.54万千瓦，是公司主要盈利来源。</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>量子</t>
+          <t>电力</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr"/>
+          <t>液冷IDC</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>-0.9299999999999999</v>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>上周，英伟达AI基础设施负责人Dion Harris在加州总部向媒体展示了下一代Vera Rubin算力系统的内部构成与供应链细节。由于功耗上升，Vera Rubin也是英伟达首个100%液冷散热的系统。</t>
+        </is>
+      </c>
       <c r="D80" s="2" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>sz002216</t>
+          <t>sz001400</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>三全食品</t>
+          <t>江顺科技</t>
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>12.76</v>
+        <v>133.45</v>
       </c>
       <c r="H80" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>食品|主导产品是速冻汤圆、速冻水饺、速冻粽子以及速冻面点等。公司产品线在产品创新上一直走在行业前列，儿童水饺及私厨、炫彩等产品系列均为行业首创。</t>
+          <t>液冷+商业航天|1.子公司江宇科技主要从事用于服务器液冷相关的3D打印产品的研发工作，已有部分样品。
+2.公司产品铝型材挤压模具和铝型材挤压配套设备应用于航空航天领域。</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>液冷, 商业航天</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr"/>
+          <t>液冷IDC</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>-0.9299999999999999</v>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>上周，英伟达AI基础设施负责人Dion Harris在加州总部向媒体展示了下一代Vera Rubin算力系统的内部构成与供应链细节。由于功耗上升，Vera Rubin也是英伟达首个100%液冷散热的系统。</t>
+        </is>
+      </c>
       <c r="D81" s="2" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>sz000035</t>
+          <t>sz002536</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>中国天楹</t>
+          <t>飞龙股份</t>
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>7.01</v>
+        <v>34.65</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>10.05</v>
+        <v>10</v>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>甲醇|公司依托吉林辽源和黑龙江安达等风光储氢氨醇一体化项目投资建设，打造涵盖绿色甲醇、绿氨、SAF 等多元化氢基能源产品生产线，形成规模化的绿色燃料供应能力。</t>
+          <t xml:space="preserve">液冷服务器|公司电子泵及温控阀系列产品可以应用在服务器液冷领域。
+</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>甲醇</t>
+          <t>液冷服务器</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>-1.63</v>
       </c>
       <c r="C82" s="2" t="inlineStr"/>
       <c r="D82" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>sz002177</t>
+          <t>sh603268</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>御银股份</t>
+          <t xml:space="preserve">*ST松发 </t>
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>9.69</v>
+        <v>115.59</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I82" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>9天7板</t>
+        </is>
+      </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>数字货币|公司是金融设备整体解决服务商，在ATM设备产能和销售规模在国内ATM制造厂商中位居前列。公司于2020年2月17日在互动平台表示，公司有数字货币ATM机上交易的相关技术储备。</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>数字货币</t>
-        </is>
-      </c>
+          <t>ST股 | 拟收购恒力重工主营船舶及高端装备的研发、生产及销售，已确定排产新造船舶140艘，货值约108亿美元，船型包含散货船、VLCC、VLOC 和集装箱船等。</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>-1.63</v>
       </c>
       <c r="C83" s="2" t="inlineStr"/>
       <c r="D83" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>sh603353</t>
+          <t>sh600525</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>和顺石油</t>
+          <t xml:space="preserve">ST长园  </t>
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>42.13</v>
+        <v>5.42</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I83" s="2" t="inlineStr"/>
+        <v>5.04</v>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>4天3板</t>
+        </is>
+      </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>芯片+石油|1.公司是湖南省第一家获国家商务部批准取得成品油批发资质的民营石油企业，主营成品油批发零售，业务涵盖成品油采购、仓储、物流、批发、零售环节，在成品油流通领域形成完整产业链。
-2.2025年11月16日晚公告，公司拟以现金收购及增资方式取得上海奎芯集成电路设计有限公司不低于34%股权并通过表决权委托合计控制其51%表决权，交易完成后奎芯科技将纳入合并报表，布局高速接口IP及Chiplet解决方案。</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>芯片, 石油</t>
-        </is>
-      </c>
+          <t>ST股 | 子公司长园光波导技术（珠海）有限公司主要从事光学方案相关检测设备及制程设备的市场与技术布局。</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>-1.63</v>
       </c>
       <c r="C84" s="2" t="inlineStr"/>
       <c r="D84" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>sh603093</t>
+          <t>sz002485</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>南华期货</t>
+          <t>ST雪发</t>
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>19.66</v>
+        <v>5.34</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I84" s="2" t="inlineStr"/>
+        <v>4.91</v>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>期货|公司从事的主要业务为：商品期货经纪、金融期货经纪、期货投资咨询、资产管理、证券投资基金代销。全资子公司南华资本及其子公司主要开展的业务为场外衍生品业务、基差贸易及做市业务等。公司是运行规范、管理先进的期货公司。根据中国证监会对期货公司分类评价结果，2018年公司的分类评级为A类AA级。公司营业网点布局较为广泛，网点数量位居行业前列。截至2019年6月30日，公司境内（不包括香港、澳门和台湾地区）拥有40个营业部及分公司，其中位于浙江省内的营业部及分公司为13个，另外位于上海、北京、广东等经济发达地区的营业部及分公司有10个。截至2019年6月30日，公司期货经纪业务客户数为95992户。</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
+          <t>ST股 | 公司文旅项目地处一线旅游目的地黄金地段，历史文化底蕴深厚，旅游资源丰富，市场潜力较大。</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>-1.63</v>
       </c>
       <c r="C85" s="2" t="inlineStr"/>
       <c r="D85" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>sz003018</t>
+          <t>sh600777</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>金富科技</t>
+          <t xml:space="preserve">*ST新潮 </t>
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>26.57</v>
+        <v>4.67</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I85" s="2" t="inlineStr"/>
+        <v>4.94</v>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>液冷|2026年2月5日公告，公司拟支付现金购买佛山市卓晖金属制品有限公司和佛山市联益热能科技有限公司各51%股权，交易对价预计不超过7.14亿元。卓晖金属与联益热能均聚焦液冷散热产品领域，主营液冷散热模组精密结构件的研发、生产与销售。卓晖金属的主要产品包括液冷铜管及其组件、不锈钢管及其组件等，联益热能则主打水冷头组件、铜水冷板、内存条散热模组等产品，两家公司均已成为液冷散热领域头部客户的核心供应商。</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>液冷</t>
-        </is>
-      </c>
+          <t>ST股 | 公司在美国德克萨斯州拥有Hoople油田资产（常规油田）、Howard和Borden油田资产（页岩油藏）两处油田资产；公司主营业务为：石油及天然气的勘探、开采和销售。</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>-1.63</v>
       </c>
       <c r="C86" s="2" t="inlineStr"/>
       <c r="D86" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>sz000628</t>
+          <t>sz000697</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>高新发展</t>
+          <t>ST炼石</t>
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>57.31</v>
+        <v>10.05</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I86" s="2" t="inlineStr"/>
+        <v>5.02</v>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>建筑|公司的主营业务为建筑业和智慧城市建设、运营及相关服务业务，建筑业是公司目前第一大收入及利润来源。</t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>建筑</t>
-        </is>
-      </c>
+          <t xml:space="preserve">ST股 | 公司主要业务为航空制造业，构建“铼元素-高温合金-单晶叶片-航空零部件-航空发动机-大型无人机整机”完整的产业链。 </t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>-1.63</v>
       </c>
       <c r="C87" s="2" t="inlineStr"/>
       <c r="D87" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>sz002356</t>
+          <t>sh603838</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>赫美集团</t>
+          <t xml:space="preserve">*ST四通 </t>
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>4.22</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="I87" s="2" t="inlineStr"/>
+        <v>4.96</v>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>氢能+纺织服装|1.公司控股子公司氢云科技在氢能源应用领域进行投入运营；公司旗下鹏飞氢美定位于氢能源战略的控股投资平台，下设子公司聚能新燃料，主要负责综合能源站的建设与运营，为终端客户提供LNG、汽柴油、氢气等加注服务。
-2.公司定位于“国际品牌运营的服务商”，主要业务为国际品牌服装、鞋帽、箱包等产品的零售，公司运营的品牌既包含国际知名品牌MCM、Fular、Pinko、Radley、AspinalOfLondon等，也包含自营品牌Oblu，经营业态有品牌专营店和奥莱店等，主要分布于北京、上海、南京、郑州、三亚、合肥等主要城市。</t>
-        </is>
-      </c>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>氢能, 纺织服装</t>
-        </is>
-      </c>
+          <t>ST股 | 公司是一家集研发、设计、生产、销售于一体的新型家居生活陶瓷供应商，产品覆盖日用陶瓷、卫生陶瓷、艺术陶瓷、建筑装饰等全系列家居生活用瓷。</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -4400,33 +4504,38 @@
       </c>
       <c r="C88" s="2" t="inlineStr"/>
       <c r="D88" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>sh603117</t>
+          <t>sz002843</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>万林物流</t>
+          <t>泰嘉股份</t>
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>5.96</v>
+        <v>27.8</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>9.959999999999999</v>
-      </c>
-      <c r="I88" s="2" t="inlineStr"/>
+        <v>10.01</v>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>6天4板</t>
+        </is>
+      </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>物流|公司是一家专注于木材供应链的综合物流服务提供商。公司依托子公司盈利港务作为国内重要木材码头的行业地位，结合自身在木材专业物流以及木材进口代理领域的专业业务能力，为国内众多木材行业企业提供包括进口代理、港口装卸、仓储、货运代理、船舶代理、货物配载、物流配送等业务在内的综合物流服务。</t>
+          <t>服务器电源+华为|1.公司电源业务包含一部分数据中心电源业务，主要为服务器电源模块产品。服务客户为行业头部品牌客户。
+2.问界的户用充电桩现由泰嘉股份旗下雅达电子独家供应。</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>物流</t>
+          <t>服务器电源, 华为</t>
         </is>
       </c>
     </row>
@@ -4443,33 +4552,37 @@
       </c>
       <c r="C89" s="2" t="inlineStr"/>
       <c r="D89" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>sh603226</t>
+          <t>sh603950</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>菲林格尔</t>
+          <t>长源东谷</t>
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>31.82</v>
+        <v>48.96</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I89" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>7天4板</t>
+        </is>
+      </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>家具|国内木地板行业领军品牌之一，产品线覆盖强化类地板、实木类地板、整体橱柜、系统收纳等木制家具产品。</t>
+          <t>发电机零部件|2025年1月10日公告，公司与玉柴集团子公司金创公司共同出资成立合资公司玉柴长源科技，玉柴长源科技将聚焦算力中心发动机缸体零部件、船电、汽车零部件等核心业务的制造加工与研发。</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>家具</t>
+          <t>发电机零部件</t>
         </is>
       </c>
     </row>
@@ -4486,33 +4599,38 @@
       </c>
       <c r="C90" s="2" t="inlineStr"/>
       <c r="D90" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>sh603897</t>
+          <t>sz002356</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>长城科技</t>
+          <t>赫美集团</t>
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>30.64</v>
+        <v>4.64</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I90" s="2" t="inlineStr"/>
+        <v>9.950000000000001</v>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>新能源汽车|公司自成立以来专注于电磁线业务领域，是目前国内同类产品的主要制造商之一。公司新能源汽车用扁线产量突破1300吨，并继续保持快速增长。</t>
+          <t>氢能+跨境电商|1.公司控股子公司氢云科技在氢能源应用领域进行投入运营；公司旗下鹏飞氢美定位于氢能源战略的控股投资平台，下设子公司聚能新燃料，主要负责综合能源站的建设与运营，为终端客户提供LNG、汽柴油、氢气等加注服务。
+2.公司定位于“国际品牌运营的服务商”，主要业务为国际品牌服装、鞋帽、箱包等产品的零售，公司运营的品牌既包含国际知名品牌MCM、Fular、Pinko、Radley、AspinalOfLondon等，也包含自营品牌Oblu，经营业态有品牌专营店和奥莱店等，主要分布于北京、上海、南京、郑州、三亚、合肥等主要城市。</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>新能源汽车</t>
+          <t>氢能, 跨境电商</t>
         </is>
       </c>
     </row>
@@ -4529,33 +4647,37 @@
       </c>
       <c r="C91" s="2" t="inlineStr"/>
       <c r="D91" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>sz301226</t>
+          <t>sh603629</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>祥明智能</t>
+          <t>利通电子</t>
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>41.82</v>
+        <v>64.37</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I91" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>华为数据中心|公司下游设备制造商使用公司的相关风机类产品配套华为通信基站与数据中心等项目。</t>
+          <t>算力租赁|公司目前对外出租AI算力规模已达10000P以上，其中，约4000P是以自有算力（报表中在固定资产科目列示）出租，其余是转租算力（在使用权资产科目列示）出租。</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>华为数据中心</t>
+          <t>算力租赁</t>
         </is>
       </c>
     </row>
@@ -4572,20 +4694,20 @@
       </c>
       <c r="C92" s="2" t="inlineStr"/>
       <c r="D92" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>sh603738</t>
+          <t>sh603115</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>泰晶科技</t>
+          <t>海星股份</t>
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>21.78</v>
+        <v>30.91</v>
       </c>
       <c r="H92" s="2" t="n">
         <v>10</v>
@@ -4593,12 +4715,142 @@
       <c r="I92" s="2" t="inlineStr"/>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>半导体材料|公司是专业从事石英晶体谐振器产品设计、生产、销售以及相关工艺设备研发、制造的高新技术企业，是我国石英晶体谐振器行业内主要厂商之一。2018年，公司多款微型片式产品先后通过联发科、紫光展锐、紫光展讯、乐鑫、恒玄科技、泰凌等众多方案商的产品认证。</t>
+          <t>MLPC电容器|公司主营产品电极箔可应用于MLPC电容器。MLPC产品可广泛应用于服务器中高功耗芯片的供电滤波场景，特别是CPU和GPU的核心电压供电。</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>半导体材料</t>
+          <t>MLPC电容器</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr"/>
+      <c r="D93" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>sz002432</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>九安医疗</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>48.83</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>医疗器械+kimi|1.公司是一家在国内外具有影响力的个人健康管理产品供应商，主要从事家用医疗器械的研发、生产及销售。
+2.公司通过认购砺思资本基金份额参股Kimi。</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>医疗器械, kimi</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr"/>
+      <c r="D94" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>sh688307</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>中润光学</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>60.02</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>半导体设备|子公司戴斯光端研发的2D/3D光学AOI检测模主要应用于半导体检测、电路板检测以及其他工业检测场合。</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>半导体设备</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr"/>
+      <c r="D95" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>sh605117</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>德业股份</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>114.95</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>逆变器|公司拥有储能逆变器、组串式并网逆变器和微型并网逆变器12组系列产品。</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>逆变器</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4640,76 +4892,76 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sz001896</t>
+          <t>sz002843</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>豫能控股</t>
+          <t>泰嘉股份</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sz002470</t>
+          <t>sh603950</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>金正大</t>
+          <t>长源东谷</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sz000899</t>
+          <t>sz000035</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>赣能股份</t>
+          <t>中国天楹</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sz002378</t>
+          <t>sh603318</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>章源钨业</t>
+          <t>水发燃气</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sz001209</t>
+          <t>sh600108</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>洪兴股份</t>
+          <t>亚盛集团</t>
         </is>
       </c>
     </row>
@@ -4719,12 +4971,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sh600744</t>
+          <t>sz002842</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>华银电力</t>
+          <t>翔鹭钨业</t>
         </is>
       </c>
     </row>
@@ -4734,12 +4986,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>sh603530</t>
+          <t>sh600498</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>神马电力</t>
+          <t>烽火通信</t>
         </is>
       </c>
     </row>
@@ -4749,12 +5001,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>sz002843</t>
+          <t>sz000960</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>泰嘉股份</t>
+          <t>锡业股份</t>
         </is>
       </c>
     </row>
@@ -4764,12 +5016,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>sz002350</t>
+          <t>sz002356</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>北京科锐</t>
+          <t>赫美集团</t>
         </is>
       </c>
     </row>
@@ -4779,12 +5031,162 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>sh603950</t>
+          <t>sz002980</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>长源东谷</t>
+          <t>华盛昌</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>sh603257</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>中国瑞林</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>sh600301</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>华锡有色</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>sh600259</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>中稀有色</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>sz000510</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>新金路</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>sh600452</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>涪陵电力</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>sh603629</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>利通电子</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>sh603738</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>泰晶科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>sz002155</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>湖南黄金</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>sh603353</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>和顺石油</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>sh603897</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>长城科技</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,19 +476,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K95"/>
+  <dimension ref="A1:K86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="104" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="76" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="275" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="202" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -552,441 +552,445 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>油气设服</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>4.43</v>
+        <v>7.649999999999999</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
+          <t>北京时间周一晚间，全球最大天然气生产商卡塔尔能源（QatarEnergy）宣布，旗下能源设施遭到袭击后宣布停产液化天然气，欧洲天然气价格飙升50%。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>sh600759</t>
+          <t>sh603318</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>洲际油气</t>
+          <t>水发燃气</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>6.83</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>9.98</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>5天3板</t>
+          <t>3天3板</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>油气|公司是以勘探开发为主的国际化独立石油公司，目前公司的运营区块主要集中在哈萨克斯坦，主力在产项目马腾油田和克山油田均位于哈萨克斯坦滨里海盆地，是国际公认的油气富集的区域之一。</t>
+          <t>燃气设备|公司是燃气输配和燃气应用领域（以天然气发电为主）的成套设备供应商，未来公司将实现从上游液化天然气生产，到中游燃气装备为主的高端制造，再到下游燃气应用领域的分布式能源和城镇燃气供应的全产业链，多维度发展。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>油气</t>
+          <t>燃气设备</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>油气设服</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>4.43</v>
+        <v>7.649999999999999</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
+          <t>北京时间周一晚间，全球最大天然气生产商卡塔尔能源（QatarEnergy）宣布，旗下能源设施遭到袭击后宣布停产液化天然气，欧洲天然气价格飙升50%。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sz002207</t>
+          <t>sz000968</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>准油股份</t>
+          <t>蓝焰控股</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>12.42</v>
+        <v>10.41</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
+        <v>10.04</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>6天3板</t>
+        </is>
+      </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>油气|公司是为石油、天然气开采企业提供油田动态监测和提高采收率技术服务的专业化企业，已形成油田动态监测资料录取、资料解释研究和应用、治理方案编制、增产措施施工及效果评价等综合技术服务能力，是西部地区实力较强的一体化油田稳产、增产技术服务企业，能够提供油田增产、油田管理和配套建设等“一站式”技术服务。</t>
+          <t>煤层气|山西煤层气龙头，A股唯一煤层气标的，市占率第二，煤层气抽采量14.33亿方，销售量7亿方，运营近3400口煤层井。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>油气</t>
+          <t>煤层气</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>油气设服</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4.43</v>
+        <v>7.649999999999999</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
+          <t>北京时间周一晚间，全球最大天然气生产商卡塔尔能源（QatarEnergy）宣布，旗下能源设施遭到袭击后宣布停产液化天然气，欧洲天然气价格飙升50%。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sz002490</t>
+          <t>sz000407</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>山东墨龙</t>
+          <t>胜利股份</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>9.68</v>
+        <v>5.86</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>10</v>
+        <v>9.94</v>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>油气|全产业链石油钻采装备制造商，主要产品包括油气开采用管、流体及结构用管、抽油机、抽油泵、抽油杆、钻机用缸套、阀门散件及大型铸锻件等。公司产品主要用于石油、天然气、煤层气、页岩气等行业。</t>
+          <t>天然气管道|公司是国内最具实力的聚乙烯（PE）管道供应商之一，担当本公司、港华燃气、华润燃气、中国燃气、中石油昆仑燃气、新奥燃气、香港水务等大型公用事业公司的主要供应商。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>油气</t>
+          <t>天然气管道</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>油气设服</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4.43</v>
+        <v>7.649999999999999</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
+          <t>北京时间周一晚间，全球最大天然气生产商卡塔尔能源（QatarEnergy）宣布，旗下能源设施遭到袭击后宣布停产液化天然气，欧洲天然气价格飙升50%。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sz002828</t>
+          <t>sh600617</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>贝肯能源</t>
+          <t>国新能源</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>14.88</v>
+        <v>3.7</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>9.98</v>
+        <v>10.12</v>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>油气|公司主要从事油气勘探和开发过程中的钻井工程技术服务及其他油田技术服务，具体包括钻井、固井、钻井液、定向井、欠平衡等，是国内规模较大的、能够提供一体化钻井工程技术服务的独立油田服务供应商。</t>
+          <t>天然气管网|山西最大的天然气管网运营企业，管网建设方面公司在省内主要业务区域已取得绝对优势地位，省级天然气管网5000余公里，年管输涉及能力超过255亿立方米，管网覆盖全省11市104县（市、区）。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>油气</t>
+          <t>天然气管网</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>油气设服</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>4.43</v>
+        <v>7.649999999999999</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
+          <t>北京时间周一晚间，全球最大天然气生产商卡塔尔能源（QatarEnergy）宣布，旗下能源设施遭到袭击后宣布停产液化天然气，欧洲天然气价格飙升50%。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sz300164</t>
+          <t>sh605169</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>通源石油</t>
+          <t>洪通燃气</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>18.08</v>
+        <v>15.37</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>19.97</v>
+        <v>10.02</v>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>油气|公司是以油田增产为核心的国际油服企业，业务涵盖钻井、定向、完井压裂、测井、射孔、带压作业、连续油管和采油、油田化学等整个油气服务产业链，其中，公司是我国复合射孔行业的领军企业、行业国家标准制定的参与者。</t>
+          <t>天然气|地处新疆巴州库尔勒市，专注清洁交通能源供应领域的天然气专业运营商。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>油气</t>
+          <t>天然气</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>油气设服</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>4.43</v>
+        <v>7.649999999999999</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
+          <t>北京时间周一晚间，全球最大天然气生产商卡塔尔能源（QatarEnergy）宣布，旗下能源设施遭到袭击后宣布停产液化天然气，欧洲天然气价格飙升50%。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sh600871</t>
+          <t>sh600681</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>石化油服</t>
+          <t>百川能源</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>3.53</v>
+        <v>4.76</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>9.969999999999999</v>
+        <v>9.93</v>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>油气|最大的综合油气工程与技术服务专业公司，全球油服行业第四，在中国的20多个省，76个盆地，561个区块开展油气工程技术服务；同时海外业务规模不断提高，在38个国家和地区执行364个项目。</t>
+          <t>天然气|公司主要从事城市燃气业务，已在河北省廊坊市、张家口市、沧州市、保定市以及天津市武清区、湖北省荆州市、安徽省阜阳市、辽宁省葫芦岛市等地区进行燃气经营。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>油气</t>
+          <t>天然气</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>油气设服</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>4.43</v>
+        <v>7.649999999999999</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
+          <t>北京时间周一晚间，全球最大天然气生产商卡塔尔能源（QatarEnergy）宣布，旗下能源设施遭到袭击后宣布停产液化天然气，欧洲天然气价格飙升50%。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sh603619</t>
+          <t>sz001299</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>中曼石油</t>
+          <t>美能能源</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>39.99</v>
+        <v>15.47</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>10.01</v>
+        <v>10.03</v>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>油气|国内最具实力的国际化钻井工程大包服务承包商和高端石油装备制造商。</t>
+          <t>天然气|公司是一家长期专注于清洁能源供应领域的专业化城市燃气综合运营服务商，主要从事城镇燃气的输配与运营业务，包括天然气终端销售和服务以及天然气用户设施设备安装业务。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>油气</t>
+          <t>天然气</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>油气设服</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>4.43</v>
+        <v>7.649999999999999</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
+          <t>北京时间周一晚间，全球最大天然气生产商卡塔尔能源（QatarEnergy）宣布，旗下能源设施遭到袭击后宣布停产液化天然气，欧洲天然气价格飙升50%。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sz300191</t>
+          <t>sh600635</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>潜能恒信</t>
+          <t>大众公用</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>44.23</v>
+        <v>6.91</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>19.99</v>
+        <v>10.03</v>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>油气|石油勘探开发综合性公司，公司已具备了提供勘探开发一体化高端油气工程服务能力，服务内容涵盖地震采集、数据处理和解释、地球物理和地质综合分析研究、石油区块评价、井位部署、油藏描述、油气成藏模拟、钻完井服务、水平井压裂设计及施工以及智能化油田管理及相关软件开发等。</t>
+          <t>天然气|公司目前是上海浦西南部、江苏省南通市区唯一的管道燃气供应商，分别在当地拥有并维护超过6500公里、2200公里的地下管道。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>油气</t>
+          <t>天然气</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>油气设服</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>4.43</v>
+        <v>7.649999999999999</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
+          <t>北京时间周一晚间，全球最大天然气生产商卡塔尔能源（QatarEnergy）宣布，旗下能源设施遭到袭击后宣布停产液化天然气，欧洲天然气价格飙升50%。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sh600339</t>
+          <t>sz300332</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>中油工程</t>
+          <t>天壕能源</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>4.66</v>
+        <v>7.24</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>9.91</v>
+        <v>20.07</v>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>油气|公司主要从事以油气田地面工程服务、储运工程服务、炼化工程服务、环境工程服务、项目管理服务为核心的石油工程设计、施工及总承包等相关石油工程建设业务，公司面向国内外石油化工工程市场提供全产业链的“一站式”综合服务。</t>
+          <t>天然气|公司全资子公司北京华盛是山西省规模较大的民营城市燃气公司之一，在山西省原平市、兴县、保德县三市县拥有燃气特许经营权。华盛燃气与中国海洋石油集团旗下全资附属公司合资成立参股子公司中联华瑞，共同建设运营神木——安平煤层气长输管道，实现鄂尔多斯盆地东缘的煤层气资源和京津冀地区用气市场对接，神安线管道是我国第一条非常规天然气长输管道。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>油气</t>
+          <t>天然气</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>油气设服</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>4.43</v>
+        <v>7.649999999999999</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
+          <t>北京时间周一晚间，全球最大天然气生产商卡塔尔能源（QatarEnergy）宣布，旗下能源设施遭到袭击后宣布停产液化天然气，欧洲天然气价格飙升50%。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sh600968</t>
+          <t>sz002682</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>海油发展</t>
+          <t>龙洲股份</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>5.04</v>
+        <v>7.67</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>10.04</v>
@@ -994,2262 +998,2305 @@
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>油气|公司业务以海洋石油生产服务为核心，重点发展FPSO生产技术服务、油田化学服务、多功能生活支持平台、油田装备运维、数据信息、监督监理等业务。</t>
+          <t>天然气|公司通过收购方式在天津市大港区投资建设有CNG天然气加工厂一座，该项目设计产能日供气量可达30万立方。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>油气</t>
+          <t>天然气</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>油气设服</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>4.43</v>
+        <v>7.649999999999999</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
+          <t>北京时间周一晚间，全球最大天然气生产商卡塔尔能源（QatarEnergy）宣布，旗下能源设施遭到袭击后宣布停产液化天然气，欧洲天然气价格飙升50%。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sz002554</t>
+          <t>920010.BJ</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>惠博普</t>
+          <t>凯添燃气</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>4.66</v>
+        <v>17.53</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>9.91</v>
+        <v>29.95</v>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>油气|公司专注于油气水高效分离技术的研发，业务主要分为油气处理成套系统装备、油气开采系统装备、油田环保系统装备、油田工程技术服务四个领域。</t>
+          <t>天然气+算力租赁|1.公司是专业的城镇燃气运营商和服务提供商，从事城市管道天然气与压缩天然气销售及燃气设施、设备安装服务。
+2.2024年3月，公司计划在宁夏银川市贺兰县投资建设“凯添智算（宁夏）中心”，建设内容为人工智能算力机房及相应配套设施。项目通过外部采购液冷设备及机架等，自建标准化专业级机房，以出租的方式为客户提供算力服务器或其他网络相关设备的托管、维护及管理等服务。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>油气</t>
+          <t>天然气, 算力租赁</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>油气设服</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>4.43</v>
+        <v>7.649999999999999</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
+          <t>北京时间周一晚间，全球最大天然气生产商卡塔尔能源（QatarEnergy）宣布，旗下能源设施遭到袭击后宣布停产液化天然气，欧洲天然气价格飙升50%。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>920088.BJ</t>
+          <t>sz002267</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>科力股份</t>
+          <t>陕天然气</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>68.59999999999999</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>30</v>
+        <v>9.98</v>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>油气|公司主营业务为提供油田化学技术服务、油田专用化学品和油田专用设备的研发、生产与销售。</t>
+          <t>天然气|公司负责陕西全省天然气长输管网的规划、建设、运营和管理，目前公司已建成投运靖边至西安一、二、三线，咸阳至宝鸡、西安至渭南、宝鸡至汉中等天然气长输管道及支专线33条，总里程超过3400公里，具备165亿立方米的年输气能力，形成了纵贯陕西南北，延伸关中东西两翼，覆盖全省11个市（区）的输气干线网络。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>油气</t>
+          <t>天然气</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>油气设服</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>4.43</v>
+        <v>7.649999999999999</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
+          <t>北京时间周一晚间，全球最大天然气生产商卡塔尔能源（QatarEnergy）宣布，旗下能源设施遭到袭击后宣布停产液化天然气，欧洲天然气价格飙升50%。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sh603727</t>
+          <t>sh601015</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">博迈科  </t>
+          <t>陕西黑猫</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>19.81</v>
+        <v>5.69</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>9.99</v>
+        <v>10.06</v>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>油气|公司主要产品大类分为海洋油气开发模块、矿业开采模块、天然气液化模块等，产品具体涉及十多种子类别。公司为海洋油气开发、矿业开采和天然气液化领域中的国内外高端客户提供能源资源设施开发的专业分包服务。</t>
+          <t>甲醇+天然气|公司以资源综合利用、循环经济产业链为生产模式，主要产品包括焦炭、甲醇、合成氨、LNG、BDO和精煤等。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>油气</t>
+          <t>甲醇, 天然气</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>油气设服</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>4.43</v>
+        <v>7.649999999999999</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
+          <t>北京时间周一晚间，全球最大天然气生产商卡塔尔能源（QatarEnergy）宣布，旗下能源设施遭到袭击后宣布停产液化天然气，欧洲天然气价格飙升50%。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sz301158</t>
+          <t>sz000421</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>德石股份</t>
+          <t>南京公用</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>31.2</v>
+        <v>7.73</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>20</v>
+        <v>9.959999999999999</v>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>油气|公司主要从事油气钻井专用工具及设备的研发、生产、销售及租赁，开展定向钻井、水平钻井的工程技术服务，业务涵盖石油、天然气、页岩气、煤层气、地热能钻井及定向穿越工程。公司是国内重要的螺杆钻具制造商之一，国内重要的井口装置制造商之一，产品已覆盖国内陆上及海上油气田。</t>
+          <t>天然气|公司旗下南京港华燃气有限公司是南京市规模最大的管道燃气经营企业。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>油气</t>
+          <t>天然气</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>油气设服</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>4.43</v>
+        <v>7.649999999999999</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
+          <t>北京时间周一晚间，全球最大天然气生产商卡塔尔能源（QatarEnergy）宣布，旗下能源设施遭到袭击后宣布停产液化天然气，欧洲天然气价格飙升50%。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sh600583</t>
+          <t>sh603706</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>海油工程</t>
+          <t>东方环宇</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>7.93</v>
+        <v>23.96</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>9.99</v>
+        <v>10.01</v>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>油气|国内惟一一家集海洋石油、天然气开发工程设计、陆地制造和海上安装、调试、维修以及液化天然气工程于一体的大型工程总承包公司，是亚太地区最大的海洋石油工程EPCI（设计、采办、建造、安装）总承包商之一。</t>
+          <t>天然气|新疆昌吉市燃气综合服务商，公司拥有昌吉市天然气门站一座及西二线昌吉接收站一座，运营管道长度达到1,048.72公里，拥有CNG母站1座，加气站13座的燃气管网系统，服务20.9万户居民客户、510户工商业用户。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>油气</t>
+          <t>天然气</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>油气设服</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>4.43</v>
+        <v>7.649999999999999</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
+          <t>北京时间周一晚间，全球最大天然气生产商卡塔尔能源（QatarEnergy）宣布，旗下能源设施遭到袭击后宣布停产液化天然气，欧洲天然气价格飙升50%。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sz002629</t>
+          <t>920014.BJ</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>仁智股份</t>
+          <t>特瑞斯</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>7.37</v>
+        <v>17.81</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>油气|公司系具有钻井液技术服务、井下作业技术服务、环保治理技术服务等多个油服产业的综合性油服公司。公司从事油田化学品与功能新材料的研发、生产与销售，产品广泛应用于石油天然气开发多个领域，已取得中石化、中石油市场准入资质。</t>
+          <t>天然气设备|公司主要从事于研发、生产、销售标准燃气调压集成设备、非标撬装燃气集成系统、燃气调压核心部件及相关配套产品三大类产品，产品主要包括长输管线输气站调压计量设备、城市门站、区域调压站调压计量设备、大型工业用调压计量系统、箱式调压计量站、楼宇调压箱、阀类产品等。产品广泛使用于国内外各类天然气，发电、市政建设、清洁能源车辆等行业和领域。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>油气</t>
+          <t>天然气设备</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>油气设服</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>4.43</v>
+        <v>7.649999999999999</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
+          <t>北京时间周一晚间，全球最大天然气生产商卡塔尔能源（QatarEnergy）宣布，旗下能源设施遭到袭击后宣布停产液化天然气，欧洲天然气价格飙升50%。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sz300157</t>
+          <t>sh605368</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>新锦动力</t>
+          <t>蓝天燃气</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>8.390000000000001</v>
+        <v>9.41</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>20.03</v>
+        <v>10.06</v>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>油气+甲醇|1.公司主要从事油气资源的勘探开发技术服务，利用自主研发油气勘探开发软件和相关技术帮助石油公司寻找油气资源。公司拥有4大类、20套勘探开发软件产品。
-2.公司自主研发生产的"NEWICM"品牌离心式压缩机是国内外生产合成氨、尿素、烧碱、甲醇等化工产品的关键装备，在合成气压缩机组、CO2压缩机组、氯气压缩机组领域处于国际第一梯队。</t>
+          <t>天然气|公司主要从事河南省内的管道天然气业务、城市燃气等业务，是河南省天然气支干线管网覆盖范围较广、输气规模较大的综合性燃气企业。</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>油气, 甲醇</t>
+          <t>天然气</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>油气设服</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>4.43</v>
+        <v>7.649999999999999</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
+          <t>北京时间周一晚间，全球最大天然气生产商卡塔尔能源（QatarEnergy）宣布，旗下能源设施遭到袭击后宣布停产液化天然气，欧洲天然气价格飙升50%。</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sh601808</t>
+          <t>sh603689</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>中海油服</t>
+          <t>皖天然气</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>18.56</v>
+        <v>9.56</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>10.02</v>
+        <v>10.01</v>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>油气|公司是全球最具规模的油田服务供应商之一，拥有完整的服务链条和强大的海上石油服务装备群。</t>
+          <t>天然气|安徽省天然气综合运营商，公司建成并投入运营的省内天然气长输支线共18条，总长约1078公里。</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>油气</t>
+          <t>天然气</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>油气设服</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>4.43</v>
+        <v>7.649999999999999</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
+          <t>北京时间周一晚间，全球最大天然气生产商卡塔尔能源（QatarEnergy）宣布，旗下能源设施遭到袭击后宣布停产液化天然气，欧洲天然气价格飙升50%。</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sz300084</t>
+          <t>sz300483</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>海默科技</t>
+          <t>首华燃气</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>13.45</v>
+        <v>25.03</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>19.98</v>
+        <v>19.99</v>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>油气|公司是国际领先的油气田多相计量和生产优化解决方案提供商，国内最大的压裂泵液力端制造商、国内领先的油气增产工程专用仪器制造商、国内油气田环保技术引领者和首家投资海外非常规油气资源的民营上市公司。</t>
+          <t>天然气|公司旗下控股子公司中海沃邦主要从事天然气的勘探、开发、生产、销售业务。</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>油气</t>
+          <t>天然气</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>1.2</v>
+        <v>7.649999999999999</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>银河证券表示，供需格局改善与行业盈利修复带动的“反内卷”概念，以及估值具备安全边际的红利资产，配置逻辑依然清晰，建议关注受益于价格上涨的有色金属板块。</t>
+          <t>北京时间周一晚间，全球最大天然气生产商卡塔尔能源（QatarEnergy）宣布，旗下能源设施遭到袭击后宣布停产液化天然气，欧洲天然气价格飙升50%。</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>sh600301</t>
+          <t>sh600333</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>华锡有色</t>
+          <t>长春燃气</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>71.23999999999999</v>
+        <v>6.51</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>4天3板</t>
-        </is>
-      </c>
+        <v>9.969999999999999</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>铟锡锑|公司是亚洲最大的锡多金属矿选矿基地、国内唯一的铟锡锑资源综合利用示范基地，拥有的多项关键战略性资源储量位居全球前列，主要金属矿产资源包括锡、锑、铟、锌、铅、银等，是国内主要的锡、锑金属生产企业之一。</t>
+          <t>天然气|吉林省燃气供应区域龙头，管道燃气用户总数达到142万户，燃气销售3.98亿立方米；公司拥有储气能力600万方以及LNG气化能力100万方/天的调峰气源厂，长春、德惠、延吉等9个区域的燃气特许经营权。</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>铟锡锑</t>
+          <t>天然气</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>1.2</v>
+        <v>7.649999999999999</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>银河证券表示，供需格局改善与行业盈利修复带动的“反内卷”概念，以及估值具备安全边际的红利资产，配置逻辑依然清晰，建议关注受益于价格上涨的有色金属板块。</t>
+          <t>北京时间周一晚间，全球最大天然气生产商卡塔尔能源（QatarEnergy）宣布，旗下能源设施遭到袭击后宣布停产液化天然气，欧洲天然气价格飙升50%。</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>sh600108</t>
+          <t>sh600903</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>亚盛集团</t>
+          <t>贵州燃气</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>4.37</v>
+        <v>7.7</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>钨矿|子公司甘肃亚盛鱼儿红矿业拟对鱼儿红牧场境内矿产资源进行开发，其中塔尔沟钨矿区拥有C+D 级三氧化钨22.42万吨(其中黑钨矿12.98万吨)，其中C级3773吨。</t>
+          <t>天然气|贵州天然气龙头，公司已在贵州省25个特定区域及1个省外特定区域取得了管道燃气特许经营权。</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>钨矿</t>
+          <t>天然气</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>1.2</v>
+        <v>7.649999999999999</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>银河证券表示，供需格局改善与行业盈利修复带动的“反内卷”概念，以及估值具备安全边际的红利资产，配置逻辑依然清晰，建议关注受益于价格上涨的有色金属板块。</t>
+          <t>北京时间周一晚间，全球最大天然气生产商卡塔尔能源（QatarEnergy）宣布，旗下能源设施遭到袭击后宣布停产液化天然气，欧洲天然气价格飙升50%。</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>sz002842</t>
+          <t>sh601139</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>翔鹭钨业</t>
+          <t>深圳燃气</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>45.72</v>
+        <v>7.87</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.07</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>钨|公司一直专注于钨制品的开发、生产与销售，主要产品包括各种规格的氧化钨、钨粉、碳化钨粉、钨合金粉及钨硬质合金等。公司是国内钨行业具备完整产业链的企业之一，从钨精矿采选、仲钨酸铵冶炼、氧化钨、钨粉、碳化钨粉、硬质合金及其工具等全系列钨产品的生产。公司是商务部批准的14家"钨品国营贸易出口资格企业"之一。</t>
+          <t>天然气|公司是一家集城市燃气、燃气资源、综合能源和智慧服务为一体的综合性公用事业上市公司，构建天然气“采运储销”全产业体系，较早实现跨区域经营。</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>钨</t>
+          <t>天然气</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>1.2</v>
+        <v>7.649999999999999</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>银河证券表示，供需格局改善与行业盈利修复带动的“反内卷”概念，以及估值具备安全边际的红利资产，配置逻辑依然清晰，建议关注受益于价格上涨的有色金属板块。</t>
+          <t>北京时间周一晚间，全球最大天然气生产商卡塔尔能源（QatarEnergy）宣布，旗下能源设施遭到袭击后宣布停产液化天然气，欧洲天然气价格飙升50%。</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>sh603257</t>
+          <t>sh600917</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>中国瑞林</t>
+          <t>重庆燃气</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>73.06999999999999</v>
+        <v>6.42</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.93</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>铜钴+钨|1.在铜、钴资源开发上，公司在全球铜冶炼领域保持技术优势，承接设计了多个标志性项目，如非洲刚果（金）的卡莫阿铜冶炼厂和洛钼集团Tenke Fungurume铜钴矿项目。
-2.2025年10月15日公告，公司与江西省国有资本运营控股集团有限公司、江西江钨私募基金管理有限公司、农银金融资产投资有限公司、交银金融资产投资有限公司、江西钨业控股集团有限公司共同签署《合作意向书》。公司拟作为有限合伙人，参与设立江钨矿业基金。江钨矿业基金总规模暂定为20亿元，投资领域聚焦钨、稀土、钽铌、钼、锡等稀有金属项目。公司拟以自有资金出资3000万元。</t>
+          <t>天然气|公司主营业务为重庆市管道燃气供应及燃气设施、设备的安装服务，综合服务，综合能源等。其中，管道燃气供应及燃气设施、设备的安装服务是公司的核心业务。</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>铜钴, 钨</t>
+          <t>天然气</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>1.2</v>
+        <v>7.649999999999999</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>银河证券表示，供需格局改善与行业盈利修复带动的“反内卷”概念，以及估值具备安全边际的红利资产，配置逻辑依然清晰，建议关注受益于价格上涨的有色金属板块。</t>
+          <t>北京时间周一晚间，全球最大天然气生产商卡塔尔能源（QatarEnergy）宣布，旗下能源设施遭到袭击后宣布停产液化天然气，欧洲天然气价格飙升50%。</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>sz002155</t>
+          <t>sz002700</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>湖南黄金</t>
+          <t>万憬能源</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>41.47</v>
+        <v>8.18</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.950000000000001</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>黄金+锑+钨|公司长期专注于黄金、锑和钨三种金属的矿山开采和深加工，拥有集矿山勘探、开采、选矿、冶炼、精炼、深加工及销售于一体的完整产业链，拥有100吨/年黄金生产线。</t>
+          <t>天然气|立足南疆的区域燃气供应商，公司运营模式为天然气产业的“中游+下游”，拥有148公里天然气长输管线，2018年8月，公司投资215亿元建设天然气精制化学品项目。</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>黄金, 锑, 钨</t>
+          <t>天然气</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>1.2</v>
+        <v>7.649999999999999</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>银河证券表示，供需格局改善与行业盈利修复带动的“反内卷”概念，以及估值具备安全边际的红利资产，配置逻辑依然清晰，建议关注受益于价格上涨的有色金属板块。</t>
+          <t>北京时间周一晚间，全球最大天然气生产商卡塔尔能源（QatarEnergy）宣布，旗下能源设施遭到袭击后宣布停产液化天然气，欧洲天然气价格飙升50%。</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>sh600259</t>
+          <t>sh603053</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>中稀有色</t>
+          <t>成都燃气</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>112.29</v>
+        <v>11.33</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+      <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>稀土+钨|广东省稀土龙头，在粤北地区控股及参股5个钨矿山。</t>
+          <t>天然气|公司主要负责天然气统一采购及绕城区域内、高新区部分区域的天然气销售及天然气安装，控股子公司新创燃气、新繁燃气、大丰燃气、威达燃气、唐昌燃气、 华新燃气主要负责新都区、郫都区和新津县的部分区域天然气销售及天然气安装。</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>稀土, 钨</t>
+          <t>天然气</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>1.2</v>
+        <v>7.649999999999999</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>银河证券表示，供需格局改善与行业盈利修复带动的“反内卷”概念，以及估值具备安全边际的红利资产，配置逻辑依然清晰，建议关注受益于价格上涨的有色金属板块。</t>
+          <t>北京时间周一晚间，全球最大天然气生产商卡塔尔能源（QatarEnergy）宣布，旗下能源设施遭到袭击后宣布停产液化天然气，欧洲天然气价格飙升50%。</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>sz000960</t>
+          <t>sh603080</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>锡业股份</t>
+          <t>新疆火炬</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>48.8</v>
+        <v>27.57</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.02</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>锡铟|公司作为全球锡铟行业的龙头企业，拥有着国际先进水平的采、选、冶及深加工成套技术，及全行业最完整的产业链，主要产品为锡锭、阴极铜、锌锭、铟锭、锡材和锡化工产品等1000多个规格品种，现有锡冶炼产能8万吨/年，锡材产能4.1万吨/年、锡化工产能2.4万吨/年、阴极铜产能12.5万吨/年、锌冶炼产能10万吨/年、铟冶炼产能60吨/年。</t>
+          <t>天然气|喀什天然气优质供应商，公司取得喀什市、疏勒县和疏附县县城“一市两县”的城市管道燃气特许经营权，市场占有率均为100%。公司喀什市建成投产12座加气站，数量位居第一，在疏勒县建成投产2座加气站，占有约50%市场份额。</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>锡铟</t>
+          <t>天然气</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>1.2</v>
+        <v>7.649999999999999</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>银河证券表示，供需格局改善与行业盈利修复带动的“反内卷”概念，以及估值具备安全边际的红利资产，配置逻辑依然清晰，建议关注受益于价格上涨的有色金属板块。</t>
+          <t>北京时间周一晚间，全球最大天然气生产商卡塔尔能源（QatarEnergy）宣布，旗下能源设施遭到袭击后宣布停产液化天然气，欧洲天然气价格飙升50%。</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>sz002667</t>
+          <t>sz002911</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>威领股份</t>
+          <t>佛燃能源</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>23.35</v>
+        <v>17.77</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>9.99</v>
+        <v>10.03</v>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>锂矿+有色|1.公司主要以新能源锂电材料产业链为主体，包括锂矿选矿、基础性锂电原料锂盐加工及冶炼业务，主要产品包括锂化合物及衍生品、锂精矿及伴生品和振动筛及PC生产线等。旗下领辉科技具备锂云母年选矿产能120万吨。
-2.2025年5月20日公告，控股孙公司天津长领矿业以2.2亿元成功竞得湖南临武嘉宇矿业74.3%股权。嘉宇矿业拥有锡矿石247万吨、铅矿石119万吨、锌矿石117万吨，年开采规模30万吨，可迅速形成稳定的采选产能。</t>
+          <t>天然气|佛山区域燃气龙头，公司在佛山市辖区内及其他业务区域内已建成的城市燃气管道包括高压管网、次高压管网及市政管网长度合计达2000余公里，为69万户居民用户和3369户工商业用户提供管道天然气服务。</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>锂矿, 有色</t>
+          <t>天然气</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>1.2</v>
+        <v>7.649999999999999</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>银河证券表示，供需格局改善与行业盈利修复带动的“反内卷”概念，以及估值具备安全边际的红利资产，配置逻辑依然清晰，建议关注受益于价格上涨的有色金属板块。</t>
+          <t>北京时间周一晚间，全球最大天然气生产商卡塔尔能源（QatarEnergy）宣布，旗下能源设施遭到袭击后宣布停产液化天然气，欧洲天然气价格飙升50%。</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>sh601069</t>
+          <t>920260.BJ</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>西部黄金</t>
+          <t>中寰股份</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>39.89</v>
+        <v>15.4</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>10.01</v>
+        <v>29.96</v>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>黄金|公司长期专注于黄金矿山开采与冶炼，拥有集矿山勘探、开采、选矿、冶炼、精炼、销售于一体的完整产业链，拥有哈图金矿、伊犁公司所属阿希金矿和哈密金矿等主要黄金生产矿山。</t>
+          <t>天然气设备|公司是天然气采集、输配送环节的设备生产商及服务提供商，主要为国内外各类天然气采集矿场、输气、配气企业提供其必需的各型井口安全控制系统、阀门执行机构和橇装设备，以及对应的售后维保服务。</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>黄金</t>
+          <t>天然气设备</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>1.2</v>
+        <v>4.84</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>银河证券表示，供需格局改善与行业盈利修复带动的“反内卷”概念，以及估值具备安全边际的红利资产，配置逻辑依然清晰，建议关注受益于价格上涨的有色金属板块。</t>
+          <t>上期所原油主力合约连续第二个交易日封涨停，现涨12%，报572.3元/桶。</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>sz001337</t>
+          <t>sh600759</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>四川黄金</t>
+          <t>洲际油气</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>55.74</v>
+        <v>7.51</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
+        <v>9.959999999999999</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>6天4板</t>
+        </is>
+      </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>黄金|公司是一家长期专注于金矿资源开发及综合利用的企业，主要从事金矿的采选及销售，产品为金精矿和合质金，已成为国内主要的金矿采选企业之一。公司拥有梭罗沟金矿采矿权和梭罗-挖金沟详查金矿探矿权，梭罗沟金矿矿区采矿许可证范围内保有资源储量为金金属量44862kg，梭罗沟金矿区挖金沟矿段查明资源储量为金金属量1332kg。</t>
+          <t>油气勘探开发|公司是以勘探开发为主的国际化独立石油公司，目前公司的运营区块主要集中在哈萨克斯坦，主力在产项目马腾油田和克山油田均位于哈萨克斯坦滨里海盆地，是国际公认的油气富集的区域之一。</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>黄金</t>
+          <t>油气勘探开发</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>1.2</v>
+        <v>4.84</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>银河证券表示，供需格局改善与行业盈利修复带动的“反内卷”概念，以及估值具备安全边际的红利资产，配置逻辑依然清晰，建议关注受益于价格上涨的有色金属板块。</t>
+          <t>上期所原油主力合约连续第二个交易日封涨停，现涨12%，报572.3元/桶。</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>sz300139</t>
+          <t>sz002490</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>晓程科技</t>
+          <t>山东墨龙</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>79.78</v>
+        <v>10.65</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>20.01</v>
-      </c>
-      <c r="I31" s="2" t="inlineStr"/>
+        <v>10.02</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>6天3板</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>黄金|公司的黄金开采及销售业务已形成黄金勘探、采矿、选冶、冶炼、销售于一体的完整产业链条。截至2023年6月30日，公司拥有三座金矿，分别为AKROMA金矿、AKOASE金矿和FGM（NAFORMAN_NOYEM）金矿，已探明的黄金储量分别为5.8吨、16.8吨和32.2吨，合计54.8吨。</t>
+          <t>油气设服|全产业链石油钻采装备制造商，主要产品包括油气开采用管、流体及结构用管、抽油机、抽油泵、抽油杆、钻机用缸套、阀门散件及大型铸锻件等。公司产品主要用于石油、天然气、煤层气、页岩气等行业。</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>黄金</t>
+          <t>油气设服</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>1.2</v>
+        <v>4.84</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>银河证券表示，供需格局改善与行业盈利修复带动的“反内卷”概念，以及估值具备安全边际的红利资产，配置逻辑依然清晰，建议关注受益于价格上涨的有色金属板块。</t>
+          <t>上期所原油主力合约连续第二个交易日封涨停，现涨12%，报572.3元/桶。</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>sz000506</t>
+          <t>sz002207</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>招金黄金</t>
+          <t>准油股份</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>22.33</v>
+        <v>13.66</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
+        <v>9.98</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>6天3板</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>黄金|公司主要业务包括以黄金为主要品种的矿业开采，子公司斐济瓦图科拉金矿有限公司所拥有的斐济瓦图科拉金矿已有90年的开采历史，已采出黄金240多吨，是全球少有的长寿大型矿山，地质勘探潜力较大。</t>
+          <t>油气设服|公司是为石油、天然气开采企业提供油田动态监测和提高采收率技术服务的专业化企业，已形成油田动态监测资料录取、资料解释研究和应用、治理方案编制、增产措施施工及效果评价等综合技术服务能力，是西部地区实力较强的一体化油田稳产、增产技术服务企业，能够提供油田增产、油田管理和配套建设等“一站式”技术服务。</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>黄金</t>
+          <t>油气设服</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>1.2</v>
+        <v>4.84</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>银河证券表示，供需格局改善与行业盈利修复带动的“反内卷”概念，以及估值具备安全边际的红利资产，配置逻辑依然清晰，建议关注受益于价格上涨的有色金属板块。</t>
+          <t>上期所原油主力合约连续第二个交易日封涨停，现涨12%，报572.3元/桶。</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>sh600988</t>
+          <t>sh600871</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>赤峰黄金</t>
+          <t>石化油服</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>43.91</v>
+        <v>3.88</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
+        <v>9.92</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>6天3板</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>黄金|公司的主营业务为黄金的采选及销售业务，主要通过下属子公司开展，公司拥有并经营7个黄金及多金属矿山，分布于中国、东南亚和西非等世界各地。子公司吉隆矿业、五龙矿业、华泰矿业及锦泰矿业从事黄金采选业务；子公司瀚丰矿业从事锌、铅、铜、钼采选业务；位于老挝的控股子公司万象矿业目前主要从事金、铜矿开采和冶炼；位于加纳的控股子公司金星瓦萨主要从事黄金采选业务。</t>
+          <t>油气设服|最大的综合油气工程与技术服务专业公司，全球油服行业第四，在中国的20多个省，76个盆地，561个区块开展油气工程技术服务；同时海外业务规模不断提高，在38个国家和地区执行364个项目。</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>黄金</t>
+          <t>油气设服</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>石油</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>8.880000000000001</v>
+        <v>4.84</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
+          <t>上期所原油主力合约连续第二个交易日封涨停，现涨12%，报572.3元/桶。</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>sh603353</t>
+          <t>sh603619</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>和顺石油</t>
+          <t>中曼石油</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46.34</v>
+        <v>43.99</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>6天3板</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>石油+半导体|1.公司是湖南省第一家获国家商务部批准取得成品油批发资质的民营石油企业，主营成品油批发零售，业务涵盖成品油采购、仓储、物流、批发、零售环节，在成品油流通领域形成完整产业链。
-2.2025年11月16日晚公告，公司拟以现金收购及增资方式取得上海奎芯集成电路设计有限公司不低于34%股权并通过表决权委托合计控制其51%表决权，交易完成后奎芯科技将纳入合并报表，布局高速接口IP及Chiplet解决方案。</t>
+          <t>油气设服|国内最具实力的国际化钻井工程大包服务承包商和高端石油装备制造商。</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>石油, 半导体</t>
+          <t>油气设服</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>石油</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>8.880000000000001</v>
+        <v>4.84</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
+          <t>上期所原油主力合约连续第二个交易日封涨停，现涨12%，报572.3元/桶。</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sz000554</t>
+          <t>sz002828</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>泰山石油</t>
+          <t>贝肯能源</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>9.859999999999999</v>
+        <v>16.37</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>10.04</v>
-      </c>
-      <c r="I35" s="2" t="inlineStr"/>
+        <v>10.01</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>6天3板</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>成品油经营|中石化旗下上市公司，主要从事成品油批发零售，车用天然气加气业务以及非油品业务。公司是山东省泰安市成油品、车用天然气的最大经销商。</t>
+          <t>油气设服|公司主要从事油气勘探和开发过程中的钻井工程技术服务及其他油田技术服务，具体包括钻井、固井、钻井液、定向井、欠平衡等，是国内规模较大的、能够提供一体化钻井工程技术服务的独立油田服务供应商。</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>成品油经营</t>
+          <t>油气设服</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>石油</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>8.880000000000001</v>
+        <v>4.84</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
+          <t>上期所原油主力合约连续第二个交易日封涨停，现涨12%，报572.3元/桶。</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sh600938</t>
+          <t>sh600339</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>中国海油</t>
+          <t>中油工程</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>39.46</v>
+        <v>5.13</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
+        <v>10.09</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>6天3板</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>油气|公司为中国最大之海上原油及天然气生产商，亦为全球最大之独立油气勘探及生产企业之一，主要业务为勘探、开发、生产及销售原油和天然气。</t>
+          <t>油气设服|公司主要从事以油气田地面工程服务、储运工程服务、炼化工程服务、环境工程服务、项目管理服务为核心的石油工程设计、施工及总承包等相关石油工程建设业务，公司面向国内外石油化工工程市场提供全产业链的“一站式”综合服务。</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>油气</t>
+          <t>油气设服</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>石油</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>8.880000000000001</v>
+        <v>4.84</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
+          <t>上期所原油主力合约连续第二个交易日封涨停，现涨12%，报572.3元/桶。</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sh600688</t>
+          <t>sh601808</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>上海石化</t>
+          <t>中海油服</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>3.49</v>
+        <v>20.42</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>10.09</v>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
+        <v>10.02</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>6天3板</t>
+        </is>
+      </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>石油化工|中国最大的炼油化工一体化综合性石油化工企业之一，具有较强的整体规模实力，是中国重要的成品油、中间石化产品、合成树脂和合成纤维生产企业。</t>
+          <t>油气设服|公司是全球最具规模的油田服务供应商之一，拥有完整的服务链条和强大的海上石油服务装备群，业务覆盖油气田勘探、开发和生产的全过程，包括钻井服务、油田技术服务、船舶服务、物探采集和工程勘察服务四大类，是全球油田服务行业屈指可数的有能力提供一体化服务的供应商之一。</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>石油化工</t>
+          <t>油气设服</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>石油</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>8.880000000000001</v>
+        <v>4.84</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
+          <t>上期所原油主力合约连续第二个交易日封涨停，现涨12%，报572.3元/桶。</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>sz000096</t>
+          <t>sz300164</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>广聚能源</t>
+          <t>通源石油</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>12.06</v>
+        <v>21.7</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>10.04</v>
-      </c>
-      <c r="I38" s="2" t="inlineStr"/>
+        <v>20.02</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>6天3板</t>
+        </is>
+      </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>成品油经营|深圳市唯一的大型液体化工品仓储企业，公司具有成品油、液化石油气、危险化学品特许经营资质。</t>
+          <t>油气设服|公司是以油田增产为核心的国际油服企业，业务涵盖钻井、定向、完井压裂、测井、射孔、带压作业、连续油管和采油、油田化学等整个油气服务产业链，其中，公司是我国复合射孔行业的领军企业、行业国家标准制定的参与者。</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>成品油经营</t>
+          <t>油气设服</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>石油</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>8.880000000000001</v>
+        <v>4.84</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
+          <t>上期所原油主力合约连续第二个交易日封涨停，现涨12%，报572.3元/桶。</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>sh600256</t>
+          <t>sz300191</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>广汇能源</t>
+          <t>潜能恒信</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>6.47</v>
+        <v>53.08</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="I39" s="2" t="inlineStr"/>
+        <v>20.01</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>6天3板</t>
+        </is>
+      </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>油气+煤炭|公司已形成以煤炭、LNG、醇醚、煤焦油、石油为核心产品，以能源物流为支撑的天然气液化、煤炭开采、煤化工转换、油气勘探开发四大业务板块，是国内唯一一家同时拥有煤、气、油三种资源的民营企业。</t>
+          <t>油气设服|石油勘探开发综合性公司，公司已具备了提供勘探开发一体化高端油气工程服务能力，服务内容涵盖地震采集、数据处理和解释、地球物理和地质综合分析研究、石油区块评价、井位部署、油藏描述、油气成藏模拟、钻完井服务、水平井压裂设计及施工以及智能化油田管理及相关软件开发等。</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>油气, 煤炭</t>
+          <t>油气设服</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>石油</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>8.880000000000001</v>
+        <v>4.84</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>国际油价周一开盘暴涨，布伦特原油期货开盘飙升13%至每桶82美元，WTI原油期货涨超10%报75美元/桶。</t>
+          <t>上期所原油主力合约连续第二个交易日封涨停，现涨12%，报572.3元/桶。</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>sh601857</t>
+          <t>sz300157</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>中国石油</t>
+          <t>新锦动力</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>11.95</v>
+        <v>10.07</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>10.04</v>
-      </c>
-      <c r="I40" s="2" t="inlineStr"/>
+        <v>20.02</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>6天3板</t>
+        </is>
+      </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>油气|集团是我国油气行业占主导地位的最大的油气生产和销售商，世界最大的石油公司之一。</t>
+          <t>油气设服+天然气|1.公司主要从事油气资源的勘探开发技术服务，利用自主研发油气勘探开发软件和相关技术帮助石油公司寻找油气资源。公司拥有4大类、20套勘探开发软件产品。
+2.子公司川油设计拥有天然气行业和市政行业工程设计资质，成功获得四川省孜藏族自治州雅江县、色达县、乡城县等县域30年燃气特许经营权。</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>油气</t>
+          <t>油气设服, 天然气</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>军工</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>0.27</v>
+        <v>4.84</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>华泰证券发布航天军工板块2026年度展望研报称，复盘“十四五”，军工体量迈上新台阶；展望“十五五”，或将由“量”的增值转向“质”的提升。</t>
+          <t>上期所原油主力合约连续第二个交易日封涨停，现涨12%，报572.3元/桶。</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>sz301302</t>
+          <t>sz002554</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>华如科技</t>
+          <t>惠博普</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>29.72</v>
+        <v>5.13</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>19.98</v>
-      </c>
-      <c r="I41" s="2" t="inlineStr"/>
+        <v>10.09</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>6天3板</t>
+        </is>
+      </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>军工信息化|公司以建模仿真为主业，致力于军用仿真、虚拟现实和数据应用技术研发与产品推广，为政府、军队、教育和科研部门，以及国防工业、交通物流、应急安全、能源化工等行业企业提供优质的仿真产品和技术服务。</t>
+          <t>油气设服|公司专注于油气水高效分离技术的研发，业务主要分为油气处理成套系统装备、油气开采系统装备、油田环保系统装备、油田工程技术服务四个领域。</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>军工信息化</t>
+          <t>油气设服</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>军工</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>0.27</v>
+        <v>4.84</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>华泰证券发布航天军工板块2026年度展望研报称，复盘“十四五”，军工体量迈上新台阶；展望“十五五”，或将由“量”的增值转向“质”的提升。</t>
+          <t>上期所原油主力合约连续第二个交易日封涨停，现涨12%，报572.3元/桶。</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>sh603488</t>
+          <t>sh603727</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>展鹏科技</t>
+          <t xml:space="preserve">博迈科  </t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>10.91</v>
+        <v>21.79</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="I42" s="2" t="inlineStr"/>
+        <v>9.99</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>6天3板</t>
+        </is>
+      </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>军工信息化|公司于2023年11月18日公告，拟以6.47元/股的价格发行股份及支付现金购买领为军融100%股权并以6.87元/股的价格发行股份募集配套资金，本次交易预计构成重大资产重组。标的公司主营军事航空仿真系列产品的研制、生产和技术服务，核心产品为面向航空兵作战训练的便携式“通用数字空战仿真系统”。</t>
+          <t>油气设服|公司主要产品大类分为海洋油气开发模块、矿业开采模块、天然气液化模块等，产品具体涉及十多种子类别。公司为海洋油气开发、矿业开采和天然气液化领域中的国内外高端客户提供能源资源设施开发的专业分包服务。</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>军工信息化</t>
+          <t>油气设服</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>军工</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>0.27</v>
+        <v>4.84</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>华泰证券发布航天军工板块2026年度展望研报称，复盘“十四五”，军工体量迈上新台阶；展望“十五五”，或将由“量”的增值转向“质”的提升。</t>
+          <t>上期所原油主力合约连续第二个交易日封涨停，现涨12%，报572.3元/桶。</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>sz002413</t>
+          <t>sh600968</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>雷科防务</t>
+          <t>海油发展</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>16.36</v>
+        <v>5.54</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
+        <v>9.92</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>军工|公司主要业务包括雷达系统业务群、智能弹药业务群、卫星应用业务群、安全存储业务群、智能网联业务群的相关产品研发、制造和销售。公司致力于相控阵雷达、合成孔径雷达和毫米波雷达等技术方面的研究，主要应用于国防军工和国民经济各个领域。</t>
+          <t>油气设服|公司业务以海洋石油生产服务为核心，重点发展FPSO生产技术服务、油田化学服务、多功能生活支持平台、油田装备运维、数据信息、监督监理等业务。</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>军工</t>
+          <t>油气设服</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>军工</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>0.27</v>
+        <v>4.84</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>华泰证券发布航天军工板块2026年度展望研报称，复盘“十四五”，军工体量迈上新台阶；展望“十五五”，或将由“量”的增值转向“质”的提升。</t>
+          <t>上期所原油主力合约连续第二个交易日封涨停，现涨12%，报572.3元/桶。</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>sz301213</t>
+          <t>920088.BJ</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>观想科技</t>
+          <t>科力股份</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>90.09999999999999</v>
+        <v>89.18000000000001</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>20.01</v>
-      </c>
-      <c r="I44" s="2" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>军工信息化|公司为客户提供装备全寿命周期管理系统、智能武器装备管控模块等相关产品及服务。公司产品和服务广泛应用于陆军、海军、空军、火箭军等国防信息化领域。</t>
+          <t>油气设服|公司主营业务为提供油田化学技术服务、油田专用化学品和油田专用设备的研发、生产与销售。</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>军工信息化</t>
+          <t>油气设服</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>军工</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>0.27</v>
+        <v>4.84</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>华泰证券发布航天军工板块2026年度展望研报称，复盘“十四五”，军工体量迈上新台阶；展望“十五五”，或将由“量”的增值转向“质”的提升。</t>
+          <t>上期所原油主力合约连续第二个交易日封涨停，现涨12%，报572.3元/桶。</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>sz003009</t>
+          <t>sz301158</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>中天火箭</t>
+          <t>德石股份</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>75.13</v>
+        <v>37.44</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I45" s="2" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>军工+商业航天|公司是国内少数掌握固体火箭发动机复合材料核心技术的主要企业之一，研制的固体火箭发动机耐烧蚀组件先后为国内多个型号的固体火箭产品成功配套，商业航天业务主要集中在军用耐烧蚀组件产品板块。</t>
+          <t>油气设服|公司主要从事油气钻井专用工具及设备的研发、生产、销售及租赁，开展定向钻井、水平钻井的工程技术服务，业务涵盖石油、天然气、页岩气、煤层气、地热能钻井及定向穿越工程。公司是国内重要的螺杆钻具制造商之一，国内重要的井口装置制造商之一，产品已覆盖国内陆上及海上油气田。</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>军工, 商业航天</t>
+          <t>油气设服</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>军工</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>0.27</v>
+        <v>4.84</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>华泰证券发布航天军工板块2026年度展望研报称，复盘“十四五”，军工体量迈上新台阶；展望“十五五”，或将由“量”的增值转向“质”的提升。</t>
+          <t>上期所原油主力合约连续第二个交易日封涨停，现涨12%，报572.3元/桶。</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>sz002389</t>
+          <t>sz002629</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>航天彩虹</t>
+          <t>仁智股份</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>26.54</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I46" s="2" t="inlineStr"/>
+        <v>10.04</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>无人机|中国航天科技集团旗下上市公司，是我国首家以无人机为主营业务的上市公司，产品在原有新材料产品的基础上，增加彩虹-3、彩虹-4和彩虹-5等中大型察打一体无人机产品以及射手系列导弹，形成多元化的产品结构。</t>
+          <t>油气设服|公司系具有钻井液技术服务、井下作业技术服务、环保治理技术服务等多个油服产业的综合性油服公司。公司从事油田化学品与功能新材料的研发、生产与销售，产品广泛应用于石油天然气开发多个领域，已取得中石化、中石油市场准入资质。</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>无人机</t>
+          <t>油气设服</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>军工</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>0.27</v>
+        <v>4.84</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>华泰证券发布航天军工板块2026年度展望研报称，复盘“十四五”，军工体量迈上新台阶；展望“十五五”，或将由“量”的增值转向“质”的提升。</t>
+          <t>上期所原油主力合约连续第二个交易日封涨停，现涨12%，报572.3元/桶。</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>sh600435</t>
+          <t>sh600583</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>北方导航</t>
+          <t>海油工程</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>18.87</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="I47" s="2" t="inlineStr"/>
+        <v>9.959999999999999</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>军工|中国兵器工业集团旗下上市公司，军民两用产品业务以“导航控制和弹药信息化技术”为主，涵盖制导控制、导航控制、探测控制、环境控制、稳定控制、电台及卫星通信、电连接器等产品和技术。公司是以军品二三四级配套为主的制造型企业，军品以导航控制、弹药信息化系统、短波电台和卫星通信系统、军用电连接器等领域的整机、核心部件为主要产品。</t>
+          <t>油气设服|国内惟一一家集海洋石油、天然气开发工程设计、陆地制造和海上安装、调试、维修以及液化天然气工程于一体的大型工程总承包公司，是亚太地区最大的海洋石油工程EPCI（设计、采办、建造、安装）总承包商之一。</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>军工</t>
+          <t>油气设服</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>甲醇</t>
+          <t>油气设服</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>3.97</v>
+        <v>4.84</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>美伊冲突对全球化工行业形成重大影响，伊朗是全球重要的化肥生产国和出口国，甲醇供应占全球10%，尿素出口量位居世界前列。</t>
+          <t>上期所原油主力合约连续第二个交易日封涨停，现涨12%，报572.3元/桶。</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>sz000035</t>
+          <t>920158.BJ</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>中国天楹</t>
+          <t>长江能科</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>7.71</v>
+        <v>23.79</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>绿色甲醇|公司依托吉林辽源和黑龙江安达等风光储氢氨醇一体化项目投资建设，打造涵盖绿色甲醇、绿氨、SAF 等多元化氢基能源产品生产线，形成规模化的绿色燃料供应能力。
-2026年2月26日公司在投资者关系活动记录表中透露，公司目前已与国际头部能源巨头签订了全球首单电制甲醇供货订单，标志着公司绿色甲醇产品正式进入国际主流能源企业供应体系。</t>
+          <t>油气设服|长江能科为电脱设备行业龙头，市场占有率全国第一，国内“三桶油”均为公司的大客户。公司主要产品包括电脱设备、分离设备、换热设备、存储设备、固碳设备、氢能设备等能源化工专用设备以及助剂和技术服务，广泛应用于油气工程、炼油化工、海洋工程、清洁能源等领域。</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>绿色甲醇</t>
+          <t>油气设服</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>甲醇</t>
+          <t>航运港口</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>3.97</v>
+        <v>4.89</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>美伊冲突对全球化工行业形成重大影响，伊朗是全球重要的化肥生产国和出口国，甲醇供应占全球10%，尿素出口量位居世界前列。</t>
+          <t>波罗的海交易所数据显示，3月2日，VLCC中东到中国TD3C航线的TCE单日上涨94%到42万美元/天，各航线平均TCE跳涨58%至28万美元/天。</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>sh600227</t>
+          <t>sh601872</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">赤天化  </t>
+          <t>招商轮船</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>3.17</v>
+        <v>19.65</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>10.07</v>
+        <v>10.02</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>4天2板</t>
+          <t>8天5板</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>甲醇|煤制甲醇，全资子公司桐梓化工拥有甲醇产能30万吨/年。</t>
+          <t>油运|公司主要从事国际原油运输、国际干散货运输业务，并通过持股50%的CLNG公司（另一持股50%的股东为中远海能下属的大连中远海运油品运输有限公司）投资经营国际LNG运输业务。</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>甲醇</t>
+          <t>油运</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>甲醇</t>
+          <t>航运港口</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>3.97</v>
+        <v>4.89</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>美伊冲突对全球化工行业形成重大影响，伊朗是全球重要的化肥生产国和出口国，甲醇供应占全球10%，尿素出口量位居世界前列。</t>
+          <t>波罗的海交易所数据显示，3月2日，VLCC中东到中国TD3C航线的TCE单日上涨94%到42万美元/天，各航线平均TCE跳涨58%至28万美元/天。</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>sh600722</t>
+          <t>sh600026</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>金牛化工</t>
+          <t>中远海能</t>
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>10.32</v>
+        <v>24.9</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I50" s="2" t="inlineStr"/>
+        <v>9.98</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>8天4板</t>
+        </is>
+      </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>甲醇|公司的主要业务为甲醇的生产和销售，产品方式为焦炉气制甲醇。公司的主要业务由持股50%的控股子公司金牛旭阳经营，金牛旭阳拥有的甲醇生产能力为20万吨/年。</t>
+          <t>油运|公司主营业务为从事国际和中国沿海原油及成品油运输、国际液化天然气(LNG)运输以及国际化学品运输，是中国沿海原油和成品油运输领域的龙头企业。</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>甲醇</t>
+          <t>油运</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>甲醇</t>
+          <t>航运港口</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>3.97</v>
+        <v>4.89</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>美伊冲突对全球化工行业形成重大影响，伊朗是全球重要的化肥生产国和出口国，甲醇供应占全球10%，尿素出口量位居世界前列。</t>
+          <t>波罗的海交易所数据显示，3月2日，VLCC中东到中国TD3C航线的TCE单日上涨94%到42万美元/天，各航线平均TCE跳涨58%至28万美元/天。</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>sz002109</t>
+          <t>sh601975</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>兴化股份</t>
+          <t>招商南油</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>4.84</v>
+        <v>4.97</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I51" s="2" t="inlineStr"/>
+        <v>9.959999999999999</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>6天3板</t>
+        </is>
+      </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>甲醇|全资子公司兴化化工主营煤制甲醇，产能30万吨/年。</t>
+          <t>油运|公司是招商局集团旗下从事油轮运输的专业化公司，市场定位为全球石化产品的运输服务商。</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>甲醇</t>
+          <t>油运</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>甲醇</t>
+          <t>航运港口</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>3.97</v>
+        <v>4.89</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>美伊冲突对全球化工行业形成重大影响，伊朗是全球重要的化肥生产国和出口国，甲醇供应占全球10%，尿素出口量位居世界前列。</t>
+          <t>波罗的海交易所数据显示，3月2日，VLCC中东到中国TD3C航线的TCE单日上涨94%到42万美元/天，各航线平均TCE跳涨58%至28万美元/天。</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>sz000912</t>
+          <t>sz002040</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>泸天化</t>
+          <t>南 京 港</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>5.35</v>
+        <v>13.17</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="I52" s="2" t="inlineStr"/>
+        <v>10.03</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>甲醇|天然气制甲醇，子公司绿源醇从事甲醇业务，拥有甲醇产能70万吨/年。</t>
+          <t>港口|中国内河最大的石油、液体化工产品中转港之一。本集团的主要经营业务为：提供原油、成品油、液体化工产品及普通货物的装卸、仓储服务。</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>甲醇</t>
+          <t>港口</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>甲醇</t>
+          <t>航运港口</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>3.97</v>
+        <v>4.89</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>美伊冲突对全球化工行业形成重大影响，伊朗是全球重要的化肥生产国和出口国，甲醇供应占全球10%，尿素出口量位居世界前列。</t>
+          <t>波罗的海交易所数据显示，3月2日，VLCC中东到中国TD3C航线的TCE单日上涨94%到42万美元/天，各航线平均TCE跳涨58%至28万美元/天。</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>sh600989</t>
+          <t>sh600798</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>宝丰能源</t>
+          <t>宁波海运</t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>26.32</v>
+        <v>4.64</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>9.99</v>
+        <v>9.950000000000001</v>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>甲醇|公司于2019年10月8日公告，募投项目焦炭气化制60万吨/年烯烃产品段一次开车成功；焦炭气化制220万吨/年甲醇项目进度已达80%，预计于2019年底前投产。</t>
+          <t>航运|公司的主营业务为国际、沿海和长江航线的航运业务、船舶代理业务及干散货货运代理业务。公司提供近洋、内贸、内支集装箱航线运输服务，经营航线33条，周均航班132班次，覆盖国内外39个主要港口。</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>甲醇</t>
+          <t>航运</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>航运港口</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>0.06999999999999999</v>
+        <v>4.89</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>LightCounting上调了对800G和1.6T光模块出货量的预测——2026年800G光模块出货量将增长一倍以上，1.6T光模块出货量则从2025年的小基数增长至数千万端口。</t>
+          <t>波罗的海交易所数据显示，3月2日，VLCC中东到中国TD3C航线的TCE单日上涨94%到42万美元/天，各航线平均TCE跳涨58%至28万美元/天。</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>sz002980</t>
+          <t>sh601022</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>华盛昌</t>
+          <t>宁波远洋</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>31.87</v>
+        <v>11.24</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.98</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>并购重组+光通信|华盛昌公告称，公司拟以现金方式收购深圳市伽蓝特科技有限公司100%股权，整体估值暂定为4.6亿元。伽蓝特专注于仪器仪表测试测量行业中的光通信模块和光芯片测试领域。</t>
+          <t>航运|公司是一家综合性航运公司，主要从事国际、沿海和长江航线的航运业务、船舶代理业务及干散货货运代理业务。</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>并购重组, 光通信</t>
+          <t>航运</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>航运港口</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>0.06999999999999999</v>
+        <v>4.89</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>LightCounting上调了对800G和1.6T光模块出货量的预测——2026年800G光模块出货量将增长一倍以上，1.6T光模块出货量则从2025年的小基数增长至数千万端口。</t>
+          <t>波罗的海交易所数据显示，3月2日，VLCC中东到中国TD3C航线的TCE单日上涨94%到42万美元/天，各航线平均TCE跳涨58%至28万美元/天。</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>sh603738</t>
+          <t>sh601866</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>泰晶科技</t>
+          <t>中远海发</t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>23.96</v>
+        <v>3.25</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.17</v>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>光通信|公司针对光通信200G、400G、800G、1.6T市场推出了高基频、高精度、低相噪CMOS、LVDS差分输出时钟解决方案，随着光模块传输速率升级，对应使用超高频、差分时钟产品，在技术上提出更高性能匹配要求。</t>
+          <t>航运|公司打造以航运及相关产业租赁、集装箱制造、投资及服务业务为核心的产业集群，建立产融结合、融融结合、多种业务协同发展的“一站式”航运金融服务平台。</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>航运</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>航运港口</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>0.06999999999999999</v>
+        <v>4.89</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>LightCounting上调了对800G和1.6T光模块出货量的预测——2026年800G光模块出货量将增长一倍以上，1.6T光模块出货量则从2025年的小基数增长至数千万端口。</t>
+          <t>波罗的海交易所数据显示，3月2日，VLCC中东到中国TD3C航线的TCE单日上涨94%到42万美元/天，各航线平均TCE跳涨58%至28万美元/天。</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>sz301338</t>
+          <t>920571.BJ</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>凯格精机</t>
+          <t>国航远洋</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>179.65</v>
+        <v>16.23</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>20</v>
+        <v>29.94</v>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>PCB+光模块设备|1.公司的锡膏印刷设备、点胶设备及柔性自动化设备应用于电子工业制造领域的电子装联环节，一般用到PCB、FPC和电子元器件的地方均会涉及到电子装联，下游可应用于消费电子、汽车电子、网络通讯、航空航天、医疗器械、智能家居等行业的生产制造。
-2.2024年2月26日公司在互动平台表示，公司主要从事自动化精密装备的研发、生产、销售及技术支持服务，公司产品可以应用于光模块领域部分电子装联环节和封装环节。</t>
+          <t>航运|公司主要从事国际远洋、国内沿海和长江中下游航线的干散货运输业务，是国内干散货运输的大型航运企业之一，拥有与业务相关的国际船舶运输经营权、国际海运辅助业经营权、水路运输经营权、水路运输服务经营权等业务资质。</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>PCB, 光模块设备</t>
+          <t>航运</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>航运港口</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>0.06999999999999999</v>
+        <v>4.89</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>LightCounting上调了对800G和1.6T光模块出货量的预测——2026年800G光模块出货量将增长一倍以上，1.6T光模块出货量则从2025年的小基数增长至数千万端口。</t>
+          <t>波罗的海交易所数据显示，3月2日，VLCC中东到中国TD3C航线的TCE单日上涨94%到42万美元/天，各航线平均TCE跳涨58%至28万美元/天。</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>sz001267</t>
+          <t>sh601083</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>汇绿生态</t>
+          <t>锦江航运</t>
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>33.55</v>
+        <v>13.73</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>10</v>
+        <v>10.02</v>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>光通信|公司旗下钧恒科技是专业从事高端光通信产品的研制、生产及推广的高新技术企业，拥有从光学组件，光电转换模块，光端机及子系统的行业垂直整合能力，能够为客户提供各种特定应用的定制化产品，包括PLCC、Mini SFF、Micro Pod等各种形态及各种复合协议的光端机及波分复用子系统。</t>
+          <t>航运|公司是一家综合性航运公司，主要从事国际、国内海上集装箱运输业务，多年来持续深耕东北亚、东南亚和国内航线。</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>航运</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>石油</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>0.06999999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>LightCounting上调了对800G和1.6T光模块出货量的预测——2026年800G光模块出货量将增长一倍以上，1.6T光模块出货量则从2025年的小基数增长至数千万端口。</t>
+          <t>上期所原油主力合约连续第二个交易日封涨停，现涨12%，报572.3元/桶。</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>sh603011</t>
+          <t>sh603353</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>合锻智能</t>
+          <t>和顺石油</t>
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>28.28</v>
+        <v>50.97</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I58" s="2" t="inlineStr"/>
+        <v>9.99</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>核聚变+光通信|1.公司在聚变堆核心部件制造领域取得突破性进展，顺利启动BEST真空室制造工作，在成型、焊接及检测工艺取得阶段性成果。
-2.参股27.18%的合肥汇智提供400G及以下光模块的结构件给光通信厂商 。</t>
+          <t>成品油批发零售|公司是湖南省第一家获国家商务部批准取得成品油批发资质的民营石油企业，主营成品油批发零售，业务涵盖成品油采购、仓储、物流、批发、零售环节，在成品油流通领域形成完整产业链。</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>核聚变, 光通信</t>
+          <t>成品油批发零售</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>石油</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>0.06999999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>LightCounting上调了对800G和1.6T光模块出货量的预测——2026年800G光模块出货量将增长一倍以上，1.6T光模块出货量则从2025年的小基数增长至数千万端口。</t>
+          <t>上期所原油主力合约连续第二个交易日封涨停，现涨12%，报572.3元/桶。</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>sh603083</t>
+          <t>sz000554</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>剑桥科技</t>
+          <t>泰山石油</t>
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>113.74</v>
+        <v>10.85</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I59" s="2" t="inlineStr"/>
+        <v>10.04</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>6天3板</t>
+        </is>
+      </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>光模块|公司系全球高速光组件和光模块技术领先企业，2019年通过收购美国Lumentum公司旗下的Oclaro日本公司的部分资产及技术转移，加上在上海和美国培养发展的两个光电子研发中心，公司又进一步在高速光模块，特别是基于最新PAM4调制技术的400G和800G以及硅光技术的光模块、400G和800G LPO线性直驱光模块领域成为领先公司之一。</t>
+          <t>成品油批发零售|中石化旗下上市公司，主要从事成品油批发零售，车用天然气加气业务以及非油品业务。公司是山东省泰安市成油品、车用天然气的最大经销商。</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>光模块</t>
+          <t>成品油批发零售</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>石油</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>-0.9299999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>美伊冲突对全球化工行业形成重大影响，伊朗是全球重要的化肥生产国和出口国，甲醇供应占全球10%，尿素出口量位居世界前列。</t>
+          <t>上期所原油主力合约连续第二个交易日封涨停，现涨12%，报572.3元/桶。</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>sz000510</t>
+          <t>sh601857</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>新金路</t>
+          <t>中国石油</t>
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>22.45</v>
+        <v>13.15</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>10</v>
+        <v>10.04</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
@@ -3258,486 +3305,506 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>化工+有色|1.公司主要从事氯碱化工、电石、PVC软制品的生产经营及仓储、物流等经营、运输业务，其中，氯碱化工是公司核心业务，主要产品包括PVC树脂、烧碱、钾碱、电石等。
-2.旗下栗木矿业已取得了广西壮族自治区应急管理厅出具的《关于广西有色栗木矿业有限公司桂林矿产地质研究院栗木钽铌锡多金属矿（60万t/a采矿改建项目）安全设施设计审查意见书》，同意公司栗木钽铌锡多金属矿一期60万t/a采矿改建项目安全设施设计。</t>
+          <t>油气|集团是我国油气行业占主导地位的最大的油气生产和销售商，世界最大的石油公司之一。</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>化工, 有色</t>
+          <t>油气</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>石油</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>-0.9299999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>美伊冲突对全球化工行业形成重大影响，伊朗是全球重要的化肥生产国和出口国，甲醇供应占全球10%，尿素出口量位居世界前列。</t>
+          <t>上期所原油主力合约连续第二个交易日封涨停，现涨12%，报572.3元/桶。</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>sh600714</t>
+          <t>sh600938</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>金瑞矿业</t>
+          <t>中国海油</t>
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>19.76</v>
+        <v>43.41</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I61" s="2" t="inlineStr"/>
+        <v>10.01</v>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>锶盐|公司主营业务为锶盐系列产品的生产和销售。主要产品包括碳酸锶（含工业级碳酸锶、电子级碳酸锶）、金属锶、铝锶合金、硝酸锶、氢氧化锶和副产品硫磺、亚硫酸钠。</t>
+          <t>油气|公司为中国最大之海上原油及天然气生产商，亦为全球最大之独立油气勘探及生产企业之一，主要业务为勘探、开发、生产及销售原油和天然气。</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>锶盐</t>
+          <t>油气</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>石油</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>-0.9299999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>美伊冲突对全球化工行业形成重大影响，伊朗是全球重要的化肥生产国和出口国，甲醇供应占全球10%，尿素出口量位居世界前列。</t>
+          <t>上期所原油主力合约连续第二个交易日封涨停，现涨12%，报572.3元/桶。</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>sh600367</t>
+          <t>sh600688</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>红星发展</t>
+          <t>上海石化</t>
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>23.55</v>
+        <v>3.84</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I62" s="2" t="inlineStr"/>
+        <v>10.03</v>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>钡盐+锶盐|公司主要业务是钡盐、锶盐和锰系产品的研发、生产和销售。公司钡盐、锶盐生产能力在全国排名第一，碳酸钡和碳酸锶市场占有率分别达到40%和30%。</t>
+          <t>炼油|中国最大的炼油化工一体化综合性石油化工企业之一，具有较强的整体规模实力，是中国重要的成品油、中间石化产品、合成树脂和合成纤维生产企业。</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>钡盐, 锶盐</t>
+          <t>炼油</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>石油</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>-0.9299999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>美伊冲突对全球化工行业形成重大影响，伊朗是全球重要的化肥生产国和出口国，甲醇供应占全球10%，尿素出口量位居世界前列。</t>
+          <t>上期所原油主力合约连续第二个交易日封涨停，现涨12%，报572.3元/桶。</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>sz000637</t>
+          <t>sh600256</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>茂化实华</t>
+          <t>广汇能源</t>
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>5.42</v>
+        <v>7.12</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>9.94</v>
-      </c>
-      <c r="I63" s="2" t="inlineStr"/>
+        <v>10.05</v>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>石油化工|公司属于石油化工行业，主要经营范围是石油化工产品的生产及销售，主要产品是液化石油气、聚丙烯、醋酸仲丁酯、MTBE、特种白油、乙醇胺、聚合级异丁烷、丙烷等。</t>
+          <t>油气|公司已形成以煤炭、LNG、醇醚、煤焦油、石油为核心产品，以能源物流为支撑的天然气液化、煤炭开采、煤化工转换、油气勘探开发四大业务板块，是国内唯一一家同时拥有煤、气、油三种资源的民营企业。</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>石油化工</t>
+          <t>油气</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>石油</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>-0.9299999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>美伊冲突对全球化工行业形成重大影响，伊朗是全球重要的化肥生产国和出口国，甲醇供应占全球10%，尿素出口量位居世界前列。</t>
+          <t>上期所原油主力合约连续第二个交易日封涨停，现涨12%，报572.3元/桶。</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>sz002545</t>
+          <t>sz000096</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>东方铁塔</t>
+          <t>广聚能源</t>
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>29.96</v>
+        <v>13.27</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I64" s="2" t="inlineStr"/>
+        <v>10.03</v>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>化肥|四川省汇元达钾肥有限责任公司之全资子公司老挝开元矿业有限公司在老挝境内拥有141平方公里的钾盐矿开采权，其中已经开采中的老挝甘蒙省龙湖矿区西段41.69平方公里矿区保有资源储量矿石量119,902.75万吨，氯化钾资源储量21,763.10万吨，矿藏储量十分丰富。老挝开元目前的产能为年产50万吨氯化钾，为老挝境内现存产能最大的氯化钾生产企业，产品主要销往中国、印度和越南、泰国、马来西亚、新加坡等东南亚国家。</t>
+          <t>成品油批发零售|公司是深圳市和珠江三角洲地区成品油主要经销者之一，成品油批发零售、化学品贸易、电力投资是公司重要的业务构成。</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>化肥</t>
+          <t>成品油批发零售</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>航运港口</t>
+          <t>石油</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>3.23</v>
+        <v>8.18</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>近期，油运市场火爆，VLCC日租金冲高，已突破20万美元/天，创近六年新高。</t>
+          <t>上期所原油主力合约连续第二个交易日封涨停，现涨12%，报572.3元/桶。</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>sh601872</t>
+          <t>sh600028</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>招商轮船</t>
+          <t>中国石化</t>
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>17.86</v>
+        <v>7.82</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>7天4板</t>
-        </is>
-      </c>
+        <v>9.99</v>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>油运|公司主要从事国际原油运输、国际干散货运输业务，并通过持股50%的CLNG公司（另一持股50%的股东为中远海能下属的大连中远海运油品运输有限公司）投资经营国际LNG运输业务。</t>
+          <t>油气|公司是中国大型油气生产商，炼油能力排名中国第一位，在中国拥有完善的成品油销售网络，是中国最大的成品油供应商。</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>油运</t>
+          <t>油气</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>航运港口</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>3.23</v>
+        <v>-3.19</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>近期，油运市场火爆，VLCC日租金冲高，已突破20万美元/天，创近六年新高。</t>
+          <t>美伊冲突对全球化工行业形成重大影响，伊朗是全球重要的化肥生产国和出口国，甲醇供应占全球10%，尿素出口量位居世界前列。</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>sz002040</t>
+          <t>sh600722</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>南 京 港</t>
+          <t>金牛化工</t>
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>11.97</v>
+        <v>11.35</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I66" s="2" t="inlineStr"/>
+        <v>9.98</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>12天6板</t>
+        </is>
+      </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>港口|中国内河最大的石油、液体化工产品中转港之一。本集团的主要经营业务为：提供原油、成品油、液体化工产品及普通货物的装卸、仓储服务。</t>
+          <t>甲醇|公司的主要业务为甲醇的生产和销售，产品方式为焦炉气制甲醇。公司的主要业务由持股50%的控股子公司金牛旭阳经营，金牛旭阳拥有的甲醇生产能力为20万吨/年。</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>甲醇</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>航运港口</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>3.23</v>
+        <v>-3.19</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>近期，油运市场火爆，VLCC日租金冲高，已突破20万美元/天，创近六年新高。</t>
+          <t>美伊冲突对全球化工行业形成重大影响，伊朗是全球重要的化肥生产国和出口国，甲醇供应占全球10%，尿素出口量位居世界前列。</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>sh601975</t>
+          <t>sh600714</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>招商南油</t>
+          <t>金瑞矿业</t>
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>4.52</v>
+        <v>21.74</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="I67" s="2" t="inlineStr"/>
+        <v>10.02</v>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>6天3板</t>
+        </is>
+      </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>油运|公司是招商局集团旗下从事油轮运输的专业化公司，市场定位为全球石化产品的运输服务商。</t>
+          <t>锶盐|公司主营业务为锶盐系列产品的生产和销售。主要产品包括碳酸锶（含工业级碳酸锶、电子级碳酸锶）、金属锶、铝锶合金、硝酸锶、氢氧化锶和副产品硫磺、亚硫酸钠。</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>油运</t>
+          <t>锶盐</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>航运港口</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>3.23</v>
+        <v>-3.19</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>近期，油运市场火爆，VLCC日租金冲高，已突破20万美元/天，创近六年新高。</t>
+          <t>美伊冲突对全球化工行业形成重大影响，伊朗是全球重要的化肥生产国和出口国，甲醇供应占全球10%，尿素出口量位居世界前列。</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>sh600026</t>
+          <t>sh600367</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>中远海能</t>
+          <t>红星发展</t>
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>22.64</v>
+        <v>25.91</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I68" s="2" t="inlineStr"/>
+        <v>10.02</v>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>油运|公司主营业务为从事国际和中国沿海原油及成品油运输、国际液化天然气(LNG)运输以及国际化学品运输，是中国沿海原油和成品油运输领域的龙头企业。</t>
+          <t>锶盐|公司主要业务是钡盐、锶盐和锰系产品的研发、生产和销售。公司钡盐、锶盐生产能力在全国排名第一，碳酸钡和碳酸锶市场占有率分别达到40%和30%。</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>油运</t>
+          <t>锶盐</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>天然气</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>4.41</v>
+        <v>-3.19</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>在美国和以色列袭击伊朗后，伊朗宣布关闭霍尔木兹海峡航道，多个油轮船东、交易商已暂停经这一海峡运输原油、燃料及液化天然气。</t>
+          <t>美伊冲突对全球化工行业形成重大影响，伊朗是全球重要的化肥生产国和出口国，甲醇供应占全球10%，尿素出口量位居世界前列。</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>sh603318</t>
+          <t>sz000301</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>水发燃气</t>
+          <t>东方盛虹</t>
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>8.82</v>
+        <v>14.58</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.04</v>
+      </c>
+      <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>天然气|公司是燃气输配和燃气应用领域（以天然气发电为主）的成套设备供应商，未来公司将实现从上游液化天然气生产，到中游燃气装备为主的高端制造，再到下游燃气应用领域的分布式能源和城镇燃气供应的全产业链，多维度发展。</t>
+          <t>化工|公司拥有PTA产能390万吨/年，下游主要用于生产涤纶长丝产品。</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>天然气</t>
+          <t>化工</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>天然气</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>4.41</v>
+        <v>-3.19</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>在美国和以色列袭击伊朗后，伊朗宣布关闭霍尔木兹海峡航道，多个油轮船东、交易商已暂停经这一海峡运输原油、燃料及液化天然气。</t>
+          <t>美伊冲突对全球化工行业形成重大影响，伊朗是全球重要的化肥生产国和出口国，甲醇供应占全球10%，尿素出口量位居世界前列。</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>sz000968</t>
+          <t>sz300839</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>蓝焰控股</t>
+          <t>博汇股份</t>
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>9.460000000000001</v>
+        <v>17.2</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>10</v>
+        <v>20.03</v>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>天然气|山西煤层气龙头，A股唯一煤层气标的，市占率第二，煤层气抽采量14.33亿方，销售量7亿方，运营近3400口煤层井。</t>
+          <t xml:space="preserve">石油化工|公司专注于燃料油深加工细分领域，致力于化工新材料细分领域的技术研究及创新，聚焦提质增效，加快产业一体化发展，实现“减油增化”，以缔造绿色化工新材料的领军者为使命，创造绿色石化新空间。公司主要业务为研发、生产、销售应用于多领域的特种芳烃系列产品，具有年产40万吨环保芳烃油和年产40万吨重芳烃的生产能力。
+</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>天然气</t>
+          <t>石油化工</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>天然气</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>4.41</v>
+        <v>-4.41</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>在美国和以色列袭击伊朗后，伊朗宣布关闭霍尔木兹海峡航道，多个油轮船东、交易商已暂停经这一海峡运输原油、燃料及液化天然气。</t>
+          <t>英伟达同意向两家开发数据中心光学技术的企业总计投资40亿美元，这类技术对人工智能系统至关重要。</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
@@ -3745,44 +3812,48 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>sh603393</t>
+          <t>sz002980</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>新天然气</t>
+          <t>华盛昌</t>
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>37.48</v>
+        <v>35.06</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>10.01</v>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>天然气|公司是新疆主要的城镇燃气经营企业，主要从事城市天然气的输配、销售、入户安装以及煤层气开采业务。公司取得了乌鲁木齐市高新区（新市区）、库车市、焉耆县、博湖县及和硕县等五个市（区、县）天然气市场的长期经营权。</t>
+          <t>并购重组+光通信|华盛昌公告称，公司拟以现金方式收购深圳市伽蓝特科技有限公司100%股权，整体估值暂定为4.6亿元。伽蓝特专注于仪器仪表测试测量行业中的光通信模块和光芯片测试领域。</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>天然气</t>
+          <t>并购重组, 光通信</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>0.9299999999999999</v>
+        <v>-4.41</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>在AI算力需求驱动下，光纤行业正步入景气周期，市场出现明显涨价现象。以G.652.D单模光纤为例，其价格已从去年低点的18至19元/芯公里，上涨至目前最高约50元/芯公里。</t>
+          <t>英伟达同意向两家开发数据中心光学技术的企业总计投资40亿美元，这类技术对人工智能系统至关重要。</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
@@ -3790,28 +3861,28 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>sz000890</t>
+          <t>sz002491</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>法尔胜</t>
+          <t>通鼎互联</t>
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>8.43</v>
+        <v>12.23</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>10.05</v>
+        <v>9.98</v>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>6天5板</t>
+          <t>6天3板</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆|公司参股的普天法尔胜光通信有限公司主要产品为光纤预制棒、光纤、光缆，上述产品可以应用于在运营商基础网络通信及广播电视通信领域。</t>
+          <t>光纤光缆|公司光电通信业务板块的产品和解决方案主要涵盖光电线缆和光通信设备两大领域，光电线缆领域的具体产品包括光纤预制棒、光纤、光缆、通信电缆、铁路信号缆、电力电缆等。</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -3823,15 +3894,15 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>0.9299999999999999</v>
+        <v>-4.41</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>在AI算力需求驱动下，光纤行业正步入景气周期，市场出现明显涨价现象。以G.652.D单模光纤为例，其价格已从去年低点的18至19元/芯公里，上涨至目前最高约50元/芯公里。</t>
+          <t>英伟达同意向两家开发数据中心光学技术的企业总计投资40亿美元，这类技术对人工智能系统至关重要。</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
@@ -3839,1018 +3910,592 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>sh600498</t>
+          <t>sz002957</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>烽火通信</t>
+          <t>科瑞技术</t>
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>56.71</v>
+        <v>31.67</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆+商业航天|1.公司系光通信行业领先企业，产品围绕光通信全产业链布局，是我国最早从事光通信传输设备、光纤光缆科研、生产的企业，已跻身全球光传输与网络接入设备、光纤光缆最具竞争力企业10强。
-2.公司全面进军卫星光通信领域，低轨星载路由(天基IP网)与星间激光通信（天基传送网）已成为公司布局卫星互联网的关键突破口，成功研发面向低轨卫星平台的高集成度、低功耗星上路由交换系统。</t>
+          <t>光通信设备|公司已为国内外大客户批量交付光通信模组生产设备。</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆, 商业航天</t>
+          <t>光通信设备</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>储能</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>0.9299999999999999</v>
+        <v>-3.17</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>在AI算力需求驱动下，光纤行业正步入景气周期，市场出现明显涨价现象。以G.652.D单模光纤为例，其价格已从去年低点的18至19元/芯公里，上涨至目前最高约50元/芯公里。</t>
+          <t>东吴证券发布研报称，展望2026年海外户储行业，考虑澳洲补贴+新老政策过渡、乌克兰灾后重建生存刚需、英国百亿补贴刺激下户储需求爆发，户储成长空间大。</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>sz000070</t>
+          <t>sz002350</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>特发信息</t>
+          <t>北京科锐</t>
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>19.66</v>
+        <v>13.08</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I74" s="2" t="inlineStr"/>
+        <v>10.01</v>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>4天3板</t>
+        </is>
+      </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆+算力租赁|1.公司拥有华南地区规模最大的光纤光缆研制、生产及检测基地，在海外市场方面，谷歌是其客户。
-2.公司除自营数据中心项目外，还曾承接鹏城云脑二期项目Atlas900 AI计算集群及通用计算与存储系统的建设集成项目、许昌市中原人工智能计算中心项目工程总承包项目以及国家超级计算深圳中心（深圳云计算中心）一楼机房建设设备购置项目等。</t>
+          <t>储能|公司控股子公司杭州平旦科技有限公司是国内较早开展储能业务的科技企业，其储能EMS（能量管理系统）产品在2016年投入到了商业化应用中。目前其储能技术包括储能EMS系统、储能BMS系统（含梯次应用BMS）、储能集装箱集成、储能电池柜集成、储能电站集成技术等。</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆, 算力租赁</t>
+          <t>储能</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>储能</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>-1.34</v>
+        <v>-3.17</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>国家电网宣布“十五五”期间将投运15项特高压直流工程，较“十四五”期间近乎翻倍。</t>
+          <t>东吴证券发布研报称，展望2026年海外户储行业，考虑澳洲补贴+新老政策过渡、乌克兰灾后重建生存刚需、英国百亿补贴刺激下户储需求爆发，户储成长空间大。</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>sh603897</t>
+          <t>sz002506</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>长城科技</t>
+          <t>协鑫集成</t>
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>33.7</v>
+        <v>5.16</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.02</v>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>电网设备|公司自成立以来专注于电磁线业务领域，是目前国内同类产品的主要制造商之一。</t>
+          <t>光伏+储能|公司致力于打造成全球领先的绿色能源系统集成商，产品覆盖高效电池、大尺寸光伏组件、储能系统等，并为客户提供智慧光储一体化集成方案，包含绿色能源工程相关的产品设计、定制、生产、安装、销售等一揽子服务内容。公司近年新建合肥、芜湖、阜宁电池组件基地，已具备12GW N型TOPCon电池产能、近30GW高效组件产能。</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>电网设备</t>
+          <t>光伏, 储能</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>-1.34</v>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>国家电网宣布“十五五”期间将投运15项特高压直流工程，较“十四五”期间近乎翻倍。</t>
-        </is>
-      </c>
+        <v>-3.2</v>
+      </c>
+      <c r="C76" s="2" t="inlineStr"/>
       <c r="D76" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>sz002380</t>
+          <t>sh600777</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>科远智慧</t>
+          <t xml:space="preserve">*ST新潮 </t>
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>35.74</v>
+        <v>4.9</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I76" s="2" t="inlineStr"/>
+        <v>4.93</v>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>智能电网|公司控股子公司南京磐控微型电网技术有限公司从事微型电网工程规划、设计、调试、技术咨询、技术服务；微型电网专用设备研发、生产等业务。</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>智能电网</t>
-        </is>
-      </c>
+          <t>ST股 | 公司在美国德克萨斯州拥有Hoople油田资产（常规油田）、Howard和Borden油田资产（页岩油藏）两处油田资产；公司主营业务为：石油及天然气的勘探、开采和销售。</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>-1.34</v>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>国家电网宣布“十五五”期间将投运15项特高压直流工程，较“十四五”期间近乎翻倍。</t>
-        </is>
-      </c>
+        <v>-3.2</v>
+      </c>
+      <c r="C77" s="2" t="inlineStr"/>
       <c r="D77" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>sh603861</t>
+          <t>sh600381</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>白云电器</t>
+          <t xml:space="preserve">*ST春天 </t>
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>20.49</v>
+        <v>3.02</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>9.98</v>
+        <v>4.859999999999999</v>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>数据中心电源|公司长期为数据中心行业提供产品和服务,已经形成服务智能算力领域领先的电力能源解决方案能力,主要产品包括中低压开关柜、UPS 配电、变压器、母线槽、动力配电箱、精密列头柜等供配电系统设备,产品已经应用于中国联通粤港澳大湾区枢纽(韶关)数据中心、佛山开普勒数据中心、腾龙亦庄云计算数据中心、明蔚京西云计算数据中心等众多项目。</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>数据中心电源</t>
-        </is>
-      </c>
+          <t>ST股 | 在大健康业务方面，公司已基本完成了涵盖保健食品、药品等冬虫夏草高效利用产品的储备和战略布局。</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>国家能源局发布通知，决定将安徽省淮南市风光热储融合系统友好型新能源电站项目等43个项目、河北省张家口市等10个城市列为新型电力系统建设能力提升试点（第一批）。</t>
-        </is>
-      </c>
+        <v>-3.2</v>
+      </c>
+      <c r="C78" s="2" t="inlineStr"/>
       <c r="D78" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>sh600452</t>
+          <t>sz002808</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>涪陵电力</t>
+          <t>*ST恒久</t>
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>14.61</v>
+        <v>4.87</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>4.96</v>
+      </c>
+      <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>电力|公司主营业务为电力供应业务、配电网节能业务。公司作为一家从事输、配、售电业务一体化经营的电力企业，公司在现有的供电区域内拥有完善的供电网网络，能够为供电辖区提供优质、可靠的供电服务，保证了对辖区电力供应的市场优势，具有较强的竞争优势。</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>电力</t>
-        </is>
-      </c>
+          <t>ST股 | 公司的控股子公司福建省闽保信息技术有限公司是一家从事信息安全领域软件开发及系统集成的高新技术企业。</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>国家能源局发布通知，决定将安徽省淮南市风光热储融合系统友好型新能源电站项目等43个项目、河北省张家口市等10个城市列为新型电力系统建设能力提升试点（第一批）。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr"/>
       <c r="D79" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>sh600236</t>
+          <t>sh600108</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>桂冠电力</t>
+          <t>亚盛集团</t>
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>9.779999999999999</v>
+        <v>4.81</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I79" s="2" t="inlineStr"/>
+        <v>10.07</v>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>电力|公司主要投资建设、经营以电力生产、销售为主业的电力能源项目，水电、风电、光伏等清洁能源占公司在役装机容量的89.79%，水电装机容量达1023.54万千瓦，是公司主要盈利来源。</t>
+          <t>农业|1.公司2026年3月2日公告，目前未开展矿产相关业务，也不存在需要披露的相关重大信息。
+2.公司主要种植经营啤酒花、马铃薯、牧草、果品、药材、食葵、辣椒、枸杞、香辛料等初级农产品和加工产品，以及生产经营节水灌溉设备。</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>农业</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>液冷IDC</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="n">
-        <v>-0.9299999999999999</v>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>上周，英伟达AI基础设施负责人Dion Harris在加州总部向媒体展示了下一代Vera Rubin算力系统的内部构成与供应链细节。由于功耗上升，Vera Rubin也是英伟达首个100%液冷散热的系统。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr"/>
       <c r="D80" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>sz001400</t>
+          <t>sz301302</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>江顺科技</t>
+          <t>华如科技</t>
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>133.45</v>
+        <v>35.66</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>10</v>
+        <v>19.99</v>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>3天2板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>液冷+商业航天|1.子公司江宇科技主要从事用于服务器液冷相关的3D打印产品的研发工作，已有部分样品。
-2.公司产品铝型材挤压模具和铝型材挤压配套设备应用于航空航天领域。</t>
+          <t>AI+军工|公司模训器材业务以实战化、智能化训练需求为牵引，运用AI、仿真、XR、网络、传感器、高精度定位等技术手段，构建实战化对抗训练装备体系，为受训人员提供高逼真战场环境和对手，全面提升受训人员实战化能力。</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>液冷, 商业航天</t>
+          <t>AI, 军工</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>液冷IDC</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="n">
-        <v>-0.9299999999999999</v>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>上周，英伟达AI基础设施负责人Dion Harris在加州总部向媒体展示了下一代Vera Rubin算力系统的内部构成与供应链细节。由于功耗上升，Vera Rubin也是英伟达首个100%液冷散热的系统。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr"/>
       <c r="D81" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>sz002536</t>
+          <t>sz001269</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>飞龙股份</t>
+          <t>欧晶科技</t>
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>34.65</v>
+        <v>26.03</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>10</v>
+        <v>10.02</v>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">液冷服务器|公司电子泵及温控阀系列产品可以应用在服务器液冷领域。
-</t>
+          <t>下修原料采购金额|欧晶科技与矽比科北美公司签署的原材料高纯石英砂的采购协议总金额从3.5亿美元下修至2.7亿美元。</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>液冷服务器</t>
+          <t>下修原料采购金额</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="n">
-        <v>-1.63</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C82" s="2" t="inlineStr"/>
       <c r="D82" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>sh603268</t>
+          <t>sh603616</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST松发 </t>
+          <t>韩建河山</t>
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>115.59</v>
+        <v>8.17</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>9天7板</t>
-        </is>
-      </c>
+        <v>9.959999999999999</v>
+      </c>
+      <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 拟收购恒力重工主营船舶及高端装备的研发、生产及销售，已确定排产新造船舶140艘，货值约108亿美元，船型包含散货船、VLCC、VLOC 和集装箱船等。</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr"/>
+          <t>并购重组+PEEK|韩建河山公告称，拟发行股份及支付现金购买兴福新材99.9978%股份，并向不超过35名符合条件的特定投资者发行股份募集配套资金，股票复牌。本次交易完成后，公司主营业务新增芳香族产品的研发、生产和销售。兴福新材是一家专注于芳香族产品的研发、生产和销售的高新技术企业，主要产品包括新一代特种工程塑料聚醚醚酮（PEEK）中间体、农药及医药中间体和PEEK纯化业务等。</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>并购重组, PEEK</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="n">
-        <v>-1.63</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C83" s="2" t="inlineStr"/>
       <c r="D83" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>sh600525</t>
+          <t>sz002952</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST长园  </t>
+          <t>亚世光电</t>
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>5.42</v>
+        <v>24.43</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>4天3板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 子公司长园光波导技术（珠海）有限公司主要从事光学方案相关检测设备及制程设备的市场与技术布局。</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr"/>
+          <t>AI眼镜|公司的主营业务为研发、设计、生产和销售定制化液晶显示器及电子纸显示模组等光电显示产品，目前已有产品应用于智能眼镜及智能手表屏。</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>AI眼镜</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="n">
-        <v>-1.63</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C84" s="2" t="inlineStr"/>
       <c r="D84" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>sz002485</t>
+          <t>sh603139</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>ST雪发</t>
+          <t>康惠股份</t>
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>5.34</v>
+        <v>28.13</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.01</v>
+      </c>
+      <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司文旅项目地处一线旅游目的地黄金地段，历史文化底蕴深厚，旅游资源丰富，市场潜力较大。</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr"/>
+          <t>中药|公司主要从事中成药品的研究、开发、生产与销售，共有3个药品生产基地，主要产品涵盖呼吸感冒类疾病、妇科类疾病、皮肤科类疾病、骨科类疾病等领域，主营产品中复方双花片、坤复康胶囊（片）、消银颗粒及附桂骨痛胶囊列入国家医保目录；消银颗粒与枣仁安神颗粒列入国家基本药物目录。</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>中药</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="n">
-        <v>-1.63</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C85" s="2" t="inlineStr"/>
       <c r="D85" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>sh600777</t>
+          <t>sh603778</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST新潮 </t>
+          <t>国晟科技</t>
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>4.67</v>
+        <v>15.51</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司在美国德克萨斯州拥有Hoople油田资产（常规油田）、Howard和Borden油田资产（页岩油藏）两处油田资产；公司主营业务为：石油及天然气的勘探、开采和销售。</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr"/>
+          <t>光伏+并购重组|1.公司目前从事大尺寸高效异质结光伏电池的研发、生产、销售，以及异质结、TOPCON、PERC等电池组件的生产与销售。控股孙公司恒立聚能涉及钙钛矿研究。
+2.国晟科技公告称，公司拟以2.406亿元的价格受让正豪科技、林琴合计持有的孚悦科技100%股权。交易完成后，公司将持有标的公司100%股权，标的公司将纳入公司合并报表。孚悦科技主要从事高精密度新型锂电池结构件的研发、生产和销售。</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>光伏, 并购重组</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="n">
-        <v>-1.63</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C86" s="2" t="inlineStr"/>
       <c r="D86" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>sz000697</t>
+          <t>sh600403</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>ST炼石</t>
+          <t>大有能源</t>
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>10.05</v>
+        <v>7.88</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.06</v>
+      </c>
+      <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST股 | 公司主要业务为航空制造业，构建“铼元素-高温合金-单晶叶片-航空零部件-航空发动机-大型无人机整机”完整的产业链。 </t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="n">
-        <v>-1.63</v>
-      </c>
-      <c r="C87" s="2" t="inlineStr"/>
-      <c r="D87" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>sh603838</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">*ST四通 </t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="n">
-        <v>8.470000000000001</v>
-      </c>
-      <c r="H87" s="2" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 公司是一家集研发、设计、生产、销售于一体的新型家居生活陶瓷供应商，产品覆盖日用陶瓷、卫生陶瓷、艺术陶瓷、建筑装饰等全系列家居生活用瓷。</t>
-        </is>
-      </c>
-      <c r="K87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr"/>
-      <c r="D88" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>sz002843</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>泰嘉股份</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="H88" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>6天4板</t>
-        </is>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>服务器电源+华为|1.公司电源业务包含一部分数据中心电源业务，主要为服务器电源模块产品。服务客户为行业头部品牌客户。
-2.问界的户用充电桩现由泰嘉股份旗下雅达电子独家供应。</t>
-        </is>
-      </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>服务器电源, 华为</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr"/>
-      <c r="D89" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>sh603950</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>长源东谷</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="n">
-        <v>48.96</v>
-      </c>
-      <c r="H89" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>7天4板</t>
-        </is>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>发电机零部件|2025年1月10日公告，公司与玉柴集团子公司金创公司共同出资成立合资公司玉柴长源科技，玉柴长源科技将聚焦算力中心发动机缸体零部件、船电、汽车零部件等核心业务的制造加工与研发。</t>
-        </is>
-      </c>
-      <c r="K89" s="2" t="inlineStr">
-        <is>
-          <t>发电机零部件</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr"/>
-      <c r="D90" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>sz002356</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>赫美集团</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="H90" s="2" t="n">
-        <v>9.950000000000001</v>
-      </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>氢能+跨境电商|1.公司控股子公司氢云科技在氢能源应用领域进行投入运营；公司旗下鹏飞氢美定位于氢能源战略的控股投资平台，下设子公司聚能新燃料，主要负责综合能源站的建设与运营，为终端客户提供LNG、汽柴油、氢气等加注服务。
-2.公司定位于“国际品牌运营的服务商”，主要业务为国际品牌服装、鞋帽、箱包等产品的零售，公司运营的品牌既包含国际知名品牌MCM、Fular、Pinko、Radley、AspinalOfLondon等，也包含自营品牌Oblu，经营业态有品牌专营店和奥莱店等，主要分布于北京、上海、南京、郑州、三亚、合肥等主要城市。</t>
-        </is>
-      </c>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>氢能, 跨境电商</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr"/>
-      <c r="D91" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>sh603629</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>利通电子</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="n">
-        <v>64.37</v>
-      </c>
-      <c r="H91" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>算力租赁|公司目前对外出租AI算力规模已达10000P以上，其中，约4000P是以自有算力（报表中在固定资产科目列示）出租，其余是转租算力（在使用权资产科目列示）出租。</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>算力租赁</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr"/>
-      <c r="D92" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>sh603115</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>海星股份</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="n">
-        <v>30.91</v>
-      </c>
-      <c r="H92" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>MLPC电容器|公司主营产品电极箔可应用于MLPC电容器。MLPC产品可广泛应用于服务器中高功耗芯片的供电滤波场景，特别是CPU和GPU的核心电压供电。</t>
-        </is>
-      </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>MLPC电容器</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr"/>
-      <c r="D93" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>sz002432</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>九安医疗</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="n">
-        <v>48.83</v>
-      </c>
-      <c r="H93" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>医疗器械+kimi|1.公司是一家在国内外具有影响力的个人健康管理产品供应商，主要从事家用医疗器械的研发、生产及销售。
-2.公司通过认购砺思资本基金份额参股Kimi。</t>
-        </is>
-      </c>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>医疗器械, kimi</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr"/>
-      <c r="D94" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>sh688307</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>中润光学</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="n">
-        <v>60.02</v>
-      </c>
-      <c r="H94" s="2" t="n">
-        <v>19.99</v>
-      </c>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>半导体设备|子公司戴斯光端研发的2D/3D光学AOI检测模主要应用于半导体检测、电路板检测以及其他工业检测场合。</t>
-        </is>
-      </c>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>半导体设备</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr"/>
-      <c r="D95" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>sh605117</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>德业股份</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="n">
-        <v>114.95</v>
-      </c>
-      <c r="H95" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>逆变器|公司拥有储能逆变器、组串式并网逆变器和微型并网逆变器12组系列产品。</t>
-        </is>
-      </c>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t>逆变器</t>
+          <t>煤炭|公司的主要产品为长焰煤、焦煤、贫煤、洗精煤、气煤。截止2024年末，公司煤炭资源量11.23亿吨，可采储量6.02亿吨，证实储量2.6亿吨。</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4896,12 +4541,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sz002843</t>
+          <t>sh603318</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>泰嘉股份</t>
+          <t>水发燃气</t>
         </is>
       </c>
     </row>
@@ -4911,42 +4556,42 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sh603950</t>
+          <t>sh600108</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>长源东谷</t>
+          <t>亚盛集团</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sz000035</t>
+          <t>sz002980</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>中国天楹</t>
+          <t>华盛昌</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sh603318</t>
+          <t>sh603353</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>水发燃气</t>
+          <t>和顺石油</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4601,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sh600108</t>
+          <t>sz300191</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>亚盛集团</t>
+          <t>潜能恒信</t>
         </is>
       </c>
     </row>
@@ -4971,12 +4616,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sz002842</t>
+          <t>sz002207</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>翔鹭钨业</t>
+          <t>准油股份</t>
         </is>
       </c>
     </row>
@@ -4986,12 +4631,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>sh600498</t>
+          <t>sh601808</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>烽火通信</t>
+          <t>中海油服</t>
         </is>
       </c>
     </row>
@@ -5001,12 +4646,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>sz000960</t>
+          <t>sh600256</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>锡业股份</t>
+          <t>广汇能源</t>
         </is>
       </c>
     </row>
@@ -5016,12 +4661,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>sz002356</t>
+          <t>sz002490</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>赫美集团</t>
+          <t>山东墨龙</t>
         </is>
       </c>
     </row>
@@ -5031,12 +4676,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>sz002980</t>
+          <t>sh601975</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>华盛昌</t>
+          <t>招商南油</t>
         </is>
       </c>
     </row>
@@ -5046,12 +4691,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>sh603257</t>
+          <t>sh601872</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>中国瑞林</t>
+          <t>招商轮船</t>
         </is>
       </c>
     </row>
@@ -5061,12 +4706,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>sh600301</t>
+          <t>sh600583</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>华锡有色</t>
+          <t>海油工程</t>
         </is>
       </c>
     </row>
@@ -5076,12 +4721,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>sh600259</t>
+          <t>sz002828</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>中稀有色</t>
+          <t>贝肯能源</t>
         </is>
       </c>
     </row>
@@ -5091,12 +4736,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>sz000510</t>
+          <t>sh600367</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>新金路</t>
+          <t>红星发展</t>
         </is>
       </c>
     </row>
@@ -5106,12 +4751,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>sh600452</t>
+          <t>sz300157</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>涪陵电力</t>
+          <t>新锦动力</t>
         </is>
       </c>
     </row>
@@ -5121,12 +4766,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>sh603629</t>
+          <t>sh601857</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>利通电子</t>
+          <t>中国石油</t>
         </is>
       </c>
     </row>
@@ -5136,12 +4781,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>sh603738</t>
+          <t>sh600871</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>泰晶科技</t>
+          <t>石化油服</t>
         </is>
       </c>
     </row>
@@ -5151,12 +4796,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>sz002155</t>
+          <t>sh600759</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>湖南黄金</t>
+          <t>洲际油气</t>
         </is>
       </c>
     </row>
@@ -5166,12 +4811,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>sh603353</t>
+          <t>sz000096</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>和顺石油</t>
+          <t>广聚能源</t>
         </is>
       </c>
     </row>
@@ -5181,12 +4826,267 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>sh603897</t>
+          <t>sz002554</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>长城科技</t>
+          <t>惠博普</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>sz301302</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>华如科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>sh600938</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>中国海油</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>sh600339</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>中油工程</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>sh603619</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>中曼石油</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>sh600968</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>海油发展</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>sz300164</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>通源石油</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>sz000968</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>蓝焰控股</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>sz002040</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>南 京 港</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>sz301158</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>德石股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>sz000554</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>泰山石油</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>sh600026</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>中远海能</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>920088.BJ</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>科力股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>sh600722</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>金牛化工</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>sh600688</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>上海石化</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>sz002629</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>仁智股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>sh603727</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">博迈科  </t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>sh600714</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>金瑞矿业</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,20 +476,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="85" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="102" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="232" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="385" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -552,404 +552,393 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>MLED</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2.9</v>
+        <v>9.16</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>据The Information报道，过去数月内，美国三大区域电网运营商相继获批了总计750亿美元的输电扩容项目。</t>
+          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>sh603530</t>
+          <t>sz300323</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>神马电力</t>
+          <t>华灿光电</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>67.20999999999999</v>
+        <v>10.25</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>5天3板</t>
-        </is>
-      </c>
+        <v>20.02</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>电网设备|国际知名的电力系统复合外绝缘产品研制企业与国内电力设备用橡胶密封件龙头企业，从事电力系统变电站复合外绝缘、输配电线路复合外绝缘和橡胶密封件等产品的研发、生产与销售。</t>
+          <t>MLED|公司是行业内最早开展Mini/Micro技术研发的芯片企业之一，率先解决Mini LED在COB应用的分光和高灰阶的显示问题，并自2019年开始，Mini LED芯片产品在行业内率先实现批量生产与销售。公司Mini LED产品采用行业领先的倒装芯片结构及LED芯片衬底转移技术，芯片产品具有整体良率及可靠性高，光色一致性好等优势，获得国内外主流终端显示客户的认可。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>电网设备</t>
+          <t>MLED</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>MLED</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2.9</v>
+        <v>9.16</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>据The Information报道，过去数月内，美国三大区域电网运营商相继获批了总计750亿美元的输电扩容项目。</t>
+          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sh603618</t>
+          <t>sz002429</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>杭电股份</t>
+          <t>兆驰股份</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>20.59</v>
+        <v>10.22</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>10.01</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>电缆+光纤光缆|1.公司电线电缆板块主要从事电线电缆的研发、生产、销售和服务。主要产品为涵盖从超高压、高压到中低压的各类电力电缆、导线、民用线缆及特种电缆。
-2.公司光通信板块主要由富春江光电及其子公司从事经营，其主要从事光通信产业链中光纤预制棒、光纤、光缆、光通信相关设备等产品研发、生产、销售和服务。公司具备光通信“光棒—光纤—光缆”一体化产业链。</t>
+          <t>MLED+AI漫剧|1.2019年12月，公司计划在南昌市高新技术产业开发区投资建设红黄光LED外延、芯片及Mini LED、Micro LED项目。项目一期计划投资人民币10亿元用于红黄光LED外延及芯片的研发、生产和销售，计划于2020年相关设备安装调试到位并正式投入运营。面对未来红黄光LED市场需求的迅速崛起，兆驰半导体拟于南昌高新区投资建设红黄光LED项目，完善LED外延及芯片的品类及应用领域，预计投产后年产能（折合4寸片）可达120万片。
+2.公司旗下风行在线已形成短带长、长改短、AI漫剧、AI小说四大核心业务，其中短带长、长改短均位居行业第一，短视频推广业务位居抖音、快手行业第一。在创作端，依托橙星梦工厂、小剪刀等AI工具，覆盖AI漫剧、短剧、小说等多元内容的快速生成与影视二创需求，已聚集1.5万创作者，日活达2000以上，并积累超1万部剧本。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>电缆, 光纤光缆</t>
+          <t>MLED, AI漫剧</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>MLED</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2.9</v>
+        <v>9.16</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>据The Information报道，过去数月内，美国三大区域电网运营商相继获批了总计750亿美元的输电扩容项目。</t>
+          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sz000533</t>
+          <t>sz002449</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>顺钠股份</t>
+          <t>国星光电</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>12.3</v>
+        <v>8.76</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>10.02</v>
+        <v>10.05</v>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>核聚变+电网设备|1.公司研制的特殊用途干式变压器包括国际热核聚变实验堆（ITER）试验平台变压器。
-2.公司控股孙公司顺特设备在超算中心和数据中心这两个领域提供过干式变压器产品，曾向阿里巴巴、秦淮数据有限公司、万国数据服务有限公司、数据港股份有限公司等客户提供过变压器设备。</t>
+          <t>MLED|公司于2022年5月19日公告，与华为技术有限公司签订全面合作协议，共同推动联合创新中心落地并挂牌，在Mini &amp; Micro LED、LED背光及显示模组、直显RGB器件、车载HUD、智能健康照明、光耦及功率器件、非视觉光源等方面开展深度创新合作。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>核聚变, 电网设备</t>
+          <t>MLED</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>MLED</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2.9</v>
+        <v>9.16</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>据The Information报道，过去数月内，美国三大区域电网运营商相继获批了总计750亿美元的输电扩容项目。</t>
+          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sz002339</t>
+          <t>sh600703</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>积成电子</t>
+          <t>三安光电</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>11.54</v>
+        <v>16.13</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>10.01</v>
+        <v>10.03</v>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>电网设备|公司在电力自动化领域产品线覆盖了电力系统发、输、变、配、用、调度各环节，是国内少数几家能够提供电力自动化整体解决方案的厂家之一。</t>
+          <t>MLED|公司于2021年9月29日晚发布021年度非公开发行A股股票预案，拟募资79亿元用于湖北三安光电有限公司Mini/Micro显示产业化项目和补充流动资金。Mini/Micro显示产业化项目总投资120亿元，达产后，新增氮化镓Mini/Micro LED芯片161万片/年、砷化镓Mini/Micro LED芯片75万片/年（均以4寸为当量片）和4K显示屏用封装产品8.4万台/年的生产能力。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>电网设备</t>
+          <t>MLED</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>MLED</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>2.9</v>
+        <v>9.16</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>据The Information报道，过去数月内，美国三大区域电网运营商相继获批了总计750亿美元的输电扩容项目。</t>
+          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sz300265</t>
+          <t>sz000727</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>通光线缆</t>
+          <t>冠捷科技</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>17.88</v>
+        <v>2.73</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>20</v>
+        <v>10.08</v>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆+特高压|1.公司主营产品包括装备线缆、光纤光缆、输电线缆三大类别，主要从事以高压、超高压和特高压为主的输电线路用电力特种光缆和导线、通信用光纤光缆、航空航天用耐高温电缆等。
-2.公司生产的OPGW成功运用于国家电网公司第一条交流750千伏超高压示范工程线路、第一条直流±800千伏特高压示范工程线路、第一条交流1,000千伏特高压示范工程线路、南方电网公司第一条500千伏超高压工程线路等国家重点示范工程。公司电力光缆产品市场占有率连续多年位居前列。</t>
+          <t>MLED|公司2021年7月22日在互动平台表示，公司已有数款使用Mini-LED背光技术的电视和高端电竞显示产品实现量产，部分产品目前已有线上购买渠道。同时，公司也已在小间距LED显示产品上积极布局了Mini-LED技术。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆, 特高压</t>
+          <t>MLED</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>MLED</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2.9</v>
+        <v>9.16</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>据The Information报道，过去数月内，美国三大区域电网运营商相继获批了总计750亿美元的输电扩容项目。</t>
+          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sz002498</t>
+          <t>sz002983</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>汉缆股份</t>
+          <t>芯瑞达</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>8.130000000000001</v>
+        <v>25.41</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>电缆|公司是集电缆及附件系统、状态检测系统、输变电工程总包三个板块于一体，研发生产经营的技术密集型企业集团。</t>
+          <t xml:space="preserve">MLED|公司2022年8月23日在互动平台表示，公司一直深耕新型显示领域，在研的Micro LED技术项目可应用于VR/AR显示终端，目前尚未转换为订单，请广大投资者注意风险。 </t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>电缆</t>
+          <t>MLED</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>MLED</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2.9</v>
+        <v>9.16</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>据The Information报道，过去数月内，美国三大区域电网运营商相继获批了总计750亿美元的输电扩容项目。</t>
+          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sz002885</t>
+          <t>sz300162</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>京泉华</t>
+          <t>雷曼光电</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>31.92</v>
+        <v>9.48</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>9.99</v>
+        <v>20</v>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IDC电源|公司有部分磁性器件及电源类产品可应用于数据中心、算力中心的供电解决方案中。
-</t>
+          <t>MLED|公司自主研发的基于COB的Micro LED超高清显示技术作为新型显示技术，可应用于大尺寸的高端专业显示、商业显示及民用显示领域，Micro LED也可以应用于小尺寸的VR、AR显示，手表等可穿戴设备显示领域，公司目前主要专注于大尺寸的Micro LED超高清显示产品。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>IDC电源</t>
+          <t>MLED</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>MLED</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>2.9</v>
+        <v>9.16</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>据The Information报道，过去数月内，美国三大区域电网运营商相继获批了总计750亿美元的输电扩容项目。</t>
+          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sz300617</t>
+          <t>sh603773</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>安靠智电</t>
+          <t>沃格光电</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>64.81</v>
+        <v>39.67</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>20</v>
+        <v>10.01</v>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>IDC电源|公司GIL和智慧模块化变电站可运用于数据中心，2022年中标腾讯仪征东升云计算数据中心项目，该项目已于2023年5月顺利交付。</t>
+          <t>MLED|2022年2月21日公告，拟设立江西德虹显示技术有限公司投资新建“玻璃基材的Mini/MicroLED基板生产项目”，项目总投资金额预计为16.5亿元。该项目拟新建6万平方米厂房，项目完全达产的建设周期约为24个月。项目实施建成后，将实现生产玻璃基材的Mini/MicroLED基板总产能524万㎡/年。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>IDC电源</t>
+          <t>MLED</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>MLED</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2.9</v>
+        <v>9.16</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>据The Information报道，过去数月内，美国三大区域电网运营商相继获批了总计750亿美元的输电扩容项目。</t>
+          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sz300880</t>
+          <t>sz300269</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>迦南智能</t>
+          <t>联建光电</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>23.22</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>20</v>
@@ -957,823 +946,809 @@
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>智能电网|公司是一家专业从事智能电表、用电信息采集终端及电能计量箱等系列产品研发、生产、销售的高新技术企业，主要产品包括单相智能电表、三相智能电表、用电信息采集终端及电能计量箱等。</t>
+          <t>MLED|公司现已在众多技术领域积累了多项国内外领先的核心技术：miniLED显示、正装/倒装发光显示、多合一像素显示技术、SMD高防护面板技术；4K/8K超高清显示控制、HDR高动态范围显示、负电压节能驱动技术、AI智能显示模组校正、X+Y+Z微米级六向微调技术、柔性透明显示技术；LED高分可视化显控技术、LED显示信息安全技术、LED触控交互、LED体感交互、VR/AR+LED显示等。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>MLED</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>MLED</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>2.9</v>
+        <v>9.16</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>据The Information报道，过去数月内，美国三大区域电网运营商相继获批了总计750亿美元的输电扩容项目。</t>
+          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sh601096</t>
+          <t>sz002845</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>宏盛华源</t>
+          <t>同兴达</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>6.28</v>
+        <v>15.7</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>9.98</v>
+        <v>10.02</v>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>特高压|公司主要从事输电线路铁塔的研发，生产和销售，主要产品为全系列电压等级的输电线路铁塔，包含角钢塔，钢管塔，钢管杆，变电构支架。公司控股股东为山东电工，实控人为国务院国资委。</t>
+          <t>MLED|公司2020年7月2日在互动平台表示，关于研发MiniLED模组，公司已有技术储备，具体量产计划根据市场情况待定。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>特高压</t>
+          <t>MLED</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>MLED</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>2.9</v>
+        <v>9.16</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>据The Information报道，过去数月内，美国三大区域电网运营商相继获批了总计750亿美元的输电扩容项目。</t>
+          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sh605196</t>
+          <t>sz300241</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>华通线缆</t>
+          <t>瑞丰光电</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>54.34</v>
+        <v>7.39</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>10</v>
+        <v>19.97</v>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>电缆|公司主要从事电线电缆的研发、生产与销售业务，主导产品包括以进户线为代表的中低压电力电缆，及以潜油泵电缆为代表的电气装备用电缆，广泛应用于电力输配、采矿/油/气等行业，并已获得美国UL、欧盟CE等国际认证，中国CRCC、CCC等国内认证，是我国在电线电缆国际认证，尤其是美国UL认证领域具有数量领先优势的企业之一。</t>
+          <t>MLED|公司2020年5月15日发布创业板非公开发行A股股票预案，拟募资不超6.99亿元投资于全彩表面贴装发光二极管（全彩LED）封装扩产项目，次毫米发光二极管（MiniLED）背光封装生产项目和微型发光二极管（MicroLED）技术研发中心项目，公司顺应行业和技术的发展及时切入Mini LED和设立Micro LED技术研发中心，有利于取得先发优势，把握行业发展的先机。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>电缆</t>
+          <t>MLED</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>MLED</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2.9</v>
+        <v>9.16</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>据The Information报道，过去数月内，美国三大区域电网运营商相继获批了总计750亿美元的输电扩容项目。</t>
+          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sh603045</t>
+          <t>sz000509</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>福达合金</t>
+          <t>华塑控股</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>32.41</v>
+        <v>3.63</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>机器人+电网设备|1.子公司浙江福达合金材料科技有限公司主要经营范围包括智能机器人的研发；智能机器人销售；工业机器人制造；工业机器人销售等。
-2.公司重点进行电接触材料产品研究开发，公司主导产品电接触材料的主要原材料为白银，所掌握的先进的贵金属提取回收技术和工艺，能实现提取高纯度银锭及铜等贵金属资源的循环利用，已建成了年回收800吨银锭的专用厂房和高标准的“三废”处理环保设施并投入量产。</t>
+          <t>MLED|公司积极布局了MiniLED、OLED和高分高刷高色域等显示领域前沿产品技术。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>机器人, 电网设备</t>
+          <t>MLED</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>油气设服</t>
+          <t>MLED</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>-2.94</v>
+        <v>9.16</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>国金证券研报表示，原油市场当前由地缘政治风险驱动，预计高波动率将持续。市场已计入8-10美元/桶地缘风险溢价，持仓结构显示看涨情绪浓厚。</t>
+          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sh600759</t>
+          <t>sz300303</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>洲际油气</t>
+          <t>聚飞光电</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>8.26</v>
+        <v>12.53</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>7天5板</t>
-        </is>
-      </c>
+        <v>20.02</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>油气设服|公司是以勘探开发为主的国际化独立石油公司，目前公司的运营区块主要集中在哈萨克斯坦，主力在产项目马腾油田和克山油田均位于哈萨克斯坦滨里海盆地，是国际公认的油气富集的区域之一。</t>
+          <t>MLED|公司于2019年11月接待机构调研时透露，MiniLED是公司拓展的一项新业务，目前处于小批量送样阶段。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>油气设服</t>
+          <t>MLED</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>油气设服</t>
+          <t>MLED</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>-2.94</v>
+        <v>9.16</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>国金证券研报表示，原油市场当前由地缘政治风险驱动，预计高波动率将持续。市场已计入8-10美元/桶地缘风险溢价，持仓结构显示看涨情绪浓厚。</t>
+          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sh603318</t>
+          <t>sz000536</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>水发燃气</t>
+          <t>华映科技</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>10.67</v>
+        <v>4.74</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>4天4板</t>
-        </is>
-      </c>
+        <v>9.98</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>油气设服|公司主要从事燃气发电相关的燃气输配和燃气应用领域相关产品的设计、生产、销售和服务，为天然气输配提供压力调节系统和天然气发电提供预处理系统。产品包括燃气输配系统、燃气应用系统和备品备件三大类。</t>
+          <t>MLED|2023年3月18日公告，公司与兆元光电签订合资协议，共同投资设立一家合资公司，为在Micro LED/MiniLED赛道上做前期布局。合资公司注册资本为3.03亿元，其中公司以货币出资1.48亿元，占注册资本比例48.92%。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>油气设服</t>
+          <t>MLED</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>油气设服</t>
+          <t>MLED</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>-2.94</v>
+        <v>9.16</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>国金证券研报表示，原油市场当前由地缘政治风险驱动，预计高波动率将持续。市场已计入8-10美元/桶地缘风险溢价，持仓结构显示看涨情绪浓厚。</t>
+          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sz002490</t>
+          <t>sz000045</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>山东墨龙</t>
+          <t>深纺织Ａ</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>11.72</v>
+        <v>13.2</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7天4板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>油气设服|全产业链石油钻采装备制造商，主要产品包括油气开采用管、流体及结构用管、抽油机、抽油泵、抽油杆、钻机用缸套、阀门散件及大型铸锻件等。公司产品主要用于石油、天然气、煤层气、页岩气等行业。</t>
+          <t>MLED|公司的偏光片产品可用于采用mini LED背光的LCD显示屏。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>油气设服</t>
+          <t>MLED</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>油气设服</t>
+          <t>MLED</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>-2.94</v>
+        <v>9.16</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>国金证券研报表示，原油市场当前由地缘政治风险驱动，预计高波动率将持续。市场已计入8-10美元/桶地缘风险溢价，持仓结构显示看涨情绪浓厚。</t>
+          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sz002207</t>
+          <t>sz002587</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>准油股份</t>
+          <t>奥拓电子</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>15.03</v>
+        <v>7.01</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>7天4板</t>
-        </is>
-      </c>
+        <v>10.05</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>油气设服|公司是为石油、天然气开采企业提供油田动态监测和提高采收率技术服务的专业化企业，已形成油田动态监测资料录取、资料解释研究和应用、治理方案编制、增产措施施工及效果评价等综合技术服务能力，是西部地区实力较强的一体化油田稳产、增产技术服务企业，能够提供油田增产、油田管理和配套建设等“一站式”技术服务。</t>
+          <t>MLED|公司作为国内最早研发MiniLED显示产品的企业，已在全世界范围内申请了30项专利，其中19项已获得授权，推出了行业领先的超小点间距0.78mm的MiniLED显示产品，并在2019ISE上展出全球最大、分辨率最高的8K超高清MiniLED显示屏。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>油气设服</t>
+          <t>MLED</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>油气设服</t>
+          <t>MLED</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>-2.94</v>
+        <v>9.16</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>国金证券研报表示，原油市场当前由地缘政治风险驱动，预计高波动率将持续。市场已计入8-10美元/桶地缘风险溢价，持仓结构显示看涨情绪浓厚。</t>
+          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sh600871</t>
+          <t>sz300389</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>石化油服</t>
+          <t>艾比森</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>4.27</v>
+        <v>20.64</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>7天4板</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>油气设服|最大的综合油气工程与技术服务专业公司，全球油服行业第四，在中国的20多个省，76个盆地，561个区块开展油气工程技术服务；同时海外业务规模不断提高，在38个国家和地区执行364个项目。</t>
+          <t>MLED|2019年，公司在市场上推出了采用IMD四合一集成封装技术的MiniLED产品，实现了真正意义上的高品质量产和应用。目前，公司已将MiniLED技术成熟并应用于多条产品线，包括AX系列、A27 Pro系列以及CR系列等，并在MiniLED开发上申请了专利16项，其中发明专利5项。</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>油气设服</t>
+          <t>MLED</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>存储器</t>
+          <t>MLED</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>1.53</v>
+        <v>9.16</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>佰维存储公告称，1-2月预盈15亿元-18亿元，存储行业供不应求。</t>
+          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sh688525</t>
+          <t>sh688079</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>佰维存储</t>
+          <t xml:space="preserve">美迪凯  </t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>175.99</v>
+        <v>13.82</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>20</v>
+        <v>19.97</v>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>存储芯片|佰维存储公告称，预计2026年1-2月实现营业收入40亿元至45亿元，同比增长340%至395%；归属于上市公司股东的净利润为15亿元至18亿元，同比扭亏为盈。2026年存储行业迎来高度景气周期，AI算力与国产替代驱动DRAM/NAND价格持续上涨，行业供不应求，公司受益显著。</t>
+          <t>MLED|公司的Micro LED产品已全流程制样，产品已经点亮。</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>存储芯片</t>
+          <t>MLED</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>存储器</t>
+          <t>MLED</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1.53</v>
+        <v>9.16</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>佰维存储公告称，1-2月预盈15亿元-18亿元，存储行业供不应求。</t>
+          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sh603175</t>
+          <t>sz300708</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>超颖电子</t>
+          <t>聚灿光电</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>79.64</v>
+        <v>12.52</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>10</v>
+        <v>20.04</v>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>存储芯片|在储存领域，公司产品主要应用于机械硬盘、固态硬盘、内存条等，与全球机械硬盘制造商龙头希捷、西部数据及全球知名固态硬盘制造商海力士等建立了稳定合作。</t>
+          <t>MLED|公司于2022年6月21日披露2022年度向特定对象发行A股股票预案，拟定增募资不超12亿元，用于Mini/Micro LED芯片研发及制造扩建项目。项目总投资金额为15.5亿元，建成后，将形成年产720万片Mini/Micro LED芯片产能。</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>存储芯片</t>
+          <t>MLED</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>存储器</t>
+          <t>MLED</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>1.53</v>
+        <v>9.16</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>佰维存储公告称，1-2月预盈15亿元-18亿元，存储行业供不应求。</t>
+          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>sz001309</t>
+          <t>sh688055</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>龙腾光电</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>251.57</v>
+        <v>4.25</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>10</v>
+        <v>20.06</v>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>存储芯片|德明利在投资者关系活动记录表中称，国内外头部科技厂商正大力增加资本支出规模加码AI投入，算力基础设施建设持续扩张，服务器和数据中心的存储需求增长持续提升行业景气度，预计四季度存储价格有望维持上涨趋势。公司SATA SSD主控芯片以及新一代自研SD6.0主控芯片均已经完成了产品验证与客户导入工作，目前已实现批量销售。</t>
+          <t>MLED|公司将Mini LED作为重要核心技术，成功推出最佳分区调光技术Mini LED车载显示屏、笔记本电脑屏及电竞显示屏等产品，同时公司加大对车载Mini LED背光技术不同架构的开发与研究，重点推进其在车载产品上的量产进程，并积极探索Mini LED在游戏、医疗等各类显示应用场景。</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>存储芯片</t>
+          <t>MLED</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>存储器</t>
+          <t>智能电网</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>1.53</v>
+        <v>3.04</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>佰维存储公告称，1-2月预盈15亿元-18亿元，存储行业供不应求。</t>
+          <t>据报道，过去数月内，美国三大区域电网运营商相继获批了总计750亿美元的输电扩容项目，核心是建设一批765千伏超高压线路。</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>sh603316</t>
+          <t>sz000533</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>诚邦股份</t>
+          <t>顺钠股份</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>14.53</v>
+        <v>13.53</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>存储芯片|公司旗下芯存科技主要从事半导体存储器的研发设计、封装测试、生产和销售，已量产并销售的主要产品为移动存储（包括TFCARD、USB模块等）、固态硬盘（包括SATASSD、PCIESSD、PSSD）等。</t>
+          <t>核聚变+变压器|1.公司研制的特殊用途干式变压器包括国际热核聚变实验堆（ITER）试验平台变压器。
+2.公司控股孙公司顺特设备在超算中心和数据中心这两个领域提供过干式变压器产品，曾向阿里巴巴、秦淮数据有限公司、万国数据服务有限公司、数据港股份有限公司等客户提供过变压器设备。</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>存储芯片</t>
+          <t>核聚变, 变压器</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>智能电网</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>0.8</v>
+        <v>3.04</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>近日，国家能源局组织召开绿色燃料产业发展专题座谈会。会议指出了绿色燃料保障能源安全、降低碳排放、促进新能源非电利用与消纳的三大战略目标。</t>
+          <t>据报道，过去数月内，美国三大区域电网运营商相继获批了总计750亿美元的输电扩容项目，核心是建设一批765千伏超高压线路。</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>sh600236</t>
+          <t>sz002498</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>桂冠电力</t>
+          <t>汉缆股份</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>10.85</v>
+        <v>8.94</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>10.04</v>
+        <v>9.959999999999999</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3天2板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>绿电|公司主要投资建设、经营以电力生产、销售为主业的电力能源项目，水电、风电、光伏等清洁能源占公司在役装机容量的89.79%，水电装机容量达1023.54万千瓦，是公司主要盈利来源。</t>
+          <t>智能电网|公司是集电缆及附件系统、状态检测系统、输变电工程总包三个板块于一体，研发生产经营的技术密集型企业集团。</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>绿电</t>
+          <t>智能电网</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>智能电网</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>0.8</v>
+        <v>3.04</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>近日，国家能源局组织召开绿色燃料产业发展专题座谈会。会议指出了绿色燃料保障能源安全、降低碳排放、促进新能源非电利用与消纳的三大战略目标。</t>
+          <t>据报道，过去数月内，美国三大区域电网运营商相继获批了总计750亿美元的输电扩容项目，核心是建设一批765千伏超高压线路。</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>sh600821</t>
+          <t>sz002339</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>金开新能</t>
+          <t>积成电子</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>7.87</v>
+        <v>12.69</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>10.07</v>
+        <v>9.969999999999999</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4天2板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>电力+算力租赁|1.公司主营业务为新能源电力的开发、投资、建设及运营，包括光伏发电和风力发电两个板块。
-2.2024年10月8日公告，公司全资子公司金开新能科技有限公司拟于新疆昌吉市投资建设国家超算广州中心新疆分中心昌吉智算中心项目，算力总规模达到5,000PFlops。</t>
+          <t>智能电网|公司在电力自动化领域产品线覆盖了电力系统发、输、变、配、用、调度各环节，是国内少数几家能够提供电力自动化整体解决方案的厂家之一。</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>电力, 算力租赁</t>
+          <t>智能电网</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>智能电网</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0.8</v>
+        <v>3.04</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>近日，国家能源局组织召开绿色燃料产业发展专题座谈会。会议指出了绿色燃料保障能源安全、降低碳排放、促进新能源非电利用与消纳的三大战略目标。</t>
+          <t>据报道，过去数月内，美国三大区域电网运营商相继获批了总计750亿美元的输电扩容项目，核心是建设一批765千伏超高压线路。</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>sz000862</t>
+          <t>sz300265</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>银星能源</t>
+          <t>通光线缆</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>7.34</v>
+        <v>21.46</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>10.04</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
+        <v>20.02</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>绿电|公司新能源发电业务包括风力发电、太阳能光伏发电以及分布式项目发电。</t>
+          <t>电缆|公司生产的OPGW成功运用于国家电网公司第一条交流750千伏超高压示范工程线路、第一条直流±800千伏特高压示范工程线路、第一条交流1,000千伏特高压示范工程线路、南方电网公司第一条500千伏超高压工程线路等国家重点示范工程。公司电力光缆产品市场占有率连续多年位居前列。</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>绿电</t>
+          <t>电缆</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>智能电网</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>0.8</v>
+        <v>3.04</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>近日，国家能源局组织召开绿色燃料产业发展专题座谈会。会议指出了绿色燃料保障能源安全、降低碳排放、促进新能源非电利用与消纳的三大战略目标。</t>
+          <t>据报道，过去数月内，美国三大区域电网运营商相继获批了总计750亿美元的输电扩容项目，核心是建设一批765千伏超高压线路。</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>sh600149</t>
+          <t>sh601179</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>廊坊发展</t>
+          <t>中国西电</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>6.97</v>
+        <v>18.11</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>9.94</v>
+        <v>10.02</v>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>供热+房地产|1.公司是廊坊市国有控股的唯一一家A股上市公司，所从事供热业务具有公用事业显著特征，公司供热经营区域面积超100平方公里，是廊坊市覆盖区域最大的供热企业。
-2.廊坊控股旗下有各类土地资源累计达34万多亩。廊坊控股旗下土地资源大部分来自五个产业园区一级土地开发。</t>
+          <t>电网设备|公司主要经营输配电及控制设备研发、设计、制造、销售、检测、相关设备成套、技术研究、服务与工程承包等业务。</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>供热, 房地产</t>
+          <t>电网设备</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>智能电网</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>-0.62</v>
+        <v>3.04</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>今年以来，互联网巨头开启AI普及化的运动，而近期OpenClaw等Agent应用的兴起，则预示着AI应用正逐步走向2C、2B的场景。</t>
+          <t>据报道，过去数月内，美国三大区域电网运营商相继获批了总计750亿美元的输电扩容项目，核心是建设一批765千伏超高压线路。</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>sh605268</t>
+          <t>sz002857</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>王力安防</t>
+          <t>三晖电气</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>11.52</v>
+        <v>23.75</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>10.03</v>
+        <v>10</v>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>AI应用|公司机器人安全门首创AI遥感解锁，AI智能防夹功能，实现与智能家居互联；自研AI电机驱动算法技术，实现自动开关门，搭载可视智慧猫眼，独创安全G点，关门自动反锁，独创超C级圆柱体专利锁芯。</t>
+          <t>电网设备|公司围绕电网公司“计量资产全寿命周期管理”要求，依托电能表检定这一核心环节的技术优势，以服务于电能表为核心，建立了电能表标准检测设备、电能表自动化流水线型检定系统、电能表智能化仓储系统、用电信息采集系统、互感品等产品，覆盖电能表全生命周期。</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>电网设备</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>-0.62</v>
+        <v>1.69</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>今年以来，互联网巨头开启AI普及化的运动，而近期OpenClaw等Agent应用的兴起，则预示着AI应用正逐步走向2C、2B的场景。</t>
+          <t>情报公司IDTechEx预测，2036年全球人形机器人市场规模将达约295亿美元，汽车制造和物流领域将率先普及，然后再拓展到更广泛的商业和消费市场。</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
@@ -1781,16 +1756,16 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>sz002877</t>
+          <t>sz003036</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>智能自控</t>
+          <t>泰坦股份</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>9.9</v>
+        <v>18.26</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>10</v>
@@ -1798,27 +1773,28 @@
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>AI应用|公司是专业化生产和销售全系列智能控制阀产品的高科技民营企业，坚持先进装备的国产化和技术自主创新。控制阀利用人工智能技术和计算机技术、嵌入式数字解决方案实现智能化，使控制阀具有自适应、自校准、自诊断等功能。数字式阀门定位器普及应用到控制阀和电动执行机构中，从而使得智能一体化设计以及智能化的预测性维护成为未来主流。</t>
+          <t>机器人+固态电池|1.2026年2月2日公司在互动平台表示，公司纺织智能柔性操作机器人研发进展顺利，相关产品目前处于运行测试和进一步优化阶段。
+2.公司设立了控股子公司，主要从事固态电池锂硫磷氯电解质的研发和生产。</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>机器人, 固态电池</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>-0.62</v>
+        <v>1.69</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>今年以来，互联网巨头开启AI普及化的运动，而近期OpenClaw等Agent应用的兴起，则预示着AI应用正逐步走向2C、2B的场景。</t>
+          <t>情报公司IDTechEx预测，2036年全球人形机器人市场规模将达约295亿美元，汽车制造和物流领域将率先普及，然后再拓展到更广泛的商业和消费市场。</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
@@ -1826,45 +1802,45 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>sz301129</t>
+          <t>sz002456</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>瑞纳智能</t>
+          <t>欧菲光</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>29.23</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>19.99</v>
+        <v>10.01</v>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>AI应用+半导体|1.6月26日盘后瑞纳智能公告，公司全资子公司合肥瑞纳智能能源管理有限公司中标“枣庄市薛城区基于数字资产运营管理的AI智慧供热合同能源管理项目”，中标价为2.06亿元。
-2.公司全资子公司合肥高纳半导体科技有限责任公司主要从事第三代半导体 SiC 单晶生长和设备研发、SiC 衬底加工、 SiC 外延生产销售。</t>
+          <t>消费电子+机器人|1.公司是消费电子领域重要的光学光电模组供应商，业务涵盖微摄像头模组、触摸屏和触控显示全贴合模组、指纹识别模组。
+2.公司深入布局机器视觉深度模块方向，参与小米全尺寸人形仿生机器人深度视觉模组开发。</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>AI应用, 半导体</t>
+          <t>消费电子, 机器人</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>-0.62</v>
+        <v>1.69</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>今年以来，互联网巨头开启AI普及化的运动，而近期OpenClaw等Agent应用的兴起，则预示着AI应用正逐步走向2C、2B的场景。</t>
+          <t>情报公司IDTechEx预测，2036年全球人形机器人市场规模将达约295亿美元，汽车制造和物流领域将率先普及，然后再拓展到更广泛的商业和消费市场。</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -1872,29 +1848,30 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>sz002178</t>
+          <t>sz002520</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>延华智能</t>
+          <t>日发精机</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>6.68</v>
+        <v>6.77</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>10.05</v>
+        <v>10.08</v>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>AI医疗|在智慧医疗领域，公司研究开发了HIS系统、智能化电子病历系统、基于微服务的医院信息化集成平台，基于AI的临床辅助诊断系统、全流程医疗质量管理系统、智能决策分析系统、智能导诊系统、城市智慧救护车云服务平台、医疗质量信息管理平台、医院总值班信息系统平台、医护一体化平台等。</t>
+          <t>工业母机+机器人|1.数控机床系公司主营业务之一，公司专业生产数控机床，产品数控化率100%，行业排名第一，全部是市场中高端的普及型数控车床和加工中心。
+2.公司拥有桁架机械手直角坐标机器人方面的专利，并已大量应用到自动化连线设备。</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>AI医疗</t>
+          <t>工业母机, 机器人</t>
         </is>
       </c>
     </row>
@@ -1905,28 +1882,28 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>-0.33</v>
+        <v>1.69</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>全国人大代表，小米集团创始人、董事长兼CEO雷军在今年全国两会提交的建议案中提到加快推动通用人形机器人在智能制造应用。</t>
+          <t>情报公司IDTechEx预测，2036年全球人形机器人市场规模将达约295亿美元，汽车制造和物流领域将率先普及，然后再拓展到更广泛的商业和消费市场。</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>sz001396</t>
+          <t>sh603337</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>誉帆科技</t>
+          <t>杰克科技</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>54.81</v>
+        <v>44.14</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>9.99</v>
@@ -1934,323 +1911,324 @@
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司在排水管道的检测、非开挖修复与清洗领域开展机器人技术的应用及研发。</t>
+          <t>机器人+AI|公司在2024年年报中透露，公司高端产品研发取得里程碑进展，高端AI缝纫机原型样机成功落地，“杰克1号”人形机器人、无人模板机等“机器人+AI人工智能+缝制机械”多技术融合的智能高端产品初具雏形。</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>机器人, AI</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>-0.33</v>
+        <v>1.51</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>全国人大代表，小米集团创始人、董事长兼CEO雷军在今年全国两会提交的建议案中提到加快推动通用人形机器人在智能制造应用。</t>
+          <t>政府工作报告在介绍2026年政府工作任务时提出，深化拓展“人工智能+”，促进新一代智能终端和智能体加快推广，推动重点行业领域人工智能商业化规模化应用。</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>sz002162</t>
+          <t>sh605268</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>悦心健康</t>
+          <t>王力安防</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>6.08</v>
+        <v>12.67</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>9.950000000000001</v>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
+        <v>9.98</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>养老+机器人|公司计划通过技术创新和合作，进一步拓展智慧养老场景，包括且不限于引入或开发养老和辅助机器人、优化智慧养老产品等，以满足老年人多样化的需求。</t>
+          <t>AI+防盗门|公司机器人安全门首创AI遥感解锁，AI智能防夹功能，实现与智能家居互联；自研AI电机驱动算法技术，实现自动开关门，搭载可视智慧猫眼，独创安全G点，关门自动反锁，独创超C级圆柱体专利锁芯。</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>养老, 机器人</t>
+          <t>AI, 防盗门</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>-0.33</v>
+        <v>1.51</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>全国人大代表，小米集团创始人、董事长兼CEO雷军在今年全国两会提交的建议案中提到加快推动通用人形机器人在智能制造应用。</t>
+          <t>政府工作报告在介绍2026年政府工作任务时提出，深化拓展“人工智能+”，促进新一代智能终端和智能体加快推广，推动重点行业领域人工智能商业化规模化应用。</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>sz001282</t>
+          <t>sz002877</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>三联锻造</t>
+          <t>智能自控</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>25.3</v>
+        <v>10.89</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>机器人|2025年4月24日公告，公司拟设立芜湖三联锻造股份有限公司机器人及航空部件研究院分公司，以拓展在机器人和航空航天领域的研发能力。</t>
+          <t>AI+阀门|公司是专业化生产和销售全系列智能控制阀产品的高科技民营企业，坚持先进装备的国产化和技术自主创新。控制阀利用人工智能技术和计算机技术、嵌入式数字解决方案实现智能化，使控制阀具有自适应、自校准、自诊断等功能。数字式阀门定位器普及应用到控制阀和电动执行机构中，从而使得智能一体化设计以及智能化的预测性维护成为未来主流。</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>AI, 阀门</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>农业种植</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>2.91</v>
+        <v>1.51</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>中东地缘冲突扰动全球化肥与粮食供给，国际粮价预期上行。</t>
+          <t>政府工作报告在介绍2026年政府工作任务时提出，深化拓展“人工智能+”，促进新一代智能终端和智能体加快推广，推动重点行业领域人工智能商业化规模化应用。</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>sh600108</t>
+          <t>sz002195</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>亚盛集团</t>
+          <t>岩山科技</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>5.29</v>
+        <v>10.69</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>9.98</v>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>4天4板</t>
-        </is>
-      </c>
+      <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>农业种植|1.公司2026年3月2日公告，目前未开展矿产相关业务，也不存在需要披露的相关重大信息。
-2.公司主要种植经营啤酒花、马铃薯、牧草、果品、药材、食葵、辣椒、枸杞、香辛料等初级农产品和加工产品，以及生产经营节水灌溉设备。</t>
+          <t>脑机接口+AI|1.公司旗下岩思类脑研究院以脑电大数据与脑电大模型为核心技术底座，面向脑科学和人工智能领域的前瞻性研究，开展脑机接口解码算法与系统、非器质性脑疾病（例如癫痫、抑郁症、严重失眠等）的诊断和评估、大脑内在状态调控等方向的科学研究和产品开发，推动研究成果商业化落地。
+2.黑芝麻智能与公司旗下RockAI联合发布基于武当C1200家族芯片的AI Agent解决方案，该方案将部署于未来的智能座舱应用中。</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>农业种植</t>
+          <t>脑机接口, AI</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>农业种植</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>2.91</v>
+        <v>1.51</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>中东地缘冲突扰动全球化肥与粮食供给，国际粮价预期上行。</t>
+          <t>政府工作报告在介绍2026年政府工作任务时提出，深化拓展“人工智能+”，促进新一代智能终端和智能体加快推广，推动重点行业领域人工智能商业化规模化应用。</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sh600313</t>
+          <t>sh688031</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>农发种业</t>
+          <t>星环科技-U</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>9.24</v>
+        <v>223.21</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>种业|公司主营业务的核心为农作物种子业务，产品涵盖玉米、水稻、小麦、棉花、油菜、甘蔗和马铃薯等多种农作物种子（苗），分别由公司所属的河南地神等8家种业子公司开展农作物种子的研发、繁育、生产和销售。</t>
+          <t xml:space="preserve">AI+商业航天|1.公司提供从语料处理、模型训练、知识库建设、应用开发、智能体构建等一整套工具链，致力于开发数据分析的垂直领域大模型，并基于该数据分析垂类大模型，打造数据分析相关智能体。
+2.公司冠名了我国首颗商业红外气象卫星“星环号·南信大星”，“星环号·南信大星”从中国酒泉卫星发射基地发射升空，并顺利进入预定轨道发射任务取得圆满成功。“星环号·南信大星”采用了星环科技自主可控的全栈基础软件产品进行开源产品国产化替代，通过对卫星气象数据进行分析，服务于山火监测、环境保护、能源电力、安全生产、农林渔业、气象、金融等多个领域。 </t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>种业</t>
+          <t>AI, 商业航天</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>无人机</t>
+          <t>石油化工</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Vital Knowledge分析师Adam Crisafulli在报告中表示：“尽管美以军队在该地区占据绝对优势，但他们无法拦截伊朗发射的每一枚廉价导弹和无人机。”</t>
+          <t>郑商所PX、PTA期货主力合约盘中双双触及涨停。</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sz002389</t>
+          <t>sz002986</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>航天彩虹</t>
+          <t>宇新股份</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>28.77</v>
+        <v>16.01</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>3天2板</t>
-        </is>
-      </c>
+        <v>10.03</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>无人机|中国航天科技集团旗下上市公司，是我国首家以无人机为主营业务的上市公司，产品在原有新材料产品的基础上，增加彩虹-3、彩虹-4和彩虹-5等中大型察打一体无人机产品以及射手系列导弹，形成多元化的产品结构。</t>
+          <t>石化|公司立足大亚湾石化区，目前已发展成为华南地区最大的LPG深加工企业。公司主要产品包括以LPG中的异丁烷、异丁烯、正丁烯等组分为原料生产的异辛烷、甲基叔丁基醚，主要用于生产车用成品汽油。</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>无人机</t>
+          <t>石化</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>无人机</t>
+          <t>石油化工</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Vital Knowledge分析师Adam Crisafulli在报告中表示：“尽管美以军队在该地区占据绝对优势，但他们无法拦截伊朗发射的每一枚廉价导弹和无人机。”</t>
+          <t>郑商所PX、PTA期货主力合约盘中双双触及涨停。</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sz002357</t>
+          <t>sh600800</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>富临运业</t>
+          <t>渤海化学</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>16.04</v>
+        <v>4.81</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>10.01</v>
+        <v>10.07</v>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>无人机物流|富临运业与丰翼科技签署合作协议，双方将围绕低空经济领域展开深度合作，共同推动低空物流新业态的发展与创新。丰翼科技为顺丰集团旗下专注于无人机物流与技术产品研发的企业。</t>
+          <t>石化|石化业务为公司的核心业务板块，全资子公司渤海石化一直专注于丙烷制丙烯业务，是京津冀地区最具有话语权的丙烯生产商，下游的丙烯客户涵盖聚丙烯、丁辛醇、环氧丙烷、苯酚丙酮、丙烯酸等行业。</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>无人机物流</t>
+          <t>石化</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>石油化工</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>-0.76</v>
+        <v>1</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>闰土股份公告称，还原物是分散染料的较重要的中间体之一。因近期还原物价格上涨，公司分散染料黑价格近期也已每吨累计上涨约9,000元。</t>
+          <t>郑商所PX、PTA期货主力合约盘中双双触及涨停。</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>sz301373</t>
+          <t>sz300072</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>凌玮科技</t>
+          <t>海新能科</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>49.61</v>
+        <v>5.88</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>20</v>
@@ -2258,406 +2236,1825 @@
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>化工+半导体材料|1.公司的主营业务是纳米二氧化硅新材料的研发、生产、销售，涂层助剂及其他材料的销售。
-2.公司产品已进入精密基材抛光液等新的应用领域。抛光液可用于半导体芯片的CMP抛光以及电子产品精密部件的抛光。</t>
+          <t>石化+生物燃料|1.公司依托自主研发的核心技术和产品，为石化能源与化工行业提供相关工艺技术、净化剂与催化剂、核心设备以及工程服务等综合解决方案，为生态农业和绿色能源提供生物质综合利用解决方案以及新型产品。
+2.公司依托核心催化剂，以公司的悬浮床技术作为核心转化单元，开发了独特的新型生物燃料生产技术，可以为市场提供大量的绿色油品和绿色化工原料，既解决了大量固体废弃生物质无法得到经济、有效利用的问题，又可以形成规模化的绿色能源和循环经济产业，实现显著的二氧化碳减排。</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>化工, 半导体材料</t>
+          <t>石化, 生物燃料</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>石油化工</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>-0.76</v>
+        <v>1</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>闰土股份公告称，还原物是分散染料的较重要的中间体之一。因近期还原物价格上涨，公司分散染料黑价格近期也已每吨累计上涨约9,000元。</t>
+          <t>郑商所PX、PTA期货主力合约盘中双双触及涨停。</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>sz000525</t>
+          <t>sz000703</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>红太阳</t>
+          <t>恒逸石化</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>6.83</v>
+        <v>13.09</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>农药|公司产品范围涵盖除草剂、杀虫剂、杀菌剂、动物营养和三药中间体等系列，拥有草甘膦产能4万吨/年。</t>
+          <t>石化|公司在国内同行中形成独有的“涤纶+锦纶”双纶驱动石化产业链为核心业务，以供应链服务业务为成长业务，差别化纤维产品、工业智能技术应用为新兴业务的“石化+”多层次立体产业布局。</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>农药</t>
+          <t>石化</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>发电机概念</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>0.17</v>
+        <v>2.28</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>银河证券研报指出，主流云厂商2026年资本开支规模持续超预期，GPU性能的提升带动海外光模块速率升级趋势明确，高速率高价值量的光模块放量节奏有望加速。</t>
+          <t>花旗发布研报称，东方电气取得关键战略突破。公司已从加拿大客户获得20台50MW燃气轮机发电机组的里程碑式订单，单价为2亿元人民币，毛利率达40-50%。</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>sz000890</t>
+          <t>sh600875</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>法尔胜</t>
+          <t>东方电气</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>8.869999999999999</v>
+        <v>42.21</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>8天6板</t>
-        </is>
-      </c>
+        <v>10.01</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆|公司参股的普天法尔胜光通信有限公司主要产品为光纤预制棒、光纤、光缆，上述产品可以应用于在运营商基础网络通信及广播电视通信领域。</t>
+          <t>燃气轮机|公司在2025世界清洁能源装备大会上发布了自主研发的首款15兆瓦纯氢燃气轮机。</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>燃气轮机</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>发电机概念</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="C41" s="2" t="inlineStr"/>
+        <v>2.28</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>花旗发布研报称，东方电气取得关键战略突破。公司已从加拿大客户获得20台50MW燃气轮机发电机组的里程碑式订单，单价为2亿元人民币，毛利率达40-50%。</t>
+        </is>
+      </c>
       <c r="D41" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>sz000697</t>
+          <t>sh601727</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>ST炼石</t>
+          <t>上海电气</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>10.23</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>5.029999999999999</v>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>4天3板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST股 | 公司主要业务为航空制造业，构建“铼元素-高温合金-单晶叶片-航空零部件-航空发动机-大型无人机整机”完整的产业链。 </t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr"/>
+          <t>燃气轮机|在燃机领域，公司通过国际并购与技术消化吸收，突破了国外OEM长期以来对燃气轮机研发、服务的壁垒，建立了完整的重型燃气轮机开发设计平台，具备了贯穿燃气轮机全产业链和全生命周期的技术和服务能力。</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>燃气轮机</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>发电机概念</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="C42" s="2" t="inlineStr"/>
+        <v>2.28</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>花旗发布研报称，东方电气取得关键战略突破。公司已从加拿大客户获得20台50MW燃气轮机发电机组的里程碑式订单，单价为2亿元人民币，毛利率达40-50%。</t>
+        </is>
+      </c>
       <c r="D42" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>sz000711</t>
+          <t>sh600590</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>ST京蓝</t>
+          <t>泰豪科技</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>3.82</v>
+        <v>14.71</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>4.95</v>
+        <v>10.02</v>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 主要业务包括流域水生态修复、灌区节水综合系统工程、污水治理、沿河生态景观工程、智慧水务等。</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr"/>
+          <t>柴油发电机|公司所生产的智能应急电源主要应用于应急及备用供电，产品覆盖1-10000KW各类型智能柴（重）油发电机组、拖车电站、静音发电机组等，在工业企业、数据中心、石油化工、通信、高层建筑等诸多领域均有应用。</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>柴油发电机</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr"/>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>三星电子Q1 DRAM价格涨幅从70%上调至100%。此外，佰维存储公告称，预计2026年1-2月实现营业收入40亿元至45亿元，同比增长340%至395%。</t>
+        </is>
+      </c>
       <c r="D43" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>sz002167</t>
+          <t>sh603688</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>东方锆业</t>
+          <t>石英股份</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>16.07</v>
+        <v>53.04</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>锆+黄金|1.全球锆产品品种最齐全的制造商之一，公司产品包括锆矿砂、硅酸锆、氯氧化锆、电熔锆、二氧化锆、复合氧化锆、氧化锆陶瓷结构件及海绵锆八大系列共一百多个品种规格。
-2.2019年，公司参股的澳大利亚上市公司Image对外公告在100%拥有权的勘探权证（E28/1895和E28/2242）上Erayinia勘探区测出高品位黄金。</t>
+          <t>石英+半导体材料|1.公司生产的高纯石英棒是制备石英纤维电子纱（布）关键基础原材料。
+2.公司产品主要有高纯石英砂、石英管、石英棒、石英板、石英筒、石英锭、石英砣等各类高纯石英材料，产品主要应用于光电、光纤、光学、光伏、半导体等领域。</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>锆, 黄金</t>
+          <t>石英, 半导体材料</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr"/>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>三星电子Q1 DRAM价格涨幅从70%上调至100%。此外，佰维存储公告称，预计2026年1-2月实现营业收入40亿元至45亿元，同比增长340%至395%。</t>
+        </is>
+      </c>
       <c r="D44" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>sz000010</t>
+          <t>sz002559</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>美丽生态</t>
+          <t>亚威股份</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>4.42</v>
+        <v>10.47</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>9.950000000000001</v>
+        <v>9.98</v>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>环保|公司主营业务涵盖市政基础设施、公路、景观绿化、房屋建设、生态环保等领域。</t>
+          <t>机器人+存储芯片|1.公司主要产品为数控平板加工机床、普通平板加工机床、数控卷板加工机械。线性和水平多关节机器人供货库卡、徕斯和亚威内部。
+2.公司参股企业苏州芯测全资收购的韩国GSI公司拥有技术难度较高的存储芯片测试机业务，稳定供货于海力士、安靠等行业龙头。</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>环保</t>
+          <t>机器人, 存储芯片</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr"/>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>三星电子Q1 DRAM价格涨幅从70%上调至100%。此外，佰维存储公告称，预计2026年1-2月实现营业收入40亿元至45亿元，同比增长340%至395%。</t>
+        </is>
+      </c>
       <c r="D45" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>sh600545</t>
+          <t>sh603058</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>卓郎智能</t>
+          <t>永吉股份</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>3.43</v>
+        <v>13.74</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>9.94</v>
+        <v>10.01</v>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>玻璃纤维捻线机|2025年6月28日公司官微透露，公司与国际复材签订了加捻事业部史上最大额玻璃纤维捻线机订单。玻纤凭借其低介电常数等特性，已成为制造高频高速PCB与高性能芯片封装材料的不二之选。</t>
+          <t>半导体+AI应用|1.公司旗下埃延半导体是一家拥有独立自主知识产权的科研制造公司，致力于大硅片及第三代半导体材料衬底外延设备的生产制造以及衬底材料的研发，主要产品是研发和量产外延片所需的生产设备。
+2.子公司重庆叁圭动漫科技经营范围包括动漫游戏开发；人工智能基础软件开发；人工智能基础资源与技术平台；人工智能应用软件开发；人工智能通用应用系统；人工智能双创服务平台；人工智能行业应用系统集成服务；人工智能公共数据平台；人工智能硬件销售等。</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>玻璃纤维捻线机</t>
+          <t>半导体, AI应用</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr"/>
+          <t>算力工程</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>IDC咨询发布报告称，由于智能体任务执行密度的增长和任务复杂度的提升，也将带来智能体Token消耗年均超30倍的指数级跃升。</t>
+        </is>
+      </c>
       <c r="D46" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>sh688176</t>
+          <t>sh600666</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>亚虹医药-U</t>
+          <t xml:space="preserve">奥瑞德  </t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>13.67</v>
+        <v>3.98</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>20.02</v>
+        <v>9.94</v>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>新药获批上市|亚虹医药公告称，公司收到国家药品监督管理局核准签发的《药品注册证书》，批准APL-1702（商标名：希维她®/CEVIRA®，通用名：盐酸氨酮戊酸己酯软膏宫颈光动力治疗系统）上市，用于治疗18岁及以上经组织学证实为子宫颈上皮内瘤变2级（CIN2）患者。</t>
+          <t>算力租赁|公司设立全资子公司北京智算力、深圳智算力，使用自有资金投资建设算力租赁一、二、三期项目。</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>新药获批上市</t>
+          <t>算力租赁</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr"/>
+          <t>算力工程</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>IDC咨询发布报告称，由于智能体任务执行密度的增长和任务复杂度的提升，也将带来智能体Token消耗年均超30倍的指数级跃升。</t>
+        </is>
+      </c>
       <c r="D47" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>sz002272</t>
+          <t>sz300895</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>川润股份</t>
+          <t>铜牛信息</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>21.07</v>
+        <v>61.54</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>10.03</v>
+        <v>20.01</v>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>液冷+华为概念|1.公司液冷技术在能源、工业等领域有多年成熟应用，在储能、数据中心、云计算、算力设备、通信网络、电力电网、电源转换等领域为客户提供液冷产品和温控节能解决方案。公司已实现服务器浸没式液冷产品“零”突破。
-2.2024年3月11日公司官微透露，华夏鲲鹏与川润在华灏鲲鹏西部产业基地隆重举行战略合作签约仪式。双方将在数字能源领域实现深度合作。</t>
+          <t>算力租赁|公司是北京市国资委下属企业，是在国内尤其是在北京地区少数拥有自有房产自建数据中心且自主搭建云平台的专业IDC服务商之一。</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>液冷, 华为概念</t>
+          <t>算力租赁</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>算力工程</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>IDC咨询发布报告称，由于智能体任务执行密度的增长和任务复杂度的提升，也将带来智能体Token消耗年均超30倍的指数级跃升。</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>sz000815</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>美利云</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>算力租赁|公司主要从事IDC业务，专业为大型互联网企业提供数据机房机柜出租托管，同时提供宽带接入服务。公司数据中心位于“东数西算”节点城市之一，具备高性能网络资源、低成本电力、高规格设计、优质气候条件及可扩展的空间。涉及的底层和应用层面的云计算、算力、AI人工智能技术、搜索技术、网络安全等相关业务和服务正在积极探索。</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>算力租赁</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>量子科技</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>政府工作报告提出，建立未来产业投入增长和风险分担机制，培育发展未来能源、量子科技等未来产业。</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>sz000555</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>神州信息</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>18.02</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>量子科技+AI|1.公司通过与国盾量子、国科量子深度战略合作，加强量子通信网络的运维服务及政府、金融、军工国防等行业应用解决方案的开发，并于2019年正式发布由公司自主研发的新一代企业级即时加密通讯工具“量信通”产品。
+2.子公司华通云数据是火山引擎的HiAgent的合作伙伴，目前双方共同致力于HiAgent平台在教育和企业行业的应用推广。</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>量子科技, AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>量子科技</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>政府工作报告提出，建立未来产业投入增长和风险分担机制，培育发展未来能源、量子科技等未来产业。</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>sh600468</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>百利电气</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>量子科技+超导|超导量子是量子通信的重要技术，高温超导线材是超导产品的核心基础材料，公司控股子公司北京英纳超导技术有限公司是国内较早成立的专业研发生产高温超导材料的企业，承担过多项国家863项目、科技部重大专项、北京市重大科技计划等重大超导项目，其“高性能铋系高温超导长带材的研制与开发”曾获得国务院国家科学技术进步二等奖。</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>量子科技, 超导</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>核电</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>据不完全统计，2026年以来，星环聚能、中科清能、东昇聚变、束研聚创等可控核聚变项目陆续更新了融资进展。</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>sz002471</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>中超控股</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>核电+商业航天|1.公司在2022年年度报告中透露，公司已完成研发出一种耐高温抗拉耐腐蚀型核电站用电缆，其具有优良的耐长期热老化性能、耐辐照、电气性能稳定、阻燃性能好及无卤低烟低毒等特点，适应核电站恶劣的工作环境。
+2.孙公司江苏精铸专业从事高温合金精密铸件的制造，转化上海交大前期航空发动机及燃气轮机、航天特种飞行器、运载火箭等关键热端零部件的技术研发成果，并进一步研究优化高温合金精密铸件批量化生产工艺。</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>核电, 商业航天</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>核电</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>据不完全统计，2026年以来，星环聚能、中科清能、东昇聚变、束研聚创等可控核聚变项目陆续更新了融资进展。</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>sh600516</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>方大炭素</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">核电|公司是中国炭和石墨制品龙头企业，公司是我国第一个自行设计建设的大型综合炭素生产企业，也是全国唯一的大型高炉炭砖生产基地，2017年，公司高温气冷堆炭堆内构件展示项目获得中国国际高新技术成果交易会优秀产品奖。 </t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>核电</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>光通信</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>英伟达近日分别发布声明称，将在多年期协议中分别向Lumentum Holdings Inc.和相干公司投资20亿美元。两项交易均包括采购协议以及先进激光组件的使用。</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>sz001267</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>汇绿生态</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>36.96</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>光通信|公司旗下钧恒科技是专业从事高端光通信产品的研制、生产及推广的高新技术企业，拥有从光学组件，光电转换模块，光端机及子系统的行业垂直整合能力，能够为客户提供各种特定应用的定制化产品，包括PLCC、Mini SFF、Micro Pod等各种形态及各种复合协议的光端机及波分复用子系统。</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>光通信</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>光通信</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>英伟达近日分别发布声明称，将在多年期协议中分别向Lumentum Holdings Inc.和相干公司投资20亿美元。两项交易均包括采购协议以及先进激光组件的使用。</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>sz002796</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>世嘉科技</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>57.32</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>光模块|2025年8月4日公告，公司看好光通信细分行业的市场前景，认可光彩芯辰（浙江）科技有限公司在光通信领域内的前期投入、技术储备以及客户资源。公司拟通过增资扩股的方式取得光彩芯辰部分股权，并与光彩芯辰签署了《增资意向协议》。如交易顺利完成，公司将于交易完成后预计持有光彩芯辰不超过20%的股权。光彩芯辰主要从事100G—800G多系列光通信模块的研发制造，总部及生产基地均位于中新嘉善现代产业园。</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>光模块</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>氢能</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>全国政协委员，中国工程院院士马永生在2026全国两会建言中提出，强化顶层设计，构建国家氢能基础设施一张网。支持大型能源企业开展跨省氢能管道试点，加快绿氢认证与碳交易市场的衔接。</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>sz002733</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>雄韬股份</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>24.48</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>氢能+IDC电源|1.公司的主营业务产品为铅酸蓄电池、锂电池及氢燃料电池，锂离子电池产品涵盖磷酸铁锂、钴酸锂、锰酸锂三大系列，其中磷酸铁锂电池项目被列为国家火炬计划重点项目和深圳市科技资助项目，也是公司最主要的锂离子电池产品。
+2.公司主要为数据中心及算力中心提供UPS电池。</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>氢能, IDC电源</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>sz000711</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>ST京蓝</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>23天16板</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 主要业务包括流域水生态修复、灌区节水综合系统工程、污水治理、沿河生态景观工程、智慧水务等。</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C57" s="2" t="inlineStr"/>
+      <c r="D57" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>sh603268</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*ST松发 </t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>123.38</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>12天8板</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 拟收购恒力重工主营船舶及高端装备的研发、生产及销售，已确定排产新造船舶140艘，货值约108亿美元，船型包含散货船、VLCC、VLOC 和集装箱船等。</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C58" s="2" t="inlineStr"/>
+      <c r="D58" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>sh603838</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*ST四通 </t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>5天3板</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司是一家集研发、设计、生产、销售于一体的新型家居生活陶瓷供应商，产品覆盖日用陶瓷、卫生陶瓷、艺术陶瓷、建筑装饰等全系列家居生活用瓷。</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C59" s="2" t="inlineStr"/>
+      <c r="D59" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>sh603813</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*ST原尚 </t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>36.18</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司参股公司广东原锋新能源科技的股东之一锋源是国内极少的集全套自主知识产权氢燃料电池电堆以及核心零部件膜电极、催化剂、金属双极板等研发、生产、销售一体的公司。</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C60" s="2" t="inlineStr"/>
+      <c r="D60" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>sz002592</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>ST八菱</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司配套氢燃料电池客车的产品技术目前已经形成商业化，广泛应用于燃气客车、混合动力客车和军车等领域。</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr"/>
+      <c r="D61" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>sz002713</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>*ST东易</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司基于数字化系统优势和业务场景优势，研发推出了行业内首个新一代AIGC技术和真家系统结合的全新设计工具“真家 AIGC”，同时打造出AI 创意大师、AI小白设计家两款智能应用设计工具。</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C62" s="2" t="inlineStr"/>
+      <c r="D62" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>sz002868</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>*ST绿康</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>42.07</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 绿康生化公告称，公司收到通知，公司控股股东上海康怡投资有限公司、股东杭州义睿投资合伙企业（有限合伙）、上饶市长鑫贰号企业管理中心（有限合伙）、杭州皓赢投资合伙企业（有限合伙）与福建纵腾网络有限公司签署了《股份转让协议》，约定由上述股份转让方向纵腾网络转让上市公司46,608,397股普通股股份，占上市公司总股本的29.99%。</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr"/>
+      <c r="D63" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>sz002569</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>*ST步森</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 主营业务为“步森”品牌男装的设计、生产和销售。</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C64" s="2" t="inlineStr"/>
+      <c r="D64" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>sz000908</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>*ST景峰</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司专注医药健康产业，涉足药品研发、生产、销售等领域，产品涵盖了心脑血管、抗肿瘤、骨科、妇儿等用药领域。</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C65" s="2" t="inlineStr"/>
+      <c r="D65" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>sz000793</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>*ST华闻</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 地处海南省海口市，国广环球传媒控股旗下上市公司，主营传媒业务。</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr"/>
+      <c r="D66" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>sh600545</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>卓郎智能</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>玻璃纤维捻线机|2025年6月28日公司官微透露，公司与国际复材签订了加捻事业部史上最大额玻璃纤维捻线机订单。玻纤凭借其低介电常数等特性，已成为制造高频高速PCB与高性能芯片封装材料的不二之选。</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>玻璃纤维捻线机</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr"/>
+      <c r="D67" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>sz002952</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>亚世光电</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>OLED|公司于2019年4月在互动平台表示，公司主要聚焦工控仪表、通讯终端、办公室自动化等细分应用市场领域，目前主要是LCD显示类型的产品，对于OLED显示类型的产品也有一定涉足，这主要是由客户的定制化需求所决定的。</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>OLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr"/>
+      <c r="D68" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>sz002235</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>安妮股份</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>股权变更重大进展|安妮股份3月4日晚间公告表示，深交所已对转让双方提交的申请材料进行了完备性核对，并出具了《深圳证券交易所上市公司股份协议转让确认书》。公司控制权变更事项迎来重大进展。</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>股权变更重大进展</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr"/>
+      <c r="D69" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>sz002355</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>兴民智通</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>无人驾驶|公司为无人驾驶开发了高网络可靠性的双5G智能网联终端产品—通信域控制器（ICVBOX），目前已在L3、L4无人驾驶汽车Robotaxi、无人物流车上配套，服务客户涵盖百度萝卜快跑、Momenta以及国内主流车企。</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>无人驾驶</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr"/>
+      <c r="D70" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>920001.BJ</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>纬达光电</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>21.33</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>偏光片|公司主要从事偏光片和光学薄膜材料的研发、生产与销售。公司已掌握AMOLED、PMOLED偏光片产品的关键生产技术和工艺，预计新增产能建成后可广泛开拓OLED市场。</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>偏光片</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr"/>
+      <c r="D71" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>sh605098</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>行动教育</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>51.26</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>教育|公司定位于“建设世界级实效管理教育机构”，主要致力于为中小民营企业提供全生命周期的生态化知识服务和智力支持平台。</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>教育</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr"/>
+      <c r="D72" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>sz002800</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>天顺股份</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>一带一路+物流|公司作为疆内第三方物流、供应链管理的龙头企业，国际铁路业务在2022年开行了莫斯科、杜伊斯堡、汉堡、梅杰乌、阿拉木图、热特苏、塔什干、格鲁吉亚、意大利、梅尔辛、马拉等中亚、中欧方向的班列。国际航班货源业务在2022年以乌鲁木齐为中心开通了格鲁吉亚第比利斯等全货机航线；在海口开设海口至莫斯科航线；在武汉开设了武汉至莫斯科航线。</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>一带一路, 物流</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr"/>
+      <c r="D73" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>sz000920</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>沃顿科技</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>13.63</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">盐湖提锂|公司膜产品可以用在膜浓缩工艺的盐湖提锂中。
+</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>盐湖提锂</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr"/>
+      <c r="D74" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>sh600744</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>华银电力</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>电力|作为湖南省火电装机主要发电企业，公司主要从事火力发电业务，同时经营水电、风电、太阳能业务以及电力销售业务。</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr"/>
+      <c r="D75" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>sh600828</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>茂业商业</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>零售|公司业务以商业零售为主，并辅以部分物业租赁和酒店业务。</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr"/>
+      <c r="D76" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>sh600844</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>金煤科技</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>煤化工|公司为专注于煤制乙二醇产业的新型化工企业，目前主要通过控股子公司通辽金煤的大型化工装置生产乙二醇并联产草酸。</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>煤化工</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr"/>
+      <c r="D77" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>sz002913</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>奥士康</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>48.29</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>PCB|公司PCB产品主要应用于数据中心及服务器、AIPC、通信及网络设备、汽车电子等领域。</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr"/>
+      <c r="D78" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>sh605298</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>必得科技</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>49.81</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>高铁|公司主营中高速动车组列车、城轨列车等轨道交通车辆配套产品的研发、生产与销售，主要产品包括车辆通风系统、电缆保护系统和智能控制撒砂系统等系统化、系列化产品及其他轨道交通车辆配套产品。</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>高铁</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr"/>
+      <c r="D79" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>sh603001</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>奥康国际</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>纺织|主要从事皮鞋及皮具产品的研发、生产、零售及分销业务。</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>纺织</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr"/>
+      <c r="D80" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>sh603067</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>振华股份</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>45.87</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>固态电池+铬|1.子公司厦门首能半固态电解液还处于向下游客户小批量供应，共同研发阶段。
+2.公司是国内铬盐行业唯一的上市公司，铬盐生产规模、技术水平、产品质量、市场占有率处于国内龙头地位，是国内铬盐行业综合竞争力最强的企业。</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>固态电池, 铬</t>
         </is>
       </c>
     </row>
@@ -2672,7 +4069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2699,91 +4096,106 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sh603318</t>
+          <t>sh600545</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>水发燃气</t>
+          <t>卓郎智能</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sh600108</t>
+          <t>sz300265</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>亚盛集团</t>
+          <t>通光线缆</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sz002207</t>
+          <t>sz002877</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>准油股份</t>
+          <t>智能自控</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sz002490</t>
+          <t>sz002339</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>山东墨龙</t>
+          <t>积成电子</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sh600871</t>
+          <t>sh605268</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>石化油服</t>
+          <t>王力安防</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sh600759</t>
+          <t>sz002498</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>洲际油气</t>
+          <t>汉缆股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>sz000533</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>顺钠股份</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,19 +476,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K80"/>
+  <dimension ref="A1:K89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="102" customWidth="1" min="3" max="3"/>
+    <col width="103" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="385" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="344" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -552,618 +552,624 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.16</v>
+        <v>2.72</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
+          <t>中东颗粒尿素价格自上周五以来每吨上涨约130美元，目前报575至650美元。此外南京钛白化工、安纳达等多家钛白粉企业宣布上调产品出厂价格。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>sz300323</t>
+          <t>sh600722</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>华灿光电</t>
+          <t>金牛化工</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>10.25</v>
+        <v>13.53</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>20.02</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>5天3板</t>
+        </is>
+      </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>MLED|公司是行业内最早开展Mini/Micro技术研发的芯片企业之一，率先解决Mini LED在COB应用的分光和高灰阶的显示问题，并自2019年开始，Mini LED芯片产品在行业内率先实现批量生产与销售。公司Mini LED产品采用行业领先的倒装芯片结构及LED芯片衬底转移技术，芯片产品具有整体良率及可靠性高，光色一致性好等优势，获得国内外主流终端显示客户的认可。</t>
+          <t>甲醇|公司的主要业务为甲醇的生产和销售，产品方式为焦炉气制甲醇。公司的主要业务由持股50%的控股子公司金牛旭阳经营，金牛旭阳拥有的甲醇生产能力为20万吨/年。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>甲醇</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>9.16</v>
+        <v>2.72</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
+          <t>中东颗粒尿素价格自上周五以来每吨上涨约130美元，目前报575至650美元。此外南京钛白化工、安纳达等多家钛白粉企业宣布上调产品出厂价格。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sz002429</t>
+          <t>sz002470</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>兆驰股份</t>
+          <t>金正大</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>10.22</v>
+        <v>2.86</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>MLED+AI漫剧|1.2019年12月，公司计划在南昌市高新技术产业开发区投资建设红黄光LED外延、芯片及Mini LED、Micro LED项目。项目一期计划投资人民币10亿元用于红黄光LED外延及芯片的研发、生产和销售，计划于2020年相关设备安装调试到位并正式投入运营。面对未来红黄光LED市场需求的迅速崛起，兆驰半导体拟于南昌高新区投资建设红黄光LED项目，完善LED外延及芯片的品类及应用领域，预计投产后年产能（折合4寸片）可达120万片。
-2.公司旗下风行在线已形成短带长、长改短、AI漫剧、AI小说四大核心业务，其中短带长、长改短均位居行业第一，短视频推广业务位居抖音、快手行业第一。在创作端，依托橙星梦工厂、小剪刀等AI工具，覆盖AI漫剧、短剧、小说等多元内容的快速生成与影视二创需求，已聚集1.5万创作者，日活达2000以上，并积累超1万部剧本。</t>
+          <t>化肥|公司的复合肥、缓控释肥、硝基复合肥、水溶肥及其他新型肥料在技术和市场占有率方面居国内领先地位，具有较强的竞争优势。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>MLED, AI漫剧</t>
+          <t>化肥</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>9.16</v>
+        <v>2.72</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
+          <t>中东颗粒尿素价格自上周五以来每吨上涨约130美元，目前报575至650美元。此外南京钛白化工、安纳达等多家钛白粉企业宣布上调产品出厂价格。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sz002449</t>
+          <t>sz002165</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>国星光电</t>
+          <t>红 宝 丽</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>8.76</v>
+        <v>12.21</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>10.05</v>
+        <v>10</v>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>MLED|公司于2022年5月19日公告，与华为技术有限公司签订全面合作协议，共同推动联合创新中心落地并挂牌，在Mini &amp; Micro LED、LED背光及显示模组、直显RGB器件、车载HUD、智能健康照明、光耦及功率器件、非视觉光源等方面开展深度创新合作。</t>
+          <t>光刻胶+化工|1.公司异丙醇胺产品是一种绿色环保的精细化工原料，可应用于电子清洗行业，例如光刻胶在应用中的残留物清洗。
+2.公司泰兴环氧丙烷产业基地具备12万吨环氧丙烷产能，该项目采用具有自主知识产权的共氧化法新工艺，是国内首套工业化装置，整个生产过程仅产生少量的工业废水。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>光刻胶, 化工</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>9.16</v>
+        <v>2.72</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
+          <t>中东颗粒尿素价格自上周五以来每吨上涨约130美元，目前报575至650美元。此外南京钛白化工、安纳达等多家钛白粉企业宣布上调产品出厂价格。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sh600703</t>
+          <t>sz000677</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>三安光电</t>
+          <t>恒天海龙</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>16.13</v>
+        <v>4.4</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>10.03</v>
+        <v>10</v>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>MLED|公司于2021年9月29日晚发布021年度非公开发行A股股票预案，拟募资79亿元用于湖北三安光电有限公司Mini/Micro显示产业化项目和补充流动资金。Mini/Micro显示产业化项目总投资120亿元，达产后，新增氮化镓Mini/Micro LED芯片161万片/年、砷化镓Mini/Micro LED芯片75万片/年（均以4寸为当量片）和4K显示屏用封装产品8.4万台/年的生产能力。</t>
+          <t>军工+化工|1.公司生产的芳纶布可由下游客户用于生产防弹头盔，防弹头盔属于军工产品。
+2.公司主导产品为高性能高模低缩浸胶涤纶帘子布、帆布。主要生产设备高模低缩工业长丝生产线、双浴法浸胶生产线系从德国、美国等引进。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>军工, 化工</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>9.16</v>
+        <v>2.72</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
+          <t>中东颗粒尿素价格自上周五以来每吨上涨约130美元，目前报575至650美元。此外南京钛白化工、安纳达等多家钛白粉企业宣布上调产品出厂价格。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sz000727</t>
+          <t>sz002809</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>冠捷科技</t>
+          <t>红墙股份</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>2.73</v>
+        <v>13.68</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>10.08</v>
+        <v>9.969999999999999</v>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>MLED|公司2021年7月22日在互动平台表示，公司已有数款使用Mini-LED背光技术的电视和高端电竞显示产品实现量产，部分产品目前已有线上购买渠道。同时，公司也已在小间距LED显示产品上积极布局了Mini-LED技术。</t>
+          <t>环氧丙烷|公司投资6.6亿元建设年产32万吨环氧乙烷及环氧丙烷衍生物项目，其中计划建设年产15万吨减水剂聚醚生产线、年产7万吨非离子表面活性剂生产线、年产2万吨聚醚多元醇生产线、年产4万吨丙烯酸羟基酯生产线和年产4万吨聚羧酸高性能减水剂生产线。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>环氧丙烷</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>9.16</v>
+        <v>2.72</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
+          <t>中东颗粒尿素价格自上周五以来每吨上涨约130美元，目前报575至650美元。此外南京钛白化工、安纳达等多家钛白粉企业宣布上调产品出厂价格。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sz002983</t>
+          <t>sh600470</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>芯瑞达</t>
+          <t>六国化工</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>25.41</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MLED|公司2022年8月23日在互动平台表示，公司一直深耕新型显示领域，在研的Micro LED技术项目可应用于VR/AR显示终端，目前尚未转换为订单，请广大投资者注意风险。 </t>
+          <t>化肥|公司是华东地区磷复肥和磷化工一体化专业制造的大型企业，主营业务为化肥(含氮肥、磷肥、钾肥)、肥料（含复合肥料、复混肥料、有机肥料及微生物肥料）、化学制品（含精制磷酸、磷酸盐）、化学原料的生产加工和销售。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>化肥</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>9.16</v>
+        <v>2.72</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
+          <t>中东颗粒尿素价格自上周五以来每吨上涨约130美元，目前报575至650美元。此外南京钛白化工、安纳达等多家钛白粉企业宣布上调产品出厂价格。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sz300162</t>
+          <t>sh600227</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>雷曼光电</t>
+          <t xml:space="preserve">赤天化  </t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>9.48</v>
+        <v>3.29</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>20</v>
+        <v>10.03</v>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>MLED|公司自主研发的基于COB的Micro LED超高清显示技术作为新型显示技术，可应用于大尺寸的高端专业显示、商业显示及民用显示领域，Micro LED也可以应用于小尺寸的VR、AR显示，手表等可穿戴设备显示领域，公司目前主要专注于大尺寸的Micro LED超高清显示产品。</t>
+          <t>化肥+甲醇|公司是贵州省最大的氮肥生产企业，公司化肥化工生产基地分别是以天然气为原料生产的赤水化工分公司（年产63万吨尿素）和以煤为生产原料的公司全资子公司桐梓化工（年产52万吨尿素、30万吨甲醇）。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>化肥, 甲醇</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>9.16</v>
+        <v>2.72</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
+          <t>中东颗粒尿素价格自上周五以来每吨上涨约130美元，目前报575至650美元。此外南京钛白化工、安纳达等多家钛白粉企业宣布上调产品出厂价格。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sh603773</t>
+          <t>sh603285</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>沃格光电</t>
+          <t>键邦股份</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>39.67</v>
+        <v>37.76</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>10.01</v>
+        <v>9.99</v>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>MLED|2022年2月21日公告，拟设立江西德虹显示技术有限公司投资新建“玻璃基材的Mini/MicroLED基板生产项目”，项目总投资金额预计为16.5亿元。该项目拟新建6万平方米厂房，项目完全达产的建设周期约为24个月。项目实施建成后，将实现生产玻璃基材的Mini/MicroLED基板总产能524万㎡/年。</t>
+          <t>化工|公司产品主要作为稳定剂、催化剂、增塑剂、偶联剂等功能助剂应用于PVC塑料、涂料以及锂电材料等领域。公司开发了富临精工等国内知名的锂电池正极材料企业等客户资源。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>化工</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>9.16</v>
+        <v>2.72</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
+          <t>中东颗粒尿素价格自上周五以来每吨上涨约130美元，目前报575至650美元。此外南京钛白化工、安纳达等多家钛白粉企业宣布上调产品出厂价格。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sz300269</t>
+          <t>sz000545</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>联建光电</t>
+          <t>金浦钛业</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>8.640000000000001</v>
+        <v>3.75</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>20</v>
+        <v>9.969999999999999</v>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>MLED|公司现已在众多技术领域积累了多项国内外领先的核心技术：miniLED显示、正装/倒装发光显示、多合一像素显示技术、SMD高防护面板技术；4K/8K超高清显示控制、HDR高动态范围显示、负电压节能驱动技术、AI智能显示模组校正、X+Y+Z微米级六向微调技术、柔性透明显示技术；LED高分可视化显控技术、LED显示信息安全技术、LED触控交互、LED体感交互、VR/AR+LED显示等。</t>
+          <t>钛白粉+锂电池|1.全资子公司南京钛白是我国最早生产钛白粉的企业之一，也是国内最早研制、生产高档金红石钛白粉和化纤钛白粉的企业之一，目前已成为国内大型硫酸法钛白粉生产企业和行业骨干企业。
+2.2022年3月28日公告，公司拟在安徽（淮北）新型煤化工合成材料基地投资建设20万吨/年电池级磷酸铁、20万吨/年磷酸铁锂等新能源电池材料一体化项目，该项目总投资在100亿元左右。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>钛白粉, 锂电池</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>9.16</v>
+        <v>2.72</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
+          <t>中东颗粒尿素价格自上周五以来每吨上涨约130美元，目前报575至650美元。此外南京钛白化工、安纳达等多家钛白粉企业宣布上调产品出厂价格。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sz002845</t>
+          <t>sh600319</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>同兴达</t>
+          <t>亚星化学</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>15.7</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>10.02</v>
+        <v>10.06</v>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>MLED|公司2020年7月2日在互动平台表示，关于研发MiniLED模组，公司已有技术储备，具体量产计划根据市场情况待定。</t>
+          <t>化工|公司主营氯化聚乙烯（CPE）、离子膜烧碱、水合肼、ADC发泡剂等高科技化学产品，同时从事新型化学材料的开发和研究，是目前世界上最主要的含氯聚合物研发生产企业。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>化工</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>9.16</v>
+        <v>2.72</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
+          <t>中东颗粒尿素价格自上周五以来每吨上涨约130美元，目前报575至650美元。此外南京钛白化工、安纳达等多家钛白粉企业宣布上调产品出厂价格。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sz300241</t>
+          <t>sz002648</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>瑞丰光电</t>
+          <t>卫星化学</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>7.39</v>
+        <v>26.91</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>19.97</v>
+        <v>10.02</v>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>MLED|公司2020年5月15日发布创业板非公开发行A股股票预案，拟募资不超6.99亿元投资于全彩表面贴装发光二极管（全彩LED）封装扩产项目，次毫米发光二极管（MiniLED）背光封装生产项目和微型发光二极管（MicroLED）技术研发中心项目，公司顺应行业和技术的发展及时切入Mini LED和设立Micro LED技术研发中心，有利于取得先发优势，把握行业发展的先机。</t>
+          <t>化工|公司一直致力于C3产业链的发展，覆盖丙烯、丙烯酸、丙烯酸酯、丙烯酸酯纺织乳液、聚丙烯酸钠盐(高吸水性树脂)等产品的研发、生产与销售，是国内首家拥有C3产业链一体化的上市公司。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>化工</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>9.16</v>
+        <v>2.72</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
+          <t>中东颗粒尿素价格自上周五以来每吨上涨约130美元，目前报575至650美元。此外南京钛白化工、安纳达等多家钛白粉企业宣布上调产品出厂价格。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sz000509</t>
+          <t>sz002637</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>华塑控股</t>
+          <t>赞宇科技</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>3.63</v>
+        <v>14.58</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>10</v>
+        <v>10.04</v>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>MLED|公司积极布局了MiniLED、OLED和高分高刷高色域等显示领域前沿产品技术。</t>
+          <t>油脂化工|公司油脂化工业务主要由杭州油化、南通凯塔和杜库达三家控股子公司负责生产经营。油脂化工业务主要以棕榈油为原料，主要产品包括硬脂酸、脂肪酸、油酸、脂肪醇、脂肪胺、二聚酸、聚酰胺树脂、甘油及其他助剂等油脂化工产品。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>油脂化工</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>9.16</v>
+        <v>2.72</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
+          <t>中东颗粒尿素价格自上周五以来每吨上涨约130美元，目前报575至650美元。此外南京钛白化工、安纳达等多家钛白粉企业宣布上调产品出厂价格。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sz300303</t>
+          <t>sz000833</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>聚飞光电</t>
+          <t>粤桂股份</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>12.53</v>
+        <v>26.32</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>20.02</v>
+        <v>9.99</v>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>MLED|公司于2019年11月接待机构调研时透露，MiniLED是公司拓展的一项新业务，目前处于小批量送样阶段。</t>
+          <t>硫化工|云硫矿业是粤桂股份硫化工产业板块实体子公司，位于广东云浮市云城区，探明硫铁矿储量2.08亿吨，占全国硫铁矿富矿资源的85%，平均品位31.04%，品质优良，原矿产能约300万吨/年，按百川盈孚网公布的全国硫铁矿产量计算，公司硫铁矿产量占全国产量约16.63%。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>硫化工</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>9.16</v>
+        <v>2.72</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
+          <t>中东颗粒尿素价格自上周五以来每吨上涨约130美元，目前报575至650美元。此外南京钛白化工、安纳达等多家钛白粉企业宣布上调产品出厂价格。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sz000536</t>
+          <t>sh605399</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>华映科技</t>
+          <t>晨光新材</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>4.74</v>
+        <v>16.64</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>9.98</v>
@@ -1171,282 +1177,292 @@
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>MLED|2023年3月18日公告，公司与兆元光电签订合资协议，共同投资设立一家合资公司，为在Micro LED/MiniLED赛道上做前期布局。合资公司注册资本为3.03亿元，其中公司以货币出资1.48亿元，占注册资本比例48.92%。</t>
+          <t>光伏+有机硅|1.公司是国内功能性硅烷行业中产业链最为完整的企业之一。
+2.公司三氯氢硅可用于多晶硅制造，硅烷偶联剂产品可用于EVA、POE胶膜，以提升使用寿命，也可用于光伏组件中背板的密封胶、灌封胶中。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>光伏, 有机硅</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>9.16</v>
+        <v>2.72</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
+          <t>中东颗粒尿素价格自上周五以来每吨上涨约130美元，目前报575至650美元。此外南京钛白化工、安纳达等多家钛白粉企业宣布上调产品出厂价格。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sz000045</t>
+          <t>sh600075</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>深纺织Ａ</t>
+          <t>新疆天业</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>13.2</v>
+        <v>7.19</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>10</v>
+        <v>9.94</v>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>MLED|公司的偏光片产品可用于采用mini LED背光的LCD显示屏。</t>
+          <t>氯碱化工|公司通过资产重组、收购氯碱化工资产，已具备较为完整的“自备电力→电石→聚氯乙烯树脂及副产品→电石渣及其他废弃物制水泥”一体化产业联动式绿色环保型循环经济产业链，具有89万吨PVC产能（包括69万吨通用PVC、10万吨特种树脂、10万吨糊树脂）、65万吨离子膜烧碱产能、134万吨电石产能，同时拥有2×300MW、2×330MW自备热电站以及405万吨电石渣制水泥装置。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>氯碱化工</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>智能电网</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>9.16</v>
+        <v>2.45</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
+          <t>当地时间4日，微软、谷歌、OpenAI、亚马逊、Meta、xAI和甲骨文这七家公司代表在美国白宫签署自主供电承诺。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sz002587</t>
+          <t>sz000533</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>奥拓电子</t>
+          <t>顺钠股份</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>7.01</v>
+        <v>14.88</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
+        <v>9.98</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>MLED|公司作为国内最早研发MiniLED显示产品的企业，已在全世界范围内申请了30项专利，其中19项已获得授权，推出了行业领先的超小点间距0.78mm的MiniLED显示产品，并在2019ISE上展出全球最大、分辨率最高的8K超高清MiniLED显示屏。</t>
+          <t>核聚变+变压器|1.公司研制的特殊用途干式变压器包括国际热核聚变实验堆（ITER）试验平台变压器。
+2.公司控股孙公司顺特设备在超算中心和数据中心这两个领域提供过干式变压器产品，曾向阿里巴巴、秦淮数据有限公司、万国数据服务有限公司、数据港股份有限公司等客户提供过变压器设备。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>核聚变, 变压器</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>智能电网</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>9.16</v>
+        <v>2.45</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
+          <t>当地时间4日，微软、谷歌、OpenAI、亚马逊、Meta、xAI和甲骨文这七家公司代表在美国白宫签署自主供电承诺。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sz300389</t>
+          <t>sz002498</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>艾比森</t>
+          <t>汉缆股份</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>20.64</v>
+        <v>9.83</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
+        <v>9.959999999999999</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>MLED|2019年，公司在市场上推出了采用IMD四合一集成封装技术的MiniLED产品，实现了真正意义上的高品质量产和应用。目前，公司已将MiniLED技术成熟并应用于多条产品线，包括AX系列、A27 Pro系列以及CR系列等，并在MiniLED开发上申请了专利16项，其中发明专利5项。</t>
+          <t>电缆|公司是集电缆及附件系统、状态检测系统、输变电工程总包三个板块于一体，研发生产经营的技术密集型企业集团。</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>电缆</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>智能电网</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>9.16</v>
+        <v>2.45</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
+          <t>当地时间4日，微软、谷歌、OpenAI、亚马逊、Meta、xAI和甲骨文这七家公司代表在美国白宫签署自主供电承诺。</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sh688079</t>
+          <t>sh601567</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">美迪凯  </t>
+          <t>三星医疗</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>13.82</v>
+        <v>29.41</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>19.97</v>
+        <v>9.99</v>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>MLED|公司的Micro LED产品已全流程制样，产品已经点亮。</t>
+          <t>变压器+签订大单|三星医疗公告称，公司下属全资子公司三星瑞典与荷兰Enexis电力局签订变压器框架合同，提供油浸式变压器产品，合同金额总计1.17亿欧元，约合9.49亿人民币。该合同金额占公司2024年度经审计营业收入的6.50%，预计将对公司经营业绩产生积极影响。</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>变压器, 签订大单</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>智能电网</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>9.16</v>
+        <v>2.45</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
+          <t>当地时间4日，微软、谷歌、OpenAI、亚马逊、Meta、xAI和甲骨文这七家公司代表在美国白宫签署自主供电承诺。</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sz300708</t>
+          <t>sz002227</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>聚灿光电</t>
+          <t>奥 特 迅</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>12.52</v>
+        <v>10.77</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>20.04</v>
+        <v>10.01</v>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>MLED|公司于2022年6月21日披露2022年度向特定对象发行A股股票预案，拟定增募资不超12亿元，用于Mini/Micro LED芯片研发及制造扩建项目。项目总投资金额为15.5亿元，建成后，将形成年产720万片Mini/Micro LED芯片产能。</t>
+          <t>电网设备|公司专注于高端工业电源及应用，如电力自动化电源、核安全级电源、特高压输电用取能电源等，众多产品广泛应用于国家电网、南方电网以及核电站建设等多个领域。在工业电源领域，公司首创将高频开关技术引入直流操作电源，成果广泛应用于三峡水电站、白鹤滩水电站、田湾核电站、南水北调和西电东送等数百个大型国内外水电、变电及核电项目。</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>电网设备</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>智能电网</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>9.16</v>
+        <v>2.45</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
+          <t>当地时间4日，微软、谷歌、OpenAI、亚马逊、Meta、xAI和甲骨文这七家公司代表在美国白宫签署自主供电承诺。</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>sh688055</t>
+          <t>sz000720</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>龙腾光电</t>
+          <t>新能泰山</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>20.06</v>
+        <v>10</v>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>MLED|公司将Mini LED作为重要核心技术，成功推出最佳分区调光技术Mini LED车载显示屏、笔记本电脑屏及电竞显示屏等产品，同时公司加大对车载Mini LED背光技术不同架构的开发与研究，重点推进其在车载产品上的量产进程，并积极探索Mini LED在游戏、医疗等各类显示应用场景。</t>
+          <t>电缆|子公司曲阜电缆主要从事电线电缆、光纤光缆、电力光缆等产品的研发、制造与销售，曲阜电缆生产、 销售的电线电缆产品是公司重点发展的智慧供应链业务产品之一。</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>电缆</t>
         </is>
       </c>
     </row>
@@ -1457,46 +1473,41 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>3.04</v>
+        <v>2.45</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>据报道，过去数月内，美国三大区域电网运营商相继获批了总计750亿美元的输电扩容项目，核心是建设一批765千伏超高压线路。</t>
+          <t>当地时间4日，微软、谷歌、OpenAI、亚马逊、Meta、xAI和甲骨文这七家公司代表在美国白宫签署自主供电承诺。</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>sz000533</t>
+          <t>sh601616</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>顺钠股份</t>
+          <t>广电电气</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>13.53</v>
+        <v>6.16</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+      <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>核聚变+变压器|1.公司研制的特殊用途干式变压器包括国际热核聚变实验堆（ITER）试验平台变压器。
-2.公司控股孙公司顺特设备在超算中心和数据中心这两个领域提供过干式变压器产品，曾向阿里巴巴、秦淮数据有限公司、万国数据服务有限公司、数据港股份有限公司等客户提供过变压器设备。</t>
+          <t>电网设备|公司是以高低压成套设备及元器件产品的生产和销售为主营业务的公司，集研发、生产、销售、服务于一体，为各行各业用户提供整体配电解决方案，是国内知名的电气设备供应商。</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>核聚变, 变压器</t>
+          <t>电网设备</t>
         </is>
       </c>
     </row>
@@ -1507,45 +1518,41 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>3.04</v>
+        <v>2.45</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>据报道，过去数月内，美国三大区域电网运营商相继获批了总计750亿美元的输电扩容项目，核心是建设一批765千伏超高压线路。</t>
+          <t>当地时间4日，微软、谷歌、OpenAI、亚马逊、Meta、xAI和甲骨文这七家公司代表在美国白宫签署自主供电承诺。</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>sz002498</t>
+          <t>sz301638</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>汉缆股份</t>
+          <t>南网数字</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>8.94</v>
+        <v>28.38</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>9.959999999999999</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>智能电网|公司是集电缆及附件系统、状态检测系统、输变电工程总包三个板块于一体，研发生产经营的技术密集型企业集团。</t>
+          <t>智能电网+AI|公司开发上线自主可控电力行业“大瓦特”人工智能大模型。“大瓦特”人工智能平台作为电力行业国产自主可控人工智能平台，推动电力行业智能化升级。</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>智能电网, AI</t>
         </is>
       </c>
     </row>
@@ -1556,45 +1563,41 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>3.04</v>
+        <v>2.45</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>据报道，过去数月内，美国三大区域电网运营商相继获批了总计750亿美元的输电扩容项目，核心是建设一批765千伏超高压线路。</t>
+          <t>当地时间4日，微软、谷歌、OpenAI、亚马逊、Meta、xAI和甲骨文这七家公司代表在美国白宫签署自主供电承诺。</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>sz002339</t>
+          <t>sh603097</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>积成电子</t>
+          <t>江苏华辰</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>12.69</v>
+        <v>41.05</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>9.969999999999999</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.99</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>智能电网|公司在电力自动化领域产品线覆盖了电力系统发、输、变、配、用、调度各环节，是国内少数几家能够提供电力自动化整体解决方案的厂家之一。</t>
+          <t>变压器|节能干式变压器是我公司的主要产品之一，部分产品被用于数据中心的建设和运营，为数据中心的安全运营提供供电保障。</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>变压器</t>
         </is>
       </c>
     </row>
@@ -1605,45 +1608,41 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>3.04</v>
+        <v>2.45</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>据报道，过去数月内，美国三大区域电网运营商相继获批了总计750亿美元的输电扩容项目，核心是建设一批765千伏超高压线路。</t>
+          <t>当地时间4日，微软、谷歌、OpenAI、亚马逊、Meta、xAI和甲骨文这七家公司代表在美国白宫签署自主供电承诺。</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>sz300265</t>
+          <t>sz002063</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>通光线缆</t>
+          <t>远光软件</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>21.46</v>
+        <v>7.01</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>20.02</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.05</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>电缆|公司生产的OPGW成功运用于国家电网公司第一条交流750千伏超高压示范工程线路、第一条直流±800千伏特高压示范工程线路、第一条交流1,000千伏特高压示范工程线路、南方电网公司第一条500千伏超高压工程线路等国家重点示范工程。公司电力光缆产品市场占有率连续多年位居前列。</t>
+          <t>智能电网+AI|公司凭借丰富的行业经验与积累，依托大数据、区块链、人工智能、云计算、物联网等新兴技术，通过对外投资、并购等方式，公司积极打通能源行业上下游产业链，为电力行业提供从发电、输电、配电、售电、用电各环节业务的一系列信息化服务，助力电力行业加速信息化与工业化深度融合。</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>电缆</t>
+          <t>智能电网, AI</t>
         </is>
       </c>
     </row>
@@ -1654,41 +1653,41 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>3.04</v>
+        <v>2.45</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>据报道，过去数月内，美国三大区域电网运营商相继获批了总计750亿美元的输电扩容项目，核心是建设一批765千伏超高压线路。</t>
+          <t>当地时间4日，微软、谷歌、OpenAI、亚马逊、Meta、xAI和甲骨文这七家公司代表在美国白宫签署自主供电承诺。</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>sh601179</t>
+          <t>sh601868</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>中国西电</t>
+          <t>中国能建</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>18.11</v>
+        <v>2.89</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>10.02</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>电网设备|公司主要经营输配电及控制设备研发、设计、制造、销售、检测、相关设备成套、技术研究、服务与工程承包等业务。</t>
+          <t>电力基建|公司是一家为中国乃至全球能源电力、基础设施等行业提供系统性、一体化、全周期、一揽子发展方案和服务的综合性特大型集团公司，公司作为能源电力和基础设施建设领域的主力军和排头兵，先后承建了三峡工程、南水北调、西气东输、西电东送、三代核电等一系列关系国计民生的重大工程。</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>电网设备</t>
+          <t>电力基建</t>
         </is>
       </c>
     </row>
@@ -1699,28 +1698,28 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>3.04</v>
+        <v>2.45</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>据报道，过去数月内，美国三大区域电网运营商相继获批了总计750亿美元的输电扩容项目，核心是建设一批765千伏超高压线路。</t>
+          <t>当地时间4日，微软、谷歌、OpenAI、亚马逊、Meta、xAI和甲骨文这七家公司代表在美国白宫签署自主供电承诺。</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>sz002857</t>
+          <t>sh603063</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>三晖电气</t>
+          <t>禾望电气</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>23.75</v>
+        <v>31.9</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>10</v>
@@ -1728,671 +1727,671 @@
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>电网设备|公司围绕电网公司“计量资产全寿命周期管理”要求，依托电能表检定这一核心环节的技术优势，以服务于电能表为核心，建立了电能表标准检测设备、电能表自动化流水线型检定系统、电能表智能化仓储系统、用电信息采集系统、互感品等产品，覆盖电能表全生命周期。</t>
+          <t>IDC电源|参股公司欧伏电气与捷通智慧科技股份有限公司等数据中心领域领先企业保持稳定合作。</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>电网设备</t>
+          <t>IDC电源</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>智能电网</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>1.69</v>
+        <v>2.45</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>情报公司IDTechEx预测，2036年全球人形机器人市场规模将达约295亿美元，汽车制造和物流领域将率先普及，然后再拓展到更广泛的商业和消费市场。</t>
+          <t>当地时间4日，微软、谷歌、OpenAI、亚马逊、Meta、xAI和甲骨文这七家公司代表在美国白宫签署自主供电承诺。</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>sz003036</t>
+          <t>sz001216</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>泰坦股份</t>
+          <t>华瓷股份</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>18.26</v>
+        <v>20.99</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>机器人+固态电池|1.2026年2月2日公司在互动平台表示，公司纺织智能柔性操作机器人研发进展顺利，相关产品目前处于运行测试和进一步优化阶段。
-2.公司设立了控股子公司，主要从事固态电池锂硫磷氯电解质的研发和生产。</t>
+          <t xml:space="preserve">特高压|子公司华联火炬的支柱绝缘子、穿墙套管等产品可用于柔性直流输电，有向国网、南网等客户供货。
+</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>机器人, 固态电池</t>
+          <t>特高压</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>智能电网</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>1.69</v>
+        <v>2.45</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>情报公司IDTechEx预测，2036年全球人形机器人市场规模将达约295亿美元，汽车制造和物流领域将率先普及，然后再拓展到更广泛的商业和消费市场。</t>
+          <t>当地时间4日，微软、谷歌、OpenAI、亚马逊、Meta、xAI和甲骨文这七家公司代表在美国白宫签署自主供电承诺。</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>sz002456</t>
+          <t>sz002843</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>欧菲光</t>
+          <t>泰嘉股份</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>9.779999999999999</v>
+        <v>27.93</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>消费电子+机器人|1.公司是消费电子领域重要的光学光电模组供应商，业务涵盖微摄像头模组、触摸屏和触控显示全贴合模组、指纹识别模组。
-2.公司深入布局机器视觉深度模块方向，参与小米全尺寸人形仿生机器人深度视觉模组开发。</t>
+          <t>IDC电源+华为|1.公司电源业务包含一部分数据中心电源业务，主要为服务器电源模块产品。服务客户为行业头部品牌客户。
+2.问界的户用充电桩现由泰嘉股份旗下雅达电子独家供应。</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>消费电子, 机器人</t>
+          <t>IDC电源, 华为</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>发电机概念</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>1.69</v>
+        <v>3.74</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>情报公司IDTechEx预测，2036年全球人形机器人市场规模将达约295亿美元，汽车制造和物流领域将率先普及，然后再拓展到更广泛的商业和消费市场。</t>
+          <t>花旗发布研报称，东方电气取得关键战略突破。公司已从加拿大客户获得20台50MW燃气轮机发电机组的里程碑式订单，单价为2亿元人民币，毛利率达40-50%。</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>sz002520</t>
+          <t>sh600590</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>日发精机</t>
+          <t>泰豪科技</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>6.77</v>
+        <v>16.18</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
+        <v>9.99</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>工业母机+机器人|1.数控机床系公司主营业务之一，公司专业生产数控机床，产品数控化率100%，行业排名第一，全部是市场中高端的普及型数控车床和加工中心。
-2.公司拥有桁架机械手直角坐标机器人方面的专利，并已大量应用到自动化连线设备。</t>
+          <t>智能电网+柴发|1.公司智慧能源产业围绕能源互联网、电力信息化、智能电源等方向开展业务，主要产品有区域综合能源服务平台、电力信息化相关软件、智能应急电源以及配电自动化产品。
+2.公司所生产的智能应急电源主要应用于应急及备用供电，产品覆盖1-10000KW各类型智能柴（重）油发电机组、拖车电站、静音发电机组等，在工业企业、数据中心、石油化工、通信、高层建筑等诸多领域均有应用。</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>工业母机, 机器人</t>
+          <t>智能电网, 柴发</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>发电机概念</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>1.69</v>
+        <v>3.74</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>情报公司IDTechEx预测，2036年全球人形机器人市场规模将达约295亿美元，汽车制造和物流领域将率先普及，然后再拓展到更广泛的商业和消费市场。</t>
+          <t>花旗发布研报称，东方电气取得关键战略突破。公司已从加拿大客户获得20台50MW燃气轮机发电机组的里程碑式订单，单价为2亿元人民币，毛利率达40-50%。</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>sh603337</t>
+          <t>sz002448</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>杰克科技</t>
+          <t>中原内配</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>44.14</v>
+        <v>17.91</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>9.99</v>
+        <v>10.01</v>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>机器人+AI|公司在2024年年报中透露，公司高端产品研发取得里程碑进展，高端AI缝纫机原型样机成功落地，“杰克1号”人形机器人、无人模板机等“机器人+AI人工智能+缝制机械”多技术融合的智能高端产品初具雏形。</t>
+          <t>柴油发电机|子公司河南中原吉凯恩气缸套有限公司生产和销售的大缸径气缸套可配套于柴油发电机组，客户包含卡特彼勒、MTU、康明斯、潍柴、玉柴等国内外知名品牌。</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>机器人, AI</t>
+          <t>柴油发电机</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>发电机概念</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>1.51</v>
+        <v>3.74</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>政府工作报告在介绍2026年政府工作任务时提出，深化拓展“人工智能+”，促进新一代智能终端和智能体加快推广，推动重点行业领域人工智能商业化规模化应用。</t>
+          <t>花旗发布研报称，东方电气取得关键战略突破。公司已从加拿大客户获得20台50MW燃气轮机发电机组的里程碑式订单，单价为2亿元人民币，毛利率达40-50%。</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>sh605268</t>
+          <t>sz002478</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>王力安防</t>
+          <t>常宝股份</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>12.67</v>
+        <v>13.87</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.99</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>AI+防盗门|公司机器人安全门首创AI遥感解锁，AI智能防夹功能，实现与智能家居互联；自研AI电机驱动算法技术，实现自动开关门，搭载可视智慧猫眼，独创安全G点，关门自动反锁，独创超C级圆柱体专利锁芯。</t>
+          <t>燃气轮机概念|HRSG产品为公司特色价值产品，主要应用于燃气轮机余热锅炉发电领域。</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>AI, 防盗门</t>
+          <t>燃气轮机概念</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>发电机概念</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>1.51</v>
+        <v>3.74</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>政府工作报告在介绍2026年政府工作任务时提出，深化拓展“人工智能+”，促进新一代智能终端和智能体加快推广，推动重点行业领域人工智能商业化规模化应用。</t>
+          <t>花旗发布研报称，东方电气取得关键战略突破。公司已从加拿大客户获得20台50MW燃气轮机发电机组的里程碑式订单，单价为2亿元人民币，毛利率达40-50%。</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>sz002877</t>
+          <t>sh600482</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>智能自控</t>
+          <t>中国动力</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>10.89</v>
+        <v>39.26</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>AI+阀门|公司是专业化生产和销售全系列智能控制阀产品的高科技民营企业，坚持先进装备的国产化和技术自主创新。控制阀利用人工智能技术和计算机技术、嵌入式数字解决方案实现智能化，使控制阀具有自适应、自校准、自诊断等功能。数字式阀门定位器普及应用到控制阀和电动执行机构中，从而使得智能一体化设计以及智能化的预测性维护成为未来主流。</t>
+          <t>燃气轮机|公司柴油机和燃气轮机产品广泛应用于陆用、海上发电领域。面对数据中心对柴油发电机组的需求，公司正在积极布局相关领域，研究开发适配产品。</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>AI, 阀门</t>
+          <t>燃气轮机</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>发电机概念</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>1.51</v>
+        <v>3.74</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>政府工作报告在介绍2026年政府工作任务时提出，深化拓展“人工智能+”，促进新一代智能终端和智能体加快推广，推动重点行业领域人工智能商业化规模化应用。</t>
+          <t>花旗发布研报称，东方电气取得关键战略突破。公司已从加拿大客户获得20台50MW燃气轮机发电机组的里程碑式订单，单价为2亿元人民币，毛利率达40-50%。</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>sz002195</t>
+          <t>sz000534</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>岩山科技</t>
+          <t>万泽股份</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>10.69</v>
+        <v>41.24</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>脑机接口+AI|1.公司旗下岩思类脑研究院以脑电大数据与脑电大模型为核心技术底座，面向脑科学和人工智能领域的前瞻性研究，开展脑机接口解码算法与系统、非器质性脑疾病（例如癫痫、抑郁症、严重失眠等）的诊断和评估、大脑内在状态调控等方向的科学研究和产品开发，推动研究成果商业化落地。
-2.黑芝麻智能与公司旗下RockAI联合发布基于武当C1200家族芯片的AI Agent解决方案，该方案将部署于未来的智能座舱应用中。</t>
+          <t>燃气轮机|公司的高温合金产品主要用于航空发动机、燃气轮机（地面与船舶燃机、核电、机车动力等领域）、涡轮增压器等，主要客户即该领域公司。</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>脑机接口, AI</t>
+          <t>燃气轮机</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>发电机概念</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>1.51</v>
+        <v>3.74</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>政府工作报告在介绍2026年政府工作任务时提出，深化拓展“人工智能+”，促进新一代智能终端和智能体加快推广，推动重点行业领域人工智能商业化规模化应用。</t>
+          <t>花旗发布研报称，东方电气取得关键战略突破。公司已从加拿大客户获得20台50MW燃气轮机发电机组的里程碑式订单，单价为2亿元人民币，毛利率达40-50%。</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sh688031</t>
+          <t>sz301032</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>星环科技-U</t>
+          <t>新柴股份</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>223.21</v>
+        <v>15.13</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>20</v>
+        <v>19.98</v>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI+商业航天|1.公司提供从语料处理、模型训练、知识库建设、应用开发、智能体构建等一整套工具链，致力于开发数据分析的垂直领域大模型，并基于该数据分析垂类大模型，打造数据分析相关智能体。
-2.公司冠名了我国首颗商业红外气象卫星“星环号·南信大星”，“星环号·南信大星”从中国酒泉卫星发射基地发射升空，并顺利进入预定轨道发射任务取得圆满成功。“星环号·南信大星”采用了星环科技自主可控的全栈基础软件产品进行开源产品国产化替代，通过对卫星气象数据进行分析，服务于山火监测、环境保护、能源电力、安全生产、农林渔业、气象、金融等多个领域。 </t>
+          <t>柴油发动机|公司的主营业务为非道路用柴油发动机及相关零部件的研发、生产与销售，主要应用于工程机械、农业机械以及发电机组等领域，公司产品可配套于发电机组领域。</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>AI, 商业航天</t>
+          <t>柴油发动机</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>石油化工</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>1</v>
+        <v>1.66</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>郑商所PX、PTA期货主力合约盘中双双触及涨停。</t>
+          <t>《政府工作报告》提出“实施超大规模智算集群、算电协同等新基建工程，加强全国一体化算力监测调度，支持公共云发展”。“算电协同”首次被写入政府工作报告，明确列为新基建工程。</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sz002986</t>
+          <t>sh600821</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>宇新股份</t>
+          <t>金开新能</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>16.01</v>
+        <v>8.6</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
+        <v>9.969999999999999</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>6天3板</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>石化|公司立足大亚湾石化区，目前已发展成为华南地区最大的LPG深加工企业。公司主要产品包括以LPG中的异丁烷、异丁烯、正丁烯等组分为原料生产的异辛烷、甲基叔丁基醚，主要用于生产车用成品汽油。</t>
+          <t>电力+算力|1.公司主营业务为新能源电力的开发、投资、建设及运营，包括光伏发电和风力发电两个板块。
+2.2024年10月8日公告，公司全资子公司金开新能科技有限公司拟于新疆昌吉市投资建设国家超算广州中心新疆分中心昌吉智算中心项目，算力总规模达到5,000PFlops。</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>石化</t>
+          <t>电力, 算力</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>石油化工</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>1</v>
+        <v>1.66</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>郑商所PX、PTA期货主力合约盘中双双触及涨停。</t>
+          <t>《政府工作报告》提出“实施超大规模智算集群、算电协同等新基建工程，加强全国一体化算力监测调度，支持公共云发展”。“算电协同”首次被写入政府工作报告，明确列为新基建工程。</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sh600800</t>
+          <t>sz000601</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>渤海化学</t>
+          <t>韶能股份</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>4.81</v>
+        <v>6.14</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>10.07</v>
+        <v>10.04</v>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>石化|石化业务为公司的核心业务板块，全资子公司渤海石化一直专注于丙烷制丙烯业务，是京津冀地区最具有话语权的丙烯生产商，下游的丙烯客户涵盖聚丙烯、丁辛醇、环氧丙烷、苯酚丙酮、丙烯酸等行业。</t>
+          <t>电力|公司自成立以来，一直以能源的投资开发经营为主营业务，在不断巩固和发展水电产业的基础上，重点发展生物质能发电、加油加气充电一体化站等业务。</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>石化</t>
+          <t>电力</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>石油化工</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>1</v>
+        <v>1.66</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>郑商所PX、PTA期货主力合约盘中双双触及涨停。</t>
+          <t>《政府工作报告》提出“实施超大规模智算集群、算电协同等新基建工程，加强全国一体化算力监测调度，支持公共云发展”。“算电协同”首次被写入政府工作报告，明确列为新基建工程。</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>sz300072</t>
+          <t>sz002015</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>海新能科</t>
+          <t>协鑫能科</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>5.88</v>
+        <v>15.62</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>石化+生物燃料|1.公司依托自主研发的核心技术和产品，为石化能源与化工行业提供相关工艺技术、净化剂与催化剂、核心设备以及工程服务等综合解决方案，为生态农业和绿色能源提供生物质综合利用解决方案以及新型产品。
-2.公司依托核心催化剂，以公司的悬浮床技术作为核心转化单元，开发了独特的新型生物燃料生产技术，可以为市场提供大量的绿色油品和绿色化工原料，既解决了大量固体废弃生物质无法得到经济、有效利用的问题，又可以形成规模化的绿色能源和循环经济产业，实现显著的二氧化碳减排。</t>
+          <t>电力+算力|1.公司在立足于成熟稳健增长的清洁能源投资、开发、运营的基础上，在能源结构、业务模式及能源应用三方面进行优化转型，并将最终成为新型电力系统综合服务商。
+2.公司在上海、苏州投运两个智算中心，已投运超千P的算力资源。</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>石化, 生物燃料</t>
+          <t>电力, 算力</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>石油化工</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>1</v>
+        <v>1.66</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>郑商所PX、PTA期货主力合约盘中双双触及涨停。</t>
+          <t>《政府工作报告》提出“实施超大规模智算集群、算电协同等新基建工程，加强全国一体化算力监测调度，支持公共云发展”。“算电协同”首次被写入政府工作报告，明确列为新基建工程。</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>sz000703</t>
+          <t>sh605286</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>恒逸石化</t>
+          <t>同力天启</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>13.09</v>
+        <v>42.49</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>石化|公司在国内同行中形成独有的“涤纶+锦纶”双纶驱动石化产业链为核心业务，以供应链服务业务为成长业务，差别化纤维产品、工业智能技术应用为新兴业务的“石化+”多层次立体产业布局。</t>
+          <t>绿电|公司主营包括新能源电站开发业务，旗下包括天津铭源嘉旺100MW风电项目，承德航天鸿源300MW风场项目，承德航天天启500MW风光储氢多能互补项目等。</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>石化</t>
+          <t>绿电</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>发电机概念</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>2.28</v>
+        <v>1.66</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>花旗发布研报称，东方电气取得关键战略突破。公司已从加拿大客户获得20台50MW燃气轮机发电机组的里程碑式订单，单价为2亿元人民币，毛利率达40-50%。</t>
+          <t>《政府工作报告》提出“实施超大规模智算集群、算电协同等新基建工程，加强全国一体化算力监测调度，支持公共云发展”。“算电协同”首次被写入政府工作报告，明确列为新基建工程。</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>sh600875</t>
+          <t>sh600396</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>东方电气</t>
+          <t>华电辽能</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>42.21</v>
+        <v>3.66</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>10.01</v>
+        <v>9.91</v>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>燃气轮机|公司在2025世界清洁能源装备大会上发布了自主研发的首款15兆瓦纯氢燃气轮机。</t>
+          <t>绿电|公司是中国华电集团公司的实际控制的上市公司、中央企业的三级单位，同时也是一家集火力发电、风力发电、煤炭营销、供热、供汽为一体的综合性区域基础能源企业。</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>燃气轮机</t>
+          <t>绿电</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>发电机概念</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>2.28</v>
+        <v>1.66</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>花旗发布研报称，东方电气取得关键战略突破。公司已从加拿大客户获得20台50MW燃气轮机发电机组的里程碑式订单，单价为2亿元人民币，毛利率达40-50%。</t>
+          <t>《政府工作报告》提出“实施超大规模智算集群、算电协同等新基建工程，加强全国一体化算力监测调度，支持公共云发展”。“算电协同”首次被写入政府工作报告，明确列为新基建工程。</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>sh601727</t>
+          <t>sz001896</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>上海电气</t>
+          <t>豫能控股</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>9.460000000000001</v>
+        <v>15.88</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>10</v>
+        <v>9.969999999999999</v>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>燃气轮机|在燃机领域，公司通过国际并购与技术消化吸收，突破了国外OEM长期以来对燃气轮机研发、服务的壁垒，建立了完整的重型燃气轮机开发设计平台，具备了贯穿燃气轮机全产业链和全生命周期的技术和服务能力。</t>
+          <t>电力+算力|1.公司是河南省内唯一省级资本控股的电力上市公司，从事的主要业务包括，火电项目的投资管理、能源销售、新能源项目投资建设等。
+2.豫能控股早间公告，公司正在筹划参股投资公司控股股东河南投资集团下属控股企业先天算力（河南）科技有限公司，并联合河南投资集团以先天算力为收购主体，收购郑州合盈数据有限责任公司控股权相关事项。此次参股投资事项尚处筹划阶段，存在较大不确定性。</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>燃气轮机</t>
+          <t>电力, 算力</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>发电机概念</t>
+          <t>人工智能</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>2.28</v>
+        <v>1.59</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>花旗发布研报称，东方电气取得关键战略突破。公司已从加拿大客户获得20台50MW燃气轮机发电机组的里程碑式订单，单价为2亿元人民币，毛利率达40-50%。</t>
+          <t>工业和信息化部部长李乐成表示，“人工智能+制造”是一个必答题，不是一个选择题。“今年，我们将大力推动“人工智能+制造”，制造业的各行各业都要拥抱人工智能。</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
@@ -2400,44 +2399,48 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>sh600590</t>
+          <t>sh605268</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>泰豪科技</t>
+          <t>王力安防</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>14.71</v>
+        <v>13.94</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>10.02</v>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>柴油发电机|公司所生产的智能应急电源主要应用于应急及备用供电，产品覆盖1-10000KW各类型智能柴（重）油发电机组、拖车电站、静音发电机组等，在工业企业、数据中心、石油化工、通信、高层建筑等诸多领域均有应用。</t>
+          <t>智能经济|公司机器人安全门首创AI遥感解锁，AI智能防夹功能，实现与智能家居互联；自研AI电机驱动算法技术，实现自动开关门，搭载可视智慧猫眼，独创安全G点，关门自动反锁，独创超C级圆柱体专利锁芯。</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>柴油发电机</t>
+          <t>智能经济</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>人工智能</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>1.98</v>
+        <v>1.59</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>三星电子Q1 DRAM价格涨幅从70%上调至100%。此外，佰维存储公告称，预计2026年1-2月实现营业收入40亿元至45亿元，同比增长340%至395%。</t>
+          <t>工业和信息化部部长李乐成表示，“人工智能+制造”是一个必答题，不是一个选择题。“今年，我们将大力推动“人工智能+制造”，制造业的各行各业都要拥抱人工智能。</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
@@ -2445,45 +2448,48 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>sh603688</t>
+          <t>sh600545</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>石英股份</t>
+          <t>卓郎智能</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>53.04</v>
+        <v>4.15</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
+        <v>10.08</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>石英+半导体材料|1.公司生产的高纯石英棒是制备石英纤维电子纱（布）关键基础原材料。
-2.公司产品主要有高纯石英砂、石英管、石英棒、石英板、石英筒、石英锭、石英砣等各类高纯石英材料，产品主要应用于光电、光纤、光学、光伏、半导体等领域。</t>
+          <t>智能经济|公司的数据与服务事业部依托纺机装备数字化和智能化水平的提升，借助5G、AI、物联网、大数据、云计算等新技术手段，并依靠公司在纺织工业全产业链的整合能力和影响力，联合数字行业龙头企业打造纺织工业数据与服务业务。从单体设备智能化，到纺织工厂的数字化管理，再到智慧工厂平台化管理方案，构建三大闭环，并对纺织工业生态系统的进化进行全面综合赋能。</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>石英, 半导体材料</t>
+          <t>智能经济</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>人工智能</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>1.98</v>
+        <v>1.59</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>三星电子Q1 DRAM价格涨幅从70%上调至100%。此外，佰维存储公告称，预计2026年1-2月实现营业收入40亿元至45亿元，同比增长340%至395%。</t>
+          <t>工业和信息化部部长李乐成表示，“人工智能+制造”是一个必答题，不是一个选择题。“今年，我们将大力推动“人工智能+制造”，制造业的各行各业都要拥抱人工智能。</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
@@ -2491,45 +2497,44 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>sz002559</t>
+          <t>sz301218</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>亚威股份</t>
+          <t>华是科技</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>10.47</v>
+        <v>38.51</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>9.98</v>
+        <v>20.01</v>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>机器人+存储芯片|1.公司主要产品为数控平板加工机床、普通平板加工机床、数控卷板加工机械。线性和水平多关节机器人供货库卡、徕斯和亚威内部。
-2.公司参股企业苏州芯测全资收购的韩国GSI公司拥有技术难度较高的存储芯片测试机业务，稳定供货于海力士、安靠等行业龙头。</t>
+          <t>AI应用|公司产品和业务涉及计算机软件、物联网、大数据及人工智能等方面，公司自主研发的水上智能卡口系统、三维激光哨兵、电力现场作业安全预警系统、磁芯缺陷检测机等产品，均有人工智能技术运用；此外，公司已经在运用人工智能技术实现内河船舶辅助驾驶、自主驾驶方面进行布局。</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>机器人, 存储芯片</t>
+          <t>AI应用</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>1.98</v>
+        <v>1.38</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>三星电子Q1 DRAM价格涨幅从70%上调至100%。此外，佰维存储公告称，预计2026年1-2月实现营业收入40亿元至45亿元，同比增长340%至395%。</t>
+          <t>3月5日，《政府工作报告》提出“实施超大规模智算集群、算电协同等新基建工程，加强全国一体化算力监测调度，支持公共云发展。</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
@@ -2537,30 +2542,33 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>sh603058</t>
+          <t>sz000815</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>永吉股份</t>
+          <t>美利云</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>13.74</v>
+        <v>16.31</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I45" s="2" t="inlineStr"/>
+        <v>9.98</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>半导体+AI应用|1.公司旗下埃延半导体是一家拥有独立自主知识产权的科研制造公司，致力于大硅片及第三代半导体材料衬底外延设备的生产制造以及衬底材料的研发，主要产品是研发和量产外延片所需的生产设备。
-2.子公司重庆叁圭动漫科技经营范围包括动漫游戏开发；人工智能基础软件开发；人工智能基础资源与技术平台；人工智能应用软件开发；人工智能通用应用系统；人工智能双创服务平台；人工智能行业应用系统集成服务；人工智能公共数据平台；人工智能硬件销售等。</t>
+          <t>算力租赁|公司主要从事IDC业务，专业为大型互联网企业提供数据机房机柜出租托管，同时提供宽带接入服务。公司数据中心位于“东数西算”节点城市之一，具备高性能网络资源、低成本电力、高规格设计、优质气候条件及可扩展的空间。涉及的底层和应用层面的云计算、算力、AI人工智能技术、搜索技术、网络安全等相关业务和服务正在积极探索。</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>半导体, AI应用</t>
+          <t>算力租赁</t>
         </is>
       </c>
     </row>
@@ -2571,11 +2579,11 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>1.74</v>
+        <v>1.38</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>IDC咨询发布报告称，由于智能体任务执行密度的增长和任务复杂度的提升，也将带来智能体Token消耗年均超30倍的指数级跃升。</t>
+          <t>3月5日，《政府工作报告》提出“实施超大规模智算集群、算电协同等新基建工程，加强全国一体化算力监测调度，支持公共云发展。</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
@@ -2583,29 +2591,30 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>sh600666</t>
+          <t>sz000818</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">奥瑞德  </t>
+          <t>航锦科技</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>3.98</v>
+        <v>23.76</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>9.94</v>
+        <v>10</v>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>算力租赁|公司设立全资子公司北京智算力、深圳智算力，使用自有资金投资建设算力租赁一、二、三期项目。</t>
+          <t>算力租赁+化工|1.2024年2月6日公告，全资子公司航锦人工智能近期分别与迈异科技、易起联科技、泛超数字签订了《算力服务合同》，向迈异科技、易起联科技、泛超数字提供算力服务，三笔服务合同共计含税总金额约为8.46亿元。
+2.公司从事半导体电子和基础化工原料双主业，化工板块业务是公司的传统优势业务，主要产品包括烧碱、液氯、氯化苯、环氧丙烷、聚醚及聚氯乙烯等。</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>算力租赁</t>
+          <t>算力租赁, 化工</t>
         </is>
       </c>
     </row>
@@ -2616,11 +2625,11 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>1.74</v>
+        <v>1.38</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>IDC咨询发布报告称，由于智能体任务执行密度的增长和任务复杂度的提升，也将带来智能体Token消耗年均超30倍的指数级跃升。</t>
+          <t>3月5日，《政府工作报告》提出“实施超大规模智算集群、算电协同等新基建工程，加强全国一体化算力监测调度，支持公共云发展。</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
@@ -2628,44 +2637,45 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>sz300895</t>
+          <t>sz002261</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>铜牛信息</t>
+          <t>拓维信息</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>61.54</v>
+        <v>39.05</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>20.01</v>
+        <v>10</v>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>算力租赁|公司是北京市国资委下属企业，是在国内尤其是在北京地区少数拥有自有房产自建数据中心且自主搭建云平台的专业IDC服务商之一。</t>
+          <t>华为+算力|1.截至2023年，公司成为华为唯一“鲲鹏/昇腾+鸿蒙”软硬一体战略伙伴，是华为在人工智能领域覆盖“软件+硬件生产+生态运营”的全方位深度合作的伙伴。2022年，公司携手华为在8大节点算力中心做了布局。
+2.公司在北京参与了以“清华大学数据与计算公共平台”为代表的系列人工智能项目建设，在广州参与了广东AI智算中心建设项目。</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>算力租赁</t>
+          <t>华为, 算力</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>液冷IDC</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>1.74</v>
+        <v>0.86</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>IDC咨询发布报告称，由于智能体任务执行密度的增长和任务复杂度的提升，也将带来智能体Token消耗年均超30倍的指数级跃升。</t>
+          <t>英伟达AI基础设施负责人Dion Harris在加州总部向媒体展示了下一代Vera Rubin算力系统的内部构成与供应链细节。由于功耗上升，Vera Rubin也是英伟达首个100%液冷散热的系统。</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
@@ -2673,275 +2683,272 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>sz000815</t>
+          <t>sh603158</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>美利云</t>
+          <t>腾龙股份</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>14.83</v>
+        <v>10.96</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>10.01</v>
+        <v>10.04</v>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>算力租赁|公司主要从事IDC业务，专业为大型互联网企业提供数据机房机柜出租托管，同时提供宽带接入服务。公司数据中心位于“东数西算”节点城市之一，具备高性能网络资源、低成本电力、高规格设计、优质气候条件及可扩展的空间。涉及的底层和应用层面的云计算、算力、AI人工智能技术、搜索技术、网络安全等相关业务和服务正在积极探索。</t>
+          <t>液冷IDC|公司电子水泵产品有向客户供货，间接应用于数据中心/服务器液冷领域。</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>算力租赁</t>
+          <t>液冷IDC</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>量子科技</t>
+          <t>液冷IDC</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>2.92</v>
+        <v>0.86</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>政府工作报告提出，建立未来产业投入增长和风险分担机制，培育发展未来能源、量子科技等未来产业。</t>
+          <t>英伟达AI基础设施负责人Dion Harris在加州总部向媒体展示了下一代Vera Rubin算力系统的内部构成与供应链细节。由于功耗上升，Vera Rubin也是英伟达首个100%液冷散热的系统。</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>sz000555</t>
+          <t>sz001400</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>神州信息</t>
+          <t>江顺科技</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>18.02</v>
+        <v>125.9</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>量子科技+AI|1.公司通过与国盾量子、国科量子深度战略合作，加强量子通信网络的运维服务及政府、金融、军工国防等行业应用解决方案的开发，并于2019年正式发布由公司自主研发的新一代企业级即时加密通讯工具“量信通”产品。
-2.子公司华通云数据是火山引擎的HiAgent的合作伙伴，目前双方共同致力于HiAgent平台在教育和企业行业的应用推广。</t>
+          <t>液冷+商业航天|1.子公司江宇科技主要从事用于服务器液冷相关的3D打印产品的研发工作，已有部分样品。
+2.公司产品铝型材挤压模具和铝型材挤压配套设备应用于航空航天领域。</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>量子科技, AI</t>
+          <t>液冷, 商业航天</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>量子科技</t>
+          <t>液冷IDC</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>2.92</v>
+        <v>0.86</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>政府工作报告提出，建立未来产业投入增长和风险分担机制，培育发展未来能源、量子科技等未来产业。</t>
+          <t>英伟达AI基础设施负责人Dion Harris在加州总部向媒体展示了下一代Vera Rubin算力系统的内部构成与供应链细节。由于功耗上升，Vera Rubin也是英伟达首个100%液冷散热的系统。</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>sh600468</t>
+          <t>sh603269</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>百利电气</t>
+          <t>海鸥股份</t>
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>8.550000000000001</v>
+        <v>16.94</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>10.04</v>
+        <v>10</v>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>量子科技+超导|超导量子是量子通信的重要技术，高温超导线材是超导产品的核心基础材料，公司控股子公司北京英纳超导技术有限公司是国内较早成立的专业研发生产高温超导材料的企业，承担过多项国家863项目、科技部重大专项、北京市重大科技计划等重大超导项目，其“高性能铋系高温超导长带材的研制与开发”曾获得国务院国家科学技术进步二等奖。</t>
+          <t>数据中心温控|公司主要从事各类冷却塔的研发、设计、制造及安装业务，并依托自身产品和技术优势提供工业及民用冷却塔相关的技术服务。公司研制的冷却塔广泛应用于石化、冶金、电力等领域以及公共设施、商务建筑、数据中心等的中央空调系统。</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>量子科技, 超导</t>
+          <t>数据中心温控</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>核电</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>2.32</v>
+        <v>-0.09</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>据不完全统计，2026年以来，星环聚能、中科清能、东昇聚变、束研聚创等可控核聚变项目陆续更新了融资进展。</t>
+          <t>章源钨业发布3月上半月长单采购报价，55%黑钨精矿报价为90万元/标吨，55%白钨精矿报价为89.9万元/标吨，仲钨酸铵（国标零级）报价为133万元/吨，环比分别上涨23.3%、23.3%、24.3%。</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>sz002471</t>
+          <t>sz301265</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>中超控股</t>
+          <t>华新环保</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>9.039999999999999</v>
+        <v>19.8</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>9.98</v>
+        <v>20</v>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>核电+商业航天|1.公司在2022年年度报告中透露，公司已完成研发出一种耐高温抗拉耐腐蚀型核电站用电缆，其具有优良的耐长期热老化性能、耐辐照、电气性能稳定、阻燃性能好及无卤低烟低毒等特点，适应核电站恶劣的工作环境。
-2.孙公司江苏精铸专业从事高温合金精密铸件的制造，转化上海交大前期航空发动机及燃气轮机、航天特种飞行器、运载火箭等关键热端零部件的技术研发成果，并进一步研究优化高温合金精密铸件批量化生产工艺。</t>
+          <t>有色金属提取回收|子公司华新耀智开展钴、镍、锌等有色金属的提取业务。</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>核电, 商业航天</t>
+          <t>有色金属提取回收</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>核电</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>2.32</v>
+        <v>-0.09</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>据不完全统计，2026年以来，星环聚能、中科清能、东昇聚变、束研聚创等可控核聚变项目陆续更新了融资进展。</t>
+          <t>章源钨业发布3月上半月长单采购报价，55%黑钨精矿报价为90万元/标吨，55%白钨精矿报价为89.9万元/标吨，仲钨酸铵（国标零级）报价为133万元/吨，环比分别上涨23.3%、23.3%、24.3%。</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>sh600516</t>
+          <t>sh600397</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>方大炭素</t>
+          <t>江钨装备</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>6.88</v>
+        <v>19.99</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>10.08</v>
+        <v>10.02</v>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">核电|公司是中国炭和石墨制品龙头企业，公司是我国第一个自行设计建设的大型综合炭素生产企业，也是全国唯一的大型高炉炭砖生产基地，2017年，公司高温气冷堆炭堆内构件展示项目获得中国国际高新技术成果交易会优秀产品奖。 </t>
+          <t>稀土+钨|1.2025年4月2日公告，公司控股股东江钨控股拟将控股子公司江钨发展持有的金环磁选57%股份，与公司所持有的煤炭业务相关资产及负债进行置换，拟置入资产与拟置出资产交易价格的差额由一方向另一方以现金等方式补足。本次交易构成关联交易，预计将构成重大资产重组。金环磁选的SCT永磁筒式磁选机适用于于磁铁矿、磁黄铁矿、磁赤铁矿、钛磁铁矿、焙烧物料的粗选、扫选、精选作业，也适用于各种非金属矿物的磨后除铁作业。
+2.江钨装备公告称，为推进公司对钨产业链及钽铌产业链的资源整合工作，进一步优化公司产业布局，公司拟向特定对象发行不超过2.97亿股A股股票，募集资金总额不超过18.82亿元，用于收购江西江钨硬质合金有限公司、赣州华茂钨材料有限公司、九江有色金属冶炼有限公司100%股权。</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>核电</t>
+          <t>稀土, 钨</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>1.92</v>
+        <v>-0.09</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>英伟达近日分别发布声明称，将在多年期协议中分别向Lumentum Holdings Inc.和相干公司投资20亿美元。两项交易均包括采购协议以及先进激光组件的使用。</t>
+          <t>章源钨业发布3月上半月长单采购报价，55%黑钨精矿报价为90万元/标吨，55%白钨精矿报价为89.9万元/标吨，仲钨酸铵（国标零级）报价为133万元/吨，环比分别上涨23.3%、23.3%、24.3%。</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>sz001267</t>
+          <t>sz002667</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>汇绿生态</t>
+          <t>威领股份</t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>36.96</v>
+        <v>26.69</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>10.02</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>光通信|公司旗下钧恒科技是专业从事高端光通信产品的研制、生产及推广的高新技术企业，拥有从光学组件，光电转换模块，光端机及子系统的行业垂直整合能力，能够为客户提供各种特定应用的定制化产品，包括PLCC、Mini SFF、Micro Pod等各种形态及各种复合协议的光端机及波分复用子系统。</t>
+          <t>锂矿+有色金属|1.公司主要以新能源锂电材料产业链为主体，包括锂矿选矿、基础性锂电原料锂盐加工及冶炼业务，主要产品包括锂化合物及衍生品、锂精矿及伴生品和振动筛及PC生产线等。旗下领辉科技具备锂云母年选矿产能120万吨。
+2.2025年5月20日公告，控股孙公司天津长领矿业以2.2亿元成功竞得湖南临武嘉宇矿业74.3%股权。嘉宇矿业拥有锡矿石247万吨、铅矿石119万吨、锌矿石117万吨，年开采规模30万吨，可迅速形成稳定的采选产能。</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>锂矿, 有色金属</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>创新药</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>1.92</v>
+        <v>3.36</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>英伟达近日分别发布声明称，将在多年期协议中分别向Lumentum Holdings Inc.和相干公司投资20亿美元。两项交易均包括采购协议以及先进激光组件的使用。</t>
+          <t>政府工作报告将生物医药列入新兴支柱产业，与集成电路、航空航天、低空经济等产业并列。2026年至今2个多月，BD总包金额已超过500亿，超过2025年的40%。</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
@@ -2949,422 +2956,511 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>sz002796</t>
+          <t>sh688176</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>世嘉科技</t>
+          <t>亚虹医药-U</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>57.32</v>
+        <v>16.78</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I54" s="2" t="inlineStr"/>
+        <v>20.03</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>光模块|2025年8月4日公告，公司看好光通信细分行业的市场前景，认可光彩芯辰（浙江）科技有限公司在光通信领域内的前期投入、技术储备以及客户资源。公司拟通过增资扩股的方式取得光彩芯辰部分股权，并与光彩芯辰签署了《增资意向协议》。如交易顺利完成，公司将于交易完成后预计持有光彩芯辰不超过20%的股权。光彩芯辰主要从事100G—800G多系列光通信模块的研发制造，总部及生产基地均位于中新嘉善现代产业园。</t>
+          <t>创新药|亚虹医药公告称，公司收到国家药品监督管理局核准签发的《药品注册证书》，批准APL-1702（商标名：希维她®/CEVIRA®，通用名：盐酸氨酮戊酸己酯软膏宫颈光动力治疗系统）上市，用于治疗18岁及以上经组织学证实为子宫颈上皮内瘤变2级（CIN2）患者。</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>光模块</t>
+          <t>创新药</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>氢能</t>
+          <t>创新药</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>1.77</v>
+        <v>3.36</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>全国政协委员，中国工程院院士马永生在2026全国两会建言中提出，强化顶层设计，构建国家氢能基础设施一张网。支持大型能源企业开展跨省氢能管道试点，加快绿氢认证与碳交易市场的衔接。</t>
+          <t>政府工作报告将生物医药列入新兴支柱产业，与集成电路、航空航天、低空经济等产业并列。2026年至今2个多月，BD总包金额已超过500亿，超过2025年的40%。</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>sz002733</t>
+          <t>sh600645</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>雄韬股份</t>
+          <t>中源协和</t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>24.48</v>
+        <v>30.9</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>10.02</v>
+        <v>10</v>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>氢能+IDC电源|1.公司的主营业务产品为铅酸蓄电池、锂电池及氢燃料电池，锂离子电池产品涵盖磷酸铁锂、钴酸锂、锰酸锂三大系列，其中磷酸铁锂电池项目被列为国家火炬计划重点项目和深圳市科技资助项目，也是公司最主要的锂离子电池产品。
-2.公司主要为数据中心及算力中心提供UPS电池。</t>
+          <t>创新药|在细胞治疗板块，公司在干细胞和免疫细胞方面均有布局。截止2024年年报，公司与知名三甲医院合作共计获得12个国家卫健委/药监局两委局干细胞临床备案研究项目。根据CDE网站统计，公司间充质干细胞药物获得药物临床试验批准的数量为国内第一。</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>氢能, IDC电源</t>
+          <t>创新药</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>农业种植</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="C56" s="2" t="inlineStr"/>
+        <v>3.23</v>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>机构认为,在金属和能源价格率先走强之后,农业作为成本传导的末端环节,正在逐步进入价格上行阶段。</t>
+        </is>
+      </c>
       <c r="D56" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>sz000711</t>
+          <t>sh600108</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>ST京蓝</t>
+          <t>亚盛集团</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>4.01</v>
+        <v>5.52</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>4.97</v>
+        <v>9.959999999999999</v>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>23天16板</t>
+          <t>6天5板</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 主要业务包括流域水生态修复、灌区节水综合系统工程、污水治理、沿河生态景观工程、智慧水务等。</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr"/>
+          <t>农业种植|1.公司2026年3月2日公告，目前未开展矿产相关业务，也不存在需要披露的相关重大信息。
+2.公司主要种植经营啤酒花、马铃薯、牧草、果品、药材、食葵、辣椒、枸杞、香辛料等初级农产品和加工产品，以及生产经营节水灌溉设备。</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>农业种植</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>农业种植</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="C57" s="2" t="inlineStr"/>
+        <v>3.23</v>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>机构认为,在金属和能源价格率先走强之后,农业作为成本传导的末端环节,正在逐步进入价格上行阶段。</t>
+        </is>
+      </c>
       <c r="D57" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>sh603268</t>
+          <t>sh600354</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST松发 </t>
+          <t>敦煌种业</t>
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>123.38</v>
+        <v>7.63</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>12天8板</t>
-        </is>
-      </c>
+        <v>9.94</v>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 拟收购恒力重工主营船舶及高端装备的研发、生产及销售，已确定排产新造船舶140艘，货值约108亿美元，船型包含散货船、VLCC、VLOC 和集装箱船等。</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr"/>
+          <t>种业|公司目前主要从事各类农作物种子的研发、生产、加工、销售和脱水菜、番茄粉、番茄酱、啤酒花制品的加工、销售以及棉花及其副产品的收购、加工、仓储、贸易。</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>种业</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>人脑工程</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="C58" s="2" t="inlineStr"/>
+        <v>1.87</v>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>政府工作报告中提出，建立未来产业投入增长和风险分担机制，培育发展脑机接口等未来产业。</t>
+        </is>
+      </c>
       <c r="D58" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>sh603838</t>
+          <t>sz000516</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST四通 </t>
+          <t>国际医学</t>
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>5.01</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>5天3板</t>
-        </is>
-      </c>
+        <v>10.11</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司是一家集研发、设计、生产、销售于一体的新型家居生活陶瓷供应商，产品覆盖日用陶瓷、卫生陶瓷、艺术陶瓷、建筑装饰等全系列家居生活用瓷。</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr"/>
+          <t>脑机接口|旗下医疗机构引进脑机接口结合外骨骼机器人或功能性电刺激等相关康复设备的康复训练系统，开展了脑深部电刺激手术、脊髓神经电刺激手术、迷走神经电刺激手术等相关手术。</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>脑机接口</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>人脑工程</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="C59" s="2" t="inlineStr"/>
+        <v>1.87</v>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>政府工作报告中提出，建立未来产业投入增长和风险分担机制，培育发展脑机接口等未来产业。</t>
+        </is>
+      </c>
       <c r="D59" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>sh603813</t>
+          <t>sh603716</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST原尚 </t>
+          <t>塞力医疗</t>
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>36.18</v>
+        <v>23.18</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>4.99</v>
+        <v>10.01</v>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司参股公司广东原锋新能源科技的股东之一锋源是国内极少的集全套自主知识产权氢燃料电池电堆以及核心零部件膜电极、催化剂、金属双极板等研发、生产、销售一体的公司。</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr"/>
+          <t>脑机接口+AI医疗|子公司海思太科与浙江大学医学院附属第一医院精神卫生中心积极部署国家脑计划2030数字疗法产品——精神疾病全病程数智系统海思灵曦，该系统已在浙一精神卫生中心临床门诊正式启用，同时接收全国多中心临床病组数据。2025年4月，塞力医疗集团专注于感染及危重症快速分子诊断、脑科学数字疗法为主研方向的AI诊疗技术研发中心（TAIDx Lab）已在上海正式部署完成。</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>脑机接口, AI医疗</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>光伏</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="C60" s="2" t="inlineStr"/>
+        <v>1.3</v>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>广发证券表示，AI巨头群雄逐鹿，“算力上天”已成共识。“算力上天”的共识推动下，太空光伏作为主要供能形式有望深度受益。预计未来有望累计为光伏设备累计带来千亿级市场空间。</t>
+        </is>
+      </c>
       <c r="D60" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>sz002592</t>
+          <t>sz002506</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>ST八菱</t>
+          <t>协鑫集成</t>
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>9.85</v>
+        <v>5.56</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="I60" s="2" t="inlineStr"/>
+        <v>10.1</v>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司配套氢燃料电池客车的产品技术目前已经形成商业化，广泛应用于燃气客车、混合动力客车和军车等领域。</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr"/>
+          <t>光伏|公司致力于打造成全球领先的绿色能源系统集成商，产品覆盖高效电池、大尺寸光伏组件、储能系统等，并为客户提供智慧光储一体化集成方案，包含绿色能源工程相关的产品设计、定制、生产、安装、销售等一揽子服务内容。公司近年新建合肥、芜湖、阜宁电池组件基地，已具备12GW N型TOPCon电池产能、近30GW高效组件产能。</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>光伏</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>光伏</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="C61" s="2" t="inlineStr"/>
+        <v>1.3</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>广发证券表示，AI巨头群雄逐鹿，“算力上天”已成共识。“算力上天”的共识推动下，太空光伏作为主要供能形式有望深度受益。预计未来有望累计为光伏设备累计带来千亿级市场空间。</t>
+        </is>
+      </c>
       <c r="D61" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>sz002713</t>
+          <t>sh603778</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>*ST东易</t>
+          <t>国晟科技</t>
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>9.73</v>
+        <v>17.11</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="I61" s="2" t="inlineStr"/>
+        <v>10.03</v>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司基于数字化系统优势和业务场景优势，研发推出了行业内首个新一代AIGC技术和真家系统结合的全新设计工具“真家 AIGC”，同时打造出AI 创意大师、AI小白设计家两款智能应用设计工具。</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr"/>
+          <t>光伏+并购重组|1.公司目前从事大尺寸高效异质结光伏电池的研发、生产、销售，以及异质结、TOPCON、PERC等电池组件的生产与销售。控股孙公司恒立聚能涉及钙钛矿研究。
+2.国晟科技公告称，公司拟以2.406亿元的价格受让正豪科技、林琴合计持有的孚悦科技100%股权。交易完成后，公司将持有标的公司100%股权，标的公司将纳入公司合并报表。孚悦科技主要从事高精密度新型锂电池结构件的研发、生产和销售。</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>光伏, 并购重组</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>MLED</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="C62" s="2" t="inlineStr"/>
+        <v>-0.43</v>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
+        </is>
+      </c>
       <c r="D62" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>sz002913</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>奥士康</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>53.12</v>
+      </c>
+      <c r="H62" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>sz002868</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>*ST绿康</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>42.07</v>
-      </c>
-      <c r="H62" s="2" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="I62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 绿康生化公告称，公司收到通知，公司控股股东上海康怡投资有限公司、股东杭州义睿投资合伙企业（有限合伙）、上饶市长鑫贰号企业管理中心（有限合伙）、杭州皓赢投资合伙企业（有限合伙）与福建纵腾网络有限公司签署了《股份转让协议》，约定由上述股份转让方向纵腾网络转让上市公司46,608,397股普通股股份，占上市公司总股本的29.99%。</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr"/>
+          <t>MLED|公司的MiniLED产品主要覆盖TV\NB\PC\汽车台显等产品，大规模供货的主要是三星，2022年全年三星需求700多万平、索尼200万平米、LG200多万平米，其中，公司有机会能拿到三星接近一半的MiniLED订单份额。</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>MLED</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>MLED</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="C63" s="2" t="inlineStr"/>
+        <v>-0.43</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>根据TrendForce最新调查，传统铜缆方案在传输密度与节能上面临严峻挑战，而Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
+        </is>
+      </c>
       <c r="D63" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>sz002569</t>
+          <t>sz000509</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>*ST步森</t>
+          <t>华塑控股</t>
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>14.13</v>
+        <v>3.99</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="I63" s="2" t="inlineStr"/>
+        <v>9.92</v>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 主营业务为“步森”品牌男装的设计、生产和销售。</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr"/>
+          <t>MLED|公司积极布局了MiniLED、OLED和高分高刷高色域等显示领域前沿产品技术。</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>MLED</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="C64" s="2" t="inlineStr"/>
+        <v>0.77</v>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>中国银河证券表示，当前AI算力需求不减、存储芯片周期上行以及先进封装技术渗透共同推动半导体设备需求提振，2026年半导体设备市场规模持续增长预期强烈。</t>
+        </is>
+      </c>
       <c r="D64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>sh603316</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>诚邦股份</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="H64" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>sz000908</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>*ST景峰</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="H64" s="2" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="I64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司专注医药健康产业，涉足药品研发、生产、销售等领域，产品涵盖了心脑血管、抗肿瘤、骨科、妇儿等用药领域。</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr"/>
+          <t>存储器|公司旗下芯存科技主要从事半导体存储器的研发设计、封装测试、生产和销售，已量产并销售的主要产品为移动存储（包括TFCARD、USB模块等）、固态硬盘（包括SATASSD、PCIESSD、PSSD）等。</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>存储器</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3373,32 +3469,36 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="C65" s="2" t="inlineStr"/>
       <c r="D65" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>sz000793</t>
+          <t>sh603838</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>*ST华闻</t>
+          <t xml:space="preserve">*ST四通 </t>
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>2.85</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="I65" s="2" t="inlineStr"/>
+        <v>5.06</v>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>6天4板</t>
+        </is>
+      </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 地处海南省海口市，国广环球传媒控股旗下上市公司，主营传媒业务。</t>
+          <t>ST股 | 公司是一家集研发、设计、生产、销售于一体的新型家居生活陶瓷供应商，产品覆盖日用陶瓷、卫生陶瓷、艺术陶瓷、建筑装饰等全系列家居生活用瓷。</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr"/>
@@ -3406,33 +3506,31 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>1.21</v>
       </c>
       <c r="C66" s="2" t="inlineStr"/>
       <c r="D66" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>sh600545</t>
+          <t>sz000908</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>卓郎智能</t>
+          <t>*ST景峰</t>
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>3.77</v>
+        <v>6.38</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>9.91</v>
+        <v>4.93</v>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
@@ -3441,535 +3539,462 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>玻璃纤维捻线机|2025年6月28日公司官微透露，公司与国际复材签订了加捻事业部史上最大额玻璃纤维捻线机订单。玻纤凭借其低介电常数等特性，已成为制造高频高速PCB与高性能芯片封装材料的不二之选。</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>玻璃纤维捻线机</t>
-        </is>
-      </c>
+          <t>ST股 | 公司专注医药健康产业，涉足药品研发、生产、销售等领域，产品涵盖了心脑血管、抗肿瘤、骨科、妇儿等用药领域。</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>1.21</v>
       </c>
       <c r="C67" s="2" t="inlineStr"/>
       <c r="D67" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>sz002952</t>
+          <t>sz002713</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>亚世光电</t>
+          <t>*ST东易</t>
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>26.5</v>
+        <v>10.22</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>10</v>
+        <v>5.04</v>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>3天2板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>OLED|公司于2019年4月在互动平台表示，公司主要聚焦工控仪表、通讯终端、办公室自动化等细分应用市场领域，目前主要是LCD显示类型的产品，对于OLED显示类型的产品也有一定涉足，这主要是由客户的定制化需求所决定的。</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>OLED</t>
-        </is>
-      </c>
+          <t>ST股 | 公司基于数字化系统优势和业务场景优势，研发推出了行业内首个新一代AIGC技术和真家系统结合的全新设计工具“真家 AIGC”，同时打造出AI 创意大师、AI小白设计家两款智能应用设计工具。</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>1.21</v>
       </c>
       <c r="C68" s="2" t="inlineStr"/>
       <c r="D68" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>sz002235</t>
+          <t>sh603813</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>安妮股份</t>
+          <t xml:space="preserve">*ST原尚 </t>
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>10.62</v>
+        <v>37.99</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="I68" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>股权变更重大进展|安妮股份3月4日晚间公告表示，深交所已对转让双方提交的申请材料进行了完备性核对，并出具了《深圳证券交易所上市公司股份协议转让确认书》。公司控制权变更事项迎来重大进展。</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>股权变更重大进展</t>
-        </is>
-      </c>
+          <t>ST股 | 公司参股公司广东原锋新能源科技的股东之一锋源是国内极少的集全套自主知识产权氢燃料电池电堆以及核心零部件膜电极、催化剂、金属双极板等研发、生产、销售一体的公司。</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>1.21</v>
       </c>
       <c r="C69" s="2" t="inlineStr"/>
       <c r="D69" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>sz002355</t>
+          <t>sz002731</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>兴民智通</t>
+          <t>ST萃华</t>
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>7.33</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>10.06</v>
+        <v>5.050000000000001</v>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>无人驾驶|公司为无人驾驶开发了高网络可靠性的双5G智能网联终端产品—通信域控制器（ICVBOX），目前已在L3、L4无人驾驶汽车Robotaxi、无人物流车上配套，服务客户涵盖百度萝卜快跑、Momenta以及国内主流车企。</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>无人驾驶</t>
-        </is>
-      </c>
+          <t>ST股 | 公司是主要从事珠宝饰品设计、加工、批发和零售的“中华老字号”企业，产品以黄金饰品为主，兼营铂金饰品、镶嵌饰品等珠宝饰品。</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>1.21</v>
       </c>
       <c r="C70" s="2" t="inlineStr"/>
       <c r="D70" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>920001.BJ</t>
+          <t>sz002528</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>纬达光电</t>
+          <t>ST英飞拓</t>
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>21.33</v>
+        <v>3.19</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>29.98</v>
+        <v>4.93</v>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>偏光片|公司主要从事偏光片和光学薄膜材料的研发、生产与销售。公司已掌握AMOLED、PMOLED偏光片产品的关键生产技术和工艺，预计新增产能建成后可广泛开拓OLED市场。</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>偏光片</t>
-        </is>
-      </c>
+          <t>ST股 | 英飞拓推出5G多功能智慧灯杆，支持节能照明、视频监控、新能源充电、公共WIFI、环境监测、信息发布、应急报警、5G微基站等模块，实现多种类型的感知数据采集、分析、仿真预测，提升城市综合治理。</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>1.21</v>
       </c>
       <c r="C71" s="2" t="inlineStr"/>
       <c r="D71" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>sh605098</t>
+          <t>sz000638</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>行动教育</t>
+          <t>*ST万方</t>
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>51.26</v>
+        <v>2.08</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>10</v>
+        <v>5.050000000000001</v>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>教育|公司定位于“建设世界级实效管理教育机构”，主要致力于为中小民营企业提供全生命周期的生态化知识服务和智力支持平台。</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>教育</t>
-        </is>
-      </c>
+          <t>ST股 | 公司业务主要包括军工产业、农业产业以及生物制品等业务。公司控股子公司万方迈捷以粮库收储为核心，深入研究粮食加工、研究土地流转、研究农民就业，万方迈捷作为乾安县唯一一家自主加工的大米企业。</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>1.21</v>
       </c>
       <c r="C72" s="2" t="inlineStr"/>
       <c r="D72" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>sz002800</t>
+          <t>sz000752</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>天顺股份</t>
+          <t>ST西发</t>
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>23.41</v>
+        <v>10.47</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>10.01</v>
+        <v>5.02</v>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>一带一路+物流|公司作为疆内第三方物流、供应链管理的龙头企业，国际铁路业务在2022年开行了莫斯科、杜伊斯堡、汉堡、梅杰乌、阿拉木图、热特苏、塔什干、格鲁吉亚、意大利、梅尔辛、马拉等中亚、中欧方向的班列。国际航班货源业务在2022年以乌鲁木齐为中心开通了格鲁吉亚第比利斯等全货机航线；在海口开设海口至莫斯科航线；在武汉开设了武汉至莫斯科航线。</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>一带一路, 物流</t>
-        </is>
-      </c>
+          <t>ST股 | 公司啤酒目前在拉萨地区市场占有率约为85%，在西藏市场占有率为50%。</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>1.21</v>
       </c>
       <c r="C73" s="2" t="inlineStr"/>
       <c r="D73" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>sz000920</t>
+          <t>sz002496</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>沃顿科技</t>
+          <t>*ST辉丰</t>
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>13.63</v>
+        <v>2.08</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>10.01</v>
+        <v>5.050000000000001</v>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">盐湖提锂|公司膜产品可以用在膜浓缩工艺的盐湖提锂中。
-</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>盐湖提锂</t>
-        </is>
-      </c>
+          <t>ST股 | 公司是国内集原药、制剂生产、研发、销售于一体的大型农药生产企业。</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>1.21</v>
       </c>
       <c r="C74" s="2" t="inlineStr"/>
       <c r="D74" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>sh600744</t>
+          <t>sh600193</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>华银电力</t>
+          <t xml:space="preserve">*ST创兴 </t>
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>9.039999999999999</v>
+        <v>4.45</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>9.98</v>
+        <v>4.95</v>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>电力|作为湖南省火电装机主要发电企业，公司主要从事火力发电业务，同时经营水电、风电、太阳能业务以及电力销售业务。</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>电力</t>
-        </is>
-      </c>
+          <t>ST股 | 围绕算力服务业务，公司目前已在江苏苏州、浙江杭州、北京等地部署了算力资源池，主要用于机器视觉类应用和游戏项目的测试工作。</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>1.21</v>
       </c>
       <c r="C75" s="2" t="inlineStr"/>
       <c r="D75" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>sh600828</t>
+          <t>sz000488</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>茂业商业</t>
+          <t>ST晨鸣</t>
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>6.53</v>
+        <v>2.48</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>9.93</v>
+        <v>5.08</v>
       </c>
       <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>零售|公司业务以商业零售为主，并辅以部分物业租赁和酒店业务。</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>零售</t>
-        </is>
-      </c>
+          <t>ST股 | 公司是全国唯一一家实现制浆和造纸平衡的大型浆纸一体化企业，率先布局全产业链，在山东、广东、湖北、江西、吉林等地建有6个生产基地，年浆纸产能达1100多万吨。</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>1.21</v>
       </c>
       <c r="C76" s="2" t="inlineStr"/>
       <c r="D76" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>sh600844</t>
+          <t>sz002717</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>金煤科技</t>
+          <t>ST岭南</t>
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>3.65</v>
+        <v>1.77</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>9.94</v>
+        <v>4.73</v>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>煤化工|公司为专注于煤制乙二醇产业的新型化工企业，目前主要通过控股子公司通辽金煤的大型化工装置生产乙二醇并联产草酸。</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>煤化工</t>
-        </is>
-      </c>
+          <t>ST股 | 2022年2月16日公司在互动平台表示，岭南股份文化旅游业务涵盖主题文化旅游的规划设计，主题文化景区主题公园的创意设计、旅游投资、景区建设、策划营销和运营。</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>1.21</v>
       </c>
       <c r="C77" s="2" t="inlineStr"/>
       <c r="D77" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>sz002913</t>
+          <t>sh603021</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>奥士康</t>
+          <t xml:space="preserve">ST华鹏  </t>
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>48.29</v>
+        <v>7.18</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>10</v>
+        <v>4.97</v>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>PCB|公司PCB产品主要应用于数据中心及服务器、AIPC、通信及网络设备、汽车电子等领域。</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>PCB</t>
-        </is>
-      </c>
+          <t>ST股 | 公司是国内日用玻璃行业的企业之一，主营业务为研发、生产和销售玻璃器皿产品和玻璃瓶罐。</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>1.21</v>
       </c>
       <c r="C78" s="2" t="inlineStr"/>
       <c r="D78" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>sh605298</t>
+          <t>sz000609</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>必得科技</t>
+          <t>ST中迪</t>
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>49.81</v>
+        <v>9.57</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>10</v>
+        <v>5.050000000000001</v>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>高铁|公司主营中高速动车组列车、城轨列车等轨道交通车辆配套产品的研发、生产与销售，主要产品包括车辆通风系统、电缆保护系统和智能控制撒砂系统等系统化、系列化产品及其他轨道交通车辆配套产品。</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>高铁</t>
-        </is>
-      </c>
+          <t>ST股 | 公司房地产项目位于重庆、成都、达州，重庆的“两江中迪广场”主要为商业项目。</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -3984,20 +4009,20 @@
       </c>
       <c r="C79" s="2" t="inlineStr"/>
       <c r="D79" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>sh603001</t>
+          <t>sz003023</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>奥康国际</t>
+          <t>彩虹集团</t>
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>9.58</v>
+        <v>25.65</v>
       </c>
       <c r="H79" s="2" t="n">
         <v>9.99</v>
@@ -4005,12 +4030,12 @@
       <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>纺织|主要从事皮鞋及皮具产品的研发、生产、零售及分销业务。</t>
+          <t>家电|公司主要从事电热毯、电热暖手器等系列家用柔性取暖器具以及电热蚊香液、电热蚊香片、盘式蚊香、杀虫气雾剂等系列家用卫生杀虫用品的研发、生产和销售。</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>纺织</t>
+          <t>家电</t>
         </is>
       </c>
     </row>
@@ -4027,34 +4052,421 @@
       </c>
       <c r="C80" s="2" t="inlineStr"/>
       <c r="D80" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>sh603067</t>
+          <t>sh600676</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>振华股份</t>
+          <t>交运股份</t>
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>45.87</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>10</v>
+        <v>10.03</v>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>固态电池+铬|1.子公司厦门首能半固态电解液还处于向下游客户小批量供应，共同研发阶段。
-2.公司是国内铬盐行业唯一的上市公司，铬盐生产规模、技术水平、产品质量、市场占有率处于国内龙头地位，是国内铬盐行业综合竞争力最强的企业。</t>
+          <t>资产重组|交运股份公告称，公司拟与控股股东久事集团及其关联方进行资产置换，将所持有的乘用车销售与汽车后服务板块、汽车零部件制造与销售服务板块相关资产与久事集团及其关联方持有的文体娱乐业、旅游业相关业务资产进行置换。拟置入资产包括赛事运营公司100%股权、场馆运营公司100%股权、智慧体育公司不低于62.40%股权、浦江游览公司100%股权和久事演艺公司100%股权等；拟置出资产包括汽车修理公司100%股权、汽车动力公司100%股权、冲压件公司100%股权、压力容器公司80%股权、烟台中瑞公司100%股权、沈阳中瑞公司100%股权等。差额部分由一方向另一方以现金方式补足。本次交易构成关联交易，预计将构成重大资产重组。</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>固态电池, 铬</t>
+          <t>资产重组</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr"/>
+      <c r="D81" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>sh600825</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>新华传媒</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>传媒|新华传媒作为上海报业集团唯一上市公司，上海报业集团是国内最大最全的版权库。</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>传媒</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr"/>
+      <c r="D82" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>sz002961</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>瑞达期货</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>27.18</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>期货|公司是福建省内期货成交金额最大、盈利水平最高的期货公司。</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr"/>
+      <c r="D83" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>sz001696</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>宗申动力</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>25.54</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>无人机|公司是国内专业化小型热动力机械产品制造基地之一，子公司航发公司主要聚焦无人机及通航有人飞机动力领域，已取得关键突破和一定的市场覆盖；公司在＂发动机+”业务方面，已开始参与某型飞机配套项目科研。</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>无人机</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr"/>
+      <c r="D84" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>sz301205</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>联特科技</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>237.72</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>光模块|联特科技在互动平台表示，公司的1.6T光模块产品已送至多家客户进行测试验证，并与客户在LPO等特定方案上开展了联合设计。</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>光模块</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr"/>
+      <c r="D85" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>sz002849</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>威星智能</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>19.59</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>算力（已终止）|公司曾于2023年7月与贵安管委会、摩尔线程签署《贵安智算中心项目投资合作协议》，三方拟在贵安新区建立智算中心，预计建设2000P以上算力的智算中心，总投资约30亿。（公司于2024年4月在互动平台表示，审慎决定终止该项目。）</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>算力（已终止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr"/>
+      <c r="D86" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>sh601789</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>宁波建工</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>机柜位租赁|宁波建工2023年6月20日在投资者互动平台表示，中经云主营业务为数据中心机柜位出租，无算力出租服务。</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>机柜位租赁</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr"/>
+      <c r="D87" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>sz001326</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>联域股份</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>65.75</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>LED照明产品|公司专注于中、大功率LED照明产品的研发、生产与销售，公司产品主要为LED灯具和LED光源，覆盖户外照明、工业照明及特种照明等应用领域。</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>LED照明产品</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr"/>
+      <c r="D88" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>sh603880</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>南卫股份</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>9.950000000000001</v>
+      </c>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>医疗器械|公司特殊急救系列产品主要包括战创伤中的止血、包扎、固定、通气、输液、工具等模块，以及应用于各种生存环境（如高寒、沿海、高温高湿、核辐射）的系列辅助救治背囊。</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>医疗器械</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr"/>
+      <c r="D89" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>sh600761</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>安徽合力</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>22.52</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>工程机械+机器人|1.主营工业车辆，工程机械及关键零部件等产品的研发，生产和销售，同时包含配件服务，车辆租赁，再制造等工业车辆后市场业务，公司是国内叉车领域的龙头。
+2.据公司官网披露，公司有潜伏式机器人、料箱机器人等在售产品。</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>工程机械, 机器人</t>
         </is>
       </c>
     </row>
@@ -4069,7 +4481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4096,7 +4508,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -4111,46 +4523,46 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sz300265</t>
+          <t>sh605268</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>通光线缆</t>
+          <t>王力安防</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sz002877</t>
+          <t>sz002498</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>智能自控</t>
+          <t>汉缆股份</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sz002339</t>
+          <t>sz000533</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>积成电子</t>
+          <t>顺钠股份</t>
         </is>
       </c>
     </row>
@@ -4160,12 +4572,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sh605268</t>
+          <t>sz002913</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>王力安防</t>
+          <t>奥士康</t>
         </is>
       </c>
     </row>
@@ -4175,12 +4587,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sz002498</t>
+          <t>sh600590</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>汉缆股份</t>
+          <t>泰豪科技</t>
         </is>
       </c>
     </row>
@@ -4190,12 +4602,27 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>sz000533</t>
+          <t>sz000509</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>顺钠股份</t>
+          <t>华塑控股</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>sz000815</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>美利云</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,18 +476,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="87" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="101" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
     <col width="343" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
@@ -552,909 +552,912 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.74</v>
+        <v>4.77</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>中国信通院发布《先进计算暨算力发展指数蓝皮书（2025年）》，截至2025年6月我国计算设备智能算力规模达到782 EFlops，同比增长96%。</t>
+          <t>美国光通信技术公司AOI宣布，已收到一家长期主要超大规模客户的1.6T数据中心光收发器首批量产订单，金额逾2亿美元，标志着新一代高速光互联产品正式进入规模化商用阶段。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>sz000815</t>
+          <t>sz001267</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>美利云</t>
+          <t>汇绿生态</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>17.94</v>
+        <v>45.68</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>9.99</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>3天3板</t>
+          <t>4天2板</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>算力租赁|公司主要从事IDC业务，专业为大型互联网企业提供数据机房机柜出租托管，同时提供宽带接入服务。公司数据中心位于“东数西算”节点城市之一，具备高性能网络资源、低成本电力、高规格设计、优质气候条件及可扩展的空间。涉及的底层和应用层面的云计算、算力、AI人工智能技术、搜索技术、网络安全等相关业务和服务正在积极探索。</t>
+          <t>光通信|公司旗下钧恒科技是专业从事高端光通信产品的研制、生产及推广的高新技术企业，拥有从光学组件，光电转换模块，光端机及子系统的行业垂直整合能力，能够为客户提供各种特定应用的定制化产品，包括PLCC、Mini SFF、Micro Pod等各种形态及各种复合协议的光端机及波分复用子系统。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>算力租赁</t>
+          <t>光通信</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.74</v>
+        <v>4.77</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>中国信通院发布《先进计算暨算力发展指数蓝皮书（2025年）》，截至2025年6月我国计算设备智能算力规模达到782 EFlops，同比增长96%。</t>
+          <t>美国光通信技术公司AOI宣布，已收到一家长期主要超大规模客户的1.6T数据中心光收发器首批量产订单，金额逾2亿美元，标志着新一代高速光互联产品正式进入规模化商用阶段。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sz002261</t>
+          <t>sh603803</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>拓维信息</t>
+          <t>瑞斯康达</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>42.96</v>
+        <v>11</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>华为+算力租赁|1.截至2023年，公司成为华为唯一“鲲鹏/昇腾+鸿蒙”软硬一体战略伙伴，是华为在人工智能领域覆盖“软件+硬件生产+生态运营”的全方位深度合作的伙伴。2022年，公司携手华为在8大节点算力中心做了布局。
-2.公司在北京参与了以“清华大学数据与计算公共平台”为代表的系列人工智能项目建设，在广州参与了广东AI智算中心建设项目。</t>
+          <t>光模块|在高端光模块领域，公司联营企业易锐光电是中国少数产业链上下游关键层面具备完整核心技术和解决方案的高科技企业，新一代基于自主知识产权的25G/100G/超100G集成光收发芯片的光通信模块及光组件，用于电信网络城域网和大型数据中心网络。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>华为, 算力租赁</t>
+          <t>光模块</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.74</v>
+        <v>4.77</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>中国信通院发布《先进计算暨算力发展指数蓝皮书（2025年）》，截至2025年6月我国计算设备智能算力规模达到782 EFlops，同比增长96%。</t>
+          <t>美国光通信技术公司AOI宣布，已收到一家长期主要超大规模客户的1.6T数据中心光收发器首批量产订单，金额逾2亿美元，标志着新一代高速光互联产品正式进入规模化商用阶段。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sh688158</t>
+          <t>sh600330</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>优刻得-W</t>
+          <t>天通股份</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>45.38</v>
+        <v>17.22</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>19.99</v>
+        <v>10.03</v>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>算力租赁|2023年10月26日公司在互动平台表示，公司目前管理的AI算力规模约为3000P+，已有4090、3090显卡相关资源储备。</t>
+          <t>商业航天+铌酸锂|1.在航天航空领域，公司的蓝宝石材料因其优异的耐高温和抗辐射性能，被广泛用于制造航空航天器的窗口和仪表保护盖。蓝宝石光学窗口能够在极端环境下保持高透明度和结构完整性，确保航天器在高空、真空和辐射环境中的正常运行。
+2.2023年6月9日公司在互动平台表示，国内多家厂商已经发布数通800G薄膜铌酸锂方案的光模块，公司生产的铌酸锂单晶材料是薄膜铌酸锂调制器的上游关键原材料。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>算力租赁</t>
+          <t>商业航天, 铌酸锂</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.74</v>
+        <v>4.77</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>中国信通院发布《先进计算暨算力发展指数蓝皮书（2025年）》，截至2025年6月我国计算设备智能算力规模达到782 EFlops，同比增长96%。</t>
+          <t>美国光通信技术公司AOI宣布，已收到一家长期主要超大规模客户的1.6T数据中心光收发器首批量产订单，金额逾2亿美元，标志着新一代高速光互联产品正式进入规模化商用阶段。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sh688229</t>
+          <t>sh601869</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>博睿数据</t>
+          <t>长飞光纤</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>103.14</v>
+        <v>233.1</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>算力调度|公司一体化智能可观测平台Bonree ONE可以对任务执行、算力调度过程、算力调优结果进行观测分析，以评估算力调度的可行性，为各类数字化应用提供稳定、高效的算力支持。</t>
+          <t>光纤光缆|公司系全球光纤光缆行业的领先企业，是国内最早的光纤光缆生产厂商之一，聚焦电信运营商和数据通信相关领域，致力于光纤预制棒、光纤和光缆以及数据通信相关产品的研发创新与生产制造，形成了棒纤缆、综合布线和光模块一体化的完整产业链、相关多元化和国际化的业务模式。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>算力调度</t>
+          <t>光纤光缆</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.74</v>
+        <v>4.77</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>中国信通院发布《先进计算暨算力发展指数蓝皮书（2025年）》，截至2025年6月我国计算设备智能算力规模达到782 EFlops，同比增长96%。</t>
+          <t>美国光通信技术公司AOI宣布，已收到一家长期主要超大规模客户的1.6T数据中心光收发器首批量产订单，金额逾2亿美元，标志着新一代高速光互联产品正式进入规模化商用阶段。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sh600602</t>
+          <t>sz002281</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>云赛智联</t>
+          <t>光迅科技</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>22.26</v>
+        <v>86.16</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>国资云|公司是上海国资委旗下上市公司，定位于中立第三方高端数据中心运营商。</t>
+          <t>光模块|公司可以提供全套的液冷光模块产品，同时公司是浸没液冷智算产业发展联盟会员单位，是相关标准、工艺研究和实践的重要参与者之一。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>国资云</t>
+          <t>光模块</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.74</v>
+        <v>4.77</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>中国信通院发布《先进计算暨算力发展指数蓝皮书（2025年）》，截至2025年6月我国计算设备智能算力规模达到782 EFlops，同比增长96%。</t>
+          <t>美国光通信技术公司AOI宣布，已收到一家长期主要超大规模客户的1.6T数据中心光收发器首批量产订单，金额逾2亿美元，标志着新一代高速光互联产品正式进入规模化商用阶段。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sz002730</t>
+          <t>sh600345</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>电光科技</t>
+          <t>长江通信</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>19.17</v>
+        <v>43.76</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>9.98</v>
+        <v>10.01</v>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>算力租赁+电网设备|1.子公司浙江电光云科技有限公司目前第一期规划算力1000P，未来电光云将建立智算中心、数据中心，更好地向市场提供大数据、大模型、物联网、人工智能与机器学习、服务器托管及网络接入等方面的服务。
-2.公司子公司达得利和泰亿达两家公司，主要从事国家电网、电力、通讯科技、机场铁路交通及国家市政大型工程等领域的智能计量设备、各大系列单、三相电表箱、多组合电表箱，电力专用低压配电柜、高低压电缆分接箱、SMC电器设备箱及户外高压熔断器等产品的研发、生产和销售。</t>
+          <t>光纤光缆+商业航天|1.公司参股公司长飞光纤（持股比例15.82%）系全球光纤光缆行业的领先企业，是国内最早的光纤光缆生产厂商之一。
+2.公司全资子公司迪爱斯中标的上海垣信卫星科技有限公司的项目主要是卫星地面站园区建设和信关站建设。公司主要提供低轨卫星地面运控中心网络控制管理和指挥系统，以及按照客户要求提供地面卫星通信设备、卫星通信机房及其他软硬件设备等集成服务。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>算力租赁, 电网设备</t>
+          <t>光纤光缆, 商业航天</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.74</v>
+        <v>4.77</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>中国信通院发布《先进计算暨算力发展指数蓝皮书（2025年）》，截至2025年6月我国计算设备智能算力规模达到782 EFlops，同比增长96%。</t>
+          <t>美国光通信技术公司AOI宣布，已收到一家长期主要超大规模客户的1.6T数据中心光收发器首批量产订单，金额逾2亿美元，标志着新一代高速光互联产品正式进入规模化商用阶段。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sz002575</t>
+          <t>sh600498</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>群兴玩具</t>
+          <t>烽火通信</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>8.02</v>
+        <v>57.2</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>算力租赁|孙公司杭州图灵引擎科技有限公司与腾讯科技（深圳）有限公司签订算力服务协议，向腾讯提供集群算力服务。</t>
+          <t>光纤光缆+商业航天|1.公司系光通信行业领先企业，产品围绕光通信全产业链布局，是我国最早从事光通信传输设备、光纤光缆科研、生产的企业，已跻身全球光传输与网络接入设备、光纤光缆最具竞争力企业10强。
+2.公司全面进军卫星光通信领域，低轨星载路由(天基IP网)与星间激光通信（天基传送网）已成为公司布局卫星互联网的关键突破口，成功研发面向低轨卫星平台的高集成度、低功耗星上路由交换系统。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>算力租赁</t>
+          <t>光纤光缆, 商业航天</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.74</v>
+        <v>4.77</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>中国信通院发布《先进计算暨算力发展指数蓝皮书（2025年）》，截至2025年6月我国计算设备智能算力规模达到782 EFlops，同比增长96%。</t>
+          <t>美国光通信技术公司AOI宣布，已收到一家长期主要超大规模客户的1.6T数据中心光收发器首批量产订单，金额逾2亿美元，标志着新一代高速光互联产品正式进入规模化商用阶段。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sz002229</t>
+          <t>sh688048</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>鸿博股份</t>
+          <t>长光华芯</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>17.9</v>
+        <v>188.4</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>10.02</v>
+        <v>20</v>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>算力租赁|公司与中关村中恒文化科技创新服务联盟、英伟达、北京英博数科科技有限公司就在北京市共同合作成立北京AI创新赋能中心，开展相关人工智能科技领域项目建设及运营服务事宜签署了《合作协议》。</t>
+          <t>光芯片|公司已形成全面、丰富的通信光芯片产品矩阵，可满足超大容量的数据通信需求，距离上覆盖VR、SR、DR、FR等，速率上覆盖单波25G、50G、100G。公司的100mW CW DFB产品可用于800G/1.6T等场景的光互联应用，且满足高速率的持续演进诉求。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>算力租赁</t>
+          <t>光芯片</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.74</v>
+        <v>5.29</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>中国信通院发布《先进计算暨算力发展指数蓝皮书（2025年）》，截至2025年6月我国计算设备智能算力规模达到782 EFlops，同比增长96%。</t>
+          <t>日本化工巨头三菱瓦斯化学株式会社（MGC）宣布自4月1日起，将其电子材料部门旗下的核心产品——覆铜板（CCL）、预浸料（Prepreg）及背胶铜箔（CRS）的价格统一上调30%。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sh688316</t>
+          <t>sz002636</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>青云科技-U</t>
+          <t>金安国纪</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>89.52</v>
+        <v>27.87</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>20</v>
+        <v>9.98</v>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>算力租赁|2023年7月18日在互动平台表示，公司提供NVIDIA A100GPU的云服务器的算力租赁业务，基于AI算力调度服务提供预训练模型的算力服务。青云科技的超级智算平台适用于生命科学、CAE 仿真、海洋气象、影视渲染、石油勘探、深度学习、测绘地理、模型训练、场景推理等计算场景。
-2024年1月2日公告，控股子公司青云智算与客户签订《GPU算力服务协议》，合同费用总额1.7亿元（含税）。青云智算将为客户提供75例的GPU算力服务，100T的存储。</t>
+          <t>电子玻纤布|金安国纪公告称，为保障原材料供应，保证公司长期平稳发展，公司全资子公司安徽金瑞计划投资不超过10,000万元建设年产6000万米电子级玻纤布扩建项目，预计2026年12月底前开始试生产。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>算力租赁</t>
+          <t>电子玻纤布</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.74</v>
+        <v>5.29</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>中国信通院发布《先进计算暨算力发展指数蓝皮书（2025年）》，截至2025年6月我国计算设备智能算力规模达到782 EFlops，同比增长96%。</t>
+          <t>日本化工巨头三菱瓦斯化学株式会社（MGC）宣布自4月1日起，将其电子材料部门旗下的核心产品——覆铜板（CCL）、预浸料（Prepreg）及背胶铜箔（CRS）的价格统一上调30%。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sz001339</t>
+          <t>sh688655</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>智微智能</t>
+          <t xml:space="preserve">迅捷兴  </t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>72.95999999999999</v>
+        <v>29.4</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>算力调度|公司智算业务包括AI算力规划与设计、GPU及高性能服务器设备交付、运维调优、算力调度与优化管理平台服务、算力租赁+MaaS、算力及网络设备售后及置换等，为客户提供端到端的智算中心全流程服务，致力于成为AIGC基础设施全生命周期综合服务商。</t>
+          <t>PCB|公司产品和服务以“多品种、小批量、高层次、短交期”为特色，致力于满足客户产品生命周期各阶段的需求，业务涵盖样板、小批量板和大批量板，是行业内为数不多可以为客户提供从样板到批量生产一站式服务的PCB企业。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>算力调度</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.74</v>
+        <v>5.29</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>中国信通院发布《先进计算暨算力发展指数蓝皮书（2025年）》，截至2025年6月我国计算设备智能算力规模达到782 EFlops，同比增长96%。</t>
+          <t>日本化工巨头三菱瓦斯化学株式会社（MGC）宣布自4月1日起，将其电子材料部门旗下的核心产品——覆铜板（CCL）、预浸料（Prepreg）及背胶铜箔（CRS）的价格统一上调30%。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sz300113</t>
+          <t>sz001389</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>顺网科技</t>
+          <t>广合科技</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>29.36</v>
+        <v>120.23</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>19.98</v>
+        <v>10</v>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>边缘算力服务|公司边缘算力网络可提供足量及就近的边缘算力服务，承接来自于人工智能、云游戏、工业互联网等行业对于实时算力的需求。公司于2023年6月6日在互动平台表示，公司已落地200+座顺网雲机房，拥有50000+多线并发能力，为超过50万终端提供服务。</t>
+          <t>PCB+商业航天|公司主营业务是印制电路板的研发、生产和销售，公司5G产品广泛应用于通讯基站 、无线射频微波、有线局域网、通讯交换等领域。公司5.5G低轨卫星产品开始批量供货。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>边缘算力服务</t>
+          <t>PCB, 商业航天</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0.74</v>
+        <v>5.29</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>中国信通院发布《先进计算暨算力发展指数蓝皮书（2025年）》，截至2025年6月我国计算设备智能算力规模达到782 EFlops，同比增长96%。</t>
+          <t>日本化工巨头三菱瓦斯化学株式会社（MGC）宣布自4月1日起，将其电子材料部门旗下的核心产品——覆铜板（CCL）、预浸料（Prepreg）及背胶铜箔（CRS）的价格统一上调30%。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sz000066</t>
+          <t>sz002384</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>中国长城</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>17.26</v>
+        <v>108.06</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>量子科技+CPU|1.参股飞腾公司是CPU研发设计的国家队、国内领先的自主核心芯片提供商，致力于通算处理器、智算处理器等高端芯片的研发设计和产业化推广。
-2.中国长城量子实验室是中国长城科技集团股份有限公司与湖南知名高校共建的量子实验室，主要开展基于光量子和拓扑超导量子计算的基础科研，量子软件及控制系统研究，以及量子芯片加工制备等方面的科研工作。</t>
+          <t>PCB+光通信|1.公司成为上游供应商中为数不多的能为新能源汽车客户提供PCB（含FPC）、车载显示屏、功能性结构件等多种产品及综合解决方案的厂商，连续多年柔性线路板（FPC）排名全球第二，PCB排名全球第三。
+2.2025年6月14日公告，公司拟通过全资子公司超毅集团（香港）有限公司收购Source Photonics Holdings (Cayman)Limited（以下简称“索尔思光电”）100%股份。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>量子科技, CPU</t>
+          <t>PCB, 光通信</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.74</v>
+        <v>5.29</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>中国信通院发布《先进计算暨算力发展指数蓝皮书（2025年）》，截至2025年6月我国计算设备智能算力规模达到782 EFlops，同比增长96%。</t>
+          <t>日本化工巨头三菱瓦斯化学株式会社（MGC）宣布自4月1日起，将其电子材料部门旗下的核心产品——覆铜板（CCL）、预浸料（Prepreg）及背胶铜箔（CRS）的价格统一上调30%。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sz301396</t>
+          <t>sz300936</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>宏景科技</t>
+          <t>中英科技</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>114.29</v>
+        <v>58.54</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>20</v>
+        <v>20.01</v>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>算力租赁|公司通过高速网络整合分散的计算资源，形成可动态调度的统一算力池，支持高性能计算、AI训练等场景，以帮助客户算力组网、集成，实现算力的高效聚合、协同共享，提升算力资源利用率。</t>
+          <t>PCB+商业航天|1.公司产品高频覆铜板是制作印制电路板的核心材料，公司主要客户群体为印制电路板（PCB）制造厂商。
+2.公司ZYF-D型产品可应用于卫星导航等领域，公司产品ZYF-6000系列高频覆铜板可以应用于全球定位卫星天线、移动通信系统等领域。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>算力租赁</t>
+          <t>PCB, 商业航天</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>液冷IDC</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>1.46</v>
+        <v>3.34</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>美国正启动一轮超高压电网扩建计划，总投资额达750亿美元，聚焦765千伏输电线路建设，以应对AI数据中心等带来的电力需求激增。</t>
+          <t>英伟达AI基础设施负责人Dion Harris在加州总部向媒体展示了下一代Vera Rubin算力系统的内部构成与供应链细节。由于功耗上升，Vera Rubin也是英伟达首个100%液冷散热的系统。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sz000533</t>
+          <t>sz001400</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>顺钠股份</t>
+          <t>江顺科技</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>16.37</v>
+        <v>146.04</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4天4板</t>
+          <t>3天2板</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>核聚变+变压器|1.公司研制的特殊用途干式变压器包括国际热核聚变实验堆（ITER）试验平台变压器。
-2.公司控股孙公司顺特设备在超算中心和数据中心这两个领域提供过干式变压器产品，曾向阿里巴巴、秦淮数据有限公司、万国数据服务有限公司、数据港股份有限公司等客户提供过变压器设备。</t>
+          <t>液冷+商业航天|1.子公司江宇科技主要从事用于服务器液冷相关的3D打印产品的研发工作，已有部分样品。
+2.公司产品铝型材挤压模具和铝型材挤压配套设备应用于航空航天领域。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>核聚变, 变压器</t>
+          <t>液冷, 商业航天</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>液冷IDC</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>1.46</v>
+        <v>3.34</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>美国正启动一轮超高压电网扩建计划，总投资额达750亿美元，聚焦765千伏输电线路建设，以应对AI数据中心等带来的电力需求激增。</t>
+          <t>英伟达AI基础设施负责人Dion Harris在加州总部向媒体展示了下一代Vera Rubin算力系统的内部构成与供应链细节。由于功耗上升，Vera Rubin也是英伟达首个100%液冷散热的系统。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sh601567</t>
+          <t>sh603269</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>三星医疗</t>
+          <t>海鸥股份</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>32.35</v>
+        <v>17.93</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>10</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>3天2板</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>电网设备+签订大单|三星医疗公告称，公司下属全资子公司三星瑞典与荷兰Enexis电力局签订变压器框架合同，提供油浸式变压器产品，合同金额总计1.17亿欧元，约合9.49亿人民币。该合同金额占公司2024年度经审计营业收入的6.50%，预计将对公司经营业绩产生积极影响。</t>
+          <t>数据中心温控|公司主要从事各类冷却塔的研发、设计、制造及安装业务，并依托自身产品和技术优势提供工业及民用冷却塔相关的技术服务。公司研制的冷却塔广泛应用于石化、冶金、电力等领域以及公共设施、商务建筑、数据中心等的中央空调系统。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>电网设备, 签订大单</t>
+          <t>数据中心温控</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>液冷IDC</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>1.46</v>
+        <v>3.34</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>美国正启动一轮超高压电网扩建计划，总投资额达750亿美元，聚焦765千伏输电线路建设，以应对AI数据中心等带来的电力需求激增。</t>
+          <t>英伟达AI基础设施负责人Dion Harris在加州总部向媒体展示了下一代Vera Rubin算力系统的内部构成与供应链细节。由于功耗上升，Vera Rubin也是英伟达首个100%液冷散热的系统。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sz002300</t>
+          <t>sz002632</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>太阳电缆</t>
+          <t>道明光学</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>11.57</v>
+        <v>13.64</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>电线电缆|公司主要以电线电缆为主营业务，公司产品主要有500KV及以下交联聚乙烯绝缘电力电缆、核电站电缆、风力电缆、35～500KV海底电力电缆、海底光电复合电缆、柔性直流海底电缆和建筑用线、装备用电缆、数据电缆、架空线等。</t>
+          <t>折叠屏+液冷|1.子公司华威新材料目前拥有一种纳米银线防眩光导电膜和一种纳米银线防红外导电膜的实用新型专利。
+2.公司在2025年半年报中透露，公司以石墨烯超柔韧生产技术为依托，以新的产品形态和性能响应和开拓石墨烯产品在液冷服务器、AI眼镜等新应用场景下的热管理需求，目前样品已通过终端客户测试，且量产方案已在规划中。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>电线电缆</t>
+          <t>折叠屏, 液冷</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>液冷IDC</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>1.46</v>
+        <v>3.34</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>美国正启动一轮超高压电网扩建计划，总投资额达750亿美元，聚焦765千伏输电线路建设，以应对AI数据中心等带来的电力需求激增。</t>
+          <t>英伟达AI基础设施负责人Dion Harris在加州总部向媒体展示了下一代Vera Rubin算力系统的内部构成与供应链细节。由于功耗上升，Vera Rubin也是英伟达首个100%液冷散热的系统。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sz301179</t>
+          <t>sz002536</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>泽宇智能</t>
+          <t>飞龙股份</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>24.07</v>
+        <v>38.09</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>19.99</v>
+        <v>9.99</v>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>机器人+智能电网|1.2023年8月8日公司在互动平台表示，目前公司机器人产品处于测试迭代阶段，并即将按计划参与国网的相关测试工作。
-2.公司主要为电力体系中涉及的各个主体如发电厂、供电公司、变电站、配电房、用户等，打造电力信息通信系统，主要包括电力通信网络、调度数据网、信息管理网、无线核心网等子系统。</t>
+          <t xml:space="preserve">服务器液冷|公司电子泵及温控阀系列产品可以应用在服务器液冷领域。
+</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>机器人, 智能电网</t>
+          <t>服务器液冷</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>商业航天</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>1.46</v>
+        <v>2.7</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>美国正启动一轮超高压电网扩建计划，总投资额达750亿美元，聚焦765千伏输电线路建设，以应对AI数据中心等带来的电力需求激增。</t>
+          <t>由中国运载火箭技术研究院研制的长征八号甲遥八运载火箭，在海南商业航天发射场成功实施转运，火箭箭体被顺利运至发射区一号发射工位，计划近期择期发射。</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sz002112</t>
+          <t>sz002903</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>三变科技</t>
+          <t>宇环数控</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>27.63</v>
+        <v>30.37</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>变压器|公司主营变压器、电机、电抗器、低压成套电器设备、输变电设备等，已成为国家电网和南方电网的供应商之一。</t>
+          <t>机器人+商业航天|1.公司经营范围包括工业机器人及其关键功能部件、机械配件、金属材料的制造和销售。
+2.公司自主研发的高端复合立式磨床逐步进入航空航天市场，可用于加工航空航天领域的精密零部件及高性能材料。</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>变压器</t>
+          <t>机器人, 商业航天</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>商业航天</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1.46</v>
+        <v>2.7</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>美国正启动一轮超高压电网扩建计划，总投资额达750亿美元，聚焦765千伏输电线路建设，以应对AI数据中心等带来的电力需求激增。</t>
+          <t>由中国运载火箭技术研究院研制的长征八号甲遥八运载火箭，在海南商业航天发射场成功实施转运，火箭箭体被顺利运至发射区一号发射工位，计划近期择期发射。</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sh600268</t>
+          <t>sh603017</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>国电南自</t>
+          <t>中衡设计</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>16.34</v>
+        <v>13.48</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>10.03</v>
+        <v>10.04</v>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>电网设备|公司产业涵盖电网自动化、电厂及工业自动化、轨道交通自动化、信息与安全技术、电力电子等五大核心板块，同时以生产制造和系统集成为支撑，主要在电力、工业、新能源等领域为客户提供配套自动化、信息化产品、集成设备及整体解决方案。</t>
+          <t>商业航天|公司中标了天兵科技运载火箭及发动机智能制造 基地、山东箭元航天科技总装总测生产基地、星际荣耀火箭制造基地、安庆年发20发可回收液体火箭制造厂房建设项目等多个高端制造基地，积极为航空航天逐梦苍穹贡献中衡力量。</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>电网设备</t>
+          <t>商业航天</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>商业航天</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>1.46</v>
+        <v>2.7</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>美国正启动一轮超高压电网扩建计划，总投资额达750亿美元，聚焦765千伏输电线路建设，以应对AI数据中心等带来的电力需求激增。</t>
+          <t>由中国运载火箭技术研究院研制的长征八号甲遥八运载火箭，在海南商业航天发射场成功实施转运，火箭箭体被顺利运至发射区一号发射工位，计划近期择期发射。</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>sz003035</t>
+          <t>sz002025</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>南网能源</t>
+          <t>航天电器</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>9.58</v>
+        <v>56.03</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>9.99</v>
@@ -1462,97 +1465,93 @@
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>智能电网|公司主要从事节能服务,为客户能源使用提供诊断、设计、改造、综合能源项目投资及运营维护等一站式综合节能服务。公司协同电网公司为智能电网提供区域清洁能源的规划、投资、建设、运营等相关服务。</t>
+          <t>商业航天|公司连接器及电缆组件、电机、继电器和光模块等产品广泛应用于商业航天领域，先后承担并完成载人航天、探月、北斗、火星探测等国家重大工程和重大专项配套任务。</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>商业航天</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>商业航天</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>1.34</v>
+        <v>2.7</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>“算电协同”模式通过优化算力调度、整合绿色能源资源、提升能源利用效率，成为推动数字基础设施绿色低碳转型的关键路径。</t>
+          <t>由中国运载火箭技术研究院研制的长征八号甲遥八运载火箭，在海南商业航天发射场成功实施转运，火箭箭体被顺利运至发射区一号发射工位，计划近期择期发射。</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>sh600821</t>
+          <t>sz300629</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>金开新能</t>
+          <t>新劲刚</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>9.460000000000001</v>
+        <v>28.91</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>7天4板</t>
-        </is>
-      </c>
+        <v>20.01</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>电力+算力|1.公司主营业务为新能源电力的开发、投资、建设及运营，包括光伏发电和风力发电两个板块。
-2.2024年10月8日公告，公司全资子公司金开新能科技有限公司拟于新疆昌吉市投资建设国家超算广州中心新疆分中心昌吉智算中心项目，算力总规模达到5,000PFlops。</t>
+          <t>并购+商业航天|1.新劲刚公告称，公司正在筹划收购湖南高至科技有限公司的控股权，预计将实现对标的公司的控股。标的公司主要聚焦特殊应用领域智能仿真信息系统、飞行器关键部组件的研发生产与销售，具备飞行器总体设计能力。
+2.子公司宽普科技、仁健微波聚焦特定专业领域的射频微波产品研发及配套服务，其产品线涵盖低轨卫星相关模块及终端等方向。</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>电力, 算力</t>
+          <t>并购, 商业航天</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>1.34</v>
+        <v>2.28</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>“算电协同”模式通过优化算力调度、整合绿色能源资源、提升能源利用效率，成为推动数字基础设施绿色低碳转型的关键路径。</t>
+          <t>开源AI智能体OpenClaw持续火爆，该系统通过拆解任务、调用云端大模型API完成任务，一次任务可消耗数十万乃至数百万Token，算力需求呈指数级增长。</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>sz002015</t>
+          <t>sz002575</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>协鑫能科</t>
+          <t>群兴玩具</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>17.18</v>
+        <v>8.82</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
@@ -1561,680 +1560,670 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>电力+算力|1.公司在立足于成熟稳健增长的清洁能源投资、开发、运营的基础上，在能源结构、业务模式及能源应用三方面进行优化转型，并将最终成为新型电力系统综合服务商。
-2.公司在上海、苏州投运两个智算中心，已投运超千P的算力资源。</t>
+          <t>算力租赁|孙公司杭州图灵引擎科技有限公司与腾讯科技（深圳）有限公司签订算力服务协议，向腾讯提供集群算力服务。</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>电力, 算力</t>
+          <t>算力租赁</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>1.34</v>
+        <v>2.28</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>“算电协同”模式通过优化算力调度、整合绿色能源资源、提升能源利用效率，成为推动数字基础设施绿色低碳转型的关键路径。</t>
+          <t>开源AI智能体OpenClaw持续火爆，该系统通过拆解任务、调用云端大模型API完成任务，一次任务可消耗数十万乃至数百万Token，算力需求呈指数级增长。</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>sz000601</t>
+          <t>sz002298</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>韶能股份</t>
+          <t>中电鑫龙</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>6.75</v>
+        <v>12.41</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.02</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>绿电|公司自成立以来，一直以能源的投资开发经营为主营业务，在不断巩固和发展水电产业的基础上，重点发展生物质能发电、加油加气充电一体化站等业务。</t>
+          <t>华为算力+电磁存储|1.公司与HUAWEI公司签订了战略合作协议，双方在智慧城市、大数据中心等领域进行合作，双方积极推动智慧城市、大数据中心等项目落地。
+2.公司在2022年半年报中透露，公司专用磁存储产品具备存储密度高、使用能耗低、数据安全高的特点，有望成为长期存储大规模冷数据的更优选择。</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>绿电</t>
+          <t>华为算力, 电磁存储</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>1.34</v>
+        <v>2.28</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>“算电协同”模式通过优化算力调度、整合绿色能源资源、提升能源利用效率，成为推动数字基础设施绿色低碳转型的关键路径。</t>
+          <t>开源AI智能体OpenClaw持续火爆，该系统通过拆解任务、调用云端大模型API完成任务，一次任务可消耗数十万乃至数百万Token，算力需求呈指数级增长。</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>sz000862</t>
+          <t>sz002467</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>银星能源</t>
+          <t>二六三</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>8.359999999999999</v>
+        <v>7.59</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+      <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>绿电|公司新能源发电业务包括风力发电、太阳能光伏发电以及分布式项目发电。</t>
+          <t>AI应用+算力|1.公司在WebRTC、QoS、实时音视频等核心技术基础上，深度融合AI与大模型能力，打造智能通信中枢。通过自研AICC人工智能客户联络中心，实现企业邮箱、视频直播等场景的端到端智能化交互。同时，研发投入持续向AI驱动的云通信解决方案倾斜，构建跨网络动态负载均衡与智能运维体系，支撑亿级并发场景下的服务稳定性。
+2.公司2020年4月22日在互动平台表示，公司的子公司上海二六三通信有限公司与NTT合资的控股子公司上海奈盛通信科技有限公司是国内第一家由民营通信公司与国际一流运营商合资经营的公司，其业务平台为国内第一个以国际运营商标准自建的IDC云计算平台。</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>绿电</t>
+          <t>AI应用, 算力</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>1.34</v>
+        <v>2.28</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>“算电协同”模式通过优化算力调度、整合绿色能源资源、提升能源利用效率，成为推动数字基础设施绿色低碳转型的关键路径。</t>
+          <t>开源AI智能体OpenClaw持续火爆，该系统通过拆解任务、调用云端大模型API完成任务，一次任务可消耗数十万乃至数百万Token，算力需求呈指数级增长。</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>sz002445</t>
+          <t>sz002335</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>中南文化</t>
+          <t>科华数据</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>3.06</v>
+        <v>69.48</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>10.07</v>
+        <v>10.01</v>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
+          <t>算力+液冷|1.目前公司具备了丰富多元的智算产品体系，推出了AI裸金属、GPU服务器租赁、边缘计算、混合云、本地算力资源池、云上弹性算力等算力产品。
+2.公司液冷技术可以解决高功率、高热流密度、高计算密度的芯片和系统散热问题，大幅提升了算力输出能力，使服务器可以在相对的低温环境中满载运行，此项技术能够适用于各大智算中心。</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>算力, 液冷</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>AI应用</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>3月9日，腾讯旗下全场景AI智能体WorkBuddy正式上线。此外，火山引擎正式上线ArkClaw，开箱即用的云上SaaS版OpenClaw。</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>sh605268</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>王力安防</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>5天5板</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>智能经济|公司机器人安全门首创AI遥感解锁，AI智能防夹功能，实现与智能家居互联；自研AI电机驱动算法技术，实现自动开关门，搭载可视智慧猫眼，独创安全G点，关门自动反锁，独创超C级圆柱体专利锁芯。</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>智能经济</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>AI应用</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>3月9日，腾讯旗下全场景AI智能体WorkBuddy正式上线。此外，火山引擎正式上线ArkClaw，开箱即用的云上SaaS版OpenClaw。</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>sz000839</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>国安股份</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>AI审核|公司旗下子公司鸿联九五为企业提供一站式的审核服务体系。公司内容审核业务包括文本审核、图片审核、视频审核、音频审核、人工智能审核。</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>AI审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>AI应用</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>3月9日，腾讯旗下全场景AI智能体WorkBuddy正式上线。此外，火山引擎正式上线ArkClaw，开箱即用的云上SaaS版OpenClaw。</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>sh605287</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>德才股份</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>51.54</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>AI漫剧|旗下奇想无限深耕“网文IP+AI漫剧”转化，与头部网文平台合作，将玄幻、甜宠等成熟IP快速落地，已产出多部爆款。</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>AI漫剧</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>AI应用</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>3月9日，腾讯旗下全场景AI智能体WorkBuddy正式上线。此外，火山引擎正式上线ArkClaw，开箱即用的云上SaaS版OpenClaw。</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>sh605318</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">法狮龙  </t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>76.84</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>AI应用|10月23日，据法狮龙发布公告，公司计划投资设立的全资子公司北宸星穹已完成工商登记手续，并于2025年10月23日取得了由北京市东城区市场监督管理局核发的《营业执照》。北宸星穹经营范围包括人工智能应用软件开发；人工智能行业应用系统集成服务；人工智能基础软件开发等。</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>AI应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>招商证券研报称，2026年全国两会将“算电协同”纳入超大规模新基建工程。政策端的强力催化叠加绿电直连项目规模化落地、全国统一电力市场体系加速构建，算电协同正从政策规划走向产业实践。</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>sz002445</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>中南文化</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>并购+电力+油气|1.中南文化(002445.SZ)公告称，公司计划通过发行股份及支付现金的方式购买江阴电力投资有限公司持有的江阴苏龙热电有限公司57.30%股权，同时拟向不超过三十五名特定投资者募集配套资金。本次交易相关审计、评估工作尚未完成，交易方案需进一步论证和沟通协商。本次交易预计构成重大资产重组。本次交易完成后，上市公司在电力能源领域的业务布局将得到拓展。
 2.公司是目前国内规模较大的工业金属管件制造商，主要产品为管件、法兰、管系和压力容器，产品拥有国际多项生产商许可证书；其中，公司还拥有国家质检总局颁发的压力管道元件、压力容器等特种设备制造许可证，是中国石油天然气集团公司一级供应网络成员单位、中国石油能源一号网会员单位、中国石化资源市场成员厂组织集中采购成员厂。</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>并购, 电力, 油气</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>电力</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>“算电协同”模式通过优化算力调度、整合绿色能源资源、提升能源利用效率，成为推动数字基础设施绿色低碳转型的关键路径。</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>sz001258</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>立新能源</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>9.359999999999999</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>绿电|公司的主营业务为风力发电、光伏发电项目的投资、开发、建设和运营。公司运营的风电场、光伏电站主要位于新疆。</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>绿电</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>电力</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>“算电协同”模式通过优化算力调度、整合绿色能源资源、提升能源利用效率，成为推动数字基础设施绿色低碳转型的关键路径。</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>sh603165</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>荣晟环保</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>14.95</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>环保+电力|2022年1月4日公告，公司与安徽省全椒县人民政府签订年产130万吨再生环保纸及新能源综合利用项目战略合作框架协议，建设内容包括年产130万吨再生环保纸、生物质热电联产(年处理50万吨秸秆)、光伏产品研发和制造、1GW分布式光伏电站等运营管理，并配套建设工业固废资源综合利用项目、环保水处理项目，项目总投资105亿元。</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>环保, 电力</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>AI应用</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>发布仅四个多月，OpenClaw便创造了最快登顶GitHub星标榜的历史——以超过24.8万的GitHub星标数，超越Linux成为GitHub平台上最受欢迎的开源项目。</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>sh605268</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>王力安防</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>15.33</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>9.969999999999999</v>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>4天4板</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>智能经济|公司机器人安全门首创AI遥感解锁，AI智能防夹功能，实现与智能家居互联；自研AI电机驱动算法技术，实现自动开关门，搭载可视智慧猫眼，独创安全G点，关门自动反锁，独创超C级圆柱体专利锁芯。</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>智能经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>AI应用</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>发布仅四个多月，OpenClaw便创造了最快登顶GitHub星标榜的历史——以超过24.8万的GitHub星标数，超越Linux成为GitHub平台上最受欢迎的开源项目。</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>sh603138</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>海量数据</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>23.29</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>AI应用|公司发布的企业级大数据应用平台提供AI驱动的增强分析功能，如时序预测分析、关联分析、根因分析等，助力数据驱动决策。</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>AI应用</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>AI应用</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>发布仅四个多月，OpenClaw便创造了最快登顶GitHub星标榜的历史——以超过24.8万的GitHub星标数，超越Linux成为GitHub平台上最受欢迎的开源项目。</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>sz301606</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>绿联科技</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>80.88</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>AI NAS|中信建投研报指出，家用NAS具有综合优势，但存在产品、市场、认知等核心障碍，导致渗透率较低。当前以绿联科技为首的国产新势力的势头最猛，绿联以充电类为流基本盘，以AI NAS为第二成长曲线，海外放量与资本运作有望形成业绩与估值的双重弹性。</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>AI NAS</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>-0.62</v>
+        <v>0.49</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>国家发展改革委创新和高技术发展司司长白京羽在国新办吹风会上表示，“十五五”规划纲要草案面向中期着力打造集成电路、生物医药、航空航天等新兴支柱产业。</t>
+          <t>招商证券研报称，2026年全国两会将“算电协同”纳入超大规模新基建工程。政策端的强力催化叠加绿电直连项目规模化落地、全国统一电力市场体系加速构建，算电协同正从政策规划走向产业实践。</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>sz000534</t>
+          <t>sz000537</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>万泽股份</t>
+          <t>绿发电力</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>45.36</v>
+        <v>10.34</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>创新药+燃气轮机|1.公司主要产品金双歧和定君生均为独家创新药，受集采降价影响较小。
-2.公司的高温合金产品主要用于航空发动机、燃气轮机（地面与船舶燃机、核电、机车动力等领域）、涡轮增压器等，主要客户即该领域公司。</t>
+          <t>电算协同|绿发电力在互动平台表示，作为“新能源+”融合发展的重要场景，电算协同一直是公司密切关注并重点布局的方向。目前公司正开展相关业务的对接和论证工作，若有重大进展将按规定履行内部决策和信息披露程序。</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>创新药, 燃气轮机</t>
+          <t>电算协同</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>-0.62</v>
+        <v>0.49</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>国家发展改革委创新和高技术发展司司长白京羽在国新办吹风会上表示，“十五五”规划纲要草案面向中期着力打造集成电路、生物医药、航空航天等新兴支柱产业。</t>
+          <t>招商证券研报称，2026年全国两会将“算电协同”纳入超大规模新基建工程。政策端的强力催化叠加绿电直连项目规模化落地、全国统一电力市场体系加速构建，算电协同正从政策规划走向产业实践。</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>sh600851</t>
+          <t>sh600726</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>海欣股份</t>
+          <t>华电能源</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>8.779999999999999</v>
+        <v>3.21</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>10.03</v>
+        <v>9.93</v>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>创新药|子公司上海海欣生物技术有限公司APDC项目主要用于结直肠癌治疗，目前海欣生物就APDC三期项目正多方面探索解决方案。</t>
+          <t>电力|经过近年来的不断优化转型，公司的主营业务已从单纯的发电、供热有效拓展为集发电、供热、煤炭、工程板块"四位一体"的产业格局，公司已成为黑龙江省最大的发电及集中供热运营商。</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>电力</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>-0.62</v>
+        <v>0.49</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>国家发展改革委创新和高技术发展司司长白京羽在国新办吹风会上表示，“十五五”规划纲要草案面向中期着力打造集成电路、生物医药、航空航天等新兴支柱产业。</t>
+          <t>招商证券研报称，2026年全国两会将“算电协同”纳入超大规模新基建工程。政策端的强力催化叠加绿电直连项目规模化落地、全国统一电力市场体系加速构建，算电协同正从政策规划走向产业实践。</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>sz002082</t>
+          <t>sh601778</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>万邦德</t>
+          <t>晶科科技</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>18.66</v>
+        <v>5.61</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>10.02</v>
+        <v>10</v>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI医疗+创新药|在研发端，公司探索人工智能在创新药设计、筛选、实验设计等环节的应用，目前全球首个治疗胃轻瘫的中药1.1类新药“理中消痞颗粒”正在开展临床研究。 </t>
+          <t xml:space="preserve">绿电|公司主营业务主要包括光伏电站运营、光伏电站转让和光伏电站EPC等，涉及太阳能光伏电站的开发、投资、建设、运营和管理、转让等环节，以及光伏电站EPC工程总承包、电站运营综合服务解决方案等。光伏电站运营业务为公司成立至今的核心业务，公司开发的光伏电站项目包括领跑者光伏电站、普通地面电站、屋顶分布式光伏电站等多种类型。
+</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>AI医疗, 创新药</t>
+          <t>绿电</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>油气设服</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>-0.35</v>
+        <v>2.53</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>WTI原油期货一度暴涨超30%，报118.7美元/桶。</t>
+          <t>国家发改委主任郑栅洁在记者会上表示，将重点打造六大新兴支柱产业和六大未来产业。六大新兴支柱产业其中包括智能机器人，相关产值在2025年已经接近6万亿元。</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sz002930</t>
+          <t>sh603949</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>宏川智慧</t>
+          <t>雪龙集团</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>14.67</v>
+        <v>19.49</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>9.969999999999999</v>
+        <v>9.99</v>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>油气|公司系一家创新型石化产品物流综合服务提供商，主要为境内外石化产品生产商、贸易商和终端用户提供仓储综合服务及其他相关服务。公司主要从事仓储综合服务、中转及其他服务、物流链管理服务三大业务。</t>
+          <t>参股宇树|公司作为有限合伙人通过深创投中小企业发展基金（新疆）有限合伙企业间接持股杭州宇树科技有限公司。目前，深创投中小企业发展基金（新疆）有限合伙企业对杭州宇树科技有限公司的持股比例为1.3546%；公司对深创投中小企业发展基金（新疆）有限合伙企业的持股比例为0.7239%。</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>油气</t>
+          <t>参股宇树</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>油气设服</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>-0.35</v>
+        <v>2.53</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>WTI原油期货一度暴涨超30%，报118.7美元/桶。</t>
+          <t>国家发改委主任郑栅洁在记者会上表示，将重点打造六大新兴支柱产业和六大未来产业。六大新兴支柱产业其中包括智能机器人，相关产值在2025年已经接近6万亿元。</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sh601969</t>
+          <t>sh600376</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>海南矿业</t>
+          <t>首开股份</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>13.52</v>
+        <v>5.53</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>10.01</v>
+        <v>9.94</v>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>油气|公司旗下控股孙公司洛克石油公司是澳大利亚一家领先的独立上游油气勘探开发公司，业务范围涵盖从油气勘探、评价到开发、生产的上游全周期业务，主要资产位于中国渤海、中国北部湾、马来西亚、澳大利亚，是一家具有近20年油气作业经验的公司。</t>
+          <t>参股宇树|公司旗下首开盈信通过金石成长股权投资（杭州）合伙企业间接投资宇树科技。</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>油气</t>
+          <t>参股宇树</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>-1.29</v>
+        <v>2.53</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>早盘国内能化市场掀起涨停潮，甲醇、烧碱、纯苯、纯碱、苯乙烯、乙二醇、对二甲苯等化工品期货主力合约均封涨停。</t>
+          <t>国家发改委主任郑栅洁在记者会上表示，将重点打造六大新兴支柱产业和六大未来产业。六大新兴支柱产业其中包括智能机器人，相关产值在2025年已经接近6万亿元。</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sh600227</t>
+          <t>sz003021</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">赤天化  </t>
+          <t>兆威机电</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>3.62</v>
+        <v>124.38</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>6天3板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>氮肥+甲醇|公司是贵州省最大的氮肥生产企业，公司化肥化工生产基地分别是以天然气为原料生产的赤水化工分公司（年产63万吨尿素）和以煤为生产原料的公司全资子公司桐梓化工（年产52万吨尿素、30万吨甲醇）。</t>
+          <t>机器人|公司的微型传动、微型驱动系统产品,具有高精度运动控制、高扭矩输出和紧凑体积等特性。基于对精密减速箱、高性能电机和电控系统的产品组合,结合自身的技术优势、产品特点,公司聚焦手指等运动执行应用部位,开发仿生机器人灵巧手产品,该产品与公司的技术能力相契合,系公司未来平台化产品的重点布局。</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>氮肥, 甲醇</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>-1.29</v>
+        <v>2.96</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>早盘国内能化市场掀起涨停潮，甲醇、烧碱、纯苯、纯碱、苯乙烯、乙二醇、对二甲苯等化工品期货主力合约均封涨停。</t>
+          <t>电子元件供应链人士透露，德州仪器（TI）从4月1日起提高部分半导体产品的价格。一些分销商表示，价格上涨幅度可能在15%到85%之间。</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
@@ -2242,315 +2231,352 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>sz002068</t>
+          <t>sz002290</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>黑猫股份</t>
+          <t>禾盛新材</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>9.52</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>10.06</v>
+        <v>10</v>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>煤化工|公司主要从事炭黑、焦油精制和白炭黑等产品的生产与销售，具备炭黑年生产能力116.2万吨，是国内炭黑行业龙头企业。作为国内行业龙头，公司得到普利司通、米其林、固特异、住友、横滨、韩泰、锦湖等众多一流跨国轮胎企业认可，成为其在中国大陆为数不多的全球供应商。</t>
+          <t>算力芯片|2025年6月11日公告，公司拟以自有资金或自筹资金2.5亿元向熠知电子增资，增资后预计持有熠知电子10%股权。熠知电子系国内少数已商业落地ARM服务器处理器芯片公司，熠知TF7000系列实测性能达到国内先进水平，可同时覆盖人工智能、云计算、边缘计算多场景。熠知电子则是国产化CPU领域的核心企业之一，拥有先进的ARM架构，产品应用于多个行业，设计融合一流AI算法和先进制程工艺的智能芯片，并且以此构建人工智能硬件平台，提供行业应用解决方案。</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>煤化工</t>
+          <t>算力芯片</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>储能</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>0.54</v>
+        <v>2.96</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>方正证券认为，在欧盟推动淘汰俄罗斯天然气进口，转而增加对中东LNG依赖的背景下，若天然气价格再度大涨，势必带动欧洲户储、热泵产品销售提升。</t>
+          <t>电子元件供应链人士透露，德州仪器（TI）从4月1日起提高部分半导体产品的价格。一些分销商表示，价格上涨幅度可能在15%到85%之间。</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>sh601877</t>
+          <t>sh688300</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>正泰电器</t>
+          <t>联瑞新材</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>39.05</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>储能|参股正泰电源的储能产品包括户用储能变流器、模块化储能变流器、集中式储能变流器、户外电池柜、电池集装箱及能量管理系统等。</t>
+          <t>半导体材料|公司持续聚焦芯片先进封装、新一代高频高速覆铜板、新能源汽车动力电池模组和光伏电池胶黏剂等领域，应用于异构集成技术封装、底部填充材料（Underfill）的亚微米级球形硅微粉、应用于存储芯片封装的Lowα微米级球形硅微粉和Lowα亚微米级球形硅微粉等高尖端应用的系列化产品已通过海内外客户的认证并批量出货，液态填料已小批量出货。</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>储能</t>
+          <t>半导体材料</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>工业母机</t>
+          <t>发电机概念</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>-1.34</v>
+        <v>1.54</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>国家发改委秘书长袁达3月7日在国新办吹风会上表示，全链条推动集成电路、工业母机、高端仪器、基础软件、先进材料、生物制造等重点领域关键核心技术攻关取得决定性突破。</t>
+          <t>中信建投证券研报指出，AIDC建设进入高速增长期，测算2025-2028年美国AI需求带来的电力容量需求期间CAGR约55%，未来三年累计需求超150GW，配套设备迎来机遇。</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>sz002903</t>
+          <t>sz002760</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>宇环数控</t>
+          <t>凤形股份</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>27.61</v>
+        <v>25.23</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>工业母机+机器人|1.公司一直专业从事数控磨削设备及智能装备的研发、生产、销售与服务，为客户提供精密磨削与智能制造技术综合解决方案。
-2.公司经营范围包括工业机器人及其关键功能部件、机械配件、金属材料的制造和销售。</t>
+          <t>特种电机|子公司康富科技主要产品为船电系统解决方案及特种电机，船电系统解决方案主要应用于船电装备领域，特种电机主要应用于军用、轨道交通、核电及数据中心等市场。</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>工业母机, 机器人</t>
+          <t>特种电机</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>发电机概念</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="C41" s="2" t="inlineStr"/>
+        <v>1.54</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>中信建投证券研报指出，AIDC建设进入高速增长期，测算2025-2028年美国AI需求带来的电力容量需求期间CAGR约55%，未来三年累计需求超150GW，配套设备迎来机遇。</t>
+        </is>
+      </c>
       <c r="D41" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>sz002528</t>
+          <t>sz300257</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>ST英飞拓</t>
+          <t>开山股份</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>3.35</v>
+        <v>34.33</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>19.99</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 英飞拓推出5G多功能智慧灯杆，支持节能照明、视频监控、新能源充电、公共WIFI、环境监测、信息发布、应急报警、5G微基站等模块，实现多种类型的感知数据采集、分析、仿真预测，提升城市综合治理。</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr"/>
+          <t>发电机+电力|1.公司既有蒸汽膨胀发电机，应用于高温蒸汽发电；又有ORC（有机朗肯循环）膨胀发电机，应用于乏汽和热水发电。
+2.2016年4月，公司全资收购OTP公司，获得印尼SMGP240MW地热项目的特许开发经营权，并采取“边投资、边建设、边运营、边收益”的商业模式。2019年9月28日，第一期（126MW）首批45MW实现并网发电。</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>发电机, 电力</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>智能电网</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="C42" s="2" t="inlineStr"/>
+        <v>1.39</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>正泰董事长南存辉在两会记者会提到，这两年全球AI算力建设爆发式增长，变压器变得一台难求。“去年我们变压器出口同比增长71.4%, 工厂订单都排到2027年了。”</t>
+        </is>
+      </c>
       <c r="D42" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>sz000488</t>
+          <t>sh603421</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>ST晨鸣</t>
+          <t>鼎信通讯</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>2.6</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.04</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司是全国唯一一家实现制浆和造纸平衡的大型浆纸一体化企业，率先布局全产业链，在山东、广东、湖北、江西、吉林等地建有6个生产基地，年浆纸产能达1100多万吨。</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr"/>
+          <t>半导体+电网设备|1.鼎信通讯在互动平台表示，公司芯片开发采用平头哥的CK802 32位内核架构，平头哥与公司签订有全面技术授权协议。
+2.公司的主营业务为低压用电系统产品的研发、生产、销售及服务，主要产品包括低压电力线载波通信模块（含芯片）产品、采集终端设备、智能电能表和配电终端等，主要应用于国家智能电网的用电信息采集系统和配网自动化系统。</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>半导体, 电网设备</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>智能电网</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="C43" s="2" t="inlineStr"/>
+        <v>1.39</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>正泰董事长南存辉在两会记者会提到，这两年全球AI算力建设爆发式增长，变压器变得一台难求。“去年我们变压器出口同比增长71.4%, 工厂订单都排到2027年了。”</t>
+        </is>
+      </c>
       <c r="D43" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>sz000504</t>
+          <t>sz002350</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>*ST生物</t>
+          <t>北京科锐</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>9.49</v>
+        <v>15.22</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>4.98</v>
+        <v>9.969999999999999</v>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司是目前国内一家国资控股的干细胞、免疫细胞及组织工程产业主板上市公司，“生物医药”板块业务包括干细胞储存服务、化妆品的生产和销售、医疗器械设备及耗材的代理和销售。</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr"/>
+          <t>电网设备|公司是技术导向型配电设备制造企业，主营业务为12kV及以下配电及控制设备的研发、生产与销售。公司成立30年以来，专注于配电系统技术进步，崇尚技术创新，曾率先推出智能节电器、故障指示器、美式箱变、户外环网柜、永磁机构真空开关、GRC环保箱体和高过载变压器等新技术或产品。</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>电网设备</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>折叠屏</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="C44" s="2" t="inlineStr"/>
+        <v>3.81</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>苹果下半年将发表首款折叠机iPhone Fold，供应链消息称，苹果内部对新机销售量非常有信心，大幅调高供应链备货量，比原定目标上调两成。</t>
+        </is>
+      </c>
       <c r="D44" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>sh600289</t>
+          <t>sh600135</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST信通  </t>
+          <t>乐凯胶片</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>7.76</v>
+        <v>11.06</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="I44" s="2" t="inlineStr"/>
+        <v>10.05</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司在智能交通领域继续保持稳健发展，着重提升项目的盈利能力。</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr"/>
+          <t>折叠屏|在超细银粉、导电银浆等材料方面技术领先，乐凯集团去年底在珠海航展上展示了自主研发的用于柔性屏的纳米银线导电膜。</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>折叠屏</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>创新药</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="C45" s="2" t="inlineStr"/>
+        <v>2.51</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>2026年1-2月中国创新药BD交易总额达532.76亿美元，交易数量达44项，开年仅两个月的交易金额超过2025年任一单季度，并与2024年全年水平接近。</t>
+        </is>
+      </c>
       <c r="D45" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>sh600568</t>
+          <t>sz002294</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST中珠  </t>
+          <t>信立泰</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>3.02</v>
+        <v>54.01</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>4.859999999999999</v>
+        <v>10</v>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 以眼科领域的专用药品为主，主要有珍珠明目滴眼液、阿昔洛韦滴眼液等。</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr"/>
+          <t>创新药|公司抗心衰创新药S086、生物药“重组胰高血糖素样肽-1-Fc  融合蛋白注射液”申报临床已获得临床批件（二季度CDE受理，三季度获得批件）；甲磺酸伊马替尼、奥美沙坦酯、盐酸莫西沙星等项目申报生产获CDE  受理，目前分处于不同的审评阶段。</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>创新药</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2559,32 +2585,36 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>-0.61</v>
+        <v>1.58</v>
       </c>
       <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>sh600753</t>
+          <t>sz000711</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST海钦 </t>
+          <t>ST京蓝</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>10.82</v>
+        <v>4.22</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>5.050000000000001</v>
-      </c>
-      <c r="I46" s="2" t="inlineStr"/>
+        <v>4.98</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>26天17板</t>
+        </is>
+      </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司目前的主营业务为煤炭（含焦炭）、天然气等大宗商品供应链管理业务。</t>
+          <t>ST股 | 主要业务包括流域水生态修复、灌区节水综合系统工程、污水治理、沿河生态景观工程、智慧水务等。</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
@@ -2596,32 +2626,36 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>-0.61</v>
+        <v>1.58</v>
       </c>
       <c r="C47" s="2" t="inlineStr"/>
       <c r="D47" s="2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>sz002047</t>
+          <t>sz000488</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>*ST宝鹰</t>
+          <t>ST晨鸣</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>5.33</v>
+        <v>2.73</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="I47" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 宝鹰股份公告，公司正在筹划重大资产出售事项，拟向控股股东大横琴集团出售所持有的宝鹰建设100%股权。本次交易构成关联交易，预计构成重大资产重组。</t>
+          <t>ST股 | 公司是全国唯一一家实现制浆和造纸平衡的大型浆纸一体化企业，率先布局全产业链，在山东、广东、湖北、江西、吉林等地建有6个生产基地，年浆纸产能达1100多万吨。</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
@@ -2633,32 +2667,36 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>-0.61</v>
+        <v>1.58</v>
       </c>
       <c r="C48" s="2" t="inlineStr"/>
       <c r="D48" s="2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>sh600525</t>
+          <t>sh600568</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST长园  </t>
+          <t xml:space="preserve">ST中珠  </t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>5.82</v>
+        <v>3.17</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>5.050000000000001</v>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
+        <v>4.97</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 子公司长园光波导技术（珠海）有限公司主要从事光学方案相关检测设备及制程设备的市场与技术布局。</t>
+          <t>ST股 | 以眼科领域的专用药品为主，主要有珍珠明目滴眼液、阿昔洛韦滴眼液等。</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr"/>
@@ -2666,33 +2704,31 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>1.58</v>
       </c>
       <c r="C49" s="2" t="inlineStr"/>
       <c r="D49" s="2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>sh601789</t>
+          <t>sh600753</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>宁波建工</t>
+          <t xml:space="preserve">*ST海钦 </t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>6.04</v>
+        <v>11.36</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>10.02</v>
+        <v>4.99</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
@@ -2701,98 +2737,948 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>数据中心机柜出租|宁波建工2023年6月20日在投资者互动平台表示，中经云主营业务为数据中心机柜位出租，无算力出租服务。</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>数据中心机柜出租</t>
-        </is>
-      </c>
+          <t>ST股 | 公司目前的主营业务为煤炭（含焦炭）、天然气等大宗商品供应链管理业务。</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>1.58</v>
       </c>
       <c r="C50" s="2" t="inlineStr"/>
       <c r="D50" s="2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>sh600135</t>
+          <t>sz000504</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>乐凯胶片</t>
+          <t>*ST生物</t>
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>10.05</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>9.959999999999999</v>
-      </c>
-      <c r="I50" s="2" t="inlineStr"/>
+        <v>4.95</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>光学TAC薄膜|2023年7月18日公告，公司拟变更部分募集资金用途，向中国乐凯集团有限公司收购乐凯光电材料有限公司100%股权并对其增资。变更后的新项目中，拟2.83亿元收购乐凯光电100%股权，2.5亿元用于TAC膜3#生产线项目。乐凯光电主营业务为TAC膜、PVB 膜等光电显示材料的研发、生产和销售，是中国大陆唯一掌握LCD用TFT级偏光片用光学TAC薄膜制造技术的企业，自主研发的光学TAC薄膜产品被认定为高新技术产品。</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>光学TAC薄膜</t>
-        </is>
-      </c>
+          <t>ST股 | 公司是目前国内一家国资控股的干细胞、免疫细胞及组织工程产业主板上市公司，“生物医药”板块业务包括干细胞储存服务、化妆品的生产和销售、医疗器械设备及耗材的代理和销售。</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>1.58</v>
       </c>
       <c r="C51" s="2" t="inlineStr"/>
       <c r="D51" s="2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>sz000973</t>
+          <t>sz002592</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>佛塑科技</t>
+          <t>ST八菱</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>14.5</v>
+        <v>10.25</v>
       </c>
       <c r="H51" s="2" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司配套氢燃料电池客车的产品技术目前已经形成商业化，广泛应用于燃气客车、混合动力客车和军车等领域。</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C52" s="2" t="inlineStr"/>
+      <c r="D52" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>sh600599</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*ST熊猫 </t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司地处中国烟花之乡浏阳，经过3多年的发展已成为中国最大的出口鞭炮烟花公司</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C53" s="2" t="inlineStr"/>
+      <c r="D53" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>sz000004</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>*ST国华</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司旗下全资子公司智游网安为专业移动应用安全综合服务提供商。</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>sz002485</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>ST雪发</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司文旅项目地处一线旅游目的地黄金地段，历史文化底蕴深厚，旅游资源丰富，市场潜力较大。</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C55" s="2" t="inlineStr"/>
+      <c r="D55" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>sh603557</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST起步  </t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 国内童鞋龙头。旗下 ABC KIDS 占据我国童鞋第一、童装第七的市场地位。</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>sz001270</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>*ST铖昌</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>121.19</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司主营业务为微波毫米波模拟相控阵T/R芯片的研发、生产、销售和技术服务，产品已应用于探测、遥感、通信、导航、电子对抗等领域。</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C57" s="2" t="inlineStr"/>
+      <c r="D57" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>sz000669</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>ST金鸿</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 主营气源开发与输送、长输管网建设与管理、城市燃气经营与销售、车用加气站投资与运营、LNG点供、分布式能源项目开发与建设等。</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C58" s="2" t="inlineStr"/>
+      <c r="D58" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>sh600421</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*ST华嵘 </t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>5.029999999999999</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司实控人是中天控股集团下属浙江恒顺投资，集团旗下中天氟硅2023年撤回ipo，原计划通过IPO募集14.42亿元资金，用于30万吨/年有机硅单体扩能技改及综合利用项目。</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C59" s="2" t="inlineStr"/>
+      <c r="D59" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>sz002898</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>*ST赛隆</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>5.050000000000001</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司已建成集医药中间体、原料药、制剂的研发、生产、营销和技术服务为一体的医药全产业链的现代化制药企业。</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C60" s="2" t="inlineStr"/>
+      <c r="D60" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>sz002789</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>*ST建艺</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司是集施工、设计、资源矿产、科技工业园、高新技术建材产业、投融资为一体的规模化实体企业集团。</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr"/>
+      <c r="D61" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>sh600108</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>亚盛集团</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>8天6板</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>农业种植|1.公司2026年3月2日公告，目前未开展矿产相关业务，也不存在需要披露的相关重大信息。
+2.公司主要种植经营啤酒花、马铃薯、牧草、果品、药材、食葵、辣椒、枸杞、香辛料等初级农产品和加工产品，以及生产经营节水灌溉设备。</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>农业种植</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr"/>
+      <c r="D62" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>sh601789</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>宁波建工</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>数据中心机柜出租|宁波建工2023年6月20日在投资者互动平台表示，中经云主营业务为数据中心机柜位出租，无算力出租服务。</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>数据中心机柜出租</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr"/>
+      <c r="D63" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>sz002969</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>嘉美包装</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>25.91</v>
+      </c>
+      <c r="H63" s="2" t="n">
         <v>10.02</v>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>电池隔膜|公司并购标的金力股份持续在锂硫电池隔膜、半固态锂电池隔膜、燃料电池隔膜、固态电解质等方面进行技术布局。</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>电池隔膜</t>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>追觅创始人入主|追觅创始人旗下逐越鸿智斥资逾22.82亿元拿下嘉美包装公司控制权。追觅科技有关人士向《科创板日报》记者表示，本次收购资金全部来源于俞浩及核心团队的自有与自筹资金，无来自追觅科技公司的资金，不会影响追觅科技公司正常运营。“逐越鸿智将以‘战略赋能者’身份参与嘉美包装运营，依托追觅在技术创新与全球资源上的优势，推动其在智能化生产、高端产品研发及全球化布局上实现突破。”</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>追觅创始人入主</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr"/>
+      <c r="D64" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>sz000949</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>新乡化纤</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>化纤|公司是国内较早进入化纤行业的企业之一，主营粘胶长丝、氨纶纤维的生产与销售，主要产品粘胶长丝是再生纤维素纤维，氨纶纤维是一种综合性能非常优秀的高弹性纤维，在织物和服饰中的应用越来越广泛。</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>化纤</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr"/>
+      <c r="D65" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>sh603115</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>海星股份</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>电极箔|公司主营产品电极箔可应用于MLPC电容器。MLPC产品可广泛应用于服务器中高功耗芯片的供电滤波场景，特别是CPU和GPU的核心电压供电。</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>电极箔</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr"/>
+      <c r="D66" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>sz001332</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>锡装股份</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>65.55</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>油气+核电|公司主要从事金属压力容器的研发、设计、制造、销售及相关技术服务，已形成以换热压力容器、反应压力容器、储存压力容器、分离压力容器和海洋油气装置模块为主的非标压力容器产品系列，产品主要应用于炼油及石油化工、基础化工、核电及太阳能发电、高技术船舶及海洋工程等领域。</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>油气, 核电</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr"/>
+      <c r="D67" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>sz002729</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>好利科技</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>19.18</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>电力熔断器|公司电力熔断器产品应用市场在于UPS、变频器、光伏发电、风力发电以及电动汽车等市场。</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>电力熔断器</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr"/>
+      <c r="D68" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>sz000014</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>沙河股份</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>14.31</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>并购重组|沙河股份公告称，公司拟以支付现金的方式购买深业鹏基持有的晶华电子70%的股权。本次交易完成后，晶华电子将成为上市公司的控股子公司，纳入公司合并报表范围，交易价格2.74亿元。本次交易构成重大资产重组。本次交易完成后，沙河股份将改变现有单一房地产业务的经营现状，切入智能显示控制器、液晶显示器件的研发、生产与销售相关业务领域。</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>并购重组</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr"/>
+      <c r="D69" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>sz002993</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>奥海科技</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>50.08</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>服务器电源|公司致力于CRPS服务器通用冗余电源研发、生产和销售，服务器电源、算力电源、服务器PDB电源等产品实现批量出货，出货及在研功率范围覆盖550W至8000W。</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>服务器电源</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr"/>
+      <c r="D70" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>sh600172</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>黄河旋风</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>金刚石|公司作为超硬材料行业龙头以及唯一的全产业链布局企业，主要产品包括培育钻石及工业金刚石两大产品体系，覆盖工业金刚石、培育钻石、砂轮、刀具、钻头、锯片等，是国内乃至全球范围内品类别齐全、链条完整的超硬材料及制品制造商，可以向客户提供产品类别、规格齐全以及性能稳定的各类超硬材料及制品，包括超硬材料单晶及制品、立方氮化硼及制品、金刚石聚晶及制品以及超硬材料制品辅助材料。</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>金刚石</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr"/>
+      <c r="D71" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>920036.BJ</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>觅睿科技</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>53.69</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>北交所次新|觅睿科技为智能摄像机“小巨人”，公司专注于智能网络摄像机及物联网视频产品的研产销，并且提供相关云存储、AI等增值服务，产品主要应用于室外/内安防、智能入户、婴儿看护、智能庭院等场景。</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>北交所次新</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr"/>
+      <c r="D72" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>sh600769</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>祥龙电业</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>国企改革|公司的最终控制人为武汉东湖新技术开发区管理委员会。公司的主要业务为供水业务和建筑业务。</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>国企改革</t>
         </is>
       </c>
     </row>
@@ -2807,7 +3693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2834,7 +3720,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -2849,31 +3735,31 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sz000533</t>
+          <t>sh601789</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>顺钠股份</t>
+          <t>宁波建工</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sz000815</t>
+          <t>sh600135</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>美利云</t>
+          <t>乐凯胶片</t>
         </is>
       </c>
     </row>
@@ -2883,12 +3769,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sz000534</t>
+          <t>sz002445</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>万泽股份</t>
+          <t>中南文化</t>
         </is>
       </c>
     </row>
@@ -2898,12 +3784,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sh600821</t>
+          <t>sz002903</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>金开新能</t>
+          <t>宇环数控</t>
         </is>
       </c>
     </row>
@@ -2913,87 +3799,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sh601567</t>
+          <t>sz002575</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>三星医疗</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>sz000601</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>韶能股份</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>sh601789</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>宁波建工</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>sh600227</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">赤天化  </t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>sz002261</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>拓维信息</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>sz002015</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>协鑫能科</t>
+          <t>群兴玩具</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,20 +476,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="101" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="106" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="343" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -552,262 +552,275 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>4.77</v>
+        <v>1.19</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>美国光通信技术公司AOI宣布，已收到一家长期主要超大规模客户的1.6T数据中心光收发器首批量产订单，金额逾2亿美元，标志着新一代高速光互联产品正式进入规模化商用阶段。</t>
+          <t>全球石油运输受阻，油价高位运行直接支撑化工品价格中枢。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>sz001267</t>
+          <t>sh600722</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>汇绿生态</t>
+          <t>金牛化工</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>45.68</v>
+        <v>14</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>4天2板</t>
+          <t>8天4板</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>光通信|公司旗下钧恒科技是专业从事高端光通信产品的研制、生产及推广的高新技术企业，拥有从光学组件，光电转换模块，光端机及子系统的行业垂直整合能力，能够为客户提供各种特定应用的定制化产品，包括PLCC、Mini SFF、Micro Pod等各种形态及各种复合协议的光端机及波分复用子系统。</t>
+          <t>甲醇|公司的主要业务为甲醇的生产和销售，产品方式为焦炉气制甲醇。公司的主要业务由持股50%的控股子公司金牛旭阳经营，金牛旭阳拥有的甲醇生产能力为20万吨/年。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>甲醇</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>4.77</v>
+        <v>1.19</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>美国光通信技术公司AOI宣布，已收到一家长期主要超大规模客户的1.6T数据中心光收发器首批量产订单，金额逾2亿美元，标志着新一代高速光互联产品正式进入规模化商用阶段。</t>
+          <t>全球石油运输受阻，油价高位运行直接支撑化工品价格中枢。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sh603803</t>
+          <t>sz000833</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>瑞斯康达</t>
+          <t>粤桂股份</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>11</v>
+        <v>27.52</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
+        <v>9.99</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>光模块|在高端光模块领域，公司联营企业易锐光电是中国少数产业链上下游关键层面具备完整核心技术和解决方案的高科技企业，新一代基于自主知识产权的25G/100G/超100G集成光收发芯片的光通信模块及光组件，用于电信网络城域网和大型数据中心网络。</t>
+          <t>硫化工|云硫矿业是粤桂股份硫化工产业板块实体子公司，位于广东云浮市云城区，探明硫铁矿储量2.08亿吨，占全国硫铁矿富矿资源的85%，平均品位31.04%，品质优良，原矿产能约300万吨/年，按百川盈孚网公布的全国硫铁矿产量计算，公司硫铁矿产量占全国产量约16.63%。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>光模块</t>
+          <t>硫化工</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4.77</v>
+        <v>1.19</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>美国光通信技术公司AOI宣布，已收到一家长期主要超大规模客户的1.6T数据中心光收发器首批量产订单，金额逾2亿美元，标志着新一代高速光互联产品正式进入规模化商用阶段。</t>
+          <t>全球石油运输受阻，油价高位运行直接支撑化工品价格中枢。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sh600330</t>
+          <t>sz000545</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>天通股份</t>
+          <t>金浦钛业</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>17.22</v>
+        <v>3.83</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
+        <v>10.06</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>商业航天+铌酸锂|1.在航天航空领域，公司的蓝宝石材料因其优异的耐高温和抗辐射性能，被广泛用于制造航空航天器的窗口和仪表保护盖。蓝宝石光学窗口能够在极端环境下保持高透明度和结构完整性，确保航天器在高空、真空和辐射环境中的正常运行。
-2.2023年6月9日公司在互动平台表示，国内多家厂商已经发布数通800G薄膜铌酸锂方案的光模块，公司生产的铌酸锂单晶材料是薄膜铌酸锂调制器的上游关键原材料。</t>
+          <t>钛白粉+锂电池|1.全资子公司南京钛白是我国最早生产钛白粉的企业之一，也是国内最早研制、生产高档金红石钛白粉和化纤钛白粉的企业之一，目前已成为国内大型硫酸法钛白粉生产企业和行业骨干企业。
+2.2022年3月28日公告，公司拟在安徽（淮北）新型煤化工合成材料基地投资建设20万吨/年电池级磷酸铁、20万吨/年磷酸铁锂等新能源电池材料一体化项目，该项目总投资在100亿元左右。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>商业航天, 铌酸锂</t>
+          <t>钛白粉, 锂电池</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4.77</v>
+        <v>1.19</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>美国光通信技术公司AOI宣布，已收到一家长期主要超大规模客户的1.6T数据中心光收发器首批量产订单，金额逾2亿美元，标志着新一代高速光互联产品正式进入规模化商用阶段。</t>
+          <t>全球石油运输受阻，油价高位运行直接支撑化工品价格中枢。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sh601869</t>
+          <t>sh600075</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>长飞光纤</t>
+          <t>新疆天业</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>233.1</v>
+        <v>7.47</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr"/>
+        <v>10.01</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆|公司系全球光纤光缆行业的领先企业，是国内最早的光纤光缆生产厂商之一，聚焦电信运营商和数据通信相关领域，致力于光纤预制棒、光纤和光缆以及数据通信相关产品的研发创新与生产制造，形成了棒纤缆、综合布线和光模块一体化的完整产业链、相关多元化和国际化的业务模式。</t>
+          <t>化工|公司通过资产重组、收购氯碱化工资产，已具备较为完整的“自备电力→电石→聚氯乙烯树脂及副产品→电石渣及其他废弃物制水泥”一体化产业联动式绿色环保型循环经济产业链，具有89万吨PVC产能（包括69万吨通用PVC、10万吨特种树脂、10万吨糊树脂）、65万吨离子膜烧碱产能、134万吨电石产能，同时拥有2×300MW、2×330MW自备热电站以及405万吨电石渣制水泥装置。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>化工</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>4.77</v>
+        <v>1.19</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>美国光通信技术公司AOI宣布，已收到一家长期主要超大规模客户的1.6T数据中心光收发器首批量产订单，金额逾2亿美元，标志着新一代高速光互联产品正式进入规模化商用阶段。</t>
+          <t>全球石油运输受阻，油价高位运行直接支撑化工品价格中枢。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sz002281</t>
+          <t>sz002455</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>光迅科技</t>
+          <t>百川股份</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>86.16</v>
+        <v>14.73</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>光模块|公司可以提供全套的液冷光模块产品，同时公司是浸没液冷智算产业发展联盟会员单位，是相关标准、工艺研究和实践的重要参与者之一。</t>
+          <t>化工+固态电池|1.公司是一家从事高新技术精细化工产品生产的专业企业，主营业务为醋酸酯类、偏苯三酸酐及酯类、醇醚类、多元醇类化工产品的研发、生产和销售。
+2.子公司海基开发的准固态电池具有高能量密度、轻量化特性，兼顾低内阻与长寿命等特点。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>光模块</t>
+          <t>化工, 固态电池</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>4.77</v>
+        <v>1.19</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>美国光通信技术公司AOI宣布，已收到一家长期主要超大规模客户的1.6T数据中心光收发器首批量产订单，金额逾2亿美元，标志着新一代高速光互联产品正式进入规模化商用阶段。</t>
+          <t>全球石油运输受阻，油价高位运行直接支撑化工品价格中枢。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sh600345</t>
+          <t>sh603938</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>长江通信</t>
+          <t>三孚股份</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>43.76</v>
+        <v>30.12</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>10.01</v>
@@ -815,677 +828,672 @@
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆+商业航天|1.公司参股公司长飞光纤（持股比例15.82%）系全球光纤光缆行业的领先企业，是国内最早的光纤光缆生产厂商之一。
-2.公司全资子公司迪爱斯中标的上海垣信卫星科技有限公司的项目主要是卫星地面站园区建设和信关站建设。公司主要提供低轨卫星地面运控中心网络控制管理和指挥系统，以及按照客户要求提供地面卫星通信设备、卫星通信机房及其他软硬件设备等集成服务。</t>
+          <t>化工+半导体材料|1.公司围绕循环经济的发展模式，主要从事三氯氢硅及氢氧化钾等精细化工产品的研发、生产和销售。
+2.公司电子特气产品为电子级二氯二氢硅、电子级三氯氢硅、电子级四氯化硅，下游主要应用于先进晶圆加工，存储芯片制造，硅外延片制造，已实现向部分国内龙头存储厂商、逻辑芯片Fab厂商批量稳定供应。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆, 商业航天</t>
+          <t>化工, 半导体材料</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>4.77</v>
+        <v>1.19</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>美国光通信技术公司AOI宣布，已收到一家长期主要超大规模客户的1.6T数据中心光收发器首批量产订单，金额逾2亿美元，标志着新一代高速光互联产品正式进入规模化商用阶段。</t>
+          <t>全球石油运输受阻，油价高位运行直接支撑化工品价格中枢。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sh600498</t>
+          <t>sz001207</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>烽火通信</t>
+          <t>联科科技</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>57.2</v>
+        <v>31.27</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆+商业航天|1.公司系光通信行业领先企业，产品围绕光通信全产业链布局，是我国最早从事光通信传输设备、光纤光缆科研、生产的企业，已跻身全球光传输与网络接入设备、光纤光缆最具竞争力企业10强。
-2.公司全面进军卫星光通信领域，低轨星载路由(天基IP网)与星间激光通信（天基传送网）已成为公司布局卫星互联网的关键突破口，成功研发面向低轨卫星平台的高集成度、低功耗星上路由交换系统。</t>
+          <t>化工+机器人|1.公司主要从事二氧化硅和炭黑的研发、生产与销售，其中二氧化硅产品主要包括LK、LKHD及LKSIL系列橡胶工业用二氧化硅和非橡胶工业用二氧化硅。
+2.二氧化硅可用于制造人形机器人皮肤，公司正在积极开拓市场。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆, 商业航天</t>
+          <t>化工, 机器人</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>4.77</v>
+        <v>1.19</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>美国光通信技术公司AOI宣布，已收到一家长期主要超大规模客户的1.6T数据中心光收发器首批量产订单，金额逾2亿美元，标志着新一代高速光互联产品正式进入规模化商用阶段。</t>
+          <t>全球石油运输受阻，油价高位运行直接支撑化工品价格中枢。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sh688048</t>
+          <t>sh600328</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>长光华芯</t>
+          <t>中盐化工</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>188.4</v>
+        <v>9.94</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>20</v>
+        <v>9.959999999999999</v>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>光芯片|公司已形成全面、丰富的通信光芯片产品矩阵，可满足超大容量的数据通信需求，距离上覆盖VR、SR、DR、FR等，速率上覆盖单波25G、50G、100G。公司的100mW CW DFB产品可用于800G/1.6T等场景的光互联应用，且满足高速率的持续演进诉求。</t>
+          <t>化工|公司是一家集盐、盐化工、医药健康产品等生产及销售为一体的综合性企业，公司主营业务为以精制盐、工业盐等为代表的盐产品；以金属钠、氯酸钠为代表的精细化工产品；以纯碱为代表的基础化工产品；以苁蓉益肾颗粒、复方甘草片、维蜂盐藻等产品为代表的医药健康产品。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>光芯片</t>
+          <t>化工</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>5.29</v>
+        <v>1.19</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>日本化工巨头三菱瓦斯化学株式会社（MGC）宣布自4月1日起，将其电子材料部门旗下的核心产品——覆铜板（CCL）、预浸料（Prepreg）及背胶铜箔（CRS）的价格统一上调30%。</t>
+          <t>全球石油运输受阻，油价高位运行直接支撑化工品价格中枢。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sz002636</t>
+          <t>sz001369</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>金安国纪</t>
+          <t>双欣材料</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>27.87</v>
+        <v>16.94</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>电子玻纤布|金安国纪公告称，为保障原材料供应，保证公司长期平稳发展，公司全资子公司安徽金瑞计划投资不超过10,000万元建设年产6000万米电子级玻纤布扩建项目，预计2026年12月底前开始试生产。</t>
+          <t>化工|公司是一家专业从事聚乙烯醇（PVA）、特种纤维、醋酸乙烯（VAC）、碳化钙（电石）等PVA产业链上下游产品的研发、生产、销售的高新技术企业，拥有聚乙烯醇全产业链布局。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>电子玻纤布</t>
+          <t>化工</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>5.29</v>
+        <v>1.19</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>日本化工巨头三菱瓦斯化学株式会社（MGC）宣布自4月1日起，将其电子材料部门旗下的核心产品——覆铜板（CCL）、预浸料（Prepreg）及背胶铜箔（CRS）的价格统一上调30%。</t>
+          <t>全球石油运输受阻，油价高位运行直接支撑化工品价格中枢。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sh688655</t>
+          <t>sh600989</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">迅捷兴  </t>
+          <t>宝丰能源</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>29.4</v>
+        <v>31.85</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>20</v>
+        <v>10.02</v>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>PCB|公司产品和服务以“多品种、小批量、高层次、短交期”为特色，致力于满足客户产品生命周期各阶段的需求，业务涵盖样板、小批量板和大批量板，是行业内为数不多可以为客户提供从样板到批量生产一站式服务的PCB企业。</t>
+          <t>煤化工|公司打造了一个集“煤炭采选、焦化、甲醇、烯烃、精细化工、新能源”于一体的高端煤基新材料循环经济产业集群，包括：1、煤制烯烃，即以煤、焦炉气为原料生产甲醇，再以甲醇为原料生产聚乙烯、聚丙烯、EVA；2、焦化，即将原煤洗选为精煤，再用精煤进行炼焦生产焦炭；3、精细化工，以煤制烯烃、焦化副产品生产甲基叔丁基醚、焦化苯、工业萘、改质沥青、蒽油等精细化工产品。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>煤化工</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>5.29</v>
+        <v>1.19</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>日本化工巨头三菱瓦斯化学株式会社（MGC）宣布自4月1日起，将其电子材料部门旗下的核心产品——覆铜板（CCL）、预浸料（Prepreg）及背胶铜箔（CRS）的价格统一上调30%。</t>
+          <t>全球石油运输受阻，油价高位运行直接支撑化工品价格中枢。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sz001389</t>
+          <t>sz002092</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>广合科技</t>
+          <t>中泰化学</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>120.23</v>
+        <v>8.1</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>10</v>
+        <v>10.05</v>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>PCB+商业航天|公司主营业务是印制电路板的研发、生产和销售，公司5G产品广泛应用于通讯基站 、无线射频微波、有线局域网、通讯交换等领域。公司5.5G低轨卫星产品开始批量供货。</t>
+          <t>化工|公司拥有完整的煤炭—热电—氯碱化工—粘胶纤维—粘胶纱上下游一体化的循环经济产业链，主营聚氯乙烯树脂（PVC）、离子膜烧碱、粘胶纤维、粘胶纱等四大产品。公司本部现有150万吨PVC产能。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>PCB, 商业航天</t>
+          <t>化工</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>5.29</v>
+        <v>1.19</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>日本化工巨头三菱瓦斯化学株式会社（MGC）宣布自4月1日起，将其电子材料部门旗下的核心产品——覆铜板（CCL）、预浸料（Prepreg）及背胶铜箔（CRS）的价格统一上调30%。</t>
+          <t>全球石油运输受阻，油价高位运行直接支撑化工品价格中枢。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sz002384</t>
+          <t>sh600299</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t xml:space="preserve">安迪苏  </t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>108.06</v>
+        <v>14.61</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>10</v>
+        <v>10.02</v>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>PCB+光通信|1.公司成为上游供应商中为数不多的能为新能源汽车客户提供PCB（含FPC）、车载显示屏、功能性结构件等多种产品及综合解决方案的厂商，连续多年柔性线路板（FPC）排名全球第二，PCB排名全球第三。
-2.2025年6月14日公告，公司拟通过全资子公司超毅集团（香港）有限公司收购Source Photonics Holdings (Cayman)Limited（以下简称“索尔思光电”）100%股份。</t>
+          <t>化工|公司是全球少数几家能够同时生产液体和固体蛋氨酸的蛋氨酸生产商之一,并在中国和欧洲均拥有一体化生产平台；包括生产维生素A的法国Commentry工厂，生产固体蛋氨酸和中间体的法国LesRoches及Roussillon工厂以及生产液体蛋氨酸的西班牙Burgos工厂均产生积极影响。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>PCB, 光通信</t>
+          <t>化工</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>5.29</v>
+        <v>1.19</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>日本化工巨头三菱瓦斯化学株式会社（MGC）宣布自4月1日起，将其电子材料部门旗下的核心产品——覆铜板（CCL）、预浸料（Prepreg）及背胶铜箔（CRS）的价格统一上调30%。</t>
+          <t>全球石油运输受阻，油价高位运行直接支撑化工品价格中枢。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sz300936</t>
+          <t>sh600409</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>中英科技</t>
+          <t>三友化工</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>58.54</v>
+        <v>9.17</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>20.01</v>
+        <v>9.950000000000001</v>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>PCB+商业航天|1.公司产品高频覆铜板是制作印制电路板的核心材料，公司主要客户群体为印制电路板（PCB）制造厂商。
-2.公司ZYF-D型产品可应用于卫星导航等领域，公司产品ZYF-6000系列高频覆铜板可以应用于全球定位卫星天线、移动通信系统等领域。</t>
+          <t>化工|公司已由成立之初单一的纯碱生产企业发展成为拥有化纤、纯碱、氯碱、有机硅四大主业并配套热电、原盐、碱石、物流、国际贸易等循环经济体系的行业龙头企业。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>PCB, 商业航天</t>
+          <t>化工</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>液冷IDC</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>3.34</v>
+        <v>1.19</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>英伟达AI基础设施负责人Dion Harris在加州总部向媒体展示了下一代Vera Rubin算力系统的内部构成与供应链细节。由于功耗上升，Vera Rubin也是英伟达首个100%液冷散热的系统。</t>
+          <t>全球石油运输受阻，油价高位运行直接支撑化工品价格中枢。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sz001400</t>
+          <t>sh600873</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>江顺科技</t>
+          <t>梅花生物</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>146.04</v>
+        <v>12.62</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>3天2板</t>
-        </is>
-      </c>
+        <v>10.03</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>液冷+商业航天|1.子公司江宇科技主要从事用于服务器液冷相关的3D打印产品的研发工作，已有部分样品。
-2.公司产品铝型材挤压模具和铝型材挤压配套设备应用于航空航天领域。</t>
+          <t>化工|公司专注于氨基酸的规模化生产与创新应用。公司已构建起涵盖动物营养氨基酸（赖氨酸、苏氨酸、缬氨酸等系列产品）、食品鲜味剂（味精、呈味核苷酸二钠等鲜味剂）、医药级氨基酸（谷氨酰胺、脯氨酸等药用原料）、胶体多糖（黄原胶、海藻糖）以及大宗副产品（玉米胚芽、蛋白粉等）的完整产业生态。赖氨酸、苏氨酸产能规模稳居全球首位，味精产能位列全球第二。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>液冷, 商业航天</t>
+          <t>化工</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>液冷IDC</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>3.34</v>
+        <v>1.8</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>英伟达AI基础设施负责人Dion Harris在加州总部向媒体展示了下一代Vera Rubin算力系统的内部构成与供应链细节。由于功耗上升，Vera Rubin也是英伟达首个100%液冷散热的系统。</t>
+          <t>《数据中心绿色低碳发展专项行动计划》明确要求，国家枢纽节点新建数据中心绿电占比超过80%，绿电成为数据中心最直接的能源供给。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sh603269</t>
+          <t>sz002445</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>海鸥股份</t>
+          <t>中南文化</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>17.93</v>
+        <v>3.71</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>10</v>
+        <v>10.09</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3天2板</t>
+          <t>3天3板</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>数据中心温控|公司主要从事各类冷却塔的研发、设计、制造及安装业务，并依托自身产品和技术优势提供工业及民用冷却塔相关的技术服务。公司研制的冷却塔广泛应用于石化、冶金、电力等领域以及公共设施、商务建筑、数据中心等的中央空调系统。</t>
+          <t>并购+电力+油气|1.中南文化(002445.SZ)公告称，公司计划通过发行股份及支付现金的方式购买江阴电力投资有限公司持有的江阴苏龙热电有限公司57.30%股权，同时拟向不超过三十五名特定投资者募集配套资金。本次交易相关审计、评估工作尚未完成，交易方案需进一步论证和沟通协商。本次交易预计构成重大资产重组。本次交易完成后，上市公司在电力能源领域的业务布局将得到拓展。
+2.公司是目前国内规模较大的工业金属管件制造商，主要产品为管件、法兰、管系和压力容器，产品拥有国际多项生产商许可证书；其中，公司还拥有国家质检总局颁发的压力管道元件、压力容器等特种设备制造许可证，是中国石油天然气集团公司一级供应网络成员单位、中国石油能源一号网会员单位、中国石化资源市场成员厂组织集中采购成员厂。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>数据中心温控</t>
+          <t>并购, 电力, 油气</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>液冷IDC</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>3.34</v>
+        <v>1.8</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>英伟达AI基础设施负责人Dion Harris在加州总部向媒体展示了下一代Vera Rubin算力系统的内部构成与供应链细节。由于功耗上升，Vera Rubin也是英伟达首个100%液冷散热的系统。</t>
+          <t>《数据中心绿色低碳发展专项行动计划》明确要求，国家枢纽节点新建数据中心绿电占比超过80%，绿电成为数据中心最直接的能源供给。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sz002632</t>
+          <t>sz000537</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>道明光学</t>
+          <t>绿发电力</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>13.64</v>
+        <v>11.37</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
+        <v>9.959999999999999</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>折叠屏+液冷|1.子公司华威新材料目前拥有一种纳米银线防眩光导电膜和一种纳米银线防红外导电膜的实用新型专利。
-2.公司在2025年半年报中透露，公司以石墨烯超柔韧生产技术为依托，以新的产品形态和性能响应和开拓石墨烯产品在液冷服务器、AI眼镜等新应用场景下的热管理需求，目前样品已通过终端客户测试，且量产方案已在规划中。</t>
+          <t>电算协同|绿发电力在互动平台表示，作为“新能源+”融合发展的重要场景，电算协同一直是公司密切关注并重点布局的方向。目前公司正开展相关业务的对接和论证工作，若有重大进展将按规定履行内部决策和信息披露程序。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>折叠屏, 液冷</t>
+          <t>电算协同</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>液冷IDC</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>3.34</v>
+        <v>1.8</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>英伟达AI基础设施负责人Dion Harris在加州总部向媒体展示了下一代Vera Rubin算力系统的内部构成与供应链细节。由于功耗上升，Vera Rubin也是英伟达首个100%液冷散热的系统。</t>
+          <t>《数据中心绿色低碳发展专项行动计划》明确要求，国家枢纽节点新建数据中心绿电占比超过80%，绿电成为数据中心最直接的能源供给。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sz002536</t>
+          <t>sh600726</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>飞龙股份</t>
+          <t>华电能源</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>38.09</v>
+        <v>3.53</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
+        <v>9.969999999999999</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">服务器液冷|公司电子泵及温控阀系列产品可以应用在服务器液冷领域。
-</t>
+          <t>电力|公司是黑龙江省最大的发电及集中供热运营商，主要产品为电力、热力，火力电厂分布在黑龙江省主要中心城市。</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>服务器液冷</t>
+          <t>电力</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>商业航天</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>由中国运载火箭技术研究院研制的长征八号甲遥八运载火箭，在海南商业航天发射场成功实施转运，火箭箭体被顺利运至发射区一号发射工位，计划近期择期发射。</t>
+          <t>《数据中心绿色低碳发展专项行动计划》明确要求，国家枢纽节点新建数据中心绿电占比超过80%，绿电成为数据中心最直接的能源供给。</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sz002903</t>
+          <t>sh601330</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>宇环数控</t>
+          <t>绿色动力</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>30.37</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.99</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>机器人+商业航天|1.公司经营范围包括工业机器人及其关键功能部件、机械配件、金属材料的制造和销售。
-2.公司自主研发的高端复合立式磨床逐步进入航空航天市场，可用于加工航空航天领域的精密零部件及高性能材料。</t>
+          <t>绿电|公司是中国最早从事生活垃圾焚烧发电的企业之一，主要以BOT等特许经营的方式从事生活垃圾焚烧发电厂的投资、建设、运营、维护以及技术顾问业务。截至2024年12月31日，公司在生活垃圾焚烧发电领域运营项目37个，运营项目垃圾处理能力达4.03万吨/日，装机容量857MW，公司项目数量和垃圾处理能力均位居行业前列。</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>机器人, 商业航天</t>
+          <t>绿电</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>商业航天</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>由中国运载火箭技术研究院研制的长征八号甲遥八运载火箭，在海南商业航天发射场成功实施转运，火箭箭体被顺利运至发射区一号发射工位，计划近期择期发射。</t>
+          <t>《数据中心绿色低碳发展专项行动计划》明确要求，国家枢纽节点新建数据中心绿电占比超过80%，绿电成为数据中心最直接的能源供给。</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sh603017</t>
+          <t>sh601016</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>中衡设计</t>
+          <t>节能风电</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>13.48</v>
+        <v>4.03</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>10.04</v>
+        <v>10.11</v>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>商业航天|公司中标了天兵科技运载火箭及发动机智能制造 基地、山东箭元航天科技总装总测生产基地、星际荣耀火箭制造基地、安庆年发20发可回收液体火箭制造厂房建设项目等多个高端制造基地，积极为航空航天逐梦苍穹贡献中衡力量。</t>
+          <t>绿电|公司的主营业务为风力发电的项目开发、建设及运营。在加快风电场开发和建设的同时，加大中东部及南方区域市场开发力度，在湖北、广西、浙江、河南、四川等已有项目的区域开发后续项目，在贵州、安徽、湖南、广东、重庆、江西、山东等区域开展风电项目前期踏勘和测风工作，扩大资源储备。</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>商业航天</t>
+          <t>绿电</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>商业航天</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>由中国运载火箭技术研究院研制的长征八号甲遥八运载火箭，在海南商业航天发射场成功实施转运，火箭箭体被顺利运至发射区一号发射工位，计划近期择期发射。</t>
+          <t>《数据中心绿色低碳发展专项行动计划》明确要求，国家枢纽节点新建数据中心绿电占比超过80%，绿电成为数据中心最直接的能源供给。</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>sz002025</t>
+          <t>sz000899</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>航天电器</t>
+          <t>赣能股份</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>56.03</v>
+        <v>16.15</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>9.99</v>
+        <v>10.01</v>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>商业航天|公司连接器及电缆组件、电机、继电器和光模块等产品广泛应用于商业航天领域，先后承担并完成载人航天、探月、北斗、火星探测等国家重大工程和重大专项配套任务。</t>
+          <t>电力|公司主营业务为火力、水力发电，目前公司所属已投产运营火电厂一家、水电厂两家，总装机容量为150万千瓦。</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>商业航天</t>
+          <t>电力</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>商业航天</t>
+          <t>智能电网</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>2.7</v>
+        <v>0.03</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>由中国运载火箭技术研究院研制的长征八号甲遥八运载火箭，在海南商业航天发射场成功实施转运，火箭箭体被顺利运至发射区一号发射工位，计划近期择期发射。</t>
+          <t>正泰董事长南存辉在两会记者会提到，这两年全球AI算力建设爆发式增长，变压器变得一台难求。“去年我们变压器出口同比增长71.4%, 工厂订单都排到2027年了。”</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
@@ -1493,45 +1501,49 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>sz300629</t>
+          <t>sh603421</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>新劲刚</t>
+          <t>鼎信通讯</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>28.91</v>
+        <v>10.13</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>20.01</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr"/>
+        <v>9.99</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>并购+商业航天|1.新劲刚公告称，公司正在筹划收购湖南高至科技有限公司的控股权，预计将实现对标的公司的控股。标的公司主要聚焦特殊应用领域智能仿真信息系统、飞行器关键部组件的研发生产与销售，具备飞行器总体设计能力。
-2.子公司宽普科技、仁健微波聚焦特定专业领域的射频微波产品研发及配套服务，其产品线涵盖低轨卫星相关模块及终端等方向。</t>
+          <t>平头哥合作+电网|1.鼎信通讯在互动平台表示，公司芯片开发采用平头哥的CK802 32位内核架构，平头哥与公司签订有全面技术授权协议。
+2.公司的主营业务为低压用电系统产品的研发、生产、销售及服务，主要产品包括低压电力线载波通信模块（含芯片）产品、采集终端设备、智能电能表和配电终端等，主要应用于国家智能电网的用电信息采集系统和配网自动化系统。</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>并购, 商业航天</t>
+          <t>平头哥合作, 电网</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>智能电网</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>2.28</v>
+        <v>0.03</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>开源AI智能体OpenClaw持续火爆，该系统通过拆解任务、调用云端大模型API完成任务，一次任务可消耗数十万乃至数百万Token，算力需求呈指数级增长。</t>
+          <t>正泰董事长南存辉在两会记者会提到，这两年全球AI算力建设爆发式增长，变压器变得一台难求。“去年我们变压器出口同比增长71.4%, 工厂订单都排到2027年了。”</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
@@ -1539,48 +1551,48 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>sz002575</t>
+          <t>sh601868</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>群兴玩具</t>
+          <t>中国能建</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>8.82</v>
+        <v>3.45</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>9.98</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>4天2板</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>算力租赁|孙公司杭州图灵引擎科技有限公司与腾讯科技（深圳）有限公司签订算力服务协议，向腾讯提供集群算力服务。</t>
+          <t>电力基建|公司致力于建设“行业领先、世界一流”的能源一体化方案解决商，在能源电力勘察设计技术上处于引领地位。在能源电力领域产业政策和发展规划研究，百万千瓦级超超临界机组、三代核电常规岛、清洁燃煤发电、特高压交直流和GIL综合管廊输变电、柔性交直流输电、海上风电、太阳能热发电等勘察设计技术领域具有国际领先优势。</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>算力租赁</t>
+          <t>电力基建</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>智能电网</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>2.28</v>
+        <v>0.03</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>开源AI智能体OpenClaw持续火爆，该系统通过拆解任务、调用云端大模型API完成任务，一次任务可消耗数十万乃至数百万Token，算力需求呈指数级增长。</t>
+          <t>正泰董事长南存辉在两会记者会提到，这两年全球AI算力建设爆发式增长，变压器变得一台难求。“去年我们变压器出口同比增长71.4%, 工厂订单都排到2027年了。”</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
@@ -1588,45 +1600,44 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>sz002298</t>
+          <t>sh601700</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>中电鑫龙</t>
+          <t>风范股份</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>12.41</v>
+        <v>6.9</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>10.02</v>
+        <v>10.05</v>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>华为算力+电磁存储|1.公司与HUAWEI公司签订了战略合作协议，双方在智慧城市、大数据中心等领域进行合作，双方积极推动智慧城市、大数据中心等项目落地。
-2.公司在2022年半年报中透露，公司专用磁存储产品具备存储密度高、使用能耗低、数据安全高的特点，有望成为长期存储大规模冷数据的更优选择。</t>
+          <t>特高压+签订大单|风范股份公告称，公司在藏东南至粤港澳大湾区±800千伏特高压直流输电工程直流设备及线路材料第二批专项招标项目中中标，中标产品包括800kV直流钢管塔包1、800kV直流角钢塔包25和26，中标金额约为2.90亿元，约占公司2024年经审计营业收入的8.97%。</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>华为算力, 电磁存储</t>
+          <t>特高压, 签订大单</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>智能电网</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>2.28</v>
+        <v>0.03</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>开源AI智能体OpenClaw持续火爆，该系统通过拆解任务、调用云端大模型API完成任务，一次任务可消耗数十万乃至数百万Token，算力需求呈指数级增长。</t>
+          <t>正泰董事长南存辉在两会记者会提到，这两年全球AI算力建设爆发式增长，变压器变得一台难求。“去年我们变压器出口同比增长71.4%, 工厂订单都排到2027年了。”</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
@@ -1634,62 +1645,62 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>sz002467</t>
+          <t>sz002782</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>二六三</t>
+          <t>可立克</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>7.59</v>
+        <v>28.78</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>10</v>
+        <v>10.02</v>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>AI应用+算力|1.公司在WebRTC、QoS、实时音视频等核心技术基础上，深度融合AI与大模型能力，打造智能通信中枢。通过自研AICC人工智能客户联络中心，实现企业邮箱、视频直播等场景的端到端智能化交互。同时，研发投入持续向AI驱动的云通信解决方案倾斜，构建跨网络动态负载均衡与智能运维体系，支撑亿级并发场景下的服务稳定性。
-2.公司2020年4月22日在互动平台表示，公司的子公司上海二六三通信有限公司与NTT合资的控股子公司上海奈盛通信科技有限公司是国内第一家由民营通信公司与国际一流运营商合资经营的公司，其业务平台为国内第一个以国际运营商标准自建的IDC云计算平台。</t>
+          <t>储能+电网设备|1.公司在储能领域具备相应变压器、电感及其组合器件产品的自主开发、生产和销售能力，且在现有光伏客户端中被采用。
+2.公司主要从事电子变压器和电感等磁性元件以及电源适配器、动力电池充电器和定制电源等开关电源产品的开发、生产和销售。</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>AI应用, 算力</t>
+          <t>储能, 电网设备</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>储能</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>2.28</v>
+        <v>1.16</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>开源AI智能体OpenClaw持续火爆，该系统通过拆解任务、调用云端大模型API完成任务，一次任务可消耗数十万乃至数百万Token，算力需求呈指数级增长。</t>
+          <t>东吴证券表示，美国数据中心储能持续推动，欧洲、中东等项目大储需求旺盛，预计全球储能装机2026年60%以上增长，2027—2029年复合30%—50%增长。</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>sz002335</t>
+          <t>sz002150</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>科华数据</t>
+          <t>正泰电源</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>69.48</v>
+        <v>29.68</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>10.01</v>
@@ -1697,107 +1708,103 @@
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>算力+液冷|1.目前公司具备了丰富多元的智算产品体系，推出了AI裸金属、GPU服务器租赁、边缘计算、混合云、本地算力资源池、云上弹性算力等算力产品。
-2.公司液冷技术可以解决高功率、高热流密度、高计算密度的芯片和系统散热问题，大幅提升了算力输出能力，使服务器可以在相对的低温环境中满载运行，此项技术能够适用于各大智算中心。</t>
+          <t>储能+电网设备|1.旗下正泰电源是国内最早开始研发光伏逆变器的公司之一，业务范围涵盖光伏逆变器、光伏汇流箱、商用储能一体机、预装式光伏系统、预装式储能系统等。
+2.公司输配电控制设备业务主要产品包括高压成套开关设备、中低压成套开关设备、高低压开关元件及控制电器等，能够为下游各行业用户提供整体配电解决方案。</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>算力, 液冷</t>
+          <t>储能, 电网设备</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>储能</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>1.71</v>
+        <v>1.16</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3月9日，腾讯旗下全场景AI智能体WorkBuddy正式上线。此外，火山引擎正式上线ArkClaw，开箱即用的云上SaaS版OpenClaw。</t>
+          <t>东吴证券表示，美国数据中心储能持续推动，欧洲、中东等项目大储需求旺盛，预计全球储能装机2026年60%以上增长，2027—2029年复合30%—50%增长。</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>sh605268</t>
+          <t>sz301658</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>王力安防</t>
+          <t>首航新能</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>16.86</v>
+        <v>45.94</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>5天5板</t>
-        </is>
-      </c>
+        <v>20.01</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>智能经济|公司机器人安全门首创AI遥感解锁，AI智能防夹功能，实现与智能家居互联；自研AI电机驱动算法技术，实现自动开关门，搭载可视智慧猫眼，独创安全G点，关门自动反锁，独创超C级圆柱体专利锁芯。</t>
+          <t>储能|公司的储能电池主要为磷酸铁锂电池，能够适配多品牌光伏储能逆变器，主要应用于户用及小型工商业储能。公司光伏储能逆变器功率范围已涵盖3kW~20kW，适用于户用、小型工商业并离网储能多种场景。</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>智能经济</t>
+          <t>储能</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>储能</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>1.71</v>
+        <v>1.16</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>3月9日，腾讯旗下全场景AI智能体WorkBuddy正式上线。此外，火山引擎正式上线ArkClaw，开箱即用的云上SaaS版OpenClaw。</t>
+          <t>东吴证券表示，美国数据中心储能持续推动，欧洲、中东等项目大储需求旺盛，预计全球储能装机2026年60%以上增长，2027—2029年复合30%—50%增长。</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>sz000839</t>
+          <t>sh605117</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>国安股份</t>
+          <t>德业股份</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>3.62</v>
+        <v>131.88</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>10.03</v>
+        <v>10</v>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>AI审核|公司旗下子公司鸿联九五为企业提供一站式的审核服务体系。公司内容审核业务包括文本审核、图片审核、视频审核、音频审核、人工智能审核。</t>
+          <t>户储|公司拥有储能逆变器、组串式并网逆变器和微型并网逆变器12组系列产品。</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>AI审核</t>
+          <t>户储</t>
         </is>
       </c>
     </row>
@@ -1808,41 +1815,45 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>1.71</v>
+        <v>-0.65</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>3月9日，腾讯旗下全场景AI智能体WorkBuddy正式上线。此外，火山引擎正式上线ArkClaw，开箱即用的云上SaaS版OpenClaw。</t>
+          <t>全国多地下场“养龙虾”，常熟对“一人公司”最高拟予600万元支持；合肥高新区推出15条硬核举措，最高补贴1000万元；佛山一地推出面向公众的“小龙虾”免费部署服务。</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>sh605287</t>
+          <t>sz000839</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>德才股份</t>
+          <t>国安股份</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>51.54</v>
+        <v>3.98</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
+        <v>9.94</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>AI漫剧|旗下奇想无限深耕“网文IP+AI漫剧”转化，与头部网文平台合作，将玄幻、甜宠等成熟IP快速落地，已产出多部爆款。</t>
+          <t>AI安全|公司旗下子公司鸿联九五为企业提供一站式的审核服务体系。公司内容审核业务包括文本审核、图片审核、视频审核、音频审核、人工智能审核。</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>AI漫剧</t>
+          <t>AI安全</t>
         </is>
       </c>
     </row>
@@ -1853,36 +1864,36 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>1.71</v>
+        <v>-0.65</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>3月9日，腾讯旗下全场景AI智能体WorkBuddy正式上线。此外，火山引擎正式上线ArkClaw，开箱即用的云上SaaS版OpenClaw。</t>
+          <t>全国多地下场“养龙虾”，常熟对“一人公司”最高拟予600万元支持；合肥高新区推出15条硬核举措，最高补贴1000万元；佛山一地推出面向公众的“小龙虾”免费部署服务。</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>sh605318</t>
+          <t>sh601858</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">法狮龙  </t>
+          <t>中国科传</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>76.84</v>
+        <v>21.67</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>AI应用|10月23日，据法狮龙发布公告，公司计划投资设立的全资子公司北宸星穹已完成工商登记手续，并于2025年10月23日取得了由北京市东城区市场监督管理局核发的《营业执照》。北宸星穹经营范围包括人工智能应用软件开发；人工智能行业应用系统集成服务；人工智能基础软件开发等。</t>
+          <t>AI应用|公司自主研发的SciEngine全流程数字出版与知识服务平台（V3.0）进一步集成了学术查重检测、审稿专家自动推荐、自动在线校对、科大讯飞智能翻译、AI秒读视频、文献挖掘和语义检索等多种工具，进一步提升了出版运营与知识服务能力。</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1894,336 +1905,340 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0.49</v>
+        <v>-0.65</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>招商证券研报称，2026年全国两会将“算电协同”纳入超大规模新基建工程。政策端的强力催化叠加绿电直连项目规模化落地、全国统一电力市场体系加速构建，算电协同正从政策规划走向产业实践。</t>
+          <t>全国多地下场“养龙虾”，常熟对“一人公司”最高拟予600万元支持；合肥高新区推出15条硬核举措，最高补贴1000万元；佛山一地推出面向公众的“小龙虾”免费部署服务。</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>sz002445</t>
+          <t>sz300246</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>中南文化</t>
+          <t>宝莱特</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>3.37</v>
+        <v>16.8</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>10.13</v>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>并购+电力+油气|1.中南文化(002445.SZ)公告称，公司计划通过发行股份及支付现金的方式购买江阴电力投资有限公司持有的江阴苏龙热电有限公司57.30%股权，同时拟向不超过三十五名特定投资者募集配套资金。本次交易相关审计、评估工作尚未完成，交易方案需进一步论证和沟通协商。本次交易预计构成重大资产重组。本次交易完成后，上市公司在电力能源领域的业务布局将得到拓展。
-2.公司是目前国内规模较大的工业金属管件制造商，主要产品为管件、法兰、管系和压力容器，产品拥有国际多项生产商许可证书；其中，公司还拥有国家质检总局颁发的压力管道元件、压力容器等特种设备制造许可证，是中国石油天然气集团公司一级供应网络成员单位、中国石油能源一号网会员单位、中国石化资源市场成员厂组织集中采购成员厂。</t>
+          <t>AI医疗|公司“基于AI的S系列重症监护仪设计”是基于AI语音识别技术，在监护设备上实现语音交互，无需繁杂的手动操作，释放医护人员双手；同时基于大数据，可实现心电导联自动切换，实现重点导联自动监测；智能的光线传感器实现背光亮度自动调节，可提高医护人员操作效率。</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>并购, 电力, 油气</t>
+          <t>AI医疗</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>固态电池</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>0.49</v>
+        <v>1.71</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>招商证券研报称，2026年全国两会将“算电协同”纳入超大规模新基建工程。政策端的强力催化叠加绿电直连项目规模化落地、全国统一电力市场体系加速构建，算电协同正从政策规划走向产业实践。</t>
+          <t>中金公司研报称，固态电池产业化进展持续推进，头部电池厂商固态电池设备及传统锂电设备招标或逐步启动。</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>sz000537</t>
+          <t>sh603778</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>绿发电力</t>
+          <t>国晟科技</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>10.34</v>
+        <v>20.82</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
+        <v>9.98</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>电算协同|绿发电力在互动平台表示，作为“新能源+”融合发展的重要场景，电算协同一直是公司密切关注并重点布局的方向。目前公司正开展相关业务的对接和论证工作，若有重大进展将按规定履行内部决策和信息披露程序。</t>
+          <t>光伏+固态电池|1.国晟科技公告称，公司拟以2.406亿元的价格受让正豪科技、林琴合计持有的孚悦科技100%股权。交易完成后，公司将持有标的公司100%股权，标的公司将纳入公司合并报表。孚悦科技主要从事高精密度新型锂电池结构件的研发、生产和销售。
+2.子公司安徽国晟新能源科技有限公司拟以2.3亿元向国晟环球新能源（铁岭）有限公司进行增资，持股51.11%。铁岭环球拟投资的年产10GWh固态电池产业链AI智能制造项目已取得项目备案手续；并且铁岭环球已取得电池回收及固态电池生产制备所需的知识产权许可使用授权。</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>电算协同</t>
+          <t>光伏, 固态电池</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>固态电池</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>0.49</v>
+        <v>1.71</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>招商证券研报称，2026年全国两会将“算电协同”纳入超大规模新基建工程。政策端的强力催化叠加绿电直连项目规模化落地、全国统一电力市场体系加速构建，算电协同正从政策规划走向产业实践。</t>
+          <t>中金公司研报称，固态电池产业化进展持续推进，头部电池厂商固态电池设备及传统锂电设备招标或逐步启动。</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>sh600726</t>
+          <t>sz002733</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>华电能源</t>
+          <t>雄韬股份</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>3.21</v>
+        <v>27.05</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>9.93</v>
+        <v>10</v>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>电力|经过近年来的不断优化转型，公司的主营业务已从单纯的发电、供热有效拓展为集发电、供热、煤炭、工程板块"四位一体"的产业格局，公司已成为黑龙江省最大的发电及集中供热运营商。</t>
+          <t>固态电池+IDC电源|1.公司固态电池产品是通过“原位聚合固态电解质技术”和“电极内部电解质动态成膜固化技术”两大核心技术的突破，彻底消除电池热失控风险，并解决“固-固”界面难题，完美适配数据中心、储能电站、轨道交通等对安全性有严苛要求的领域。
+2.公司主要为数据中心及算力中心提供UPS电池。</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>固态电池, IDC电源</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>招商证券研报称，2026年全国两会将“算电协同”纳入超大规模新基建工程。政策端的强力催化叠加绿电直连项目规模化落地、全国统一电力市场体系加速构建，算电协同正从政策规划走向产业实践。</t>
+          <t>据开源证券，截至3月4日，G.652.D单模光纤价格由元旦前的18元/公里上涨至现价85~120元/公里，涨幅近650%；G.657.A1单模光纤价格由23元/公里涨至115~135元/公里，涨幅近487%。</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>sh601778</t>
+          <t>sh603803</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>晶科科技</t>
+          <t>瑞斯康达</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>5.61</v>
+        <v>12.1</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">绿电|公司主营业务主要包括光伏电站运营、光伏电站转让和光伏电站EPC等，涉及太阳能光伏电站的开发、投资、建设、运营和管理、转让等环节，以及光伏电站EPC工程总承包、电站运营综合服务解决方案等。光伏电站运营业务为公司成立至今的核心业务，公司开发的光伏电站项目包括领跑者光伏电站、普通地面电站、屋顶分布式光伏电站等多种类型。
-</t>
+          <t>光模块|在高端光模块领域，公司联营企业易锐光电是中国少数产业链上下游关键层面具备完整核心技术和解决方案的高科技企业，新一代基于自主知识产权的25G/100G/超100G集成光收发芯片的光通信模块及光组件，用于电信网络城域网和大型数据中心网络。</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>绿电</t>
+          <t>光模块</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>2.53</v>
+        <v>0.51</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>国家发改委主任郑栅洁在记者会上表示，将重点打造六大新兴支柱产业和六大未来产业。六大新兴支柱产业其中包括智能机器人，相关产值在2025年已经接近6万亿元。</t>
+          <t>据开源证券，截至3月4日，G.652.D单模光纤价格由元旦前的18元/公里上涨至现价85~120元/公里，涨幅近650%；G.657.A1单模光纤价格由23元/公里涨至115~135元/公里，涨幅近487%。</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sh603949</t>
+          <t>sz300504</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>雪龙集团</t>
+          <t>天邑股份</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>19.49</v>
+        <v>19.32</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>9.99</v>
+        <v>20</v>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>参股宇树|公司作为有限合伙人通过深创投中小企业发展基金（新疆）有限合伙企业间接持股杭州宇树科技有限公司。目前，深创投中小企业发展基金（新疆）有限合伙企业对杭州宇树科技有限公司的持股比例为1.3546%；公司对深创投中小企业发展基金（新疆）有限合伙企业的持股比例为0.7239%。</t>
+          <t>光纤光缆|公司“通信网络物理连接与保护设备”业务板块主要产品包括光纤快速活动连接器、分路器、光缆接头盒、光缆交接箱、光缆分纤箱、光缆终端盒等。</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>参股宇树</t>
+          <t>光纤光缆</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>工业母机</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>2.53</v>
+        <v>0.47</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>国家发改委主任郑栅洁在记者会上表示，将重点打造六大新兴支柱产业和六大未来产业。六大新兴支柱产业其中包括智能机器人，相关产值在2025年已经接近6万亿元。</t>
+          <t>2026年开年以来，国内机床企业订单增长显著。有企业负责人表示，自今年初以来，来自人形机器人、新能源汽车等领域的订单大幅增加，已排至9月份。</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sh600376</t>
+          <t>sz002175</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>首开股份</t>
+          <t>东方智造</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>5.53</v>
+        <v>3.53</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>9.94</v>
+        <v>9.969999999999999</v>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>参股宇树|公司旗下首开盈信通过金石成长股权投资（杭州）合伙企业间接投资宇树科技。</t>
+          <t>工业母机|公司在2022年半年报中透露，公司主要产品为电子数显量具，目前是我国生产测量范围在500mm以上非标电子数显量具量仪的最主要厂家，数量量具主要作为数控机床的辅助工具。</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>参股宇树</t>
+          <t>工业母机</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>工业母机</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>2.53</v>
+        <v>0.47</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>国家发改委主任郑栅洁在记者会上表示，将重点打造六大新兴支柱产业和六大未来产业。六大新兴支柱产业其中包括智能机器人，相关产值在2025年已经接近6万亿元。</t>
+          <t>2026年开年以来，国内机床企业订单增长显著。有企业负责人表示，自今年初以来，来自人形机器人、新能源汽车等领域的订单大幅增加，已排至9月份。</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sz003021</t>
+          <t>sz002248</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>兆威机电</t>
+          <t>华东数控</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>124.38</v>
+        <v>15.58</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>10</v>
+        <v>10.03</v>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司的微型传动、微型驱动系统产品,具有高精度运动控制、高扭矩输出和紧凑体积等特性。基于对精密减速箱、高性能电机和电控系统的产品组合,结合自身的技术优势、产品特点,公司聚焦手指等运动执行应用部位,开发仿生机器人灵巧手产品,该产品与公司的技术能力相契合,系公司未来平台化产品的重点布局。</t>
+          <t>工业母机|公司是中国机床行业生产、销售数控龙门导轨磨床数量最多、规模最大的机床制造企业，以研发和生产经营数控机床、普通机床及其关键功能部件为主营业务，产品有数控龙门铣床（龙门加工中心）、数控龙门磨床、数控外圆磨床、万能摇臂铣床、平面磨床、动静压主轴等机床和功能部件产品。</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>工业母机</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>液冷IDC</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>2.96</v>
+        <v>0.36</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>电子元件供应链人士透露，德州仪器（TI）从4月1日起提高部分半导体产品的价格。一些分销商表示，价格上涨幅度可能在15%到85%之间。</t>
+          <t>2026年GTC大会，是英伟达公司于3月16日至19日在美国加州圣何塞举办的AI大会，大会主题聚焦于人工智能与新一代AI基础设施。</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
@@ -2231,44 +2246,48 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>sz002290</t>
+          <t>sh603158</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>禾盛新材</t>
+          <t>腾龙股份</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>67.20999999999999</v>
+        <v>12.25</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I38" s="2" t="inlineStr"/>
+        <v>9.959999999999999</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>算力芯片|2025年6月11日公告，公司拟以自有资金或自筹资金2.5亿元向熠知电子增资，增资后预计持有熠知电子10%股权。熠知电子系国内少数已商业落地ARM服务器处理器芯片公司，熠知TF7000系列实测性能达到国内先进水平，可同时覆盖人工智能、云计算、边缘计算多场景。熠知电子则是国产化CPU领域的核心企业之一，拥有先进的ARM架构，产品应用于多个行业，设计融合一流AI算法和先进制程工艺的智能芯片，并且以此构建人工智能硬件平台，提供行业应用解决方案。</t>
+          <t>服务器液冷|公司电子水泵产品有向客户供货，间接应用于数据中心/服务器液冷领域。</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>算力芯片</t>
+          <t>服务器液冷</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>液冷IDC</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>2.96</v>
+        <v>0.36</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>电子元件供应链人士透露，德州仪器（TI）从4月1日起提高部分半导体产品的价格。一些分销商表示，价格上涨幅度可能在15%到85%之间。</t>
+          <t>2026年GTC大会，是英伟达公司于3月16日至19日在美国加州圣何塞举办的AI大会，大会主题聚焦于人工智能与新一代AI基础设施。</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
@@ -2276,307 +2295,286 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>sh688300</t>
+          <t>sh603757</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>联瑞新材</t>
+          <t>大元泵业</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>99.95999999999999</v>
+        <v>47.43</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>半导体材料|公司持续聚焦芯片先进封装、新一代高频高速覆铜板、新能源汽车动力电池模组和光伏电池胶黏剂等领域，应用于异构集成技术封装、底部填充材料（Underfill）的亚微米级球形硅微粉、应用于存储芯片封装的Lowα微米级球形硅微粉和Lowα亚微米级球形硅微粉等高尖端应用的系列化产品已通过海内外客户的认证并批量出货，液态填料已小批量出货。</t>
+          <t>IDC温控|公司高压电子水泵及相关屏蔽泵产品能够应用在IDC温控领域，下游客户包括维谛技术、英维克、中兴通讯、曙光数创、同飞股份等。</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>半导体材料</t>
+          <t>IDC温控</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>发电机概念</t>
+          <t>MLED</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>1.54</v>
+        <v>0.96</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>中信建投证券研报指出，AIDC建设进入高速增长期，测算2025-2028年美国AI需求带来的电力容量需求期间CAGR约55%，未来三年累计需求超150GW，配套设备迎来机遇。</t>
+          <t>根据TrendForce集邦咨询最新调查，Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>sz002760</t>
+          <t>sh603773</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>凤形股份</t>
+          <t>沃格光电</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>25.23</v>
+        <v>43.36</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>9.98</v>
+        <v>9.99</v>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>特种电机|子公司康富科技主要产品为船电系统解决方案及特种电机，船电系统解决方案主要应用于船电装备领域，特种电机主要应用于军用、轨道交通、核电及数据中心等市场。</t>
+          <t>MLED|公司目前玻璃线路板（GCP）及玻璃基封装载板相关产品主要聚焦在Mini/Micro LED显示、5G-A/6G射频天线、光模块/CPO以及大算力芯片先进封装、生物芯片等领域。</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>特种电机</t>
+          <t>MLED</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>发电机概念</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>1.54</v>
+        <v>0.24</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>中信建投证券研报指出，AIDC建设进入高速增长期，测算2025-2028年美国AI需求带来的电力容量需求期间CAGR约55%，未来三年累计需求超150GW，配套设备迎来机遇。</t>
+          <t>中信建投研报指出，受益AI推动，全球PCB行业迎来新一轮上行周期。</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>sz300257</t>
+          <t>sh603936</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>开山股份</t>
+          <t>博敏电子</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>34.33</v>
+        <v>15.42</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>19.99</v>
+        <v>9.99</v>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>发电机+电力|1.公司既有蒸汽膨胀发电机，应用于高温蒸汽发电；又有ORC（有机朗肯循环）膨胀发电机，应用于乏汽和热水发电。
-2.2016年4月，公司全资收购OTP公司，获得印尼SMGP240MW地热项目的特许开发经营权，并采取“边投资、边建设、边运营、边收益”的商业模式。2019年9月28日，第一期（126MW）首批45MW实现并网发电。</t>
+          <t>PCB+HBM|1.公司专业从事高精密印制电路板的研发、生产和销售，主要产品为多层（含HDI）和单/双面印制电路板。
+2.公司当前存储类IC载板产品主要来源于江苏博敏二期设立的IC封装载板产品线，达产后产能约1万平米/月，该产品线涵盖Memory、RF、WB-BOC、PBGA、WBCSP、FCCSP等，产品主要应用于数据存储、微机电控制、光电显示和无线射频等领域。HBM和新型SRAM产品是公司IC载板业务未来主要发展方向之一，也是后续合肥扩产项目的主力产品之一。</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>发电机, 电力</t>
+          <t>PCB, HBM</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>正泰董事长南存辉在两会记者会提到，这两年全球AI算力建设爆发式增长，变压器变得一台难求。“去年我们变压器出口同比增长71.4%, 工厂订单都排到2027年了。”</t>
-        </is>
-      </c>
+        <v>0.76</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr"/>
       <c r="D42" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>sh603421</t>
+          <t>sz000711</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>鼎信通讯</t>
+          <t>ST京蓝</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>9.210000000000001</v>
+        <v>4.43</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>10.04</v>
-      </c>
-      <c r="I42" s="2" t="inlineStr"/>
+        <v>4.98</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>27天18板</t>
+        </is>
+      </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>半导体+电网设备|1.鼎信通讯在互动平台表示，公司芯片开发采用平头哥的CK802 32位内核架构，平头哥与公司签订有全面技术授权协议。
-2.公司的主营业务为低压用电系统产品的研发、生产、销售及服务，主要产品包括低压电力线载波通信模块（含芯片）产品、采集终端设备、智能电能表和配电终端等，主要应用于国家智能电网的用电信息采集系统和配网自动化系统。</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>半导体, 电网设备</t>
-        </is>
-      </c>
+          <t>ST股 | 主要业务包括流域水生态修复、灌区节水综合系统工程、污水治理、沿河生态景观工程、智慧水务等。</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>正泰董事长南存辉在两会记者会提到，这两年全球AI算力建设爆发式增长，变压器变得一台难求。“去年我们变压器出口同比增长71.4%, 工厂订单都排到2027年了。”</t>
-        </is>
-      </c>
+        <v>0.76</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr"/>
       <c r="D43" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>sz002350</t>
+          <t>sh600753</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>北京科锐</t>
+          <t xml:space="preserve">*ST海钦 </t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>15.22</v>
+        <v>11.93</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>9.969999999999999</v>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
+        <v>5.02</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>电网设备|公司是技术导向型配电设备制造企业，主营业务为12kV及以下配电及控制设备的研发、生产与销售。公司成立30年以来，专注于配电系统技术进步，崇尚技术创新，曾率先推出智能节电器、故障指示器、美式箱变、户外环网柜、永磁机构真空开关、GRC环保箱体和高过载变压器等新技术或产品。</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>电网设备</t>
-        </is>
-      </c>
+          <t>ST股 | 公司目前的主营业务为煤炭（含焦炭）、天然气等大宗商品供应链管理业务。</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>折叠屏</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>苹果下半年将发表首款折叠机iPhone Fold，供应链消息称，苹果内部对新机销售量非常有信心，大幅调高供应链备货量，比原定目标上调两成。</t>
-        </is>
-      </c>
+        <v>0.76</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>sh600135</t>
+          <t>sz002528</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>乐凯胶片</t>
+          <t>ST英飞拓</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>11.06</v>
+        <v>3.53</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>10.05</v>
+        <v>5.06</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>4天3板</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>折叠屏|在超细银粉、导电银浆等材料方面技术领先，乐凯集团去年底在珠海航展上展示了自主研发的用于柔性屏的纳米银线导电膜。</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>折叠屏</t>
-        </is>
-      </c>
+          <t>ST股 | 英飞拓推出5G多功能智慧灯杆，支持节能照明、视频监控、新能源充电、公共WIFI、环境监测、信息发布、应急报警、5G微基站等模块，实现多种类型的感知数据采集、分析、仿真预测，提升城市综合治理。</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>2026年1-2月中国创新药BD交易总额达532.76亿美元，交易数量达44项，开年仅两个月的交易金额超过2025年任一单季度，并与2024年全年水平接近。</t>
-        </is>
-      </c>
+        <v>0.76</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>sz002294</t>
+          <t>sz000908</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>信立泰</t>
+          <t>*ST景峰</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>54.01</v>
+        <v>4.58</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I45" s="2" t="inlineStr"/>
+        <v>5.050000000000001</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>5天3板</t>
+        </is>
+      </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>创新药|公司抗心衰创新药S086、生物药“重组胰高血糖素样肽-1-Fc  融合蛋白注射液”申报临床已获得临床批件（二季度CDE受理，三季度获得批件）；甲磺酸伊马替尼、奥美沙坦酯、盐酸莫西沙星等项目申报生产获CDE  受理，目前分处于不同的审评阶段。</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>创新药</t>
-        </is>
-      </c>
+          <t>ST股 | 公司专注医药健康产业，涉足药品研发、生产、销售等领域，产品涵盖了心脑血管、抗肿瘤、骨科、妇儿等用药领域。</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2585,36 +2583,36 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>1.58</v>
+        <v>0.76</v>
       </c>
       <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>sz000711</t>
+          <t>sz000004</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>ST京蓝</t>
+          <t>*ST国华</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>4.22</v>
+        <v>5.59</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>4.98</v>
+        <v>5.08</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>26天17板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 主要业务包括流域水生态修复、灌区节水综合系统工程、污水治理、沿河生态景观工程、智慧水务等。</t>
+          <t>ST股 | 公司旗下全资子公司智游网安为专业移动应用安全综合服务提供商。</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
@@ -2626,36 +2624,36 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>1.58</v>
+        <v>0.76</v>
       </c>
       <c r="C47" s="2" t="inlineStr"/>
       <c r="D47" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>sz000488</t>
+          <t>sh600599</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>ST晨鸣</t>
+          <t xml:space="preserve">*ST熊猫 </t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>2.73</v>
+        <v>4.62</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>5</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>3天3板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司是全国唯一一家实现制浆和造纸平衡的大型浆纸一体化企业，率先布局全产业链，在山东、广东、湖北、江西、吉林等地建有6个生产基地，年浆纸产能达1100多万吨。</t>
+          <t>ST股 | 公司地处中国烟花之乡浏阳，经过3多年的发展已成为中国最大的出口鞭炮烟花公司</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
@@ -2667,27 +2665,27 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>1.58</v>
+        <v>0.76</v>
       </c>
       <c r="C48" s="2" t="inlineStr"/>
       <c r="D48" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>sh600568</t>
+          <t>sz000669</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST中珠  </t>
+          <t>ST金鸿</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>3.17</v>
+        <v>4.41</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>4.97</v>
+        <v>5</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
@@ -2696,7 +2694,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 以眼科领域的专用药品为主，主要有珍珠明目滴眼液、阿昔洛韦滴眼液等。</t>
+          <t>ST股 | 主营气源开发与输送、长输管网建设与管理、城市燃气经营与销售、车用加气站投资与运营、LNG点供、分布式能源项目开发与建设等。</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr"/>
@@ -2708,36 +2706,36 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>1.58</v>
+        <v>0.76</v>
       </c>
       <c r="C49" s="2" t="inlineStr"/>
       <c r="D49" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>sh600753</t>
+          <t>sz000609</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST海钦 </t>
+          <t>ST中迪</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>11.36</v>
+        <v>9.98</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>4.99</v>
+        <v>5.050000000000001</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>4天2板</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司目前的主营业务为煤炭（含焦炭）、天然气等大宗商品供应链管理业务。</t>
+          <t>ST股 | 公司房地产项目位于重庆、成都、达州，重庆的“两江中迪广场”主要为商业项目。</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr"/>
@@ -2749,36 +2747,32 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>1.58</v>
+        <v>0.76</v>
       </c>
       <c r="C50" s="2" t="inlineStr"/>
       <c r="D50" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>sz000504</t>
+          <t>sh603843</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>*ST生物</t>
+          <t xml:space="preserve">*ST正平 </t>
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>9.960000000000001</v>
+        <v>6.08</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>5.01</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司是目前国内一家国资控股的干细胞、免疫细胞及组织工程产业主板上市公司，“生物医药”板块业务包括干细胞储存服务、化妆品的生产和销售、医疗器械设备及耗材的代理和销售。</t>
+          <t>ST股 | 2025年2月21日公司官微披露，旗下正平智算参加海东市绿色算力产业集中签约暨推介活动并签订算电协同产业园框架协议。</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
@@ -2790,36 +2784,32 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>1.58</v>
+        <v>0.76</v>
       </c>
       <c r="C51" s="2" t="inlineStr"/>
       <c r="D51" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>sz002592</t>
+          <t>sz002656</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>ST八菱</t>
+          <t>*ST摩登</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>10.25</v>
+        <v>3.05</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>5.17</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司配套氢燃料电池客车的产品技术目前已经形成商业化，广泛应用于燃气客车、混合动力客车和军车等领域。</t>
+          <t>ST股 | 卡奴迪路(CANUDILO)品牌已成为国内较具影响力和知名度的高级男装服饰品牌之一。</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
@@ -2831,32 +2821,32 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>1.58</v>
+        <v>0.76</v>
       </c>
       <c r="C52" s="2" t="inlineStr"/>
       <c r="D52" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>sh600599</t>
+          <t>sz000608</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST熊猫 </t>
+          <t>*ST阳光</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>4.4</v>
+        <v>3.63</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>5.01</v>
+        <v>4.91</v>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司地处中国烟花之乡浏阳，经过3多年的发展已成为中国最大的出口鞭炮烟花公司</t>
+          <t>ST股 | 公司投资性房地产主要位于京沪蓉。业态上主要为集中商业和办公。</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr"/>
@@ -2868,32 +2858,33 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>1.58</v>
+        <v>0.76</v>
       </c>
       <c r="C53" s="2" t="inlineStr"/>
       <c r="D53" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>sz000004</t>
+          <t>sh600696</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>*ST国华</t>
+          <t xml:space="preserve">*ST岩石 </t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>5.32</v>
+        <v>1.89</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>4.93</v>
+        <v>5</v>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司旗下全资子公司智游网安为专业移动应用安全综合服务提供商。</t>
+          <t>ST股 | 1.公司主要从事商业保理、融资租赁、不动产运营管理和大宗商品贸易。
+2.公司持有江西章贡酒业有限责任公司25%股权。章贡酒业是全国白酒工业百强企业，江西省重点酿酒企业。</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
@@ -2905,32 +2896,32 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>1.58</v>
+        <v>0.76</v>
       </c>
       <c r="C54" s="2" t="inlineStr"/>
       <c r="D54" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>sz002485</t>
+          <t>sh600608</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>ST雪发</t>
+          <t xml:space="preserve">*ST沪科 </t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>5.46</v>
+        <v>3.18</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司文旅项目地处一线旅游目的地黄金地段，历史文化底蕴深厚，旅游资源丰富，市场潜力较大。</t>
+          <t>ST股 | 公司是一家信息技术行业公司，主要业务分为钢材制品加工制造及商品贸易业务两大板块。</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
@@ -2942,32 +2933,32 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>1.58</v>
+        <v>0.76</v>
       </c>
       <c r="C55" s="2" t="inlineStr"/>
       <c r="D55" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>sh603557</t>
+          <t>sh600355</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST起步  </t>
+          <t xml:space="preserve">*ST精伦 </t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>3.64</v>
+        <v>1.01</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>4.9</v>
+        <v>5.21</v>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 国内童鞋龙头。旗下 ABC KIDS 占据我国童鞋第一、童装第七的市场地位。</t>
+          <t>ST股 | 公司智能控制产品是公司全资子公司上海鲍麦克斯电子科技有限公司的主营产品，鲍麦克斯专业从事通用及专用伺服驱动系统、数控系统、 缝制机器人的系列化产品研发及销售。</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
@@ -2975,187 +2966,239 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="n">
-        <v>1.58</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C56" s="2" t="inlineStr"/>
       <c r="D56" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>sz001270</t>
+          <t>sh600108</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>*ST铖昌</t>
+          <t>亚盛集团</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>121.19</v>
+        <v>6.57</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I56" s="2" t="inlineStr"/>
+        <v>10.05</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>9天7板</t>
+        </is>
+      </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司主营业务为微波毫米波模拟相控阵T/R芯片的研发、生产、销售和技术服务，产品已应用于探测、遥感、通信、导航、电子对抗等领域。</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr"/>
+          <t>农业种植|1.公司2026年3月2日公告，目前未开展矿产相关业务，也不存在需要披露的相关重大信息。
+2.公司主要种植经营啤酒花、马铃薯、牧草、果品、药材、食葵、辣椒、枸杞、香辛料等初级农产品和加工产品，以及生产经营节水灌溉设备。</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>农业种植</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="n">
-        <v>1.58</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C57" s="2" t="inlineStr"/>
       <c r="D57" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>sz000669</t>
+          <t>sh601789</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>ST金鸿</t>
+          <t>宁波建工</t>
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>4.2</v>
+        <v>7.3</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I57" s="2" t="inlineStr"/>
+        <v>9.94</v>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>4天4板</t>
+        </is>
+      </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 主营气源开发与输送、长输管网建设与管理、城市燃气经营与销售、车用加气站投资与运营、LNG点供、分布式能源项目开发与建设等。</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr"/>
+          <t>机柜位出租|宁波建工2026年3月10日公告称，目前公司及中经云均不从事算力租赁业务，中经云主营业务仅为机柜位出租（用于放置服务器、网络设备等IT硬件设施的标准化位置）。</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>机柜位出租</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="n">
-        <v>1.58</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C58" s="2" t="inlineStr"/>
       <c r="D58" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>sh600421</t>
+          <t>sh600769</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST华嵘 </t>
+          <t>祥龙电业</t>
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>7.72</v>
+        <v>15.02</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>5.029999999999999</v>
-      </c>
-      <c r="I58" s="2" t="inlineStr"/>
+        <v>10.04</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司实控人是中天控股集团下属浙江恒顺投资，集团旗下中天氟硅2023年撤回ipo，原计划通过IPO募集14.42亿元资金，用于30万吨/年有机硅单体扩能技改及综合利用项目。</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr"/>
+          <t>供水|公司的最终控制人为武汉东湖新技术开发区管理委员会。公司的主要业务为供水业务和建筑业务。</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>供水</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="n">
-        <v>1.58</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C59" s="2" t="inlineStr"/>
       <c r="D59" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>sz002898</t>
+          <t>sh600172</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>*ST赛隆</t>
+          <t>黄河旋风</t>
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>11.45</v>
+        <v>11.09</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>5.050000000000001</v>
-      </c>
-      <c r="I59" s="2" t="inlineStr"/>
+        <v>10.02</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司已建成集医药中间体、原料药、制剂的研发、生产、营销和技术服务为一体的医药全产业链的现代化制药企业。</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr"/>
+          <t>金刚石|公司作为超硬材料行业龙头以及唯一的全产业链布局企业，主要产品包括培育钻石及工业金刚石两大产品体系，覆盖工业金刚石、培育钻石、砂轮、刀具、钻头、锯片等，是国内乃至全球范围内品类别齐全、链条完整的超硬材料及制品制造商，可以向客户提供产品类别、规格齐全以及性能稳定的各类超硬材料及制品，包括超硬材料单晶及制品、立方氮化硼及制品、金刚石聚晶及制品以及超硬材料制品辅助材料。</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>金刚石</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="n">
-        <v>1.58</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>sz002789</t>
+          <t>sz002667</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>*ST建艺</t>
+          <t>威领股份</t>
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>10.32</v>
+        <v>33.01</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="I60" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司是集施工、设计、资源矿产、科技工业园、高新技术建材产业、投融资为一体的规模化实体企业集团。</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr"/>
+          <t>锂矿+有色金属|1.公司主要以新能源锂电材料产业链为主体，包括锂矿选矿、基础性锂电原料锂盐加工及冶炼业务，主要产品包括锂化合物及衍生品、锂精矿及伴生品和振动筛及PC生产线等。旗下领辉科技具备锂云母年选矿产能120万吨。
+2.2025年5月20日公告，控股孙公司天津长领矿业以2.2亿元成功竞得湖南临武嘉宇矿业74.3%股权。嘉宇矿业拥有锡矿石247万吨、铅矿石119万吨、锌矿石117万吨，年开采规模30万吨，可迅速形成稳定的采选产能。</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>锂矿, 有色金属</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3170,38 +3213,34 @@
       </c>
       <c r="C61" s="2" t="inlineStr"/>
       <c r="D61" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>sh600108</t>
+          <t>sh603353</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>亚盛集团</t>
+          <t>和顺石油</t>
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>5.97</v>
+        <v>42.85</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>9.94</v>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>8天6板</t>
-        </is>
-      </c>
+        <v>10.01</v>
+      </c>
+      <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>农业种植|1.公司2026年3月2日公告，目前未开展矿产相关业务，也不存在需要披露的相关重大信息。
-2.公司主要种植经营啤酒花、马铃薯、牧草、果品、药材、食葵、辣椒、枸杞、香辛料等初级农产品和加工产品，以及生产经营节水灌溉设备。</t>
+          <t>石油+半导体|1.公司是湖南省第一家获国家商务部批准取得成品油批发资质的民营石油企业，主营成品油批发零售，业务涵盖成品油采购、仓储、物流、批发、零售环节，在成品油流通领域形成完整产业链。
+2.2025年11月16日晚公告，公司拟以现金收购及增资方式取得上海奎芯集成电路设计有限公司不低于34%股权并通过表决权委托合计控制其51%表决权，交易完成后奎芯科技将纳入合并报表，布局高速接口IP及Chiplet解决方案。</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>农业种植</t>
+          <t>石油, 半导体</t>
         </is>
       </c>
     </row>
@@ -3218,37 +3257,33 @@
       </c>
       <c r="C62" s="2" t="inlineStr"/>
       <c r="D62" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>sh601789</t>
+          <t>sh600433</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>宁波建工</t>
+          <t>冠豪高新</t>
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>6.64</v>
+        <v>3.85</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>数据中心机柜出租|宁波建工2023年6月20日在投资者互动平台表示，中经云主营业务为数据中心机柜位出租，无算力出租服务。</t>
+          <t>造纸|公司是国家级重点高新技术企业，是国内首家大规模生产热敏纸的专业公司和国内目前生产设备及工艺最先进的大型无碳复写纸、不干胶标签材料生产基地，系国家税务总局、中国印钞造币总公司选定为增值税专用发票专用无碳复写纸唯一供应产品。</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>数据中心机柜出租</t>
+          <t>造纸</t>
         </is>
       </c>
     </row>
@@ -3265,33 +3300,33 @@
       </c>
       <c r="C63" s="2" t="inlineStr"/>
       <c r="D63" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>sz002969</t>
+          <t>sz002177</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>嘉美包装</t>
+          <t>御银股份</t>
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>25.91</v>
+        <v>9.25</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>10.02</v>
+        <v>9.99</v>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>追觅创始人入主|追觅创始人旗下逐越鸿智斥资逾22.82亿元拿下嘉美包装公司控制权。追觅科技有关人士向《科创板日报》记者表示，本次收购资金全部来源于俞浩及核心团队的自有与自筹资金，无来自追觅科技公司的资金，不会影响追觅科技公司正常运营。“逐越鸿智将以‘战略赋能者’身份参与嘉美包装运营，依托追觅在技术创新与全球资源上的优势，推动其在智能化生产、高端产品研发及全球化布局上实现突破。”</t>
+          <t>数字货币|公司是金融设备整体解决服务商，在ATM设备产能和销售规模在国内ATM制造厂商中位居前列。公司于2020年2月17日在互动平台表示，公司有数字货币ATM机上交易的相关技术储备。</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>追觅创始人入主</t>
+          <t>数字货币</t>
         </is>
       </c>
     </row>
@@ -3308,20 +3343,20 @@
       </c>
       <c r="C64" s="2" t="inlineStr"/>
       <c r="D64" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>sz000949</t>
+          <t>sz002432</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>新乡化纤</t>
+          <t>九安医疗</t>
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>7.59</v>
+        <v>58.52</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>10</v>
@@ -3329,12 +3364,13 @@
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>化纤|公司是国内较早进入化纤行业的企业之一，主营粘胶长丝、氨纶纤维的生产与销售，主要产品粘胶长丝是再生纤维素纤维，氨纶纤维是一种综合性能非常优秀的高弹性纤维，在织物和服饰中的应用越来越广泛。</t>
+          <t>医疗器械+kimi|1.公司是一家在国内外具有影响力的个人健康管理产品供应商，主要从事家用医疗器械的研发、生产及销售。
+2.公司通过认购砺思资本基金份额参股Kimi。</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>化纤</t>
+          <t>医疗器械, kimi</t>
         </is>
       </c>
     </row>
@@ -3351,33 +3387,33 @@
       </c>
       <c r="C65" s="2" t="inlineStr"/>
       <c r="D65" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>sh603115</t>
+          <t>sz002831</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>海星股份</t>
+          <t>裕同科技</t>
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>32</v>
+        <v>34.06</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>电极箔|公司主营产品电极箔可应用于MLPC电容器。MLPC产品可广泛应用于服务器中高功耗芯片的供电滤波场景，特别是CPU和GPU的核心电压供电。</t>
+          <t>并购重组|2月25日，裕同科技公告，全资子公司香港裕同印刷有限公司拟收购Gelbert Eco Print Szolgáltató és Kereskedelmi Korlátolt Felelősségű Társaság合计60%的股权，本次交易完成后，Gelbert将成为公司的控股子公司，并纳入公司合并报表范围。</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>电极箔</t>
+          <t>并购重组</t>
         </is>
       </c>
     </row>
@@ -3394,33 +3430,33 @@
       </c>
       <c r="C66" s="2" t="inlineStr"/>
       <c r="D66" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>sz001332</t>
+          <t>sz000626</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>锡装股份</t>
+          <t>远大控股</t>
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>65.55</v>
+        <v>8.42</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>10</v>
+        <v>10.07</v>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>油气+核电|公司主要从事金属压力容器的研发、设计、制造、销售及相关技术服务，已形成以换热压力容器、反应压力容器、储存压力容器、分离压力容器和海洋油气装置模块为主的非标压力容器产品系列，产品主要应用于炼油及石油化工、基础化工、核电及太阳能发电、高技术船舶及海洋工程等领域。</t>
+          <t>大宗商品贸易|远大物产是公司贸易领域的核心经营和管理平台，现已发展成为集贸易、物流于一体的综合性企业集团，辐射范围涵盖长三角主要大宗商品消费地区。</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>油气, 核电</t>
+          <t>大宗商品贸易</t>
         </is>
       </c>
     </row>
@@ -3437,33 +3473,33 @@
       </c>
       <c r="C67" s="2" t="inlineStr"/>
       <c r="D67" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>sz002729</t>
+          <t>sz000062</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>好利科技</t>
+          <t>深圳华强</t>
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>19.18</v>
+        <v>26.2</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>9.98</v>
+        <v>9.99</v>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>电力熔断器|公司电力熔断器产品应用市场在于UPS、变频器、光伏发电、风力发电以及电动汽车等市场。</t>
+          <t>华为概念|公司是华为海思的重要合作伙伴，是华为海思全系列产品代理商，代理的产品包括华为海思的数字电视机顶盒芯片、智能电视芯片、显示驱动芯片、PLC传输芯片、IPCAMERA及AI芯片等。</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>电力熔断器</t>
+          <t>华为概念</t>
         </is>
       </c>
     </row>
@@ -3480,205 +3516,33 @@
       </c>
       <c r="C68" s="2" t="inlineStr"/>
       <c r="D68" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>sz000014</t>
+          <t>sh603629</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>沙河股份</t>
+          <t>利通电子</t>
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>14.31</v>
+        <v>63.15</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>并购重组|沙河股份公告称，公司拟以支付现金的方式购买深业鹏基持有的晶华电子70%的股权。本次交易完成后，晶华电子将成为上市公司的控股子公司，纳入公司合并报表范围，交易价格2.74亿元。本次交易构成重大资产重组。本次交易完成后，沙河股份将改变现有单一房地产业务的经营现状，切入智能显示控制器、液晶显示器件的研发、生产与销售相关业务领域。</t>
+          <t>算力租赁|公司目前对外出租AI算力规模已达10000P以上，其中，约4000P是以自有算力（报表中在固定资产科目列示）出租，其余是转租算力（在使用权资产科目列示）出租。</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>并购重组</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr"/>
-      <c r="D69" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>sz002993</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>奥海科技</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="n">
-        <v>50.08</v>
-      </c>
-      <c r="H69" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>服务器电源|公司致力于CRPS服务器通用冗余电源研发、生产和销售，服务器电源、算力电源、服务器PDB电源等产品实现批量出货，出货及在研功率范围覆盖550W至8000W。</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>服务器电源</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr"/>
-      <c r="D70" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>sh600172</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>黄河旋风</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="H70" s="2" t="n">
-        <v>10.04</v>
-      </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>金刚石|公司作为超硬材料行业龙头以及唯一的全产业链布局企业，主要产品包括培育钻石及工业金刚石两大产品体系，覆盖工业金刚石、培育钻石、砂轮、刀具、钻头、锯片等，是国内乃至全球范围内品类别齐全、链条完整的超硬材料及制品制造商，可以向客户提供产品类别、规格齐全以及性能稳定的各类超硬材料及制品，包括超硬材料单晶及制品、立方氮化硼及制品、金刚石聚晶及制品以及超硬材料制品辅助材料。</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>金刚石</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr"/>
-      <c r="D71" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>920036.BJ</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>觅睿科技</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="n">
-        <v>53.69</v>
-      </c>
-      <c r="H71" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>北交所次新|觅睿科技为智能摄像机“小巨人”，公司专注于智能网络摄像机及物联网视频产品的研产销，并且提供相关云存储、AI等增值服务，产品主要应用于室外/内安防、智能入户、婴儿看护、智能庭院等场景。</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>北交所次新</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr"/>
-      <c r="D72" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>sh600769</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>祥龙电业</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="n">
-        <v>13.65</v>
-      </c>
-      <c r="H72" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>国企改革|公司的最终控制人为武汉东湖新技术开发区管理委员会。公司的主要业务为供水业务和建筑业务。</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>国企改革</t>
+          <t>算力租赁</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3720,16 +3584,16 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sh605268</t>
+          <t>sh601789</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>王力安防</t>
+          <t>宁波建工</t>
         </is>
       </c>
     </row>
@@ -3739,12 +3603,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sh601789</t>
+          <t>sz002445</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>宁波建工</t>
+          <t>中南文化</t>
         </is>
       </c>
     </row>
@@ -3754,12 +3618,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sh600135</t>
+          <t>sh600108</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>乐凯胶片</t>
+          <t>亚盛集团</t>
         </is>
       </c>
     </row>
@@ -3769,12 +3633,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sz002445</t>
+          <t>sh600769</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>中南文化</t>
+          <t>祥龙电业</t>
         </is>
       </c>
     </row>
@@ -3784,12 +3648,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sz002903</t>
+          <t>sh600726</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>宇环数控</t>
+          <t>华电能源</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3663,72 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sz002575</t>
+          <t>sh600172</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>群兴玩具</t>
+          <t>黄河旋风</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>sz000839</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>国安股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>sh603421</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>鼎信通讯</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>sz000537</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>绿发电力</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>sh603803</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>瑞斯康达</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,12 +476,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K68"/>
+  <dimension ref="A1:K65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="106" customWidth="1" min="3" max="3"/>
+    <col width="92" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
@@ -489,7 +489,7 @@
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="343" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -552,560 +552,572 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1.19</v>
+        <v>1.92</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>全球石油运输受阻，油价高位运行直接支撑化工品价格中枢。</t>
+          <t>《数据中心绿色低碳发展专项行动计划》明确要求，国家枢纽节点新建数据中心绿电占比需超过80%，并将可再生能源利用目标作为节能审查重要内容。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>sh600722</t>
+          <t>sh600821</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>金牛化工</t>
+          <t>金开新能</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>14</v>
+        <v>10.87</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>9.98</v>
+        <v>10.02</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>8天4板</t>
+          <t>10天5板</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>甲醇|公司的主要业务为甲醇的生产和销售，产品方式为焦炉气制甲醇。公司的主要业务由持股50%的控股子公司金牛旭阳经营，金牛旭阳拥有的甲醇生产能力为20万吨/年。</t>
+          <t>电算协同|1.公司主营业务为新能源电力的开发、投资、建设及运营，包括光伏发电和风力发电两个板块。
+2.2024年10月8日公告，公司全资子公司金开新能科技有限公司拟于新疆昌吉市投资建设国家超算广州中心新疆分中心昌吉智算中心项目，算力总规模达到5,000PFlops。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>甲醇</t>
+          <t>电算协同</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1.19</v>
+        <v>1.92</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>全球石油运输受阻，油价高位运行直接支撑化工品价格中枢。</t>
+          <t>《数据中心绿色低碳发展专项行动计划》明确要求，国家枢纽节点新建数据中心绿电占比需超过80%，并将可再生能源利用目标作为节能审查重要内容。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sz000833</t>
+          <t>sz002445</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>粤桂股份</t>
+          <t>中南文化</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>27.52</v>
+        <v>4.08</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>9.99</v>
+        <v>9.969999999999999</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>4天2板</t>
+          <t>4天4板</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>硫化工|云硫矿业是粤桂股份硫化工产业板块实体子公司，位于广东云浮市云城区，探明硫铁矿储量2.08亿吨，占全国硫铁矿富矿资源的85%，平均品位31.04%，品质优良，原矿产能约300万吨/年，按百川盈孚网公布的全国硫铁矿产量计算，公司硫铁矿产量占全国产量约16.63%。</t>
+          <t>并购+电力+油气|1.中南文化(002445.SZ)公告称，公司计划通过发行股份及支付现金的方式购买江阴电力投资有限公司持有的江阴苏龙热电有限公司57.30%股权，同时拟向不超过三十五名特定投资者募集配套资金。本次交易相关审计、评估工作尚未完成，交易方案需进一步论证和沟通协商。本次交易预计构成重大资产重组。本次交易完成后，上市公司在电力能源领域的业务布局将得到拓展。
+2.公司是目前国内规模较大的工业金属管件制造商，主要产品为管件、法兰、管系和压力容器，产品拥有国际多项生产商许可证书；其中，公司还拥有国家质检总局颁发的压力管道元件、压力容器等特种设备制造许可证，是中国石油天然气集团公司一级供应网络成员单位、中国石油能源一号网会员单位、中国石化资源市场成员厂组织集中采购成员厂。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>硫化工</t>
+          <t>并购, 电力, 油气</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.19</v>
+        <v>1.92</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>全球石油运输受阻，油价高位运行直接支撑化工品价格中枢。</t>
+          <t>《数据中心绿色低碳发展专项行动计划》明确要求，国家枢纽节点新建数据中心绿电占比需超过80%，并将可再生能源利用目标作为节能审查重要内容。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sz000545</t>
+          <t>sz000537</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>金浦钛业</t>
+          <t>绿发电力</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>3.83</v>
+        <v>12.51</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>10.06</v>
+        <v>10.03</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4天2板</t>
+          <t>3天3板</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>钛白粉+锂电池|1.全资子公司南京钛白是我国最早生产钛白粉的企业之一，也是国内最早研制、生产高档金红石钛白粉和化纤钛白粉的企业之一，目前已成为国内大型硫酸法钛白粉生产企业和行业骨干企业。
-2.2022年3月28日公告，公司拟在安徽（淮北）新型煤化工合成材料基地投资建设20万吨/年电池级磷酸铁、20万吨/年磷酸铁锂等新能源电池材料一体化项目，该项目总投资在100亿元左右。</t>
+          <t>电算协同|公司主营业务为风能和太阳能投资、开发、运营，形成海陆齐发、风光并举、多能互补的业务布局，运营电站涵盖海上风电、陆上风电、光伏发电、光热发电、储能等多种业态。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>钛白粉, 锂电池</t>
+          <t>电算协同</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1.19</v>
+        <v>1.92</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>全球石油运输受阻，油价高位运行直接支撑化工品价格中枢。</t>
+          <t>《数据中心绿色低碳发展专项行动计划》明确要求，国家枢纽节点新建数据中心绿电占比需超过80%，并将可再生能源利用目标作为节能审查重要内容。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sh600075</t>
+          <t>sh600726</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>新疆天业</t>
+          <t>华电能源</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>7.47</v>
+        <v>3.88</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>10.01</v>
+        <v>9.92</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4天2板</t>
+          <t>3天3板</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>化工|公司通过资产重组、收购氯碱化工资产，已具备较为完整的“自备电力→电石→聚氯乙烯树脂及副产品→电石渣及其他废弃物制水泥”一体化产业联动式绿色环保型循环经济产业链，具有89万吨PVC产能（包括69万吨通用PVC、10万吨特种树脂、10万吨糊树脂）、65万吨离子膜烧碱产能、134万吨电石产能，同时拥有2×300MW、2×330MW自备热电站以及405万吨电石渣制水泥装置。</t>
+          <t>电力|公司是黑龙江省最大的发电及集中供热运营商，主要产品为电力、热力，火力电厂分布在黑龙江省主要中心城市。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>电力</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1.19</v>
+        <v>1.92</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>全球石油运输受阻，油价高位运行直接支撑化工品价格中枢。</t>
+          <t>《数据中心绿色低碳发展专项行动计划》明确要求，国家枢纽节点新建数据中心绿电占比需超过80%，并将可再生能源利用目标作为节能审查重要内容。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sz002455</t>
+          <t>sz002015</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>百川股份</t>
+          <t>协鑫能科</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>14.73</v>
+        <v>21.36</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
+        <v>9.99</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>5天3板</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>化工+固态电池|1.公司是一家从事高新技术精细化工产品生产的专业企业，主营业务为醋酸酯类、偏苯三酸酐及酯类、醇醚类、多元醇类化工产品的研发、生产和销售。
-2.子公司海基开发的准固态电池具有高能量密度、轻量化特性，兼顾低内阻与长寿命等特点。</t>
+          <t>电算协同|1.公司在立足于成熟稳健增长的清洁能源投资、开发、运营的基础上，在能源结构、业务模式及能源应用三方面进行优化转型，并将最终成为新型电力系统综合服务商。
+2.公司在上海、苏州投运两个智算中心，已投运超千P的算力资源。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>化工, 固态电池</t>
+          <t>电算协同</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1.19</v>
+        <v>1.92</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>全球石油运输受阻，油价高位运行直接支撑化工品价格中枢。</t>
+          <t>《数据中心绿色低碳发展专项行动计划》明确要求，国家枢纽节点新建数据中心绿电占比需超过80%，并将可再生能源利用目标作为节能审查重要内容。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sh603938</t>
+          <t>sh601016</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>三孚股份</t>
+          <t>节能风电</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>30.12</v>
+        <v>4.43</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
+        <v>9.93</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>化工+半导体材料|1.公司围绕循环经济的发展模式，主要从事三氯氢硅及氢氧化钾等精细化工产品的研发、生产和销售。
-2.公司电子特气产品为电子级二氯二氢硅、电子级三氯氢硅、电子级四氯化硅，下游主要应用于先进晶圆加工，存储芯片制造，硅外延片制造，已实现向部分国内龙头存储厂商、逻辑芯片Fab厂商批量稳定供应。</t>
+          <t>绿电|公司的主营业务为风力发电的项目开发、建设及运营。在加快风电场开发和建设的同时，加大中东部及南方区域市场开发力度，在湖北、广西、浙江、河南、四川等已有项目的区域开发后续项目，在贵州、安徽、湖南、广东、重庆、江西、山东等区域开展风电项目前期踏勘和测风工作，扩大资源储备。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>化工, 半导体材料</t>
+          <t>绿电</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1.19</v>
+        <v>1.92</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>全球石油运输受阻，油价高位运行直接支撑化工品价格中枢。</t>
+          <t>《数据中心绿色低碳发展专项行动计划》明确要求，国家枢纽节点新建数据中心绿电占比需超过80%，并将可再生能源利用目标作为节能审查重要内容。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sz001207</t>
+          <t>sh601330</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>联科科技</t>
+          <t>绿色动力</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>31.27</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
+        <v>10.04</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>化工+机器人|1.公司主要从事二氧化硅和炭黑的研发、生产与销售，其中二氧化硅产品主要包括LK、LKHD及LKSIL系列橡胶工业用二氧化硅和非橡胶工业用二氧化硅。
-2.二氧化硅可用于制造人形机器人皮肤，公司正在积极开拓市场。</t>
+          <t>绿电|公司是中国最早从事生活垃圾焚烧发电的企业之一，主要以BOT等特许经营的方式从事生活垃圾焚烧发电厂的投资、建设、运营、维护以及技术顾问业务。截至2024年12月31日，公司在生活垃圾焚烧发电领域运营项目37个，运营项目垃圾处理能力达4.03万吨/日，装机容量857MW，公司项目数量和垃圾处理能力均位居行业前列。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>化工, 机器人</t>
+          <t>绿电</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1.19</v>
+        <v>1.92</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>全球石油运输受阻，油价高位运行直接支撑化工品价格中枢。</t>
+          <t>《数据中心绿色低碳发展专项行动计划》明确要求，国家枢纽节点新建数据中心绿电占比需超过80%，并将可再生能源利用目标作为节能审查重要内容。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sh600328</t>
+          <t>sh601991</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>中盐化工</t>
+          <t>大唐发电</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>9.94</v>
+        <v>4.58</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>9.959999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>化工|公司是一家集盐、盐化工、医药健康产品等生产及销售为一体的综合性企业，公司主营业务为以精制盐、工业盐等为代表的盐产品；以金属钠、氯酸钠为代表的精细化工产品；以纯碱为代表的基础化工产品；以苁蓉益肾颗粒、复方甘草片、维蜂盐藻等产品为代表的医药健康产品。</t>
+          <t>电力|公司是中国大型独立发电公司之一，主要经营以火电为主的发电业务及水电、风电和其他能源发电业务。公司及子公司发电业务主要分布于全国19个省、市、自治区，京津冀、东南沿海区域是公司火电装机最为集中的区域，水电项目大多位于西南地区，风电、光伏广布全国资源富集区域。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>电力</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1.19</v>
+        <v>1.92</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>全球石油运输受阻，油价高位运行直接支撑化工品价格中枢。</t>
+          <t>《数据中心绿色低碳发展专项行动计划》明确要求，国家枢纽节点新建数据中心绿电占比需超过80%，并将可再生能源利用目标作为节能审查重要内容。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sz001369</t>
+          <t>sh600868</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>双欣材料</t>
+          <t>梅雁吉祥</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>16.94</v>
+        <v>4.33</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>化工|公司是一家专业从事聚乙烯醇（PVA）、特种纤维、醋酸乙烯（VAC）、碳化钙（电石）等PVA产业链上下游产品的研发、生产、销售的高新技术企业，拥有聚乙烯醇全产业链布局。</t>
+          <t>银锑矿+电力|1.公司旗下梅雁矿业所拥有的嵩溪锑银矿主要矿种为银矿、锑矿，采矿许可证内累计查明资源储量：银锑矿石量1264.353 Kt；锑金属量22474.82t。
+2.公司电站全部在广东省梅州地区，均为水力发电，目前公司建成投产的水电站总装机容量约为15.1万千瓦，年设计发电量约4.7亿度。公司所发电量全部由广东电网公司收购。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>银锑矿, 电力</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1.19</v>
+        <v>1.92</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>全球石油运输受阻，油价高位运行直接支撑化工品价格中枢。</t>
+          <t>《数据中心绿色低碳发展专项行动计划》明确要求，国家枢纽节点新建数据中心绿电占比需超过80%，并将可再生能源利用目标作为节能审查重要内容。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sh600989</t>
+          <t>sh603693</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>宝丰能源</t>
+          <t>江苏新能</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>31.85</v>
+        <v>15.42</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>10.02</v>
+        <v>9.99</v>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>煤化工|公司打造了一个集“煤炭采选、焦化、甲醇、烯烃、精细化工、新能源”于一体的高端煤基新材料循环经济产业集群，包括：1、煤制烯烃，即以煤、焦炉气为原料生产甲醇，再以甲醇为原料生产聚乙烯、聚丙烯、EVA；2、焦化，即将原煤洗选为精煤，再用精煤进行炼焦生产焦炭；3、精细化工，以煤制烯烃、焦化副产品生产甲基叔丁基醚、焦化苯、工业萘、改质沥青、蒽油等精细化工产品。</t>
+          <t>绿电|公司的主营业务为新能源发电项目的投资开发、建设运营及电力销售，目前主要包括风能发电、生物质能发电和光伏发电三个板块。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>煤化工</t>
+          <t>绿电</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>1.19</v>
+        <v>1.92</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>全球石油运输受阻，油价高位运行直接支撑化工品价格中枢。</t>
+          <t>《数据中心绿色低碳发展专项行动计划》明确要求，国家枢纽节点新建数据中心绿电占比需超过80%，并将可再生能源利用目标作为节能审查重要内容。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sz002092</t>
+          <t>sz000600</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>中泰化学</t>
+          <t>建投能源</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>8.1</v>
+        <v>10.7</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>10.05</v>
+        <v>9.969999999999999</v>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>化工|公司拥有完整的煤炭—热电—氯碱化工—粘胶纤维—粘胶纱上下游一体化的循环经济产业链，主营聚氯乙烯树脂（PVC）、离子膜烧碱、粘胶纤维、粘胶纱等四大产品。公司本部现有150万吨PVC产能。</t>
+          <t>电力|公司是河北省的能源投资主体，主营业务为投资、建设、运营管理以电力生产为主的能源项目，公司电力业务以燃煤火力发电和供热为主，同时涉及核电、风电、水电等新能源项目投资。目前拥有控股发电公司9家、售电公司1家，参股发电公司12家。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>电力</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>1.19</v>
+        <v>1.92</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>全球石油运输受阻，油价高位运行直接支撑化工品价格中枢。</t>
+          <t>《数据中心绿色低碳发展专项行动计划》明确要求，国家枢纽节点新建数据中心绿电占比需超过80%，并将可再生能源利用目标作为节能审查重要内容。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sh600299</t>
+          <t>sh600956</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">安迪苏  </t>
+          <t>新天绿能</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>14.61</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>10.02</v>
+        <v>10</v>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>化工|公司是全球少数几家能够同时生产液体和固体蛋氨酸的蛋氨酸生产商之一,并在中国和欧洲均拥有一体化生产平台；包括生产维生素A的法国Commentry工厂，生产固体蛋氨酸和中间体的法国LesRoches及Roussillon工厂以及生产液体蛋氨酸的西班牙Burgos工厂均产生积极影响。</t>
+          <t>绿电|公司的主营业务包括风力发电业务，在全国10多个省份均布局风电项目布局，风电运营水平处于全国领先水平。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>绿电</t>
         </is>
       </c>
     </row>
@@ -1116,41 +1128,45 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>1.19</v>
+        <v>0.04</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>全球石油运输受阻，油价高位运行直接支撑化工品价格中枢。</t>
+          <t>3月12日，国内期货主力合约开盘多数上涨，对二甲苯封涨停，PTA、瓶片期货主力合约触及涨停。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sh600409</t>
+          <t>sh600722</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>三友化工</t>
+          <t>金牛化工</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>9.17</v>
+        <v>15.4</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>9.950000000000001</v>
-      </c>
-      <c r="I14" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>9天5板</t>
+        </is>
+      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>化工|公司已由成立之初单一的纯碱生产企业发展成为拥有化纤、纯碱、氯碱、有机硅四大主业并配套热电、原盐、碱石、物流、国际贸易等循环经济体系的行业龙头企业。</t>
+          <t>甲醇|公司的主要业务为甲醇的生产和销售，产品方式为焦炉气制甲醇。公司的主要业务由持股50%的控股子公司金牛旭阳经营，金牛旭阳拥有的甲醇生产能力为20万吨/年。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>甲醇</t>
         </is>
       </c>
     </row>
@@ -1161,36 +1177,36 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>1.19</v>
+        <v>0.04</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>全球石油运输受阻，油价高位运行直接支撑化工品价格中枢。</t>
+          <t>3月12日，国内期货主力合约开盘多数上涨，对二甲苯封涨停，PTA、瓶片期货主力合约触及涨停。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sh600873</t>
+          <t>sh600691</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>梅花生物</t>
+          <t>潞化科技</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>12.62</v>
+        <v>4.03</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>10.03</v>
+        <v>10.11</v>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>化工|公司专注于氨基酸的规模化生产与创新应用。公司已构建起涵盖动物营养氨基酸（赖氨酸、苏氨酸、缬氨酸等系列产品）、食品鲜味剂（味精、呈味核苷酸二钠等鲜味剂）、医药级氨基酸（谷氨酰胺、脯氨酸等药用原料）、胶体多糖（黄原胶、海藻糖）以及大宗副产品（玉米胚芽、蛋白粉等）的完整产业生态。赖氨酸、苏氨酸产能规模稳居全球首位，味精产能位列全球第二。</t>
+          <t>化工|公司主要业务包括化工产品和化工机械设备的生产和销售，化工产品研发及工程总承包设计等，主要产品包括尿素、聚氯乙烯、烯烃、烧碱、双氧水、甲醇等。2020年公司主要产品产量：尿素343.97万吨，聚氯乙烯25.04万吨，丙烯15.32万吨，离子膜烧碱41.5万吨，甲醇34.41万吨，三氯化磷9.00万吨，双氧水36.72万吨，三聚氰胺10.54万吨。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1202,505 +1218,483 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>1.8</v>
+        <v>0.04</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>《数据中心绿色低碳发展专项行动计划》明确要求，国家枢纽节点新建数据中心绿电占比超过80%，绿电成为数据中心最直接的能源供给。</t>
+          <t>3月12日，国内期货主力合约开盘多数上涨，对二甲苯封涨停，PTA、瓶片期货主力合约触及涨停。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sz002445</t>
+          <t>sh600370</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>中南文化</t>
+          <t xml:space="preserve">三房巷  </t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>3.71</v>
+        <v>2.48</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>10.09</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>10.22</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>并购+电力+油气|1.中南文化(002445.SZ)公告称，公司计划通过发行股份及支付现金的方式购买江阴电力投资有限公司持有的江阴苏龙热电有限公司57.30%股权，同时拟向不超过三十五名特定投资者募集配套资金。本次交易相关审计、评估工作尚未完成，交易方案需进一步论证和沟通协商。本次交易预计构成重大资产重组。本次交易完成后，上市公司在电力能源领域的业务布局将得到拓展。
-2.公司是目前国内规模较大的工业金属管件制造商，主要产品为管件、法兰、管系和压力容器，产品拥有国际多项生产商许可证书；其中，公司还拥有国家质检总局颁发的压力管道元件、压力容器等特种设备制造许可证，是中国石油天然气集团公司一级供应网络成员单位、中国石油能源一号网会员单位、中国石化资源市场成员厂组织集中采购成员厂。</t>
+          <t>化工|公司成为“PTA-瓶级聚酯切片”一体化布局的优势企业，PTA产品是郑州商品交易所PTA交割免检品牌，已开发出多种全系列的瓶级聚酯切片产品。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>并购, 电力, 油气</t>
+          <t>化工</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>1.8</v>
+        <v>0.04</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>《数据中心绿色低碳发展专项行动计划》明确要求，国家枢纽节点新建数据中心绿电占比超过80%，绿电成为数据中心最直接的能源供给。</t>
+          <t>3月12日，国内期货主力合约开盘多数上涨，对二甲苯封涨停，PTA、瓶片期货主力合约触及涨停。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sz000537</t>
+          <t>sz002254</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>绿发电力</t>
+          <t>泰和新材</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>11.37</v>
+        <v>13.81</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>9.959999999999999</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.04</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>电算协同|绿发电力在互动平台表示，作为“新能源+”融合发展的重要场景，电算协同一直是公司密切关注并重点布局的方向。目前公司正开展相关业务的对接和论证工作，若有重大进展将按规定履行内部决策和信息披露程序。</t>
+          <t>化工|公司专业从事氨纶、芳纶等高性能纤维的研发生产及销售，主导产品为纽士达氨纶、泰美达间位芳纶、泰普龙对位芳纶及其上下游制品。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>电算协同</t>
+          <t>化工</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>1.8</v>
+        <v>0.04</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>《数据中心绿色低碳发展专项行动计划》明确要求，国家枢纽节点新建数据中心绿电占比超过80%，绿电成为数据中心最直接的能源供给。</t>
+          <t>3月12日，国内期货主力合约开盘多数上涨，对二甲苯封涨停，PTA、瓶片期货主力合约触及涨停。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sh600726</t>
+          <t>sz000553</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>华电能源</t>
+          <t>安道麦A</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>3.53</v>
+        <v>6.8</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>9.969999999999999</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.03</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>电力|公司是黑龙江省最大的发电及集中供热运营商，主要产品为电力、热力，火力电厂分布在黑龙江省主要中心城市。</t>
+          <t>农药|安道麦控股股东为先正达，公司主要产品涵盖除草剂、杀虫剂、杀菌剂等，拥有草甘膦产能2万吨/年。</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>农药</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>1.8</v>
+        <v>0.04</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>《数据中心绿色低碳发展专项行动计划》明确要求，国家枢纽节点新建数据中心绿电占比超过80%，绿电成为数据中心最直接的能源供给。</t>
+          <t>3月12日，国内期货主力合约开盘多数上涨，对二甲苯封涨停，PTA、瓶片期货主力合约触及涨停。</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sh601330</t>
+          <t>sz000990</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>绿色动力</t>
+          <t>诚志股份</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>8.369999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>9.99</v>
+        <v>10.01</v>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>绿电|公司是中国最早从事生活垃圾焚烧发电的企业之一，主要以BOT等特许经营的方式从事生活垃圾焚烧发电厂的投资、建设、运营、维护以及技术顾问业务。截至2024年12月31日，公司在生活垃圾焚烧发电领域运营项目37个，运营项目垃圾处理能力达4.03万吨/日，装机容量857MW，公司项目数量和垃圾处理能力均位居行业前列。</t>
+          <t>化工|2022年8月，公司拟通过全资子公司青岛华青投资建设POE（聚烯烃弹性体）项目和超高分子量聚乙烯项目。公司在南京生产基地拥有两套烯烃生产工厂，乙烯、丙烯、丁二烯总产能接近100万吨/年。</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>绿电</t>
+          <t>化工</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1.8</v>
+        <v>0.04</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>《数据中心绿色低碳发展专项行动计划》明确要求，国家枢纽节点新建数据中心绿电占比超过80%，绿电成为数据中心最直接的能源供给。</t>
+          <t>3月12日，国内期货主力合约开盘多数上涨，对二甲苯封涨停，PTA、瓶片期货主力合约触及涨停。</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sh601016</t>
+          <t>sh603281</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>节能风电</t>
+          <t>江瀚新材</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>4.03</v>
+        <v>32.81</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>10.11</v>
+        <v>9.99</v>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>绿电|公司的主营业务为风力发电的项目开发、建设及运营。在加快风电场开发和建设的同时，加大中东部及南方区域市场开发力度，在湖北、广西、浙江、河南、四川等已有项目的区域开发后续项目，在贵州、安徽、湖南、广东、重庆、江西、山东等区域开展风电项目前期踏勘和测风工作，扩大资源储备。</t>
+          <t>化工|公司是全球供应规模最大的功能性硅烷生产商，也是轮胎、复合材料、密封胶等领域国际龙头企业的主要硅烷供应商，形成涵盖含硫硅烷、氨基硅烷、乙烯基硅烷、环氧硅烷、酰氧基硅烷、硅烷交联剂及硅烷衍生物等14个系列200多个功能性硅烷品种的完整绿色循环产业链。</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>绿电</t>
+          <t>化工</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>1.8</v>
+        <v>0.04</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>《数据中心绿色低碳发展专项行动计划》明确要求，国家枢纽节点新建数据中心绿电占比超过80%，绿电成为数据中心最直接的能源供给。</t>
+          <t>3月12日，国内期货主力合约开盘多数上涨，对二甲苯封涨停，PTA、瓶片期货主力合约触及涨停。</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>sz000899</t>
+          <t>sh600935</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>赣能股份</t>
+          <t>华塑股份</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>16.15</v>
+        <v>3.31</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>10.01</v>
+        <v>9.969999999999999</v>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>电力|公司主营业务为火力、水力发电，目前公司所属已投产运营火电厂一家、水电厂两家，总装机容量为150万千瓦。</t>
+          <t>化工|公司主要从事以PVC和烧碱为核心的氯碱化工产品生产与销售，业务涵盖原盐及灰岩开采、煤炭发电及电石制备、PVC及烧碱生产和“三废”综合利用等，构建了氯碱化工一体化循环经济体系。</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>化工</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>正泰董事长南存辉在两会记者会提到，这两年全球AI算力建设爆发式增长，变压器变得一台难求。“去年我们变压器出口同比增长71.4%, 工厂订单都排到2027年了。”</t>
+          <t>3月12日，国内期货主力合约开盘多数上涨，对二甲苯封涨停，PTA、瓶片期货主力合约触及涨停。</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>sh603421</t>
+          <t>sh603077</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>鼎信通讯</t>
+          <t>和邦生物</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>10.13</v>
+        <v>3.33</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.9</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>平头哥合作+电网|1.鼎信通讯在互动平台表示，公司芯片开发采用平头哥的CK802 32位内核架构，平头哥与公司签订有全面技术授权协议。
-2.公司的主营业务为低压用电系统产品的研发、生产、销售及服务，主要产品包括低压电力线载波通信模块（含芯片）产品、采集终端设备、智能电能表和配电终端等，主要应用于国家智能电网的用电信息采集系统和配网自动化系统。</t>
+          <t>农药+有色金属|1.公司主要农药产品包括草甘膦、双甘膦（草甘膦中间体），现有草甘膦产能5万吨/年、双甘膦产能15万吨/年。
+2.公司共全资持有或通过合营取得矿产资源（包含采矿权和探矿权）合计40宗。资源类型包含：磷矿、盐矿、铅锌矿、金矿、银矿、铜矿、锂矿、锡矿（伴生稀土矿）以及硅石矿。</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>平头哥合作, 电网</t>
+          <t>农药, 有色金属</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>正泰董事长南存辉在两会记者会提到，这两年全球AI算力建设爆发式增长，变压器变得一台难求。“去年我们变压器出口同比增长71.4%, 工厂订单都排到2027年了。”</t>
+          <t>3月12日，国内期货主力合约开盘多数上涨，对二甲苯封涨停，PTA、瓶片期货主力合约触及涨停。</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>sh601868</t>
+          <t>sh600844</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>中国能建</t>
+          <t>金煤科技</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>3.45</v>
+        <v>3.94</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>9.869999999999999</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>10.06</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>电力基建|公司致力于建设“行业领先、世界一流”的能源一体化方案解决商，在能源电力勘察设计技术上处于引领地位。在能源电力领域产业政策和发展规划研究，百万千瓦级超超临界机组、三代核电常规岛、清洁燃煤发电、特高压交直流和GIL综合管廊输变电、柔性交直流输电、海上风电、太阳能热发电等勘察设计技术领域具有国际领先优势。</t>
+          <t>煤化工|公司为专注于煤制乙二醇产业的新型化工企业，目前主要通过控股子公司通辽金煤的大型化工装置生产乙二醇并联产草酸。</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>电力基建</t>
+          <t>煤化工</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>正泰董事长南存辉在两会记者会提到，这两年全球AI算力建设爆发式增长，变压器变得一台难求。“去年我们变压器出口同比增长71.4%, 工厂订单都排到2027年了。”</t>
+          <t>3月12日，国内期货主力合约开盘多数上涨，对二甲苯封涨停，PTA、瓶片期货主力合约触及涨停。</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>sh601700</t>
+          <t>sh600714</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>风范股份</t>
+          <t>金瑞矿业</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>6.9</v>
+        <v>23.79</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>10.05</v>
+        <v>9.99</v>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>特高压+签订大单|风范股份公告称，公司在藏东南至粤港澳大湾区±800千伏特高压直流输电工程直流设备及线路材料第二批专项招标项目中中标，中标产品包括800kV直流钢管塔包1、800kV直流角钢塔包25和26，中标金额约为2.90亿元，约占公司2024年经审计营业收入的8.97%。</t>
+          <t>锶盐|公司主营业务为锶盐系列产品的生产和销售。主要产品包括碳酸锶（含工业级碳酸锶、电子级碳酸锶）、金属锶、铝锶合金、硝酸锶、氢氧化锶和副产品硫磺、亚硫酸钠。</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>特高压, 签订大单</t>
+          <t>锶盐</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>风电</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0.03</v>
+        <v>0.75</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>正泰董事长南存辉在两会记者会提到，这两年全球AI算力建设爆发式增长，变压器变得一台难求。“去年我们变压器出口同比增长71.4%, 工厂订单都排到2027年了。”</t>
+          <t>英国自4月1日起取消33项风电组件进口关税，叶片、电缆等核心部件税率由6%、2%降至0，旨在释放220亿英镑投资，加速北海海风装机落地。</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>sz002782</t>
+          <t>sh603507</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>可立克</t>
+          <t>振江股份</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>28.78</v>
+        <v>38.87</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>10.02</v>
+        <v>9.99</v>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>储能+电网设备|1.公司在储能领域具备相应变压器、电感及其组合器件产品的自主开发、生产和销售能力，且在现有光伏客户端中被采用。
-2.公司主要从事电子变压器和电感等磁性元件以及电源适配器、动力电池充电器和定制电源等开关电源产品的开发、生产和销售。</t>
+          <t>风电|公司是国内专业从事新能源发电设备钢结构件的领先企业，覆盖风电和光伏设备钢结构件设计开发、焊接、机加工和表面处理等生产全过程，主要产品包括机舱罩、转子房、定子段、塔筒等风电设备产品。</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>储能, 电网设备</t>
+          <t>风电</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>储能</t>
+          <t>风电</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>1.16</v>
+        <v>0.75</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>东吴证券表示，美国数据中心储能持续推动，欧洲、中东等项目大储需求旺盛，预计全球储能装机2026年60%以上增长，2027—2029年复合30%—50%增长。</t>
+          <t>英国自4月1日起取消33项风电组件进口关税，叶片、电缆等核心部件税率由6%、2%降至0，旨在释放220亿英镑投资，加速北海海风装机落地。</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>sz002150</t>
+          <t>sz002487</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>正泰电源</t>
+          <t>大金重工</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>29.68</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>10.01</v>
@@ -1708,229 +1702,229 @@
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
+          <t>风电|公司主营业务为风力发电设备制造，主要产品有常规陆塔、大直径分片式陆塔、低风速柔性高塔、海塔、单桩、群桩、导管架、海上升压站等风电设备及相关零部件。</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>风电</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>风电</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>英国自4月1日起取消33项风电组件进口关税，叶片、电缆等核心部件税率由6%、2%降至0，旨在释放220亿英镑投资，加速北海海风装机落地。</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>sh605305</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>中际联合</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>42.58</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>风电|公司是国内领先的高空安全作业设备和高空安全作业服务解决方案提供商，产品现阶段主要应用于风力发电领域。</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>风电</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>风电</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>英国自4月1日起取消33项风电组件进口关税，叶片、电缆等核心部件税率由6%、2%降至0，旨在释放220亿英镑投资，加速北海海风装机落地。</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>sz300690</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>双一科技</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>风电|公司风电领域主要产品为风电机舱罩类产品，产品规格涵盖750KW-8MW级别。</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>风电</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>风电</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>英国自4月1日起取消33项风电组件进口关税，叶片、电缆等核心部件税率由6%、2%降至0，旨在释放220亿英镑投资，加速北海海风装机落地。</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>sh603092</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">德力佳  </t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>73.81999999999999</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>风电|公司主要从事高速重载精密齿轮传动产品的研发、生产与销售，下游应用领域目前主要为风力发电机组，核心产品为风电主齿轮箱。</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>风电</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>储能</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>华西证券认为，短期来看，在能源供给不确定性加剧、峰谷套利优化电费的双重驱动下，欧洲户储/工商储经济性与刚需性共振强化，板块景气度上行趋势明确。</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>sz002150</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>正泰电源</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>储能+电网设备|1.旗下正泰电源是国内最早开始研发光伏逆变器的公司之一，业务范围涵盖光伏逆变器、光伏汇流箱、商用储能一体机、预装式光伏系统、预装式储能系统等。
 2.公司输配电控制设备业务主要产品包括高压成套开关设备、中低压成套开关设备、高低压开关元件及控制电器等，能够为下游各行业用户提供整体配电解决方案。</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>储能, 电网设备</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>储能</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>东吴证券表示，美国数据中心储能持续推动，欧洲、中东等项目大储需求旺盛，预计全球储能装机2026年60%以上增长，2027—2029年复合30%—50%增长。</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>sz301658</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>首航新能</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>45.94</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>20.01</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>储能|公司的储能电池主要为磷酸铁锂电池，能够适配多品牌光伏储能逆变器，主要应用于户用及小型工商业储能。公司光伏储能逆变器功率范围已涵盖3kW~20kW，适用于户用、小型工商业并离网储能多种场景。</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>储能</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>储能</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>东吴证券表示，美国数据中心储能持续推动，欧洲、中东等项目大储需求旺盛，预计全球储能装机2026年60%以上增长，2027—2029年复合30%—50%增长。</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>sh605117</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>德业股份</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>131.88</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>户储|公司拥有储能逆变器、组串式并网逆变器和微型并网逆变器12组系列产品。</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>户储</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>AI应用</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>全国多地下场“养龙虾”，常熟对“一人公司”最高拟予600万元支持；合肥高新区推出15条硬核举措，最高补贴1000万元；佛山一地推出面向公众的“小龙虾”免费部署服务。</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>sz000839</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>国安股份</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>9.94</v>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>AI安全|公司旗下子公司鸿联九五为企业提供一站式的审核服务体系。公司内容审核业务包括文本审核、图片审核、视频审核、音频审核、人工智能审核。</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>AI安全</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>AI应用</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>全国多地下场“养龙虾”，常熟对“一人公司”最高拟予600万元支持；合肥高新区推出15条硬核举措，最高补贴1000万元；佛山一地推出面向公众的“小龙虾”免费部署服务。</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>sh601858</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>中国科传</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>21.67</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>AI应用|公司自主研发的SciEngine全流程数字出版与知识服务平台（V3.0）进一步集成了学术查重检测、审稿专家自动推荐、自动在线校对、科大讯飞智能翻译、AI秒读视频、文献挖掘和语义检索等多种工具，进一步提升了出版运营与知识服务能力。</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>AI应用</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>储能</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>-0.65</v>
+        <v>-0.6</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>全国多地下场“养龙虾”，常熟对“一人公司”最高拟予600万元支持；合肥高新区推出15条硬核举措，最高补贴1000万元；佛山一地推出面向公众的“小龙虾”免费部署服务。</t>
+          <t>华西证券认为，短期来看，在能源供给不确定性加剧、峰谷套利优化电费的双重驱动下，欧洲户储/工商储经济性与刚需性共振强化，板块景气度上行趋势明确。</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>sz300246</t>
+          <t>sz301667</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>宝莱特</t>
+          <t>纳百川</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>16.8</v>
+        <v>79.98</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>20</v>
@@ -1938,262 +1932,256 @@
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>AI医疗|公司“基于AI的S系列重症监护仪设计”是基于AI语音识别技术，在监护设备上实现语音交互，无需繁杂的手动操作，释放医护人员双手；同时基于大数据，可实现心电导联自动切换，实现重点导联自动监测；智能的光线传感器实现背光亮度自动调节，可提高医护人员操作效率。</t>
+          <t>储能|在储能热管理领域，公司已成为宁德时代、中创新航、阳光电源等国内排名前列的新能源电源设备厂商的供应商。</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>AI医疗</t>
+          <t>储能</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>储能</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>1.71</v>
+        <v>-0.6</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>中金公司研报称，固态电池产业化进展持续推进，头部电池厂商固态电池设备及传统锂电设备招标或逐步启动。</t>
+          <t>华西证券认为，短期来看，在能源供给不确定性加剧、峰谷套利优化电费的双重驱动下，欧洲户储/工商储经济性与刚需性共振强化，板块景气度上行趋势明确。</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>sh603778</t>
+          <t>sz000593</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>国晟科技</t>
+          <t>德龙汇能</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>20.82</v>
+        <v>15.65</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>9.98</v>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+      <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>光伏+固态电池|1.国晟科技公告称，公司拟以2.406亿元的价格受让正豪科技、林琴合计持有的孚悦科技100%股权。交易完成后，公司将持有标的公司100%股权，标的公司将纳入公司合并报表。孚悦科技主要从事高精密度新型锂电池结构件的研发、生产和销售。
-2.子公司安徽国晟新能源科技有限公司拟以2.3亿元向国晟环球新能源（铁岭）有限公司进行增资，持股51.11%。铁岭环球拟投资的年产10GWh固态电池产业链AI智能制造项目已取得项目备案手续；并且铁岭环球已取得电池回收及固态电池生产制备所需的知识产权许可使用授权。</t>
+          <t>股权变更+储能|1.德龙汇能公告称，公司控股股东顶信瑞通与诺信芯材签订了《股份转让协议》，拟通过协议转让方式向诺信芯材转让公司股份1.06亿股，占公司总股本的29.64%。本次股份转让价格为9.41元/股，股份转让的交易价款合计为10亿元。若本次交易顺利推进并实施完成，公司控股股东及实际控制人将发生变更，公司控股股东将变更为诺信芯材，公司实际控制人将变更为孙维佳。
+2.公司参股19.87%的北京好风光储能技术有限公司主要研发锂浆料储能电池，目前正在积极筹备投产。
+3.公司致力于成为一家以天然气清洁能源为主的综合能源供应商，主要从事以天然气能源为主的清洁能源供应业务。</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>光伏, 固态电池</t>
+          <t>股权变更, 储能</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>储能</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>1.71</v>
+        <v>-0.6</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>中金公司研报称，固态电池产业化进展持续推进，头部电池厂商固态电池设备及传统锂电设备招标或逐步启动。</t>
+          <t>华西证券认为，短期来看，在能源供给不确定性加剧、峰谷套利优化电费的双重驱动下，欧洲户储/工商储经济性与刚需性共振强化，板块景气度上行趋势明确。</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>sz002733</t>
+          <t>sh603527</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>雄韬股份</t>
+          <t>众源新材</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>27.05</v>
+        <v>12.39</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>10</v>
+        <v>10.04</v>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>固态电池+IDC电源|1.公司固态电池产品是通过“原位聚合固态电解质技术”和“电极内部电解质动态成膜固化技术”两大核心技术的突破，彻底消除电池热失控风险，并解决“固-固”界面难题，完美适配数据中心、储能电站、轨道交通等对安全性有严苛要求的领域。
-2.公司主要为数据中心及算力中心提供UPS电池。</t>
+          <t>储能+铜|1.2022年6月22日公告，公司拟以全资子公司安徽众源新材投资有限公司出资人民币4,000万元与众源投资最终持股比例为40%。
+2.公司主要从事紫铜带箔材的研发、生产和销售业务，已成为国内紫铜板带箔材细分行业经营规模较大、技术实力领先的企业。</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>固态电池, IDC电源</t>
+          <t>储能, 铜</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>0.51</v>
+        <v>3.93</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>据开源证券，截至3月4日，G.652.D单模光纤价格由元旦前的18元/公里上涨至现价85~120元/公里，涨幅近650%；G.657.A1单模光纤价格由23元/公里涨至115~135元/公里，涨幅近487%。</t>
+          <t>长江证券测算显示，若霍尔木兹海峡长期封锁，全球电力用煤需求可能年化增加8486万吨；若我国煤化工装置满负荷运行，仅此一项便将拉动国内煤炭消费近5000万吨。</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>sh603803</t>
+          <t>sh600121</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>瑞斯康达</t>
+          <t>郑州煤电</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>12.1</v>
+        <v>5.14</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.06</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>光模块|在高端光模块领域，公司联营企业易锐光电是中国少数产业链上下游关键层面具备完整核心技术和解决方案的高科技企业，新一代基于自主知识产权的25G/100G/超100G集成光收发芯片的光通信模块及光组件，用于电信网络城域网和大型数据中心网络。</t>
+          <t>煤炭|河南省三家省管国有煤炭上市公司之一，在全国已正式投产的煤炭企业中属中等规模，产品包括优质的工业动力煤和生活用煤等。</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>光模块</t>
+          <t>煤炭</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>0.51</v>
+        <v>3.93</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>据开源证券，截至3月4日，G.652.D单模光纤价格由元旦前的18元/公里上涨至现价85~120元/公里，涨幅近650%；G.657.A1单模光纤价格由23元/公里涨至115~135元/公里，涨幅近487%。</t>
+          <t>长江证券测算显示，若霍尔木兹海峡长期封锁，全球电力用煤需求可能年化增加8486万吨；若我国煤化工装置满负荷运行，仅此一项便将拉动国内煤炭消费近5000万吨。</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sz300504</t>
+          <t>sh601015</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>天邑股份</t>
+          <t>陕西黑猫</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>19.32</v>
+        <v>5.17</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆|公司“通信网络物理连接与保护设备”业务板块主要产品包括光纤快速活动连接器、分路器、光缆接头盒、光缆交接箱、光缆分纤箱、光缆终端盒等。</t>
+          <t>煤炭+煤化工|公司以资源综合利用、循环经济产业链为生产模式，主要产品包括焦炭、甲醇、合成氨、LNG、BDO和精煤等。</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>煤炭, 煤化工</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>工业母机</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>0.47</v>
+        <v>3.93</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2026年开年以来，国内机床企业订单增长显著。有企业负责人表示，自今年初以来，来自人形机器人、新能源汽车等领域的订单大幅增加，已排至9月份。</t>
+          <t>长江证券测算显示，若霍尔木兹海峡长期封锁，全球电力用煤需求可能年化增加8486万吨；若我国煤化工装置满负荷运行，仅此一项便将拉动国内煤炭消费近5000万吨。</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sz002175</t>
+          <t>sh600188</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>东方智造</t>
+          <t>兖矿能源</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>3.53</v>
+        <v>22.17</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>9.969999999999999</v>
+        <v>10.02</v>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>工业母机|公司在2022年半年报中透露，公司主要产品为电子数显量具，目前是我国生产测量范围在500mm以上非标电子数显量具量仪的最主要厂家，数量量具主要作为数控机床的辅助工具。</t>
+          <t>煤炭+煤化工|1.公司是中国和澳大利亚主要的煤炭生产商、销售商和贸易商之一，是华东地区最大煤炭生产商，国内动力煤龙头企业，所产煤炭涵盖动力煤、喷吹煤、焦煤等多品种，所属兖煤澳洲是澳大利亚最大专营煤炭生产商。截至2024年底，煤炭原地资源量464亿吨（JORC标准），储量规模位居行业前列。
+2.煤制甲醇，公司煤化工业务主要分布在中国的陕西省和内蒙古自治区，主要负责甲醇的生产与销售。</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>工业母机</t>
+          <t>煤炭, 煤化工</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>工业母机</t>
+          <t>碳纤维</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>0.47</v>
+        <v>2.07</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2026年开年以来，国内机床企业订单增长显著。有企业负责人表示，自今年初以来，来自人形机器人、新能源汽车等领域的订单大幅增加，已排至9月份。</t>
+          <t>中复神鹰于2026年3月11日全球首发的SYT80（T1200级）超高强度碳纤维，目前已实现百吨级稳定量产，工程化拉伸强度达8000MPa，成为全球首个实现该级别工业化量产的企业。</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
@@ -2201,44 +2189,44 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sz002248</t>
+          <t>sz000420</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>华东数控</t>
+          <t>吉林化纤</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>15.58</v>
+        <v>5.02</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>10.03</v>
+        <v>10.09</v>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>工业母机|公司是中国机床行业生产、销售数控龙门导轨磨床数量最多、规模最大的机床制造企业，以研发和生产经营数控机床、普通机床及其关键功能部件为主营业务，产品有数控龙门铣床（龙门加工中心）、数控龙门磨床、数控外圆磨床、万能摇臂铣床、平面磨床、动静压主轴等机床和功能部件产品。</t>
+          <t>碳纤维|公司碳纤维生产能力已经开始配套碳纤维复合材料的生产，建设了“1.2万吨碳纤维复材”产业项目。</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>工业母机</t>
+          <t>碳纤维</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>液冷IDC</t>
+          <t>碳纤维</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>0.36</v>
+        <v>2.07</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>2026年GTC大会，是英伟达公司于3月16日至19日在美国加州圣何塞举办的AI大会，大会主题聚焦于人工智能与新一代AI基础设施。</t>
+          <t>中复神鹰于2026年3月11日全球首发的SYT80（T1200级）超高强度碳纤维，目前已实现百吨级稳定量产，工程化拉伸强度达8000MPa，成为全球首个实现该级别工业化量产的企业。</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
@@ -2246,48 +2234,44 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>sh603158</t>
+          <t>sh688295</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>腾龙股份</t>
+          <t>中复神鹰</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>12.25</v>
+        <v>43.25</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>9.959999999999999</v>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>20.01</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>服务器液冷|公司电子水泵产品有向客户供货，间接应用于数据中心/服务器液冷领域。</t>
+          <t>碳纤维|中复神鹰公告，近日公司全新推出SYT80（T1200级）碳纤维新品，实现SYT80碳纤维的百吨级制备。该产品参数为：拉伸强度8000MPa、拉伸模量324GPa、断裂伸长率2.5%、体密度1.79g/cm3。</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>服务器液冷</t>
+          <t>碳纤维</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>液冷IDC</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>0.36</v>
+        <v>-1</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2026年GTC大会，是英伟达公司于3月16日至19日在美国加州圣何塞举办的AI大会，大会主题聚焦于人工智能与新一代AI基础设施。</t>
+          <t>2026年光纤通信大会暨展览会（OFC）是全球光通信与网络领域的盛会，定于3月15日至19日在美国洛杉矶会议中心举行。</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
@@ -2295,245 +2279,261 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>sh603757</t>
+          <t>sz002951</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>大元泵业</t>
+          <t>金时科技</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>47.43</v>
+        <v>17.24</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>10</v>
+        <v>10.02</v>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>IDC温控|公司高压电子水泵及相关屏蔽泵产品能够应用在IDC温控领域，下游客户包括维谛技术、英维克、中兴通讯、曙光数创、同飞股份等。</t>
+          <t>储能+光纤|1.公司是国内领先的储能系统及储能安全解决方案及技术服务供应商，专注于储能系统和储能消防安全系统的研发、生产、销售及技术服务，可为传统发电、新能源发电、智能电网、终端电力用户等“源－网－荷”全链条行业客户提供储能技术、储能消防安全一站式整体解决方案。
+2.公司通过智芯一号股权基金间接参股苏州易缆微，易缆微是一家光纤通信产品研发生产商，致力于光纤通信系统、光网络系统、光电传感系统、物联网系统技术研究和试验发展及进出口业务。</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>IDC温控</t>
+          <t>储能, 光纤</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>0.96</v>
+        <v>-1</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>根据TrendForce集邦咨询最新调查，Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
+          <t>2026年光纤通信大会暨展览会（OFC）是全球光通信与网络领域的盛会，定于3月15日至19日在美国洛杉矶会议中心举行。</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>sh603773</t>
+          <t>sz000890</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>沃格光电</t>
+          <t>法尔胜</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>43.36</v>
+        <v>10.08</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>9.99</v>
+        <v>10.04</v>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>MLED|公司目前玻璃线路板（GCP）及玻璃基封装载板相关产品主要聚焦在Mini/Micro LED显示、5G-A/6G射频天线、光模块/CPO以及大算力芯片先进封装、生物芯片等领域。</t>
+          <t>光纤光缆|公司参股的普天法尔胜光通信有限公司主要产品为光纤预制棒、光纤、光缆，上述产品可以应用于在运营商基础网络通信及广播电视通信领域。</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>光纤光缆</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>智能电网</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>0.24</v>
+        <v>-1.61</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>中信建投研报指出，受益AI推动，全球PCB行业迎来新一轮上行周期。</t>
+          <t>谷歌、特斯拉以及另外5家电力设备、数据中心产业链公司宣布成立“电网利用联盟”（Utilize），旨在通过提高美国的电网利用率。</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>sh603936</t>
+          <t>sh601868</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>博敏电子</t>
+          <t>中国能建</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>15.42</v>
+        <v>3.8</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I41" s="2" t="inlineStr"/>
+        <v>10.14</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>5天3板</t>
+        </is>
+      </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>PCB+HBM|1.公司专业从事高精密印制电路板的研发、生产和销售，主要产品为多层（含HDI）和单/双面印制电路板。
-2.公司当前存储类IC载板产品主要来源于江苏博敏二期设立的IC封装载板产品线，达产后产能约1万平米/月，该产品线涵盖Memory、RF、WB-BOC、PBGA、WBCSP、FCCSP等，产品主要应用于数据存储、微机电控制、光电显示和无线射频等领域。HBM和新型SRAM产品是公司IC载板业务未来主要发展方向之一，也是后续合肥扩产项目的主力产品之一。</t>
+          <t>电力基建|公司致力于建设“行业领先、世界一流”的能源一体化方案解决商，在能源电力勘察设计技术上处于引领地位。在能源电力领域产业政策和发展规划研究，百万千瓦级超超临界机组、三代核电常规岛、清洁燃煤发电、特高压交直流和GIL综合管廊输变电、柔性交直流输电、海上风电、太阳能热发电等勘察设计技术领域具有国际领先优势。</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>PCB, HBM</t>
+          <t>电力基建</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>智能电网</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="C42" s="2" t="inlineStr"/>
+        <v>-1.61</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>谷歌、特斯拉以及另外5家电力设备、数据中心产业链公司宣布成立“电网利用联盟”（Utilize），旨在通过提高美国的电网利用率。</t>
+        </is>
+      </c>
       <c r="D42" s="2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>sz000711</t>
+          <t>sz002498</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>ST京蓝</t>
+          <t>汉缆股份</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>4.43</v>
+        <v>10.38</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>27天18板</t>
-        </is>
-      </c>
+        <v>9.959999999999999</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 主要业务包括流域水生态修复、灌区节水综合系统工程、污水治理、沿河生态景观工程、智慧水务等。</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr"/>
+          <t>输变电工程总包|公司是集电缆及附件系统、状态检测系统、输变电工程总包三个板块于一体，研发生产经营的技术密集型企业集团。</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>输变电工程总包</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>MLED</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="C43" s="2" t="inlineStr"/>
+        <v>0.37</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>根据TrendForce最新观点，Micro LED CPO方案的单位传输能耗较低，可大幅降低整体能耗至铜缆方案的5%，有望凭节能优势成为光互连替代方案。</t>
+        </is>
+      </c>
       <c r="D43" s="2" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>sh600753</t>
+          <t>sh600703</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST海钦 </t>
+          <t>三安光电</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>11.93</v>
+        <v>18.74</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>9.98</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司目前的主营业务为煤炭（含焦炭）、天然气等大宗商品供应链管理业务。</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr"/>
+          <t>MLED|旗下湖北三安主要从事Mini/Micro LED外延片与芯片生产、芯片深加工等业务，截止2025年12月，已拥有芯片产能12.5万片/月，特种封装产能2,000KK/月。</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>MLED</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="C44" s="2" t="inlineStr"/>
+        <v>-1.31</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>财联社记者在AWE 2026现场看到，特斯拉携赛博越野旅行车（Cybertruck）和人形机器人（Tesla Bot）等产品亮相。</t>
+        </is>
+      </c>
       <c r="D44" s="2" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>sz002528</t>
+          <t>sh603992</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>ST英飞拓</t>
+          <t>松霖科技</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>3.53</v>
+        <v>32.18</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>4天3板</t>
-        </is>
-      </c>
+        <v>10.02</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 英飞拓推出5G多功能智慧灯杆，支持节能照明、视频监控、新能源充电、公共WIFI、环境监测、信息发布、应急报警、5G微基站等模块，实现多种类型的感知数据采集、分析、仿真预测，提升城市综合治理。</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr"/>
+          <t>机器人|旗下松霖机器人与达闼机器人签署了战略合作框架协议，共同探索人形机器人垂直场景应用、核心部件创新升级、机器人出海及其他创新领域的产业机会。</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2542,36 +2542,36 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>0.76</v>
+        <v>-0.7100000000000001</v>
       </c>
       <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>sz000908</t>
+          <t>sz000711</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>*ST景峰</t>
+          <t>ST京蓝</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>4.58</v>
+        <v>4.65</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>5.050000000000001</v>
+        <v>4.97</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>5天3板</t>
+          <t>28天19板</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司专注医药健康产业，涉足药品研发、生产、销售等领域，产品涵盖了心脑血管、抗肿瘤、骨科、妇儿等用药领域。</t>
+          <t>ST股 | 主要业务包括流域水生态修复、灌区节水综合系统工程、污水治理、沿河生态景观工程、智慧水务等。</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
@@ -2583,36 +2583,36 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>0.76</v>
+        <v>-0.7100000000000001</v>
       </c>
       <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>sz000004</t>
+          <t>sz002528</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>*ST国华</t>
+          <t>ST英飞拓</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>5.59</v>
+        <v>3.71</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>5.08</v>
+        <v>5.1</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>5天4板</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司旗下全资子公司智游网安为专业移动应用安全综合服务提供商。</t>
+          <t>ST股 | 英飞拓推出5G多功能智慧灯杆，支持节能照明、视频监控、新能源充电、公共WIFI、环境监测、信息发布、应急报警、5G微基站等模块，实现多种类型的感知数据采集、分析、仿真预测，提升城市综合治理。</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
@@ -2624,36 +2624,36 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>0.76</v>
+        <v>-0.7100000000000001</v>
       </c>
       <c r="C47" s="2" t="inlineStr"/>
       <c r="D47" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>sh600599</t>
+          <t>sz000908</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST熊猫 </t>
+          <t>*ST景峰</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>4.62</v>
+        <v>4.81</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>5</v>
+        <v>5.02</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>6天4板</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司地处中国烟花之乡浏阳，经过3多年的发展已成为中国最大的出口鞭炮烟花公司</t>
+          <t>ST股 | 公司专注医药健康产业，涉足药品研发、生产、销售等领域，产品涵盖了心脑血管、抗肿瘤、骨科、妇儿等用药领域。</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
@@ -2665,36 +2665,36 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>0.76</v>
+        <v>-0.7100000000000001</v>
       </c>
       <c r="C48" s="2" t="inlineStr"/>
       <c r="D48" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>sz000669</t>
+          <t>sz000004</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>ST金鸿</t>
+          <t>*ST国华</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>4.41</v>
+        <v>5.87</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>5</v>
+        <v>5.01</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>3天3板</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 主营气源开发与输送、长输管网建设与管理、城市燃气经营与销售、车用加气站投资与运营、LNG点供、分布式能源项目开发与建设等。</t>
+          <t>ST股 | 公司旗下全资子公司智游网安为专业移动应用安全综合服务提供商。</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr"/>
@@ -2706,36 +2706,36 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>0.76</v>
+        <v>-0.7100000000000001</v>
       </c>
       <c r="C49" s="2" t="inlineStr"/>
       <c r="D49" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>sz000609</t>
+          <t>sz000669</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>ST中迪</t>
+          <t>ST金鸿</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>9.98</v>
+        <v>4.63</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>5.050000000000001</v>
+        <v>4.99</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>4天2板</t>
+          <t>3天3板</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司房地产项目位于重庆、成都、达州，重庆的“两江中迪广场”主要为商业项目。</t>
+          <t>ST股 | 主营气源开发与输送、长输管网建设与管理、城市燃气经营与销售、车用加气站投资与运营、LNG点供、分布式能源项目开发与建设等。</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr"/>
@@ -2747,32 +2747,36 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>0.76</v>
+        <v>-0.7100000000000001</v>
       </c>
       <c r="C50" s="2" t="inlineStr"/>
       <c r="D50" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>sh603843</t>
+          <t>sh600599</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST正平 </t>
+          <t xml:space="preserve">*ST熊猫 </t>
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>6.08</v>
+        <v>4.85</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="I50" s="2" t="inlineStr"/>
+        <v>4.98</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 2025年2月21日公司官微披露，旗下正平智算参加海东市绿色算力产业集中签约暨推介活动并签订算电协同产业园框架协议。</t>
+          <t>ST股 | 公司地处中国烟花之乡浏阳，经过3多年的发展已成为中国最大的出口鞭炮烟花公司</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
@@ -2784,32 +2788,36 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>0.76</v>
+        <v>-0.7100000000000001</v>
       </c>
       <c r="C51" s="2" t="inlineStr"/>
       <c r="D51" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>sz002656</t>
+          <t>sz000609</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>*ST摩登</t>
+          <t>ST中迪</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>3.05</v>
+        <v>10.48</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="I51" s="2" t="inlineStr"/>
+        <v>5.01</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>5天3板</t>
+        </is>
+      </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 卡奴迪路(CANUDILO)品牌已成为国内较具影响力和知名度的高级男装服饰品牌之一。</t>
+          <t>ST股 | 公司房地产项目位于重庆、成都、达州，重庆的“两江中迪广场”主要为商业项目。</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
@@ -2821,32 +2829,36 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>0.76</v>
+        <v>-0.7100000000000001</v>
       </c>
       <c r="C52" s="2" t="inlineStr"/>
       <c r="D52" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>sz000608</t>
+          <t>sz002656</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>*ST阳光</t>
+          <t>*ST摩登</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>3.63</v>
+        <v>3.2</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="I52" s="2" t="inlineStr"/>
+        <v>4.92</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司投资性房地产主要位于京沪蓉。业态上主要为集中商业和办公。</t>
+          <t>ST股 | 卡奴迪路(CANUDILO)品牌已成为国内较具影响力和知名度的高级男装服饰品牌之一。</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr"/>
@@ -2858,33 +2870,36 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>0.76</v>
+        <v>-0.7100000000000001</v>
       </c>
       <c r="C53" s="2" t="inlineStr"/>
       <c r="D53" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>sh600696</t>
+          <t>sh603843</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST岩石 </t>
+          <t xml:space="preserve">*ST正平 </t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>1.89</v>
+        <v>6.38</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I53" s="2" t="inlineStr"/>
+        <v>4.93</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 1.公司主要从事商业保理、融资租赁、不动产运营管理和大宗商品贸易。
-2.公司持有江西章贡酒业有限责任公司25%股权。章贡酒业是全国白酒工业百强企业，江西省重点酿酒企业。</t>
+          <t>ST股 | 2025年2月21日公司官微披露，旗下正平智算参加海东市绿色算力产业集中签约暨推介活动并签订算电协同产业园框架协议。</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
@@ -2896,32 +2911,36 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>0.76</v>
+        <v>-0.7100000000000001</v>
       </c>
       <c r="C54" s="2" t="inlineStr"/>
       <c r="D54" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>sh600608</t>
+          <t>sz002047</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST沪科 </t>
+          <t>*ST宝鹰</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>3.18</v>
+        <v>5.72</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>4.95</v>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司是一家信息技术行业公司，主要业务分为钢材制品加工制造及商品贸易业务两大板块。</t>
+          <t>ST股 | 宝鹰股份公告，公司正在筹划重大资产出售事项，拟向控股股东大横琴集团出售所持有的宝鹰建设100%股权。本次交易构成关联交易，预计构成重大资产重组。</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
@@ -2933,32 +2952,32 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>0.76</v>
+        <v>-0.7100000000000001</v>
       </c>
       <c r="C55" s="2" t="inlineStr"/>
       <c r="D55" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>sh600355</t>
+          <t>sz000697</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST精伦 </t>
+          <t>ST炼石</t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>1.01</v>
+        <v>10.84</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>5.21</v>
+        <v>5.04</v>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司智能控制产品是公司全资子公司上海鲍麦克斯电子科技有限公司的主营产品，鲍麦克斯专业从事通用及专用伺服驱动系统、数控系统、 缝制机器人的系列化产品研发及销售。</t>
+          <t xml:space="preserve">ST股 | 公司主要业务为航空制造业，构建“铼元素-高温合金-单晶叶片-航空零部件-航空发动机-大型无人机整机”完整的产业链。 </t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
@@ -2966,50 +2985,40 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>-0.7100000000000001</v>
       </c>
       <c r="C56" s="2" t="inlineStr"/>
       <c r="D56" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>sh600108</t>
+          <t>sz002512</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>亚盛集团</t>
+          <t>ST达华</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>6.57</v>
+        <v>4.54</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>9天7板</t>
-        </is>
-      </c>
+        <v>5.09</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>农业种植|1.公司2026年3月2日公告，目前未开展矿产相关业务，也不存在需要披露的相关重大信息。
-2.公司主要种植经营啤酒花、马铃薯、牧草、果品、药材、食葵、辣椒、枸杞、香辛料等初级农产品和加工产品，以及生产经营节水灌溉设备。</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>农业种植</t>
-        </is>
-      </c>
+          <t>ST股 | 1.在量子安全通信领域，公司已经形成了量子安全卫星互联网通信的全套解决方案，已进行试点应用。
+2.公司子公司海丝卫星是专业提供卫星互联网服务的运营商，通过直接为终端客户提供一站式全场景卫星宽带接入及行业垂直应用服务，解决海洋通信、应急通信及偏远山区等场景网络覆盖问题。</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3024,37 +3033,37 @@
       </c>
       <c r="C57" s="2" t="inlineStr"/>
       <c r="D57" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>sh601789</t>
+          <t>sz301396</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>宁波建工</t>
+          <t>宏景科技</t>
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>7.3</v>
+        <v>149.98</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>9.94</v>
+        <v>20</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>4天4板</t>
+          <t>4天2板</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>机柜位出租|宁波建工2026年3月10日公告称，目前公司及中经云均不从事算力租赁业务，中经云主营业务仅为机柜位出租（用于放置服务器、网络设备等IT硬件设施的标准化位置）。</t>
+          <t>算力租赁|公司通过高速网络整合分散的计算资源，形成可动态调度的统一算力池，支持高性能计算、AI训练等场景，以帮助客户算力组网、集成，实现算力的高效聚合、协同共享，提升算力资源利用率。</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>机柜位出租</t>
+          <t>算力租赁</t>
         </is>
       </c>
     </row>
@@ -3071,37 +3080,38 @@
       </c>
       <c r="C58" s="2" t="inlineStr"/>
       <c r="D58" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>sh600769</t>
+          <t>sh601969</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>祥龙电业</t>
+          <t>海南矿业</t>
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>15.02</v>
+        <v>13.42</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>10.04</v>
+        <v>10</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>4天2板</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>供水|公司的最终控制人为武汉东湖新技术开发区管理委员会。公司的主要业务为供水业务和建筑业务。</t>
+          <t>铁矿石+油气|1.公司注册地位于昌江县，聚焦于铁矿石和油气两大资源类产业。
+2.公司旗下控股孙公司洛克石油公司是澳大利亚一家领先的独立上游油气勘探开发公司，业务范围涵盖从油气勘探、评价到开发、生产的上游全周期业务，主要资产位于中国渤海、中国北部湾、马来西亚、澳大利亚，是一家具有近20年油气作业经验的公司。</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>供水</t>
+          <t>铁矿石, 油气</t>
         </is>
       </c>
     </row>
@@ -3118,37 +3128,34 @@
       </c>
       <c r="C59" s="2" t="inlineStr"/>
       <c r="D59" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>sh600172</t>
+          <t>sh603978</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>黄河旋风</t>
+          <t>深圳新星</t>
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>11.09</v>
+        <v>27.52</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.99</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>金刚石|公司作为超硬材料行业龙头以及唯一的全产业链布局企业，主要产品包括培育钻石及工业金刚石两大产品体系，覆盖工业金刚石、培育钻石、砂轮、刀具、钻头、锯片等，是国内乃至全球范围内品类别齐全、链条完整的超硬材料及制品制造商，可以向客户提供产品类别、规格齐全以及性能稳定的各类超硬材料及制品，包括超硬材料单晶及制品、立方氮化硼及制品、金刚石聚晶及制品以及超硬材料制品辅助材料。</t>
+          <t>锂电池+铝|1.公司全资子公司松岩冶金建设年产15,000吨的六氟磷酸锂项目。该产品为锂电池电解液中组成材料之一。
+2.公司铝晶粒细化剂及铝中间合金广泛应用于军工、航空航天、轨道交通、汽车、电子等领域高新铝合金材的制造。</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>金刚石</t>
+          <t>锂电池, 铝</t>
         </is>
       </c>
     </row>
@@ -3165,38 +3172,34 @@
       </c>
       <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>sz002667</t>
+          <t>sh603626</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>威领股份</t>
+          <t>科森科技</t>
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>33.01</v>
+        <v>24.37</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>10.02</v>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>锂矿+有色金属|1.公司主要以新能源锂电材料产业链为主体，包括锂矿选矿、基础性锂电原料锂盐加工及冶炼业务，主要产品包括锂化合物及衍生品、锂精矿及伴生品和振动筛及PC生产线等。旗下领辉科技具备锂云母年选矿产能120万吨。
-2.2025年5月20日公告，控股孙公司天津长领矿业以2.2亿元成功竞得湖南临武嘉宇矿业74.3%股权。嘉宇矿业拥有锡矿石247万吨、铅矿石119万吨、锌矿石117万吨，年开采规模30万吨，可迅速形成稳定的采选产能。</t>
+          <t>折叠屏+固态电池|1.公司已布局的折叠屏业务主要供货华为。
+2.公司持有固态电池生产、研发企业清陶能源部分股权，同时作为清陶能源供应商，公司为清陶能源及其控制的公司提供电池周边结构件产品。此外，公司与清陶成立合资公司科森清陶，以科森清陶为载体，在固态电池等领域开展相关业务合作。</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>锂矿, 有色金属</t>
+          <t>折叠屏, 固态电池</t>
         </is>
       </c>
     </row>
@@ -3213,34 +3216,33 @@
       </c>
       <c r="C61" s="2" t="inlineStr"/>
       <c r="D61" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>sh603353</t>
+          <t>sz001260</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>和顺石油</t>
+          <t>坤泰股份</t>
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>42.85</v>
+        <v>24.53</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>石油+半导体|1.公司是湖南省第一家获国家商务部批准取得成品油批发资质的民营石油企业，主营成品油批发零售，业务涵盖成品油采购、仓储、物流、批发、零售环节，在成品油流通领域形成完整产业链。
-2.2025年11月16日晚公告，公司拟以现金收购及增资方式取得上海奎芯集成电路设计有限公司不低于34%股权并通过表决权委托合计控制其51%表决权，交易完成后奎芯科技将纳入合并报表，布局高速接口IP及Chiplet解决方案。</t>
+          <t>汽车内饰产品|公司的内饰产品主要包括三大类，汽车簇绒地毯、汽车针刺地毯、汽车脚垫，公司和众多新能源车企有业务往来。</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>石油, 半导体</t>
+          <t>汽车内饰产品</t>
         </is>
       </c>
     </row>
@@ -3257,33 +3259,33 @@
       </c>
       <c r="C62" s="2" t="inlineStr"/>
       <c r="D62" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>sh600433</t>
+          <t>sh601038</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>冠豪高新</t>
+          <t>一拖股份</t>
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>3.85</v>
+        <v>15.82</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>造纸|公司是国家级重点高新技术企业，是国内首家大规模生产热敏纸的专业公司和国内目前生产设备及工艺最先进的大型无碳复写纸、不干胶标签材料生产基地，系国家税务总局、中国印钞造币总公司选定为增值税专用发票专用无碳复写纸唯一供应产品。</t>
+          <t>拖拉机|国内拖拉机行业龙头，拥有国内最完备的拖拉机制造体系，锻件、铸件、齿轮、柴油机、变速箱、覆盖件等关键零部件均由本公司自行生产。</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>造纸</t>
+          <t>拖拉机</t>
         </is>
       </c>
     </row>
@@ -3300,33 +3302,33 @@
       </c>
       <c r="C63" s="2" t="inlineStr"/>
       <c r="D63" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>sz002177</t>
+          <t>sz002869</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>御银股份</t>
+          <t>金溢科技</t>
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>9.25</v>
+        <v>24.15</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>9.99</v>
+        <v>10.02</v>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>数字货币|公司是金融设备整体解决服务商，在ATM设备产能和销售规模在国内ATM制造厂商中位居前列。公司于2020年2月17日在互动平台表示，公司有数字货币ATM机上交易的相关技术储备。</t>
+          <t>智能驾驶|公司是智慧交通领域领先的数智化解决方案及产品提供商，打造了完整的车、路、云产品体系,包括车载V2X系列产品、路端V2X边端系统集成产品、云端车路协同云平台和C-V2X车载HMI人机交互系统等。</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>数字货币</t>
+          <t>智能驾驶</t>
         </is>
       </c>
     </row>
@@ -3343,34 +3345,33 @@
       </c>
       <c r="C64" s="2" t="inlineStr"/>
       <c r="D64" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>sz002432</t>
+          <t>sz002652</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>九安医疗</t>
+          <t>扬子新材</t>
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>58.52</v>
+        <v>5.37</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>10</v>
+        <v>10.04</v>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>医疗器械+kimi|1.公司是一家在国内外具有影响力的个人健康管理产品供应商，主要从事家用医疗器械的研发、生产及销售。
-2.公司通过认购砺思资本基金份额参股Kimi。</t>
+          <t>洁净室|公司有多款产品可满足于半导体洁净室的不同需求，主要包括：高洁净彩涂板、抗静电彩涂板、HAS恒耐板等。</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>医疗器械, kimi</t>
+          <t>洁净室</t>
         </is>
       </c>
     </row>
@@ -3387,162 +3388,33 @@
       </c>
       <c r="C65" s="2" t="inlineStr"/>
       <c r="D65" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>sz002831</t>
+          <t>sz301068</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>裕同科技</t>
+          <t>大地海洋</t>
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>34.06</v>
+        <v>35.16</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>10.01</v>
+        <v>20</v>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>并购重组|2月25日，裕同科技公告，全资子公司香港裕同印刷有限公司拟收购Gelbert Eco Print Szolgáltató és Kereskedelmi Korlátolt Felelősségű Társaság合计60%的股权，本次交易完成后，Gelbert将成为公司的控股子公司，并纳入公司合并报表范围。</t>
+          <t>环保|公司是一家专注于废弃资源综合利用和循环经济发展的高新技术企业。</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>并购重组</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr"/>
-      <c r="D66" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>sz000626</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>远大控股</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="n">
-        <v>8.42</v>
-      </c>
-      <c r="H66" s="2" t="n">
-        <v>10.07</v>
-      </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>大宗商品贸易|远大物产是公司贸易领域的核心经营和管理平台，现已发展成为集贸易、物流于一体的综合性企业集团，辐射范围涵盖长三角主要大宗商品消费地区。</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>大宗商品贸易</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr"/>
-      <c r="D67" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>sz000062</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>深圳华强</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="H67" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>华为概念|公司是华为海思的重要合作伙伴，是华为海思全系列产品代理商，代理的产品包括华为海思的数字电视机顶盒芯片、智能电视芯片、显示驱动芯片、PLC传输芯片、IPCAMERA及AI芯片等。</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>华为概念</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr"/>
-      <c r="D68" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>sh603629</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>利通电子</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="n">
-        <v>63.15</v>
-      </c>
-      <c r="H68" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>算力租赁|公司目前对外出租AI算力规模已达10000P以上，其中，约4000P是以自有算力（报表中在固定资产科目列示）出租，其余是转租算力（在使用权资产科目列示）出租。</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>算力租赁</t>
+          <t>环保</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3588,12 +3460,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sh601789</t>
+          <t>sz002445</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>宁波建工</t>
+          <t>中南文化</t>
         </is>
       </c>
     </row>
@@ -3603,27 +3475,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sz002445</t>
+          <t>sh600726</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>中南文化</t>
+          <t>华电能源</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sh600108</t>
+          <t>sz000537</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>亚盛集团</t>
+          <t>绿发电力</t>
         </is>
       </c>
     </row>
@@ -3633,12 +3505,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sh600769</t>
+          <t>sh601330</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>祥龙电业</t>
+          <t>绿色动力</t>
         </is>
       </c>
     </row>
@@ -3648,12 +3520,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sh600726</t>
+          <t>sz002150</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>华电能源</t>
+          <t>正泰电源</t>
         </is>
       </c>
     </row>
@@ -3663,12 +3535,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sh600172</t>
+          <t>sh601868</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>黄河旋风</t>
+          <t>中国能建</t>
         </is>
       </c>
     </row>
@@ -3678,12 +3550,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>sz000839</t>
+          <t>sh600722</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>国安股份</t>
+          <t>金牛化工</t>
         </is>
       </c>
     </row>
@@ -3693,42 +3565,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>sh603421</t>
+          <t>sh601016</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>鼎信通讯</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>sz000537</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>绿发电力</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>sh603803</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>瑞斯康达</t>
+          <t>节能风电</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,19 +476,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K69"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="97" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="103" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="555" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="289" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -552,224 +552,213 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>存储器</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-0.06999999999999999</v>
+        <v>4.15</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>3月13日，生意社甲醇基准价为2750.00元/吨，与本月初(2200.00元/吨)相比，上涨了25.00%。</t>
+          <t>市场调查机构CounterPoint Research表示，与以往的周期不同，当前内存市场即使价格上涨，需求也不会下降。供应短缺问题至少要到2027年下半年才能得到实质性解决。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>sh600722</t>
+          <t>sz300042</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>金牛化工</t>
+          <t>朗科科技</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>16.94</v>
+        <v>45.6</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>20天10板</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>甲醇|公司的主要业务为甲醇的生产和销售，产品方式为焦炉气制甲醇。公司的主要业务由持股50%的控股子公司金牛旭阳经营，金牛旭阳拥有的甲醇生产能力为20万吨/年。</t>
+          <t>存储芯片+算力|1.公司致力于为全球存储应用领域提供解决方案，存储产品已经覆盖SSD固态硬盘、DRAM内存条、嵌入式存储和移动存储等领域。
+2.2024年2月，公司与韶关政府、中兴通讯和韶关数投签署合作协议，拟在建设算力产业生态、提升数据中心建设水平和数字化转型深度合作方面展开合作。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>甲醇</t>
+          <t>存储芯片, 算力</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>存储器</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>-0.06999999999999999</v>
+        <v>4.15</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>3月13日，生意社甲醇基准价为2750.00元/吨，与本月初(2200.00元/吨)相比，上涨了25.00%。</t>
+          <t>市场调查机构CounterPoint Research表示，与以往的周期不同，当前内存市场即使价格上涨，需求也不会下降。供应短缺问题至少要到2027年下半年才能得到实质性解决。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sh600691</t>
+          <t>sz000620</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>潞化科技</t>
+          <t>盈新发展</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>4.43</v>
+        <v>3.31</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.969999999999999</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>煤化工|公司主要业务包括化工产品和化工机械设备的生产和销售，化工产品研发及工程总承包设计等，主要产品包括尿素、聚氯乙烯、烯烃、烧碱、双氧水、甲醇等。</t>
+          <t>存储芯片|盈新发展公告称，公司与广东长兴信息管理咨询有限公司、张治强签署《股权收购意向协议》，拟以支付现金方式收购长兴咨询、张治强合计持有的广东长兴半导体科技有限公司81.8091%股权。本次交易完成后，公司预计将实现对长兴半导体控股。本次交易不构成重大资产重组，不涉及发行股份，不会导致公司控制权变更。广东长兴半导体科技有限公司成立于2012年，是一家专注于存储器芯片封装测试和存储模组制造的高新技术企业。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>煤化工</t>
+          <t>存储芯片</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>存储器</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>-0.06999999999999999</v>
+        <v>4.15</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3月13日，生意社甲醇基准价为2750.00元/吨，与本月初(2200.00元/吨)相比，上涨了25.00%。</t>
+          <t>市场调查机构CounterPoint Research表示，与以往的周期不同，当前内存市场即使价格上涨，需求也不会下降。供应短缺问题至少要到2027年下半年才能得到实质性解决。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sh600370</t>
+          <t>sh600667</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">三房巷  </t>
+          <t>太极实业</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>2.73</v>
+        <v>11.26</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.959999999999999</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>化工|公司成为“PTA-瓶级聚酯切片”一体化布局的优势企业，PTA产品是郑州商品交易所PTA交割免检品牌，已开发出多种全系列的瓶级聚酯切片产品。</t>
+          <t>存储芯片|公司半导体业务是为DRAM和NANDFlash等集成电路产品提供封装、封装测试、模组装配和模组测试等后工序服务。控股子公司海太公司拥有完整的封装测试生产线与SK海力士12英寸晶圆生产线紧密配套。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>存储芯片</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>存储器</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-0.06999999999999999</v>
+        <v>4.15</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3月13日，生意社甲醇基准价为2750.00元/吨，与本月初(2200.00元/吨)相比，上涨了25.00%。</t>
+          <t>市场调查机构CounterPoint Research表示，与以往的周期不同，当前内存市场即使价格上涨，需求也不会下降。供应短缺问题至少要到2027年下半年才能得到实质性解决。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sz002470</t>
+          <t>sz300606</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>金正大</t>
+          <t>金太阳</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>3.22</v>
+        <v>40.73</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>9.9</v>
+        <v>20.01</v>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>化肥|公司的复合肥、缓控释肥、硝基复合肥、水溶肥及其他新型肥料在技术和市场占有率方面居国内领先地位，具有较强的竞争优势。</t>
+          <t>存算一体芯片|参股中科声龙专注于为全球客户提供算力芯片系统的研发、设计、生产、销售和相应的技术指导等综合服务，在基于3D异质集成的大规模存算一体芯片领域处于业界领先水平。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>化肥</t>
+          <t>存算一体芯片</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>存储器</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>-0.06999999999999999</v>
+        <v>4.15</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3月13日，生意社甲醇基准价为2750.00元/吨，与本月初(2200.00元/吨)相比，上涨了25.00%。</t>
+          <t>市场调查机构CounterPoint Research表示，与以往的周期不同，当前内存市场即使价格上涨，需求也不会下降。供应短缺问题至少要到2027年下半年才能得到实质性解决。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sz002165</t>
+          <t>sh603986</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>红 宝 丽</t>
+          <t>兆易创新</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>12.76</v>
+        <v>306.16</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>10</v>
@@ -777,731 +766,733 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>光刻胶+化工|1.公司异丙醇胺产品是一种绿色环保的精细化工原料，可应用于电子清洗行业，例如光刻胶在应用中的残留物清洗。
-2.公司泰兴环氧丙烷产业基地具备12万吨环氧丙烷产能，该项目采用具有自主知识产权的共氧化法新工艺，是国内首套工业化装置，整个生产过程仅产生少量的工业废水。</t>
+          <t>存储芯片|公司是中国大陆领先的闪存芯片设计企业，存储器产品包括闪存芯片（NORFlash、NANDFlash）和动态随机存取存储器（DRAM）。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>光刻胶, 化工</t>
+          <t>存储芯片</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>存储器</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-0.06999999999999999</v>
+        <v>4.15</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3月13日，生意社甲醇基准价为2750.00元/吨，与本月初(2200.00元/吨)相比，上涨了25.00%。</t>
+          <t>市场调查机构CounterPoint Research表示，与以往的周期不同，当前内存市场即使价格上涨，需求也不会下降。供应短缺问题至少要到2027年下半年才能得到实质性解决。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>sh603175</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>超颖电子</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>88.19</v>
+      </c>
+      <c r="H7" s="2" t="n">
         <v>10</v>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>sz002109</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>兴化股份</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>9.98</v>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>煤化工|全资子公司兴化化工主营煤制甲醇，产能30万吨/年。</t>
+          <t>PCB+存储芯片|1.公司主营业务是印制电路板的研发、生产和销售，拥有HDI板、厚铜板、金属基板、高频板、高速板等特殊材料、特殊工艺产品的生产能力，产品广泛应用于汽车电子、显示、储存、消费电子、通信等领域，并积极布局AR/VR、航天卫星等领域。
+2.在储存领域，公司产品主要应用于机械硬盘、固态硬盘、内存条等，与全球机械硬盘制造商龙头希捷、西部数据及全球知名固态硬盘制造商海力士等建立了稳定合作。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>煤化工</t>
+          <t>PCB, 存储芯片</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>深海科技</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>-0.06999999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3月13日，生意社甲醇基准价为2750.00元/吨，与本月初(2200.00元/吨)相比，上涨了25.00%。</t>
+          <t>3月16日出版的第6期《求是》杂志将发表重要文章《推动海洋经济高质量发展》。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sz002637</t>
+          <t>sz002086</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>赞宇科技</t>
+          <t>东方海洋</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>15.87</v>
+        <v>2.5</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>9.98</v>
+        <v>10.13</v>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>化工+生物柴油|1.公司油脂化工业务主要由杭州油化、南通凯塔和杜库达三家控股子公司负责生产经营。油脂化工业务主要以棕榈油为原料，主要产品包括硬脂酸、脂肪酸、油酸、脂肪醇、脂肪胺、二聚酸、聚酰胺树脂、甘油及其他助剂等油脂化工产品。
-2.2023年8月17日公司在机构调研中表示，公司将在马来西亚拿笃POIC工业园投资建设年产55万吨的油脂化学品项目,包括20万吨生物柴油、20万吨脂肪酸甲酯、10万吨脂肪醇、5万吨甘油。</t>
+          <t>海洋经济|公司与中科院海洋所、中国海洋大学等大院大所深度合作，共同搭建具有国内领先水平、功能配套的保种、育种、良种繁育一体化的科研推广平台。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>化工, 生物柴油</t>
+          <t>海洋经济</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>深海科技</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-0.06999999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3月13日，生意社甲醇基准价为2750.00元/吨，与本月初(2200.00元/吨)相比，上涨了25.00%。</t>
+          <t>3月16日出版的第6期《求是》杂志将发表重要文章《推动海洋经济高质量发展》。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sh600746</t>
+          <t>sz002427</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>江苏索普</t>
+          <t>尤夫股份</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>9.26</v>
+        <v>7.69</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>9.98</v>
+        <v>10.01</v>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>化工|公司及子公司主营业务为包括醋酸及衍生品、氯碱等化工原料的生产与销售。</t>
+          <t>化工+海洋经济|公司开发的拒海水聚酯工业丝产品已广泛应用于船舶、海洋钻井、深海风电系泊缆绳，产品通过DNV、ABS船级社测试认证。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>化工, 海洋经济</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>深海科技</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-0.06999999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3月13日，生意社甲醇基准价为2750.00元/吨，与本月初(2200.00元/吨)相比，上涨了25.00%。</t>
+          <t>3月16日出版的第6期《求是》杂志将发表重要文章《推动海洋经济高质量发展》。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>sz002278</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>神开股份</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="H10" s="2" t="n">
         <v>10</v>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>sz002669</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>康达新材</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>15.35</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>10.04</v>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>化工+光刻胶|1.公司已经成为国内领先的精细化工高端制造企业之一，主要从事中、高端胶粘剂及新材料产品的研发、生产和销售。
-2.控股子公司彩晶光电目前已系统掌握TFT-LCD液晶面板及半导体集成电路IC正性光刻胶核心原材料光引发剂PAC&amp;PAG的生产技术及工艺。</t>
+          <t>油气+海洋经济|公司的部分仪器和设备已用于深海油气勘探和开发，代表案例如神开录井核心设备SK-3007氢焰色谱仪以及其配套使用的SK-7H06恒量脱气器，成功应用于我国自主设计建造的首艘大洋钻探船“梦想”号，助力我国深海油气勘探；又如亚洲第一深水导管架平台“海基一号”所使用的全套井口设备均为神开自主设计研发和制造，助力我国海上油气增储上产。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>化工, 光刻胶</t>
+          <t>油气, 海洋经济</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>深海科技</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>-0.06999999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3月13日，生意社甲醇基准价为2750.00元/吨，与本月初(2200.00元/吨)相比，上涨了25.00%。</t>
+          <t>3月16日出版的第6期《求是》杂志将发表重要文章《推动海洋经济高质量发展》。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sh600227</t>
+          <t>sz002724</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">赤天化  </t>
+          <t>海洋王</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>4.37</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>10.08</v>
+        <v>10.05</v>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>化肥+甲醇|公司是贵州省最大的氮肥生产企业，公司化肥化工生产基地分别是以天然气为原料生产的赤水化工分公司（年产63万吨尿素）和以煤为生产原料的公司全资子公司桐梓化工（年产52万吨尿素、30万吨甲醇）。</t>
+          <t>海洋经济|公司是一家主做工业照明的企业，照明产品广泛应用在铁路、电网、海油钻采、矿井采矿、智慧港口、海上平台、智慧电厂、应急救灾、工业设备、制造业厂房等工业应用场景。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>化肥, 甲醇</t>
+          <t>海洋经济</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>-0.8099999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>英国自4月1日起取消33项风电组件进口关税，叶片、电缆等核心部件税率由6%、2%降至0，旨在释放220亿英镑投资，加速北海海风装机落地。</t>
+          <t>中信证券指出，英伟达GTC 2026大会召开在即，预计公司的芯片产品矩阵有望进一步扩充，除Vera Rubin AI平台的全套六款核心芯片外，有可能在大会上披露Rubin Ultra芯片及机柜更多细节。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sz002487</t>
+          <t>sz000890</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>大金重工</t>
+          <t>法尔胜</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>80.65000000000001</v>
+        <v>12.2</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>3天3板</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>风电|公司主营业务为风力发电设备制造，主要产品有常规陆塔、大直径分片式陆塔、低风速柔性高塔、海塔、单桩、群桩、导管架、海上升压站等风电设备及相关零部件。</t>
+          <t>光纤光缆|公司参股的普天法尔胜光通信有限公司主要产品为光纤预制棒、光纤、光缆，上述产品可以应用于在运营商基础网络通信及广播电视通信领域。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>光纤光缆</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-0.8099999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>英国自4月1日起取消33项风电组件进口关税，叶片、电缆等核心部件税率由6%、2%降至0，旨在释放220亿英镑投资，加速北海海风装机落地。</t>
+          <t>中信证券指出，英伟达GTC 2026大会召开在即，预计公司的芯片产品矩阵有望进一步扩充，除Vera Rubin AI平台的全套六款核心芯片外，有可能在大会上披露Rubin Ultra芯片及机柜更多细节。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sz002531</t>
+          <t>sz002980</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>天顺风能</t>
+          <t>华盛昌</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>12.42</v>
+        <v>38.65</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>10.01</v>
+        <v>9.99</v>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>风电|公司为国内领先的风塔专业生产商，主营产品为1.5MW及以上功率风机的风塔。</t>
+          <t>并购重组+光通信|华盛昌公告称，公司拟以现金方式收购深圳市伽蓝特科技有限公司100%股权，整体估值暂定为4.6亿元。伽蓝特专注于仪器仪表测试测量行业中的光通信模块和光芯片测试领域。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>并购重组, 光通信</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>-0.8099999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>英国自4月1日起取消33项风电组件进口关税，叶片、电缆等核心部件税率由6%、2%降至0，旨在释放220亿英镑投资，加速北海海风装机落地。</t>
+          <t>中信证券指出，英伟达GTC 2026大会召开在即，预计公司的芯片产品矩阵有望进一步扩充，除Vera Rubin AI平台的全套六款核心芯片外，有可能在大会上披露Rubin Ultra芯片及机柜更多细节。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sz300185</t>
+          <t>sh603738</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>通裕重工</t>
+          <t>泰晶科技</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>4.21</v>
+        <v>25.31</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>19.94</v>
+        <v>10</v>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>风电|公司是国内重型装备制造领域新兴的民营企业，主要从事大型自由锻件产品的研发、生产和销售，主要产品为MW级风力发电机主轴和DN50-1600m球墨铸铁管管模等大型锻件。公司为大型铸锻件行业风电、模具、核电领域的行业龙头；也是是国内最大的管模提供商。</t>
+          <t>光通信|公司针对光通信200G、400G、800G、1.6T市场推出了高基频、高精度、低相噪CMOS、LVDS差分输出时钟解决方案，随着光模块传输速率升级，对应使用超高频、差分时钟产品，在技术上提出更高性能匹配要求。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>光通信</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>-0.8099999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>英国自4月1日起取消33项风电组件进口关税，叶片、电缆等核心部件税率由6%、2%降至0，旨在释放220亿英镑投资，加速北海海风装机落地。</t>
+          <t>中信证券指出，英伟达GTC 2026大会召开在即，预计公司的芯片产品矩阵有望进一步扩充，除Vera Rubin AI平台的全套六款核心芯片外，有可能在大会上披露Rubin Ultra芯片及机柜更多细节。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sh603062</t>
+          <t>sh603052</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>麦加芯彩</t>
+          <t>可川科技</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>56.29</v>
+        <v>64.13</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>风电+储能|1.公司风力发电设备防护涂层系列产品可以应用到风电叶片涂层防护及塔筒保护领域，目前已在国内主要风电叶片厂成功应用并且得到了认可。
-2.公司已实现对某头部企业储能涂料供货，标志着公司储能涂料技术的储备已经得以现实应用。</t>
+          <t>光通信+复合铝箔|1.2023年6月19日公告，为把握全球半导体行业光芯片、光模块产业发展机遇，公司计划与自然人吕志远签署《英特磊半导体技术(上海)股份有限公司之股东协议》(简称“《股东协议》”，共同发起设立英特磊，主要从事光通信模块及激光传感器等业务。英特磊注册资本为人民币5,000万元，其中公司认缴出资额为人民币2,550万元，持股比例为51%。
+2.2024年11月18日公告，复合集流体项目已采购了试验线和规模化生产线，并于2024年第三季度将规模化生产线的试产产品向客户送样验证，公司已于近日收到某国际知名消费电子电池生产商关于复合铝箔的首笔小额订单。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>风电, 储能</t>
+          <t>光通信, 复合铝箔</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>-0.8099999999999999</v>
+        <v>-0.51</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>英国自4月1日起取消33项风电组件进口关税，叶片、电缆等核心部件税率由6%、2%降至0，旨在释放220亿英镑投资，加速北海海风装机落地。</t>
+          <t>航运数据显示，目前有21艘满载尿素、硫磺和磷肥的船只滞留波斯湾，涉及近百万吨化肥原料；若航运中断常态化，全球肥料原料供应可能会减少30%至50%。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sh605222</t>
+          <t>sh600227</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>起帆电缆</t>
+          <t xml:space="preserve">赤天化  </t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>23.06</v>
+        <v>4.81</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
+        <v>10.07</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7天4板</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>核电+风电|1.公司可用于核电领域的产品有核电站用防火电力及信号组合电缆、核电站用铝合金导体组合电缆等系列。
-2.公司全资子公司宜昌起帆电缆有限公司已开始生产大长度海底电缆，有关海缆生产线已投入运营，相关产品已运用到海上风电项目。</t>
+          <t>化肥|公司是贵州省最大的氮肥生产企业，公司化肥化工生产基地分别是以天然气为原料生产的赤水化工分公司（年产63万吨尿素）和以煤为生产原料的公司全资子公司桐梓化工（年产52万吨尿素、30万吨甲醇）。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>核电, 风电</t>
+          <t>化肥</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>-0.8099999999999999</v>
+        <v>-0.51</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>英国自4月1日起取消33项风电组件进口关税，叶片、电缆等核心部件税率由6%、2%降至0，旨在释放220亿英镑投资，加速北海海风装机落地。</t>
+          <t>航运数据显示，目前有21艘满载尿素、硫磺和磷肥的船只滞留波斯湾，涉及近百万吨化肥原料；若航运中断常态化，全球肥料原料供应可能会减少30%至50%。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sh601218</t>
+          <t>sh600370</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>吉鑫科技</t>
+          <t xml:space="preserve">三房巷  </t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>6.94</v>
+        <v>3</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
+        <v>9.890000000000001</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>风电|公司是一家专注于研发、制造和销售大型风力发电机组用零部件的龙头企业，主要生产750KW-12MW风力发电机组用轮毂、底座、轴、轴承座等系列产品。</t>
+          <t>化工|公司成为“PTA-瓶级聚酯切片”一体化布局的优势企业，PTA产品是郑州商品交易所PTA交割免检品牌，已开发出多种全系列的瓶级聚酯切片产品。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>化工</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>-0.8099999999999999</v>
+        <v>-0.51</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>英国自4月1日起取消33项风电组件进口关税，叶片、电缆等核心部件税率由6%、2%降至0，旨在释放220亿英镑投资，加速北海海风装机落地。</t>
+          <t>航运数据显示，目前有21艘满载尿素、硫磺和磷肥的船只滞留波斯湾，涉及近百万吨化肥原料；若航运中断常态化，全球肥料原料供应可能会减少30%至50%。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sh603248</t>
+          <t>sh605366</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>锡华科技</t>
+          <t>宏柏新材</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>28.2</v>
+        <v>10.79</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>9.98</v>
+        <v>9.99</v>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>风电|公司主要从事大型高端装备专用部件的研发、制造与销售，产品结构以风电齿轮箱专用部件为主、注塑机厚大专用部件为辅，是全球行业领先、质量可靠、技术卓越的大型高端装备专用部件制造商。</t>
+          <t>化工|公司主营业务为功能性硅烷、纳米硅材料等硅基新材料及其他化学助剂的研发、生产与销售，是我国功能性硅烷，特别是含硫硅烷细分领域中具备循环经济体系及世界领先产业规模的企业之一，拥有全球产量最大的含硫硅烷（含固体硅烷）生产线。</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>化工</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>核电</t>
+          <t>航运</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>-0.83</v>
+        <v>3.29</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>国盛证券指出，2026年中国聚变产业有望超预期加速发展，多个核聚变项目订单招标总额有望迎来5倍左右增长。</t>
+          <t>中信建投研报称，由库存安全阈值上移催生的常规补库与安全补库叠加需求，若在政策边际松动或行业旺季临近阶段集中释放，将成为驱动油运行业下一轮运价大幅上行的核心催化因素。</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sh603169</t>
+          <t>sh600751</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>兰石重装</t>
+          <t>海航科技</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>12.8</v>
+        <v>4.32</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>9.969999999999999</v>
+        <v>9.92</v>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>核聚变+油气|1.公司研制的新型（微通道）高效紧凑型焊接式热交换器（PCHE）在核工业西南物理研究院承担的“中国聚变工程实验堆（CFETR）氦冷固态包层热工测试项目中实现该设备在国内核聚变领域的首次应用。
-2.公司主要业务包括：炼油、化工、煤化工、核电、生物医药等能源行业高端压力容器、快速锻造液压机组、板式换热器等装备的研发、设计、制造及检测、检修服务，炼油化工、煤化工等能源行业工程总承包。</t>
+          <t>航运|公司成立之初便立足航运市场，以国际近洋集装箱班轮运输、国内沿海集装箱班轮运输及船务代理和货运代理等为主营业务，在天津市乃至全国都属较早布局航运市场的企业之一。公司总可控运力达105万载重吨。</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>核聚变, 油气</t>
+          <t>航运</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>核电</t>
+          <t>航运</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>-0.83</v>
+        <v>3.29</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>国盛证券指出，2026年中国聚变产业有望超预期加速发展，多个核聚变项目订单招标总额有望迎来5倍左右增长。</t>
+          <t>中信建投研报称，由库存安全阈值上移催生的常规补库与安全补库叠加需求，若在政策边际松动或行业旺季临近阶段集中释放，将成为驱动油运行业下一轮运价大幅上行的核心催化因素。</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sh603280</t>
+          <t>sh601975</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>南方路机</t>
+          <t>招商南油</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>40.7</v>
+        <v>4.81</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>10</v>
+        <v>10.07</v>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>核电+机器人|1.公司生产的核电专用搅拌站，能够满足核岛建设关于连续浇筑、大体积、低温混凝土等严格技术要求，技术难度高，实现国产设备在核电建设专用站的进口替代，已成功运用在中广核核电项目。
-2.公司的建筑垃圾资源化处理设备的智能分拣机器人，能高效应对混合建筑垃圾、建筑混合废弃物、橡胶、木头等物料进行分拣，实现对建筑垃圾、装修垃圾等物料的分类回收和再利用，与公司其他产品均可广泛运用于灾后重建。</t>
+          <t>油运|公司是招商局集团旗下从事油轮运输的专业化公司，市场定位为全球石化产品的运输服务商。</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>核电, 机器人</t>
+          <t>油运</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>核电</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>-0.83</v>
+        <v>2.19</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>国盛证券指出，2026年中国聚变产业有望超预期加速发展，多个核聚变项目订单招标总额有望迎来5倍左右增长。</t>
+          <t>分析师郭明錤最新供应链调查，英伟达已与PCB厂商就下一代覆铜板(CCL)材料M10启动测试，目标应用涵盖Rubin Ultra及Feynman平台的正交背板与交换刀片主板。</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>sz002438</t>
+          <t>sh600545</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>江苏神通</t>
+          <t>卓郎智能</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>19.26</v>
+        <v>4.21</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>9.99</v>
+        <v>9.92</v>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>商业航天+核电|1.公司参股企业神通新能源已与航天五院在卫星电推进系统阀门建立合作关系。
-2.公司作为我国核电阀门设备的主要供应商之一，投入研发力量开展包括核聚变科学装置在内的各类核能应用技术装备所需特种阀门的研制，已取得小批量订单。</t>
+          <t>玻纤捻线机|2025年6月28日公司官微透露，公司与国际复材签订了加捻事业部史上最大额玻璃纤维捻线机订单。玻纤凭借其低介电常数等特性，已成为制造高频高速PCB与高性能芯片封装材料的不二之选。</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>商业航天, 核电</t>
+          <t>玻纤捻线机</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>核电</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>-0.83</v>
+        <v>2.19</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>国盛证券指出，2026年中国聚变产业有望超预期加速发展，多个核聚变项目订单招标总额有望迎来5倍左右增长。</t>
+          <t>分析师郭明錤最新供应链调查，英伟达已与PCB厂商就下一代覆铜板(CCL)材料M10启动测试，目标应用涵盖Rubin Ultra及Feynman平台的正交背板与交换刀片主板。</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>sh601611</t>
+          <t>sz002636</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>中国核建</t>
+          <t>金安国纪</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>19.21</v>
+        <v>31.96</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>10.02</v>
@@ -1509,452 +1500,452 @@
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>核聚变|公司参与了“国际热核聚变实验堆（ITER）”项目建设，成功实现主机安装第一阶段相关任务。</t>
+          <t>PCB|公司主要产品包括各种通用FR-5、FR-4、CEM-3等系列覆铜板及铝基覆铜板、半固化片等和特殊指标要求的无卤环保、高阻燃、耐CAF、高TG、高CTI等系列覆铜板；此外，公司还从事覆铜板的原材料电子级玻纤布以及下游PCB产品的生产和销售。</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>核聚变</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>热泵</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>1.02</v>
+        <v>0.73</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>方正证券认为，在欧盟推动淘汰俄罗斯天然气进口，转而增加对中东LNG依赖的背景下，若天然气价格再度大涨，势必带动欧洲户储、热泵产品销售提升。</t>
+          <t>工信部2026年度拟在50个地区开展城域“毫秒用算”专项行动，提升算力高效运载能力，推动算网融合发展。</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>sh603366</t>
+          <t>sz002467</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>日出东方</t>
+          <t>二六三</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>10.32</v>
+        <v>7.52</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>10.02</v>
+        <v>9.94</v>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>热泵|空气源热泵（空气能）产品是公司重点发展的产品类别。公司为加强空气源热泵产品的销售能力，在原有销售队伍和渠道的基础上，构建了更为专业的销售队伍和更加细分的销售渠道，经销商数量维持稳定增长。</t>
+          <t>AI应用+算力|1.公司在WebRTC、QoS、实时音视频等核心技术基础上，深度融合AI与大模型能力，打造智能通信中枢。通过自研AICC人工智能客户联络中心，实现企业邮箱、视频直播等场景的端到端智能化交互。同时，研发投入持续向AI驱动的云通信解决方案倾斜，构建跨网络动态负载均衡与智能运维体系，支撑亿级并发场景下的服务稳定性。
+2.公司2020年4月22日在互动平台表示，公司的子公司上海二六三通信有限公司与NTT合资的控股子公司上海奈盛通信科技有限公司是国内第一家由民营通信公司与国际一流运营商合资经营的公司，其业务平台为国内第一个以国际运营商标准自建的IDC云计算平台。</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>热泵</t>
+          <t>AI应用, 算力</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>热泵</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>1.02</v>
+        <v>0.73</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>方正证券认为，在欧盟推动淘汰俄罗斯天然气进口，转而增加对中东LNG依赖的背景下，若天然气价格再度大涨，势必带动欧洲户储、热泵产品销售提升。</t>
+          <t>工信部2026年度拟在50个地区开展城域“毫秒用算”专项行动，提升算力高效运载能力，推动算网融合发展。</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>sz002543</t>
+          <t>sz002990</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>万和电气</t>
+          <t>盛视科技</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>9.789999999999999</v>
+        <v>28.95</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>热泵|公司是国内热水器行业龙头企业，拥有产品、渠道与品牌优势，空气能热泵业务发展潜力大。子公司广东万和新能源科技有限公司负责空气能热泵相关业务。</t>
+          <t>算力+AI应用|1.2023年11月3日公司在互动平台表示，公司在武汉和深圳两地均配备有充足的算力集群，可对产品研发和项目交付的模型训练工作提供支撑服务。
+2.公司持续加大对人工智能、大数据、物联网等新一代信息技术的研发投入，旨在为客户提供符合未来发展的智能产品和“AI+行业”解决方案。公司在智慧口岸领域深耕二十余年，已成长为国内领先的智慧口岸查验系统整体解决方案提供商。同时，基于在智慧口岸领域的技术积累，公司已将业务拓展至智能交通、智慧机场、智慧园区、智慧城市管理等其他应用领域。</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>热泵</t>
+          <t>算力, AI应用</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>热泵</t>
+          <t>智能电网</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>1.02</v>
+        <v>-0.96</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>方正证券认为，在欧盟推动淘汰俄罗斯天然气进口，转而增加对中东LNG依赖的背景下，若天然气价格再度大涨，势必带动欧洲户储、热泵产品销售提升。</t>
+          <t>据南方电网消息，今年前两月，公司完成固定资产投资250.8亿元，同比增长95.3%；公司累计完成项目物资供应121亿元，同比增加57%。</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>sz002084</t>
+          <t>sh603421</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>海鸥住工</t>
+          <t>鼎信通讯</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>4.29</v>
+        <v>10.32</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
+        <v>10.02</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>5天3板</t>
+        </is>
+      </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>热泵|2022年8月24日公司在互动平台表示，公司控股子公司珠海爱迪生自主研发的恒温控制类阀组及系统部分应用于大功率热水器、空气能热泵、燃气热水器等产品。</t>
+          <t>半导体+电网设备|1.鼎信通讯在互动平台表示，公司芯片开发采用平头哥的CK802 32位内核架构，平头哥与公司签订有全面技术授权协议。
+2.公司的主营业务为低压用电系统产品的研发、生产、销售及服务，主要产品包括低压电力线载波通信模块（含芯片）产品、采集终端设备、智能电能表和配电终端等，主要应用于国家智能电网的用电信息采集系统和配网自动化系统。</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>热泵</t>
+          <t>半导体, 电网设备</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>医疗器械</t>
+          <t>智能电网</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.96</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>英科医疗发布涨价函称，丁二烯上涨约25.6%，丙烯腈上涨约17%，DOTP上涨约15%，辛醇上涨约18%。</t>
+          <t>据南方电网消息，今年前两月，公司完成固定资产投资250.8亿元，同比增长95.3%；公司累计完成项目物资供应121亿元，同比增加57%。</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>sz002382</t>
+          <t>sz000533</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>蓝帆医疗</t>
+          <t>顺钠股份</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>7.59</v>
+        <v>18.66</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>10</v>
+        <v>10.02</v>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>医用手套|蓝帆医疗在机构调研时表示，2025年末公司已通过一系列举措大幅改善手套业务成本竞争力，即便外部环境无进一步大幅改善，在2026年初的价格形势下，预期手套业务也将从2025年大幅亏损转向2026年明显盈利，释放明确业绩弹性。</t>
+          <t>核聚变+电网设备|1.公司研制的特殊用途干式变压器包括国际热核聚变实验堆（ITER）试验平台变压器。
+2.公司控股孙公司顺特设备在超算中心和数据中心这两个领域提供过干式变压器产品，曾向阿里巴巴、秦淮数据有限公司、万国数据服务有限公司、数据港股份有限公司等客户提供过变压器设备。</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>医用手套</t>
+          <t>核聚变, 电网设备</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>医疗器械</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>-0.27</v>
+        <v>-2.08</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>英科医疗发布涨价函称，丁二烯上涨约25.6%，丙烯腈上涨约17%，DOTP上涨约15%，辛醇上涨约18%。</t>
+          <t>随着人工智能的发展、算力需求的增加，对上游能源行业的拉动作用比较明显。1—2月份，电力、热力生产和供应业增加值同比增长5.1%。</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>sz002950</t>
+          <t>sh600396</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>奥美医疗</t>
+          <t>华电辽能</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>11.3</v>
+        <v>4.27</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>10.03</v>
+        <v>10.05</v>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>医用手套|公司长期专注于医疗健康事业，主营业务为医用敷料等一次性医用耗材的研发、生产和销售，产品包括丁腈橡胶医用外科手套。</t>
+          <t>电力|公司是中国华电集团公司的实际控制的上市公司、中央企业的三级单位，同时也是一家集火力发电、风力发电、煤炭营销、供热、供汽为一体的综合性区域基础能源企业。</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>医用手套</t>
+          <t>电力</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>医疗器械</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>-0.27</v>
+        <v>-2.08</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>英科医疗发布涨价函称，丁二烯上涨约25.6%，丙烯腈上涨约17%，DOTP上涨约15%，辛醇上涨约18%。</t>
+          <t>随着人工智能的发展、算力需求的增加，对上游能源行业的拉动作用比较明显。1—2月份，电力、热力生产和供应业增加值同比增长5.1%。</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>sz300981</t>
+          <t>sz002310</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>中红医疗</t>
+          <t>东方新能</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>15.77</v>
+        <v>2.99</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>20.02</v>
+        <v>9.93</v>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>医用手套|公司主要从事高品质丁腈手套、PVC手套等医用及工业用一次性防护手套的研发、生产与销售。</t>
+          <t>绿电|2025年12月15日公告，公司拟以现金支付方式购买海城锐海100%股权和电投瑞享80%股权。其中，海城锐海100%股权拟通过在天津产权交易中心摘牌方式购买。标的资产的审计和评估工作尚未完成，评估值及交易价格均尚未确定（海城锐海100%股权在天津产权交易所的挂牌转让底价为1410万元）。本次交易预计构成重大资产重组。通过本次交易，东方园林新增光伏电站、风电场的投资、开发、建设和运营等新能源业务。</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>医用手套</t>
+          <t>绿电</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>储能</t>
+          <t>复合集流体</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>-1.64</v>
+        <v>2.81</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>中国电建公告称，公司与阿布扎比未来能源公司签订了阿联酋阿布扎比RTC2.1GW+7.75GWh光储项目EPC合同，合同金额折合人民币约为139.62亿元。</t>
+          <t>3月10日，建滔集团发布涨价通知，通知表示，自当日接单起，对板料、PP(半固化片)及铜箔加工费等所有厚度规格产品同步提价10%。</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>sh601669</t>
+          <t>sz002426</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>中国电建</t>
+          <t>胜利精密</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>7.19</v>
+        <v>4.47</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>9.94</v>
+        <v>10.1</v>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>签订储能大单|中国电建公告称，公司阿布扎比分公司与下属子公司中国电建集团华东勘测设计研究院有限公司组成联营体，与阿布扎比未来能源公司签订了阿联酋阿布扎比RTC2.1GW+7.75GWh光储项目EPC合同，合同金额折合人民币约为139.62亿元。</t>
+          <t>复合铜箔|公司复合铜箔项目采用PET或PP作为基材原料，选择“基材-磁控溅射-水镀”的工艺路线；目前送样检测的客户为动力电池厂商</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>签订储能大单</t>
+          <t>复合铜箔</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>储能</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>-1.64</v>
+        <v>1.1</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>中国电建公告称，公司与阿布扎比未来能源公司签订了阿联酋阿布扎比RTC2.1GW+7.75GWh光储项目EPC合同，合同金额折合人民币约为139.62亿元。</t>
+          <t>国家统计局发布数据显示，1—2月份，社会消费品零售总额86079亿元，同比增长2.8%，比上年12月份加快1.9个百分点。</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>sz003027</t>
+          <t>sz000639</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>同兴科技</t>
+          <t>西王食品</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>24.52</v>
+        <v>3.14</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>10</v>
+        <v>10.18</v>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>储能电池|2022年9月16日公告，公司近期与中国科大签署了《中国科学技术大学同兴环保科技股份有限公司共建“中国科大-同兴环保储能电池材料及器件联合实验室”合作协议》，决定共同建立“中国科大-同兴环保储能电池材料及器件联合实验室”，开展锂离子电池、钠离子电池等储能电池电极材料相关的基础、前瞻性技术和关键共性技术研究，并进行产学研合作。</t>
+          <t>食用油|国内最大的玉米胚芽油生产基地，主要生产销售西王牌系列健康食用油。</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>储能电池</t>
+          <t>食用油</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>储能</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>-1.64</v>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>中国电建公告称，公司与阿布扎比未来能源公司签订了阿联酋阿布扎比RTC2.1GW+7.75GWh光储项目EPC合同，合同金额折合人民币约为139.62亿元。</t>
-        </is>
-      </c>
+        <v>0.48</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr"/>
       <c r="D31" s="2" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>sz002323</t>
+          <t>sz000908</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>雅博股份</t>
+          <t>*ST景峰</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>2.54</v>
+        <v>5.3</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>9.959999999999999</v>
-      </c>
-      <c r="I31" s="2" t="inlineStr"/>
+        <v>4.95</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>8天6板</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>储能|参股精工电子专注于锂离子电池高端定制化应用领域，以出口为主，主要产品涵盖分布式储能系统、光伏储能、AGV、轻型动力产品等。</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>储能</t>
-        </is>
-      </c>
+          <t>ST股 | 公司专注医药健康产业，涉足药品研发、生产、销售等领域，产品涵盖了心脑血管、抗肿瘤、骨科、妇儿等用药领域。</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>-2.27</v>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>今年的政府工作报告提出，实施超大规模智算集群、算电协同等新基建工程。此外，根据《数据中心绿色低碳发展专项行动计划》明确要求，国家枢纽节点新建数据中心绿电占比超过80%。</t>
-        </is>
-      </c>
+        <v>0.48</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>sz002445</t>
+          <t>sz000669</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>中南文化</t>
+          <t>ST金鸿</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>4.49</v>
+        <v>5.1</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>10.05</v>
+        <v>4.94</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
@@ -1963,569 +1954,475 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>并购+电力+油气|1.中南文化(002445.SZ)公告称，公司计划通过发行股份及支付现金的方式购买江阴电力投资有限公司持有的江阴苏龙热电有限公司57.30%股权，同时拟向不超过三十五名特定投资者募集配套资金。本次交易相关审计、评估工作尚未完成，交易方案需进一步论证和沟通协商。本次交易预计构成重大资产重组。本次交易完成后，上市公司在电力能源领域的业务布局将得到拓展。
-2.公司是目前国内规模较大的工业金属管件制造商，主要产品为管件、法兰、管系和压力容器，产品拥有国际多项生产商许可证书；其中，公司还拥有国家质检总局颁发的压力管道元件、压力容器等特种设备制造许可证，是中国石油天然气集团公司一级供应网络成员单位、中国石油能源一号网会员单位、中国石化资源市场成员厂组织集中采购成员厂。</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>并购, 电力, 油气</t>
-        </is>
-      </c>
+          <t>ST股 | 主营气源开发与输送、长输管网建设与管理、城市燃气经营与销售、车用加气站投资与运营、LNG点供、分布式能源项目开发与建设等。</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>-2.27</v>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>今年的政府工作报告提出，实施超大规模智算集群、算电协同等新基建工程。此外，根据《数据中心绿色低碳发展专项行动计划》明确要求，国家枢纽节点新建数据中心绿电占比超过80%。</t>
-        </is>
-      </c>
+        <v>0.48</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr"/>
       <c r="D33" s="2" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>sh600726</t>
+          <t>sh600599</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>华电能源</t>
+          <t xml:space="preserve">*ST熊猫 </t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>4.27</v>
+        <v>5.34</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>10.05</v>
+        <v>4.91</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4天4板</t>
+          <t>5天5板</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>电力|公司是黑龙江省最大的发电及集中供热运营商，主要产品为电力、热力，火力电厂分布在黑龙江省主要中心城市。</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>电力</t>
-        </is>
-      </c>
+          <t>ST股 | 公司地处中国烟花之乡浏阳，经过3多年的发展已成为中国最大的出口鞭炮烟花公司</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>-2.27</v>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>今年的政府工作报告提出，实施超大规模智算集群、算电协同等新基建工程。此外，根据《数据中心绿色低碳发展专项行动计划》明确要求，国家枢纽节点新建数据中心绿电占比超过80%。</t>
-        </is>
-      </c>
+        <v>0.48</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr"/>
       <c r="D34" s="2" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>sz002056</t>
+          <t>sh603843</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>横店东磁</t>
+          <t xml:space="preserve">*ST正平 </t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>25.84</v>
+        <v>7.04</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
+        <v>5.07</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>4天4板</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>算电协同|据2026年3月9日互动易，公司以磁材器件介入算力硬件、以光伏储能提供绿色电力，并通过产业基金投资BCIGroup参与“算电协同”算力基建规划与运营。</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>算电协同</t>
-        </is>
-      </c>
+          <t>ST股 | 2025年2月21日公司官微披露，旗下正平智算参加海东市绿色算力产业集中签约暨推介活动并签订算电协同产业园框架协议。</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>长江证券测算显示，若霍尔木兹海峡长期封锁，全球电力用煤需求可能年化增加8486万吨；若我国煤化工装置满负荷运行，仅此一项便将拉动国内煤炭消费近5000万吨。</t>
-        </is>
-      </c>
+        <v>0.48</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr"/>
       <c r="D35" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sh600121</t>
+          <t>sz002789</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>郑州煤电</t>
+          <t>*ST建艺</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>5.65</v>
+        <v>11.46</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>9.92</v>
+        <v>5.04</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>5天3板</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>煤炭|河南省三家省管国有煤炭上市公司之一，在全国已正式投产的煤炭企业中属中等规模，产品包括优质的工业动力煤和生活用煤等。</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>煤炭</t>
-        </is>
-      </c>
+          <t>ST股 | 公司是集施工、设计、资源矿产、科技工业园、高新技术建材产业、投融资为一体的规模化实体企业集团。</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>长江证券测算显示，若霍尔木兹海峡长期封锁，全球电力用煤需求可能年化增加8486万吨；若我国煤化工装置满负荷运行，仅此一项便将拉动国内煤炭消费近5000万吨。</t>
-        </is>
-      </c>
+        <v>0.48</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sh600408</t>
+          <t>sz002693</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>安泰集团</t>
+          <t>*ST双成</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>4.13</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>10.13</v>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
+        <v>4.95</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>煤炭|公司主营焦炭及其副产品，炼焦采用的是JN60-6型焦炉，产品主要销售给钢铁企业。目前公司焦炭年生产能力已达到240万吨，是山西省焦化龙头企业之一。</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>煤炭</t>
-        </is>
-      </c>
+          <t>ST股 | 地处海南省海口市，专业从事化学合成多肽药品。</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>国金证券表示，锂电3月排产显著复苏，环比增长11%～22%，同比增长37%～56%。2026年3月，电池/正极/负极/隔膜/电解液预排产累计同增36%～57%，其中电解液、隔膜同比超50%。</t>
-        </is>
-      </c>
+        <v>0.48</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr"/>
       <c r="D37" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sh603659</t>
+          <t>sz002512</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">璞泰来  </t>
+          <t>ST达华</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>32.41</v>
+        <v>4.79</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
+        <v>5.04</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>隔膜|公司是国内锂离子电池隔膜领域的领先企业，负极产业龙头之一，已在锂电产业中的负极材料、涂覆隔膜、涂布机设备、铝塑膜等领域开展深度布局。</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>隔膜</t>
-        </is>
-      </c>
+          <t>ST股 | 1.在量子安全通信领域，公司已经形成了量子安全卫星互联网通信的全套解决方案，已进行试点应用。
+2.公司子公司海丝卫星是专业提供卫星互联网服务的运营商，通过直接为终端客户提供一站式全场景卫星宽带接入及行业垂直应用服务，解决海洋通信、应急通信及偏远山区等场景网络覆盖问题。</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>国金证券表示，锂电3月排产显著复苏，环比增长11%～22%，同比增长37%～56%。2026年3月，电池/正极/负极/隔膜/电解液预排产累计同增36%～57%，其中电解液、隔膜同比超50%。</t>
-        </is>
-      </c>
+        <v>0.48</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>sh600232</t>
+          <t>sz000488</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>金鹰股份</t>
+          <t>ST晨鸣</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>8.779999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>10.03</v>
+        <v>5.07</v>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>锂电池|公司业务包括锂电池正极材料的研发、生产与销售，产品包括三元正极材料系列产品以及锰酸锂系列产品。</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>锂电池</t>
-        </is>
-      </c>
+          <t>ST股 | 公司是全国唯一一家实现制浆和造纸平衡的大型浆纸一体化企业，率先布局全产业链，在山东、广东、湖北、江西、吉林等地建有6个生产基地，年浆纸产能达1100多万吨。</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>业绩超预期</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>-0.9900000000000001</v>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>市场不确定性加剧，一批2025年度业绩超预期的股票走势抢眼。</t>
-        </is>
-      </c>
+        <v>0.48</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr"/>
       <c r="D39" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>sh603929</t>
+          <t>sh603557</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>亚翔集成</t>
+          <t xml:space="preserve">ST起步  </t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>140.83</v>
+        <v>4.21</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>10</v>
+        <v>4.99</v>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>业绩|亚翔集成发布2025年年度报告，公司实现营业收入49.07亿元，同比下降8.81%；归属于上市公司股东的净利润为8.92亿元，同比增长40.30%。公司拟向全体股东每10股派发现金红利16.50元（含税），分红总额为3.52亿元。</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>业绩</t>
-        </is>
-      </c>
+          <t>ST股 | 国内童鞋龙头。旗下 ABC KIDS 占据我国童鞋第一、童装第七的市场地位。</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>业绩超预期</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>-0.9900000000000001</v>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>市场不确定性加剧，一批2025年度业绩超预期的股票走势抢眼。</t>
-        </is>
-      </c>
+        <v>0.48</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>sh603558</t>
+          <t>sh600892</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>健盛集团</t>
+          <t xml:space="preserve">*ST大晟 </t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>12.99</v>
+        <v>3.81</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>9.99</v>
+        <v>4.96</v>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>业绩|健盛集团发布2025年度报告，2025年实现营业收入25.89亿元，同比增长0.59%；归属于上市公司股东的净利润4.05亿元，同比增长24.62%。</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>业绩</t>
-        </is>
-      </c>
+          <t>ST股 | 公司的主营业务为网络游戏研发、运营以及影视剧制作、发行业务。</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>-1.95</v>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>2026年光纤通信大会暨展览会（OFC）是全球光通信与网络领域的盛会，定于3月15日至19日在美国洛杉矶会议中心举行。</t>
-        </is>
-      </c>
+        <v>0.48</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr"/>
       <c r="D41" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>sh603803</t>
+          <t>sh600381</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>瑞斯康达</t>
+          <t xml:space="preserve">*ST春天 </t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>13.75</v>
+        <v>2.74</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>4天3板</t>
-        </is>
-      </c>
+        <v>4.98</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>光模块|在高端光模块领域，公司联营企业易锐光电是中国少数产业链上下游关键层面具备完整核心技术和解决方案的高科技企业，新一代基于自主知识产权的25G/100G/超100G集成光收发芯片的光通信模块及光组件，用于电信网络城域网和大型数据中心网络。</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>光模块</t>
-        </is>
-      </c>
+          <t>ST股 | 在大健康业务方面，公司已基本完成了涵盖保健食品、药品等冬虫夏草高效利用产品的储备和战略布局。</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>-1.95</v>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>2026年光纤通信大会暨展览会（OFC）是全球光通信与网络领域的盛会，定于3月15日至19日在美国洛杉矶会议中心举行。</t>
-        </is>
-      </c>
+        <v>0.48</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr"/>
       <c r="D42" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>sz002429</t>
+          <t>sz002529</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>兆驰股份</t>
+          <t>*ST海源</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>11.94</v>
+        <v>7.34</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>10.05</v>
+        <v>5.01</v>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>光通信全面进展|兆驰股份发布对外投资建设光通信半导体激光芯片及高速光模块项目的进展公告称，目前，公司高速光模块项目已完成近5万平方米洁净智造基地建设并全面启用。截至本公告日，200G及以下光模块已规模化生产；首批400G/800G并行光收发模块全流程制造生产线已完成设备安装与调试，400G/800G光模块可靠性测试完成已进入小批量生产阶段，并有序推进至规模化量产阶段；1.6T光模块已进入快速研发阶段，围绕LPO、NPO、CPO多路径并行攻关，构建下一代高速低功耗解决方案。同时，公司激光芯片项目也取得阶段性进展。公司前期已配置20腔可兼容LED砷化镓芯片与激光芯片生产线的MOCVD（金属有机化学气相沉积）设备，目前已增补部分后段设备，建成激光芯片生产线。公司可根据产品研发、验证测试进度及客户订单需求，灵活协调LED砷化镓芯片与激光芯片的产能分配，保障激光芯片产能供给。截至本公告日，25G DFB及以下速率光芯片已完成研发及试生产，逐步向量产阶段过渡；应用于400G/800G/1.6T光模块的大功率系列CW DFB激光芯片和50G EML激光芯片正在按既定计划稳步推进研发；面向Micro LED光互连CPO（共封装光学）技术的Micro LED光源芯片已完成研发工作，目前处于样品验证测试阶段。</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>光通信全面进展</t>
-        </is>
-      </c>
+          <t>ST股 | 公司拟收购赛维电源科技有限公司100%股权，赛维电源拥有先进的光伏组件研发生产技术，公司通过此次收购，将建立光伏组件方面的核心技术和管理团队，进入光伏组件领域。</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>-0.7000000000000001</v>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>2026年3月初，日本材料巨头力森诺科和三菱瓦斯化学相继宣布，将覆铜板及相关材料价格大幅上调30%。</t>
-        </is>
-      </c>
+        <v>0.48</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr"/>
       <c r="D43" s="2" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>sh600226</t>
+          <t>sh603789</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>亨通股份</t>
+          <t xml:space="preserve">*ST星农 </t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>6.02</v>
+        <v>5.64</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>10.05</v>
+        <v>5.029999999999999</v>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>农药+PCB|1.公司农药主要有生物农药阿维菌素系列产品，具有高效、广谱、低残留和对人畜及环境安全等特点，应用于蔬菜、果树、小麦、水稻、棉花、烟草等作物虫害的防治；公司生产的兽药和饲料添加剂主要用于畜禽的治疗、防疫和动物营养添加剂等三大领域。主要产品有 L-色氨酸预混剂、 L-色氨酸精品、莫能菌素等。
-2.子公司亨通铜箔主要从事电解铜箔的研发、生产与销售，电子铜箔是制作覆铜板（CCL）和印制电路板（PCB）的重要基础原材料。</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>农药, PCB</t>
-        </is>
-      </c>
+          <t>ST股 | 公司拥有包括水稻、小麦、玉米等粮食作物的收获机，以及棉花、花生等经济作物的收获机，并覆盖旋耕、收割、打捆、烘干等主要农业生产环节。</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>-1.15</v>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>希捷首席商务官Ban Seng Teh表示，如果氦气供应中断持续数周以上，可能会迫使芯片制造商将更多产能分配给人工智能存储器，从而加剧本已严重的内存短缺问题。</t>
-        </is>
-      </c>
+        <v>0.48</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>sh603607</t>
+          <t>sz000668</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>京华激光</t>
+          <t>*ST荣控</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>24.55</v>
+        <v>14.13</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>9.99</v>
+        <v>4.98</v>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>IP经济+光刻机|1.公司主要为国内卡游龙头提供卡牌深加工服务，配套的IP包括“奥特曼”“叶罗丽”“名侦探柯南”“三国”“仙剑奇侠传”“小马宝莉”等。
-2.公司控股的美国菲涅尔制版科技公司是一家多年从事微结构光学技术研发及相关设备制造和维护的企业，先后研发出多台技术先进、性能突出、与光学制版有关的光刻机设备。</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>IP经济, 光刻机</t>
-        </is>
-      </c>
+          <t>ST股 | 公司主营业务为房地产开发，经营模式以自主开发销售为主，曾推出国内第一个小户型楼盘，第一家运动主题社区，在业内产生较大影响。</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2534,36 +2431,33 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>-0.05</v>
+        <v>0.48</v>
       </c>
       <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>sz000908</t>
+          <t>sz002253</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>*ST景峰</t>
+          <t>*ST智胜</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>5.05</v>
+        <v>10.8</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>7天5板</t>
-        </is>
-      </c>
+        <v>4.96</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司专注医药健康产业，涉足药品研发、生产、销售等领域，产品涵盖了心脑血管、抗肿瘤、骨科、妇儿等用药领域。</t>
+          <t>ST股 | 1.公司于2021年6月18日在互动平台表示，公司与华为目前的合作主要是在昇腾芯片，鲲鹏服务器上的三维人脸识别算法的平台适配以及智慧园区的方案实施。
+2.公司拥有自主研发的针对低空安全管控需求研制的低空监视雷达系统，可以实现组网对广域范围低空空域进行连续监视。</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
@@ -2575,36 +2469,32 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>-0.05</v>
+        <v>0.48</v>
       </c>
       <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>sh600599</t>
+          <t>sh600289</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST熊猫 </t>
+          <t xml:space="preserve">ST信通  </t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>5.09</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>4天4板</t>
-        </is>
-      </c>
+        <v>5.02</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司地处中国烟花之乡浏阳，经过3多年的发展已成为中国最大的出口鞭炮烟花公司</t>
+          <t>ST股 | 公司在智能交通领域继续保持稳健发展，着重提升项目的盈利能力。</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
@@ -2612,154 +2502,174 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="n">
-        <v>-0.05</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C47" s="2" t="inlineStr"/>
       <c r="D47" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>sz000004</t>
+          <t>sh600683</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>*ST国华</t>
+          <t>京投发展</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>6.16</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>4.94</v>
+        <v>10.05</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>4天4板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司旗下全资子公司智游网安为专业移动应用安全综合服务提供商。</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr"/>
+          <t>剥离地产业务|京投发展公告称，公司拟将持有的房地产开发业务相关资产及负债转让至控股股东京投公司，采用现金支付方式，不涉及发行股份，不影响公司股权结构，不会因此导致公司控股股东发生变更。本事项预计构成重大资产重组。</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>剥离地产业务</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="n">
-        <v>-0.05</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C48" s="2" t="inlineStr"/>
       <c r="D48" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>sz000669</t>
+          <t>sh603929</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>ST金鸿</t>
+          <t>亚翔集成</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>4.86</v>
+        <v>154.91</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>4.97</v>
+        <v>10</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>4天4板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 主营气源开发与输送、长输管网建设与管理、城市燃气经营与销售、车用加气站投资与运营、LNG点供、分布式能源项目开发与建设等。</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr"/>
+          <t>业绩|亚翔集成发布2025年年度报告，公司实现营业收入49.07亿元，同比下降8.81%；归属于上市公司股东的净利润为8.92亿元，同比增长40.30%。公司拟向全体股东每10股派发现金红利16.50元（含税），分红总额为3.52亿元。</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>业绩</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="n">
-        <v>-0.05</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C49" s="2" t="inlineStr"/>
       <c r="D49" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>sh603843</t>
+          <t>sh603248</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST正平 </t>
+          <t>锡华科技</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>6.7</v>
+        <v>31.02</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>5.02</v>
+        <v>10</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>3天3板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 2025年2月21日公司官微披露，旗下正平智算参加海东市绿色算力产业集中签约暨推介活动并签订算电协同产业园框架协议。</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr"/>
+          <t>风电|公司主要从事大型高端装备专用部件的研发、制造与销售，产品结构以风电齿轮箱专用部件为主、注塑机厚大专用部件为辅，是全球行业领先、质量可靠、技术卓越的大型高端装备专用部件制造商。</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>风电</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="n">
-        <v>-0.05</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C50" s="2" t="inlineStr"/>
       <c r="D50" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>sz002789</t>
+          <t>sh603778</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>*ST建艺</t>
+          <t>国晟科技</t>
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>10.91</v>
+        <v>22.54</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
@@ -2768,121 +2678,148 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司是集施工、设计、资源矿产、科技工业园、高新技术建材产业、投融资为一体的规模化实体企业集团。</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr"/>
+          <t>光伏+锂电池|1.公司目前从事大尺寸高效异质结光伏电池的研发、生产、销售，以及异质结、TOPCON、PERC等电池组件的生产与销售。控股孙公司恒立聚能涉及钙钛矿研究。
+2.国晟科技公告称，公司拟以2.406亿元的价格受让正豪科技、林琴合计持有的孚悦科技100%股权。交易完成后，公司将持有标的公司100%股权，标的公司将纳入公司合并报表。孚悦科技主要从事高精密度新型锂电池结构件的研发、生产和销售。</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>光伏, 锂电池</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="n">
-        <v>-0.05</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C51" s="2" t="inlineStr"/>
       <c r="D51" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>sz002693</t>
+          <t>sz002831</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>*ST双成</t>
+          <t>裕同科技</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>7.67</v>
+        <v>38.02</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="I51" s="2" t="inlineStr"/>
+        <v>10.01</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 地处海南省海口市，专业从事化学合成多肽药品。</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr"/>
+          <t>并购重组|裕同科技公告称，公司拟通过自有或自筹资金向观点投资收购其持有的华研科技51%股份，交易金额为4.49亿元。本次交易构成关联交易，公司实际控制人王华君、吴兰兰夫妇合计持有观点投资100%股权。交易完成后，华研科技将成为公司的控股子公司，并纳入公司合并报表范围。东莞市华研新材料科技有限公司成立于2016年，致力于为客户提供一站式精密金属及陶瓷零组件整体解决方案，一体化设计、研发、制造、组装整体解决方案的专精特新国家级“小巨人”高新技术企业。</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>并购重组</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="n">
-        <v>-0.05</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C52" s="2" t="inlineStr"/>
       <c r="D52" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>sh603261</t>
+          <t>sh600302</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST立航 </t>
+          <t>标准股份</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>32.63</v>
+        <v>11.29</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>4.99</v>
+        <v>10.04</v>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司是以飞机地面保障设备、航空器试验和检测设备、飞机工艺装备、飞机零件加工和飞机部件装配等专业研发、设计、制造、销售为一体的军民融合企业。</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr"/>
+          <t>拟股权转让|标准股份公告称，公司控股股东标准集团拟通过公开征集转让方式协议转让其持有的公司不超过27.77%（含）且不低于控制权变更比例的股份。公司股票将于2025年10月28日开市起复牌。标准集团直接持有公司1.48亿股A股股份，占公司总股本的42.77%，均为非限售流通股份。</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>拟股权转让</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="n">
-        <v>-0.05</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C53" s="2" t="inlineStr"/>
       <c r="D53" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>sz002620</t>
+          <t>sz001278</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>ST瑞和</t>
+          <t>一彬科技</t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>7.12</v>
+        <v>25.32</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>5.01</v>
+        <v>9.99</v>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司主要从事政府机构、房地产开发商、大型企业、高档酒店、交通枢纽、园林绿化等综合性专业化装饰设计、工程施工业务以及光伏电站运营、光伏项目施工安装等。</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr"/>
+          <t>机器人|公司通过参股共青城民生创新智能投资合伙企业（有限合伙）间接投资法奥意威（苏州）机器人系统有限公司，持股比例为1.28%。法奥机器人主营全零部件自研协作机器人研发、制造及销售，产品主要应用场景有:3D 焊接机器人、移动焊接机器人、移动码垛工作站、螺丝锁付工作站、井字棋游戏机器人以及喷涂、上下料、餐饮制作等应用场景。</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2897,38 +2834,33 @@
       </c>
       <c r="C54" s="2" t="inlineStr"/>
       <c r="D54" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>sz002903</t>
+          <t>sz000020</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>宇环数控</t>
+          <t>深华发Ａ</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>31.03</v>
+        <v>15.94</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>5天3板</t>
-        </is>
-      </c>
+        <v>10.01</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>机器人+商业航天|1.公司经营范围包括工业机器人及其关键功能部件、机械配件、金属材料的制造和销售。
-2.公司自主研发的高端复合立式磨床逐步进入航空航天市场，可用于加工航空航天领域的精密零部件及高性能材料。</t>
+          <t>面板|公司主营业务分为液晶显示器整机、注塑件、保丽龙（轻型材料包装）、物业租赁四大模块。液晶显示器整机业务生产经营各种彩色电视机、液晶显示器、液晶显示屏，是公司主要收入来源。</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>机器人, 商业航天</t>
+          <t>面板</t>
         </is>
       </c>
     </row>
@@ -2945,37 +2877,33 @@
       </c>
       <c r="C55" s="2" t="inlineStr"/>
       <c r="D55" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>sz000890</t>
+          <t>sh605299</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>法尔胜</t>
+          <t>舒华体育</t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>11.09</v>
+        <v>13.9</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.969999999999999</v>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆|公司参股的普天法尔胜光通信有限公司主要产品为光纤预制棒、光纤、光缆，上述产品可以应用于在运营商基础网络通信及广播电视通信领域。</t>
+          <t>体育产业|公司主营业务为健身器材和展示架产品的研发、生产和销售，其中健身器材包括室内健身器材、室外路径产品。</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>体育产业</t>
         </is>
       </c>
     </row>
@@ -2992,37 +2920,33 @@
       </c>
       <c r="C56" s="2" t="inlineStr"/>
       <c r="D56" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>sz002969</t>
+          <t>sh600152</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>嘉美包装</t>
+          <t>维科技术</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>26.47</v>
+        <v>10.75</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>10.03</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>追觅创始人入主|追觅创始人旗下逐越鸿智斥资逾22.82亿元拿下嘉美包装公司控制权。追觅科技有关人士向《科创板日报》记者表示，本次收购资金全部来源于俞浩及核心团队的自有与自筹资金，无来自追觅科技公司的资金，不会影响追觅科技公司正常运营。“逐越鸿智将以‘战略赋能者’身份参与嘉美包装运营，依托追觅在技术创新与全球资源上的优势，推动其在智能化生产、高端产品研发及全球化布局上实现突破。”</t>
+          <t>3C数码电池|公司以3C数码电池为核心业务，并以小动力BMS、高倍率电池、小型聚合物锂离子电池为快速增长业务。公司是行业领先的集锂离子电池研发、制造、销售及服务于一体的新能源科技型企业，具备电芯制造、封装和系统整合方案一体化能力。</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>追觅创始人入主</t>
+          <t>3C数码电池</t>
         </is>
       </c>
     </row>
@@ -3039,33 +2963,33 @@
       </c>
       <c r="C57" s="2" t="inlineStr"/>
       <c r="D57" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>sz000677</t>
+          <t>sh600313</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>恒天海龙</t>
+          <t>农发种业</t>
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>5.02</v>
+        <v>9.08</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>10.09</v>
+        <v>10.06</v>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>并购重组|恒天海龙公告称，公司拟通过全资子公司海龙飞控以现金方式收购群健航空不少于40%股权，交易完成后海龙飞控将成为目标公司控股股东。该协议为初步意向协议，目前尚未签署正式《股权收购协议》，相关事项存在不确定性。</t>
+          <t>种业|公司主营业务的核心为农作物种子业务，产品涵盖玉米、水稻、小麦、棉花、油菜、甘蔗和马铃薯等多种农作物种子（苗），分别由公司所属的河南地神等8家种业子公司开展农作物种子的研发、繁育、生产和销售。</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>并购重组</t>
+          <t>种业</t>
         </is>
       </c>
     </row>
@@ -3082,33 +3006,33 @@
       </c>
       <c r="C58" s="2" t="inlineStr"/>
       <c r="D58" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>sz002931</t>
+          <t>sz000617</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>锋龙股份</t>
+          <t>中油资本</t>
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>81.58</v>
+        <v>9.77</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>10.01</v>
+        <v>10.02</v>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>优必选入主完成|锋龙股份公告称，本次股份协议转让已完成，公司控股股东变更为优必选，实际控制人变更为周剑。根据中国证券登记结算有限责任公司于2026年3月12日出具的《证券过户登记确认书》，本次协议转让事项过户登记手续已办理完毕，过户日期为2026年3月11日，过户股数为6552.99万股，占公司股份总数的29.99%，股份性质为无限售流通股。</t>
+          <t>数字货币+跨境支付|公司及所属金融企业开展数字人民币方面的研究规划，参股企业昆仑数智联合出资成立的鲲鹏快付公司正在开展数字人民币支付业务；公司为昆仑银行大股东，昆仑银行是参与CIPS的银行机构之一。</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>优必选入主完成</t>
+          <t>数字货币, 跨境支付</t>
         </is>
       </c>
     </row>
@@ -3125,34 +3049,33 @@
       </c>
       <c r="C59" s="2" t="inlineStr"/>
       <c r="D59" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>sz000010</t>
+          <t>sz002995</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>美丽生态</t>
+          <t>天地在线</t>
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>4.53</v>
+        <v>24.77</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>9.950000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>环保+算力|1.公司主营业务涵盖市政基础设施、公路、景观绿化、房屋建设、生态环保等领域。
-2.公司逐步拓展主营延伸业务向大数据算力等新兴产业倾斜，设立美丽算力科技运营（海南）有限公司。</t>
+          <t>AI应用|公司已推出AI数字人SAAS产品“星河AI数字人系统”以及帮助企业提高工作效率和协作能力的AI智能应用产品“AIbase” ，满足客户在营销及提升企业经营效能的不同需求。</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>环保, 算力</t>
+          <t>AI应用</t>
         </is>
       </c>
     </row>
@@ -3169,33 +3092,33 @@
       </c>
       <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>sz001366</t>
+          <t>sz002235</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>播恩集团</t>
+          <t>安妮股份</t>
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>15.76</v>
+        <v>11.56</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>9.98</v>
+        <v>9.99</v>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>豆粕减量替代|播恩集团积极探索玉米、豆粕的减量替代，以帮助客户降低饲料成本，提高养殖效率。公司产品812 含有丰富的游离氨基酸，如赖氨酸、缬氨酸、精氨酸等多种必需的氨基酸，消化吸收好，可有效平衡饲料原料中某些抗营养因子造成的蛋白缺乏，提高蛋白原料利用率，降低豆粕使用量。</t>
+          <t>控制权变更|安妮股份3月4日晚间公告表示，深交所已对转让双方提交的申请材料进行了完备性核对，并出具了《深圳证券交易所上市公司股份协议转让确认书》。公司控制权变更事项迎来重大进展。</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>豆粕减量替代</t>
+          <t>控制权变更</t>
         </is>
       </c>
     </row>
@@ -3212,378 +3135,33 @@
       </c>
       <c r="C61" s="2" t="inlineStr"/>
       <c r="D61" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>sh600683</t>
+          <t>sz300051</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>京投发展</t>
+          <t>琏升科技</t>
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>8.76</v>
+        <v>11.12</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>10.05</v>
+        <v>19.96</v>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>房地产|公司的最终控制人为北京市人民政府国有资产监督管理委员会。公司主营业务为房地产开发、经营及租赁。</t>
+          <t>光伏|2023年12月1日公司在调研中表示，公司目前已在眉山丹棱和江苏南通规划了2个生产基地，眉山琏升光伏异质结电池片项目总共规划8GW，江苏南通项目总规划12GW。</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>房地产</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr"/>
-      <c r="D62" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>sh603029</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>天鹅股份</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="H62" s="2" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>农机+供销社|我国棉花加工机械制造行业的龙头之一。 实际控制人为山东省供销合作社联合社。</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>农机, 供销社</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr"/>
-      <c r="D63" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>sh600847</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>万里股份</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="n">
-        <v>15.51</v>
-      </c>
-      <c r="H63" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>铅酸蓄电池|公司是中国铅酸蓄电池行业首家上市公司，以生产“万里”牌各型铅酸蓄电池闻名于世，被誉为“中国蓄能专家”。</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>铅酸蓄电池</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr"/>
-      <c r="D64" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>sh603538</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">美诺华  </t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>25.37</v>
-      </c>
-      <c r="H64" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>CDMO|公司正在加速打造CDMO一站式综合服务平台，为制药企业提供贯穿药品临床前研发、临床试验阶段以及上市审批、商业化生产等环节的综合性研发生产服务，包括为其提供医药特别是创新药的工艺研发及制备、工艺优化、放大生产、注册和验证批生产以及商业化生产等定制研发生产服务。</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>CDMO</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr"/>
-      <c r="D65" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>sh600756</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>浪潮软件</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>17.63</v>
-      </c>
-      <c r="H65" s="2" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>AI+信创|公司基于大模型技术创新， 在政务服务方面打造ECGAP5.0政务平台， 推出大模型+事项智理、 智能问答、 “边聊边办” 、 智能审批、 智能问数、 无感评价六大场景， 打造青岛“数字张大为” 和“边聊边办” 等典型案例， 形成可复制推广的AI+政务服务创新范式。</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>AI, 信创</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr"/>
-      <c r="D66" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>sh600307</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>酒钢宏兴</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="H66" s="2" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>钢铁+铜|1.西北地区综合型钢铁企业，具备年产1000万吨以上钢材的生产能力，拥有四座矿山，铁矿储量达3.5亿吨。
-2.2024年7月4日公告，近期公司通过公开竞标方式，以3.3亿元价格竞得了甘肃省肃南县桦树沟西部铁铜矿详查探矿权。该探矿权和公司镜铁山矿桦树沟采矿权无缝衔接。经甘肃省矿产资源储量评审中心评审，此次竞得的该详查探矿权范围内查明和预测的资源量为：铁矿石资源量4885.15万吨，TFe平均品位33.88%。铜矿石资源量424.81万吨，Cu平均品位0.98%。</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>钢铁, 铜</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr"/>
-      <c r="D67" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>sh600336</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">澳柯玛  </t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="H67" s="2" t="n">
-        <v>9.950000000000001</v>
-      </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>家电|公司是国内优质冷柜企业，也是世界知名制冷设备供应商，扩散布局冰洗空、厨电、热水器等白色家电。公司控股股东为青岛市企业发展投资有限公司，实际控制人为青岛市国资委。</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>家电</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr"/>
-      <c r="D68" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>sh600234</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>科新发展</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="n">
-        <v>14.92</v>
-      </c>
-      <c r="H68" s="2" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>建筑装修|公司主营业务为以广告传媒业务、建筑装修装饰工程业务为主，同时以自有资产开展写字楼出租业务。主要产品有物业出租、营销策划、建筑装饰工程。</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>建筑装修</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr"/>
-      <c r="D69" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>sz003041</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>真爱美家</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="n">
-        <v>69.84999999999999</v>
-      </c>
-      <c r="H69" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>实控人变更|真爱美家公告称，公司控股股东真爱集团与受让方广州探迹远擎科技合伙企业（有限合伙）签署《股份转让协议》。真爱集团拟向探迹远擎转让公司股份4318.56万股（占公司总股本的29.99%），转让价格27.74元/股，总额11.98亿元。以股份转让完成为前提，探迹远擎拟向除其外的公司全体股东发出不可撤销的部分要约收购，要约收购公司股份的数量为2160万股（占公司总股本的15%），要约收购价格为每股27.74元。交易完成后，探迹远擎将拥有公司44.99%的股份及该等股份对应的表决权，公司控股股东变更为探迹远擎，实控人变更为黎展。</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>实控人变更</t>
+          <t>光伏</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3625,46 +3203,46 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sz002445</t>
+          <t>sh600370</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>中南文化</t>
+          <t xml:space="preserve">三房巷  </t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sh600726</t>
+          <t>sz000890</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>华电能源</t>
+          <t>法尔胜</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sh600722</t>
+          <t>sh603929</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>金牛化工</t>
+          <t>亚翔集成</t>
         </is>
       </c>
     </row>
@@ -3674,12 +3252,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sz002487</t>
+          <t>sh603248</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>大金重工</t>
+          <t>锡华科技</t>
         </is>
       </c>
     </row>
@@ -3689,12 +3267,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sh600121</t>
+          <t>sh600227</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>郑州煤电</t>
+          <t xml:space="preserve">赤天化  </t>
         </is>
       </c>
     </row>
@@ -3704,42 +3282,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sh600370</t>
+          <t>sh600683</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">三房巷  </t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>sh600691</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>潞化科技</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>sz000890</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>法尔胜</t>
+          <t>京投发展</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,19 +476,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="103" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="95" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="289" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="244" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -552,467 +552,496 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>存储器</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>4.15</v>
+        <v>-0.89</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>市场调查机构CounterPoint Research表示，与以往的周期不同，当前内存市场即使价格上涨，需求也不会下降。供应短缺问题至少要到2027年下半年才能得到实质性解决。</t>
+          <t>国家明确要求国家算力枢纽节点新建数据中心的绿电占比不低于80%，这一硬性指标不仅为绿电创造了巨大的新增消纳场景，也推动着“绿电直连”“源网荷储一体化”等新型商业模式加速落地。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>sz300042</t>
+          <t>sh601016</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>朗科科技</t>
+          <t>节能风电</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>45.6</v>
+        <v>4.55</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr"/>
+        <v>9.9</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>5天3板</t>
+        </is>
+      </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>存储芯片+算力|1.公司致力于为全球存储应用领域提供解决方案，存储产品已经覆盖SSD固态硬盘、DRAM内存条、嵌入式存储和移动存储等领域。
-2.2024年2月，公司与韶关政府、中兴通讯和韶关数投签署合作协议，拟在建设算力产业生态、提升数据中心建设水平和数字化转型深度合作方面展开合作。</t>
+          <t>绿电|公司的主营业务为风力发电的项目开发、建设及运营。在加快风电场开发和建设的同时，加大中东部及南方区域市场开发力度，在湖北、广西、浙江、河南、四川等已有项目的区域开发后续项目，在贵州、安徽、湖南、广东、重庆、江西、山东等区域开展风电项目前期踏勘和测风工作，扩大资源储备。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>存储芯片, 算力</t>
+          <t>绿电</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>存储器</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>4.15</v>
+        <v>-0.89</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>市场调查机构CounterPoint Research表示，与以往的周期不同，当前内存市场即使价格上涨，需求也不会下降。供应短缺问题至少要到2027年下半年才能得到实质性解决。</t>
+          <t>国家明确要求国家算力枢纽节点新建数据中心的绿电占比不低于80%，这一硬性指标不仅为绿电创造了巨大的新增消纳场景，也推动着“绿电直连”“源网荷储一体化”等新型商业模式加速落地。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sz000620</t>
+          <t>sh600396</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>盈新发展</t>
+          <t>华电辽能</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>3.31</v>
+        <v>4.7</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>9.969999999999999</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
+        <v>10.07</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>存储芯片|盈新发展公告称，公司与广东长兴信息管理咨询有限公司、张治强签署《股权收购意向协议》，拟以支付现金方式收购长兴咨询、张治强合计持有的广东长兴半导体科技有限公司81.8091%股权。本次交易完成后，公司预计将实现对长兴半导体控股。本次交易不构成重大资产重组，不涉及发行股份，不会导致公司控制权变更。广东长兴半导体科技有限公司成立于2012年，是一家专注于存储器芯片封装测试和存储模组制造的高新技术企业。</t>
+          <t>电力+氢能|1.公司是中国华电集团公司的实际控制的上市公司、中央企业的三级单位，同时也是一家集火力发电、风力发电、煤炭营销、供热、供汽为一体的综合性区域基础能源企业。
+2.2023年3月14日公告，拟与华电科工共同出资建设25MW风电离网制氢一体化项目，风电设备年利用小时数3000小时，年发电量约7500万千瓦时，全部发电量均用于本项目制取绿氢，预计年产绿氢1230吨。项目总投资2.78亿元。公司与华电科工拟按70%和30%比例组建项目公司。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>存储芯片</t>
+          <t>电力, 氢能</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>存储器</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4.15</v>
+        <v>-0.89</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>市场调查机构CounterPoint Research表示，与以往的周期不同，当前内存市场即使价格上涨，需求也不会下降。供应短缺问题至少要到2027年下半年才能得到实质性解决。</t>
+          <t>国家明确要求国家算力枢纽节点新建数据中心的绿电占比不低于80%，这一硬性指标不仅为绿电创造了巨大的新增消纳场景，也推动着“绿电直连”“源网荷储一体化”等新型商业模式加速落地。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sh600667</t>
+          <t>sh603693</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>太极实业</t>
+          <t>江苏新能</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>11.26</v>
+        <v>15.88</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>9.959999999999999</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
+        <v>9.969999999999999</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>存储芯片|公司半导体业务是为DRAM和NANDFlash等集成电路产品提供封装、封装测试、模组装配和模组测试等后工序服务。控股子公司海太公司拥有完整的封装测试生产线与SK海力士12英寸晶圆生产线紧密配套。</t>
+          <t>绿电|公司的主营业务为新能源发电项目的投资开发、建设运营及电力销售，目前主要包括风能发电、生物质能发电和光伏发电三个板块。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>存储芯片</t>
+          <t>绿电</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>存储器</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4.15</v>
+        <v>-0.89</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>市场调查机构CounterPoint Research表示，与以往的周期不同，当前内存市场即使价格上涨，需求也不会下降。供应短缺问题至少要到2027年下半年才能得到实质性解决。</t>
+          <t>国家明确要求国家算力枢纽节点新建数据中心的绿电占比不低于80%，这一硬性指标不仅为绿电创造了巨大的新增消纳场景，也推动着“绿电直连”“源网荷储一体化”等新型商业模式加速落地。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sz300606</t>
+          <t>sz002256</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>金太阳</t>
+          <t>兆新股份</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>40.73</v>
+        <v>4.27</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>20.01</v>
+        <v>10.05</v>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>存算一体芯片|参股中科声龙专注于为全球客户提供算力芯片系统的研发、设计、生产、销售和相应的技术指导等综合服务，在基于3D异质集成的大规模存算一体芯片领域处于业界领先水平。</t>
+          <t>绿电+化工|1.公司新能源领域业务为光伏电站投资、建设、运营和管理。截至2024年期末，公司在安徽、江西、浙江、宁夏及四川等多个省份运营和管理10座太阳能光伏电站，累计并网装机容量约131.82MW。
+2.公司生产的精细化工产品包括环保功能涂料及辅料、绿色环保家居用品和环保节能汽车养护用品等，广泛应用于家庭用品、个人用品、工业与汽车用品等领域</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>存算一体芯片</t>
+          <t>绿电, 化工</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>存储器</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>4.15</v>
+        <v>-0.89</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>市场调查机构CounterPoint Research表示，与以往的周期不同，当前内存市场即使价格上涨，需求也不会下降。供应短缺问题至少要到2027年下半年才能得到实质性解决。</t>
+          <t>国家明确要求国家算力枢纽节点新建数据中心的绿电占比不低于80%，这一硬性指标不仅为绿电创造了巨大的新增消纳场景，也推动着“绿电直连”“源网荷储一体化”等新型商业模式加速落地。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sh603986</t>
+          <t>sh603685</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>兆易创新</t>
+          <t>晨丰科技</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>306.16</v>
+        <v>29.65</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>10</v>
+        <v>10.02</v>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>存储芯片|公司是中国大陆领先的闪存芯片设计企业，存储器产品包括闪存芯片（NORFlash、NANDFlash）和动态随机存取存储器（DRAM）。</t>
+          <t>PCB+电力|1.公司的印制电路板主要应用于照明市场及显示背光源市场。
+2.截止2024年9月，公司建成投运的新能源发电装机容量为121.41兆瓦(其中风电装机容量为117兆瓦);公司拥有在建及拟建风电机组装机容量为247.85兆瓦、光伏机组装机容量为498.75兆瓦;已取得项目建设指标尚未完成项目核准备案的风电机组装机容量为125.50兆瓦。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>存储芯片</t>
+          <t>PCB, 电力</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>存储器</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>4.15</v>
+        <v>-2.13</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>市场调查机构CounterPoint Research表示，与以往的周期不同，当前内存市场即使价格上涨，需求也不会下降。供应短缺问题至少要到2027年下半年才能得到实质性解决。</t>
+          <t>昨日，瓶片期货价格显著上涨，收盘涨幅在7.44%；华东市场主流报价升至9000元/吨，单日上涨350元/吨。此外，机构指出，若航运中断常态化，全球肥料原料供应可能会减少30%至50%。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sh603175</t>
+          <t>sh600227</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>超颖电子</t>
+          <t xml:space="preserve">赤天化  </t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>88.19</v>
+        <v>5.29</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
+        <v>9.98</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12天6板</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>PCB+存储芯片|1.公司主营业务是印制电路板的研发、生产和销售，拥有HDI板、厚铜板、金属基板、高频板、高速板等特殊材料、特殊工艺产品的生产能力，产品广泛应用于汽车电子、显示、储存、消费电子、通信等领域，并积极布局AR/VR、航天卫星等领域。
-2.在储存领域，公司产品主要应用于机械硬盘、固态硬盘、内存条等，与全球机械硬盘制造商龙头希捷、西部数据及全球知名固态硬盘制造商海力士等建立了稳定合作。</t>
+          <t>化肥|公司是贵州省最大的氮肥生产企业，公司化肥化工生产基地分别是以天然气为原料生产的赤水化工分公司（年产63万吨尿素）和以煤为生产原料的公司全资子公司桐梓化工（年产52万吨尿素、30万吨甲醇）。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>PCB, 存储芯片</t>
+          <t>化肥</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>深海科技</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1.08</v>
+        <v>-2.13</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3月16日出版的第6期《求是》杂志将发表重要文章《推动海洋经济高质量发展》。</t>
+          <t>昨日，瓶片期货价格显著上涨，收盘涨幅在7.44%；华东市场主流报价升至9000元/吨，单日上涨350元/吨。此外，机构指出，若航运中断常态化，全球肥料原料供应可能会减少30%至50%。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sz002086</t>
+          <t>sh600370</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>东方海洋</t>
+          <t xml:space="preserve">三房巷  </t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>10.13</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>4天4板</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>海洋经济|公司与中科院海洋所、中国海洋大学等大院大所深度合作，共同搭建具有国内领先水平、功能配套的保种、育种、良种繁育一体化的科研推广平台。</t>
+          <t>化工|公司成为“PTA-瓶级聚酯切片”一体化布局的优势企业，PTA产品是郑州商品交易所PTA交割免检品牌，已开发出多种全系列的瓶级聚酯切片产品。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>海洋经济</t>
+          <t>化工</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>深海科技</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1.08</v>
+        <v>-2.13</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3月16日出版的第6期《求是》杂志将发表重要文章《推动海洋经济高质量发展》。</t>
+          <t>昨日，瓶片期货价格显著上涨，收盘涨幅在7.44%；华东市场主流报价升至9000元/吨，单日上涨350元/吨。此外，机构指出，若航运中断常态化，全球肥料原料供应可能会减少30%至50%。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sz002427</t>
+          <t>sh600691</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>尤夫股份</t>
+          <t>潞化科技</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>7.69</v>
+        <v>4.72</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
+        <v>10.02</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>4天3板</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>化工+海洋经济|公司开发的拒海水聚酯工业丝产品已广泛应用于船舶、海洋钻井、深海风电系泊缆绳，产品通过DNV、ABS船级社测试认证。</t>
+          <t>煤化工|公司主要业务包括化工产品和化工机械设备的生产和销售，化工产品研发及工程总承包设计等，主要产品包括尿素、聚氯乙烯、烯烃、烧碱、双氧水、甲醇等。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>化工, 海洋经济</t>
+          <t>煤化工</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>深海科技</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1.08</v>
+        <v>-2.13</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3月16日出版的第6期《求是》杂志将发表重要文章《推动海洋经济高质量发展》。</t>
+          <t>昨日，瓶片期货价格显著上涨，收盘涨幅在7.44%；华东市场主流报价升至9000元/吨，单日上涨350元/吨。此外，机构指出，若航运中断常态化，全球肥料原料供应可能会减少30%至50%。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sz002278</t>
+          <t>sz002470</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>神开股份</t>
+          <t>金正大</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>13.75</v>
+        <v>3.6</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
+        <v>10.09</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>油气+海洋经济|公司的部分仪器和设备已用于深海油气勘探和开发，代表案例如神开录井核心设备SK-3007氢焰色谱仪以及其配套使用的SK-7H06恒量脱气器，成功应用于我国自主设计建造的首艘大洋钻探船“梦想”号，助力我国深海油气勘探；又如亚洲第一深水导管架平台“海基一号”所使用的全套井口设备均为神开自主设计研发和制造，助力我国海上油气增储上产。</t>
+          <t>化肥|公司的复合肥、缓控释肥、硝基复合肥、水溶肥及其他新型肥料在技术和市场占有率方面居国内领先地位，具有较强的竞争优势。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>油气, 海洋经济</t>
+          <t>化肥</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>深海科技</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1.08</v>
+        <v>-2.13</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3月16日出版的第6期《求是》杂志将发表重要文章《推动海洋经济高质量发展》。</t>
+          <t>昨日，瓶片期货价格显著上涨，收盘涨幅在7.44%；华东市场主流报价升至9000元/吨，单日上涨350元/吨。此外，机构指出，若航运中断常态化，全球肥料原料供应可能会减少30%至50%。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sz002724</t>
+          <t>sz001369</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>海洋王</t>
+          <t>双欣材料</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>8.210000000000001</v>
+        <v>19.18</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>10.05</v>
+        <v>9.98</v>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>海洋经济|公司是一家主做工业照明的企业，照明产品广泛应用在铁路、电网、海油钻采、矿井采矿、智慧港口、海上平台、智慧电厂、应急救灾、工业设备、制造业厂房等工业应用场景。</t>
+          <t>化工+次新|公司是一家专业从事聚乙烯醇（PVA）、特种纤维、醋酸乙烯（VAC）、碳化钙（电石）等PVA产业链上下游产品的研发、生产、销售的高新技术企业，拥有聚乙烯醇全产业链布局。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>海洋经济</t>
+          <t>化工, 次新</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>光伏</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.75</v>
+        <v>-1.93</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>中信证券指出，英伟达GTC 2026大会召开在即，预计公司的芯片产品矩阵有望进一步扩充，除Vera Rubin AI平台的全套六款核心芯片外，有可能在大会上披露Rubin Ultra芯片及机柜更多细节。</t>
+          <t>近日，中科天算与炎和科技联合宣布，太空超算原型系统正式发布，并成功完成太空算力系统与钙钛矿能源系统全流程联调验证。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
@@ -1020,48 +1049,49 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sz000890</t>
+          <t>sh603778</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>法尔胜</t>
+          <t>国晟科技</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>12.2</v>
+        <v>24.79</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>10.01</v>
+        <v>9.98</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3天3板</t>
+          <t>8天4板</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆|公司参股的普天法尔胜光通信有限公司主要产品为光纤预制棒、光纤、光缆，上述产品可以应用于在运营商基础网络通信及广播电视通信领域。</t>
+          <t>光伏+锂电池|1.公司目前从事大尺寸高效异质结光伏电池的研发、生产、销售，以及异质结、TOPCON、PERC等电池组件的生产与销售。控股孙公司恒立聚能涉及钙钛矿研究。
+2.国晟科技公告称，公司拟以2.406亿元的价格受让正豪科技、林琴合计持有的孚悦科技100%股权。交易完成后，公司将持有标的公司100%股权，标的公司将纳入公司合并报表。孚悦科技主要从事高精密度新型锂电池结构件的研发、生产和销售。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>光伏, 锂电池</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>光伏</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0.75</v>
+        <v>-1.93</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>中信证券指出，英伟达GTC 2026大会召开在即，预计公司的芯片产品矩阵有望进一步扩充，除Vera Rubin AI平台的全套六款核心芯片外，有可能在大会上披露Rubin Ultra芯片及机柜更多细节。</t>
+          <t>近日，中科天算与炎和科技联合宣布，太空超算原型系统正式发布，并成功完成太空算力系统与钙钛矿能源系统全流程联调验证。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
@@ -1069,44 +1099,48 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sz002980</t>
+          <t>sz002323</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>华盛昌</t>
+          <t>雅博股份</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>38.65</v>
+        <v>2.75</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>并购重组+光通信|华盛昌公告称，公司拟以现金方式收购深圳市伽蓝特科技有限公司100%股权，整体估值暂定为4.6亿元。伽蓝特专注于仪器仪表测试测量行业中的光通信模块和光芯片测试领域。</t>
+          <t>光伏|光伏业务占比约61%，以分布式光伏为主，业务涵盖BAPV(在现有建筑上安装的光伏系统)和BIPV(光伏建筑一体化)，宣城基地2.5GW HJT组件和105MW柔性BIPV产品已量产。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>并购重组, 光通信</t>
+          <t>光伏</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>光伏</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.75</v>
+        <v>-1.93</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>中信证券指出，英伟达GTC 2026大会召开在即，预计公司的芯片产品矩阵有望进一步扩充，除Vera Rubin AI平台的全套六款核心芯片外，有可能在大会上披露Rubin Ultra芯片及机柜更多细节。</t>
+          <t>近日，中科天算与炎和科技联合宣布，太空超算原型系统正式发布，并成功完成太空算力系统与钙钛矿能源系统全流程联调验证。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
@@ -1114,44 +1148,44 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sh603738</t>
+          <t>sz002506</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>泰晶科技</t>
+          <t>协鑫集成</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>25.31</v>
+        <v>5.63</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>10</v>
+        <v>9.959999999999999</v>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>光通信|公司针对光通信200G、400G、800G、1.6T市场推出了高基频、高精度、低相噪CMOS、LVDS差分输出时钟解决方案，随着光模块传输速率升级，对应使用超高频、差分时钟产品，在技术上提出更高性能匹配要求。</t>
+          <t>光伏|公司致力于打造成全球领先的绿色能源系统集成商，产品覆盖高效电池、大尺寸光伏组件、储能系统等，并为客户提供智慧光储一体化集成方案，包含绿色能源工程相关的产品设计、定制、生产、安装、销售等一揽子服务内容。公司近年新建合肥、芜湖、阜宁电池组件基地，已具备12GW N型TOPCon电池产能、近30GW高效组件产能。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>光伏</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>光伏</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0.75</v>
+        <v>-1.93</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>中信证券指出，英伟达GTC 2026大会召开在即，预计公司的芯片产品矩阵有望进一步扩充，除Vera Rubin AI平台的全套六款核心芯片外，有可能在大会上披露Rubin Ultra芯片及机柜更多细节。</t>
+          <t>近日，中科天算与炎和科技联合宣布，太空超算原型系统正式发布，并成功完成太空算力系统与钙钛矿能源系统全流程联调验证。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
@@ -1159,45 +1193,44 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sh603052</t>
+          <t>sz002629</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>可川科技</t>
+          <t>仁智股份</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>64.13</v>
+        <v>6.97</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>10</v>
+        <v>9.94</v>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>光通信+复合铝箔|1.2023年6月19日公告，为把握全球半导体行业光芯片、光模块产业发展机遇，公司计划与自然人吕志远签署《英特磊半导体技术(上海)股份有限公司之股东协议》(简称“《股东协议》”，共同发起设立英特磊，主要从事光通信模块及激光传感器等业务。英特磊注册资本为人民币5,000万元，其中公司认缴出资额为人民币2,550万元，持股比例为51%。
-2.2024年11月18日公告，复合集流体项目已采购了试验线和规模化生产线，并于2024年第三季度将规模化生产线的试产产品向客户送样验证，公司已于近日收到某国际知名消费电子电池生产商关于复合铝箔的首笔小额订单。</t>
+          <t>新能源电力工程|公司新能源电力工程项目以光伏发电、储能电站等施工建设为主，业务范围辐射华东、华南、华中等多个地区。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>光通信, 复合铝箔</t>
+          <t>新能源电力工程</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>房地产概念</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>-0.51</v>
+        <v>0.25</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>航运数据显示，目前有21艘满载尿素、硫磺和磷肥的船只滞留波斯湾，涉及近百万吨化肥原料；若航运中断常态化，全球肥料原料供应可能会减少30%至50%。</t>
+          <t>《关于调整上海市商业用房购房贷款最低首付款比例政策的通知》发布，自2026年3月16日起，上海市商业用房购房贷款最低首付款比例调整为不低于30%。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
@@ -1205,48 +1238,44 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sh600227</t>
+          <t>sz000042</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">赤天化  </t>
+          <t>中洲控股</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>4.81</v>
+        <v>9.5</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>10.07</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7天4板</t>
-        </is>
-      </c>
+        <v>9.950000000000001</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>化肥|公司是贵州省最大的氮肥生产企业，公司化肥化工生产基地分别是以天然气为原料生产的赤水化工分公司（年产63万吨尿素）和以煤为生产原料的公司全资子公司桐梓化工（年产52万吨尿素、30万吨甲醇）。</t>
+          <t>房地产|公司以房地产开发为主营业务，项目分布于粤港澳大湾区、大上海、成渝、环渤海四大经济圈核心城市。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>化肥</t>
+          <t>房地产</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>房地产概念</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>-0.51</v>
+        <v>0.25</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>航运数据显示，目前有21艘满载尿素、硫磺和磷肥的船只滞留波斯湾，涉及近百万吨化肥原料；若航运中断常态化，全球肥料原料供应可能会减少30%至50%。</t>
+          <t>《关于调整上海市商业用房购房贷款最低首付款比例政策的通知》发布，自2026年3月16日起，上海市商业用房购房贷款最低首付款比例调整为不低于30%。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
@@ -1254,48 +1283,44 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sh600370</t>
+          <t>sh600791</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">三房巷  </t>
+          <t>京能置业</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>3</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>9.890000000000001</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>9.99</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>化工|公司成为“PTA-瓶级聚酯切片”一体化布局的优势企业，PTA产品是郑州商品交易所PTA交割免检品牌，已开发出多种全系列的瓶级聚酯切片产品。</t>
+          <t>房地产|公司主营房地产开发与经营，拥有十余年的房地产开发经验，拥有一套较为完善的房地产开发和管理模式。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>房地产</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>房地产概念</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>-0.51</v>
+        <v>0.25</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>航运数据显示，目前有21艘满载尿素、硫磺和磷肥的船只滞留波斯湾，涉及近百万吨化肥原料；若航运中断常态化，全球肥料原料供应可能会减少30%至50%。</t>
+          <t>《关于调整上海市商业用房购房贷款最低首付款比例政策的通知》发布，自2026年3月16日起，上海市商业用房购房贷款最低首付款比例调整为不低于30%。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
@@ -1303,179 +1328,189 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sh605366</t>
+          <t>sz002285</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>宏柏新材</t>
+          <t>世联行</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>10.79</v>
+        <v>3.41</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>化工|公司主营业务为功能性硅烷、纳米硅材料等硅基新材料及其他化学助剂的研发、生产与销售，是我国功能性硅烷，特别是含硫硅烷细分领域中具备循环经济体系及世界领先产业规模的企业之一，拥有全球产量最大的含硫硅烷（含固体硅烷）生产线。</t>
+          <t>房地产+AMC|1.公司专注房地产服务业，凭借对行业发展的理解和客户需求的认知，叠加了金融、资管、互联网+（电商）等创新服务。
+2.公司旗下财信世联定位轻资产服务，致力于成为不良资产经营管理领域的专业“资产打理人”。</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>房地产, AMC</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>航运</t>
+          <t>氢能</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>3.29</v>
+        <v>-2.26</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>中信建投研报称，由库存安全阈值上移催生的常规补库与安全补库叠加需求，若在政策边际松动或行业旺季临近阶段集中释放，将成为驱动油运行业下一轮运价大幅上行的核心催化因素。</t>
+          <t xml:space="preserve">工信部等三部门发布《关于开展氢能综合应用试点工作的通知》：氢能终端价格到2030年下降约43%。每个城市群试点期为4年，单个城市群试点期内奖励上限不超过16亿元。
+</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sh600751</t>
+          <t>sh600408</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>海航科技</t>
+          <t>安泰集团</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>4.32</v>
+        <v>4.3</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>9.92</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
+        <v>9.969999999999999</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>航运|公司成立之初便立足航运市场，以国际近洋集装箱班轮运输、国内沿海集装箱班轮运输及船务代理和货运代理等为主营业务，在天津市乃至全国都属较早布局航运市场的企业之一。公司总可控运力达105万载重吨。</t>
+          <t>煤炭+氢能|1.公司主营焦炭及其副产品，炼焦采用的是JN60-6型焦炉，产品主要销售给钢铁企业。目前公司焦炭年生产能力已达到240万吨，是山西省焦化龙头企业之一。
+2.公司于2023年3月17日披露2023年非公开发行A股股票预案，拟定增募资不超过6.7亿元，用于山西宏安焦化科技有限公司150t/h干熄焦及配套余热综合利用项目、山西安泰集团股份有限公司30000m³/h焦炉煤气制氢项目。其中30000m³/h焦炉煤气制氢项目总投资6.45亿元，项目主要是以焦炉煤气为原料制取氢气。</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>航运</t>
+          <t>煤炭, 氢能</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>航运</t>
+          <t>氢能</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>3.29</v>
+        <v>-2.26</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>中信建投研报称，由库存安全阈值上移催生的常规补库与安全补库叠加需求，若在政策边际松动或行业旺季临近阶段集中释放，将成为驱动油运行业下一轮运价大幅上行的核心催化因素。</t>
+          <t xml:space="preserve">工信部等三部门发布《关于开展氢能综合应用试点工作的通知》：氢能终端价格到2030年下降约43%。每个城市群试点期为4年，单个城市群试点期内奖励上限不超过16亿元。
+</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sh601975</t>
+          <t>sz000572</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>招商南油</t>
+          <t>海马汽车</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>4.81</v>
+        <v>6.82</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>10.07</v>
+        <v>10</v>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>油运|公司是招商局集团旗下从事油轮运输的专业化公司，市场定位为全球石化产品的运输服务商。</t>
+          <t>氢能|公司通过多年氢燃料电池汽车研发，从最初“35MPa储氢瓶+30kW石墨双极板电堆”的第一代氢燃料电池技术验证样车，发展到搭载“70MPa高压储氢瓶+100kW高功率金属双极板电堆”可示范运营的第四代氢燃料电池汽车。公司规划在海南推进全产业链零碳排放汽车生态体建设，于海南的首座制氢加氢一体化站及配套分布式光伏项目已建设完成并投入运营，制氢加氢一体化站采用太阳能发电，采用绿电于站内电解水制备绿氢并存储。</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>油运</t>
+          <t>氢能</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>氢能</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>2.19</v>
+        <v>-2.26</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>分析师郭明錤最新供应链调查，英伟达已与PCB厂商就下一代覆铜板(CCL)材料M10启动测试，目标应用涵盖Rubin Ultra及Feynman平台的正交背板与交换刀片主板。</t>
+          <t xml:space="preserve">工信部等三部门发布《关于开展氢能综合应用试点工作的通知》：氢能终端价格到2030年下降约43%。每个城市群试点期为4年，单个城市群试点期内奖励上限不超过16亿元。
+</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>sh600545</t>
+          <t>sh605167</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>卓郎智能</t>
+          <t xml:space="preserve">利柏特  </t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>4.21</v>
+        <v>18.57</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>9.92</v>
+        <v>10.01</v>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>玻纤捻线机|2025年6月28日公司官微透露，公司与国际复材签订了加捻事业部史上最大额玻璃纤维捻线机订单。玻纤凭借其低介电常数等特性，已成为制造高频高速PCB与高性能芯片封装材料的不二之选。</t>
+          <t>核电+氢能|1.公司具有代表性的产品为核电气体分离装置，该装置用于核电制氦，是热核聚变实验堆辅助装备之一。
+2.公司专注于工业模块的设计和制造，目前已开展电解氢装置模块化技术研究。</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>玻纤捻线机</t>
+          <t>核电, 氢能</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>2.19</v>
+        <v>0.19</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>分析师郭明錤最新供应链调查，英伟达已与PCB厂商就下一代覆铜板(CCL)材料M10启动测试，目标应用涵盖Rubin Ultra及Feynman平台的正交背板与交换刀片主板。</t>
+          <t>工业和信息化部、财政部、国家发展改革委发布《关于开展氢能综合应用试点工作的通知》。绿氢在化工、钢铁、供热等领域的规模化应用，首次获得国家级财政资金的直接支持。</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
@@ -1483,44 +1518,49 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>sz002636</t>
+          <t>sh600307</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>金安国纪</t>
+          <t>酒钢宏兴</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>31.96</v>
+        <v>2.2</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>PCB|公司主要产品包括各种通用FR-5、FR-4、CEM-3等系列覆铜板及铝基覆铜板、半固化片等和特殊指标要求的无卤环保、高阻燃、耐CAF、高TG、高CTI等系列覆铜板；此外，公司还从事覆铜板的原材料电子级玻纤布以及下游PCB产品的生产和销售。</t>
+          <t>钢铁+铜|1.西北地区综合型钢铁企业，具备年产1000万吨以上钢材的生产能力，拥有四座矿山，铁矿储量达3.5亿吨。
+2.2024年7月4日公告，近期公司通过公开竞标方式，以3.3亿元价格竞得了甘肃省肃南县桦树沟西部铁铜矿详查探矿权。该探矿权和公司镜铁山矿桦树沟采矿权无缝衔接。经甘肃省矿产资源储量评审中心评审，此次竞得的该详查探矿权范围内查明和预测的资源量为：铁矿石资源量4885.15万吨，TFe平均品位33.88%。铜矿石资源量424.81万吨，Cu平均品位0.98%。</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>钢铁, 铜</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>0.73</v>
+        <v>0.19</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>工信部2026年度拟在50个地区开展城域“毫秒用算”专项行动，提升算力高效运载能力，推动算网融合发展。</t>
+          <t>工业和信息化部、财政部、国家发展改革委发布《关于开展氢能综合应用试点工作的通知》。绿氢在化工、钢铁、供热等领域的规模化应用，首次获得国家级财政资金的直接支持。</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
@@ -1528,45 +1568,44 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>sz002467</t>
+          <t>sh600569</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>二六三</t>
+          <t>安阳钢铁</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>7.52</v>
+        <v>2.82</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>9.94</v>
+        <v>10.16</v>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>AI应用+算力|1.公司在WebRTC、QoS、实时音视频等核心技术基础上，深度融合AI与大模型能力，打造智能通信中枢。通过自研AICC人工智能客户联络中心，实现企业邮箱、视频直播等场景的端到端智能化交互。同时，研发投入持续向AI驱动的云通信解决方案倾斜，构建跨网络动态负载均衡与智能运维体系，支撑亿级并发场景下的服务稳定性。
-2.公司2020年4月22日在互动平台表示，公司的子公司上海二六三通信有限公司与NTT合资的控股子公司上海奈盛通信科技有限公司是国内第一家由民营通信公司与国际一流运营商合资经营的公司，其业务平台为国内第一个以国际运营商标准自建的IDC云计算平台。</t>
+          <t>钢铁|公司是集炼焦、烧结、冶炼、轧材及科研开发为一体的大型钢铁联合企业，可生产的钢材品种有中厚板、热轧卷板、冷轧卷板、高速线材、建材、型材等。</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>AI应用, 算力</t>
+          <t>钢铁</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>风电</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>0.73</v>
+        <v>-1.64</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>工信部2026年度拟在50个地区开展城域“毫秒用算”专项行动，提升算力高效运载能力，推动算网融合发展。</t>
+          <t>自然资源部党组在《求是》杂志发文指出，以产业更新推动建设现代海洋产业体系。大力发展海洋新兴产业，推动海上风电规范有序建设。</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
@@ -1574,45 +1613,48 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>sz002990</t>
+          <t>sh603248</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>盛视科技</t>
+          <t>锡华科技</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>28.95</v>
+        <v>34.12</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>9.99</v>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>算力+AI应用|1.2023年11月3日公司在互动平台表示，公司在武汉和深圳两地均配备有充足的算力集群，可对产品研发和项目交付的模型训练工作提供支撑服务。
-2.公司持续加大对人工智能、大数据、物联网等新一代信息技术的研发投入，旨在为客户提供符合未来发展的智能产品和“AI+行业”解决方案。公司在智慧口岸领域深耕二十余年，已成长为国内领先的智慧口岸查验系统整体解决方案提供商。同时，基于在智慧口岸领域的技术积累，公司已将业务拓展至智能交通、智慧机场、智慧园区、智慧城市管理等其他应用领域。</t>
+          <t>风电+次新|公司主要从事大型高端装备专用部件的研发、制造与销售，产品结构以风电齿轮箱专用部件为主、注塑机厚大专用部件为辅，是全球行业领先、质量可靠、技术卓越的大型高端装备专用部件制造商。</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>算力, AI应用</t>
+          <t>风电, 次新</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>风电</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>-0.96</v>
+        <v>-1.64</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>据南方电网消息，今年前两月，公司完成固定资产投资250.8亿元，同比增长95.3%；公司累计完成项目物资供应121亿元，同比增加57%。</t>
+          <t>自然资源部党组在《求是》杂志发文指出，以产业更新推动建设现代海洋产业体系。大力发展海洋新兴产业，推动海上风电规范有序建设。</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
@@ -1620,49 +1662,46 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>sh603421</t>
+          <t>sz301226</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>鼎信通讯</t>
+          <t>祥明智能</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>10.32</v>
+        <v>41.74</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>5天3板</t>
-        </is>
-      </c>
+        <v>20.01</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>半导体+电网设备|1.鼎信通讯在互动平台表示，公司芯片开发采用平头哥的CK802 32位内核架构，平头哥与公司签订有全面技术授权协议。
-2.公司的主营业务为低压用电系统产品的研发、生产、销售及服务，主要产品包括低压电力线载波通信模块（含芯片）产品、采集终端设备、智能电能表和配电终端等，主要应用于国家智能电网的用电信息采集系统和配网自动化系统。</t>
+          <t>风电+航天+储能|1.公司风机产品在风电设备上已有批量应用。
+2.公司在2025年WRC展会中首次公开展示四类核心产品：关节模组、内转子无框电机、外转子无框电机及航天无框电机。
+3.公司风机组件类产品可以应用到储能行业。离心风机、轴流风机可用于储能设备来调节温度。</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>半导体, 电网设备</t>
+          <t>风电, 航天, 储能</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>储能</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>-0.96</v>
+        <v>-2.47</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>据南方电网消息，今年前两月，公司完成固定资产投资250.8亿元，同比增长95.3%；公司累计完成项目物资供应121亿元，同比增加57%。</t>
+          <t>东吴证券预测，美国数据中心储能持续推动，欧洲、中东等项目大储需求旺盛。预计户储进入新的一轮增长周期，全球储能装机2026年或有60%以上增长，2027—2029年复合30%—50%增长。</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
@@ -1670,212 +1709,221 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
+          <t>sz002150</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>正泰电源</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>34.87</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>5天3板</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>储能+电网设备|1.旗下正泰电源是国内最早开始研发光伏逆变器的公司之一，业务范围涵盖光伏逆变器、光伏汇流箱、商用储能一体机、预装式光伏系统、预装式储能系统等。
+2.公司输配电控制设备业务主要产品包括高压成套开关设备、中低压成套开关设备、高低压开关元件及控制电器等，能够为下游各行业用户提供整体配电解决方案。</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>储能, 电网设备</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>储能</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>东吴证券预测，美国数据中心储能持续推动，欧洲、中东等项目大储需求旺盛。预计户储进入新的一轮增长周期，全球储能装机2026年或有60%以上增长，2027—2029年复合30%—50%增长。</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>sz301667</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>纳百川</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>105.36</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>储能|在储能热管理领域，公司已成为宁德时代、中创新航、阳光电源等国内排名前列的新能源电源设备厂商的供应商。</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>储能</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>智能电网</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>-2.99</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>国家电网3月14日发布消息，统计数据显示，1—2月，固定资产投资累计完成757亿元，同比增长80.6%，电网基础支撑和投资拉动效应显著。</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>sz000533</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>顺钠股份</t>
         </is>
       </c>
-      <c r="G26" s="2" t="n">
-        <v>18.66</v>
-      </c>
-      <c r="H26" s="2" t="n">
+      <c r="G28" s="2" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="H28" s="2" t="n">
         <v>10.02</v>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>核聚变+电网设备|1.公司研制的特殊用途干式变压器包括国际热核聚变实验堆（ITER）试验平台变压器。
 2.公司控股孙公司顺特设备在超算中心和数据中心这两个领域提供过干式变压器产品，曾向阿里巴巴、秦淮数据有限公司、万国数据服务有限公司、数据港股份有限公司等客户提供过变压器设备。</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>核聚变, 电网设备</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>电力</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>-2.08</v>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>随着人工智能的发展、算力需求的增加，对上游能源行业的拉动作用比较明显。1—2月份，电力、热力生产和供应业增加值同比增长5.1%。</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>sh600396</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>华电辽能</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>电力|公司是中国华电集团公司的实际控制的上市公司、中央企业的三级单位，同时也是一家集火力发电、风力发电、煤炭营销、供热、供汽为一体的综合性区域基础能源企业。</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>电力</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>电力</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>-2.08</v>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>随着人工智能的发展、算力需求的增加，对上游能源行业的拉动作用比较明显。1—2月份，电力、热力生产和供应业增加值同比增长5.1%。</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>sz002310</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>东方新能</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>绿电|2025年12月15日公告，公司拟以现金支付方式购买海城锐海100%股权和电投瑞享80%股权。其中，海城锐海100%股权拟通过在天津产权交易中心摘牌方式购买。标的资产的审计和评估工作尚未完成，评估值及交易价格均尚未确定（海城锐海100%股权在天津产权交易所的挂牌转让底价为1410万元）。本次交易预计构成重大资产重组。通过本次交易，东方园林新增光伏电站、风电场的投资、开发、建设和运营等新能源业务。</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>绿电</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>复合集流体</t>
+          <t>智能电网</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>2.81</v>
+        <v>-2.99</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>3月10日，建滔集团发布涨价通知，通知表示，自当日接单起，对板料、PP(半固化片)及铜箔加工费等所有厚度规格产品同步提价10%。</t>
+          <t>国家电网3月14日发布消息，统计数据显示，1—2月，固定资产投资累计完成757亿元，同比增长80.6%，电网基础支撑和投资拉动效应显著。</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>sz002426</t>
+          <t>sz301680</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>胜利精密</t>
+          <t>固德电材</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>4.47</v>
+        <v>130.8</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>10.1</v>
+        <v>20</v>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>复合铜箔|公司复合铜箔项目采用PET或PP作为基材原料，选择“基材-磁控溅射-水镀”的工艺路线；目前送样检测的客户为动力电池厂商</t>
+          <t>电网设备+次新|公司电力电工绝缘产品包括：发电侧绝缘产品的VPI浸渍树脂、绝缘结构件、云母带，供电侧绝缘产品的浇注树脂、母线用云母件，用电侧绝缘产品的电机灌封树脂、家电绝缘件、医疗设备特种树脂。在电力发电设备领域，公司主要客户包括东方电气、上海电气、哈电集团等大型发电设备制造商；在特高压输配电领域，公司与特变电工、思源电气、南京电气、中国西电等输配电龙头企业保持深度合作。</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>复合铜箔</t>
+          <t>电网设备, 次新</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>国家统计局发布数据显示，1—2月份，社会消费品零售总额86079亿元，同比增长2.8%，比上年12月份加快1.9个百分点。</t>
-        </is>
-      </c>
+        <v>-0.73</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="2" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>sz000639</t>
+          <t>sz000908</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>西王食品</t>
+          <t>*ST景峰</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>3.14</v>
+        <v>5.57</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>10.18</v>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
+        <v>5.09</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>9天7板</t>
+        </is>
+      </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>食用油|国内最大的玉米胚芽油生产基地，主要生产销售西王牌系列健康食用油。</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>食用油</t>
-        </is>
-      </c>
+          <t>ST股 | 公司专注医药健康产业，涉足药品研发、生产、销售等领域，产品涵盖了心脑血管、抗肿瘤、骨科、妇儿等用药领域。</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1884,36 +1932,36 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0.48</v>
+        <v>-0.73</v>
       </c>
       <c r="C31" s="2" t="inlineStr"/>
       <c r="D31" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>sz000908</t>
+          <t>sh600599</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>*ST景峰</t>
+          <t xml:space="preserve">*ST熊猫 </t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>5.3</v>
+        <v>5.61</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>4.95</v>
+        <v>5.06</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8天6板</t>
+          <t>6天6板</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司专注医药健康产业，涉足药品研发、生产、销售等领域，产品涵盖了心脑血管、抗肿瘤、骨科、妇儿等用药领域。</t>
+          <t>ST股 | 公司地处中国烟花之乡浏阳，经过3多年的发展已成为中国最大的出口鞭炮烟花公司</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
@@ -1925,11 +1973,11 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>0.48</v>
+        <v>-0.73</v>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -1942,14 +1990,14 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="H32" s="2" t="n">
         <v>5.1</v>
       </c>
-      <c r="H32" s="2" t="n">
-        <v>4.94</v>
-      </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5天5板</t>
+          <t>6天6板</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -1966,27 +2014,27 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>0.48</v>
+        <v>-0.73</v>
       </c>
       <c r="C33" s="2" t="inlineStr"/>
       <c r="D33" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>sh600599</t>
+          <t>sh603843</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST熊猫 </t>
+          <t xml:space="preserve">*ST正平 </t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>5.34</v>
+        <v>7.39</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>4.91</v>
+        <v>4.97</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
@@ -1995,7 +2043,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司地处中国烟花之乡浏阳，经过3多年的发展已成为中国最大的出口鞭炮烟花公司</t>
+          <t>ST股 | 2025年2月21日公司官微披露，旗下正平智算参加海东市绿色算力产业集中签约暨推介活动并签订算电协同产业园框架协议。</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
@@ -2007,36 +2055,36 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>0.48</v>
+        <v>-0.73</v>
       </c>
       <c r="C34" s="2" t="inlineStr"/>
       <c r="D34" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>sh603843</t>
+          <t>sz000488</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST正平 </t>
+          <t>ST晨鸣</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>7.04</v>
+        <v>3.05</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>5.07</v>
+        <v>5.17</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4天4板</t>
+          <t>8天5板</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 2025年2月21日公司官微披露，旗下正平智算参加海东市绿色算力产业集中签约暨推介活动并签订算电协同产业园框架协议。</t>
+          <t>ST股 | 公司是全国唯一一家实现制浆和造纸平衡的大型浆纸一体化企业，率先布局全产业链，在山东、广东、湖北、江西、吉林等地建有6个生产基地，年浆纸产能达1100多万吨。</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
@@ -2048,36 +2096,37 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>0.48</v>
+        <v>-0.73</v>
       </c>
       <c r="C35" s="2" t="inlineStr"/>
       <c r="D35" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sz002789</t>
+          <t>sz002253</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>*ST建艺</t>
+          <t>*ST智胜</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>11.46</v>
+        <v>11.34</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>5.04</v>
+        <v>5</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5天3板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司是集施工、设计、资源矿产、科技工业园、高新技术建材产业、投融资为一体的规模化实体企业集团。</t>
+          <t>ST股 | 1.公司于2021年6月18日在互动平台表示，公司与华为目前的合作主要是在昇腾芯片，鲲鹏服务器上的三维人脸识别算法的平台适配以及智慧园区的方案实施。
+2.公司拥有自主研发的针对低空安全管控需求研制的低空监视雷达系统，可以实现组网对广域范围低空空域进行连续监视。</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
@@ -2089,27 +2138,27 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>0.48</v>
+        <v>-0.73</v>
       </c>
       <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sz002693</t>
+          <t>sh600381</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>*ST双成</t>
+          <t xml:space="preserve">*ST春天 </t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>8.050000000000001</v>
+        <v>2.88</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>4.95</v>
+        <v>5.11</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
@@ -2118,7 +2167,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 地处海南省海口市，专业从事化学合成多肽药品。</t>
+          <t>ST股 | 在大健康业务方面，公司已基本完成了涵盖保健食品、药品等冬虫夏草高效利用产品的储备和战略布局。</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
@@ -2130,37 +2179,36 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>0.48</v>
+        <v>-0.73</v>
       </c>
       <c r="C37" s="2" t="inlineStr"/>
       <c r="D37" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sz002512</t>
+          <t>sh600289</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>ST达华</t>
+          <t xml:space="preserve">ST信通  </t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>4.79</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>5.04</v>
+        <v>5.02</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3天2板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 1.在量子安全通信领域，公司已经形成了量子安全卫星互联网通信的全套解决方案，已进行试点应用。
-2.公司子公司海丝卫星是专业提供卫星互联网服务的运营商，通过直接为终端客户提供一站式全场景卫星宽带接入及行业垂直应用服务，解决海洋通信、应急通信及偏远山区等场景网络覆盖问题。</t>
+          <t>ST股 | 公司在智能交通领域继续保持稳健发展，着重提升项目的盈利能力。</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
@@ -2172,32 +2220,33 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>0.48</v>
+        <v>-0.73</v>
       </c>
       <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>sz000488</t>
+          <t>sh603398</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>ST晨鸣</t>
+          <t xml:space="preserve">*ST沐邦 </t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>2.9</v>
+        <v>10.21</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>5.07</v>
+        <v>5.04</v>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司是全国唯一一家实现制浆和造纸平衡的大型浆纸一体化企业，率先布局全产业链，在山东、广东、湖北、江西、吉林等地建有6个生产基地，年浆纸产能达1100多万吨。</t>
+          <t>ST股 | 1.沐邦高科公告，与铜陵狮子山高新技术产业开发区管理委员会、铜陵高新发展投资有限公司签订《项目投资协议书》，项目名称为年产10GW-N型高效电池片、10GW切片生产基地项目。
+2.公司上市的IP产品 “樱桃小丸子”第一期为“盲盒”类产品。</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
@@ -2209,32 +2258,32 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>0.48</v>
+        <v>-0.73</v>
       </c>
       <c r="C39" s="2" t="inlineStr"/>
       <c r="D39" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>sh603557</t>
+          <t>sz000820</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST起步  </t>
+          <t>*ST节能</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>4.21</v>
+        <v>3.49</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>4.99</v>
+        <v>5.12</v>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 国内童鞋龙头。旗下 ABC KIDS 占据我国童鞋第一、童装第七的市场地位。</t>
+          <t>ST股 | 公司致力于工业节能环保技术与资源综合利用技术的研发与推广，是工业节能环保与资源综合利用的技术方案提供商和工程总承包商。</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
@@ -2246,32 +2295,32 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>0.48</v>
+        <v>-0.73</v>
       </c>
       <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>sh600892</t>
+          <t>sz002808</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST大晟 </t>
+          <t>*ST恒久</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>3.81</v>
+        <v>4.32</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>4.96</v>
+        <v>5.11</v>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司的主营业务为网络游戏研发、运营以及影视剧制作、发行业务。</t>
+          <t>ST股 | 公司的控股子公司福建省闽保信息技术有限公司是一家从事信息安全领域软件开发及系统集成的高新技术企业。</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
@@ -2283,32 +2332,32 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>0.48</v>
+        <v>-0.73</v>
       </c>
       <c r="C41" s="2" t="inlineStr"/>
       <c r="D41" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>sh600381</t>
+          <t>sh603580</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST春天 </t>
+          <t xml:space="preserve">*ST艾艾 </t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>2.74</v>
+        <v>15.7</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>4.98</v>
+        <v>5.02</v>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 在大健康业务方面，公司已基本完成了涵盖保健食品、药品等冬虫夏草高效利用产品的储备和战略布局。</t>
+          <t>ST股 | 公司是专业从事为轻型输送带的研发、生产及销售，境外营业收入大于50%。</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
@@ -2320,32 +2369,32 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>0.48</v>
+        <v>-0.73</v>
       </c>
       <c r="C42" s="2" t="inlineStr"/>
       <c r="D42" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>sz002529</t>
+          <t>sh600265</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>*ST海源</t>
+          <t xml:space="preserve">ST景谷  </t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>7.34</v>
+        <v>20.72</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司拟收购赛维电源科技有限公司100%股权，赛维电源拥有先进的光伏组件研发生产技术，公司通过此次收购，将建立光伏组件方面的核心技术和管理团队，进入光伏组件领域。</t>
+          <t>ST股 | 公司是云南省林业产业化、农业产业化和国家重点扶贫龙头企业。公司主要从事林化产品加工和人造板制造、森林资源培育、木材采运、加工及林业技术研发等业务。</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
@@ -2353,151 +2402,191 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="n">
-        <v>0.48</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C43" s="2" t="inlineStr"/>
       <c r="D43" s="2" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>sh603789</t>
+          <t>sz000890</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST星农 </t>
+          <t>法尔胜</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>5.64</v>
+        <v>13.42</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>5.029999999999999</v>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>4天4板</t>
+        </is>
+      </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司拥有包括水稻、小麦、玉米等粮食作物的收获机，以及棉花、花生等经济作物的收获机，并覆盖旋耕、收割、打捆、烘干等主要农业生产环节。</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr"/>
+          <t>光纤光缆|公司参股的普天法尔胜光通信有限公司主要产品为光纤预制棒、光纤、光缆，上述产品可以应用于在运营商基础网络通信及广播电视通信领域。</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>光纤光缆</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="n">
-        <v>0.48</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>sz000668</t>
+          <t>sh600683</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>*ST荣控</t>
+          <t>京投发展</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>14.13</v>
+        <v>10.6</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="I44" s="2" t="inlineStr"/>
+        <v>9.959999999999999</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司主营业务为房地产开发，经营模式以自主开发销售为主，曾推出国内第一个小户型楼盘，第一家运动主题社区，在业内产生较大影响。</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr"/>
+          <t>剥离地产业务|京投发展公告称，公司拟将持有的房地产开发业务相关资产及负债转让至控股股东京投公司，采用现金支付方式，不涉及发行股份，不影响公司股权结构，不会因此导致公司控股股东发生变更。本事项预计构成重大资产重组。</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>剥离地产业务</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="n">
-        <v>0.48</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>sz002253</t>
+          <t>sh603929</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>*ST智胜</t>
+          <t>亚翔集成</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>10.8</v>
+        <v>170.4</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="I45" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 1.公司于2021年6月18日在互动平台表示，公司与华为目前的合作主要是在昇腾芯片，鲲鹏服务器上的三维人脸识别算法的平台适配以及智慧园区的方案实施。
-2.公司拥有自主研发的针对低空安全管控需求研制的低空监视雷达系统，可以实现组网对广域范围低空空域进行连续监视。</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr"/>
+          <t>洁净室+业绩|1.公司作为一站式洁净室系统集成工程服务的专业提供商，主营业务为IC半导体、光电等高科技电子产业及生物医药、云计算中心等相关领域的建厂工程提供洁净室工程服务。
+2.亚翔集成发布2025年年度报告，公司实现营业收入49.07亿元，同比下降8.81%；归属于上市公司股东的净利润为8.92亿元，同比增长40.30%。公司拟向全体股东每10股派发现金红利16.50元（含税），分红总额为3.52亿元。</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>洁净室, 业绩</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="n">
-        <v>0.48</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>sh600289</t>
+          <t>sz000020</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST信通  </t>
+          <t>深华发Ａ</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>8.369999999999999</v>
+        <v>17.53</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="I46" s="2" t="inlineStr"/>
+        <v>9.969999999999999</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司在智能交通领域继续保持稳健发展，着重提升项目的盈利能力。</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
+          <t>面板|公司主营业务分为液晶显示器整机、注塑件、保丽龙（轻型材料包装）、物业租赁四大模块。液晶显示器整机业务生产经营各种彩色电视机、液晶显示器、液晶显示屏，是公司主要收入来源。</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>面板</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2512,23 +2601,23 @@
       </c>
       <c r="C47" s="2" t="inlineStr"/>
       <c r="D47" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>sh600683</t>
+          <t>sh600545</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>京投发展</t>
+          <t>卓郎智能</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>9.640000000000001</v>
+        <v>4.63</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>10.05</v>
+        <v>9.98</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
@@ -2537,12 +2626,12 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>剥离地产业务|京投发展公告称，公司拟将持有的房地产开发业务相关资产及负债转让至控股股东京投公司，采用现金支付方式，不涉及发行股份，不影响公司股权结构，不会因此导致公司控股股东发生变更。本事项预计构成重大资产重组。</t>
+          <t>玻纤捻线机|2025年6月28日公司官微透露，公司与国际复材签订了加捻事业部史上最大额玻璃纤维捻线机订单。玻纤凭借其低介电常数等特性，已成为制造高频高速PCB与高性能芯片封装材料的不二之选。</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>剥离地产业务</t>
+          <t>玻纤捻线机</t>
         </is>
       </c>
     </row>
@@ -2559,37 +2648,37 @@
       </c>
       <c r="C48" s="2" t="inlineStr"/>
       <c r="D48" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>sh603929</t>
+          <t>sh603992</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>亚翔集成</t>
+          <t>松霖科技</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>154.91</v>
+        <v>33.3</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>4天2板</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>业绩|亚翔集成发布2025年年度报告，公司实现营业收入49.07亿元，同比下降8.81%；归属于上市公司股东的净利润为8.92亿元，同比增长40.30%。公司拟向全体股东每10股派发现金红利16.50元（含税），分红总额为3.52亿元。</t>
+          <t>机器人|旗下松霖机器人与达闼机器人签署了战略合作框架协议，共同探索人形机器人垂直场景应用、核心部件创新升级、机器人出海及其他创新领域的产业机会。</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>业绩</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
@@ -2606,37 +2695,37 @@
       </c>
       <c r="C49" s="2" t="inlineStr"/>
       <c r="D49" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>sh603248</t>
+          <t>sh688295</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>锡华科技</t>
+          <t>中复神鹰</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>31.02</v>
+        <v>59.4</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>4天2板</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>风电|公司主要从事大型高端装备专用部件的研发、制造与销售，产品结构以风电齿轮箱专用部件为主、注塑机厚大专用部件为辅，是全球行业领先、质量可靠、技术卓越的大型高端装备专用部件制造商。</t>
+          <t>碳纤维|中复神鹰公告，近日公司全新推出SYT80（T1200级）碳纤维新品，实现SYT80碳纤维的百吨级制备。该产品参数为：拉伸强度8000MPa、拉伸模量324GPa、断裂伸长率2.5%、体密度1.79g/cm3。</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>碳纤维</t>
         </is>
       </c>
     </row>
@@ -2653,38 +2742,33 @@
       </c>
       <c r="C50" s="2" t="inlineStr"/>
       <c r="D50" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>sh603778</t>
+          <t>sh605277</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>国晟科技</t>
+          <t>新亚电子</t>
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>22.54</v>
+        <v>25.58</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>10.02</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>光伏+锂电池|1.公司目前从事大尺寸高效异质结光伏电池的研发、生产、销售，以及异质结、TOPCON、PERC等电池组件的生产与销售。控股孙公司恒立聚能涉及钙钛矿研究。
-2.国晟科技公告称，公司拟以2.406亿元的价格受让正豪科技、林琴合计持有的孚悦科技100%股权。交易完成后，公司将持有标的公司100%股权，标的公司将纳入公司合并报表。孚悦科技主要从事高精密度新型锂电池结构件的研发、生产和销售。</t>
+          <t>高速铜缆连接线|新亚电子在互动平台表示，公司高频高速铜缆连接线通过安费诺进入戴尔、惠普、谷歌、亚马逊、微软、甲骨文、Meta、浪潮、新华三、中科曙光等知名服务器制造商供应链。</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>光伏, 锂电池</t>
+          <t>高速铜缆连接线</t>
         </is>
       </c>
     </row>
@@ -2701,37 +2785,33 @@
       </c>
       <c r="C51" s="2" t="inlineStr"/>
       <c r="D51" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>sz002831</t>
+          <t>sh600643</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>裕同科技</t>
+          <t>爱建集团</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>38.02</v>
+        <v>5.12</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>10.11</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>并购重组|裕同科技公告称，公司拟通过自有或自筹资金向观点投资收购其持有的华研科技51%股份，交易金额为4.49亿元。本次交易构成关联交易，公司实际控制人王华君、吴兰兰夫妇合计持有观点投资100%股权。交易完成后，华研科技将成为公司的控股子公司，并纳入公司合并报表范围。东莞市华研新材料科技有限公司成立于2016年，致力于为客户提供一站式精密金属及陶瓷零组件整体解决方案，一体化设计、研发、制造、组装整体解决方案的专精特新国家级“小巨人”高新技术企业。</t>
+          <t>多元金融|公司致力于成为一家以金融业为主体、专注于提供财富管理和资产管理综合服务的成长性上市公司，下属爱建信托公司、爱建租赁公司、华瑞租赁公司、爱建资产公司、爱建产业公司、爱建资本公司、爱建基金销售公司、爱建香港公司、爱建保理公司等子公司围绕相应主业开展业务。</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>并购重组</t>
+          <t>多元金融</t>
         </is>
       </c>
     </row>
@@ -2748,33 +2828,33 @@
       </c>
       <c r="C52" s="2" t="inlineStr"/>
       <c r="D52" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>sh600302</t>
+          <t>sz002565</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>标准股份</t>
+          <t>顺灏股份</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>11.29</v>
+        <v>14.74</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>10.04</v>
+        <v>10</v>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>拟股权转让|标准股份公告称，公司控股股东标准集团拟通过公开征集转让方式协议转让其持有的公司不超过27.77%（含）且不低于控制权变更比例的股份。公司股票将于2025年10月28日开市起复牌。标准集团直接持有公司1.48亿股A股股份，占公司总股本的42.77%，均为非限售流通股份。</t>
+          <t>太空算力|公司2025年6月以1.1亿元人民币投资北京轨道辰光科技有限公司，持股比例为19.30%。轨道辰光的主要业务是通过将算力卫星发射至晨昏轨道，组建太空数据中心，为客户提供算力服务，其经营范围包括微小卫星生产制造、微小卫星科研试验、互联网信息服务等。轨道辰光首颗试验星算力规模预计25p。</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>拟股权转让</t>
+          <t>太空算力</t>
         </is>
       </c>
     </row>
@@ -2791,377 +2871,33 @@
       </c>
       <c r="C53" s="2" t="inlineStr"/>
       <c r="D53" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>sz001278</t>
+          <t>sh603387</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>一彬科技</t>
+          <t>基蛋生物</t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>25.32</v>
+        <v>9.44</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>9.99</v>
+        <v>10.02</v>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司通过参股共青城民生创新智能投资合伙企业（有限合伙）间接投资法奥意威（苏州）机器人系统有限公司，持股比例为1.28%。法奥机器人主营全零部件自研协作机器人研发、制造及销售，产品主要应用场景有:3D 焊接机器人、移动焊接机器人、移动码垛工作站、螺丝锁付工作站、井字棋游戏机器人以及喷涂、上下料、餐饮制作等应用场景。</t>
+          <t>医疗器械|基蛋生物属于医疗器械制造行业，主要从事 POCT （中文译为现场即时检测）体外诊断产品的研发、生产和销售，主要产品为 POCT 体外诊断试剂及配套仪器。</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr"/>
-      <c r="D54" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>sz000020</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>深华发Ａ</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>15.94</v>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>面板|公司主营业务分为液晶显示器整机、注塑件、保丽龙（轻型材料包装）、物业租赁四大模块。液晶显示器整机业务生产经营各种彩色电视机、液晶显示器、液晶显示屏，是公司主要收入来源。</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>面板</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr"/>
-      <c r="D55" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>sh605299</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>舒华体育</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>9.969999999999999</v>
-      </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>体育产业|公司主营业务为健身器材和展示架产品的研发、生产和销售，其中健身器材包括室内健身器材、室外路径产品。</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>体育产业</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr"/>
-      <c r="D56" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>sh600152</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>维科技术</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>3C数码电池|公司以3C数码电池为核心业务，并以小动力BMS、高倍率电池、小型聚合物锂离子电池为快速增长业务。公司是行业领先的集锂离子电池研发、制造、销售及服务于一体的新能源科技型企业，具备电芯制造、封装和系统整合方案一体化能力。</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>3C数码电池</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr"/>
-      <c r="D57" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>sh600313</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>农发种业</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>9.08</v>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>10.06</v>
-      </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>种业|公司主营业务的核心为农作物种子业务，产品涵盖玉米、水稻、小麦、棉花、油菜、甘蔗和马铃薯等多种农作物种子（苗），分别由公司所属的河南地神等8家种业子公司开展农作物种子的研发、繁育、生产和销售。</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>种业</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr"/>
-      <c r="D58" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>sz000617</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>中油资本</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>9.77</v>
-      </c>
-      <c r="H58" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>数字货币+跨境支付|公司及所属金融企业开展数字人民币方面的研究规划，参股企业昆仑数智联合出资成立的鲲鹏快付公司正在开展数字人民币支付业务；公司为昆仑银行大股东，昆仑银行是参与CIPS的银行机构之一。</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>数字货币, 跨境支付</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr"/>
-      <c r="D59" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>sz002995</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>天地在线</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>24.77</v>
-      </c>
-      <c r="H59" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>AI应用|公司已推出AI数字人SAAS产品“星河AI数字人系统”以及帮助企业提高工作效率和协作能力的AI智能应用产品“AIbase” ，满足客户在营销及提升企业经营效能的不同需求。</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>AI应用</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr"/>
-      <c r="D60" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>sz002235</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>安妮股份</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>11.56</v>
-      </c>
-      <c r="H60" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>控制权变更|安妮股份3月4日晚间公告表示，深交所已对转让双方提交的申请材料进行了完备性核对，并出具了《深圳证券交易所上市公司股份协议转让确认书》。公司控制权变更事项迎来重大进展。</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>控制权变更</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr"/>
-      <c r="D61" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>sz300051</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>琏升科技</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="n">
-        <v>11.12</v>
-      </c>
-      <c r="H61" s="2" t="n">
-        <v>19.96</v>
-      </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>光伏|2023年12月1日公司在调研中表示，公司目前已在眉山丹棱和江苏南通规划了2个生产基地，眉山琏升光伏异质结电池片项目总共规划8GW，江苏南通项目总规划12GW。</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>光伏</t>
+          <t>医疗器械</t>
         </is>
       </c>
     </row>
@@ -3176,7 +2912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3203,7 +2939,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -3218,7 +2954,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
@@ -3233,7 +2969,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -3248,7 +2984,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
@@ -3263,7 +2999,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -3278,16 +3014,91 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>sh600683</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>京投发展</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>sh600683</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>京投发展</t>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>sh600545</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>卓郎智能</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>sz000020</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>深华发Ａ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>sh603778</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>国晟科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>sh600396</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>华电辽能</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>sz000533</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>顺钠股份</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,19 +476,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="89" customWidth="1" min="3" max="3"/>
+    <col width="75" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="227" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="232" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -560,139 +560,138 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>国家明确要求国家算力枢纽节点新建数据中心的绿电占比不低于80%，这一硬性指标不仅为绿电创造了巨大的新增消纳场景，也推动着“绿电直连”“源网荷储一体化”等新型商业模式加速落地。</t>
+          <t>2026年政府工作报告中，“算电协同”首次被写入，明确列为新基建工程。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>sh600726</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>华电能源</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>9.959999999999999</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>9天6板</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>电力|公司是黑龙江省最大的发电及集中供热运营商，主要产品为电力、热力，火力电厂分布在黑龙江省主要中心城市。</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>2026年政府工作报告中，“算电协同”首次被写入，明确列为新基建工程。</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>sh600396</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n">
-        <v>5.69</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>10.06</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>4天4板</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="G3" s="2" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>5天5板</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>电力+氢能|1.公司是中国华电集团公司的实际控制的上市公司、中央企业的三级单位，同时也是一家集火力发电、风力发电、煤炭营销、供热、供汽为一体的综合性区域基础能源企业。
 2.2023年3月14日公告，拟与华电科工共同出资建设25MW风电离网制氢一体化项目，风电设备年利用小时数3000小时，年发电量约7500万千瓦时，全部发电量均用于本项目制取绿氢，预计年产绿氢1230吨。项目总投资2.78亿元。公司与华电科工拟按70%和30%比例组建项目公司。</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>电力, 氢能</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>电力</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B4" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>国家明确要求国家算力枢纽节点新建数据中心的绿电占比不低于80%，这一硬性指标不仅为绿电创造了巨大的新增消纳场景，也推动着“绿电直连”“源网荷储一体化”等新型商业模式加速落地。</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2026年政府工作报告中，“算电协同”首次被写入，明确列为新基建工程。</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>sz000601</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>韶能股份</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>9.959999999999999</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>算电协同|1.公司自成立以来，一直以能源的投资开发经营为主营业务，在不断巩固和发展水电产业的基础上，重点发展生物质能发电、加油加气充电一体化站等业务。
 2.韶能算电公司拟在乐昌市成立全资子公司，开发清洁电源业务，注册资本10亿元；若该项目投产，有利于壮大公司清洁能源规模，为韶关数据集群提供绿电供应。</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>算电协同</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>电力</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>国家明确要求国家算力枢纽节点新建数据中心的绿电占比不低于80%，这一硬性指标不仅为绿电创造了巨大的新增消纳场景，也推动着“绿电直连”“源网荷储一体化”等新型商业模式加速落地。</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>sz000539</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>粤电力Ａ</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>算电协同|1.公司主要从事电力项目的投资、建设和经营管理，电力的生产和销售业务，拥有大型燃煤发电、LNG发电、风力发电和水力发电等多种能源项目。
-2.粤电力A互动平台表示，广东能源克拉玛依光伏项目规划配套建设算力规模500PFlops的智算中心。</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>算电协同</t>
@@ -710,11 +709,11 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>国家明确要求国家算力枢纽节点新建数据中心的绿电占比不低于80%，这一硬性指标不仅为绿电创造了巨大的新增消纳场景，也推动着“绿电直连”“源网荷储一体化”等新型商业模式加速落地。</t>
+          <t>2026年政府工作报告中，“算电协同”首次被写入，明确列为新基建工程。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -727,14 +726,14 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>3.16</v>
+        <v>3.48</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>10.1</v>
+        <v>10.13</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4天2板</t>
+          <t>5天3板</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -759,38 +758,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>国家明确要求国家算力枢纽节点新建数据中心的绿电占比不低于80%，这一硬性指标不仅为绿电创造了巨大的新增消纳场景，也推动着“绿电直连”“源网荷储一体化”等新型商业模式加速落地。</t>
+          <t>2026年政府工作报告中，“算电协同”首次被写入，明确列为新基建工程。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sh600979</t>
+          <t>sz002256</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>广安爱众</t>
+          <t>兆新股份</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>5.74</v>
+        <v>4.49</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>9.959999999999999</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
+        <v>10.05</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>算电协同|1.公司主营业务为水力发电、供电、天然气供应、生活饮用水、水电气仪表校验安装和调试。
-2.公司参股20%重庆亿众旗下子公司于青海省海东市建设“丝绸云谷”低碳算力产业园，计划一期建设容量为180MW的液冷芯能舱，投建7.2万个标准机架，为9万台高性能服务器提供稳健的运行环境。</t>
+          <t>绿电+化工|1.公司新能源领域业务为光伏电站投资、建设、运营和管理。截至2024年期末，公司在安徽、江西、浙江、宁夏及四川等多个省份运营和管理10座太阳能光伏电站，累计并网装机容量约131.82MW。
+2.公司生产的精细化工产品包括环保功能涂料及辅料、绿色环保家居用品和环保节能汽车养护用品等，广泛应用于家庭用品、个人用品、工业与汽车用品等领域</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>算电协同</t>
+          <t>绿电, 化工</t>
         </is>
       </c>
     </row>
@@ -805,32 +808,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>国家明确要求国家算力枢纽节点新建数据中心的绿电占比不低于80%，这一硬性指标不仅为绿电创造了巨大的新增消纳场景，也推动着“绿电直连”“源网荷储一体化”等新型商业模式加速落地。</t>
+          <t>2026年政府工作报告中，“算电协同”首次被写入，明确列为新基建工程。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sz001258</t>
+          <t>sz000862</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>立新能源</t>
+          <t>银星能源</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>10.25</v>
+        <v>8.44</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>9.98</v>
+        <v>10.04</v>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>绿电|公司的主营业务为风力发电、光伏发电项目的投资、开发、建设和运营。公司运营的风电场、光伏电站主要位于新疆。</t>
+          <t>绿电|公司新能源发电业务包括风力发电、太阳能光伏发电以及分布式项目发电。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -850,65 +853,65 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>国家明确要求国家算力枢纽节点新建数据中心的绿电占比不低于80%，这一硬性指标不仅为绿电创造了巨大的新增消纳场景，也推动着“绿电直连”“源网荷储一体化”等新型商业模式加速落地。</t>
+          <t>2026年政府工作报告中，“算电协同”首次被写入，明确列为新基建工程。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sh600726</t>
+          <t>sh603165</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>华电能源</t>
+          <t>荣晟环保</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>5.02</v>
+        <v>14.96</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>10.09</v>
+        <v>10</v>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>电力|公司是黑龙江省最大的发电及集中供热运营商，主要产品为电力、热力，火力电厂分布在黑龙江省主要中心城市。</t>
+          <t>绿电|2022年1月4日公告，公司与安徽省全椒县人民政府签订年产130万吨再生环保纸及新能源综合利用项目战略合作框架协议，建设内容包括年产130万吨再生环保纸、生物质热电联产(年处理50万吨秸秆)、光伏产品研发和制造、1GW分布式光伏电站等运营管理，并配套建设工业固废资源综合利用项目、环保水处理项目，项目总投资105亿元。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>绿电</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-1.48</v>
+        <v>0.2</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>阿里云宣布AI算力、存储等产品最高涨价34％。百度智能云同日发布AI算力、存储等产品调价公告。</t>
+          <t>2026年政府工作报告中，“算电协同”首次被写入，明确列为新基建工程。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sh600666</t>
+          <t>sh600310</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">奥瑞德  </t>
+          <t>广西能源</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
@@ -917,191 +920,188 @@
       <c r="H9" s="2" t="n">
         <v>9.91</v>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+      <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>算力租赁|公司设立全资子公司北京智算力、深圳智算力，使用自有资金投资建设算力租赁一、二、三期项目。</t>
+          <t>电力|公司主营业务为电力生产和销售，包括水力发电、火力发电、光伏发电，拥有完整的发、供电网络，电厂和电网“厂网合一”，发电、供电和配电业务一体化经营。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>算力租赁</t>
+          <t>电力</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>储能</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-1.48</v>
+        <v>-0.75</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>阿里云宣布AI算力、存储等产品最高涨价34％。百度智能云同日发布AI算力、存储等产品调价公告。</t>
+          <t>据CESA储能应用分会产业数据库不完全统计，2026年2月，中国企业在海外共斩获30个储能订单，总计容量为35.71GWh。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sz000815</t>
+          <t>sz002150</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>美利云</t>
+          <t>正泰电源</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>19.32</v>
+        <v>34.88</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>10.02</v>
+        <v>10</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>8天4板</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>算力租赁|公司是中国诚通控股集团旗下上市公司，数据中心位于宁夏中卫市，处于国家战略工程“东数西算”的双节点城市。</t>
+          <t>储能+电网设备|1.旗下正泰电源是国内最早开始研发光伏逆变器的公司之一，业务范围涵盖光伏逆变器、光伏汇流箱、商用储能一体机、预装式光伏系统、预装式储能系统等。
+2.公司输配电控制设备业务主要产品包括高压成套开关设备、中低压成套开关设备、高低压开关元件及控制电器等，能够为下游各行业用户提供整体配电解决方案。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>算力租赁</t>
+          <t>储能, 电网设备</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>储能</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>-1.48</v>
+        <v>-0.75</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>阿里云宣布AI算力、存储等产品最高涨价34％。百度智能云同日发布AI算力、存储等产品调价公告。</t>
+          <t>据CESA储能应用分会产业数据库不完全统计，2026年2月，中国企业在海外共斩获30个储能订单，总计容量为35.71GWh。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sh600996</t>
+          <t>sz301658</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>贵广网络</t>
+          <t>首航新能</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>9.5</v>
+        <v>60.35</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>9.950000000000001</v>
+        <v>20</v>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>算力+华为|1.贵州广播电视台旗下上市公司。公司将致力于贵州与粤港澳、长三角、京津冀等地区大数据中心集群的算力资源对接，充分发挥贵州省作为南方数据中心示范基地优势，有效承接东部算力需求。
-2.公司与华为技术有限公司在深圳签订战略合作协议，公司与华为将携手在贵州省内就华为融合视频、华为云、大数据及AI、广电5G及基础网络、集客业务、物联网等领域进行紧密合作。</t>
+          <t>储能|公司的储能电池主要为磷酸铁锂电池，能够适配多品牌光伏储能逆变器，主要应用于户用及小型工商业储能。公司光伏储能逆变器功率范围已涵盖3kW~20kW，适用于户用、小型工商业并离网储能多种场景。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>算力, 华为</t>
+          <t>储能</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>储能</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>-1.48</v>
+        <v>-0.75</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>阿里云宣布AI算力、存储等产品最高涨价34％。百度智能云同日发布AI算力、存储等产品调价公告。</t>
+          <t>据CESA储能应用分会产业数据库不完全统计，2026年2月，中国企业在海外共斩获30个储能订单，总计容量为35.71GWh。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sz300895</t>
+          <t>sh603381</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>铜牛信息</t>
+          <t>永臻股份</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>76.34</v>
+        <v>28.22</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>19.99</v>
+        <v>10.02</v>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>算力租赁|公司是北京市国资委下属企业，是在国内尤其是在北京地区少数拥有自有房产自建数据中心且自主搭建云平台的专业IDC服务商之一。</t>
+          <t>储能+光伏|1.公司主要从事绿色能源结构材料的研发、生产、销售及应用，已成为国内领先的铝合金光伏结构件制造商之一。
+2.公司与比亚迪汽车工业有限公司于2025年10月9日签署了《战略合作协议》，在储能等项目以及比亚迪所需的储能铝合金部件等领域开展合作。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>算力租赁</t>
+          <t>储能, 光伏</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>储能</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-1.48</v>
+        <v>-0.75</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>阿里云宣布AI算力、存储等产品最高涨价34％。百度智能云同日发布AI算力、存储等产品调价公告。</t>
+          <t>据CESA储能应用分会产业数据库不完全统计，2026年2月，中国企业在海外共斩获30个储能订单，总计容量为35.71GWh。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sh603629</t>
+          <t>sz001283</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>利通电子</t>
+          <t>豪鹏科技</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>68.06999999999999</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>10</v>
@@ -1109,225 +1109,230 @@
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>算力租赁|公司目前对外出租AI算力规模已达10000P以上，其中，约4000P是以自有算力（报表中在固定资产科目列示）出租，其余是转租算力（在使用权资产科目列示）出租。</t>
+          <t>储能|2023年1月9日公司接受机构调研时表示，公司现有产品中包含便携式储能产品，其广泛应用于应急救灾、户外活动及家庭备用电源等场景，目前公司主要向一家北美客户供应电池模组，公司将在做好当前客户服务的基础上，积极开拓新客户和新业务模式布局。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>算力租赁</t>
+          <t>储能</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>储能</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>-1.48</v>
+        <v>-0.75</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>阿里云宣布AI算力、存储等产品最高涨价34％。百度智能云同日发布AI算力、存储等产品调价公告。</t>
+          <t>据CESA储能应用分会产业数据库不完全统计，2026年2月，中国企业在海外共斩获30个储能订单，总计容量为35.71GWh。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sh600186</t>
+          <t>sz300827</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>莲花控股</t>
+          <t>上能电气</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>7.11</v>
+        <v>44.93</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>10.06</v>
+        <v>20.01</v>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>食品饮料+算力租赁|1.拥有全国性营销网络的味精企业，主要业务为生产销售味精、鸡精、面粉、谷朊粉等。
-2.2023年9月，新华三集团与公司举行战略合作签约仪式，携手莲花健康共建国内领先、国际一流的智能算力中心，满足通用大模型、自动驾驶、机器人、元宇宙、游戏、传媒等应用行业在内的算力需求。</t>
+          <t>储能|公司储能产品包括集中式储能变流器、组串式储能变流器及储能集成系统。具有100kW到12.5MW全功率段范围产品以及适应微网的并离网储能系统解决方案、构网型储能系统解决方案等，同时提供储能系统集成和储能电站整体解决方案，可适用于发、输、配、微电网等多应用场合。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>食品饮料, 算力租赁</t>
+          <t>储能</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>天然气</t>
+          <t>光伏</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>2.01</v>
+        <v>-0.8099999999999999</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>WTI原油上涨至98美元/桶，布伦特原油上涨至105美元/桶。此外，美国天然气期货涨超6%，现报3.258美元/百万英热。</t>
+          <t>当地时间3月16日，英伟达在GTC开发者大会上宣布推出VeraRubinSpace-1太空计算平台，正式布局轨道AI数据中心，开启太空算力新时代。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sh600617</t>
+          <t>sh603778</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>国新能源</t>
+          <t>国晟科技</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>3.63</v>
+        <v>24.21</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>8天4板</t>
+        </is>
+      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>天然气|山西最大的天然气管网运营企业，管网建设方面公司在省内主要业务区域已取得绝对优势地位，省级天然气管网5000余公里，年管输涉及能力超过255亿立方米，管网覆盖全省11市104县（市、区）。</t>
+          <t>光伏+锂电池|1.公司目前从事大尺寸高效异质结光伏电池的研发、生产、销售，以及异质结、TOPCON、PERC等电池组件的生产与销售。控股孙公司恒立聚能涉及钙钛矿研究。
+2.国晟科技公告称，公司拟以2.406亿元的价格受让正豪科技、林琴合计持有的孚悦科技100%股权。交易完成后，公司将持有标的公司100%股权，标的公司将纳入公司合并报表。孚悦科技主要从事高精密度新型锂电池结构件的研发、生产和销售。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>天然气</t>
+          <t>光伏, 锂电池</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>天然气</t>
+          <t>光伏</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>2.01</v>
+        <v>-0.8099999999999999</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>WTI原油上涨至98美元/桶，布伦特原油上涨至105美元/桶。此外，美国天然气期货涨超6%，现报3.258美元/百万英热。</t>
+          <t>当地时间3月16日，英伟达在GTC开发者大会上宣布推出VeraRubinSpace-1太空计算平台，正式布局轨道AI数据中心，开启太空算力新时代。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sz000968</t>
+          <t>sz002309</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>蓝焰控股</t>
+          <t>中利集团</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>9.81</v>
+        <v>3.81</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>9.98</v>
+        <v>10.12</v>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>煤层气|山西煤层气龙头，A股唯一煤层气标的，市占率第二，煤层气抽采量14.33亿方，销售量7亿方，运营近3400口煤层井。</t>
+          <t>光伏+光纤光缆|1.公司的新能源光伏组件业务板块，包括单晶大尺寸高效光伏电池片和光伏组件的研发、生产和销售。公司拥有钙钛矿叠层电池及组件研发专利等技术储备6项。
+2.公司光通讯线缆板块已延伸到高分子材料、光纤、电缆的全产业链，作为华为核心战略供应商，为华为提供通信用电缆，包括5G用新品光电混合缆。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>煤层气</t>
+          <t>光伏, 光纤光缆</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>天然气</t>
+          <t>体育产业</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>2.01</v>
+        <v>-1.88</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>WTI原油上涨至98美元/桶，布伦特原油上涨至105美元/桶。此外，美国天然气期货涨超6%，现报3.258美元/百万英热。</t>
+          <t>进入4月，江苏、广东、福建等多地足球、篮球联赛陆续拉开战幕。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sz300332</t>
+          <t>sh605299</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>天壕能源</t>
+          <t>舒华体育</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>7.14</v>
+        <v>15.29</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>燃气|公司全资子公司北京华盛是山西省规模较大的民营城市燃气公司之一，在山西省原平市、兴县、保德县三市县拥有燃气特许经营权。华盛燃气与中国海洋石油集团旗下全资附属公司合资成立参股子公司中联华瑞，共同建设运营神木——安平煤层气长输管道，实现鄂尔多斯盆地东缘的煤层气资源和京津冀地区用气市场对接，神安线管道是我国第一条非常规天然气长输管道。</t>
+          <t>体育|公司主营业务为健身器材和展示架产品的研发、生产和销售，其中健身器材包括室内健身器材、室外路径产品。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>燃气</t>
+          <t>体育</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>天然气</t>
+          <t>体育产业</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>2.01</v>
+        <v>-1.88</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>WTI原油上涨至98美元/桶，布伦特原油上涨至105美元/桶。此外，美国天然气期货涨超6%，现报3.258美元/百万英热。</t>
+          <t>进入4月，江苏、广东、福建等多地足球、篮球联赛陆续拉开战幕。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sh605169</t>
+          <t>sh605099</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>洪通燃气</t>
+          <t>共创草坪</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>14.19</v>
+        <v>42.47</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>10</v>
@@ -1335,44 +1340,44 @@
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>天然气|地处新疆巴州库尔勒市，专注清洁交通能源供应领域的天然气专业运营商。</t>
+          <t>草坪|公司是全球生产和销售规模最大的人造草坪企业，FIFA（国际足联）8家全球人造草坪优选供应商之一，WorldRugby（世界橄榄球运动联盟）8家全球人造草坪优选供应商之一、FIH（国际曲联）11家全球人造草坪优选供应商之一。</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>天然气</t>
+          <t>草坪</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>-3.46</v>
+        <v>-1.09</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>全球化工巨头巴斯夫宣布，将欧洲地区所有家用护理、工业及机构清洁和工业配方产品的价格上调30%或以上。</t>
+          <t>美股光通信概念领涨，Lumentum涨超10%，Applied Optoelectronics涨超10%，Coherent涨超7%。</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sz002109</t>
+          <t>sz002428</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>兴化股份</t>
+          <t>云南锗业</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>5.28</v>
+        <v>43.46</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>10</v>
@@ -1380,105 +1385,96 @@
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>煤制甲醇|全资子公司兴化化工主营煤制甲醇，产能30万吨/年。</t>
+          <t>磷化铟|云南锗业发布投资者关系活动记录表公告，公司磷化铟晶片现有产能15万片/年(2-4英寸)，受光通信市场需求增加及原材料价格上涨影响，近期产品价格有所上涨。公司已批量向下游外延厂商或具备外延能力的器件厂商供货。公司光纤级锗产品为光纤用四氯化锗，目前产能为60吨/年。公司光纤级锗产品已批量稳定生产多年，客户涵盖国内下游知名光纤生产厂商。</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>煤制甲醇</t>
+          <t>磷化铟</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>-3.46</v>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>全球化工巨头巴斯夫宣布，将欧洲地区所有家用护理、工业及机构清洁和工业配方产品的价格上调30%或以上。</t>
-        </is>
-      </c>
+        <v>-1.34</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sh601015</t>
+          <t>sz000908</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>陕西黑猫</t>
+          <t>*ST景峰</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>5.14</v>
+        <v>6.45</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>10.06</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr"/>
+        <v>5.050000000000001</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>12天10板</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>煤化工|公司以资源综合利用、循环经济产业链为生产模式，主要产品包括焦炭、甲醇、合成氨、LNG、BDO和精煤等。</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>煤化工</t>
-        </is>
-      </c>
+          <t>ST股 | 公司专注医药健康产业，涉足药品研发、生产、销售等领域，产品涵盖了心脑血管、抗肿瘤、骨科、妇儿等用药领域。</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>-1.98</v>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>OFC 2026大会集中释放AI基建需求信号，隔夜美股光通信板块大涨，Lumentum涨超7%，Coherent涨超4%。</t>
-        </is>
-      </c>
+        <v>-1.34</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr"/>
       <c r="D21" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>sz002902</t>
+          <t>sh603843</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>铭普光磁</t>
+          <t xml:space="preserve">*ST正平 </t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>23.96</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
+        <v>5.050000000000001</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>8天7板</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>光通信+储能|1.铭普光磁在互动平台表示，公司于2024年10月14日召开股东大会审议通过《关于变更部分募集资金用途的议案》，在新增募投项目“光模块及光器件产品改建项目”中，已规划增加800G光模块产能。
-2.2022年5月31日公司在互动平台表示，公司目前生产的用于光伏领域的主要有光伏逆变器用电抗器、高频变压器和电感器，及通信局站用光伏供电系统。</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>光通信, 储能</t>
-        </is>
-      </c>
+          <t>ST股 | 2025年2月21日公司官微披露，旗下正平智算参加海东市绿色算力产业集中签约暨推介活动并签订算电协同产业园框架协议。</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1487,36 +1483,36 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>-1.56</v>
+        <v>-1.34</v>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>sz000908</t>
+          <t>sz000669</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>*ST景峰</t>
+          <t>ST金鸿</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>6.14</v>
+        <v>5.3</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>4.96</v>
+        <v>4.95</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11天9板</t>
+          <t>9天7板</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司专注医药健康产业，涉足药品研发、生产、销售等领域，产品涵盖了心脑血管、抗肿瘤、骨科、妇儿等用药领域。</t>
+          <t>ST股 | 主营气源开发与输送、长输管网建设与管理、城市燃气经营与销售、车用加气站投资与运营、LNG点供、分布式能源项目开发与建设等。</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
@@ -1528,36 +1524,36 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>-1.56</v>
+        <v>-1.34</v>
       </c>
       <c r="C23" s="2" t="inlineStr"/>
       <c r="D23" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>sh600599</t>
+          <t>sh600381</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST熊猫 </t>
+          <t xml:space="preserve">*ST春天 </t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>6.18</v>
+        <v>3.33</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>4.92</v>
+        <v>5.050000000000001</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8天8板</t>
+          <t>5天5板</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司地处中国烟花之乡浏阳，经过3多年的发展已成为中国最大的出口鞭炮烟花公司</t>
+          <t>ST股 | 在大健康业务方面，公司已基本完成了涵盖保健食品、药品等冬虫夏草高效利用产品的储备和战略布局。</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr"/>
@@ -1569,36 +1565,36 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>-1.56</v>
+        <v>-1.34</v>
       </c>
       <c r="C24" s="2" t="inlineStr"/>
       <c r="D24" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>sh603843</t>
+          <t>sh603580</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST正平 </t>
+          <t xml:space="preserve">*ST艾艾 </t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>7.72</v>
+        <v>18.18</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>5.029999999999999</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7天6板</t>
+          <t>4天4板</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 2025年2月21日公司官微披露，旗下正平智算参加海东市绿色算力产业集中签约暨推介活动并签订算电协同产业园框架协议。</t>
+          <t>ST股 | 公司是专业从事为轻型输送带的研发、生产及销售，境外营业收入大于50%。</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
@@ -1610,36 +1606,36 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>-1.56</v>
+        <v>-1.34</v>
       </c>
       <c r="C25" s="2" t="inlineStr"/>
       <c r="D25" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>sh600381</t>
+          <t>sh603813</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST春天 </t>
+          <t xml:space="preserve">*ST原尚 </t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>3.17</v>
+        <v>32.16</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>4.97</v>
+        <v>5</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4天4板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 在大健康业务方面，公司已基本完成了涵盖保健食品、药品等冬虫夏草高效利用产品的储备和战略布局。</t>
+          <t>ST股 | 公司参股公司广东原锋新能源科技的股东之一锋源是国内极少的集全套自主知识产权氢燃料电池电堆以及核心零部件膜电极、催化剂、金属双极板等研发、生产、销售一体的公司。</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
@@ -1651,36 +1647,37 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>-1.56</v>
+        <v>-1.34</v>
       </c>
       <c r="C26" s="2" t="inlineStr"/>
       <c r="D26" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>sh603580</t>
+          <t>sh603398</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST艾艾 </t>
+          <t xml:space="preserve">*ST沐邦 </t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>17.31</v>
+        <v>11.27</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>4.97</v>
+        <v>5.029999999999999</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3天3板</t>
+          <t>4天2板</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司是专业从事为轻型输送带的研发、生产及销售，境外营业收入大于50%。</t>
+          <t>ST股 | 1.沐邦高科公告，与铜陵狮子山高新技术产业开发区管理委员会、铜陵高新发展投资有限公司签订《项目投资协议书》，项目名称为年产10GW-N型高效电池片、10GW切片生产基地项目。
+2.公司上市的IP产品 “樱桃小丸子”第一期为“盲盒”类产品。</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
@@ -1692,32 +1689,32 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>-1.56</v>
+        <v>-1.34</v>
       </c>
       <c r="C27" s="2" t="inlineStr"/>
       <c r="D27" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>sh603813</t>
+          <t>sh600608</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST原尚 </t>
+          <t xml:space="preserve">*ST沪科 </t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>30.63</v>
+        <v>2.87</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>5.01</v>
+        <v>5.13</v>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司参股公司广东原锋新能源科技的股东之一锋源是国内极少的集全套自主知识产权氢燃料电池电堆以及核心零部件膜电极、催化剂、金属双极板等研发、生产、销售一体的公司。</t>
+          <t>ST股 | 公司是一家信息技术行业公司，主要业务分为钢材制品加工制造及商品贸易业务两大板块。</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
@@ -1729,32 +1726,33 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>-1.56</v>
+        <v>-1.34</v>
       </c>
       <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>sh600777</t>
+          <t>sh600696</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST新潮 </t>
+          <t xml:space="preserve">*ST岩石 </t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>5.64</v>
+        <v>1.65</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>5.029999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司在美国德克萨斯州拥有Hoople油田资产（常规油田）、Howard和Borden油田资产（页岩油藏）两处油田资产；公司主营业务为：石油及天然气的勘探、开采和销售。</t>
+          <t>ST股 | 1.公司主要从事商业保理、融资租赁、不动产运营管理和大宗商品贸易。
+2.公司持有江西章贡酒业有限责任公司25%股权。章贡酒业是全国白酒工业百强企业，江西省重点酿酒企业。</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
@@ -1766,32 +1764,32 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>-1.56</v>
+        <v>-1.34</v>
       </c>
       <c r="C29" s="2" t="inlineStr"/>
       <c r="D29" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>sz000004</t>
+          <t>sz000638</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>*ST国华</t>
+          <t>*ST万方</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>5.54</v>
+        <v>1.41</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>4.92</v>
+        <v>5.220000000000001</v>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司旗下全资子公司智游网安为专业移动应用安全综合服务提供商。</t>
+          <t>ST股 | 公司业务主要包括军工产业、农业产业以及生物制品等业务。公司控股子公司万方迈捷以粮库收储为核心，深入研究粮食加工、研究土地流转、研究农民就业，万方迈捷作为乾安县唯一一家自主加工的大米企业。</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
@@ -1799,49 +1797,39 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>-1.34</v>
       </c>
       <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>sz000020</t>
+          <t>sh600355</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>深华发Ａ</t>
+          <t xml:space="preserve">*ST精伦 </t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>21.21</v>
+        <v>0.78</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>4天4板</t>
-        </is>
-      </c>
+        <v>5.41</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>面板|公司主营业务分为液晶显示器整机、注塑件、保丽龙（轻型材料包装）、物业租赁四大模块。液晶显示器整机业务生产经营各种彩色电视机、液晶显示器、液晶显示屏，是公司主要收入来源。</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>面板</t>
-        </is>
-      </c>
+          <t>ST股 | 公司智能控制产品是公司全资子公司上海鲍麦克斯电子科技有限公司的主营产品，鲍麦克斯专业从事通用及专用伺服驱动系统、数控系统、 缝制机器人的系列化产品研发及销售。</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1856,37 +1844,37 @@
       </c>
       <c r="C31" s="2" t="inlineStr"/>
       <c r="D31" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>sh603687</t>
+          <t>sz000020</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">大胜达  </t>
+          <t>深华发Ａ</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>12.17</v>
+        <v>23.33</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>10.04</v>
+        <v>10</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>5天5板</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>并购重组|大胜达公告称，公司拟通过股权受让及增资方式合计投资5.5亿元取得芯瞳半导体技术（厦门）有限公司22.9831%的股权。其中，以2786万元受让2.7074%股权，以2214万元受让1.5961%股权，并以5亿元增资（分两次，第一次2.5亿元，第二次2.5亿元需满足流片成功条件）。同时，控股股东新胜达以5000万元同条件增资，取得1.9608%股权。芯瞳半导体成立于2019年，是国内专注于通用高性能图形处理器芯片设计研发与销售的先驱企业。</t>
+          <t>面板|公司主营业务分为液晶显示器整机、注塑件、保丽龙（轻型材料包装）、物业租赁四大模块。液晶显示器整机业务生产经营各种彩色电视机、液晶显示器、液晶显示屏，是公司主要收入来源。</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>并购重组</t>
+          <t>面板</t>
         </is>
       </c>
     </row>
@@ -1903,38 +1891,37 @@
       </c>
       <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>sz002432</t>
+          <t>sh600683</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>九安医疗</t>
+          <t>京投发展</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>65.95</v>
+        <v>10.86</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>10.01</v>
+        <v>10.03</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>6天4板</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>医疗器械+Kimi|1.公司是一家在国内外具有影响力的个人健康管理产品供应商，主要从事家用医疗器械的研发、生产及销售。
-2.公司通过认购砺思资本基金份额参股Kimi。</t>
+          <t>剥离地产业务|京投发展公告称，公司拟将持有的房地产开发业务相关资产及负债转让至控股股东京投公司，采用现金支付方式，不涉及发行股份，不影响公司股权结构，不会因此导致公司控股股东发生变更。本事项预计构成重大资产重组。</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>医疗器械, Kimi</t>
+          <t>剥离地产业务</t>
         </is>
       </c>
     </row>
@@ -1951,37 +1938,37 @@
       </c>
       <c r="C33" s="2" t="inlineStr"/>
       <c r="D33" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>sz000617</t>
+          <t>sh603687</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>中油资本</t>
+          <t xml:space="preserve">大胜达  </t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>10.71</v>
+        <v>13.39</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>9.959999999999999</v>
+        <v>10.02</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4天2板</t>
+          <t>3天3板</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>多元金融|中石油集团旗下上市公司，公司主要通过其控股、参股公司昆仑银行、中油财务、昆仑金融租赁、中油资产、专属保险、中意财险是一家全方位综合性金融业务公司。</t>
+          <t>并购重组+算力芯片|大胜达公告称，公司拟通过股权受让及增资方式合计投资5.5亿元取得芯瞳半导体技术（厦门）有限公司22.9831%的股权。其中，以2786万元受让2.7074%股权，以2214万元受让1.5961%股权，并以5亿元增资（分两次，第一次2.5亿元，第二次2.5亿元需满足流片成功条件）。同时，控股股东新胜达以5000万元同条件增资，取得1.9608%股权。芯瞳半导体成立于2019年，是国内专注于通用高性能图形处理器芯片设计研发与销售的先驱企业。</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>并购重组, 算力芯片</t>
         </is>
       </c>
     </row>
@@ -1998,33 +1985,37 @@
       </c>
       <c r="C34" s="2" t="inlineStr"/>
       <c r="D34" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>sh601218</t>
+          <t>sh600617</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>吉鑫科技</t>
+          <t>国新能源</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>7.43</v>
+        <v>3.99</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>10.07</v>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
+        <v>9.92</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>风电|公司是一家专注于研发、制造和销售大型风力发电机组用零部件的龙头企业，主要生产750KW-12MW风力发电机组用轮毂、底座、轴、轴承座等系列产品。</t>
+          <t>天然气|山西最大的天然气管网运营企业，管网建设方面公司在省内主要业务区域已取得绝对优势地位，省级天然气管网5000余公里，年管输涉及能力超过255亿立方米，管网覆盖全省11市104县（市、区）。</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>天然气</t>
         </is>
       </c>
     </row>
@@ -2041,33 +2032,33 @@
       </c>
       <c r="C35" s="2" t="inlineStr"/>
       <c r="D35" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sh603366</t>
+          <t>sz000677</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>日出东方</t>
+          <t>恒天海龙</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>10.75</v>
+        <v>4.98</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>10.03</v>
+        <v>9.93</v>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>热泵|空气源热泵（空气能）产品是公司重点发展的产品类别。公司为加强空气源热泵产品的销售能力，在原有销售队伍和渠道的基础上，构建了更为专业的销售队伍和更加细分的销售渠道，经销商数量维持稳定增长。</t>
+          <t>并购重组|恒天海龙公告称，公司拟通过全资子公司海龙飞控以现金方式收购群健航空不少于40%股权，交易完成后海龙飞控将成为目标公司控股股东。该协议为初步意向协议，目前尚未签署正式《股权收购协议》，相关事项存在不确定性。</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>热泵</t>
+          <t>并购重组</t>
         </is>
       </c>
     </row>
@@ -2084,33 +2075,33 @@
       </c>
       <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sh605389</t>
+          <t>sz000509</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>长龄液压</t>
+          <t>华塑控股</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>77.03</v>
+        <v>4.54</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>10</v>
+        <v>9.93</v>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>要约收购|长龄液压公告称，公司股票将于2026年3月11日开市起复牌。本次要约收购期限内，预受要约的股东账户总数为3户，预受要约股份总数为1729.05万股，占上市公司股份总数的12.00007%。收购人无锡核芯破浪科技合伙企业将按照《江苏长龄液压股份有限公司要约收购报告书》的约定，按照同等比例收购已预受要约的股份。本次要约收购完成后，核芯破浪及其一致行动人共计持有长龄液压6050.22万股股份，占上市公司总股本的41.99%。</t>
+          <t>MLED|公司积极布局了MiniLED、OLED和高分高刷高色域等显示领域前沿产品技术。</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>要约收购</t>
+          <t>MLED</t>
         </is>
       </c>
     </row>
@@ -2127,20 +2118,20 @@
       </c>
       <c r="C37" s="2" t="inlineStr"/>
       <c r="D37" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sh603130</t>
+          <t>sh603026</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">云中马  </t>
+          <t>石大胜华</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>45.6</v>
+        <v>75.41</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>10.01</v>
@@ -2148,13 +2139,141 @@
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>机器人+商业航天|1.参股公司中玺新材料（安徽）有限公司主营超高分子量聚乙烯的生产和销售，是超高分子量聚乙烯纤维的核心原材料。除了应用于超高纤维之外，该种材料下游应用还有管材、板材、滤材、锂电池隔膜、人工关节等。
-2.参股航升卫星是一家商业微小卫星研发商，其具备独立的卫星总体设计与工程研制能力。</t>
+          <t>锂电池电解液|公司是能够同时提供锂离子电池电解液及电解液溶剂、溶质、添加剂产品的全产业链公司，具备五大碳酸酯溶剂、六氟磷酸锂及部分添加剂的生产能力，形成锂电池溶剂、电解液、高端新材料三大业务版块。</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>机器人, 商业航天</t>
+          <t>锂电池电解液</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>sh600604</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>市北高新</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>创投|公司旗下上海聚能湾企业服务有限公司孵化器是以大数据、云计算为产业特色的国家级科技企业孵化器，已构建完成“创业苗圃+孵化器+加速器”的完整孵化体系。</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>创投</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr"/>
+      <c r="D39" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>sh603538</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">美诺华  </t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>27.84</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>益生菌减重|近日，由宁波美诺华天康药业有限公司申办的一项单中心、开放、自身对照人体试食临床试验，评估了益生菌（JH389）胶囊产品的减重效果和安全性。结果显示，服用该产品8周可显著改善受试者体重、体脂及肥胖相关指标。</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>益生菌减重</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>sh605050</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">福然德  </t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>机器人|公司与开普勒机器人合作成立合资公司德普智擎，是公司在汽车产业机器人应用、机器人材料轻量化的拓展和尝试。</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2196,7 +2315,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -2211,7 +2330,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
@@ -2226,31 +2345,31 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sz000539</t>
+          <t>sz000601</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>粤电力Ａ</t>
+          <t>韶能股份</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sz000601</t>
+          <t>sh603687</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>韶能股份</t>
+          <t xml:space="preserve">大胜达  </t>
         </is>
       </c>
     </row>
@@ -2260,12 +2379,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sz000815</t>
+          <t>sz002310</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>美利云</t>
+          <t>东方新能</t>
         </is>
       </c>
     </row>
@@ -2275,12 +2394,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sz002432</t>
+          <t>sh600726</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>九安医疗</t>
+          <t>华电能源</t>
         </is>
       </c>
     </row>
@@ -2290,27 +2409,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>sh600666</t>
+          <t>sh600617</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">奥瑞德  </t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>sh603687</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">大胜达  </t>
+          <t>国新能源</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,12 +476,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="75" customWidth="1" min="3" max="3"/>
+    <col width="92" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
@@ -556,45 +556,46 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.2</v>
+        <v>-2.22</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026年政府工作报告中，“算电协同”首次被写入，明确列为新基建工程。</t>
+          <t>华泰证券研报称，霍尔木兹海峡的封锁让市场对化石能源价格易涨难跌逐步确立信心，重申对电力板块的全面看多，包括水核风光生物质在内的绿电或充分受益。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>sh600726</t>
+          <t>sh600396</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>华电能源</t>
+          <t>华电辽能</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>5.52</v>
+        <v>6.89</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>9.959999999999999</v>
+        <v>10.06</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>9天6板</t>
+          <t>6天6板</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>电力|公司是黑龙江省最大的发电及集中供热运营商，主要产品为电力、热力，火力电厂分布在黑龙江省主要中心城市。</t>
+          <t>电缆+氢能|1.公司是中国华电集团公司的实际控制的上市公司、中央企业的三级单位，同时也是一家集火力发电、风力发电、煤炭营销、供热、供汽为一体的综合性区域基础能源企业。
+2.2023年3月14日公告，拟与华电科工共同出资建设25MW风电离网制氢一体化项目，风电设备年利用小时数3000小时，年发电量约7500万千瓦时，全部发电量均用于本项目制取绿氢，预计年产绿氢1230吨。项目总投资2.78亿元。公司与华电科工拟按70%和30%比例组建项目公司。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>电缆, 氢能</t>
         </is>
       </c>
     </row>
@@ -605,46 +606,45 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.2</v>
+        <v>-2.22</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026年政府工作报告中，“算电协同”首次被写入，明确列为新基建工程。</t>
+          <t>华泰证券研报称，霍尔木兹海峡的封锁让市场对化石能源价格易涨难跌逐步确立信心，重申对电力板块的全面看多，包括水核风光生物质在内的绿电或充分受益。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sh600396</t>
+          <t>sz002310</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>华电辽能</t>
+          <t>东方新能</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>6.26</v>
+        <v>3.83</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>10.02</v>
+        <v>10.06</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>5天5板</t>
+          <t>6天4板</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>电力+氢能|1.公司是中国华电集团公司的实际控制的上市公司、中央企业的三级单位，同时也是一家集火力发电、风力发电、煤炭营销、供热、供汽为一体的综合性区域基础能源企业。
-2.2023年3月14日公告，拟与华电科工共同出资建设25MW风电离网制氢一体化项目，风电设备年利用小时数3000小时，年发电量约7500万千瓦时，全部发电量均用于本项目制取绿氢，预计年产绿氢1230吨。项目总投资2.78亿元。公司与华电科工拟按70%和30%比例组建项目公司。</t>
+          <t>并购重组+绿电|2025年12月15日公告，公司拟以现金支付方式购买海城锐海100%股权和电投瑞享80%股权。其中，海城锐海100%股权拟通过在天津产权交易中心摘牌方式购买。标的资产的审计和评估工作尚未完成，评估值及交易价格均尚未确定（海城锐海100%股权在天津产权交易所的挂牌转让底价为1410万元）。本次交易预计构成重大资产重组。通过本次交易，东方园林新增光伏电站、风电场的投资、开发、建设和运营等新能源业务。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>电力, 氢能</t>
+          <t>并购重组, 绿电</t>
         </is>
       </c>
     </row>
@@ -655,46 +655,45 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.2</v>
+        <v>-2.22</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026年政府工作报告中，“算电协同”首次被写入，明确列为新基建工程。</t>
+          <t>华泰证券研报称，霍尔木兹海峡的封锁让市场对化石能源价格易涨难跌逐步确立信心，重申对电力板块的全面看多，包括水核风光生物质在内的绿电或充分受益。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sz000601</t>
+          <t>sz001258</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>韶能股份</t>
+          <t>立新能源</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>8.140000000000001</v>
+        <v>10.62</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>10</v>
+        <v>10.05</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3天3板</t>
+          <t>3天2板</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>算电协同|1.公司自成立以来，一直以能源的投资开发经营为主营业务，在不断巩固和发展水电产业的基础上，重点发展生物质能发电、加油加气充电一体化站等业务。
-2.韶能算电公司拟在乐昌市成立全资子公司，开发清洁电源业务，注册资本10亿元；若该项目投产，有利于壮大公司清洁能源规模，为韶关数据集群提供绿电供应。</t>
+          <t>绿电|公司的主营业务为风力发电、光伏发电项目的投资、开发、建设和运营。公司运营的风电场、光伏电站主要位于新疆。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>算电协同</t>
+          <t>绿电</t>
         </is>
       </c>
     </row>
@@ -705,45 +704,42 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.2</v>
+        <v>-2.22</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2026年政府工作报告中，“算电协同”首次被写入，明确列为新基建工程。</t>
+          <t>华泰证券研报称，霍尔木兹海峡的封锁让市场对化石能源价格易涨难跌逐步确立信心，重申对电力板块的全面看多，包括水核风光生物质在内的绿电或充分受益。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sz002310</t>
+          <t>sh600758</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>东方新能</t>
+          <t>辽宁能源</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>3.48</v>
+        <v>4.73</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>10.13</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>5天3板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>绿电|2025年12月15日公告，公司拟以现金支付方式购买海城锐海100%股权和电投瑞享80%股权。其中，海城锐海100%股权拟通过在天津产权交易中心摘牌方式购买。标的资产的审计和评估工作尚未完成，评估值及交易价格均尚未确定（海城锐海100%股权在天津产权交易所的挂牌转让底价为1410万元）。本次交易预计构成重大资产重组。通过本次交易，东方园林新增光伏电站、风电场的投资、开发、建设和运营等新能源业务。</t>
+          <t>煤炭+电力|1.公司下辖7个煤矿，煤炭产品核定生产能力达到1160万吨/年，各矿煤种以冶金煤为主。
+2.公司下辖2个热电联产的电厂，即辽宁沈煤红阳热电有限公司和灯塔市红阳热电有限公司，电力总装机容量为708MW，其中包括2×330MW燃煤发电机组，4×12MW煤矸石发电机组。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>绿电</t>
+          <t>煤炭, 电力</t>
         </is>
       </c>
     </row>
@@ -754,46 +750,42 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.2</v>
+        <v>-2.22</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2026年政府工作报告中，“算电协同”首次被写入，明确列为新基建工程。</t>
+          <t>华泰证券研报称，霍尔木兹海峡的封锁让市场对化石能源价格易涨难跌逐步确立信心，重申对电力板块的全面看多，包括水核风光生物质在内的绿电或充分受益。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sz002256</t>
+          <t>sh600149</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>兆新股份</t>
+          <t>廊坊发展</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>4.49</v>
+        <v>6.36</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>10.03</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>绿电+化工|1.公司新能源领域业务为光伏电站投资、建设、运营和管理。截至2024年期末，公司在安徽、江西、浙江、宁夏及四川等多个省份运营和管理10座太阳能光伏电站，累计并网装机容量约131.82MW。
-2.公司生产的精细化工产品包括环保功能涂料及辅料、绿色环保家居用品和环保节能汽车养护用品等，广泛应用于家庭用品、个人用品、工业与汽车用品等领域</t>
+          <t>电力+房地产|1.公司是廊坊市国有控股的唯一一家A股上市公司，所从事供热业务具有公用事业显著特征，公司供热经营区域面积超100平方公里，是廊坊市覆盖区域最大的供热企业。
+2.廊坊控股旗下有各类土地资源累计达34万多亩。廊坊控股旗下土地资源大部分来自五个产业园区一级土地开发。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>绿电, 化工</t>
+          <t>电力, 房地产</t>
         </is>
       </c>
     </row>
@@ -804,36 +796,36 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.2</v>
+        <v>-2.22</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2026年政府工作报告中，“算电协同”首次被写入，明确列为新基建工程。</t>
+          <t>华泰证券研报称，霍尔木兹海峡的封锁让市场对化石能源价格易涨难跌逐步确立信心，重申对电力板块的全面看多，包括水核风光生物质在内的绿电或充分受益。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sz000862</t>
+          <t>sh600032</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>银星能源</t>
+          <t>浙江新能</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>8.44</v>
+        <v>10.76</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>10.04</v>
+        <v>10.02</v>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>绿电|公司新能源发电业务包括风力发电、太阳能光伏发电以及分布式项目发电。</t>
+          <t>绿电|公司的主营业务为水力发电、光伏发电、风力发电等可再生能源项目的投资、开发、建设和运营管理。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -849,714 +841,734 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.2</v>
+        <v>-2.22</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2026年政府工作报告中，“算电协同”首次被写入，明确列为新基建工程。</t>
+          <t>华泰证券研报称，霍尔木兹海峡的封锁让市场对化石能源价格易涨难跌逐步确立信心，重申对电力板块的全面看多，包括水核风光生物质在内的绿电或充分受益。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sh603165</t>
+          <t>sh603105</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>荣晟环保</t>
+          <t>芯能科技</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>14.96</v>
+        <v>12.74</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>10</v>
+        <v>10.02</v>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>绿电|2022年1月4日公告，公司与安徽省全椒县人民政府签订年产130万吨再生环保纸及新能源综合利用项目战略合作框架协议，建设内容包括年产130万吨再生环保纸、生物质热电联产(年处理50万吨秸秆)、光伏产品研发和制造、1GW分布式光伏电站等运营管理，并配套建设工业固废资源综合利用项目、环保水处理项目，项目总投资105亿元。</t>
+          <t>绿电+虚拟电厂|1.公司主营业务包括分布式光伏电站投资运营、分布式光伏解决方案提供以及光伏产品研发制造。
+2.公司于2021年建成“网荷光储充智能微网”示范项目是小型分布式虚拟电厂，并已稳定运行至今。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>绿电</t>
+          <t>绿电, 虚拟电厂</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.2</v>
+        <v>-4.44</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2026年政府工作报告中，“算电协同”首次被写入，明确列为新基建工程。</t>
+          <t>国际原油价格持续高位震荡，国内化工企业纷纷启动调价模式，从上游基础化工品到下游终端产品，调价潮正在蔓延，行业成本传导效应凸显。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sh600310</t>
+          <t>sh600844</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>广西能源</t>
+          <t>金煤科技</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>4.88</v>
+        <v>4.03</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>9.91</v>
+        <v>10.11</v>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>电力|公司主营业务为电力生产和销售，包括水力发电、火力发电、光伏发电，拥有完整的发、供电网络，电厂和电网“厂网合一”，发电、供电和配电业务一体化经营。</t>
+          <t>煤化工|公司为专注于煤制乙二醇产业的新型化工企业，目前主要通过控股子公司通辽金煤的大型化工装置生产乙二醇并联产草酸。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>煤化工</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>储能</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-0.75</v>
+        <v>-4.44</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>据CESA储能应用分会产业数据库不完全统计，2026年2月，中国企业在海外共斩获30个储能订单，总计容量为35.71GWh。</t>
+          <t>国际原油价格持续高位震荡，国内化工企业纷纷启动调价模式，从上游基础化工品到下游终端产品，调价潮正在蔓延，行业成本传导效应凸显。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>sh600792</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>云煤能源</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>煤化工|云南省最大的焦化企业，主要产品有冶金焦炭、焦油、粗苯、煤气、甲醇、硫酸铵、硫磺等产品。</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>煤化工</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>化工</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>-4.44</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>国际原油价格持续高位震荡，国内化工企业纷纷启动调价模式，从上游基础化工品到下游终端产品，调价潮正在蔓延，行业成本传导效应凸显。</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>sh603616</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>韩建河山</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>并购重组+化工|2026年2月3日公告，公司拟发行股份及支付现金购买兴福新材99.9978%股份，并向不超过35名符合条件的特定投资者发行股份募集配套资金。本次交易完成后，公司主营业务新增芳香族产品的研发、生产和销售。本次交易构成重大资产重组。兴福新材是一家专注于芳香族产品的研发、生产和销售的高新技术企业，主要产品包括新一代特种工程塑料聚醚醚酮（PEEK）中间体、农药及医药中间体和PEEK纯化业务等。</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>并购重组, 化工</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>化工</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>-4.44</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>国际原油价格持续高位震荡，国内化工企业纷纷启动调价模式，从上游基础化工品到下游终端产品，调价潮正在蔓延，行业成本传导效应凸显。</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>sz000703</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>恒逸石化</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>化工|公司在国内同行中形成独有的“涤纶+锦纶”双纶驱动石化产业链为核心业务，以供应链服务业务为成长业务，差别化纤维产品、工业智能技术应用为新兴业务的“石化+”多层次立体产业布局。</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>化工</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>-5.23</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>上交所受理宇树科技股份有限公司科创板IPO申请，拟融资金额42.02亿元。</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>sh600376</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>首开股份</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>参股宇树科技|公司旗下首开盈信通过金石成长股权投资（杭州）合伙企业间接投资宇树科技。</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>参股宇树科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>-5.23</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>上交所受理宇树科技股份有限公司科创板IPO申请，拟融资金额42.02亿元。</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>sh600143</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>金发科技</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>机器人|公司的特种工程塑料可以用于人形机器人的伺服电机及连接器上。</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>-5.23</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>上交所受理宇树科技股份有限公司科创板IPO申请，拟融资金额42.02亿元。</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>sz002896</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>中大力德</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>机器人|公司是从事机械传动与控制应用领域关键零部件的研发、生产、销售和服务的高新技术企业，主要产品包括精密减速器、传动行星减速器、各类小型及微型减速电机等，为各类机械设备提供安全、高效、精密的动力传动与控制应用解决方案。</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>-5.23</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>上交所受理宇树科技股份有限公司科创板IPO申请，拟融资金额42.02亿元。</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>sh603272</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>联翔股份</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>23.98</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>机器人|2025年12月30日公告，董事会审议通过变更经营范围议案，新增服务消费机器人制造、服务消费机器人销售、工业机器人制造、工业机器人销售、智能机器人的研发等制造销售，并同步修订公司章程。</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>光伏</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>-4.01</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉自建芯片工厂“Terafab”项目即将于近期启动。当地时间3月21日，马斯克在社交媒体透露，该项目目标是每年生产超过1太瓦的计算能力，其中约80%用于太空，约20%用于地面。</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>sz002309</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>中利集团</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>9.969999999999999</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>光伏+光纤光缆|1.公司的新能源光伏组件业务板块，包括单晶大尺寸高效光伏电池片和光伏组件的研发、生产和销售。公司拥有钙钛矿叠层电池及组件研发专利等技术储备6项。
+2.公司光通讯线缆板块已延伸到高分子材料、光纤、电缆的全产业链，作为华为核心战略供应商，为华为提供通信用电缆，包括5G用新品光电混合缆。</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>光伏, 光纤光缆</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>光伏</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>-4.01</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉自建芯片工厂“Terafab”项目即将于近期启动。当地时间3月21日，马斯克在社交媒体透露，该项目目标是每年生产超过1太瓦的计算能力，其中约80%用于太空，约20%用于地面。</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>sz002218</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>拓日新能</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>光伏+商业航天|公司于2015年参与了东方红卫星“开拓一号”单晶硅太阳电池项目，具备成熟的卫星用光伏组件生产制造能力。</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>光伏, 商业航天</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>光伏</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>-4.01</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉自建芯片工厂“Terafab”项目即将于近期启动。当地时间3月21日，马斯克在社交媒体透露，该项目目标是每年生产超过1太瓦的计算能力，其中约80%用于太空，约20%用于地面。</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>sz300345</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>华民股份</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>光伏+机器人|1.公司控股子公司鸿新新能源科技是一家其致力于成为光伏产业链上游单晶硅棒及单晶硅片材料环节专业化制造商。
+2.华民股份公告称，公司与广东天太机器人有限公司签署《投资意向协议》，将按照估值不超过11亿元，通过认缴新增注册资本额或受让老股的方式，以现金投资不超过1亿元，交易完成后预计持股比例为8%左右。</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>光伏, 机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>单车</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>3月23日晚24点，国内将迎来新一轮成品油调价窗口。电单车出行性价比凸显。</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>sh603529</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>爱玛科技</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>31.11</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>电单车|公司主营业务为电动自行车、电动轻便摩托车、电动摩托车的研发、生产及销售，此外，还有电动三轮车、自行车产品。</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>电单车</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>单车</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>3月23日晚24点，国内将迎来新一轮成品油调价窗口。电单车出行性价比凸显。</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>sh603787</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>新日股份</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>电单车|公司是专业从事电动自行车、电动轻便摩托车、电动摩托车等电动两轮车研发、生产与销售的企业，主导产品为电动两轮车。</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>电单车</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>智能电网</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>-4.399999999999999</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>央视财经报道，2025年，我国变压器出口总值达646亿元，比2024年增长近36%。我国已成为世界第一大变压器生产国，在原材料、成本、生产周期等方面都具备明显优势。</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>sz002150</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>正泰电源</t>
         </is>
       </c>
-      <c r="G10" s="2" t="n">
-        <v>34.88</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8天4板</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="G22" s="2" t="n">
+        <v>38.37</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>9天5板</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>储能+电网设备|1.旗下正泰电源是国内最早开始研发光伏逆变器的公司之一，业务范围涵盖光伏逆变器、光伏汇流箱、商用储能一体机、预装式光伏系统、预装式储能系统等。
 2.公司输配电控制设备业务主要产品包括高压成套开关设备、中低压成套开关设备、高低压开关元件及控制电器等，能够为下游各行业用户提供整体配电解决方案。</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>储能, 电网设备</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>储能</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>据CESA储能应用分会产业数据库不完全统计，2026年2月，中国企业在海外共斩获30个储能订单，总计容量为35.71GWh。</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>sz301658</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>首航新能</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>60.35</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>储能|公司的储能电池主要为磷酸铁锂电池，能够适配多品牌光伏储能逆变器，主要应用于户用及小型工商业储能。公司光伏储能逆变器功率范围已涵盖3kW~20kW，适用于户用、小型工商业并离网储能多种场景。</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>储能</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>储能</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>据CESA储能应用分会产业数据库不完全统计，2026年2月，中国企业在海外共斩获30个储能订单，总计容量为35.71GWh。</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>sh603381</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>永臻股份</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>28.22</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>储能+光伏|1.公司主要从事绿色能源结构材料的研发、生产、销售及应用，已成为国内领先的铝合金光伏结构件制造商之一。
-2.公司与比亚迪汽车工业有限公司于2025年10月9日签署了《战略合作协议》，在储能等项目以及比亚迪所需的储能铝合金部件等领域开展合作。</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>储能, 光伏</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>储能</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>据CESA储能应用分会产业数据库不完全统计，2026年2月，中国企业在海外共斩获30个储能订单，总计容量为35.71GWh。</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>sz001283</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>豪鹏科技</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>67.20999999999999</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>储能|2023年1月9日公司接受机构调研时表示，公司现有产品中包含便携式储能产品，其广泛应用于应急救灾、户外活动及家庭备用电源等场景，目前公司主要向一家北美客户供应电池模组，公司将在做好当前客户服务的基础上，积极开拓新客户和新业务模式布局。</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>储能</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>储能</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>据CESA储能应用分会产业数据库不完全统计，2026年2月，中国企业在海外共斩获30个储能订单，总计容量为35.71GWh。</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>sz300827</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>上能电气</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>44.93</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>20.01</v>
-      </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>储能|公司储能产品包括集中式储能变流器、组串式储能变流器及储能集成系统。具有100kW到12.5MW全功率段范围产品以及适应微网的并离网储能系统解决方案、构网型储能系统解决方案等，同时提供储能系统集成和储能电站整体解决方案，可适用于发、输、配、微电网等多应用场合。</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>储能</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>光伏</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>-0.8099999999999999</v>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>当地时间3月16日，英伟达在GTC开发者大会上宣布推出VeraRubinSpace-1太空计算平台，正式布局轨道AI数据中心，开启太空算力新时代。</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>sh603778</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>国晟科技</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>24.21</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>8天4板</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>光伏+锂电池|1.公司目前从事大尺寸高效异质结光伏电池的研发、生产、销售，以及异质结、TOPCON、PERC等电池组件的生产与销售。控股孙公司恒立聚能涉及钙钛矿研究。
-2.国晟科技公告称，公司拟以2.406亿元的价格受让正豪科技、林琴合计持有的孚悦科技100%股权。交易完成后，公司将持有标的公司100%股权，标的公司将纳入公司合并报表。孚悦科技主要从事高精密度新型锂电池结构件的研发、生产和销售。</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>光伏, 锂电池</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>光伏</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>-0.8099999999999999</v>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>当地时间3月16日，英伟达在GTC开发者大会上宣布推出VeraRubinSpace-1太空计算平台，正式布局轨道AI数据中心，开启太空算力新时代。</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>sz002309</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>中利集团</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>10.12</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>光伏+光纤光缆|1.公司的新能源光伏组件业务板块，包括单晶大尺寸高效光伏电池片和光伏组件的研发、生产和销售。公司拥有钙钛矿叠层电池及组件研发专利等技术储备6项。
-2.公司光通讯线缆板块已延伸到高分子材料、光纤、电缆的全产业链，作为华为核心战略供应商，为华为提供通信用电缆，包括5G用新品光电混合缆。</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>光伏, 光纤光缆</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>体育产业</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>-1.88</v>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>进入4月，江苏、广东、福建等多地足球、篮球联赛陆续拉开战幕。</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>sh605299</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>舒华体育</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>15.29</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>体育|公司主营业务为健身器材和展示架产品的研发、生产和销售，其中健身器材包括室内健身器材、室外路径产品。</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>体育</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>体育产业</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>-1.88</v>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>进入4月，江苏、广东、福建等多地足球、篮球联赛陆续拉开战幕。</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>sh605099</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>共创草坪</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>42.47</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>草坪|公司是全球生产和销售规模最大的人造草坪企业，FIFA（国际足联）8家全球人造草坪优选供应商之一，WorldRugby（世界橄榄球运动联盟）8家全球人造草坪优选供应商之一、FIH（国际曲联）11家全球人造草坪优选供应商之一。</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>草坪</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>光通信</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>-1.09</v>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>美股光通信概念领涨，Lumentum涨超10%，Applied Optoelectronics涨超10%，Coherent涨超7%。</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>sz002428</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>云南锗业</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>43.46</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>磷化铟|云南锗业发布投资者关系活动记录表公告，公司磷化铟晶片现有产能15万片/年(2-4英寸)，受光通信市场需求增加及原材料价格上涨影响，近期产品价格有所上涨。公司已批量向下游外延厂商或具备外延能力的器件厂商供货。公司光纤级锗产品为光纤用四氯化锗，目前产能为60吨/年。公司光纤级锗产品已批量稳定生产多年，客户涵盖国内下游知名光纤生产厂商。</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>磷化铟</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>-1.34</v>
-      </c>
-      <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>sz000908</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>*ST景峰</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>5.050000000000001</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>12天10板</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 公司专注医药健康产业，涉足药品研发、生产、销售等领域，产品涵盖了心脑血管、抗肿瘤、骨科、妇儿等用药领域。</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>-1.34</v>
-      </c>
-      <c r="C21" s="2" t="inlineStr"/>
-      <c r="D21" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>sh603843</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">*ST正平 </t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>8.109999999999999</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>5.050000000000001</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>8天7板</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 2025年2月21日公司官微披露，旗下正平智算参加海东市绿色算力产业集中签约暨推介活动并签订算电协同产业园框架协议。</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>-1.34</v>
-      </c>
-      <c r="C22" s="2" t="inlineStr"/>
-      <c r="D22" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>sz000669</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>ST金鸿</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>9天7板</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 主营气源开发与输送、长输管网建设与管理、城市燃气经营与销售、车用加气站投资与运营、LNG点供、分布式能源项目开发与建设等。</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>智能电网</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>-1.34</v>
-      </c>
-      <c r="C23" s="2" t="inlineStr"/>
+        <v>-4.399999999999999</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>央视财经报道，2025年，我国变压器出口总值达646亿元，比2024年增长近36%。我国已成为世界第一大变压器生产国，在原材料、成本、生产周期等方面都具备明显优势。</t>
+        </is>
+      </c>
       <c r="D23" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>sh600381</t>
+          <t>sh603016</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST春天 </t>
+          <t xml:space="preserve">新宏泰  </t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>3.33</v>
+        <v>38.58</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>5.050000000000001</v>
+        <v>10.01</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5天5板</t>
+          <t>4天2板</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 在大健康业务方面，公司已基本完成了涵盖保健食品、药品等冬虫夏草高效利用产品的储备和战略布局。</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr"/>
+          <t>电网设备|公司主营业务为断路器关键部件，低压断路器及刀熔开关的研发，生产与销售，公司实控人为无锡市人民政府国有资产监督管理委员会。</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>电网设备</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1565,36 +1577,36 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>-1.34</v>
+        <v>-3.83</v>
       </c>
       <c r="C24" s="2" t="inlineStr"/>
       <c r="D24" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>sh603580</t>
+          <t>sz000908</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST艾艾 </t>
+          <t>*ST景峰</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>18.18</v>
+        <v>6.77</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>5.029999999999999</v>
+        <v>4.96</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4天4板</t>
+          <t>13天11板</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司是专业从事为轻型输送带的研发、生产及销售，境外营业收入大于50%。</t>
+          <t>ST股 | 公司专注医药健康产业，涉足药品研发、生产、销售等领域，产品涵盖了心脑血管、抗肿瘤、骨科、妇儿等用药领域。</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
@@ -1606,36 +1618,36 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>-1.34</v>
+        <v>-3.83</v>
       </c>
       <c r="C25" s="2" t="inlineStr"/>
       <c r="D25" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>sh603813</t>
+          <t>sh603843</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST原尚 </t>
+          <t xml:space="preserve">*ST正平 </t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>32.16</v>
+        <v>8.52</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>5</v>
+        <v>5.06</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>9天8板</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司参股公司广东原锋新能源科技的股东之一锋源是国内极少的集全套自主知识产权氢燃料电池电堆以及核心零部件膜电极、催化剂、金属双极板等研发、生产、销售一体的公司。</t>
+          <t>ST股 | 2025年2月21日公司官微披露，旗下正平智算参加海东市绿色算力产业集中签约暨推介活动并签订算电协同产业园框架协议。</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
@@ -1647,37 +1659,36 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>-1.34</v>
+        <v>-3.83</v>
       </c>
       <c r="C26" s="2" t="inlineStr"/>
       <c r="D26" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>sh603398</t>
+          <t>sz000638</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST沐邦 </t>
+          <t>*ST万方</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>11.27</v>
+        <v>1.48</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>5.029999999999999</v>
+        <v>4.96</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4天2板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 1.沐邦高科公告，与铜陵狮子山高新技术产业开发区管理委员会、铜陵高新发展投资有限公司签订《项目投资协议书》，项目名称为年产10GW-N型高效电池片、10GW切片生产基地项目。
-2.公司上市的IP产品 “樱桃小丸子”第一期为“盲盒”类产品。</t>
+          <t>ST股 | 公司业务主要包括军工产业、农业产业以及生物制品等业务。公司控股子公司万方迈捷以粮库收储为核心，深入研究粮食加工、研究土地流转、研究农民就业，万方迈捷作为乾安县唯一一家自主加工的大米企业。</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
@@ -1689,32 +1700,36 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>-1.34</v>
+        <v>-3.83</v>
       </c>
       <c r="C27" s="2" t="inlineStr"/>
       <c r="D27" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>sh600608</t>
+          <t>sh600355</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST沪科 </t>
+          <t xml:space="preserve">*ST精伦 </t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>2.87</v>
+        <v>0.82</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>5.13</v>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司是一家信息技术行业公司，主要业务分为钢材制品加工制造及商品贸易业务两大板块。</t>
+          <t>ST股 | 公司智能控制产品是公司全资子公司上海鲍麦克斯电子科技有限公司的主营产品，鲍麦克斯专业从事通用及专用伺服驱动系统、数控系统、 缝制机器人的系列化产品研发及销售。</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
@@ -1726,11 +1741,11 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>-1.34</v>
+        <v>-3.83</v>
       </c>
       <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -1743,12 +1758,16 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
+        <v>4.850000000000001</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
           <t>ST股 | 1.公司主要从事商业保理、融资租赁、不动产运营管理和大宗商品贸易。
@@ -1764,32 +1783,36 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>-1.34</v>
+        <v>-3.83</v>
       </c>
       <c r="C29" s="2" t="inlineStr"/>
       <c r="D29" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>sz000638</t>
+          <t>sh600608</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>*ST万方</t>
+          <t xml:space="preserve">*ST沪科 </t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>1.41</v>
+        <v>3.01</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>5.220000000000001</v>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
+        <v>4.88</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司业务主要包括军工产业、农业产业以及生物制品等业务。公司控股子公司万方迈捷以粮库收储为核心，深入研究粮食加工、研究土地流转、研究农民就业，万方迈捷作为乾安县唯一一家自主加工的大米企业。</t>
+          <t>ST股 | 公司是一家信息技术行业公司，主要业务分为钢材制品加工制造及商品贸易业务两大板块。</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
@@ -1801,32 +1824,32 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>-1.34</v>
+        <v>-3.83</v>
       </c>
       <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>sh600355</t>
+          <t>sh600107</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST精伦 </t>
+          <t xml:space="preserve">ST尔雅  </t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.78</v>
+        <v>5.59</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>5.41</v>
+        <v>5.08</v>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司智能控制产品是公司全资子公司上海鲍麦克斯电子科技有限公司的主营产品，鲍麦克斯专业从事通用及专用伺服驱动系统、数控系统、 缝制机器人的系列化产品研发及销售。</t>
+          <t>ST股 | 公司的主营业务为服装、服饰和纺织品研发、设计、制造和销售。</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
@@ -1834,13 +1857,11 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>-3.83</v>
       </c>
       <c r="C31" s="2" t="inlineStr"/>
       <c r="D31" s="2" t="n">
@@ -1848,46 +1869,36 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>sz000020</t>
+          <t>sz002620</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>深华发Ａ</t>
+          <t>ST瑞和</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>23.33</v>
+        <v>7.15</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>5天5板</t>
-        </is>
-      </c>
+        <v>4.99</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>面板|公司主营业务分为液晶显示器整机、注塑件、保丽龙（轻型材料包装）、物业租赁四大模块。液晶显示器整机业务生产经营各种彩色电视机、液晶显示器、液晶显示屏，是公司主要收入来源。</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>面板</t>
-        </is>
-      </c>
+          <t>ST股 | 公司主要从事政府机构、房地产开发商、大型企业、高档酒店、交通枢纽、园林绿化等综合性专业化装饰设计、工程施工业务以及光伏电站运营、光伏项目施工安装等。</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>-3.83</v>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="n">
@@ -1895,46 +1906,36 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>sh600683</t>
+          <t>sh600136</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>京投发展</t>
+          <t xml:space="preserve">ST明诚  </t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>10.86</v>
+        <v>1.82</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>6天4板</t>
-        </is>
-      </c>
+        <v>5.2</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>剥离地产业务|京投发展公告称，公司拟将持有的房地产开发业务相关资产及负债转让至控股股东京投公司，采用现金支付方式，不涉及发行股份，不影响公司股权结构，不会因此导致公司控股股东发生变更。本事项预计构成重大资产重组。</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>剥离地产业务</t>
-        </is>
-      </c>
+          <t>ST股 | 影视业务系公司两大主营业务之一，包括影视娱乐内容制作、运营、发行等。</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>-3.83</v>
       </c>
       <c r="C33" s="2" t="inlineStr"/>
       <c r="D33" s="2" t="n">
@@ -1942,35 +1943,27 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>sh603687</t>
+          <t>sh603377</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">大胜达  </t>
+          <t xml:space="preserve">ST东时  </t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>13.39</v>
+        <v>3.72</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>5.08</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>并购重组+算力芯片|大胜达公告称，公司拟通过股权受让及增资方式合计投资5.5亿元取得芯瞳半导体技术（厦门）有限公司22.9831%的股权。其中，以2786万元受让2.7074%股权，以2214万元受让1.5961%股权，并以5亿元增资（分两次，第一次2.5亿元，第二次2.5亿元需满足流片成功条件）。同时，控股股东新胜达以5000万元同条件增资，取得1.9608%股权。芯瞳半导体成立于2019年，是国内专注于通用高性能图形处理器芯片设计研发与销售的先驱企业。</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>并购重组, 算力芯片</t>
-        </is>
-      </c>
+          <t>ST股 | 公司持有海若通航55%的股权，海若通航是一家具备CCAR-91部通航作业，CCAR-141部飞行培训，CCAR-145部航空器维修资质的通用航空运营商。</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1985,37 +1978,37 @@
       </c>
       <c r="C34" s="2" t="inlineStr"/>
       <c r="D34" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>sh600617</t>
+          <t>sh603803</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>国新能源</t>
+          <t>瑞斯康达</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>3.99</v>
+        <v>14.61</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>9.92</v>
+        <v>10.02</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>10天5板</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>天然气|山西最大的天然气管网运营企业，管网建设方面公司在省内主要业务区域已取得绝对优势地位，省级天然气管网5000余公里，年管输涉及能力超过255亿立方米，管网覆盖全省11市104县（市、区）。</t>
+          <t>光通信|在高端光模块领域，公司联营企业易锐光电是中国少数产业链上下游关键层面具备完整核心技术和解决方案的高科技企业，新一代基于自主知识产权的25G/100G/超100G集成光收发芯片的光通信模块及光组件，用于电信网络城域网和大型数据中心网络。</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>天然气</t>
+          <t>光通信</t>
         </is>
       </c>
     </row>
@@ -2032,33 +2025,37 @@
       </c>
       <c r="C35" s="2" t="inlineStr"/>
       <c r="D35" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sz000677</t>
+          <t>sh603687</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>恒天海龙</t>
+          <t xml:space="preserve">大胜达  </t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>4.98</v>
+        <v>14.73</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="I35" s="2" t="inlineStr"/>
+        <v>10.01</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>4天4板</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>并购重组|恒天海龙公告称，公司拟通过全资子公司海龙飞控以现金方式收购群健航空不少于40%股权，交易完成后海龙飞控将成为目标公司控股股东。该协议为初步意向协议，目前尚未签署正式《股权收购协议》，相关事项存在不确定性。</t>
+          <t>并购重组+算力芯片|大胜达公告称，公司拟通过股权受让及增资方式合计投资5.5亿元取得芯瞳半导体技术（厦门）有限公司22.9831%的股权。其中，以2786万元受让2.7074%股权，以2214万元受让1.5961%股权，并以5亿元增资（分两次，第一次2.5亿元，第二次2.5亿元需满足流片成功条件）。同时，控股股东新胜达以5000万元同条件增资，取得1.9608%股权。芯瞳半导体成立于2019年，是国内专注于通用高性能图形处理器芯片设计研发与销售的先驱企业。</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>并购重组</t>
+          <t>并购重组, 算力芯片</t>
         </is>
       </c>
     </row>
@@ -2075,33 +2072,37 @@
       </c>
       <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sz000509</t>
+          <t>sz002565</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>华塑控股</t>
+          <t>顺灏股份</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>4.54</v>
+        <v>16.98</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
+        <v>9.969999999999999</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>5天3板</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>MLED|公司积极布局了MiniLED、OLED和高分高刷高色域等显示领域前沿产品技术。</t>
+          <t>太空算力|公司2025年6月以1.1亿元人民币投资北京轨道辰光科技有限公司，持股比例为19.30%。轨道辰光的主要业务是通过将算力卫星发射至晨昏轨道，组建太空数据中心，为客户提供算力服务，其经营范围包括微小卫星生产制造、微小卫星科研试验、互联网信息服务等。轨道辰光首颗试验星算力规模预计25p。</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>MLED</t>
+          <t>太空算力</t>
         </is>
       </c>
     </row>
@@ -2118,33 +2119,33 @@
       </c>
       <c r="C37" s="2" t="inlineStr"/>
       <c r="D37" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sh603026</t>
+          <t>sz300385</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>石大胜华</t>
+          <t>雪浪环境</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>75.41</v>
+        <v>15.61</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>10.01</v>
+        <v>19.98</v>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>锂电池电解液|公司是能够同时提供锂离子电池电解液及电解液溶剂、溶质、添加剂产品的全产业链公司，具备五大碳酸酯溶剂、六氟磷酸锂及部分添加剂的生产能力，形成锂电池溶剂、电解液、高端新材料三大业务版块。</t>
+          <t>重整|雪浪环境公告称，公司与上海氦星万联科技发展合伙企业(有限合伙)等四方及预重整引导人签署《重整投资协议》，并与上海氦星光曜科技发展合伙企业签署附属协议。根据协议，重整完成后氦星万联将成为公司控股股东。</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>锂电池电解液</t>
+          <t>重整</t>
         </is>
       </c>
     </row>
@@ -2161,33 +2162,33 @@
       </c>
       <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>sh600604</t>
+          <t>sh603727</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>市北高新</t>
+          <t xml:space="preserve">博迈科  </t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>5.7</v>
+        <v>19.75</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>10.04</v>
+        <v>10.03</v>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>创投|公司旗下上海聚能湾企业服务有限公司孵化器是以大数据、云计算为产业特色的国家级科技企业孵化器，已构建完成“创业苗圃+孵化器+加速器”的完整孵化体系。</t>
+          <t>油气|公司主要产品大类分为海洋油气开发模块、矿业开采模块、天然气液化模块等，产品具体涉及十多种子类别。公司为海洋油气开发、矿业开采和天然气液化领域中的国内外高端客户提供能源资源设施开发的专业分包服务。</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>创投</t>
+          <t>油气</t>
         </is>
       </c>
     </row>
@@ -2204,76 +2205,33 @@
       </c>
       <c r="C39" s="2" t="inlineStr"/>
       <c r="D39" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>sh603538</t>
+          <t>sz300868</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">美诺华  </t>
+          <t>杰美特</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>27.84</v>
+        <v>46.33</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>10</v>
+        <v>19.99</v>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>益生菌减重|近日，由宁波美诺华天康药业有限公司申办的一项单中心、开放、自身对照人体试食临床试验，评估了益生菌（JH389）胶囊产品的减重效果和安全性。结果显示，服用该产品8周可显著改善受试者体重、体脂及肥胖相关指标。</t>
+          <t>并购重组|杰美特公告称，公司拟以现金方式购买深圳戴尔蒙德科技有限公司21.5%股权，交易价格为1.29亿元，资金来源为公司自有资金及自筹资金。公司拟通过本次交易拓宽公司产业布局，形成新的业绩增长点。</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>益生菌减重</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>sh605050</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">福然德  </t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>14.43</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>机器人|公司与开普勒机器人合作成立合资公司德普智擎，是公司在汽车产业机器人应用、机器人材料轻量化的拓展和尝试。</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>机器人</t>
+          <t>并购重组</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2315,31 +2273,31 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sz000020</t>
+          <t>sh600396</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>深华发Ａ</t>
+          <t>华电辽能</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sh600396</t>
+          <t>sh603687</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>华电辽能</t>
+          <t xml:space="preserve">大胜达  </t>
         </is>
       </c>
     </row>
@@ -2349,27 +2307,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sz000601</t>
+          <t>sz002310</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>韶能股份</t>
+          <t>东方新能</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sh603687</t>
+          <t>sz002150</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">大胜达  </t>
+          <t>正泰电源</t>
         </is>
       </c>
     </row>
@@ -2379,42 +2337,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sz002310</t>
+          <t>sz002309</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>东方新能</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>sh600726</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>华电能源</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>sh600617</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>国新能源</t>
+          <t>中利集团</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,19 +476,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="92" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="88" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="232" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="303" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -556,15 +556,15 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-2.22</v>
+        <v>5.3</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>华泰证券研报称，霍尔木兹海峡的封锁让市场对化石能源价格易涨难跌逐步确立信心，重申对电力板块的全面看多，包括水核风光生物质在内的绿电或充分受益。</t>
+          <t>3月23日，国家数据局表示，下一步将会同相关部门大力推进算电协同工程，确保枢纽节点新建算力设施绿电应用占比达到80%以上，最大程度发挥绿色电力的支撑作用。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -577,25 +577,25 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>6.89</v>
+        <v>7.58</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10.06</v>
+        <v>10.01</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>6天6板</t>
+          <t>7天7板</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>电缆+氢能|1.公司是中国华电集团公司的实际控制的上市公司、中央企业的三级单位，同时也是一家集火力发电、风力发电、煤炭营销、供热、供汽为一体的综合性区域基础能源企业。
+          <t>电力+氢能|1.公司是中国华电集团公司的实际控制的上市公司、中央企业的三级单位，同时也是一家集火力发电、风力发电、煤炭营销、供热、供汽为一体的综合性区域基础能源企业。
 2.2023年3月14日公告，拟与华电科工共同出资建设25MW风电离网制氢一体化项目，风电设备年利用小时数3000小时，年发电量约7500万千瓦时，全部发电量均用于本项目制取绿氢，预计年产绿氢1230吨。项目总投资2.78亿元。公司与华电科工拟按70%和30%比例组建项目公司。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>电缆, 氢能</t>
+          <t>电力, 氢能</t>
         </is>
       </c>
     </row>
@@ -606,45 +606,46 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>-2.22</v>
+        <v>5.3</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>华泰证券研报称，霍尔木兹海峡的封锁让市场对化石能源价格易涨难跌逐步确立信心，重申对电力板块的全面看多，包括水核风光生物质在内的绿电或充分受益。</t>
+          <t>3月23日，国家数据局表示，下一步将会同相关部门大力推进算电协同工程，确保枢纽节点新建算力设施绿电应用占比达到80%以上，最大程度发挥绿色电力的支撑作用。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sz002310</t>
+          <t>sz000601</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>东方新能</t>
+          <t>韶能股份</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>3.83</v>
+        <v>8.06</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>10.06</v>
+        <v>9.959999999999999</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>6天4板</t>
+          <t>5天4板</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>并购重组+绿电|2025年12月15日公告，公司拟以现金支付方式购买海城锐海100%股权和电投瑞享80%股权。其中，海城锐海100%股权拟通过在天津产权交易中心摘牌方式购买。标的资产的审计和评估工作尚未完成，评估值及交易价格均尚未确定（海城锐海100%股权在天津产权交易所的挂牌转让底价为1410万元）。本次交易预计构成重大资产重组。通过本次交易，东方园林新增光伏电站、风电场的投资、开发、建设和运营等新能源业务。</t>
+          <t>电算协同|1.公司自成立以来，一直以能源的投资开发经营为主营业务，在不断巩固和发展水电产业的基础上，重点发展生物质能发电、加油加气充电一体化站等业务。
+2.韶能算电公司拟在乐昌市成立全资子公司，开发清洁电源业务，注册资本10亿元；若该项目投产，有利于壮大公司清洁能源规模，为韶关数据集群提供绿电供应。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>并购重组, 绿电</t>
+          <t>电算协同</t>
         </is>
       </c>
     </row>
@@ -655,45 +656,46 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>-2.22</v>
+        <v>5.3</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>华泰证券研报称，霍尔木兹海峡的封锁让市场对化石能源价格易涨难跌逐步确立信心，重申对电力板块的全面看多，包括水核风光生物质在内的绿电或充分受益。</t>
+          <t>3月23日，国家数据局表示，下一步将会同相关部门大力推进算电协同工程，确保枢纽节点新建算力设施绿电应用占比达到80%以上，最大程度发挥绿色电力的支撑作用。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sz001258</t>
+          <t>sz000539</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>立新能源</t>
+          <t>粤电力Ａ</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>10.62</v>
+        <v>6.78</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>10.05</v>
+        <v>10.06</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3天2板</t>
+          <t>5天3板</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>绿电|公司的主营业务为风力发电、光伏发电项目的投资、开发、建设和运营。公司运营的风电场、光伏电站主要位于新疆。</t>
+          <t>电算协同|1.公司主要从事电力项目的投资、建设和经营管理，电力的生产和销售业务，拥有大型燃煤发电、LNG发电、风力发电和水力发电等多种能源项目。
+2.粤电力A互动平台表示，广东能源克拉玛依光伏项目规划配套建设算力规模500PFlops的智算中心。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>绿电</t>
+          <t>电算协同</t>
         </is>
       </c>
     </row>
@@ -704,15 +706,15 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-2.22</v>
+        <v>5.3</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>华泰证券研报称，霍尔木兹海峡的封锁让市场对化石能源价格易涨难跌逐步确立信心，重申对电力板块的全面看多，包括水核风光生物质在内的绿电或充分受益。</t>
+          <t>3月23日，国家数据局表示，下一步将会同相关部门大力推进算电协同工程，确保枢纽节点新建算力设施绿电应用占比达到80%以上，最大程度发挥绿色电力的支撑作用。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -725,12 +727,16 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>4.73</v>
+        <v>5.2</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr"/>
+        <v>9.94</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
           <t>煤炭+电力|1.公司下辖7个煤矿，煤炭产品核定生产能力达到1160万吨/年，各矿煤种以冶金煤为主。
@@ -750,42 +756,45 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>-2.22</v>
+        <v>5.3</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>华泰证券研报称，霍尔木兹海峡的封锁让市场对化石能源价格易涨难跌逐步确立信心，重申对电力板块的全面看多，包括水核风光生物质在内的绿电或充分受益。</t>
+          <t>3月23日，国家数据局表示，下一步将会同相关部门大力推进算电协同工程，确保枢纽节点新建算力设施绿电应用占比达到80%以上，最大程度发挥绿色电力的支撑作用。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sh600149</t>
+          <t>sh600032</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>廊坊发展</t>
+          <t>浙江新能</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>6.36</v>
+        <v>11.84</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
+        <v>10.04</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>电力+房地产|1.公司是廊坊市国有控股的唯一一家A股上市公司，所从事供热业务具有公用事业显著特征，公司供热经营区域面积超100平方公里，是廊坊市覆盖区域最大的供热企业。
-2.廊坊控股旗下有各类土地资源累计达34万多亩。廊坊控股旗下土地资源大部分来自五个产业园区一级土地开发。</t>
+          <t>绿电|公司的主营业务为水力发电、光伏发电、风力发电等可再生能源项目的投资、开发、建设和运营管理。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>电力, 房地产</t>
+          <t>绿电</t>
         </is>
       </c>
     </row>
@@ -796,36 +805,40 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-2.22</v>
+        <v>5.3</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>华泰证券研报称，霍尔木兹海峡的封锁让市场对化石能源价格易涨难跌逐步确立信心，重申对电力板块的全面看多，包括水核风光生物质在内的绿电或充分受益。</t>
+          <t>3月23日，国家数据局表示，下一步将会同相关部门大力推进算电协同工程，确保枢纽节点新建算力设施绿电应用占比达到80%以上，最大程度发挥绿色电力的支撑作用。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sh600032</t>
+          <t>sh603165</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>浙江新能</t>
+          <t>荣晟环保</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>10.76</v>
+        <v>15.32</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
+        <v>9.98</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>绿电|公司的主营业务为水力发电、光伏发电、风力发电等可再生能源项目的投资、开发、建设和运营管理。</t>
+          <t>绿电|2022年1月4日公告，公司与安徽省全椒县人民政府签订年产130万吨再生环保纸及新能源综合利用项目战略合作框架协议，建设内容包括年产130万吨再生环保纸、生物质热电联产(年处理50万吨秸秆)、光伏产品研发和制造、1GW分布式光伏电站等运营管理，并配套建设工业固废资源综合利用项目、环保水处理项目，项目总投资105亿元。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -841,209 +854,209 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>-2.22</v>
+        <v>5.3</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>华泰证券研报称，霍尔木兹海峡的封锁让市场对化石能源价格易涨难跌逐步确立信心，重申对电力板块的全面看多，包括水核风光生物质在内的绿电或充分受益。</t>
+          <t>3月23日，国家数据局表示，下一步将会同相关部门大力推进算电协同工程，确保枢纽节点新建算力设施绿电应用占比达到80%以上，最大程度发挥绿色电力的支撑作用。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sh603105</t>
+          <t>sz000722</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>芯能科技</t>
+          <t>湖南发展</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>12.74</v>
+        <v>15.11</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>10.02</v>
+        <v>9.969999999999999</v>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>绿电+虚拟电厂|1.公司主营业务包括分布式光伏电站投资运营、分布式光伏解决方案提供以及光伏产品研发制造。
-2.公司于2021年建成“网荷光储充智能微网”示范项目是小型分布式虚拟电厂，并已稳定运行至今。</t>
+          <t>电力|公司主营业务为水力发电综合开发经营以及医疗、机构养老、“互联网+社区居家养老”服务体系的投资、建设及运营管理。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>绿电, 虚拟电厂</t>
+          <t>电力</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-4.44</v>
+        <v>5.3</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>国际原油价格持续高位震荡，国内化工企业纷纷启动调价模式，从上游基础化工品到下游终端产品，调价潮正在蔓延，行业成本传导效应凸显。</t>
+          <t>3月23日，国家数据局表示，下一步将会同相关部门大力推进算电协同工程，确保枢纽节点新建算力设施绿电应用占比达到80%以上，最大程度发挥绿色电力的支撑作用。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sh600844</t>
+          <t>sz002445</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>金煤科技</t>
+          <t>中南文化</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>4.03</v>
+        <v>4.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>10.11</v>
+        <v>9.969999999999999</v>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>煤化工|公司为专注于煤制乙二醇产业的新型化工企业，目前主要通过控股子公司通辽金煤的大型化工装置生产乙二醇并联产草酸。</t>
+          <t>并购重组+电力|中南文化公告称，公司计划通过发行股份及支付现金的方式购买江阴电力投资有限公司持有的江阴苏龙热电有限公司57.30%股权，同时拟向不超过三十五名特定投资者募集配套资金。本次交易相关审计、评估工作尚未完成，交易方案需进一步论证和沟通协商。本次交易预计构成重大资产重组。本次交易完成后，上市公司在电力能源领域的业务布局将得到拓展。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>煤化工</t>
+          <t>并购重组, 电力</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-4.44</v>
+        <v>5.3</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>国际原油价格持续高位震荡，国内化工企业纷纷启动调价模式，从上游基础化工品到下游终端产品，调价潮正在蔓延，行业成本传导效应凸显。</t>
+          <t>3月23日，国家数据局表示，下一步将会同相关部门大力推进算电协同工程，确保枢纽节点新建算力设施绿电应用占比达到80%以上，最大程度发挥绿色电力的支撑作用。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sh600792</t>
+          <t>sz300335</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>云煤能源</t>
+          <t>迪森股份</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>4.92</v>
+        <v>8.4</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>10.07</v>
+        <v>20</v>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>煤化工|云南省最大的焦化企业，主要产品有冶金焦炭、焦油、粗苯、煤气、甲醇、硫酸铵、硫磺等产品。</t>
+          <t>电力|公司的B端运营业务可以为工业及商业用户提供热力（蒸汽、热水）、冷气、电力等多种清洁能源整体解决方案，实现区域能源的资源整合和综合利用。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>煤化工</t>
+          <t>电力</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>-4.44</v>
+        <v>5.3</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>国际原油价格持续高位震荡，国内化工企业纷纷启动调价模式，从上游基础化工品到下游终端产品，调价潮正在蔓延，行业成本传导效应凸显。</t>
+          <t>3月23日，国家数据局表示，下一步将会同相关部门大力推进算电协同工程，确保枢纽节点新建算力设施绿电应用占比达到80%以上，最大程度发挥绿色电力的支撑作用。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sh603616</t>
+          <t>sz000065</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>韩建河山</t>
+          <t>北方国际</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>7.25</v>
+        <v>14.22</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>10.02</v>
+        <v>9.98</v>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>并购重组+化工|2026年2月3日公告，公司拟发行股份及支付现金购买兴福新材99.9978%股份，并向不超过35名符合条件的特定投资者发行股份募集配套资金。本次交易完成后，公司主营业务新增芳香族产品的研发、生产和销售。本次交易构成重大资产重组。兴福新材是一家专注于芳香族产品的研发、生产和销售的高新技术企业，主要产品包括新一代特种工程塑料聚醚醚酮（PEEK）中间体、农药及医药中间体和PEEK纯化业务等。</t>
+          <t>一带一路+海外绿电|1.公司控股股东是中国兵器工业集团旗下中国北方工业有限公司，公司主营国际工程承包业务、建筑工程等。
+2.公司旗下控股子公司克罗地亚能源工程股份公司是以开发塞尼风电项目设立的特殊目的公司，以获取克罗地亚塞尼156MW风电项目的建设、运营权。公司拟通过匈牙利子公司以自有资金1300万欧元收购Aurora Solar d.o.o.80%的股权，并投资、建设及运营波黑科曼耶山125MWp光伏项目。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>并购重组, 化工</t>
+          <t>一带一路, 海外绿电</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>-4.44</v>
+        <v>5.3</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>国际原油价格持续高位震荡，国内化工企业纷纷启动调价模式，从上游基础化工品到下游终端产品，调价潮正在蔓延，行业成本传导效应凸显。</t>
+          <t>3月23日，国家数据局表示，下一步将会同相关部门大力推进算电协同工程，确保枢纽节点新建算力设施绿电应用占比达到80%以上，最大程度发挥绿色电力的支撑作用。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sz000703</t>
+          <t>sh600744</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>恒逸石化</t>
+          <t>华银电力</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>11.84</v>
+        <v>8.77</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>10.04</v>
@@ -1051,1187 +1064,3969 @@
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>化工|公司在国内同行中形成独有的“涤纶+锦纶”双纶驱动石化产业链为核心业务，以供应链服务业务为成长业务，差别化纤维产品、工业智能技术应用为新兴业务的“石化+”多层次立体产业布局。</t>
+          <t>电力|作为湖南省火电装机主要发电企业，公司主要从事火力发电业务，同时经营水电、风电、太阳能业务以及电力销售业务。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>电力</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-5.23</v>
+        <v>5.3</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>上交所受理宇树科技股份有限公司科创板IPO申请，拟融资金额42.02亿元。</t>
+          <t>3月23日，国家数据局表示，下一步将会同相关部门大力推进算电协同工程，确保枢纽节点新建算力设施绿电应用占比达到80%以上，最大程度发挥绿色电力的支撑作用。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sh600376</t>
+          <t>sh600821</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>首开股份</t>
+          <t>金开新能</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>5.87</v>
+        <v>11.07</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>9.93</v>
+        <v>10.04</v>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>参股宇树科技|公司旗下首开盈信通过金石成长股权投资（杭州）合伙企业间接投资宇树科技。</t>
+          <t>电算协同|1.公司主营业务为新能源电力的开发、投资、建设及运营，包括光伏发电和风力发电两个板块。
+2.2024年10月8日公告，公司全资子公司金开新能科技有限公司拟于新疆昌吉市投资建设国家超算广州中心新疆分中心昌吉智算中心项目，算力总规模达到5,000PFlops。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>参股宇树科技</t>
+          <t>电算协同</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>-5.23</v>
+        <v>5.3</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>上交所受理宇树科技股份有限公司科创板IPO申请，拟融资金额42.02亿元。</t>
+          <t>3月23日，国家数据局表示，下一步将会同相关部门大力推进算电协同工程，确保枢纽节点新建算力设施绿电应用占比达到80%以上，最大程度发挥绿色电力的支撑作用。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sh600143</t>
+          <t>sh600982</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>金发科技</t>
+          <t>宁波能源</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>17.57</v>
+        <v>6.27</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>10.02</v>
+        <v>10</v>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司的特种工程塑料可以用于人形机器人的伺服电机及连接器上。</t>
+          <t>电力|公司主要从事热电联产、生物质发电、抽水蓄能和综合能源服务，以及能源类相关金融投资等业务。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>电力</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>-5.23</v>
+        <v>5.3</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>上交所受理宇树科技股份有限公司科创板IPO申请，拟融资金额42.02亿元。</t>
+          <t>3月23日，国家数据局表示，下一步将会同相关部门大力推进算电协同工程，确保枢纽节点新建算力设施绿电应用占比达到80%以上，最大程度发挥绿色电力的支撑作用。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sz002896</t>
+          <t>sh601016</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>中大力德</t>
+          <t>节能风电</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>77</v>
+        <v>4.91</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>10</v>
+        <v>10.09</v>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司是从事机械传动与控制应用领域关键零部件的研发、生产、销售和服务的高新技术企业，主要产品包括精密减速器、传动行星减速器、各类小型及微型减速电机等，为各类机械设备提供安全、高效、精密的动力传动与控制应用解决方案。</t>
+          <t>绿电|公司的主营业务为风力发电的项目开发、建设及运营。在加快风电场开发和建设的同时，加大中东部及南方区域市场开发力度，在湖北、广西、浙江、河南、四川等已有项目的区域开发后续项目，在贵州、安徽、湖南、广东、重庆、江西、山东等区域开展风电项目前期踏勘和测风工作，扩大资源储备。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>绿电</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>-5.23</v>
+        <v>5.3</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>上交所受理宇树科技股份有限公司科创板IPO申请，拟融资金额42.02亿元。</t>
+          <t>3月23日，国家数据局表示，下一步将会同相关部门大力推进算电协同工程，确保枢纽节点新建算力设施绿电应用占比达到80%以上，最大程度发挥绿色电力的支撑作用。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sh603272</t>
+          <t>sh600868</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>联翔股份</t>
+          <t>梅雁吉祥</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>23.98</v>
+        <v>3.78</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>10</v>
+        <v>9.879999999999999</v>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>机器人|2025年12月30日公告，董事会审议通过变更经营范围议案，新增服务消费机器人制造、服务消费机器人销售、工业机器人制造、工业机器人销售、智能机器人的研发等制造销售，并同步修订公司章程。</t>
+          <t>锑银矿+电力|1.公司旗下梅雁矿业所拥有的嵩溪锑银矿主要矿种为银矿、锑矿，采矿许可证内累计查明资源储量：银锑矿石量1264.353 Kt；锑金属量22474.82t。
+2.公司电站全部在广东省梅州地区，均为水力发电，目前公司建成投产的水电站总装机容量约为15.1万千瓦，年设计发电量约4.7亿度。公司所发电量全部由广东电网公司收购。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>锑银矿, 电力</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>锂电池</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>自2025年11月以来，截至2026年3月23日碳酸锂期货价格已累计涨逾70%，今年以来已累计涨逾19%。</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>sz300497</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>富祥药业</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>锂电+一季度业绩|富祥药业公告称，预计2026年第一季度归属于上市公司股东的净利润为5200万元-7500万元，上年同期为223.88万元，同比增长2222.67%-3250.01%。报告期内，受益于新能源行业景气度持续提升，动力电池市场需求稳步增长，储能电池市场需求快速爆发，带动上游锂电材料需求持续攀升。公司锂电池电解液添加剂业务经营态势良好，VC、FEC等核心产品量价齐升，从而推动公司业绩同比大幅增长。</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>锂电, 一季度业绩</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>锂电池</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>自2025年11月以来，截至2026年3月23日碳酸锂期货价格已累计涨逾70%，今年以来已累计涨逾19%。</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>sz002192</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>融捷股份</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>负极材料+锂矿|1.融捷股份公告称，公司第九届董事会第三次会议审议通过多项议案，其中包括全资子公司兰州融捷材料科技有限公司拟投资约11亿元建设年产5万吨高性能锂离子电池负极材料项目。
+2.公司拥有康定市甲基卡锂辉石矿134号脉的采矿权，矿山储量2899.5万吨，具有105万吨/年露天开采能力及45万吨/年矿石处理的选矿能力。</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>负极材料, 锂矿</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>锂电池</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>自2025年11月以来，截至2026年3月23日碳酸锂期货价格已累计涨逾70%，今年以来已累计涨逾19%。</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>sh603937</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>丽岛新材</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>电池集流体材料|2022年5月18日公告，公司拟与安徽五河经济开发区管委会签订《投资合同》，在五河县建设新能源电池集流体材料项目，项目总投资10亿元。</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>电池集流体材料</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>锂电池</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>自2025年11月以来，截至2026年3月23日碳酸锂期货价格已累计涨逾70%，今年以来已累计涨逾19%。</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>sh603527</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>众源新材</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>锂电池|公司一直专注于紫铜带箔材的研发、生产和销售，经过十余年发展，公司紫铜带箔材产品生产能力由设立之初的0.6万吨/年，逐步增加至目前的10万吨/年。</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>锂电池</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>锂电池</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>自2025年11月以来，截至2026年3月23日碳酸锂期货价格已累计涨逾70%，今年以来已累计涨逾19%。</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>sz002631</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>德尔未来</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>锂电池+石墨烯|1.公司参股公司益舟新能源是一家专业从事锂离子电池功能材料的应用开发研究和产业化工作，为锂离子电池性能提升提供技术解决方案的高科技企业，目前主要生产销售高安全性功能隔膜及其关联材料、用于高功率密度电池的功能涂层电池箔及其关联浆料等。
+2.旗下厦门英烯科技主要从事石墨烯智能穿戴应用，能源材料、器件及功能涂料应用，二维半导体材料方面的研究和产业化。</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>锂电池, 石墨烯</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>锂电池</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>自2025年11月以来，截至2026年3月23日碳酸锂期货价格已累计涨逾70%，今年以来已累计涨逾19%。</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>sz002083</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>孚日股份</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>电解液添加剂|子公司孚日新能源积极布局锂电池电解液添加剂产品，主要生产氯代碳酸乙烯酯（CEC）、碳酸亚乙烯酯（VC）粗品和电池级产品等动力锂电池上下游系列产品。</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>电解液添加剂</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>锂电池</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>自2025年11月以来，截至2026年3月23日碳酸锂期货价格已累计涨逾70%，今年以来已累计涨逾19%。</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>sh600773</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>西藏城投</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>18.08</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>锂矿+房地产|1.公司参股企业国能矿业（持股比例41%）投资开发的西藏阿里龙木错和结则茶卡两个盐湖。
+2.公司主营业务为房地产开发与销售，房地产产品涉及保障房、普通住宅、商办楼等多种物业类型。</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>锂矿, 房地产</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>锂电池</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>自2025年11月以来，截至2026年3月23日碳酸锂期货价格已累计涨逾70%，今年以来已累计涨逾19%。</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>sz000688</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>国城矿业</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>35.86</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>锂矿+有色金属|1.公司通过持有国城常青100%份额间接参股金鑫矿业48%股权，从而通过布局锂矿资源切入新能源产业上游核心领域。金鑫矿业主要业务为党坝乡锂辉石矿的勘探及开采，保有锂矿石资源量5075.9万吨，其中Li2O资源量67.54万吨，平均品位1.33%。
+2.2024年12月17日公告，公司拟通过支付现金和承担债务方式购买国城控股集团持有的国城实业不低于60%股权。本次交易构成关联交易，预计构成重大资产重组。通过本次交易，公司将实现对国城实业的控股，在现有以锌精矿、铅精矿、银精矿、铜精矿等为主要产品的有色金属布局基础上，增加钼精矿采选业务，公司产品结构将进一步丰富。</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>锂矿, 有色金属</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>锂电池</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>自2025年11月以来，截至2026年3月23日碳酸锂期货价格已累计涨逾70%，今年以来已累计涨逾19%。</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>sz001203</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>大中矿业</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>40.26</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>锂矿|公司取得湖南鸡脚山锂矿（控制权）和四川加达锂矿两大资源，鸡脚山矿区通天庙矿段的锂矿矿石量48987.2万吨，折合碳酸锂当量324.43万吨；加达锂矿首采区锂矿矿石量4343.60万吨，折合碳酸锂当量约148.42万吨。</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>锂矿</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>智能电网</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>3月23日，国家电力投资集团有限公司举行2026年第一次新闻通气会。国家电投计划今年投资2000亿元，同比增长17%。其中，一季度要完成投资230亿元，实现同比增长35%。</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>sz000720</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>新能泰山</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>电缆+光纤光缆|子公司曲阜电缆主要从事电线电缆、光纤光缆、电力光缆等产品的研发、制造与销售，曲阜电缆生产、 销售的电线电缆产品是公司重点发展的智慧供应链业务产品之一。</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>电缆, 光纤光缆</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>智能电网</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>3月23日，国家电力投资集团有限公司举行2026年第一次新闻通气会。国家电投计划今年投资2000亿元，同比增长17%。其中，一季度要完成投资230亿元，实现同比增长35%。</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>sz002350</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>北京科锐</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>电网设备+氢能|1.公司是技术导向型配电设备制造企业，主营业务为12kV及以下配电及控制设备的研发、生产与销售。公司成立30年以来，专注于配电系统技术进步，崇尚技术创新，曾率先推出智能节电器、故障指示器、美式箱变、户外环网柜、永磁机构真空开关、GRC环保箱体和高过载变压器等新技术或产品。
+2.子公司北京稳力科技有限公司是一家专注于燃料电池系统及其零部件（BOP）设计、开发、生产和销售的高科技企业。</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>电网设备, 氢能</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>智能电网</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>3月23日，国家电力投资集团有限公司举行2026年第一次新闻通气会。国家电投计划今年投资2000亿元，同比增长17%。其中，一季度要完成投资230亿元，实现同比增长35%。</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>sh688551</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">科威尔  </t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>47.34</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>测试电源+氢能|1.公司是一家专注于测试电源行业的综合测试设备供应商，为客户提供测试电源和基于测试电源的测试系统解决方案，已基本形成大、小功率测试电源和测试系统的产品线，是业内为数不多的同时具备三个产品线的公司，是国内测试电源设备行业重要的厂家之一。
+2.公司布局从用氢端到制氢端的相关测试产品，在用氢环节，围绕燃料电池各系统的可靠性展开测试，包括燃料电池电堆测试系统、燃料电池发动机测试系统、燃料电池DC/DC测试系统、燃料电池空压机测试系统、燃料电池专用直流回馈式电子负载、燃料电池氢气循环泵测试系统、燃料电池EIS测试系统等产品系列。</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>测试电源, 氢能</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>智能电网</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>3月23日，国家电力投资集团有限公司举行2026年第一次新闻通气会。国家电投计划今年投资2000亿元，同比增长17%。其中，一季度要完成投资230亿元，实现同比增长35%。</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>sh603421</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>鼎信通讯</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>半导体+智能电网|1.鼎信通讯在互动平台表示，公司芯片开发采用平头哥的CK802 32位内核架构，平头哥与公司签订有全面技术授权协议。
+2.公司的主营业务为低压用电系统产品的研发、生产、销售及服务，主要产品包括低压电力线载波通信模块（含芯片）产品、采集终端设备、智能电能表和配电终端等，主要应用于国家智能电网的用电信息采集系统和配网自动化系统。</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>半导体, 智能电网</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>智能电网</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>3月23日，国家电力投资集团有限公司举行2026年第一次新闻通气会。国家电投计划今年投资2000亿元，同比增长17%。其中，一季度要完成投资230亿元，实现同比增长35%。</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>sz002498</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>汉缆股份</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>电缆|公司是集电缆及附件系统、状态检测系统、输变电工程总包三个板块于一体，研发生产经营的技术密集型企业集团。</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>电缆</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>智能电网</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>3月23日，国家电力投资集团有限公司举行2026年第一次新闻通气会。国家电投计划今年投资2000亿元，同比增长17%。其中，一季度要完成投资230亿元，实现同比增长35%。</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>sh605196</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>华通线缆</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>44.33</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>电网设备|公司主要从事电线电缆的研发、生产与销售业务，主导产品包括以进户线为代表的中低压电力电缆，及以潜油泵电缆为代表的电气装备用电缆，广泛应用于电力输配、采矿/油/气等行业，并已获得美国UL、欧盟CE等国际认证，中国CRCC、CCC等国内认证，是我国在电线电缆国际认证，尤其是美国UL认证领域具有数量领先优势的企业之一。</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>电网设备</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>智能电网</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>3月23日，国家电力投资集团有限公司举行2026年第一次新闻通气会。国家电投计划今年投资2000亿元，同比增长17%。其中，一季度要完成投资230亿元，实现同比增长35%。</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>sz002316</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>亚联发展</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>AI+智能电网|公司基于华为Atlas人工智能计算平台开发的“无人值守变电站智能运检系统V6”及基于华为Tai Shan 200系列开发的“变电站智能网关系统V1.1”获得华为技术认证书，并且在南方电网顺利投放使用。</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>AI, 智能电网</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>智能电网</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>3月23日，国家电力投资集团有限公司举行2026年第一次新闻通气会。国家电投计划今年投资2000亿元，同比增长17%。其中，一季度要完成投资230亿元，实现同比增长35%。</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>sh600192</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>长城电工</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>电网设备|公司主要从事高中低压开关成套设备、高中低压电器元件、母线槽、电气传动自动化装置、新能源装备等电工电器类产品的研发、生产与销售，先后为三峡工程、载人航天、奥运鸟巢、青藏铁路等多项国家重点工程提供优质产品。</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>电网设备</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
           <t>光伏</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n">
-        <v>-4.01</v>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>特斯拉自建芯片工厂“Terafab”项目即将于近期启动。当地时间3月21日，马斯克在社交媒体透露，该项目目标是每年生产超过1太瓦的计算能力，其中约80%用于太空，约20%用于地面。</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="B34" s="2" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉自建芯片工厂“Terafab”项目即将于近期启动，该项目目标是每年生产超过1太瓦的计算能力，其中约80%用于太空，约20%用于地面。</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>sz002309</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>中利集团</t>
         </is>
       </c>
-      <c r="G17" s="2" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>9.969999999999999</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="G34" s="2" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>光伏+光纤光缆|1.公司的新能源光伏组件业务板块，包括单晶大尺寸高效光伏电池片和光伏组件的研发、生产和销售。公司拥有钙钛矿叠层电池及组件研发专利等技术储备6项。
 2.公司光通讯线缆板块已延伸到高分子材料、光纤、电缆的全产业链，作为华为核心战略供应商，为华为提供通信用电缆，包括5G用新品光电混合缆。</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>光伏, 光纤光缆</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>光伏</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>-4.01</v>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>特斯拉自建芯片工厂“Terafab”项目即将于近期启动。当地时间3月21日，马斯克在社交媒体透露，该项目目标是每年生产超过1太瓦的计算能力，其中约80%用于太空，约20%用于地面。</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>sz002218</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>拓日新能</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>6.59</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>光伏+商业航天|公司于2015年参与了东方红卫星“开拓一号”单晶硅太阳电池项目，具备成熟的卫星用光伏组件生产制造能力。</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>光伏, 商业航天</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>光伏</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>-4.01</v>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>特斯拉自建芯片工厂“Terafab”项目即将于近期启动。当地时间3月21日，马斯克在社交媒体透露，该项目目标是每年生产超过1太瓦的计算能力，其中约80%用于太空，约20%用于地面。</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>sz300345</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>华民股份</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>8.99</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>20.03</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>光伏+机器人|1.公司控股子公司鸿新新能源科技是一家其致力于成为光伏产业链上游单晶硅棒及单晶硅片材料环节专业化制造商。
-2.华民股份公告称，公司与广东天太机器人有限公司签署《投资意向协议》，将按照估值不超过11亿元，通过认缴新增注册资本额或受让老股的方式，以现金投资不超过1亿元，交易完成后预计持股比例为8%左右。</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>光伏, 机器人</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>单车</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>-1.26</v>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>3月23日晚24点，国内将迎来新一轮成品油调价窗口。电单车出行性价比凸显。</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>sh603529</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>爱玛科技</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>31.11</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>电单车|公司主营业务为电动自行车、电动轻便摩托车、电动摩托车的研发、生产及销售，此外，还有电动三轮车、自行车产品。</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>电单车</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>单车</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>-1.26</v>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>3月23日晚24点，国内将迎来新一轮成品油调价窗口。电单车出行性价比凸显。</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>sh603787</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>新日股份</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>14.82</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>电单车|公司是专业从事电动自行车、电动轻便摩托车、电动摩托车等电动两轮车研发、生产与销售的企业，主导产品为电动两轮车。</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>电单车</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>智能电网</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>-4.399999999999999</v>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>央视财经报道，2025年，我国变压器出口总值达646亿元，比2024年增长近36%。我国已成为世界第一大变压器生产国，在原材料、成本、生产周期等方面都具备明显优势。</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>sz002150</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>正泰电源</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>38.37</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>9天5板</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>储能+电网设备|1.旗下正泰电源是国内最早开始研发光伏逆变器的公司之一，业务范围涵盖光伏逆变器、光伏汇流箱、商用储能一体机、预装式光伏系统、预装式储能系统等。
-2.公司输配电控制设备业务主要产品包括高压成套开关设备、中低压成套开关设备、高低压开关元件及控制电器等，能够为下游各行业用户提供整体配电解决方案。</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>储能, 电网设备</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>智能电网</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>-4.399999999999999</v>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>央视财经报道，2025年，我国变压器出口总值达646亿元，比2024年增长近36%。我国已成为世界第一大变压器生产国，在原材料、成本、生产周期等方面都具备明显优势。</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>sh603016</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">新宏泰  </t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>38.58</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>电网设备|公司主营业务为断路器关键部件，低压断路器及刀熔开关的研发，生产与销售，公司实控人为无锡市人民政府国有资产监督管理委员会。</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>电网设备</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>-3.83</v>
-      </c>
-      <c r="C24" s="2" t="inlineStr"/>
-      <c r="D24" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>sz000908</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>*ST景峰</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>6.77</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>13天11板</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 公司专注医药健康产业，涉足药品研发、生产、销售等领域，产品涵盖了心脑血管、抗肿瘤、骨科、妇儿等用药领域。</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>-3.83</v>
-      </c>
-      <c r="C25" s="2" t="inlineStr"/>
-      <c r="D25" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>sh603843</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">*ST正平 </t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>8.52</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>9天8板</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 2025年2月21日公司官微披露，旗下正平智算参加海东市绿色算力产业集中签约暨推介活动并签订算电协同产业园框架协议。</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>-3.83</v>
-      </c>
-      <c r="C26" s="2" t="inlineStr"/>
-      <c r="D26" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>sz000638</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>*ST万方</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 公司业务主要包括军工产业、农业产业以及生物制品等业务。公司控股子公司万方迈捷以粮库收储为核心，深入研究粮食加工、研究土地流转、研究农民就业，万方迈捷作为乾安县唯一一家自主加工的大米企业。</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>-3.83</v>
-      </c>
-      <c r="C27" s="2" t="inlineStr"/>
-      <c r="D27" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>sh600355</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">*ST精伦 </t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 公司智能控制产品是公司全资子公司上海鲍麦克斯电子科技有限公司的主营产品，鲍麦克斯专业从事通用及专用伺服驱动系统、数控系统、 缝制机器人的系列化产品研发及销售。</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>-3.83</v>
-      </c>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>sh600696</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">*ST岩石 </t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>4.850000000000001</v>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 1.公司主要从事商业保理、融资租赁、不动产运营管理和大宗商品贸易。
-2.公司持有江西章贡酒业有限责任公司25%股权。章贡酒业是全国白酒工业百强企业，江西省重点酿酒企业。</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>-3.83</v>
-      </c>
-      <c r="C29" s="2" t="inlineStr"/>
-      <c r="D29" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>sh600608</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">*ST沪科 </t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 公司是一家信息技术行业公司，主要业务分为钢材制品加工制造及商品贸易业务两大板块。</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>-3.83</v>
-      </c>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>sh600107</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ST尔雅  </t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>5.59</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 公司的主营业务为服装、服饰和纺织品研发、设计、制造和销售。</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>-3.83</v>
-      </c>
-      <c r="C31" s="2" t="inlineStr"/>
-      <c r="D31" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>sz002620</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>ST瑞和</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 公司主要从事政府机构、房地产开发商、大型企业、高档酒店、交通枢纽、园林绿化等综合性专业化装饰设计、工程施工业务以及光伏电站运营、光伏项目施工安装等。</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>-3.83</v>
-      </c>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>sh600136</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ST明诚  </t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 影视业务系公司两大主营业务之一，包括影视娱乐内容制作、运营、发行等。</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>-3.83</v>
-      </c>
-      <c r="C33" s="2" t="inlineStr"/>
-      <c r="D33" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>sh603377</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ST东时  </t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 公司持有海若通航55%的股权，海若通航是一家具备CCAR-91部通航作业，CCAR-141部飞行培训，CCAR-145部航空器维修资质的通用航空运营商。</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr"/>
-      <c r="D34" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>sh603803</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>瑞斯康达</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>14.61</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>10天5板</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>光通信|在高端光模块领域，公司联营企业易锐光电是中国少数产业链上下游关键层面具备完整核心技术和解决方案的高科技企业，新一代基于自主知识产权的25G/100G/超100G集成光收发芯片的光通信模块及光组件，用于电信网络城域网和大型数据中心网络。</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>光通信</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr"/>
+          <t>光伏</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉自建芯片工厂“Terafab”项目即将于近期启动，该项目目标是每年生产超过1太瓦的计算能力，其中约80%用于太空，约20%用于地面。</t>
+        </is>
+      </c>
       <c r="D35" s="2" t="n">
         <v>6</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sh603687</t>
+          <t>sz002218</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">大胜达  </t>
+          <t>拓日新能</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>14.73</v>
+        <v>7.25</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>10.01</v>
+        <v>10.02</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4天4板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>并购重组+算力芯片|大胜达公告称，公司拟通过股权受让及增资方式合计投资5.5亿元取得芯瞳半导体技术（厦门）有限公司22.9831%的股权。其中，以2786万元受让2.7074%股权，以2214万元受让1.5961%股权，并以5亿元增资（分两次，第一次2.5亿元，第二次2.5亿元需满足流片成功条件）。同时，控股股东新胜达以5000万元同条件增资，取得1.9608%股权。芯瞳半导体成立于2019年，是国内专注于通用高性能图形处理器芯片设计研发与销售的先驱企业。</t>
+          <t>光伏+商业航天|公司于2015年参与了东方红卫星“开拓一号”单晶硅太阳电池项目，具备成熟的卫星用光伏组件生产制造能力。</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>并购重组, 算力芯片</t>
+          <t>光伏, 商业航天</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr"/>
+          <t>光伏</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉自建芯片工厂“Terafab”项目即将于近期启动，该项目目标是每年生产超过1太瓦的计算能力，其中约80%用于太空，约20%用于地面。</t>
+        </is>
+      </c>
       <c r="D36" s="2" t="n">
         <v>6</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sz002565</t>
+          <t>sh603759</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>顺灏股份</t>
+          <t>海天股份</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>16.98</v>
+        <v>10.13</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>9.969999999999999</v>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>5天3板</t>
-        </is>
-      </c>
+        <v>9.99</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>太空算力|公司2025年6月以1.1亿元人民币投资北京轨道辰光科技有限公司，持股比例为19.30%。轨道辰光的主要业务是通过将算力卫星发射至晨昏轨道，组建太空数据中心，为客户提供算力服务，其经营范围包括微小卫星生产制造、微小卫星科研试验、互联网信息服务等。轨道辰光首颗试验星算力规模预计25p。</t>
+          <t>与通威合作|海天股份公告称，公司于2026年3月23日与通威太阳能有限公司签署战略合作框架协议。双方将在光伏电池浆料领域开展深度合作，包括HJT、TOPCon、钙钛矿等新型浆料的研发与应用，并建立共同研发及知识产权共享机制。</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>太空算力</t>
+          <t>与通威合作</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr"/>
+          <t>光伏</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉自建芯片工厂“Terafab”项目即将于近期启动，该项目目标是每年生产超过1太瓦的计算能力，其中约80%用于太空，约20%用于地面。</t>
+        </is>
+      </c>
       <c r="D37" s="2" t="n">
         <v>6</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sz300385</t>
+          <t>sz002323</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>雪浪环境</t>
+          <t>雅博股份</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>15.61</v>
+        <v>2.62</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>19.98</v>
+        <v>10.08</v>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>重整|雪浪环境公告称，公司与上海氦星万联科技发展合伙企业(有限合伙)等四方及预重整引导人签署《重整投资协议》，并与上海氦星光曜科技发展合伙企业签署附属协议。根据协议，重整完成后氦星万联将成为公司控股股东。</t>
+          <t>光伏+锂电池|1.光伏业务占比约61%，以分布式光伏为主，业务涵盖BAPV(在现有建筑上安装的光伏系统)和BIPV(光伏建筑一体化)，宣城基地2.5GW HJT组件和105MW柔性BIPV产品已量产。
+2.参股精工电子专注于锂离子电池高端定制化应用领域，以出口为主，主要产品涵盖分布式储能系统、光伏储能、AGV、轻型动力产品等。</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>重整</t>
+          <t>光伏, 锂电池</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr"/>
+          <t>光伏</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉自建芯片工厂“Terafab”项目即将于近期启动，该项目目标是每年生产超过1太瓦的计算能力，其中约80%用于太空，约20%用于地面。</t>
+        </is>
+      </c>
       <c r="D38" s="2" t="n">
         <v>6</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>sh603727</t>
+          <t>sh600537</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">博迈科  </t>
+          <t>亿晶光电</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>19.75</v>
+        <v>3.65</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>10.03</v>
+        <v>9.94</v>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>油气|公司主要产品大类分为海洋油气开发模块、矿业开采模块、天然气液化模块等，产品具体涉及十多种子类别。公司为海洋油气开发、矿业开采和天然气液化领域中的国内外高端客户提供能源资源设施开发的专业分包服务。</t>
+          <t>光伏|公司主要业务包括晶棒/硅锭生长、硅片加工、电池制造、组件封装、光伏发电，晶棒/硅锭生长、硅片加工、电池制造业务主要是为公司自身的太阳能电池组件生产配套，公司致力于销售产业链下游的最终产品太阳能电池组件。</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>油气</t>
+          <t>光伏</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr"/>
+          <t>光伏</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉自建芯片工厂“Terafab”项目即将于近期启动，该项目目标是每年生产超过1太瓦的计算能力，其中约80%用于太空，约20%用于地面。</t>
+        </is>
+      </c>
       <c r="D39" s="2" t="n">
         <v>6</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>sz300868</t>
+          <t>sh605366</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>杰美特</t>
+          <t>宏柏新材</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>46.33</v>
+        <v>10.19</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>19.99</v>
+        <v>10.04</v>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>并购重组|杰美特公告称，公司拟以现金方式购买深圳戴尔蒙德科技有限公司21.5%股权，交易价格为1.29亿元，资金来源为公司自有资金及自筹资金。公司拟通过本次交易拓宽公司产业布局，形成新的业绩增长点。</t>
+          <t>光伏+有机硅|1.目前公司现有年产10万吨工业级三氯氢硅，可对外出售光伏级三氯氢硅产品。
+2.公司主营业务为功能性硅烷、纳米硅材料等硅基新材料及其他化学助剂的研发、生产与销售。</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>并购重组</t>
+          <t>光伏, 有机硅</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>光通信</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>在上周举行的2026年光纤通信大会暨展览会上，各光通信厂商均强调光模块核心器件及材料的扩产计划。</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>sz002428</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>云南锗业</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>44.66</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>磷化铟|云南锗业发布投资者关系活动记录表公告，公司磷化铟晶片现有产能15万片/年(2-4英寸)，受光通信市场需求增加及原材料价格上涨影响，近期产品价格有所上涨。公司已批量向下游外延厂商或具备外延能力的器件厂商供货。公司光纤级锗产品为光纤用四氯化锗，目前产能为60吨/年。公司光纤级锗产品已批量稳定生产多年，客户涵盖国内下游知名光纤生产厂商。</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>磷化铟</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>光通信</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>在上周举行的2026年光纤通信大会暨展览会上，各光通信厂商均强调光模块核心器件及材料的扩产计划。</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>sz002491</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>通鼎互联</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>光纤光缆|公司光电通信业务板块的产品和解决方案主要涵盖光电线缆和光通信设备两大领域，光电线缆领域的具体产品包括光纤预制棒、光纤、光缆、通信电缆、铁路信号缆、电力电缆等。</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>光纤光缆</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>光通信</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>在上周举行的2026年光纤通信大会暨展览会上，各光通信厂商均强调光模块核心器件及材料的扩产计划。</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>sz002222</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>福晶科技</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>64.79000000000001</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>光通信+光刻机|1.公司部分精密光学元件产品应用于光通讯领域。
+2.公司曾通过欧洲代理向ASML提供及其少量光学元件。此外，华为是公司的客户，公司在业务范围内向其提供光学元件产品。</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>光通信, 光刻机</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>光通信</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>在上周举行的2026年光纤通信大会暨展览会上，各光通信厂商均强调光模块核心器件及材料的扩产计划。</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>sh601869</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>长飞光纤</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>233.31</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>光纤光缆|公司系全球光纤光缆行业的领先企业，是国内最早的光纤光缆生产厂商之一，聚焦电信运营商和数据通信相关领域，致力于光纤预制棒、光纤和光缆以及数据通信相关产品的研发创新与生产制造，形成了棒纤缆、综合布线和光模块一体化的完整产业链、相关多元化和国际化的业务模式。</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>光纤光缆</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>光通信</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>在上周举行的2026年光纤通信大会暨展览会上，各光通信厂商均强调光模块核心器件及材料的扩产计划。</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>sh600184</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>光电股份</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>15.86</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>光通信+军工|1.子公司新华光自主研发的光通信核心材料GP，突破了批量生产工艺，已经送样给光通信领域多家企业测试使用。
+2.公司控股股东是中国兵器工业集团旗下北方光电集团，公司专注于防务和光电材料与器件两大业务板块。</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>光通信, 军工</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>军工</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>十五五规划为我国国防和军队现代化的高质量推进做出了总部署，新域新质作战力量建设将加快先进武器装备的更新换代，军工装备迎来新的发展时期。</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>sz000677</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>恒天海龙</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>军工+低空经济|1.公司生产的芳纶布可由下游客户用于生产防弹头盔，防弹头盔属于军工产品。
+2.恒天海龙公告称，公司拟通过全资子公司海龙飞控以现金方式收购群健航空不少于40%股权，交易完成后海龙飞控将成为目标公司控股股东。该协议为初步意向协议，目前尚未签署正式《股权收购协议》，相关事项存在不确定性。</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>军工, 低空经济</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>军工</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>十五五规划为我国国防和军队现代化的高质量推进做出了总部署，新域新质作战力量建设将加快先进武器装备的更新换代，军工装备迎来新的发展时期。</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>sh601606</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>长城军工</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>39.34</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>军工|公司为控股型公司，主营业务均通过子公司开展，以军品业务为主，下属四家军品子公司神剑科技、方圆机电、东风机电、红星机电均属重点军工企业，并在其对应领域占据重要地位，主要从事迫击炮弹系列、光电对抗系列、单兵火箭系列、引信系列、子弹药系列、火工品系列等产品的研发、生产和销售。</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>军工</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>军工</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>十五五规划为我国国防和军队现代化的高质量推进做出了总部署，新域新质作战力量建设将加快先进武器装备的更新换代，军工装备迎来新的发展时期。</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>sh600698</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>湖南天雁</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>军工|公司控股股东是中国兵器装备集团旗下中国长安汽车集团，公司是国内最早生产车用涡轮增压器的企业。</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>军工</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>军工</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>十五五规划为我国国防和军队现代化的高质量推进做出了总部署，新域新质作战力量建设将加快先进武器装备的更新换代，军工装备迎来新的发展时期。</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>sz002265</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>建设工业</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>22.19</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>军工+机器人|公司在第十五届中国国际航空航天博览会轻武器展区展出的多功能足式机器人、小型室内清剿机器人、小型智能察打机器人、便携式无人飞行枪械系统、班组多旋翼察打无人机等。</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>军工, 机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>军工</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>十五五规划为我国国防和军队现代化的高质量推进做出了总部署，新域新质作战力量建设将加快先进武器装备的更新换代，军工装备迎来新的发展时期。</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>sz002519</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>银河电子</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>军工+商业航天|1.公司军品智能机电业务由同智机电开展运营，主要业务是为满足我国国防建设需要，为不同行业的特定客户提供特种车辆的智能供配电管理系统、智能电源管理系统、环境控制系统、健康管理系统等。
+2.参股格思航天作为卫星ODM厂商承接量产卫星设计制造与卫星核心组部件研发业务，拥有完善的卫星设计与制造条件保障资源。</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>军工, 商业航天</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>纺织服装</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>机构指出，伴随美国关税政策的明朗化，下游海外客户逐渐转为积极，板块业绩有望较2025年有所回暖。</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>sh600137</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>浪莎股份</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>21.69</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>纺织|致力于专业研发、生产和经营各种保暖内衣、时尚内衣、短裤、文胸等针织服装,以及外贸服装的贴牌加工。</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>纺织</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>纺织服装</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>机构指出，伴随美国关税政策的明朗化，下游海外客户逐渐转为积极，板块业绩有望较2025年有所回暖。</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>sh600527</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>江南高纤</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>化纤|国内涤纶毛条和复合纤维的龙头公司。公司产品主要包括涤纶毛条和复合短纤维。下游主要供给纸尿裤、卫生巾等一次性卫生材料。</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>化纤</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>纺织服装</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>机构指出，伴随美国关税政策的明朗化，下游海外客户逐渐转为积极，板块业绩有望较2025年有所回暖。</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>sh603808</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">歌力思  </t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>纺织|国内高端女装行业的佼佼者。拥有品牌歌力思，新品牌Laurel、EdHardy、IRO、VT等。</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>纺织</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>纺织服装</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>机构指出，伴随美国关税政策的明朗化，下游海外客户逐渐转为积极，板块业绩有望较2025年有所回暖。</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>sh600510</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黑牡丹  </t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>房地产+纺织|黑牡丹(集团)股份有限公司始建于1940年，2002年于上交所上市，是一家业务涵盖新基建、新型城镇化建设和纺织服装三大板块的国有控股上市公司。</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>房地产, 纺织</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>兴业证券指出，国内头部科技企业持续加大资本开支、加快本土大模型迭代，国产算力厂商及上游半导体设备材料等方向仍具备广阔成长空间。</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>sh603929</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>亚翔集成</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>191.18</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>洁净室+业绩|1.公司作为一站式洁净室系统集成工程服务的专业提供商，主营业务为IC半导体、光电等高科技电子产业及生物医药、云计算中心等相关领域的建厂工程提供洁净室工程服务。
+2.亚翔集成发布2025年年度报告，公司实现营业收入49.07亿元，同比下降8.81%；归属于上市公司股东的净利润为8.92亿元，同比增长40.30%。公司拟向全体股东每10股派发现金红利16.50元（含税），分红总额为3.52亿元。</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>洁净室, 业绩</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>兴业证券指出，国内头部科技企业持续加大资本开支、加快本土大模型迭代，国产算力厂商及上游半导体设备材料等方向仍具备广阔成长空间。</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>sz301226</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>祥明智能</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>42.96</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>储能+洁净室|1.公司风机组件类产品可以应用到储能行业。离心风机、轴流风机可用于储能设备来调节温度。
+2.公司的洁净与净化类产品在国内外工业洁净厂房装备中得到了广泛的应用，具体项目包括韩国三星半导体、韩国LG显示器、英特尔芯片（大连、成都）、京东方科技、长沙蓝思科技、重庆富士康等。目前，公司洁净室工程主要客户集中于电子行业，其中芯片和光电产业是公司服务的主要领域。</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>储能, 洁净室</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>兴业证券指出，国内头部科技企业持续加大资本开支、加快本土大模型迭代，国产算力厂商及上游半导体设备材料等方向仍具备广阔成长空间。</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>sz002685</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>华东重机</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>9.950000000000001</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>算力芯片+工业母机|1.子公司厦门锐信图芯的GPU已经与国内主流CPU、操作系统等生态厂商完成适配，在国产化台式机、一体机、笔记本和平板电脑当中批量应用，产品已切入到党政办公、交通、教育、税务、电力和轨道交通等行业。
+2.全资子公司润星科技是专业从事高端智能装备的研发、制造、销售和服务的高新技术企业，主要产品包括中高档数控机床、工业机器人、以及自动化交钥匙工程等。</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>算力芯片, 工业母机</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>兴业证券指出，国内头部科技企业持续加大资本开支、加快本土大模型迭代，国产算力厂商及上游半导体设备材料等方向仍具备广阔成长空间。</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>sh600076</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>康欣新材</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>半导体设备|2026年1月20日公告，公司拟通过受让股权加增资的方式，使用现金3.92亿元取得无锡宇邦半导体科技51%股权。标的公司是深耕集成电路制造领域的修复设备供应商，通过精准修复实现设备的价值再生，并辅以零部件及耗材供应与技术支持，为客户提供一体化的服务方案。</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>半导体设备</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>氢能</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>华泰证券指出，3月16日工信部、财政部、发改委联合发布《关于开展氢能综合应用试点工作的通知》，2026年或成为绿氢产业拐点之年。</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>sh601226</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>华电科工</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>氢能+光伏|1.2020年，公司成立了氢能事业部，以可再生能源高效利用、二氧化碳减排利用、工业尾气综合利用为方向，致力于为客户提供制售氢、装备制造、工程总包等一体化服务。公司控股子公司通用氢能主要从事质子交换膜燃料电池关键材料的开发与生产，拥有氢能燃料电池核心材料产品气体扩散层、质子交换膜及催化剂的生产配方、生产工艺、核心技术。
+2.2023年8月8日公告，董事会同意公司为抢抓内蒙古区域新能源建设市场发展机遇，保障区域内在手新能源项目顺利执行，促进光伏业务快速发展，在巴彦淖尔市磴口县出资设立全资子公司华电(巴彦淖尔)新能源装备有限公司，开展光伏支架的生产、加工和销售业务，注册资本为5000万元。</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>氢能, 光伏</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>氢能</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>华泰证券指出，3月16日工信部、财政部、发改委联合发布《关于开展氢能综合应用试点工作的通知》，2026年或成为绿氢产业拐点之年。</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>sh600475</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>华光环能</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>18.76</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>光伏+氢能|1.子公司中设国联拥有光伏开发运营能力，能够提供专业的光伏发电服务和系统解决方案，截至2024年年报，开发运营有325MW光伏项目，区域覆盖江苏、安徽、山东、浙江、江西、广东等多省市地区。
+2.2022年，公司与大连理工大学合作成立零碳工程技术研究中心，进行电解水制氢、碳捕捉技术等示范项目的开发。公司已经形成了年产1GW电解水制氢设备制造能力，具备2000Nm3/h以下多系列碱性电解水制氢系统技术。</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>光伏, 氢能</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>氢能</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>华泰证券指出，3月16日工信部、财政部、发改委联合发布《关于开展氢能综合应用试点工作的通知》，2026年或成为绿氢产业拐点之年。</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>sz000811</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>冰轮环境</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>18.11</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>液冷+氢能|1.公司可以为液冷业务提供冷源装备和换热装置，公司风冷螺杆机组和变频离心式冷水机组入选工信部《绿色数据中心先进适用技术产品目录》。
+2.公司战略定位是专业装备商，聚焦全流程压缩机，如充装压缩机、加氢压缩机、液化压缩机、氢燃料电池车空气压缩机、氢气循环泵等。</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>液冷, 氢能</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>算力工程</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>国家数据局表示，2024年初，中国日均Token(词元)调用量为1000亿；至2025年底，跃升至100万亿；今年3月，已突破140万亿，两年增长超千倍。</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>sh600666</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奥瑞德  </t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>5天3板</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>算力租赁|公司设立全资子公司北京智算力、深圳智算力，使用自有资金投资建设算力租赁一、二、三期项目。</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>算力租赁</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>算力工程</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>国家数据局表示，2024年初，中国日均Token(词元)调用量为1000亿；至2025年底，跃升至100万亿；今年3月，已突破140万亿，两年增长超千倍。</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>sh600186</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>莲花控股</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>味精+算力租赁|1.拥有全国性营销网络的味精企业，主要业务为生产销售味精、鸡精、面粉、谷朊粉等。
+2.2023年9月，新华三集团与公司举行战略合作签约仪式，携手莲花健康共建国内领先、国际一流的智能算力中心，满足通用大模型、自动驾驶、机器人、元宇宙、游戏、传媒等应用行业在内的算力需求。</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>味精, 算力租赁</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>算力工程</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>国家数据局表示，2024年初，中国日均Token(词元)调用量为1000亿；至2025年底，跃升至100万亿；今年3月，已突破140万亿，两年增长超千倍。</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>sz002771</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>真视通</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>AI+算力租赁| 1.公司主要面向能源、政府、金融、交通、教育、医疗等行业的大中型用户，提供多媒体视讯系统建设服务，公司的多媒体视讯系统业务主要分为多媒体信息系统。
+2.公司协议购买的GPU为英伟达H800芯片的服务器，合同金额2.91亿，1000张H800芯片算力约在2000p左右，本次采购基本都是为算力租赁准备的。</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>AI, 算力租赁</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>航运</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>中信证券认为，地缘冲突带来的供应链重构，成为本轮油运周期的核心驱动地缘因素主导背景下，伊朗事件等地缘事件强化油运行业周期动能，2026年油运龙头利润有望创新高。</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>sh601975</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>招商南油</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>油运|公司是招商局集团旗下从事油轮运输的专业化公司，市场定位为全球石化产品的运输服务商。</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>油运</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>航运</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>中信证券认为，地缘冲突带来的供应链重构，成为本轮油运周期的核心驱动地缘因素主导背景下，伊朗事件等地缘事件强化油运行业周期动能，2026年油运龙头利润有望创新高。</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>sh600026</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>中远海能</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>25.87</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>油运|公司主营业务为从事国际和中国沿海原油及成品油运输、国际液化天然气(LNG)运输以及国际化学品运输，是中国沿海原油和成品油运输领域的龙头企业。</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>油运</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>体育产业</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>2026年美加墨世界杯将于‌当地时间2026年6月11日‌正式开幕。</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>sh605299</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>舒华体育</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>16.13</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>健身器材|公司主营业务为健身器材和展示架产品的研发、生产和销售，其中健身器材包括室内健身器材、室外路径产品。</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>健身器材</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>体育产业</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>2026年美加墨世界杯将于‌当地时间2026年6月11日‌正式开幕。</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>sz002887</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>绿茵生态</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>草坪|公司承包过足球草坪业务，有能力为运动场提供草坪。</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>草坪</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>节能环保</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>4.399999999999999</v>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>3月20日，工业和信息化部、国家发展改革委、国务院国资委、国家能源局等四部门联合印发《节能装备高质量发展实施方案(2026—2028年)》。</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>sz000035</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>中国天楹</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>环保+氢能|1.公司以垃圾焚烧发电、城乡环境卫生服务与环保装备制造为压舱石，打通了从前端清扫、中转分选、末端处置的城乡环境卫生服务全产业链。
+2.公司依托吉林辽源和黑龙江安达等风光储氢氨醇一体化项目投资建设，打造涵盖绿色甲醇、绿氨、SAF 等多元化氢基能源产品生产线，形成规模化的绿色燃料供应能力。
+2026年2月26日公司在投资者关系活动记录表中透露，公司目前已与国际头部能源巨头签订了全球首单电制甲醇供货订单，标志着公司绿色甲醇产品正式进入国际主流能源企业供应体系。</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>环保, 氢能</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>节能环保</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>4.399999999999999</v>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>3月20日，工业和信息化部、国家发展改革委、国务院国资委、国家能源局等四部门联合印发《节能装备高质量发展实施方案(2026—2028年)》。</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>sz002663</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>普邦股份</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>环保+基建|公司的园林景观业务包括住宅景观、度假景观以及市政景观业务。子公司深蓝环保是国内污水处理、一般工业固废处理处置等领域最具综合实力的环保企业之一。</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>环保, 基建</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>新型城镇化</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>大同证券指出，109项重大工程落地提速，发债方面，2026年专项债发行前置，叠加超长期特别国债等工具持续发力，为能源工程、重大基建等项目提供坚实资金支撑。</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>sh603017</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>中衡设计</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>基建+商业航天|1.公司主要从事建筑专业领域的工程设计、工程总承包、工程监理及项目管理业务。
+2.公司中标了天兵科技运载火箭及发动机智能制造 基地、山东箭元航天科技总装总测生产基地、星际荣耀火箭制造基地、安庆年发20发可回收液体火箭制造厂房建设项目等多个高端制造基地。</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>基建, 商业航天</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>新型城镇化</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>大同证券指出，109项重大工程落地提速，发债方面，2026年专项债发行前置，叠加超长期特别国债等工具持续发力，为能源工程、重大基建等项目提供坚实资金支撑。</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>sh600234</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>科新发展</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>建筑装修|公司主营业务为以广告传媒业务、建筑装修装饰工程业务为主，同时以自有资产开展写字楼出租业务。主要产品有物业出租、营销策划、建筑装饰工程。</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>建筑装修</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>AI应用</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>据全球大模型聚合路由平台OpenRouter3月23日数据显示，上周（3.16-3.22）全球模型调用量排名榜中，国产大模型调用量连续三周超过美国模型。</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>sh601858</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>中国科传</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>24.27</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>AI+数据要素|1.公司自主研发的SciEngine全流程数字出版与知识服务平台（V3.0）进一步集成了学术查重检测、审稿专家自动推荐、自动在线校对、科大讯飞智能翻译、AI秒读视频、文献挖掘和语义检索等多种工具，进一步提升了出版运营与知识服务能力。
+2.公司围绕专业学科知识库、数字教育云服务、医疗健康大数据、期刊融合平台等方向，先后推出了“科学文库”“科学智库”“中国生物志库”“中国古生物地层知识库”“中科云教育平台”“状元共享课堂”“中科医库”“SciEngine全流程数字出版与知识服务平台”等多个数字化产品和知识服务平台。</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>AI, 数据要素</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>AI应用</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>据全球大模型聚合路由平台OpenRouter3月23日数据显示，上周（3.16-3.22）全球模型调用量排名榜中，国产大模型调用量连续三周超过美国模型。</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>sz002082</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>万邦德</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>19.79</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI+创新药|在研发端，公司探索人工智能在创新药设计、筛选、实验设计等环节的应用，目前全球首个治疗胃轻瘫的中药1.1类新药“理中消痞颗粒”正在开展临床研究。 </t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>AI, 创新药</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>CRO/CMO</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>4.760000000000001</v>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>诺和诺德司美格鲁肽在中国的核心化合物专利到期。这意味着，这款被称为“全球药王”的单品，长期垄断格局就此打破。</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>sh603538</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">美诺华  </t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>29.44</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>CDMO|公司正在加速打造CDMO一站式综合服务平台，为制药企业提供贯穿药品临床前研发、临床试验阶段以及上市审批、商业化生产等环节的综合性研发生产服务，包括为其提供医药特别是创新药的工艺研发及制备、工艺优化、放大生产、注册和验证批生产以及商业化生产等定制研发生产服务。</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>CDMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>机构指出，随着LPU/LPX机柜在2026年底至2027年进入量产高峰期，对高阶PCB的需求将呈现井喷态势。</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>sz002636</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>金安国纪</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>30.99</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>PCB+玻纤布|公司主要产品包括各种通用FR-5、FR-4、CEM-3等系列覆铜板及铝基覆铜板、半固化片等和特殊指标要求的无卤环保、高阻燃、耐CAF、高TG、高CTI等系列覆铜板；此外，公司还从事覆铜板的原材料电子级玻纤布以及下游PCB产品的生产和销售。</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>PCB, 玻纤布</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>中信证券指出，2026年是全球机器人产业的量产元年，行业正式从“技术愿景”全面转向“产业实景”，进入规模化交付与商业化落地的关键拐点。</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>sh605056</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>咸亨国际</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>储能+机器人|1.公司下属子公司杭州贝特设备制造有限公司的BL5000/8000便携式UPS电源，BL2000/BL3000应急电源系列，BL300/500/1000/1500应急电源系列，可负载保电、应急抢修、户外施工、家庭应急灯无电场合。
+2.公司2021年8月24日在互动平台表示，公司有智能巡检无人机和消防灭火机器人，公司从事电网智能巡检无人机已经有近八年时间，可以提供技术服务、飞手培训及其完整的智能巡检无人机解决方案。</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>储能, 机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>稀土永磁</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>中信证券表示，2026年起全球稀土供需缺口有望持续扩大，对稀土价格形成长期支撑，带动产业链公司盈利能力持续提升。</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>sz002645</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>华宏科技</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>稀土永磁+机器人|1.公司旗下全资子公司鑫泰科技主营业务为稀土废料的综合利用，即通过钕铁硼废料、荧光粉废料生产高纯稀土氧化物，其全资子公司中杭新材从事稀土永磁材料生产业务。
+2.公司生产的高性能磁材产品已经应用于新能源汽车电机、工业机器人电机、3C电子等高科技领域。</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>稀土永磁, 机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C78" s="2" t="inlineStr"/>
+      <c r="D78" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>sh603843</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*ST正平 </t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>5.050000000000001</v>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>10天9板</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 2025年2月21日公司官微披露，旗下正平智算参加海东市绿色算力产业集中签约暨推介活动并签订算电协同产业园框架协议。</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C79" s="2" t="inlineStr"/>
+      <c r="D79" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>sz000638</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>*ST万方</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司业务主要包括军工产业、农业产业以及生物制品等业务。公司控股子公司万方迈捷以粮库收储为核心，深入研究粮食加工、研究土地流转、研究农民就业，万方迈捷作为乾安县唯一一家自主加工的大米企业。</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C80" s="2" t="inlineStr"/>
+      <c r="D80" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>sh600355</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*ST精伦 </t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司智能控制产品是公司全资子公司上海鲍麦克斯电子科技有限公司的主营产品，鲍麦克斯专业从事通用及专用伺服驱动系统、数控系统、 缝制机器人的系列化产品研发及销售。</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C81" s="2" t="inlineStr"/>
+      <c r="D81" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>sh600608</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*ST沪科 </t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司是一家信息技术行业公司，主要业务分为钢材制品加工制造及商品贸易业务两大板块。</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C82" s="2" t="inlineStr"/>
+      <c r="D82" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>sh603398</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*ST沐邦 </t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>11.41</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>6天3板</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 1.沐邦高科公告，与铜陵狮子山高新技术产业开发区管理委员会、铜陵高新发展投资有限公司签订《项目投资协议书》，项目名称为年产10GW-N型高效电池片、10GW切片生产基地项目。
+2.公司上市的IP产品 “樱桃小丸子”第一期为“盲盒”类产品。</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C83" s="2" t="inlineStr"/>
+      <c r="D83" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>sz002620</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>ST瑞和</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>5.029999999999999</v>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司主要从事政府机构、房地产开发商、大型企业、高档酒店、交通枢纽、园林绿化等综合性专业化装饰设计、工程施工业务以及光伏电站运营、光伏项目施工安装等。</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C84" s="2" t="inlineStr"/>
+      <c r="D84" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>sh600107</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST尔雅  </t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司的主营业务为服装、服饰和纺织品研发、设计、制造和销售。</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C85" s="2" t="inlineStr"/>
+      <c r="D85" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>sz002528</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>ST英飞拓</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 英飞拓推出5G多功能智慧灯杆，支持节能照明、视频监控、新能源充电、公共WIFI、环境监测、信息发布、应急报警、5G微基站等模块，实现多种类型的感知数据采集、分析、仿真预测，提升城市综合治理。</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C86" s="2" t="inlineStr"/>
+      <c r="D86" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>sz002789</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>*ST建艺</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司是集施工、设计、资源矿产、科技工业园、高新技术建材产业、投融资为一体的规模化实体企业集团。</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C87" s="2" t="inlineStr"/>
+      <c r="D87" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>sz002211</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>ST宏达</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>5.140000000000001</v>
+      </c>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 1.公司主营业务主要分为硅橡胶及其制品的加工销售、专网通信设备的加工、组装、检测及销售业务等。
+2.公司目前于量子领域在产的产品有量子随机数发生器，其可基于量子物理原理产生随机数，可应用于量子通信、量子信息、传统信息安全、密码学、蒙特卡洛模拟、数值计算、随机抽样、神经网络计算等。</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C88" s="2" t="inlineStr"/>
+      <c r="D88" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>sz002005</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>ST德豪</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 小家电及LED双主营业务。是国内拥有包括LED芯片、LED封装、LED应用产品(照明和显示)、照明品牌及渠道在内的LED全产业链布局的极少数企业之一。</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C89" s="2" t="inlineStr"/>
+      <c r="D89" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>sz002512</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>ST达华</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 1.在量子安全通信领域，公司已经形成了量子安全卫星互联网通信的全套解决方案，已进行试点应用。
+2.公司子公司海丝卫星是专业提供卫星互联网服务的运营商，通过直接为终端客户提供一站式全场景卫星宽带接入及行业垂直应用服务，解决海洋通信、应急通信及偏远山区等场景网络覆盖问题。</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C90" s="2" t="inlineStr"/>
+      <c r="D90" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>sz000608</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>*ST阳光</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司投资性房地产主要位于京沪蓉。业态上主要为集中商业和办公。</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C91" s="2" t="inlineStr"/>
+      <c r="D91" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>sz002199</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>*ST东晶</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>5.029999999999999</v>
+      </c>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司致力于高精度、高稳定性、高品质石英晶体元器件系列产品的研发、设计与生产。公司与日本松下、索尼、东芝、夏普、 JVC，以及韩国三星、LG 和国内华为、中兴、 OPPO、小米等公司保持长期稳定的战略合作关系。</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C92" s="2" t="inlineStr"/>
+      <c r="D92" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>sz002289</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>*ST宇顺</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>26.13</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司主营业务为液晶显示屏及模组、触摸屏及模组、触摸显示一体化模组等产品的研发、生产和销售。</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C93" s="2" t="inlineStr"/>
+      <c r="D93" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>sz003004</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>*ST声迅</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 1.公司现有AIOT平台已经实现以图搜人、视频结构化、人员轨迹、客流密度、区域入侵、人数统计、风险预警等30余项功能，音视频智能分析应用达到100万路以上，积累海量数据。
+2.公司已经推出了声迅无人机探测与反制系统，该系统集态势感知、信息呈现、决策辅助、指挥管理于一体，可以对无人机的侦测、识别、测向、防御管控。</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C94" s="2" t="inlineStr"/>
+      <c r="D94" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>sz000668</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>*ST荣控</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>13.34</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司主营业务为房地产开发，经营模式以自主开发销售为主，曾推出国内第一个小户型楼盘，第一家运动主题社区，在业内产生较大影响。</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr"/>
+      <c r="D95" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>sz300385</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>雪浪环境</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>18.73</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>重整|雪浪环境公告称，公司与上海氦星万联科技发展合伙企业(有限合伙)等四方及预重整引导人签署《重整投资协议》，并与上海氦星光曜科技发展合伙企业签署附属协议。根据协议，重整完成后氦星万联将成为公司控股股东。</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>重整</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr"/>
+      <c r="D96" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>sz000509</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>华塑控股</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>MLED|公司积极布局了MiniLED、OLED和高分高刷高色域等显示领域前沿产品技术。</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>MLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr"/>
+      <c r="D97" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>sh600539</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>狮头股份</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>机器视觉|2025年3月7日公告，公司拟以发行股份及支付现金方式向王旭龙琦等14名交易对方收购杭州利珀科技100%股权，同时向上市公司实控人旗下企业募集配套资金。本次交易预计构成重大资产重组。标的公司自成立以来一直致力于机器视觉相关技术产品的研发、生产与销售。</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>机器视觉</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr"/>
+      <c r="D98" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>sz002795</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>永和智控</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>医疗器械|子公司成都永和成医疗科技有限公司主营业务为医疗器械研发、租赁及销售。</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>医疗器械</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr"/>
+      <c r="D99" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>sh603115</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>海星股份</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>35.21</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>MLPC电容器|公司主营产品电极箔可应用于MLPC电容器。MLPC产品可广泛应用于服务器中高功耗芯片的供电滤波场景，特别是CPU和GPU的核心电压供电。</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>MLPC电容器</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr"/>
+      <c r="D100" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>sz000415</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>渤海租赁</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>租赁|公司是首家于中国A股上市的租赁产业集团。公司主营业务涵盖飞机租赁、集装箱租赁、境内融资租赁等。</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>租赁</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr"/>
+      <c r="D101" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>sh603922</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金鸿顺  </t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>汽车|公司主营业务为汽车车身和底盘冲压零部件及其相关模具的开发，生产与销售。公司既是上汽大众，上汽通用，上海汽车，广汽菲克，东南汽车及东风裕隆等国内知名整车制造商的一级供应商，也向本特勒，博世，大陆汽车和卡斯马等著名跨国汽车零部件供应商提供配套。</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>汽车</t>
         </is>
       </c>
     </row>
@@ -2246,7 +5041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2273,7 +5068,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -2288,31 +5083,31 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sh603687</t>
+          <t>sz002309</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">大胜达  </t>
+          <t>中利集团</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sz002310</t>
+          <t>sh600758</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>东方新能</t>
+          <t>辽宁能源</t>
         </is>
       </c>
     </row>
@@ -2322,12 +5117,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sz002150</t>
+          <t>sz002218</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>正泰电源</t>
+          <t>拓日新能</t>
         </is>
       </c>
     </row>
@@ -2337,12 +5132,27 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sz002309</t>
+          <t>sz300385</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>中利集团</t>
+          <t>雪浪环境</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>sh600032</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>浙江新能</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,19 +476,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K94"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="99" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="103" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="204" customWidth="1" min="10" max="10"/>
+    <col width="291" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -552,134 +552,133 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2.44</v>
+        <v>0.98</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>广期所碳酸锂主力合约涨超6%，逼近17万元/吨关口。</t>
+          <t>据国家药监局消息，今年前三个月，我国创新药对外授权交易总额超过600亿美元，接近2025年全年的一半。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>sz002192</t>
+          <t>sh603538</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>融捷股份</t>
+          <t xml:space="preserve">美诺华  </t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>78</v>
+        <v>43.1</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>4天4板</t>
+          <t>7天6板</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>负极材料+锂矿|1.融捷股份公告称，公司第九届董事会第三次会议审议通过多项议案，其中包括全资子公司兰州融捷材料科技有限公司拟投资约11亿元建设年产5万吨高性能锂离子电池负极材料项目。
-2.公司拥有康定市甲基卡锂辉石矿134号脉的采矿权，矿山储量2899.5万吨，具有105万吨/年露天开采能力及45万吨/年矿石处理的选矿能力。</t>
+          <t>减肥药|2026年3月19日公司在官微公布益生菌（JH389）胶囊产品临床数据，结果显示，服用该产品8周可显著改善受试者体重、体脂及肥胖相关指标，有助于全面提升生活质量、有助于正向调节肠道菌群结构，同时对糖脂代谢及各项安全性指标无不良影响。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>负极材料, 锂矿</t>
+          <t>减肥药</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2.44</v>
+        <v>0.98</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>广期所碳酸锂主力合约涨超6%，逼近17万元/吨关口。</t>
+          <t>据国家药监局消息，今年前三个月，我国创新药对外授权交易总额超过600亿美元，接近2025年全年的一半。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sh603026</t>
+          <t>sz002038</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>石大胜华</t>
+          <t>双鹭药业</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>93.84999999999999</v>
+        <v>7.27</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>6天3板</t>
+          <t>4天3板</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>电解液|公司是能够同时提供锂离子电池电解液及电解液溶剂、溶质、添加剂产品的全产业链公司，具备五大碳酸酯溶剂、六氟磷酸锂及部分添加剂的生产能力，形成锂电池溶剂、电解液、高端新材料三大业务版块。</t>
+          <t>创新药|公司目前具有较强竞争力的储备品种有包括即将上市的G-CSF长效制剂、人促卵泡激素长、短效制剂，GLP-1类似物长、短效和双靶点制剂，心脑血管领域开发的创新药和特色仿制药等。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>电解液</t>
+          <t>创新药</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2.44</v>
+        <v>0.98</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>广期所碳酸锂主力合约涨超6%，逼近17万元/吨关口。</t>
+          <t>据国家药监局消息，今年前三个月，我国创新药对外授权交易总额超过600亿美元，接近2025年全年的一半。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sz002263</t>
+          <t>sh600488</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>大东南</t>
+          <t>津药药业</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>4.07</v>
+        <v>4.76</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>10</v>
+        <v>9.93</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
@@ -688,1479 +687,1508 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>隔膜+复合铜箔|1.公司产品覆盖传统包装薄膜、锂电池隔膜、耐高温超薄电容膜、光学膜。
-2.公司复合铜箔用电容薄膜的研发已经完成，此项目使公司生产更超薄产品成为可能，且技术指标均达到或超过国家标准。</t>
+          <t>原料药|公司主要从事皮质激素类、氨基酸类原料药及制剂的研发、生产和销售，产品包括地塞米松系列、泼尼松系列、甲泼尼龙系列、倍他米松系列等40余个皮质激素原料药品种，23个氨基酸原料药品种，以及16个剂型药品。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>隔膜, 复合铜箔</t>
+          <t>原料药</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2.44</v>
+        <v>0.98</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>广期所碳酸锂主力合约涨超6%，逼近17万元/吨关口。</t>
+          <t>据国家药监局消息，今年前三个月，我国创新药对外授权交易总额超过600亿美元，接近2025年全年的一半。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sz000695</t>
+          <t>sh600513</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>滨海能源</t>
+          <t>联环药业</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>14.29</v>
+        <v>28.17</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>锂电池+储能|1.公司全面聚焦锂电负极材料业务，自建及协同控股股东石墨化产能已形成一定规模优势，于2023年7月底实现4万吨后端成品线投料试生产，并于11月底实现1.8万吨自有石墨化产品线投产调试。
-2.公司生产的负极材料可广泛应用于储能项目。</t>
+          <t>创新药|主要产品有创新药物爱普列特片(川流)，新药依巴斯汀片(苏迪)、非洛地平片(联环尔定)、非洛地平缓释胶囊(联环笑定)等二十多个。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>锂电池, 储能</t>
+          <t>创新药</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>2.44</v>
+        <v>0.98</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>广期所碳酸锂主力合约涨超6%，逼近17万元/吨关口。</t>
+          <t>据国家药监局消息，今年前三个月，我国创新药对外授权交易总额超过600亿美元，接近2025年全年的一半。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sz002176</t>
+          <t>sz002432</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>江特电机</t>
+          <t>九安医疗</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>10.29</v>
+        <v>75.5</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
+        <v>9.99</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>锂矿+机器人|1.公司全资子公司银锂新能源是利用锂云母、锂辉石制备高纯度碳酸锂、氢氧化锂的锂电新能源高新技术企业。
-2.下属深圳尉尔正进行人形机器人关节模组开发，并批量出货机器人专用E/B系列电机用于国内头部机器人企业。</t>
+          <t>医疗器械+kimi|1.公司是一家在国内外具有影响力的个人健康管理产品供应商，主要从事家用医疗器械的研发、生产及销售。
+2.公司通过认购砺思资本基金份额参股Kimi。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>锂矿, 机器人</t>
+          <t>医疗器械, kimi</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2.44</v>
+        <v>0.98</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>广期所碳酸锂主力合约涨超6%，逼近17万元/吨关口。</t>
+          <t>据国家药监局消息，今年前三个月，我国创新药对外授权交易总额超过600亿美元，接近2025年全年的一半。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sh603978</t>
+          <t>sz002675</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>深圳新星</t>
+          <t>东诚药业</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>25.69</v>
+        <v>14.48</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>10.02</v>
+        <v>10.03</v>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>电解液+商业航天|1.公司全资子公司松岩冶金建设年产15,000吨的六氟磷酸锂项目。该产品为锂电池电解液中组成材料之一。
-2.公司铝晶粒细化剂及铝中间合金广泛应用于军工、航空航天、轨道交通、汽车、电子等领域高新铝合金材的制造。</t>
+          <t>创新药|公司着力打造放射性诊疗一体化药物创新平台——烟台蓝纳成，其具有放射性诊疗一体化药物创新研发和全球领先的纳米递送技术的特点，适应症涵盖前列腺癌、胃癌、结直肠癌、鼻咽癌等多种癌症的诊断与治疗产品，其中部分产品进行中美双报。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>电解液, 商业航天</t>
+          <t>创新药</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2.44</v>
+        <v>0.98</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>广期所碳酸锂主力合约涨超6%，逼近17万元/吨关口。</t>
+          <t>据国家药监局消息，今年前三个月，我国创新药对外授权交易总额超过600亿美元，接近2025年全年的一半。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sz000546</t>
+          <t>sz002370</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>金圆股份</t>
+          <t>亚太药业</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>6.61</v>
+        <v>7.18</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>9.98</v>
+        <v>9.950000000000001</v>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>盐湖提锂|公司旗下控股子公司锂源矿业主要从事盐湖卤水锂、钾、硼等资源的勘查和开发。</t>
+          <t>创新药|截止2024年年报，公司二类新药右旋酮洛芬缓释贴片II期a临床已经结束，尚在评估是否需要开展II期b。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>盐湖提锂</t>
+          <t>创新药</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>2.44</v>
+        <v>0.98</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>广期所碳酸锂主力合约涨超6%，逼近17万元/吨关口。</t>
+          <t>据国家药监局消息，今年前三个月，我国创新药对外授权交易总额超过600亿美元，接近2025年全年的一半。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sz002240</t>
+          <t>sh688677</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>盛新锂能</t>
+          <t>海泰新光</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>42.23</v>
+        <v>47.83</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>10</v>
+        <v>19.99</v>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>锂矿|我国在四川雅江探获锂资源近百万吨，是亚洲迄今探明最大规模伟晶岩型单体锂矿。盛新锂能旗下公司拥有木绒矿探矿权。</t>
+          <t>医疗器械|公司是医用成像器械行业的高新技术企业，主要从事医用内窥镜器械和光学产品的研发、生产和销售。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>锂矿</t>
+          <t>医疗器械</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2.44</v>
+        <v>0.98</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>广期所碳酸锂主力合约涨超6%，逼近17万元/吨关口。</t>
+          <t>据国家药监局消息，今年前三个月，我国创新药对外授权交易总额超过600亿美元，接近2025年全年的一半。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sh600110</t>
+          <t>sh603716</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>诺德股份</t>
+          <t>塞力医疗</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>8.66</v>
+        <v>22.75</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>10.04</v>
+        <v>10.01</v>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>锂电池+PCB|1.公司主要从事锂离子电池用电解铜箔的研发、生产和销售，产品主要应用于动力锂电池生产制造，是国内主要知名锂离子电池厂商的供应商。
-2.公司紧跟AI算力设备对高频材料的需求升级，新一代HVLP铜箔产品已通过部分客户认证，可满足高速覆铜板（CCL）对低损耗、高稳定性的要求。</t>
+          <t>创新药+AI|1.公司战略投资的心血管领域长效治疗性疫苗的创新性研发公司——武汉华纪元生物技术开发有限公司，其自主研发国家1类生物创新药HJY-ATRQβ-001正式获得国家药品监督管理局（NMPA）的新药临床试验申请（IND）受理通知书。
+2.公司作为以“人工智能+医疗大数据”为基础的智慧医疗综合体系建设供应商，始终聚焦医疗技术更新迭代与医疗领域应用场景的创新融合。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>锂电池, PCB</t>
+          <t>创新药, AI</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>2.44</v>
+        <v>0.98</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>广期所碳酸锂主力合约涨超6%，逼近17万元/吨关口。</t>
+          <t>据国家药监局消息，今年前三个月，我国创新药对外授权交易总额超过600亿美元，接近2025年全年的一半。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sz002756</t>
+          <t>sh603122</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>永兴材料</t>
+          <t>合富中国</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>81.20999999999999</v>
+        <v>16.92</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>锂矿|公司拥有上游优质锂矿资源，控股子公司花桥矿业拥有的化山瓷石矿矿权面积1.8714平方公里，采矿证范围内累计查明陶瓷土矿资源储量49225.21万吨，其中，累计查明Li2O≥0.20%陶瓷土矿矿石量41000.80万吨，是公司锂云母和碳酸锂生产原材料的主要保障渠道。公司联营公司花锂矿业拥有白水洞高岭土矿矿权面积0.7614平方公里，累计查明控制的经济资源量矿石量730.74万吨。</t>
+          <t>医药+海峡两岸概念|1.公司系医疗流通领域的渠道商，具备与境内外试剂耗材和医疗设备原厂、各大代理商及医疗机构长期互惠、合作共赢的核心竞争力。
+2.公司为唯一一家海峡两岸市场“双上市”的医疗企业，其母公司合富医疗控股在台湾上市，公司实际控制人为台湾企业家王琼芝，在两岸医疗流通领域有深度合作。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>锂矿</t>
+          <t>医药, 海峡两岸概念</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>2.44</v>
+        <v>1.43</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>广期所碳酸锂主力合约涨超6%，逼近17万元/吨关口。</t>
+          <t>伊朗使用导弹和无人机“有效”打击了阿联酋和巴林境内与美国有关的铝厂。受此消息刺激，LME铝价在伊朗袭击中东工厂后上涨5%。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sh600955</t>
+          <t>sz002578</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>维远股份</t>
+          <t>闽发铝业</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>17.05</v>
+        <v>4.26</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>10</v>
+        <v>10.08</v>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>化工+锂电池|1.公司主营业务为“苯酚、丙酮—双酚A—聚碳酸酯”产业链有机化学新材料产品的研发、生产与销售，是目前国内唯一具备完整聚碳酸酯产业链的公司。
-2.2022年2月28日公告，公司与日本宇部兴产株式会社签署了《2万吨/年高纯碳酸二甲酯技术许可协议》，宇部将其拥有的通过碳酸二甲酯生产高纯碳酸二甲酯的技术许可给公司生产HPDMC；HPDMC主要应用于锂电池电解液。</t>
+          <t>铝+福建|公司是国内行业中较早涉足工业型材领域的企业之一，主营业务和产品主要是建筑铝型材、工业铝型材和建筑铝模板的研发、生产、销售。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>化工, 锂电池</t>
+          <t>铝, 福建</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2.44</v>
+        <v>1.43</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>广期所碳酸锂主力合约涨超6%，逼近17万元/吨关口。</t>
+          <t>伊朗使用导弹和无人机“有效”打击了阿联酋和巴林境内与美国有关的铝厂。受此消息刺激，LME铝价在伊朗袭击中东工厂后上涨5%。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sz002386</t>
+          <t>sz002160</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>天原股份</t>
+          <t>常铝股份</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>6.31</v>
+        <v>5.49</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>9.93</v>
+        <v>10.02</v>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>化工+锂电池|1.公司秉持稳健的经营发展理念，目前已发展形成氯碱化工、化工新材料、新能源电池材料等业务板块。
-2.公司新能源锂电产业的主要载体为宜宾光原锂电和宜宾锂宝新材料两家公司。公司于2020年11月16日在互动平台表示，目前公司三元正极材料和前驱体各2万吨，未来规划为各10万吨。</t>
+          <t>铝|公司主要从事于铝板带箔的研发、生产和销售，其产品涵盖空调铝箔、合金铝箔等多个品种，主要用于下游空调器散热器和汽车热交换系统用铝材的生产制造，其中家电行业以的空调生产商居多。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>化工, 锂电池</t>
+          <t>铝</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>2.44</v>
+        <v>1.43</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>广期所碳酸锂主力合约涨超6%，逼近17万元/吨关口。</t>
+          <t>伊朗使用导弹和无人机“有效”打击了阿联酋和巴林境内与美国有关的铝厂。受此消息刺激，LME铝价在伊朗袭击中东工厂后上涨5%。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sz000155</t>
+          <t>sz002532</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>川能动力</t>
+          <t>天山铝业</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>16.16</v>
+        <v>17.73</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>10.01</v>
+        <v>9.99</v>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>锂电池|公司持有鼎盛锂业72%股权，鼎盛锂业主要从事电池级碳酸锂、氢氧化锂等锂盐产品生产、销售、研发。公司拟与亿纬锂能、蜂巢能源共同组建合资公司，投资建设3万吨/年锂盐项目。新设合资公司注册资本7.5亿元，公司持股比例51%。</t>
+          <t>铝+业绩|1.公司主营业务为电解铝、氧化铝、预焙阳极、高纯铝、铝深加工产品及材料的生产和销售，形成了从铝土矿、氧化铝到电解铝、高纯铝、铝箔研发制造的上下游一体化，并配套自备电厂和预焙阳极的完整铝产业链布局。
+2.天山铝业公告称，预计2026年第一季度归属于上市公司股东的净利润为22亿元，同比增长107.92%。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>铝, 业绩</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>2.44</v>
+        <v>1.43</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>广期所碳酸锂主力合约涨超6%，逼近17万元/吨关口。</t>
+          <t>伊朗使用导弹和无人机“有效”打击了阿联酋和巴林境内与美国有关的铝厂。受此消息刺激，LME铝价在伊朗袭击中东工厂后上涨5%。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sz301292</t>
+          <t>sh601068</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>海科新源</t>
+          <t>中铝国际</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>96.29000000000001</v>
+        <v>6.28</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>20</v>
+        <v>9.98</v>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>电解液溶剂|公司是全球锂离子电池电解液溶剂龙头企业，拥有完备的产品体系，包括碳酸二甲酯（DMC）、碳酸二乙酯（DEC）、碳酸甲乙酯（EMC）、碳酸乙烯酯（EC）、碳酸丙烯酯（PC），是国内为数不多能够同时提供5种碳酸酯溶剂的生产企业。</t>
+          <t>盐湖提锂+有色金属|1.公司子公司长沙有色冶金院设计的年产1万吨碳酸锂项目采用世界先进的离子选择迁移合成碳酸锂的盐湖提锂工艺。
+2.公司是中国有色金属行业领先的技术、服务、装备及产品综合解决方案的提供商，能为整个有色金属产业链各类业务提供全方位的综合技术及工程设计及建设服务。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>电解液溶剂</t>
+          <t>盐湖提锂, 有色金属</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>2.44</v>
+        <v>1.43</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>广期所碳酸锂主力合约涨超6%，逼近17万元/吨关口。</t>
+          <t>伊朗使用导弹和无人机“有效”打击了阿联酋和巴林境内与美国有关的铝厂。受此消息刺激，LME铝价在伊朗袭击中东工厂后上涨5%。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sh603399</t>
+          <t>sz002501</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>永杉锂业</t>
+          <t>利源股份</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>11.72</v>
+        <v>2.04</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>10.05</v>
+        <v>10.27</v>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>锂+钼|1.公司主要从事电池级碳酸锂和电池级氢氧化锂的研发、生产和销售，产品下游主要应用领域包括新能源汽车用动力电池、储能电池及消费电子类产品电池等。
-2.国内大型钼业企业，拥有焙烧、冶炼、钼化工、钼金属深加工等一体化的生产能力，拥有钼矿采矿权和探矿权，产品主要包括焙烧钼精矿、钼铁、钼酸铵、高纯氧化钼、钼粉、钼板、钼棒、钼顶头等。</t>
+          <t>铝|公司主要从事铝型材及深加工产品、轨道交通装备的研发、生产与销售业务，产品可分为工业铝型材、建筑铝型材及多种铝型材深加工产品、轨道车辆装备等。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>锂, 钼</t>
+          <t>铝</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>2.44</v>
+        <v>1.43</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>广期所碳酸锂主力合约涨超6%，逼近17万元/吨关口。</t>
+          <t>伊朗使用导弹和无人机“有效”打击了阿联酋和巴林境内与美国有关的铝厂。受此消息刺激，LME铝价在伊朗袭击中东工厂后上涨5%。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sz002460</t>
+          <t>sh601388</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>赣锋锂业</t>
+          <t>怡球资源</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>79.67</v>
+        <v>3.94</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>10</v>
+        <v>10.06</v>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>锂矿|公司是世界领先的锂生态企业，拥有五大类逾40种锂化合物及金属锂产品的生产能力，是锂系列产品供应最齐全的制造商之一，完善的产品供应组合能够满足客户独特且多元化的需求。</t>
+          <t>再生铝|公司的主营业务是利用所回收的来源于废旧汽车、建材、电器、机械、包装、设备等及生产过程中产生的铝渣、边角料等各方面的废铝资源，进行分选、熔炼、浇注等生产工序，制造出替代原铝的再生铝产品。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>锂矿</t>
+          <t>再生铝</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>2.44</v>
+        <v>1.43</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>广期所碳酸锂主力合约涨超6%，逼近17万元/吨关口。</t>
+          <t>伊朗使用导弹和无人机“有效”打击了阿联酋和巴林境内与美国有关的铝厂。受此消息刺激，LME铝价在伊朗袭击中东工厂后上涨5%。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sz002068</t>
+          <t>sh600219</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>黑猫股份</t>
+          <t>南山铝业</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>6.49</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>10.05</v>
+        <v>10</v>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>锂电池+煤化工|1.2022年4月21日公告，公司拟设立江西黑猫高性能材料有限公司，投资新建年产5000吨碳纳米管粉体及配套产业一体化项目，项目预计投资总额约6.8亿元。
-2.国内炭黑行业龙头，产能规模当前已跻身世界炭黑企业第三位，公司炭黑生产是煤焦油深加工产业链的下游产业，具备炭黑生产能力110万吨/年。</t>
+          <t>铝|公司形成从热电-氧化铝-电解铝-熔铸-(铝型材/热轧-冷轧-箔轧/锻压）的完整的铝产业链生产线，主要产品包括上游产品电力、蒸汽、氧化铝、铝合金锭，下游产品铝板带箔、挤压型材、压延材及大型机械机加工结构件。</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>锂电池, 煤化工</t>
+          <t>铝</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>商业航天</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>2.44</v>
+        <v>1.32</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>广期所碳酸锂主力合约涨超6%，逼近17万元/吨关口。</t>
+          <t>星河动力董事长表示，星河动力的发射订单已排至2028年，任务储备饱满。液体可重复使用火箭智神星一号也将于近期实现首飞。</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sh600338</t>
+          <t>sz002361</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>西藏珠峰</t>
+          <t>神剑股份</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>17.48</v>
+        <v>15</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
+        <v>9.969999999999999</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>盐湖提锂|公司在新能源储能金属锂资源丰富的南美洲“锂三角”中心位置的阿根廷，正在推进控股锂钾公司的安赫莱斯“年产3万吨碳酸锂盐湖提锂建设项目”的开发建设；此外，公司拥有同区域控股的另一阿里扎罗（Arizaro）锂项目未开发盐湖湖区矿权面积363平方公里。</t>
+          <t>商业航天|公司参与了星网项目建设，提供卫星上相关零部件。目前航天类产品有卫星天线、反射器及支撑塔等。</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>盐湖提锂</t>
+          <t>商业航天</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>商业航天</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>3.51</v>
+        <v>1.32</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>招银国际指出，生物医药产业定位跃升为新兴支柱产业，预示全链条政策红利将持续释放，AI制药技术突破与中国创新药出海BD爆发形成双重共振，行业基本面有望加速向好。</t>
+          <t>星河动力董事长表示，星河动力的发射订单已排至2028年，任务储备饱满。液体可重复使用火箭智神星一号也将于近期实现首飞。</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sh603538</t>
+          <t>sh603601</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">美诺华  </t>
+          <t>再升科技</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>39.18</v>
+        <v>14.5</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>9.99</v>
+        <v>10.02</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6天5板</t>
+          <t>4天3板</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>减肥药|2026年3月19日公司在官微公布益生菌（JH389）胶囊产品临床数据，结果显示，服用该产品8周可显著改善受试者体重、体脂及肥胖相关指标，有助于全面提升生活质量、有助于正向调节肠道菌群结构，同时对糖脂代谢及各项安全性指标无不良影响。</t>
+          <t>商业航天|公司研发生产的高硅氧纤维已与国际知名航天公司开展商业合作，长期供应系列产品。</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>减肥药</t>
+          <t>商业航天</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>商业航天</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>3.51</v>
+        <v>1.32</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>招银国际指出，生物医药产业定位跃升为新兴支柱产业，预示全链条政策红利将持续释放，AI制药技术突破与中国创新药出海BD爆发形成双重共振，行业基本面有望加速向好。</t>
+          <t>星河动力董事长表示，星河动力的发射订单已排至2028年，任务储备饱满。液体可重复使用火箭智神星一号也将于近期实现首飞。</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>sz002082</t>
+          <t>sz001400</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>万邦德</t>
+          <t>江顺科技</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>26.04</v>
+        <v>164.1</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4天3板</t>
+          <t>4天2板</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">创新药+AI|在研发端，公司探索人工智能在创新药设计、筛选、实验设计等环节的应用，目前全球首个治疗胃轻瘫的中药1.1类新药“理中消痞颗粒”正在开展临床研究。 </t>
+          <t>铝+商业航天|1.公司主要从事铝型材挤压模具及配件、铝型材挤压配套设备、精密机械零部件等产品的研发、设计、生产和销售。
+2.公司产品铝型材挤压模具和铝型材挤压配套设备应用于航空航天领域。</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>创新药, AI</t>
+          <t>铝, 商业航天</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>商业航天</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>3.51</v>
+        <v>1.32</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>招银国际指出，生物医药产业定位跃升为新兴支柱产业，预示全链条政策红利将持续释放，AI制药技术突破与中国创新药出海BD爆发形成双重共振，行业基本面有望加速向好。</t>
+          <t>星河动力董事长表示，星河动力的发射订单已排至2028年，任务储备饱满。液体可重复使用火箭智神星一号也将于近期实现首飞。</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>sz002038</t>
+          <t>sh600343</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>双鹭药业</t>
+          <t>航天动力</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>6.61</v>
+        <v>32.58</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>3天2板</t>
-        </is>
-      </c>
+        <v>9.99</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>创新药|公司目前具有较强竞争力的储备品种有包括即将上市的G-CSF长效制剂、人促卵泡激素长、短效制剂，GLP-1类似物长、短效和双靶点制剂，心脑血管领域开发的创新药和特色仿制药等。</t>
+          <t>军工+商业航天|1.公司涉军业务包括军用特种车辆液力传动系统、军用车载加油泵、洗消用泵等。
+2.公司是航天六院唯一的资产证券化平台。航天六院是我国液体火箭发动机研制中心和专业抓总单位，承担着为我国运载火箭和导弹武器提供液体火箭发动机的重任。</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>军工, 商业航天</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>商业航天</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>3.51</v>
+        <v>1.32</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>招银国际指出，生物医药产业定位跃升为新兴支柱产业，预示全链条政策红利将持续释放，AI制药技术突破与中国创新药出海BD爆发形成双重共振，行业基本面有望加速向好。</t>
+          <t>星河动力董事长表示，星河动力的发射订单已排至2028年，任务储备饱满。液体可重复使用火箭智神星一号也将于近期实现首飞。</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>sh600513</t>
+          <t>sh603017</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>联环药业</t>
+          <t>中衡设计</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>25.61</v>
+        <v>15.76</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>10.01</v>
+        <v>9.98</v>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>药品过审|联环药业公告称，公司控股子公司常乐制药近日收到国家药监局核准签发的尼可地尔片《药品补充申请批准通知书》，该药品已通过仿制药质量和疗效一致性评价。尼可地尔片用于治疗心绞痛，2024年度国内样本医院销售额约为6.35亿元。</t>
+          <t>商业航天|公司中标了天兵科技运载火箭及发动机智能制造 基地、山东箭元航天科技总装总测生产基地、星际荣耀火箭制造基地、安庆年发20发可回收液体火箭制造厂房建设项目等多个高端制造基地，积极为航空航天逐梦苍穹贡献中衡力量。</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>药品过审</t>
+          <t>商业航天</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>商业航天</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>3.51</v>
+        <v>1.32</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>招银国际指出，生物医药产业定位跃升为新兴支柱产业，预示全链条政策红利将持续释放，AI制药技术突破与中国创新药出海BD爆发形成双重共振，行业基本面有望加速向好。</t>
+          <t>星河动力董事长表示，星河动力的发射订单已排至2028年，任务储备饱满。液体可重复使用火箭智神星一号也将于近期实现首飞。</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>sh603387</t>
+          <t>sh605222</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>基蛋生物</t>
+          <t>起帆电缆</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>9.9</v>
+        <v>22.36</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>医疗器械|公司通过自主研发，构建了胶体金免疫层析、荧光免疫层析、生化检测、化学发光免疫分析、分子诊断、诊断试剂原材料开发和校准品质控品在内的七大技术平台，又通过并购投资布局血凝、血细胞、尿液分析等领域。</t>
+          <t>商业航天|公司产品涵盖电力电缆、电气装备用电线电缆、通信电缆和裸电线四大类，广泛应用于水利、电力、家装、轨道交通、建筑工程、航空航天、新能源等众多领域。</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>医疗器械</t>
+          <t>商业航天</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>商业航天</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>3.51</v>
+        <v>1.32</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>招银国际指出，生物医药产业定位跃升为新兴支柱产业，预示全链条政策红利将持续释放，AI制药技术突破与中国创新药出海BD爆发形成双重共振，行业基本面有望加速向好。</t>
+          <t>星河动力董事长表示，星河动力的发射订单已排至2028年，任务储备饱满。液体可重复使用火箭智神星一号也将于近期实现首飞。</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>sh600488</t>
+          <t>sz300900</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>津药药业</t>
+          <t>广联航空</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>4.33</v>
+        <v>38.16</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>9.9</v>
+        <v>20</v>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>医药|公司主要从事皮质激素类、氨基酸类原料药及制剂的研发、生产和销售，产品包括地塞米松系列、泼尼松系列、甲泼尼龙系列、倍他米松系列等40余个皮质激素原料药品种，23个氨基酸原料药品种，以及16个剂型药品。</t>
+          <t>商业航天+燃气轮机|1.公司是国内知名的民营航空航天工业配套产品供应商，持续跟进微厘空间一号系统（ALNES）北斗低轨卫星导航增强系统组网卫星、天都二号通导技术试验星、探月卫星等航天产品的整体结构、主框架结构及内部复合材料结构等研制工作。
+2.公司具备整台燃气轮机机匣总成制造能力，核心产品涵盖压气机机匣、燃烧外壳、涡轮支撑环总成等关键部套，可实现从燃气轮机的全序加工。</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>商业航天, 燃气轮机</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>光纤光缆</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>3.51</v>
+        <v>2.6</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>招银国际指出，生物医药产业定位跃升为新兴支柱产业，预示全链条政策红利将持续释放，AI制药技术突破与中国创新药出海BD爆发形成双重共振，行业基本面有望加速向好。</t>
+          <t>中信建投证券研报称，今年2月，我国出口光纤3779.9吨，金额7.9亿元，同比增长63.6%，126.8%。</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>sz002773</t>
+          <t>sz002309</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>康弘药业</t>
+          <t>中利集团</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>27.65</v>
+        <v>4.76</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
+        <v>9.93</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>7天5板</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>创新药|在合成生物技术方面，注射用KH617是公司自主研发的拟用于治疗晚期实体瘤患者（包括成人弥漫性胶质瘤）的具有自主知识产权的化药1类创新药，也是公司合成生物学平台首个进入临床试验申报的产品；该项目采用生物合成技术生产高纯度原料药，其制剂在几种临床前疾病模型中均显示出了对多种实体瘤的良好抑瘤作用。</t>
+          <t>光伏+光纤光缆|1.公司的新能源光伏组件业务板块，包括单晶大尺寸高效光伏电池片和光伏组件的研发、生产和销售。公司拥有钙钛矿叠层电池及组件研发专利等技术储备6项。
+2.公司光通讯线缆板块已延伸到高分子材料、光纤、电缆的全产业链，作为华为核心战略供应商，为华为提供通信用电缆，包括5G用新品光电混合缆。</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>光伏, 光纤光缆</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>光纤光缆</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>3.51</v>
+        <v>2.6</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>招银国际指出，生物医药产业定位跃升为新兴支柱产业，预示全链条政策红利将持续释放，AI制药技术突破与中国创新药出海BD爆发形成双重共振，行业基本面有望加速向好。</t>
+          <t>中信建投证券研报称，今年2月，我国出口光纤3779.9吨，金额7.9亿元，同比增长63.6%，126.8%。</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>sh603127</t>
+          <t>sh603618</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>昭衍新药</t>
+          <t>杭电股份</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>30.24</v>
+        <v>26.71</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr"/>
+        <v>10.01</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>4天3板</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>CRO|公司专注于药物全生命周期的安全性评价和监测，建立了独具特色的药物非临床研究服务、临床试验及相关服务。</t>
+          <t>电网设备+光纤光缆|1.公司电线电缆板块主要从事电线电缆的研发、生产、销售和服务。主要产品为涵盖从超高压、高压到中低压的各类电力电缆、导线、民用线缆及特种电缆。
+2.公司光通信板块主要由富春江光电及其子公司从事经营，其主要从事光通信产业链中光纤预制棒、光纤、光缆、光通信相关设备等产品研发、生产、销售和服务。公司具备光通信“光棒—光纤—光缆”一体化产业链。</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>CRO</t>
+          <t>电网设备, 光纤光缆</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>光纤光缆</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>3.51</v>
+        <v>2.6</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>招银国际指出，生物医药产业定位跃升为新兴支柱产业，预示全链条政策红利将持续释放，AI制药技术突破与中国创新药出海BD爆发形成双重共振，行业基本面有望加速向好。</t>
+          <t>中信建投证券研报称，今年2月，我国出口光纤3779.9吨，金额7.9亿元，同比增长63.6%，126.8%。</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>sz002755</t>
+          <t>sh601869</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>奥赛康</t>
+          <t>长飞光纤</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>15.39</v>
+        <v>301.69</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>5天3板</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>创新药|公司是一家创新与研发驱动的医药制造企业，公司药物治疗领域主要覆盖消化、抗肿瘤、抗感染、慢性病四大领域，业务涵盖原料药及制剂的研发、生产、销售，在中国医药细分市场具有较高的品牌影响力。</t>
+          <t>光纤光缆|公司系全球光纤光缆行业的领先企业，是国内最早的光纤光缆生产厂商之一，聚焦电信运营商和数据通信相关领域，致力于光纤预制棒、光纤和光缆以及数据通信相关产品的研发创新与生产制造，形成了棒纤缆、综合布线和光模块一体化的完整产业链、相关多元化和国际化的业务模式。</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>光纤光缆</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>光纤光缆</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>3.51</v>
+        <v>2.6</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>招银国际指出，生物医药产业定位跃升为新兴支柱产业，预示全链条政策红利将持续释放，AI制药技术突破与中国创新药出海BD爆发形成双重共振，行业基本面有望加速向好。</t>
+          <t>中信建投证券研报称，今年2月，我国出口光纤3779.9吨，金额7.9亿元，同比增长63.6%，126.8%。</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>sz002294</t>
+          <t>sz000890</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>信立泰</t>
+          <t>法尔胜</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>61.88</v>
+        <v>14.83</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>10.01</v>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>创新药|公司抗心衰创新药S086、生物药“重组胰高血糖素样肽-1-Fc  融合蛋白注射液”申报临床已获得临床批件（二季度CDE受理，三季度获得批件）；甲磺酸伊马替尼、奥美沙坦酯、盐酸莫西沙星等项目申报生产获CDE  受理，目前分处于不同的审评阶段。</t>
+          <t>光纤光缆|公司参股的普天法尔胜光通信有限公司主要产品为光纤预制棒、光纤、光缆，上述产品可以应用于在运营商基础网络通信及广播电视通信领域。</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>光纤光缆</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>光纤光缆</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>3.51</v>
+        <v>2.6</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>招银国际指出，生物医药产业定位跃升为新兴支柱产业，预示全链条政策红利将持续释放，AI制药技术突破与中国创新药出海BD爆发形成双重共振，行业基本面有望加速向好。</t>
+          <t>中信建投证券研报称，今年2月，我国出口光纤3779.9吨，金额7.9亿元，同比增长63.6%，126.8%。</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>sh688068</t>
+          <t>sh600345</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>热景生物</t>
+          <t>长江通信</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>132.13</v>
+        <v>43.23</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>创新药+AI医疗|1.在创新药领域，公司通过参股公司尧景基因、舜景医药、智源医药等分别布局核酸药物、抗体药物等生物制药领域前沿创新技术方向的研发。
-2.2024年6月6日公司在互动平台表示，公司在北京中关村科技园区大兴生物医药产业基地成立“X-Gen AI 新药发现与设计研究中心”，团队核心成员来自国内外顶尖高校及科研院所。</t>
+          <t>参股长飞光纤|公司参股公司长飞光纤（持股比例15.82%）系全球光纤光缆行业的领先企业，是国内最早的光纤光缆生产厂商之一。</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>创新药, AI医疗</t>
+          <t>参股长飞光纤</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>光纤光缆</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>3.51</v>
+        <v>2.6</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>招银国际指出，生物医药产业定位跃升为新兴支柱产业，预示全链条政策红利将持续释放，AI制药技术突破与中国创新药出海BD爆发形成双重共振，行业基本面有望加速向好。</t>
+          <t>中信建投证券研报称，今年2月，我国出口光纤3779.9吨，金额7.9亿元，同比增长63.6%，126.8%。</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>sz300204</t>
+          <t>sh600487</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>舒泰神</t>
+          <t>亨通光电</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>27.76</v>
+        <v>53.85</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>20.02</v>
+        <v>10.01</v>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>创新药|作为创新型生物制药企业，公司已上市产品包括创新生物药、特色化学药，涉及神经系统、肠道系统等众多治疗领域。</t>
+          <t>光纤光缆|公司拥有全球光纤通信（光棒-光纤-光缆-光器件-光网络及海洋光网络）、量子通信、数据通信全产业链及自主核心技术，致力于提供光纤光网、量子保密通信、海洋观测网及智慧海洋工程系统解决方案及设计-施工-运维服务为一体的工程EPC总包服务， 目前已形成“产品+平台+服务”综合服务模式，已成为通信产业全价值链综合服务商。</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>光纤光缆</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>3.51</v>
+        <v>0.21</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>招银国际指出，生物医药产业定位跃升为新兴支柱产业，预示全链条政策红利将持续释放，AI制药技术突破与中国创新药出海BD爆发形成双重共振，行业基本面有望加速向好。</t>
+          <t>机构研报指出，特斯拉OptimusV3进入亮相发布时间窗口，并计划年内启动大规模量产，并且特斯拉已将弗里蒙特工厂的Model S/X产线改造为Optimus专用产线，中期规划年产能达100万台。</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>sz002432</t>
+          <t>sh603272</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>九安医疗</t>
+          <t>联翔股份</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>68.64</v>
+        <v>35.55</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
+        <v>9.99</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>6天3板</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>医疗器械+kimi|1.公司是一家在国内外具有影响力的个人健康管理产品供应商，主要从事家用医疗器械的研发、生产及销售。
-2.公司通过认购砺思资本基金份额参股Kimi。</t>
+          <t>机器人|2025年12月30日公告，董事会审议通过变更经营范围议案，新增服务消费机器人制造、服务消费机器人销售、工业机器人制造、工业机器人销售、智能机器人的研发等制造销售，并同步修订公司章程。</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>医疗器械, kimi</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>2.39</v>
+        <v>0.21</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>进入3月，地缘政治局势骤然紧张，叠加霍尔木兹海峡航运受阻，国际原油不断攀升，带动化工板块整体上扬。</t>
+          <t>机构研报指出，特斯拉OptimusV3进入亮相发布时间窗口，并计划年内启动大规模量产，并且特斯拉已将弗里蒙特工厂的Model S/X产线改造为Optimus专用产线，中期规划年产能达100万台。</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>sz000008</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>神州高铁</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="H33" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>sh600844</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>金煤科技</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>9.91</v>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>5天3板</t>
-        </is>
-      </c>
+      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>煤化工|公司为专注于煤制乙二醇产业的新型化工企业，目前主要通过控股子公司通辽金煤的大型化工装置生产乙二醇并联产草酸。</t>
+          <t>高铁+机器人|1.公司提供轨道交通运营维护全产业链智能装备系统，并以此为依托，提供轨道交通运营及维保专业服务，是中国轨道交通运营维护领域首家涵盖全产业链装备及运营维保服务的上市公司。
+2.神州高铁在互动平台表示，近年来，公司积极加强智能化、数字化产品研发，动车组空心车轴超声检测机器人、动车组车轮超声检测机器人等智能产品已进入样机测试阶段。</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>煤化工</t>
+          <t>高铁, 机器人</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>2.39</v>
+        <v>0.21</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>进入3月，地缘政治局势骤然紧张，叠加霍尔木兹海峡航运受阻，国际原油不断攀升，带动化工板块整体上扬。</t>
+          <t>机构研报指出，特斯拉OptimusV3进入亮相发布时间窗口，并计划年内启动大规模量产，并且特斯拉已将弗里蒙特工厂的Model S/X产线改造为Optimus专用产线，中期规划年产能达100万台。</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>sh603897</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>长城科技</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>32.89</v>
+      </c>
+      <c r="H34" s="2" t="n">
         <v>10</v>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>sh603585</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>苏利股份</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>20.74</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>10.03</v>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>农药|公司主营业务为农药、阻燃剂及其他精细化工产品的研发、生产和销售。农药类产品包括百菌清原药、嘧菌酯原药、农药制剂及其他农药类产品。</t>
+          <t>机器人|公司电磁线产品的应用领域包括工业电机、家用电器、汽车电机、电动工具和低压电器，其中工业电机涵盖水泵电机、轮毂电机、吸尘器电机、微特电机、中小型电机等产品领域，家用电器主要包括空调压缩机和风扇电机等，汽车电机包括新能源汽车驱动电机在内的车用各式电机产品应用领域，低压电器分别为仪表仪器、以及应用于包括机器人应用领域等在内的低压线圈产品。</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>农药</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>2.39</v>
+        <v>0.21</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>进入3月，地缘政治局势骤然紧张，叠加霍尔木兹海峡航运受阻，国际原油不断攀升，带动化工板块整体上扬。</t>
+          <t>机构研报指出，特斯拉OptimusV3进入亮相发布时间窗口，并计划年内启动大规模量产，并且特斯拉已将弗里蒙特工厂的Model S/X产线改造为Optimus专用产线，中期规划年产能达100万台。</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sz002470</t>
+          <t>sz000048</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>金正大</t>
+          <t>京基智农</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>3.09</v>
+        <v>22.61</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>9.959999999999999</v>
+        <v>10.02</v>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>化肥|公司的复合肥、缓控释肥、硝基复合肥、水溶肥及其他新型肥料在技术和市场占有率方面居国内领先地位，具有较强的竞争优势。</t>
+          <t>猪肉+机器人|1.旗下康达尔养猪有限公司已形成优质黑猪品牌肉产业链，主要为种猪和猪苗。
+2.2025年12月30日公告，公司已与江苏汇博机器人技术股份有限公司及后者股东团队签署股权投资意向协议，拟通过现金增资及受让老股方式取得江苏汇博控制权，若增资与受让老股后持股不足51%，将通过签署一致行动协议、委派过半数董事实现控制及合并报表。交易完成后双方将联合设立具身机器人研究院，由江苏汇博核心创始人、首席科学家孙立宁担任首席科学家。江苏汇博承诺2026年内发布2款人形机器人产品，并承诺在2026年至2028年间，每年收入增长率不低于30%，每年申请具身机器人专利不少于200项。</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>化肥</t>
+          <t>猪肉, 机器人</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>2.39</v>
+        <v>0.21</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>进入3月，地缘政治局势骤然紧张，叠加霍尔木兹海峡航运受阻，国际原油不断攀升，带动化工板块整体上扬。</t>
+          <t>机构研报指出，特斯拉OptimusV3进入亮相发布时间窗口，并计划年内启动大规模量产，并且特斯拉已将弗里蒙特工厂的Model S/X产线改造为Optimus专用产线，中期规划年产能达100万台。</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sh600727</t>
+          <t>sh603239</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>鲁北化工</t>
+          <t>浙江仙通</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>7.8</v>
+        <v>23.46</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>10.01</v>
+        <v>9.99</v>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>化肥|公司是山东省较大的磷复肥、复合肥和水泥生产企业，打造形成了集磷铵-硫酸-水泥联产、海水资源深度梯级利用、钛白粉清洁生产等循环经济产业链。</t>
+          <t>机器人|2025年9月25日公告，公司拟以4000万元对浩海星空进行增资，投资完成后持有浩海星空10%的股份。增资完成后，公司与浩海星空拟出资设立合资公司，合资公司由浙江仙通控股，注册在浙江省台州市仙居县，合资公司注册资本2000万元人民币，其中公司认缴出资1020万元，占注册资本的51%。本次合作事项为机器人业务相关。</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>化肥</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
@@ -2171,42 +2199,45 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>2.39</v>
+        <v>0.51</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>进入3月，地缘政治局势骤然紧张，叠加霍尔木兹海峡航运受阻，国际原油不断攀升，带动化工板块整体上扬。</t>
+          <t>据生意社及行业数据显示，关键化工品价格显著上涨，其中西南市场甲醇价格较2月底上涨约38.9%，溴素报价月内涨幅超50%，尿素、钾肥等化肥产品3月以来也普遍提价。</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sz002455</t>
+          <t>sz003042</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>百川股份</t>
+          <t>中农联合</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>14.41</v>
+        <v>19.77</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
+        <v>10.02</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>TMA+锂电池|1.公司是一家从事高新技术精细化工产品生产的专业企业，主营业务为醋酸酯类、偏苯三酸酐及酯类、醇醚类、多元醇类化工产品的研发、生产和销售。
-2.公司旗下海基新能源主营锂离子电池、电池组以及系统的研发、生产、销售和服务，产品定位于“泛储能”应用领域，下游应用覆盖至大型集装箱式储能系统、工商业储能产品、户用储能设备以及通信备电等多个应用领域。</t>
+          <t>农药|公司实控人为中华全国供销合作总社。公司是专业从事农药中间体、原药及制剂产品的研发、生产和销售的全产业链农药生产企业。</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>TMA, 锂电池</t>
+          <t>农药</t>
         </is>
       </c>
     </row>
@@ -2217,41 +2248,45 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>2.39</v>
+        <v>0.51</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>进入3月，地缘政治局势骤然紧张，叠加霍尔木兹海峡航运受阻，国际原油不断攀升，带动化工板块整体上扬。</t>
+          <t>据生意社及行业数据显示，关键化工品价格显著上涨，其中西南市场甲醇价格较2月底上涨约38.9%，溴素报价月内涨幅超50%，尿素、钾肥等化肥产品3月以来也普遍提价。</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>sz000822</t>
+          <t>sh603585</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>山东海化</t>
+          <t>苏利股份</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>6.45</v>
+        <v>22.81</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>10.07</v>
-      </c>
-      <c r="I38" s="2" t="inlineStr"/>
+        <v>9.98</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>纯碱|公司致力于纯碱、溴素、氯化钙、原盐等产品的生产和销售，其中纯碱为公司主导产品，广泛应用于化工、玻璃、冶金、造纸、印染、合成洗涤剂、石油化工、食品、医药卫生等行业。</t>
+          <t>农药|公司主营业务为农药、阻燃剂及其他精细化工产品的研发、生产和销售。农药类产品包括百菌清原药、嘧菌酯原药、农药制剂及其他农药类产品。</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>纯碱</t>
+          <t>农药</t>
         </is>
       </c>
     </row>
@@ -2262,2460 +2297,1662 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>2.39</v>
+        <v>0.51</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>进入3月，地缘政治局势骤然紧张，叠加霍尔木兹海峡航运受阻，国际原油不断攀升，带动化工板块整体上扬。</t>
+          <t>据生意社及行业数据显示，关键化工品价格显著上涨，其中西南市场甲醇价格较2月底上涨约38.9%，溴素报价月内涨幅超50%，尿素、钾肥等化肥产品3月以来也普遍提价。</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>sh600227</t>
+          <t>sz002810</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">赤天化  </t>
+          <t>山东赫达</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>4.27</v>
+        <v>22.9</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>10.05</v>
+        <v>9.99</v>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>化肥+煤化工|公司是贵州省最大的氮肥生产企业，公司化肥化工生产基地分别是以天然气为原料生产的赤水化工分公司（年产63万吨尿素）和以煤为生产原料的公司全资子公司桐梓化工（年产52万吨尿素、30万吨甲醇）。</t>
+          <t>化工|公司是国内第一、全球第四的纤维素醚供应商，具有自主研发、生产全系列建材级、医药级和食品级非离子型纤维素醚产品的能力。</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>化肥, 煤化工</t>
+          <t>化工</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>锂电池</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>2.39</v>
+        <v>0.16</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>进入3月，地缘政治局势骤然紧张，叠加霍尔木兹海峡航运受阻，国际原油不断攀升，带动化工板块整体上扬。</t>
+          <t>机构指出，储能需求非线性增长推动下，锂电新周期愈发明确。</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>sz002850</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>科达利</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>177.32</v>
+      </c>
+      <c r="H40" s="2" t="n">
         <v>10</v>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>sz000553</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>安道麦A</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>10.02</v>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>农药|安道麦控股股东为先正达，公司主要产品涵盖除草剂、杀虫剂、杀菌剂等，拥有草甘膦产能2万吨/年。</t>
+          <t>锂电池+机器人|1.公司为国内动力锂电池精密结构件龙头企业，也是国内最早从事动力锂电池精密结构件研发和生产的企业之一。
+2.公司基于人形机器人在未来的发展前景，通过谐波减速器等产品业务，拓展人形机器人关节部件领域，打开未来成长空间。</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>农药</t>
+          <t>锂电池, 机器人</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>锂电池</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>2.39</v>
+        <v>0.16</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>进入3月，地缘政治局势骤然紧张，叠加霍尔木兹海峡航运受阻，国际原油不断攀升，带动化工板块整体上扬。</t>
+          <t>机构指出，储能需求非线性增长推动下，锂电新周期愈发明确。</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>sz003042</t>
+          <t>sh600135</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>中农联合</t>
+          <t>乐凯胶片</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>17.97</v>
+        <v>11.06</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>9.98</v>
+        <v>10.05</v>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>农药|公司实控人为中华全国供销合作总社。公司是专业从事农药中间体、原药及制剂产品的研发、生产和销售的全产业链农药生产企业。</t>
+          <t>光伏+锂电池|2015年5月，公司向乐凯集团等对象定增募资6亿元投向高性能锂离子电池PE隔膜、锂电隔膜涂布、太阳能电池背板等五个项目，募集资金投入建设年产4000万平米的湿法分步双向拉伸的锂离子电池PE隔膜生产线、年产500万平方米陶瓷涂布型锂电隔膜的锂电隔膜涂布生产线、年产1200万平方米涂层改性隔膜成品的锂电隔膜涂布生产线和新增年产1500万平米太阳能电池背板生产能力。“高性能锂离子电池PE隔膜产业化建设项目”和“锂电隔膜涂布生产线一期项目”已于2018年12月竣工验收。</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>农药</t>
+          <t>光伏, 锂电池</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>锂电池</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>2.39</v>
+        <v>0.16</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>进入3月，地缘政治局势骤然紧张，叠加霍尔木兹海峡航运受阻，国际原油不断攀升，带动化工板块整体上扬。</t>
+          <t>机构指出，储能需求非线性增长推动下，锂电新周期愈发明确。</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>sh603778</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>国晟科技</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="H42" s="2" t="n">
         <v>10</v>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>sh600470</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>六国化工</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>10.07</v>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>化肥|公司是华东地区磷复肥和磷化工一体化专业制造的大型企业，主营业务为化肥(含氮肥、磷肥、钾肥)、肥料（含复合肥料、复混肥料、有机肥料及微生物肥料）、化学制品（含精制磷酸、磷酸盐）、化学原料的生产加工和销售。</t>
+          <t>光伏+锂电池|1.公司目前从事大尺寸高效异质结光伏电池的研发、生产、销售，以及异质结、TOPCON、PERC等电池组件的生产与销售。控股孙公司恒立聚能涉及钙钛矿研究。
+2.国晟科技公告称，公司拟以2.406亿元的价格受让正豪科技、林琴合计持有的孚悦科技100%股权。交易完成后，公司将持有标的公司100%股权，标的公司将纳入公司合并报表。孚悦科技主要从事高精密度新型锂电池结构件的研发、生产和销售。</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>化肥</t>
+          <t>光伏, 锂电池</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>农业种植</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>-0.64</v>
+        <v>2.9</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>国家能源局发布2026年1-2月份全国电力统计数据。截至2月底，全国累计发电装机容量39.5亿千瓦，同比增长15.9%。</t>
+          <t>高盛表示，化肥短缺可能导致因施肥延迟或不当而造成产量降低，同时一些农民可能转向化肥密集度较低的作物,进一步收紧谷物供应。</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>sz002445</t>
+          <t>sh600127</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>中南文化</t>
+          <t>金健米业</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>4.44</v>
+        <v>7.51</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>15天8板</t>
-        </is>
-      </c>
+        <v>9.959999999999999</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>并购重组+电力|中南文化公告称，公司计划通过发行股份及支付现金的方式购买江阴电力投资有限公司持有的江阴苏龙热电有限公司57.30%股权，同时拟向不超过三十五名特定投资者募集配套资金。本次交易相关审计、评估工作尚未完成，交易方案需进一步论证和沟通协商。本次交易预计构成重大资产重组。本次交易完成后，上市公司在电力能源领域的业务布局将得到拓展。</t>
+          <t>大米|公司以优质粮油、新型健康食品和药品的开发、生产、销售为主，主要产品有大米、面粉、面条、植物油、牛奶、药品、休闲食品等。</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>并购重组, 电力</t>
+          <t>大米</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>农业种植</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>-0.64</v>
+        <v>2.9</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>国家能源局发布2026年1-2月份全国电力统计数据。截至2月底，全国累计发电装机容量39.5亿千瓦，同比增长15.9%。</t>
+          <t>高盛表示，化肥短缺可能导致因施肥延迟或不当而造成产量降低，同时一些农民可能转向化肥密集度较低的作物,进一步收紧谷物供应。</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>sh600982</t>
+          <t>sh600359</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>宁波能源</t>
+          <t>新农开发</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>7.35</v>
+        <v>7.65</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>4天3板</t>
-        </is>
-      </c>
+        <v>10.07</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>电力|公司主要从事热电联产、生物质发电、抽水蓄能和综合能源服务，以及能源类相关金融投资等业务。</t>
+          <t>农业种植|公司的最终控制人为新疆生产建设兵团第一师国有资产监督管理委员会。公司主营为棉纱、香梨、大米、甘草、棉浆粕、清弹棉、生态棉、细绒棉、长绒棉的生产。</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>农业种植</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>-0.64</v>
+        <v>0.77</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>国家能源局发布2026年1-2月份全国电力统计数据。截至2月底，全国累计发电装机容量39.5亿千瓦，同比增长15.9%。</t>
+          <t>业内机构LightCounting测算，当前光模块需求量已超供应量两倍以上，800G光模块需求将持续旺盛，1.6T光模块2026年将进入规模化放量阶段，海外大客户已上修2026年采购计划至2000万只。</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>sh600310</t>
+          <t>sz002980</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>广西能源</t>
+          <t>华盛昌</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>6.6</v>
+        <v>43.78</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>6天3板</t>
-        </is>
-      </c>
+      <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>电力|公司主营业务为电力生产和销售，包括水力发电、火力发电、光伏发电，拥有完整的发、供电网络，电厂和电网“厂网合一”，发电、供电和配电业务一体化经营。</t>
+          <t>并购重组+光通信|华盛昌公告称，公司拟以现金方式收购深圳市伽蓝特科技有限公司100%股权，整体估值暂定为4.6亿元。伽蓝特专注于仪器仪表测试测量行业中的光通信模块和光芯片测试领域。</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>并购重组, 光通信</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>-0.64</v>
+        <v>0.77</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>国家能源局发布2026年1-2月份全国电力统计数据。截至2月底，全国累计发电装机容量39.5亿千瓦，同比增长15.9%。</t>
+          <t>业内机构LightCounting测算，当前光模块需求量已超供应量两倍以上，800G光模块需求将持续旺盛，1.6T光模块2026年将进入规模化放量阶段，海外大客户已上修2026年采购计划至2000万只。</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>sz000767</t>
+          <t>sz002222</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>晋控电力</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>5.09</v>
+        <v>71.94</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>9.94</v>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>电力+铝|1.公司主要营业范围为电力商品、热力商品的生产和销售。
-2.公司参股公司中铝山西新材料（持股比例14.02%）是山西省第一家拥有“矿山-氧化铝-电解铝-铝加工”并配套自备发电机组的完整铝产业链的大型企业。</t>
+          <t>光通信+光刻机|1.公司部分精密光学元件产品应用于光通讯领域。
+2.公司曾通过欧洲代理向ASML提供及其少量光学元件。此外，华为是公司的客户，公司在业务范围内向其提供光学元件产品。</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>电力, 铝</t>
+          <t>光通信, 光刻机</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>-0.64</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>国家能源局发布2026年1-2月份全国电力统计数据。截至2月底，全国累计发电装机容量39.5亿千瓦，同比增长15.9%。</t>
+          <t>福建省国资委印发《实施“五大行动”　推动所出资企业向新向优发展工作方案（2026—2028年）》，加快向新质生产力领域布局，向高质量效益转型。</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>sz002310</t>
+          <t>sz000592</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>东方新能</t>
+          <t>平潭发展</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>3.84</v>
+        <v>11.62</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="I47" s="2" t="inlineStr"/>
+        <v>10.04</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>绿电|2025年12月15日公告，公司拟以现金支付方式购买海城锐海100%股权和电投瑞享80%股权。其中，海城锐海100%股权拟通过在天津产权交易中心摘牌方式购买。标的资产的审计和评估工作尚未完成，评估值及交易价格均尚未确定（海城锐海100%股权在天津产权交易所的挂牌转让底价为1410万元）。本次交易预计构成重大资产重组。通过本次交易，东方园林新增光伏电站、风电场的投资、开发、建设和运营等新能源业务。</t>
+          <t>福建|公司在林木业务方面已基本形成“林板一体化”的发展产业链，拥有经营林区近90万亩，在福建省处于行业领先龙头地位。</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>绿电</t>
+          <t>福建</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>-0.64</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>国家能源局发布2026年1-2月份全国电力统计数据。截至2月底，全国累计发电装机容量39.5亿千瓦，同比增长15.9%。</t>
+          <t>福建省国资委印发《实施“五大行动”　推动所出资企业向新向优发展工作方案（2026—2028年）》，加快向新质生产力领域布局，向高质量效益转型。</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>sz001896</t>
+          <t>sz000753</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>豫能控股</t>
+          <t>漳州发展</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>16.54</v>
+        <v>7.21</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>9.969999999999999</v>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
+        <v>10.08</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>电算协同|1.公司是河南省内唯一省级资本控股的电力上市公司，从事的主要业务包括，火电项目的投资管理、能源销售、新能源项目投资建设等。
-2.豫能控股早间公告，公司正在筹划参股投资公司控股股东河南投资集团下属控股企业先天算力（河南）科技有限公司，并联合河南投资集团以先天算力为收购主体，收购郑州合盈数据有限责任公司控股权相关事项。此次参股投资事项尚处筹划阶段，存在较大不确定性。</t>
+          <t>福建+绿电|公司海上风电相关业务主要为全资子公司漳发新能源与南平电缆等公司共同在东山投建海底电缆项目，漳发新能源持有20%股权，业务覆盖福建及周边海上风电场。</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>电算协同</t>
+          <t>福建, 绿电</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>1.01</v>
+        <v>0.15</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Lumentum表示，到2026年底，EML的产能将较2025年增长超50%，此前公司已推进约40%的磷化铟(InP)扩产计划，预测到2030年，AIDC对磷化铟的需求年复合增长率将达到85%。</t>
+          <t>3月29日，上海人工智能实验室联合相关主体启动“超智融合算力”平台，为原始创新提供可统一调度的算力、可直接用于AI训练数据等底层支撑。</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>sz002428</t>
+          <t>sh600996</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>云南锗业</t>
+          <t>贵广网络</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>51.36</v>
+        <v>11.02</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>6天3板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>磷化铟|云南锗业发布投资者关系活动记录表公告，公司磷化铟晶片现有产能15万片/年(2-4英寸)，受光通信市场需求增加及原材料价格上涨影响，近期产品价格有所上涨。公司已批量向下游外延厂商或具备外延能力的器件厂商供货。公司光纤级锗产品为光纤用四氯化锗，目前产能为60吨/年。公司光纤级锗产品已批量稳定生产多年，客户涵盖国内下游知名光纤生产厂商。</t>
+          <t>贵州+算力|据中国信通院消息，3月26日，中国算力平台（贵州）建设工作在贵阳启动。贵州广播电视台旗下上市公司。公司将致力于贵州与粤港澳、长三角、京津冀等地区大数据中心集群的算力资源对接，充分发挥贵州省作为南方数据中心示范基地优势，有效承接东部算力需求。</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>磷化铟</t>
+          <t>贵州, 算力</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>1.01</v>
+        <v>0.15</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Lumentum表示，到2026年底，EML的产能将较2025年增长超50%，此前公司已推进约40%的磷化铟(InP)扩产计划，预测到2030年，AIDC对磷化铟的需求年复合增长率将达到85%。</t>
+          <t>3月29日，上海人工智能实验室联合相关主体启动“超智融合算力”平台，为原始创新提供可统一调度的算力、可直接用于AI训练数据等底层支撑。</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>sh603618</t>
+          <t>sh600602</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>杭电股份</t>
+          <t>云赛智联</t>
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>24.28</v>
+        <v>23.33</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>3天2板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>电网设备+光纤光缆|1.公司电线电缆板块主要从事电线电缆的研发、生产、销售和服务。主要产品为涵盖从超高压、高压到中低压的各类电力电缆、导线、民用线缆及特种电缆。
-2.公司光通信板块主要由富春江光电及其子公司从事经营，其主要从事光通信产业链中光纤预制棒、光纤、光缆、光通信相关设备等产品研发、生产、销售和服务。公司具备光通信“光棒—光纤—光缆”一体化产业链。</t>
+          <t>国资云|公司是上海国资委旗下上市公司，定位于中立第三方高端数据中心运营商。</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>电网设备, 光纤光缆</t>
+          <t>国资云</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Lumentum表示，到2026年底，EML的产能将较2025年增长超50%，此前公司已推进约40%的磷化铟(InP)扩产计划，预测到2030年，AIDC对磷化铟的需求年复合增长率将达到85%。</t>
-        </is>
-      </c>
+        <v>0.41</v>
+      </c>
+      <c r="C51" s="2" t="inlineStr"/>
       <c r="D51" s="2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>sz000890</t>
+          <t>sz000908</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>法尔胜</t>
+          <t>ST景峰</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>13.48</v>
+        <v>8.16</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>10.04</v>
-      </c>
-      <c r="I51" s="2" t="inlineStr"/>
+        <v>5.02</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>18天14板</t>
+        </is>
+      </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆|公司参股的普天法尔胜光通信有限公司主要产品为光纤预制棒、光纤、光缆，上述产品可以应用于在运营商基础网络通信及广播电视通信领域。</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>光纤光缆</t>
-        </is>
-      </c>
+          <t>ST股 | 公司专注医药健康产业，涉足药品研发、生产、销售等领域，产品涵盖了心脑血管、抗肿瘤、骨科、妇儿等用药领域。</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Lumentum表示，到2026年底，EML的产能将较2025年增长超50%，此前公司已推进约40%的磷化铟(InP)扩产计划，预测到2030年，AIDC对磷化铟的需求年复合增长率将达到85%。</t>
-        </is>
-      </c>
+        <v>0.41</v>
+      </c>
+      <c r="C52" s="2" t="inlineStr"/>
       <c r="D52" s="2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>sh603738</t>
+          <t>sz002620</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>泰晶科技</t>
+          <t>ST瑞和</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>26.19</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I52" s="2" t="inlineStr"/>
+        <v>4.95</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>6天6板</t>
+        </is>
+      </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>光通信|公司针对光通信200G、400G、800G、1.6T市场推出了高基频、高精度、低相噪CMOS、LVDS差分输出时钟解决方案，随着光模块传输速率升级，对应使用超高频、差分时钟产品，在技术上提出更高性能匹配要求。</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>光通信</t>
-        </is>
-      </c>
+          <t>ST股 | 公司主要从事政府机构、房地产开发商、大型企业、高档酒店、交通枢纽、园林绿化等综合性专业化装饰设计、工程施工业务以及光伏电站运营、光伏项目施工安装等。</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>2026年1-2月，国内实现社零总额8.61万亿元，同比增长2.8%，环比提升1.9pct。</t>
-        </is>
-      </c>
+        <v>0.41</v>
+      </c>
+      <c r="C53" s="2" t="inlineStr"/>
       <c r="D53" s="2" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>sh605388</t>
+          <t>sz002024</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>均瑶健康</t>
+          <t>ST易购</t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>7.05</v>
+        <v>1.47</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="I53" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>乳酸菌饮品|公司主营常温乳酸菌系列饮品的研发、生产和销售，2011年起，公司战略进入常温乳酸菌饮品市场，推出“味动力”乳酸菌系列饮品，是国内最早生产与销售常温乳酸菌饮品的品牌企业之一。</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>乳酸菌饮品</t>
-        </is>
-      </c>
+          <t>ST股 | 已经形成零售、金融、物流三大业务单元协同发展。</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>2026年1-2月，国内实现社零总额8.61万亿元，同比增长2.8%，环比提升1.9pct。</t>
-        </is>
-      </c>
+        <v>0.41</v>
+      </c>
+      <c r="C54" s="2" t="inlineStr"/>
       <c r="D54" s="2" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>sh603076</t>
+          <t>sz001270</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>乐惠国际</t>
+          <t>*ST铖昌</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>28.12</v>
+        <v>108.99</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I54" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>啤酒|公司目前的主要业务是液体食品装备，包括啤酒、饮料和乳品装备及无菌灌装设备的设计、制造、安装和服务。</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>啤酒</t>
-        </is>
-      </c>
+          <t>ST股 | 公司主营业务为微波毫米波模拟相控阵T/R芯片的研发、生产、销售和技术服务，产品已应用于探测、遥感、通信、导航、电子对抗等领域。</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>2026年1-2月，国内实现社零总额8.61万亿元，同比增长2.8%，环比提升1.9pct。</t>
-        </is>
-      </c>
+        <v>0.41</v>
+      </c>
+      <c r="C55" s="2" t="inlineStr"/>
       <c r="D55" s="2" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>sz300858</t>
+          <t>sz002808</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>科拓生物</t>
+          <t>*ST恒久</t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>18.19</v>
+        <v>4.94</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>19.99</v>
-      </c>
-      <c r="I55" s="2" t="inlineStr"/>
+        <v>5.11</v>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>食品添加剂|公司是一家主要从事复配食品添加剂、食用益生菌制品以及动植物微生态制剂研发、生产与销售的高新技术企业。</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>食品添加剂</t>
-        </is>
-      </c>
+          <t>ST股 | 公司的控股子公司福建省闽保信息技术有限公司是一家从事信息安全领域软件开发及系统集成的高新技术企业。</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>3月26日，中国算力平台（贵州）建设工作在贵阳启动。贵州省通信管理局、中国信息通信研究院、贵州省内基础电信企业、相关互联网数据中心企业等单位代表参加启动建设工作。</t>
-        </is>
-      </c>
+        <v>0.41</v>
+      </c>
+      <c r="C56" s="2" t="inlineStr"/>
       <c r="D56" s="2" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>sh600666</t>
+          <t>sz002713</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">奥瑞德  </t>
+          <t>*ST东易</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>6.08</v>
+        <v>12.36</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>9.950000000000001</v>
+        <v>5.01</v>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>8天5板</t>
+          <t>4天2板</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>算力租赁|公司设立全资子公司北京智算力、深圳智算力，使用自有资金投资建设算力租赁一、二、三期项目。</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>算力租赁</t>
-        </is>
-      </c>
+          <t>ST股 | 公司基于数字化系统优势和业务场景优势，研发推出了行业内首个新一代AIGC技术和真家系统结合的全新设计工具“真家 AIGC”，同时打造出AI 创意大师、AI小白设计家两款智能应用设计工具。</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>3月26日，中国算力平台（贵州）建设工作在贵阳启动。贵州省通信管理局、中国信息通信研究院、贵州省内基础电信企业、相关互联网数据中心企业等单位代表参加启动建设工作。</t>
-        </is>
-      </c>
+        <v>0.41</v>
+      </c>
+      <c r="C57" s="2" t="inlineStr"/>
       <c r="D57" s="2" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>sh600996</t>
+          <t>sh603261</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>贵广网络</t>
+          <t xml:space="preserve">*ST立航 </t>
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>10.02</v>
+        <v>34.49</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I57" s="2" t="inlineStr"/>
+        <v>4.99</v>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>贵州算力|据中国信通院消息，3月26日，中国算力平台（贵州）建设工作在贵阳启动。贵州广播电视台旗下上市公司。公司将致力于贵州与粤港澳、长三角、京津冀等地区大数据中心集群的算力资源对接，充分发挥贵州省作为南方数据中心示范基地优势，有效承接东部算力需求。</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>贵州算力</t>
-        </is>
-      </c>
+          <t>ST股 | 公司是以飞机地面保障设备、航空器试验和检测设备、飞机工艺装备、飞机零件加工和飞机部件装配等专业研发、设计、制造、销售为一体的军民融合企业。</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>3月26日，中国算力平台（贵州）建设工作在贵阳启动。贵州省通信管理局、中国信息通信研究院、贵州省内基础电信企业、相关互联网数据中心企业等单位代表参加启动建设工作。</t>
-        </is>
-      </c>
+        <v>0.41</v>
+      </c>
+      <c r="C58" s="2" t="inlineStr"/>
       <c r="D58" s="2" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>sz002042</t>
+          <t>sz002424</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>华孚时尚</t>
+          <t>ST百灵</t>
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>4.42</v>
+        <v>5.07</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>9.950000000000001</v>
+        <v>4.97</v>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>算力租赁|2024年1月2日公告，公司全资子公司浙江华孚计划投资“上虞华尚数智中心AIGC智算中心项目”，项目规划建设规模3000PFLOPS AI算力。</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>算力租赁</t>
-        </is>
-      </c>
+          <t>ST股 | 公司是我国最大的苗药研发、生产企业之一,贵州中药行业的龙头企业，国内中药行业的知名企业。</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>国家统计局数据显示，1—2月份，有色金属冶炼和压延加工业利润增长1.5倍。</t>
-        </is>
-      </c>
+        <v>0.41</v>
+      </c>
+      <c r="C59" s="2" t="inlineStr"/>
       <c r="D59" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>sz002842</t>
+          <t>sz000668</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>翔鹭钨业</t>
+          <t>*ST荣控</t>
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>33.13</v>
+        <v>14.7</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>9.99</v>
+        <v>5</v>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>钨|公司一直专注于钨制品的开发、生产与销售，主要产品包括各种规格的氧化钨、钨粉、碳化钨粉、钨合金粉及钨硬质合金等。公司是国内钨行业具备完整产业链的企业之一，从钨精矿采选、仲钨酸铵冶炼、氧化钨、钨粉、碳化钨粉、硬质合金及其工具等全系列钨产品的生产。公司是商务部批准的14家"钨品国营贸易出口资格企业"之一。</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>钨</t>
-        </is>
-      </c>
+          <t>ST股 | 公司主营业务为房地产开发，经营模式以自主开发销售为主，曾推出国内第一个小户型楼盘，第一家运动主题社区，在业内产生较大影响。</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>国家统计局数据显示，1—2月份，有色金属冶炼和压延加工业利润增长1.5倍。</t>
-        </is>
-      </c>
+        <v>0.41</v>
+      </c>
+      <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>sh603132</t>
+          <t>sz000972</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>金徽股份</t>
+          <t>*ST中基</t>
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>16.73</v>
+        <v>3.99</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>9.99</v>
+        <v>5</v>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>锌+铅|公司主营业务为有色金属采选，主要产品为锌精矿、铅精矿（含银），已形成178万吨/年的矿石采选能力，成为甘肃省内生产规模较大和效益较好的绿色矿山企业。</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>锌, 铅</t>
-        </is>
-      </c>
+          <t>ST股 | 公司依托新疆得天独厚的地域和自然优势，致力于发展番茄“红色产业”，产业规模居于前列，产品行销世界数十国家和地区，是全球主要食品企业长期、固定的原料供应商。</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>SEMI中国总裁冯莉表示，在AI算力以及全球数字化经济驱动下，全球半导体产业迎来了历史性时刻，原定于2030年才会达到的万亿美元芯时代有望于2026年底提前到来。</t>
-        </is>
-      </c>
+        <v>0.41</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr"/>
       <c r="D61" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>sh603324</t>
+          <t>sh603838</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>盛剑科技</t>
+          <t xml:space="preserve">*ST四通 </t>
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>25.5</v>
+        <v>8.76</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>10.01</v>
+        <v>5.04</v>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>洁净室|公司为华为武汉研发生产项目-海思光工厂洁净室提供工艺废气治理系统。</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>洁净室</t>
-        </is>
-      </c>
+          <t>ST股 | 公司是一家集研发、设计、生产、销售于一体的新型家居生活陶瓷供应商，产品覆盖日用陶瓷、卫生陶瓷、艺术陶瓷、建筑装饰等全系列家居生活用瓷。</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>SEMI中国总裁冯莉表示，在AI算力以及全球数字化经济驱动下，全球半导体产业迎来了历史性时刻，原定于2030年才会达到的万亿美元芯时代有望于2026年底提前到来。</t>
-        </is>
-      </c>
+        <v>0.41</v>
+      </c>
+      <c r="C62" s="2" t="inlineStr"/>
       <c r="D62" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>sh603002</t>
+          <t>sh603580</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>宏昌电子</t>
+          <t xml:space="preserve">*ST艾艾 </t>
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>10.34</v>
+        <v>17.36</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>10</v>
+        <v>5.02</v>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>先进封装+PCB|1.2023年6月26日公告，全资子公司珠海宏昌与晶化科技合作，在先进封装过程中集成电路载板之增层膜新材料,或特定产品开展密切的研发及销售合作关系。
-2.公司主要从事电子级环氧树脂、覆铜板两大类产品的生产和销售，覆铜板主营产品为多层板用环氧玻璃布覆铜板、多层板用环氧玻璃布半固化片。</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>先进封装, PCB</t>
-        </is>
-      </c>
+          <t>ST股 | 公司是专业从事为轻型输送带的研发、生产及销售，境外营业收入大于50%。</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>中国信息通信研究院联合40余家单位共同起草的具身智能领域首个行业标准3月26日正式发布。</t>
-        </is>
-      </c>
+        <v>0.41</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr"/>
       <c r="D63" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>sz002265</t>
+          <t>sh600381</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>建设工业</t>
+          <t xml:space="preserve">*ST春天 </t>
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>25.03</v>
+        <v>3</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>4.9</v>
+      </c>
+      <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>军工+机器人|公司在第十五届中国国际航空航天博览会轻武器展区展出的多功能足式机器人、小型室内清剿机器人、小型智能察打机器人、便携式无人飞行枪械系统、班组多旋翼察打无人机等。</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>军工, 机器人</t>
-        </is>
-      </c>
+          <t>ST股 | 在大健康业务方面，公司已基本完成了涵盖保健食品、药品等冬虫夏草高效利用产品的储备和战略布局。</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>中国信息通信研究院联合40余家单位共同起草的具身智能领域首个行业标准3月26日正式发布。</t>
-        </is>
-      </c>
+        <v>0.41</v>
+      </c>
+      <c r="C64" s="2" t="inlineStr"/>
       <c r="D64" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>sz002526</t>
+          <t>sz002168</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>山东矿机</t>
+          <t>*ST惠程</t>
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>3.66</v>
+        <v>3.98</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>9.91</v>
+        <v>5.01</v>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>无人机+机器人|1.公司旗下全资子公司山东长空雁航空科技有限责任公司是从事低空无人机研发、生产、维修、销售和技术咨询，具备微型涡喷发动机关键零部件加工的公司。 
-2.公司具有高尖端的加工装备、成熟可靠的技术工艺以及优良的职工队伍，自行研制的机器人和自动化生产线。</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>无人机, 机器人</t>
-        </is>
-      </c>
+          <t>ST股 | 公司旗下控股子公司哆可梦以基于大数据精细化营销的流量经营业务和移动游戏的研发、发行及游戏平台的运营为主营业务</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>3月23日，国家电力投资集团有限公司举行2026年第一次新闻通气会。国家电投计划今年投资2000亿元，同比增长17%。其中，一季度要完成投资230亿元，实现同比增长35%。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr"/>
       <c r="D65" s="2" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>sz000720</t>
+          <t>sh600539</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>新能泰山</t>
+          <t>狮头股份</t>
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>5.51</v>
+        <v>15.63</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>9.98</v>
+        <v>9.99</v>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>4天4板</t>
+          <t>5天4板</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>电线电缆+光纤光缆|子公司曲阜电缆主要从事电线电缆、光纤光缆、电力光缆等产品的研发、制造与销售，曲阜电缆生产、 销售的电线电缆产品是公司重点发展的智慧供应链业务产品之一。</t>
+          <t>并购重组|2025年3月7日公告，公司拟以发行股份及支付现金方式向王旭龙琦等14名交易对方收购杭州利珀科技100%股权，同时向上市公司实控人旗下企业募集配套资金。本次交易预计构成重大资产重组。标的公司自成立以来一直致力于机器视觉相关技术产品的研发、生产与销售。</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>电线电缆, 光纤光缆</t>
+          <t>并购重组</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>3月23日，国家电力投资集团有限公司举行2026年第一次新闻通气会。国家电投计划今年投资2000亿元，同比增长17%。其中，一季度要完成投资230亿元，实现同比增长35%。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr"/>
       <c r="D66" s="2" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>sh600268</t>
+          <t>sh600502</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>国电南自</t>
+          <t>安徽建工</t>
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>14.99</v>
+        <v>5.12</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>9.98</v>
+        <v>10.11</v>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>智能电网|公司产业涵盖电网自动化、电厂及工业自动化、轨道交通自动化、信息与安全技术、电力电子等五大核心板块，同时以生产制造和系统集成为支撑，主要在电力、工业、新能源等领域为客户提供配套自动化、信息化产品、集成设备及整体解决方案。</t>
+          <t>基建|公司是一家国有控股上市公司，主营业务包括工程施工、房地产开发、水电投资建设与运营。</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>基建</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>液冷IDC</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>随着算力持续放量与数据中心建设提速，液冷技术已从“可选配置”变为“强制标配”，市场即将迎来前所未有的机遇期。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr"/>
       <c r="D67" s="2" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>sh603090</t>
+          <t>sz301008</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>宏盛股份</t>
+          <t>宏昌科技</t>
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>65.44</v>
+        <v>35.24</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>10</v>
+        <v>19.99</v>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>液冷IDC|公司掌握液冷散热技术，能够为多种场景提供解决方案，同时，公司与苏州和信精密科技股份有限公司合资成立了无锡和宏智散热科技有限公司，和信精密是行业内领先的数据中心设备供应商，双方通过设立合资公司的形式，拓展数据中心环境温度控制业务。</t>
+          <t>投资张雪机车|在3月28日进行的世界超级摩托车锦标赛（WSBK）中量级赛事（葡萄牙站）中，法国车手Valentin Debise驾驶张雪机车（编号53）820RR-RS车型，以领先近4秒的优势强势夺冠。宏昌科技通过旗下投资基金间接投资了张雪机车。</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>液冷IDC</t>
+          <t>投资张雪机车</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>液冷IDC</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>随着算力持续放量与数据中心建设提速，液冷技术已从“可选配置”变为“强制标配”，市场即将迎来前所未有的机遇期。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr"/>
       <c r="D68" s="2" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>sz002272</t>
+          <t>sz002686</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>川润股份</t>
+          <t>亿利达</t>
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>17.66</v>
+        <v>7.89</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>10.03</v>
+        <v>10.04</v>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>液冷+华为概念|1.公司液冷技术在能源、工业等领域有多年成熟应用，在储能、数据中心、云计算、算力设备、通信网络、电力电网、电源转换等领域为客户提供液冷产品和温控节能解决方案。公司已实现服务器浸没式液冷产品“零”突破。
-2.2024年3月11日公司官微透露，华夏鲲鹏与川润在华灏鲲鹏西部产业基地隆重举行战略合作签约仪式。双方将在数字能源领域实现深度合作。</t>
+          <t>数据中心风机|公司EC风机产品可以应用于数据中心冷却设备，与国内多家精密空调制造企业有合作。</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>液冷, 华为概念</t>
+          <t>数据中心风机</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>商业航天</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="n">
-        <v>0.8699999999999999</v>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>2026年3月26日6时51分，我国在太原卫星发射中心使用长征二号丁运载火箭，成功将四维高景二号05、06星发射升空，卫星顺利进入预定轨道，发射任务取得圆满成功。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr"/>
       <c r="D69" s="2" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>sz002361</t>
+          <t>sh688693</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>神剑股份</t>
+          <t xml:space="preserve">锴威特  </t>
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>13.64</v>
+        <v>54.9</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>商业航天|公司参与了星网项目建设，提供卫星上相关零部件。目前航天类产品有卫星天线、反射器及支撑塔等。</t>
+          <t>并购重组|锴威特公告称，公司拟通过发行股份及支付现金方式向易坤、晶格共智、晶格共创、晶格共赢、晶格顶峰、晶格未来等26名交易对方购买其合计持有的晶艺半导体100.00%股份，并募集配套资金。截至预案签署日，相关审计、评估工作尚未完成，标的资产财务数据及评估结果将在重组报告书中披露。本次交易预计构成重大资产重组。</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>商业航天</t>
+          <t>并购重组</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="n">
-        <v>1.2</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C70" s="2" t="inlineStr"/>
       <c r="D70" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>sz000908</t>
+          <t>sh603016</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>ST景峰</t>
+          <t xml:space="preserve">新宏泰  </t>
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>7.77</v>
+        <v>45.02</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>17天13板</t>
-        </is>
-      </c>
+        <v>9.99</v>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司专注医药健康产业，涉足药品研发、生产、销售等领域，产品涵盖了心脑血管、抗肿瘤、骨科、妇儿等用药领域。</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr"/>
+          <t>电网设备|公司主营业务为断路器关键部件，低压断路器及刀熔开关的研发，生产与销售，公司实控人为无锡市人民政府国有资产监督管理委员会。</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>电网设备</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="n">
-        <v>1.2</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C71" s="2" t="inlineStr"/>
       <c r="D71" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>sz002620</t>
+          <t>sz003036</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>ST瑞和</t>
+          <t>泰坦股份</t>
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>8.69</v>
+        <v>27.1</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>5天5板</t>
-        </is>
-      </c>
+        <v>9.98</v>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司主要从事政府机构、房地产开发商、大型企业、高档酒店、交通枢纽、园林绿化等综合性专业化装饰设计、工程施工业务以及光伏电站运营、光伏项目施工安装等。</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr"/>
+          <t>机器人+固态电池|1.2026年2月2日公司在互动平台表示，公司纺织智能柔性操作机器人研发进展顺利，相关产品目前处于运行测试和进一步优化阶段。
+2.公司设立了控股子公司，主要从事固态电池锂硫磷氯电解质的研发和生产。</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>机器人, 固态电池</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="n">
-        <v>1.2</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C72" s="2" t="inlineStr"/>
       <c r="D72" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>sz002199</t>
+          <t>sz300385</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>*ST东晶</t>
+          <t>雪浪环境</t>
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>19.82</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>4天4板</t>
-        </is>
-      </c>
+        <v>19.98</v>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司致力于高精度、高稳定性、高品质石英晶体元器件系列产品的研发、设计与生产。公司与日本松下、索尼、东芝、夏普、 JVC，以及韩国三星、LG 和国内华为、中兴、 OPPO、小米等公司保持长期稳定的战略合作关系。</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr"/>
+          <t>重整|雪浪环境公告称，公司与上海氦星万联科技发展合伙企业(有限合伙)等四方及预重整引导人签署《重整投资协议》，并与上海氦星光曜科技发展合伙企业签署附属协议。根据协议，重整完成后氦星万联将成为公司控股股东。</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>重整</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="n">
-        <v>1.2</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C73" s="2" t="inlineStr"/>
       <c r="D73" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>sz000638</t>
+          <t>sh603256</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>*ST万方</t>
+          <t>宏和科技</t>
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>1.48</v>
+        <v>72.14</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>6天4板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司业务主要包括军工产业、农业产业以及生物制品等业务。公司控股子公司万方迈捷以粮库收储为核心，深入研究粮食加工、研究土地流转、研究农民就业，万方迈捷作为乾安县唯一一家自主加工的大米企业。</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr"/>
+          <t>电子玻纤布|公司是全球领先的中高端电子级玻璃纤维布专业厂商，是全球少数具备极薄布生产能力的厂商之一。公司主要产品为中高端电子级玻璃纤维布系列产品，为制造电子产品核心铜箔基板的重要原料。</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>电子玻纤布</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="n">
-        <v>1.2</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C74" s="2" t="inlineStr"/>
       <c r="D74" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>sh603429</t>
+          <t>sh603061</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST集友 </t>
+          <t xml:space="preserve">金海通  </t>
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>9.359999999999999</v>
+        <v>284.67</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>5.050000000000001</v>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 子公司集新能源主要在固态电池方向系统地开展关键材料研究。</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr"/>
+          <t>半导体设备|公司是一家从事研发、生产并销售半导体芯片测试设备的高新技术企业，深耕集成电路测试分选机（Test handler）领域，其UPH（单位小时产出）最大可达到13500颗，可测试芯片尺寸范围可涵盖2*2mm~100*100mm。</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>半导体设备</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="n">
-        <v>1.2</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C75" s="2" t="inlineStr"/>
       <c r="D75" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>sz002569</t>
+          <t>sz002634</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>*ST步森</t>
+          <t>棒杰股份</t>
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>14.67</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.01</v>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 主营业务为“步森”品牌男装的设计、生产和销售。</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr"/>
+          <t>重整+光伏|1.棒杰股份2月2日公告,公司及子公司扬州棒杰近日收到扬州经开区法院送达的《民事裁定书》,法院于1月30日裁定受理兴业银行苏州分行对扬州棒杰的重整申请。
+2.公司拟投资设立全资子公司棒杰新能源集团有限公司布局光伏产业，注册资本为5亿元。从而形成“无缝服装+光伏”双主业的业务结构。公司与江苏诺信就扬州经开区600MW地面光伏电站一期240MW农光互补项目建设等合作。</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>重整, 光伏</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="n">
-        <v>1.2</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C76" s="2" t="inlineStr"/>
       <c r="D76" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>sh605081</t>
+          <t>sh600724</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST太和 </t>
+          <t>宁波富达</t>
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>7.8</v>
+        <v>6.39</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>4.98</v>
+        <v>9.98</v>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 1.公司是水环境生态治理行业内的专业公司，主要采用生物-生态方式对富营养化水体进行水环境生态修复与构建。
-2.公司饮用水项目的水源位于黑龙江省拜泉县，是我国仅有的三大天然苏打水水源点之一，占据着得天独厚的资源优势。</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr"/>
+          <t>房地产|公司的最终控制人为宁波市人民政府国有资产监督管理委员会。公司主营商业地产的出租、自营联营及托管业务，其中包括物业管理 。</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>房地产</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="n">
-        <v>1.2</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C77" s="2" t="inlineStr"/>
       <c r="D77" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>sz002024</t>
+          <t>sh603358</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>ST易购</t>
+          <t>华达科技</t>
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>1.4</v>
+        <v>33.33</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>5.26</v>
+        <v>10</v>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 已经形成零售、金融、物流三大业务单元协同发展。</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C78" s="2" t="inlineStr"/>
-      <c r="D78" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>sh600599</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">*ST熊猫 </t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="H78" s="2" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 公司地处中国烟花之乡浏阳，经过3多年的发展已成为中国最大的出口鞭炮烟花公司</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C79" s="2" t="inlineStr"/>
-      <c r="D79" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>sz002731</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>ST萃华</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="n">
-        <v>7.79</v>
-      </c>
-      <c r="H79" s="2" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 公司是主要从事珠宝饰品设计、加工、批发和零售的“中华老字号”企业，产品以黄金饰品为主，兼营铂金饰品、镶嵌饰品等珠宝饰品。</t>
-        </is>
-      </c>
-      <c r="K79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C80" s="2" t="inlineStr"/>
-      <c r="D80" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>sz000615</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>*ST美谷</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="H80" s="2" t="n">
-        <v>5.029999999999999</v>
-      </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 公司主要开展医美科技、医美材料和医美服务三大板块业务</t>
-        </is>
-      </c>
-      <c r="K80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C81" s="2" t="inlineStr"/>
-      <c r="D81" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>sz002305</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>*ST南置</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="H81" s="2" t="n">
-        <v>4.850000000000001</v>
-      </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 公司是一家武汉市以商业地产为引导的综合性物业开发企业。</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C82" s="2" t="inlineStr"/>
-      <c r="D82" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>sz000903</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>ST云动</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H82" s="2" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 公司于2024年9月14日公告披露与九识智能签署了《战略合作协议》，开展L4级智能配送机器人业务，正在按照战略协议要求开展相关准备工作。此外，公司生产的智能物流配送样车正在申请道路测试。</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C83" s="2" t="inlineStr"/>
-      <c r="D83" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>sz000488</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>ST晨鸣</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="H83" s="2" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 公司是全国唯一一家实现制浆和造纸平衡的大型浆纸一体化企业，率先布局全产业链，在山东、广东、湖北、江西、吉林等地建有6个生产基地，年浆纸产能达1100多万吨。</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C84" s="2" t="inlineStr"/>
-      <c r="D84" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>sz002122</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>ST汇洲</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="H84" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 1.公司旗下中能数投专注于数据中心和算力中心建设、运宫、运维以及提供云计算、数据中心、和算力平台服务，拟在衢州智造新城辖区范围内投资建设智算中心项目。
-2.控股子公司热热文化在技术体系的支撑下，为客户提供百联网内容审核以及技术服务业务，目前业务已在一定程度上应用了人工智能审核，今后也将在现有基础上不断完善和发展。</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr"/>
-      <c r="D85" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>sh605299</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>舒华体育</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="n">
-        <v>19.25</v>
-      </c>
-      <c r="H85" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>10天5板</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>体育产业|公司主营业务为健身器材和展示架产品的研发、生产和销售，其中健身器材包括室内健身器材、室外路径产品。</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>体育产业</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr"/>
-      <c r="D86" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>sh600539</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>狮头股份</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="n">
-        <v>14.21</v>
-      </c>
-      <c r="H86" s="2" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>4天3板</t>
-        </is>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>机器视觉|2025年3月7日公告，公司拟以发行股份及支付现金方式向王旭龙琦等14名交易对方收购杭州利珀科技100%股权，同时向上市公司实控人旗下企业募集配套资金。本次交易预计构成重大资产重组。标的公司自成立以来一直致力于机器视觉相关技术产品的研发、生产与销售。</t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>机器视觉</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr"/>
-      <c r="D87" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>sh603115</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>海星股份</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="n">
-        <v>43.43</v>
-      </c>
-      <c r="H87" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>电极箔|公司主营产品电极箔可应用于MLPC电容器。MLPC产品可广泛应用于服务器中高功耗芯片的供电滤波场景，特别是CPU和GPU的核心电压供电。</t>
-        </is>
-      </c>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>电极箔</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr"/>
-      <c r="D88" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>sz002995</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>天地在线</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="n">
-        <v>23.65</v>
-      </c>
-      <c r="H88" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>AI应用|公司已推出AI数字人SAAS产品“星河AI数字人系统”以及帮助企业提高工作效率和协作能力的AI智能应用产品“AIbase” ，满足客户在营销及提升企业经营效能的不同需求。</t>
-        </is>
-      </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>AI应用</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr"/>
-      <c r="D89" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>sh600769</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>祥龙电业</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="H89" s="2" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>水务|公司的最终控制人为武汉东湖新技术开发区管理委员会。公司的主要业务为供水业务和建筑业务。</t>
-        </is>
-      </c>
-      <c r="K89" s="2" t="inlineStr">
-        <is>
-          <t>水务</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr"/>
-      <c r="D90" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>sh603248</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>锡华科技</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="n">
-        <v>29.04</v>
-      </c>
-      <c r="H90" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>次新+风电|公司主要从事大型高端装备专用部件的研发、制造与销售，产品结构以风电齿轮箱专用部件为主、注塑机厚大专用部件为辅，是全球行业领先、质量可靠、技术卓越的大型高端装备专用部件制造商。</t>
-        </is>
-      </c>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>次新, 风电</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr"/>
-      <c r="D91" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>sz001313</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>粤海饲料</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="H91" s="2" t="n">
-        <v>10.04</v>
-      </c>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>水产饲料|公司主要从事水产饲料研发、生产及销售,并以虾料、海水鱼料等特种水产饲料为主。</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>水产饲料</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr"/>
-      <c r="D92" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>sz002328</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>新朋股份</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="H92" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>储能|新朋股份公告称，公司下属全资子公司泰国英诺实业与美国捷普公司签署《电池储能系统项目》投资合作协议，围绕电池储能系统中大型箱体等项目共同投资开发合作。</t>
-        </is>
-      </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>储能</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr"/>
-      <c r="D93" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>sz300461</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>田中精机</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="n">
-        <v>55.63</v>
-      </c>
-      <c r="H93" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>电感|公司研发投入包括：一体成型电感智能成套生产设备研发。项目目的为电感是用绝缘导线绕制而成的电磁感应元件，也是电子电路中常用的元器件之一。</t>
-        </is>
-      </c>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>电感</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr"/>
-      <c r="D94" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>sh600748</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>上实发展</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="H94" s="2" t="n">
-        <v>10.04</v>
-      </c>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>房地产|公司控股股东为上海实业控股有限公司，公司主营业务为房地产开发与经营。</t>
-        </is>
-      </c>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>房地产</t>
+          <t>增持|华达科技公告称，基于对公司发展前景的信心和公司股票长期投资价值的认可，股东张耀坤计划6个月内以集中竞价或大宗交易方式增持公司A股股份，累计增持金额不低于2亿元且不超过3亿元，增持价格不超过70元/股。</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>增持</t>
         </is>
       </c>
     </row>
@@ -4730,7 +3967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4757,46 +3994,46 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sz000720</t>
+          <t>sh603538</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>新能泰山</t>
+          <t xml:space="preserve">美诺华  </t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sh603538</t>
+          <t>sz002361</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">美诺华  </t>
+          <t>神剑股份</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sz002192</t>
+          <t>sh600996</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>融捷股份</t>
+          <t>贵广网络</t>
         </is>
       </c>
     </row>
@@ -4806,12 +4043,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sh603026</t>
+          <t>sh600539</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>石大胜华</t>
+          <t>狮头股份</t>
         </is>
       </c>
     </row>
@@ -4821,12 +4058,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sz000767</t>
+          <t>sz002038</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>晋控电力</t>
+          <t>双鹭药业</t>
         </is>
       </c>
     </row>
@@ -4836,12 +4073,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sz002082</t>
+          <t>sh603585</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>万邦德</t>
+          <t>苏利股份</t>
         </is>
       </c>
     </row>
@@ -4851,12 +4088,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>sh600844</t>
+          <t>sh600513</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>金煤科技</t>
+          <t>联环药业</t>
         </is>
       </c>
     </row>
@@ -4866,12 +4103,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>sh600310</t>
+          <t>sh603618</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>广西能源</t>
+          <t>杭电股份</t>
         </is>
       </c>
     </row>
@@ -4881,12 +4118,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>sz002361</t>
+          <t>sz003042</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>神剑股份</t>
+          <t>中农联合</t>
         </is>
       </c>
     </row>
@@ -4896,12 +4133,42 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>sz002263</t>
+          <t>sz002432</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>大东南</t>
+          <t>九安医疗</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>sz000890</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>法尔胜</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>sh600488</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>津药药业</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,19 +476,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K77"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="103" customWidth="1" min="3" max="3"/>
+    <col width="100" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="291" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="216" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -552,246 +552,234 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>高铁轨交</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.98</v>
+        <v>0.62</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>据国家药监局消息，今年前三个月，我国创新药对外授权交易总额超过600亿美元，接近2025年全年的一半。</t>
+          <t>央视财经报道，长江入海口，“十五五”重大工程——沿江高铁的标志性项目正加紧施工，沿江高铁总投资超5000亿元。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>sh603538</t>
+          <t>sz000927</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">美诺华  </t>
+          <t>中国铁物</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>43.1</v>
+        <v>3.34</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10.01</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>7天6板</t>
+          <t>5天3板</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>减肥药|2026年3月19日公司在官微公布益生菌（JH389）胶囊产品临床数据，结果显示，服用该产品8周可显著改善受试者体重、体脂及肥胖相关指标，有助于全面提升生活质量、有助于正向调节肠道菌群结构，同时对糖脂代谢及各项安全性指标无不良影响。</t>
+          <t>高铁+物流|围绕路网安全和降本增效，公司开展了铁路专用检测设备研发、线路综合检测、钢轨道岔廓形设计、高铁轨道线路斜裂纹检测、高铁铁路轨道精调、钢轨焊接、大小机打磨集成服务、施工监测、道岔大修等线路综合运维集成服务，形成了完整的线路运维服务体系。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>减肥药</t>
+          <t>高铁, 物流</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>高铁轨交</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.98</v>
+        <v>0.62</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>据国家药监局消息，今年前三个月，我国创新药对外授权交易总额超过600亿美元，接近2025年全年的一半。</t>
+          <t>央视财经报道，长江入海口，“十五五”重大工程——沿江高铁的标志性项目正加紧施工，沿江高铁总投资超5000亿元。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sz002038</t>
+          <t>sz000008</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>双鹭药业</t>
+          <t>神州高铁</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>7.27</v>
+        <v>3.27</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>9.98</v>
+        <v>10.1</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>4天3板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>创新药|公司目前具有较强竞争力的储备品种有包括即将上市的G-CSF长效制剂、人促卵泡激素长、短效制剂，GLP-1类似物长、短效和双靶点制剂，心脑血管领域开发的创新药和特色仿制药等。</t>
+          <t>高铁+机器人|1.公司提供轨道交通运营维护全产业链智能装备系统，并以此为依托，提供轨道交通运营及维保专业服务，是中国轨道交通运营维护领域首家涵盖全产业链装备及运营维保服务的上市公司。
+2.神州高铁在互动平台表示，近年来，公司积极加强智能化、数字化产品研发，动车组空心车轴超声检测机器人、动车组车轮超声检测机器人等智能产品已进入样机测试阶段。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>高铁, 机器人</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>高铁轨交</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.98</v>
+        <v>0.62</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>据国家药监局消息，今年前三个月，我国创新药对外授权交易总额超过600亿美元，接近2025年全年的一半。</t>
+          <t>央视财经报道，长江入海口，“十五五”重大工程——沿江高铁的标志性项目正加紧施工，沿江高铁总投资超5000亿元。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sh600488</t>
+          <t>sz301048</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>津药药业</t>
+          <t>金鹰重工</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>4.76</v>
+        <v>13.09</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>19.98</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>原料药|公司主要从事皮质激素类、氨基酸类原料药及制剂的研发、生产和销售，产品包括地塞米松系列、泼尼松系列、甲泼尼龙系列、倍他米松系列等40余个皮质激素原料药品种，23个氨基酸原料药品种，以及16个剂型药品。</t>
+          <t>高铁|公司是国内领先的轨道工程装备产品供应商，是国铁集团系统内唯一取得相关产品型号合格证和制造许可并能够研制并生产轨道工程装备的企业。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>原料药</t>
+          <t>高铁</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>高铁轨交</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.98</v>
+        <v>0.62</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>据国家药监局消息，今年前三个月，我国创新药对外授权交易总额超过600亿美元，接近2025年全年的一半。</t>
+          <t>央视财经报道，长江入海口，“十五五”重大工程——沿江高铁的标志性项目正加紧施工，沿江高铁总投资超5000亿元。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sh600513</t>
+          <t>sh600528</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>联环药业</t>
+          <t>中铁工业</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>28.17</v>
+        <v>9.17</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.950000000000001</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>创新药|主要产品有创新药物爱普列特片(川流)，新药依巴斯汀片(苏迪)、非洛地平片(联环尔定)、非洛地平缓释胶囊(联环笑定)等二十多个。</t>
+          <t>高铁+盾构机|公司是中国中铁重组整合中铁山桥、中铁宝桥、中铁科工和中铁装备成立的专业从事隧道掘进设备、铁路道岔、钢桥梁、大型铁路施工机械以及新型轨道交通的研发设计、制造安装和技术服务的企业集团。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>高铁, 盾构机</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>高铁轨交</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.98</v>
+        <v>0.62</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>据国家药监局消息，今年前三个月，我国创新药对外授权交易总额超过600亿美元，接近2025年全年的一半。</t>
+          <t>央视财经报道，长江入海口，“十五五”重大工程——沿江高铁的标志性项目正加紧施工，沿江高铁总投资超5000亿元。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sz002432</t>
+          <t>sh600495</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>九安医疗</t>
+          <t>晋西车轴</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>75.5</v>
+        <v>4.93</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.04</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>医疗器械+kimi|1.公司是一家在国内外具有影响力的个人健康管理产品供应商，主要从事家用医疗器械的研发、生产及销售。
-2.公司通过认购砺思资本基金份额参股Kimi。</t>
+          <t>高铁|公司控股股东是中国兵器工业集团旗下晋西工业集团，公司是国内外铁路装备行业车轴细分领域中最具影响力的供应商之一。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>医疗器械, kimi</t>
+          <t>高铁</t>
         </is>
       </c>
     </row>
@@ -802,41 +790,45 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.98</v>
+        <v>-0.6</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>据国家药监局消息，今年前三个月，我国创新药对外授权交易总额超过600亿美元，接近2025年全年的一半。</t>
+          <t>据媒体报道，4月17日至22日，美国癌症研究协会（AACR）年会将在圣地亚哥举行，104家中国药企将携250余款创新药亮相。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sz002675</t>
+          <t>sz002082</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>东诚药业</t>
+          <t>万邦德</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>14.48</v>
+        <v>30.2</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
+        <v>10.02</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6天4板</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>创新药|公司着力打造放射性诊疗一体化药物创新平台——烟台蓝纳成，其具有放射性诊疗一体化药物创新研发和全球领先的纳米递送技术的特点，适应症涵盖前列腺癌、胃癌、结直肠癌、鼻咽癌等多种癌症的诊断与治疗产品，其中部分产品进行中美双报。</t>
+          <t xml:space="preserve">创新药+AI|在研发端，公司探索人工智能在创新药设计、筛选、实验设计等环节的应用，目前全球首个治疗胃轻瘫的中药1.1类新药“理中消痞颗粒”正在开展临床研究。 </t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>创新药, AI</t>
         </is>
       </c>
     </row>
@@ -847,41 +839,45 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.98</v>
+        <v>-0.6</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>据国家药监局消息，今年前三个月，我国创新药对外授权交易总额超过600亿美元，接近2025年全年的一半。</t>
+          <t>据媒体报道，4月17日至22日，美国癌症研究协会（AACR）年会将在圣地亚哥举行，104家中国药企将携250余款创新药亮相。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sz002370</t>
+          <t>sh600488</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>亚太药业</t>
+          <t>津药药业</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>7.18</v>
+        <v>5.24</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>9.950000000000001</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
+        <v>10.08</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>创新药|截止2024年年报，公司二类新药右旋酮洛芬缓释贴片II期a临床已经结束，尚在评估是否需要开展II期b。</t>
+          <t>原料药|公司主要从事皮质激素类、氨基酸类原料药及制剂的研发、生产和销售，产品包括地塞米松系列、泼尼松系列、甲泼尼龙系列、倍他米松系列等40余个皮质激素原料药品种，23个氨基酸原料药品种，以及16个剂型药品。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>原料药</t>
         </is>
       </c>
     </row>
@@ -892,41 +888,42 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.98</v>
+        <v>-0.6</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>据国家药监局消息，今年前三个月，我国创新药对外授权交易总额超过600亿美元，接近2025年全年的一半。</t>
+          <t>据媒体报道，4月17日至22日，美国癌症研究协会（AACR）年会将在圣地亚哥举行，104家中国药企将携250余款创新药亮相。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>sz002821</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>凯莱英</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>110.77</v>
+      </c>
+      <c r="H9" s="2" t="n">
         <v>10</v>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>sh688677</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>海泰新光</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>47.83</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>19.99</v>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>医疗器械|公司是医用成像器械行业的高新技术企业，主要从事医用内窥镜器械和光学产品的研发、生产和销售。</t>
+          <t>业绩+CRO|1.凯莱英公告称，公司发布2025年年度报告，实现营业收入66.70亿元，同比增长14.91%；归属于上市公司股东的净利润11.33亿元，同比增长19.35%。公司拟向全体股东每10股派发现金红利13元(含税)，送红股0股，不以公积金转增股本。
+2.公司是一家全球领先、技术驱动型的医药外包服务一站式综合服务商，通过为国内外制药公司、生物技术公司提供药品全生命周期的一站式CMC服务、高效和高质量的研发与生产服务。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>医疗器械</t>
+          <t>业绩, CRO</t>
         </is>
       </c>
     </row>
@@ -937,42 +934,41 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.98</v>
+        <v>-0.6</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>据国家药监局消息，今年前三个月，我国创新药对外授权交易总额超过600亿美元，接近2025年全年的一半。</t>
+          <t>据媒体报道，4月17日至22日，美国癌症研究协会（AACR）年会将在圣地亚哥举行，104家中国药企将携250余款创新药亮相。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sh603716</t>
+          <t>sh605116</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>塞力医疗</t>
+          <t xml:space="preserve">奥锐特  </t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>22.75</v>
+        <v>29.39</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>10.01</v>
+        <v>9.99</v>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>创新药+AI|1.公司战略投资的心血管领域长效治疗性疫苗的创新性研发公司——武汉华纪元生物技术开发有限公司，其自主研发国家1类生物创新药HJY-ATRQβ-001正式获得国家药品监督管理局（NMPA）的新药临床试验申请（IND）受理通知书。
-2.公司作为以“人工智能+医疗大数据”为基础的智慧医疗综合体系建设供应商，始终聚焦医疗技术更新迭代与医疗领域应用场景的创新融合。</t>
+          <t>创新药|参股源道医药聚焦慢病领域，致力于 FIRST-IN-CLASS 原创新药的自主研发；利用研究团队在人工智能药物设计方面特有的技术优势，通过精准药物设计高效地发现新药先导物，充分分析临床数据快速推进慢病个性化和精准化治疗药物的发现。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>创新药, AI</t>
+          <t>创新药</t>
         </is>
       </c>
     </row>
@@ -983,585 +979,590 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.98</v>
+        <v>-0.6</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>据国家药监局消息，今年前三个月，我国创新药对外授权交易总额超过600亿美元，接近2025年全年的一半。</t>
+          <t>据媒体报道，4月17日至22日，美国癌症研究协会（AACR）年会将在圣地亚哥举行，104家中国药企将携250余款创新药亮相。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>sz002788</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>鹭燕医药</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>16.17</v>
+      </c>
+      <c r="H11" s="2" t="n">
         <v>10</v>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>sh603122</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>合富中国</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>16.92</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>10.01</v>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>医药+海峡两岸概念|1.公司系医疗流通领域的渠道商，具备与境内外试剂耗材和医疗设备原厂、各大代理商及医疗机构长期互惠、合作共赢的核心竞争力。
-2.公司为唯一一家海峡两岸市场“双上市”的医疗企业，其母公司合富医疗控股在台湾上市，公司实际控制人为台湾企业家王琼芝，在两岸医疗流通领域有深度合作。</t>
+          <t>医药+福建|公司从事医药分销和零售，隶属于医药流通行业，系福建省最大的医药流通企业。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>医药, 海峡两岸概念</t>
+          <t>医药, 福建</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>商业航天</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>1.43</v>
+        <v>-0.8</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>伊朗使用导弹和无人机“有效”打击了阿联酋和巴林境内与美国有关的铝厂。受此消息刺激，LME铝价在伊朗袭击中东工厂后上涨5%。</t>
+          <t>据中科宇航消息，3月30日19时，力箭二号遥一运载火箭在东风商业航天创新试验区发射，将新征程01卫星、新征程02卫星和天视卫星01星精准送入预定轨道，发射任务取得圆满成功。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sz002578</t>
+          <t>sz002361</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>闽发铝业</t>
+          <t>神剑股份</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>4.26</v>
+        <v>16.5</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>4天4板</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>铝+福建|公司是国内行业中较早涉足工业型材领域的企业之一，主营业务和产品主要是建筑铝型材、工业铝型材和建筑铝模板的研发、生产、销售。</t>
+          <t>商业航天|公司参与了星网项目建设，提供卫星上相关零部件。目前航天类产品有卫星天线、反射器及支撑塔等。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>铝, 福建</t>
+          <t>商业航天</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>商业航天</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>1.43</v>
+        <v>-0.8</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>伊朗使用导弹和无人机“有效”打击了阿联酋和巴林境内与美国有关的铝厂。受此消息刺激，LME铝价在伊朗袭击中东工厂后上涨5%。</t>
+          <t>据中科宇航消息，3月30日19时，力箭二号遥一运载火箭在东风商业航天创新试验区发射，将新征程01卫星、新征程02卫星和天视卫星01星精准送入预定轨道，发射任务取得圆满成功。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sz002160</t>
+          <t>sz002565</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>常铝股份</t>
+          <t>顺灏股份</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>5.49</v>
+        <v>17.01</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>10.02</v>
+        <v>10.03</v>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>铝|公司主要从事于铝板带箔的研发、生产和销售，其产品涵盖空调铝箔、合金铝箔等多个品种，主要用于下游空调器散热器和汽车热交换系统用铝材的生产制造，其中家电行业以的空调生产商居多。</t>
+          <t>太空算力|公司2025年6月以1.1亿元人民币投资北京轨道辰光科技有限公司，持股比例为19.30%。轨道辰光的主要业务是通过将算力卫星发射至晨昏轨道，组建太空数据中心，为客户提供算力服务，其经营范围包括微小卫星生产制造、微小卫星科研试验、互联网信息服务等。轨道辰光首颗试验星算力规模预计25p。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>铝</t>
+          <t>太空算力</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>商业航天</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>1.43</v>
+        <v>-0.8</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>伊朗使用导弹和无人机“有效”打击了阿联酋和巴林境内与美国有关的铝厂。受此消息刺激，LME铝价在伊朗袭击中东工厂后上涨5%。</t>
+          <t>据中科宇航消息，3月30日19时，力箭二号遥一运载火箭在东风商业航天创新试验区发射，将新征程01卫星、新征程02卫星和天视卫星01星精准送入预定轨道，发射任务取得圆满成功。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sz002532</t>
+          <t>sh600894</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>天山铝业</t>
+          <t>广日股份</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>17.73</v>
+        <v>9.59</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>铝+业绩|1.公司主营业务为电解铝、氧化铝、预焙阳极、高纯铝、铝深加工产品及材料的生产和销售，形成了从铝土矿、氧化铝到电解铝、高纯铝、铝箔研发制造的上下游一体化，并配套自备电厂和预焙阳极的完整铝产业链布局。
-2.天山铝业公告称，预计2026年第一季度归属于上市公司股东的净利润为22亿元，同比增长107.92%。</t>
+          <t>参股中科宇航|公司参股的广州国资国企创新投资基金合伙企业(有限合伙)仅间接持有中科宇航技术股份有限公司约0.1%股权。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>铝, 业绩</t>
+          <t>参股中科宇航</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>商业航天</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>1.43</v>
+        <v>-0.8</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>伊朗使用导弹和无人机“有效”打击了阿联酋和巴林境内与美国有关的铝厂。受此消息刺激，LME铝价在伊朗袭击中东工厂后上涨5%。</t>
+          <t>据中科宇航消息，3月30日19时，力箭二号遥一运载火箭在东风商业航天创新试验区发射，将新征程01卫星、新征程02卫星和天视卫星01星精准送入预定轨道，发射任务取得圆满成功。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sh601068</t>
+          <t>sz002342</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>中铝国际</t>
+          <t>巨力索具</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>6.28</v>
+        <v>14.4</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>9.98</v>
+        <v>10.01</v>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>盐湖提锂+有色金属|1.公司子公司长沙有色冶金院设计的年产1万吨碳酸锂项目采用世界先进的离子选择迁移合成碳酸锂的盐湖提锂工艺。
-2.公司是中国有色金属行业领先的技术、服务、装备及产品综合解决方案的提供商，能为整个有色金属产业链各类业务提供全方位的综合技术及工程设计及建设服务。</t>
+          <t>商业航天|公司为神舟十九号发射任务提供了火箭转运索具、总装索具、火箭分离索具等。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>盐湖提锂, 有色金属</t>
+          <t>商业航天</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>商业航天</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>1.43</v>
+        <v>-0.8</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>伊朗使用导弹和无人机“有效”打击了阿联酋和巴林境内与美国有关的铝厂。受此消息刺激，LME铝价在伊朗袭击中东工厂后上涨5%。</t>
+          <t>据中科宇航消息，3月30日19时，力箭二号遥一运载火箭在东风商业航天创新试验区发射，将新征程01卫星、新征程02卫星和天视卫星01星精准送入预定轨道，发射任务取得圆满成功。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sz002501</t>
+          <t>sz301079</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>利源股份</t>
+          <t>邵阳液压</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>2.04</v>
+        <v>44.76</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>10.27</v>
+        <v>20</v>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>铝|公司主要从事铝型材及深加工产品、轨道交通装备的研发、生产与销售业务，产品可分为工业铝型材、建筑铝型材及多种铝型材深加工产品、轨道车辆装备等。</t>
+          <t>机器人+商业航天|1.公司的深海机器人液压控制系统能够深潜1500米进行数据采集和故障诊断。
+2.公司主营业务为液压柱塞泵、液压缸、液压系统的设计、研发、生产、销售和液压产品专业技术服务，产品可以用于航空航天领域，西昌卫星发射中心、福建航空装备维修中心都是公司的重要客户。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>铝</t>
+          <t>机器人, 商业航天</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>体育产业</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>1.43</v>
+        <v>0.59</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>伊朗使用导弹和无人机“有效”打击了阿联酋和巴林境内与美国有关的铝厂。受此消息刺激，LME铝价在伊朗袭击中东工厂后上涨5%。</t>
+          <t>当地时间3月28日，WSBK葡萄牙站SSP组别，法国车手瓦伦丁·德比斯夺冠，其所骑820RR-RS，来自中国摩托车制造商重庆张雪机车工业有限公司。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sh601388</t>
+          <t>sh605299</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>怡球资源</t>
+          <t>舒华体育</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>3.94</v>
+        <v>21.33</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>10.06</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
+        <v>10.01</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>12天6板</t>
+        </is>
+      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>再生铝|公司的主营业务是利用所回收的来源于废旧汽车、建材、电器、机械、包装、设备等及生产过程中产生的铝渣、边角料等各方面的废铝资源，进行分选、熔炼、浇注等生产工序，制造出替代原铝的再生铝产品。</t>
+          <t>体育产业+福建|公司主营业务为健身器材和展示架产品的研发、生产和销售，其中健身器材包括室内健身器材、室外路径产品。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>再生铝</t>
+          <t>体育产业, 福建</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>有色金属概念</t>
+          <t>体育产业</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>1.43</v>
+        <v>0.59</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>伊朗使用导弹和无人机“有效”打击了阿联酋和巴林境内与美国有关的铝厂。受此消息刺激，LME铝价在伊朗袭击中东工厂后上涨5%。</t>
+          <t>当地时间3月28日，WSBK葡萄牙站SSP组别，法国车手瓦伦丁·德比斯夺冠，其所骑820RR-RS，来自中国摩托车制造商重庆张雪机车工业有限公司。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sh600219</t>
+          <t>sz301008</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>南山铝业</t>
+          <t>宏昌科技</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>6.49</v>
+        <v>42.29</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
+        <v>20.01</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>铝|公司形成从热电-氧化铝-电解铝-熔铸-(铝型材/热轧-冷轧-箔轧/锻压）的完整的铝产业链生产线，主要产品包括上游产品电力、蒸汽、氧化铝、铝合金锭，下游产品铝板带箔、挤压型材、压延材及大型机械机加工结构件。</t>
+          <t>参股张雪机车|宏昌科技通过旗下投资基金间接投资了张雪机车。</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>铝</t>
+          <t>参股张雪机车</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>商业航天</t>
+          <t>体育产业</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>1.32</v>
+        <v>0.59</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>星河动力董事长表示，星河动力的发射订单已排至2028年，任务储备饱满。液体可重复使用火箭智神星一号也将于近期实现首飞。</t>
+          <t>当地时间3月28日，WSBK葡萄牙站SSP组别，法国车手瓦伦丁·德比斯夺冠，其所骑820RR-RS，来自中国摩托车制造商重庆张雪机车工业有限公司。</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sz002361</t>
+          <t>sh600158</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>神剑股份</t>
+          <t>中体产业</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>15</v>
+        <v>11.99</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>9.969999999999999</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>商业航天|公司参与了星网项目建设，提供卫星上相关零部件。目前航天类产品有卫星天线、反射器及支撑塔等。</t>
+          <t>体育产业|公司作为国家体育总局唯一一家A股上市公司，在赛事活动、体育传播、教育培训、体育彩票、体育空间平台、体育认证等业务领域已初步完成全国性布局。</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>商业航天</t>
+          <t>体育产业</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>商业航天</t>
+          <t>体育产业</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1.32</v>
+        <v>0.59</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>星河动力董事长表示，星河动力的发射订单已排至2028年，任务储备饱满。液体可重复使用火箭智神星一号也将于近期实现首飞。</t>
+          <t>当地时间3月28日，WSBK葡萄牙站SSP组别，法国车手瓦伦丁·德比斯夺冠，其所骑820RR-RS，来自中国摩托车制造商重庆张雪机车工业有限公司。</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sh603601</t>
+          <t>sz000913</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>再升科技</t>
+          <t>钱江摩托</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>14.5</v>
+        <v>16.67</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>4天3板</t>
-        </is>
-      </c>
+        <v>10.03</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>商业航天|公司研发生产的高硅氧纤维已与国际知名航天公司开展商业合作，长期供应系列产品。</t>
+          <t xml:space="preserve">摩托车+体育|1.公司致力于高性能摩托车核心技术研发、制造、销售及服务，拥有Benelli、QJMOTOR、钱江等燃油车品牌，排量覆盖50cc-1200cc，品类覆盖复古、街车、巡航、旅行、仿赛、越野等。
+2.钱江携赛800在欧洲参加2024赛季世界超级摩托车锦标赛WSBK，和世界各大知名品牌同场竞技。 </t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>商业航天</t>
+          <t>摩托车, 体育</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>商业航天</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>1.32</v>
+        <v>-0.7799999999999999</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>星河动力董事长表示，星河动力的发射订单已排至2028年，任务储备饱满。液体可重复使用火箭智神星一号也将于近期实现首飞。</t>
+          <t>福建省国资委印发《实施“五大行动”　推动所出资企业向新向优发展工作方案（2026—2028年）》，加快向新质生产力领域布局，向高质量效益转型。</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>sz001400</t>
+          <t>sz000592</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>江顺科技</t>
+          <t>平潭发展</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>164.1</v>
+        <v>12.78</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4天2板</t>
+          <t>5天3板</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>铝+商业航天|1.公司主要从事铝型材挤压模具及配件、铝型材挤压配套设备、精密机械零部件等产品的研发、设计、生产和销售。
-2.公司产品铝型材挤压模具和铝型材挤压配套设备应用于航空航天领域。</t>
+          <t>林业+福建|公司在林木业务方面已基本形成“林板一体化”的发展产业链，拥有经营林区近90万亩，在福建省处于行业领先龙头地位。</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>铝, 商业航天</t>
+          <t>林业, 福建</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>商业航天</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>1.32</v>
+        <v>-0.7799999999999999</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>星河动力董事长表示，星河动力的发射订单已排至2028年，任务储备饱满。液体可重复使用火箭智神星一号也将于近期实现首飞。</t>
+          <t>福建省国资委印发《实施“五大行动”　推动所出资企业向新向优发展工作方案（2026—2028年）》，加快向新质生产力领域布局，向高质量效益转型。</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>sh600343</t>
+          <t>sz002578</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>航天动力</t>
+          <t>闽发铝业</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>32.58</v>
+        <v>4.69</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr"/>
+        <v>10.09</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>军工+商业航天|1.公司涉军业务包括军用特种车辆液力传动系统、军用车载加油泵、洗消用泵等。
-2.公司是航天六院唯一的资产证券化平台。航天六院是我国液体火箭发动机研制中心和专业抓总单位，承担着为我国运载火箭和导弹武器提供液体火箭发动机的重任。</t>
+          <t>铝+福建|公司是国内行业中较早涉足工业型材领域的企业之一，主营业务和产品主要是建筑铝型材、工业铝型材和建筑铝模板的研发、生产、销售。</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>军工, 商业航天</t>
+          <t>铝, 福建</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>商业航天</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>1.32</v>
+        <v>-0.7799999999999999</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>星河动力董事长表示，星河动力的发射订单已排至2028年，任务储备饱满。液体可重复使用火箭智神星一号也将于近期实现首飞。</t>
+          <t>福建省国资委印发《实施“五大行动”　推动所出资企业向新向优发展工作方案（2026—2028年）》，加快向新质生产力领域布局，向高质量效益转型。</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>sh603017</t>
+          <t>sz000993</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>中衡设计</t>
+          <t>闽东电力</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>15.76</v>
+        <v>16.31</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>9.98</v>
@@ -1569,476 +1570,465 @@
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>商业航天|公司中标了天兵科技运载火箭及发动机智能制造 基地、山东箭元航天科技总装总测生产基地、星际荣耀火箭制造基地、安庆年发20发可回收液体火箭制造厂房建设项目等多个高端制造基地，积极为航空航天逐梦苍穹贡献中衡力量。</t>
+          <t>福建+电力|公司致力于清洁能源、新能源等领域的发展。发电业务是公司业务的核心业务，主要包括水力发电和风力发电。是电力产业链的发电环节，相对电网企业，处于弱势地位，由于水电、风电生产均属清洁能源，电调顺序靠前，与火电相比，来自电网的竞争压力相对较小。公司目前是宁德市唯一以经营清洁能源发电为主营业务的国有控股上市公司。</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>商业航天</t>
+          <t>福建, 电力</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>商业航天</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>1.32</v>
+        <v>-0.7799999999999999</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>星河动力董事长表示，星河动力的发射订单已排至2028年，任务储备饱满。液体可重复使用火箭智神星一号也将于近期实现首飞。</t>
+          <t>福建省国资委印发《实施“五大行动”　推动所出资企业向新向优发展工作方案（2026—2028年）》，加快向新质生产力领域布局，向高质量效益转型。</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>sh605222</t>
+          <t>sh603826</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>起帆电缆</t>
+          <t>坤彩科技</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>22.36</v>
+        <v>27.67</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>9.99</v>
+        <v>10.02</v>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>商业航天|公司产品涵盖电力电缆、电气装备用电线电缆、通信电缆和裸电线四大类，广泛应用于水利、电力、家装、轨道交通、建筑工程、航空航天、新能源等众多领域。</t>
+          <t>化工+福建|公司是一家专业从事无机颜料研发、生产、销售的高新技术企业，经过多年的发展，现已成为全球珠光材料龙头企业。公司提供的珠光材料、二氧化钛、氧化铁、二氯氧钛、三氯化铁等系列产品同属于无机材料，可广泛应用于涂料、塑料、汽车、造纸、化妆品（日化）、油墨、陶瓷、建材、食品、纺织、光伏、新能源、环保等行业。</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>商业航天</t>
+          <t>化工, 福建</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>商业航天</t>
+          <t>汽车零部件</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>1.32</v>
+        <v>-1.06</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>星河动力董事长表示，星河动力的发射订单已排至2028年，任务储备饱满。液体可重复使用火箭智神星一号也将于近期实现首飞。</t>
+          <t>北京时间3月28日，世界超级摩托车锦标赛（WSBK）赛场上，中国摩托车品牌张雪机车以近4秒的绝对优势夺冠，一举打破了杜卡迪、雅马哈、川崎等国际豪强对该组别长达数十年的垄断。</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>sz300900</t>
+          <t>sz003033</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>广联航空</t>
+          <t>征和工业</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>38.16</v>
+        <v>60.61</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>商业航天+燃气轮机|1.公司是国内知名的民营航空航天工业配套产品供应商，持续跟进微厘空间一号系统（ALNES）北斗低轨卫星导航增强系统组网卫星、天都二号通导技术试验星、探月卫星等航天产品的整体结构、主框架结构及内部复合材料结构等研制工作。
-2.公司具备整台燃气轮机机匣总成制造能力，核心产品涵盖压气机机匣、燃烧外壳、涡轮支撑环总成等关键部套，可实现从燃气轮机的全序加工。</t>
+          <t>摩托车+机器人|1.公司作为国内链传动行业的领军企业，专注于各类链传动系统的研发、制造与销售，产品应用于摩托车、汽车、自行车等领域。
+2.2025年4月28日公司在调研中表示，公司研发的的微型链系统项目，重点攻关机器人灵巧手传动技术，尚处于早期技术探索与储备阶段。</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>商业航天, 燃气轮机</t>
+          <t>摩托车, 机器人</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>汽车零部件</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>2.6</v>
+        <v>-1.06</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>中信建投证券研报称，今年2月，我国出口光纤3779.9吨，金额7.9亿元，同比增长63.6%，126.8%。</t>
+          <t>北京时间3月28日，世界超级摩托车锦标赛（WSBK）赛场上，中国摩托车品牌张雪机车以近4秒的绝对优势夺冠，一举打破了杜卡迪、雅马哈、川崎等国际豪强对该组别长达数十年的垄断。</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>sz002309</t>
+          <t>sz000030</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>中利集团</t>
+          <t>富奥股份</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>4.76</v>
+        <v>5.56</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>7天5板</t>
-        </is>
-      </c>
+        <v>10.1</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>光伏+光纤光缆|1.公司的新能源光伏组件业务板块，包括单晶大尺寸高效光伏电池片和光伏组件的研发、生产和销售。公司拥有钙钛矿叠层电池及组件研发专利等技术储备6项。
-2.公司光通讯线缆板块已延伸到高分子材料、光纤、电缆的全产业链，作为华为核心战略供应商，为华为提供通信用电缆，包括5G用新品光电混合缆。</t>
+          <t>汽车零部件|公司为混合动力车型，如红旗EV、奥迪C8 PHEV配套的相关产品（如电动压缩机、电池冷却器、散热器）已经实现量产。</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>光伏, 光纤光缆</t>
+          <t>汽车零部件</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>汽车零部件</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>2.6</v>
+        <v>-1.06</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>中信建投证券研报称，今年2月，我国出口光纤3779.9吨，金额7.9亿元，同比增长63.6%，126.8%。</t>
+          <t>北京时间3月28日，世界超级摩托车锦标赛（WSBK）赛场上，中国摩托车品牌张雪机车以近4秒的绝对优势夺冠，一举打破了杜卡迪、雅马哈、川崎等国际豪强对该组别长达数十年的垄断。</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>sh603618</t>
+          <t>sz000678</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>杭电股份</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>26.71</v>
+        <v>12.64</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>10.01</v>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>4天3板</t>
-        </is>
-      </c>
+      <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>电网设备+光纤光缆|1.公司电线电缆板块主要从事电线电缆的研发、生产、销售和服务。主要产品为涵盖从超高压、高压到中低压的各类电力电缆、导线、民用线缆及特种电缆。
-2.公司光通信板块主要由富春江光电及其子公司从事经营，其主要从事光通信产业链中光纤预制棒、光纤、光缆、光通信相关设备等产品研发、生产、销售和服务。公司具备光通信“光棒—光纤—光缆”一体化产业链。</t>
+          <t>摩托车零部件|公司专注于各类滚动轴承的研发、生产与销售，其产品覆盖汽车、摩托车、工程机械及家用电器等多个领域。</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>电网设备, 光纤光缆</t>
+          <t>摩托车零部件</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>2.6</v>
+        <v>-1.16</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>中信建投证券研报称，今年2月，我国出口光纤3779.9吨，金额7.9亿元，同比增长63.6%，126.8%。</t>
+          <t>国盛证券表示，Agent进入实际落地阶段，OpenClaw引领渗透加速。</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>sh601869</t>
+          <t>sz002995</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>长飞光纤</t>
+          <t>天地在线</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>301.69</v>
+        <v>24.66</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5天3板</t>
+          <t>3天2板</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆|公司系全球光纤光缆行业的领先企业，是国内最早的光纤光缆生产厂商之一，聚焦电信运营商和数据通信相关领域，致力于光纤预制棒、光纤和光缆以及数据通信相关产品的研发创新与生产制造，形成了棒纤缆、综合布线和光模块一体化的完整产业链、相关多元化和国际化的业务模式。</t>
+          <t>AI数字人|公司已推出AI数字人SAAS产品“星河AI数字人系统”以及帮助企业提高工作效率和协作能力的AI智能应用产品“AIbase” ，满足客户在营销及提升企业经营效能的不同需求。</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>AI数字人</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>2.6</v>
+        <v>-1.16</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>中信建投证券研报称，今年2月，我国出口光纤3779.9吨，金额7.9亿元，同比增长63.6%，126.8%。</t>
+          <t>国盛证券表示，Agent进入实际落地阶段，OpenClaw引领渗透加速。</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>sz000890</t>
+          <t>sh603039</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>法尔胜</t>
+          <t>泛微网络</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>14.83</v>
+        <v>43.45</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆|公司参股的普天法尔胜光通信有限公司主要产品为光纤预制棒、光纤、光缆，上述产品可以应用于在运营商基础网络通信及广播电视通信领域。</t>
+          <t>AI智能体|泛微数智大脑Xiaoe.AI为组织每个用户提供了一位7*24工作的智能助理。有了Xiaoe.AI的支撑，办理事务无需摸索与学习多个系统，也不用填写大量的、重复的表单和信息，只要对着手机喊话就完成工作，让组织的业务运营更加敏捷。</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>AI智能体</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>2.6</v>
+        <v>-1.16</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>中信建投证券研报称，今年2月，我国出口光纤3779.9吨，金额7.9亿元，同比增长63.6%，126.8%。</t>
+          <t>国盛证券表示，Agent进入实际落地阶段，OpenClaw引领渗透加速。</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>sh600345</t>
+          <t>sh603660</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>长江通信</t>
+          <t>苏州科达</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>43.23</v>
+        <v>9.74</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>10.06</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>参股长飞光纤|公司参股公司长飞光纤（持股比例15.82%）系全球光纤光缆行业的领先企业，是国内最早的光纤光缆生产厂商之一。</t>
+          <t>AI+量子通信|1.2023年7月正式推出了KD-GPT大模型，包括多模态大模型、AIGC图像大模型和行业大模型已经初具雏形，并开始在实际项目中投入应用。
+2.苏州科达的量子网呈产品，是国内唯一支持量子通信技术的视频会议产品。</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>参股长飞光纤</t>
+          <t>AI, 量子通信</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>光伏</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>2.6</v>
+        <v>-2.36</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>中信建投证券研报称，今年2月，我国出口光纤3779.9吨，金额7.9亿元，同比增长63.6%，126.8%。</t>
+          <t>华金证券表示，商业航天产业趋势已来，关注太空光伏新技术方向。</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>sh600487</t>
+          <t>sz002634</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>棒杰股份</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>53.85</v>
+        <v>8.94</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I31" s="2" t="inlineStr"/>
+        <v>9.959999999999999</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆|公司拥有全球光纤通信（光棒-光纤-光缆-光器件-光网络及海洋光网络）、量子通信、数据通信全产业链及自主核心技术，致力于提供光纤光网、量子保密通信、海洋观测网及智慧海洋工程系统解决方案及设计-施工-运维服务为一体的工程EPC总包服务， 目前已形成“产品+平台+服务”综合服务模式，已成为通信产业全价值链综合服务商。</t>
+          <t>重整+光伏|1.棒杰股份2月2日公告,公司及子公司扬州棒杰近日收到扬州经开区法院送达的《民事裁定书》,法院于1月30日裁定受理兴业银行苏州分行对扬州棒杰的重整申请。
+2.公司拟投资设立全资子公司棒杰新能源集团有限公司布局光伏产业，注册资本为5亿元。从而形成“无缝服装+光伏”双主业的业务结构。公司与江苏诺信就扬州经开区600MW地面光伏电站一期240MW农光互补项目建设等合作。</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>重整, 光伏</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>光伏</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>0.21</v>
+        <v>-2.36</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>机构研报指出，特斯拉OptimusV3进入亮相发布时间窗口，并计划年内启动大规模量产，并且特斯拉已将弗里蒙特工厂的Model S/X产线改造为Optimus专用产线，中期规划年产能达100万台。</t>
+          <t>华金证券表示，商业航天产业趋势已来，关注太空光伏新技术方向。</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>sh603272</t>
+          <t>sh601908</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>联翔股份</t>
+          <t xml:space="preserve">京运通  </t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>35.55</v>
+        <v>5.01</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>9.99</v>
+        <v>10.11</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6天3板</t>
+          <t>4天2板</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>机器人|2025年12月30日公告，董事会审议通过变更经营范围议案，新增服务消费机器人制造、服务消费机器人销售、工业机器人制造、工业机器人销售、智能机器人的研发等制造销售，并同步修订公司章程。</t>
+          <t>光伏+半导体|1.公司主营光伏设备（单晶硅生长炉、多晶硅铸锭炉）、多晶硅锭及硅片、光伏电站（地面光伏发电及分布式光伏发电）。
+2.公司半导体相关业务有区熔产品、碳化硅炉、金刚石炉等，金刚石炉目前实现小批量对外销售。</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>光伏, 半导体</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>光伏</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>0.21</v>
+        <v>-2.36</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>机构研报指出，特斯拉OptimusV3进入亮相发布时间窗口，并计划年内启动大规模量产，并且特斯拉已将弗里蒙特工厂的Model S/X产线改造为Optimus专用产线，中期规划年产能达100万台。</t>
+          <t>华金证券表示，商业航天产业趋势已来，关注太空光伏新技术方向。</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>sz000008</t>
+          <t>sz002218</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>神州高铁</t>
+          <t>拓日新能</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>2.97</v>
+        <v>6.93</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>10</v>
@@ -2046,444 +2036,447 @@
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>高铁+机器人|1.公司提供轨道交通运营维护全产业链智能装备系统，并以此为依托，提供轨道交通运营及维保专业服务，是中国轨道交通运营维护领域首家涵盖全产业链装备及运营维保服务的上市公司。
-2.神州高铁在互动平台表示，近年来，公司积极加强智能化、数字化产品研发，动车组空心车轴超声检测机器人、动车组车轮超声检测机器人等智能产品已进入样机测试阶段。</t>
+          <t>太空光伏|公司于2015年参与了东方红卫星“开拓一号”单晶硅太阳电池项目，具备成熟的卫星用光伏组件生产制造能力。</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>高铁, 机器人</t>
+          <t>太空光伏</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>盾构机</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>0.21</v>
+        <v>1.17</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>机构研报指出，特斯拉OptimusV3进入亮相发布时间窗口，并计划年内启动大规模量产，并且特斯拉已将弗里蒙特工厂的Model S/X产线改造为Optimus专用产线，中期规划年产能达100万台。</t>
+          <t>央视财经报道，长江入海口，“十五五”重大工程——沿江高铁的标志性项目正加紧施工，沿江高铁总投资超5000亿元。</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>sh603897</t>
+          <t>sz002542</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>长城科技</t>
+          <t>中化岩土</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>32.89</v>
+        <v>3.28</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>10</v>
+        <v>10.07</v>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司电磁线产品的应用领域包括工业电机、家用电器、汽车电机、电动工具和低压电器，其中工业电机涵盖水泵电机、轮毂电机、吸尘器电机、微特电机、中小型电机等产品领域，家用电器主要包括空调压缩机和风扇电机等，汽车电机包括新能源汽车驱动电机在内的车用各式电机产品应用领域，低压电器分别为仪表仪器、以及应用于包括机器人应用领域等在内的低压线圈产品。</t>
+          <t>盾构机|公司旗下上海力行主营业务为盾构机设备制造和租赁，主要服务对象为国内大型铁路、公路、城市轨道交通及市政等重点施工企业。上海力行盾构机设备既有适用于各地层的大型地铁盾构机，也有适用于水务、电力隧道和城市维修建设的小型盾构机。</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>盾构机</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>盾构机</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>0.21</v>
+        <v>1.17</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>机构研报指出，特斯拉OptimusV3进入亮相发布时间窗口，并计划年内启动大规模量产，并且特斯拉已将弗里蒙特工厂的Model S/X产线改造为Optimus专用产线，中期规划年产能达100万台。</t>
+          <t>央视财经报道，长江入海口，“十五五”重大工程——沿江高铁的标志性项目正加紧施工，沿江高铁总投资超5000亿元。</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sz000048</t>
+          <t>sz001239</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>京基智农</t>
+          <t>永达股份</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>22.61</v>
+        <v>15.86</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>10.02</v>
+        <v>9.99</v>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>猪肉+机器人|1.旗下康达尔养猪有限公司已形成优质黑猪品牌肉产业链，主要为种猪和猪苗。
-2.2025年12月30日公告，公司已与江苏汇博机器人技术股份有限公司及后者股东团队签署股权投资意向协议，拟通过现金增资及受让老股方式取得江苏汇博控制权，若增资与受让老股后持股不足51%，将通过签署一致行动协议、委派过半数董事实现控制及合并报表。交易完成后双方将联合设立具身机器人研究院，由江苏汇博核心创始人、首席科学家孙立宁担任首席科学家。江苏汇博承诺2026年内发布2款人形机器人产品，并承诺在2026年至2028年间，每年收入增长率不低于30%，每年申请具身机器人专利不少于200项。</t>
+          <t>盾构机+机器人|1.公司的隧道掘进及配套设备主要为盾构机的盾体、刀盘体、管片机以及与之配套的定制化支撑管片等金属结构产品。
+2.子公司江苏金源高端装备有限公司的主营业务为高速重载齿轮锻件的研发、生产和销售，产品部分应用于机器人领域。</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>猪肉, 机器人</t>
+          <t>盾构机, 机器人</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>光纤光缆</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>0.21</v>
+        <v>-0.06</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>机构研报指出，特斯拉OptimusV3进入亮相发布时间窗口，并计划年内启动大规模量产，并且特斯拉已将弗里蒙特工厂的Model S/X产线改造为Optimus专用产线，中期规划年产能达100万台。</t>
+          <t>中信建投证券研报称，今年2月，我国出口光纤3779.9吨、金额7.9亿元，同比增长63.6%、126.8%。如果折算为公里数，2月我国出口光纤约2520万芯公里，占我国光纤月有效产量的65%左右。</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sh603239</t>
+          <t>sz000720</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>浙江仙通</t>
+          <t>新能泰山</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>23.46</v>
+        <v>5.46</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
+        <v>10.08</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>6天5板</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>机器人|2025年9月25日公告，公司拟以4000万元对浩海星空进行增资，投资完成后持有浩海星空10%的股份。增资完成后，公司与浩海星空拟出资设立合资公司，合资公司由浙江仙通控股，注册在浙江省台州市仙居县，合资公司注册资本2000万元人民币，其中公司认缴出资1020万元，占注册资本的51%。本次合作事项为机器人业务相关。</t>
+          <t>电线电缆+光纤光缆|子公司曲阜电缆主要从事电线电缆、光纤光缆、电力光缆等产品的研发、制造与销售，曲阜电缆生产、 销售的电线电缆产品是公司重点发展的智慧供应链业务产品之一。</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>电线电缆, 光纤光缆</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>光纤光缆</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>0.51</v>
+        <v>-0.06</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>据生意社及行业数据显示，关键化工品价格显著上涨，其中西南市场甲醇价格较2月底上涨约38.9%，溴素报价月内涨幅超50%，尿素、钾肥等化肥产品3月以来也普遍提价。</t>
+          <t>中信建投证券研报称，今年2月，我国出口光纤3779.9吨、金额7.9亿元，同比增长63.6%、126.8%。如果折算为公里数，2月我国出口光纤约2520万芯公里，占我国光纤月有效产量的65%左右。</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sz003042</t>
+          <t>sz000070</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>中农联合</t>
+          <t>特发信息</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>19.77</v>
+        <v>17.8</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.01</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>农药|公司实控人为中华全国供销合作总社。公司是专业从事农药中间体、原药及制剂产品的研发、生产和销售的全产业链农药生产企业。</t>
+          <t>光纤光缆+商业航天|1.公司拥有一系列先进的纤缆生产及检测设备，组建了华南地区规模最大的光纤光缆研制、生产及检测基地，产品主要包括光纤、光缆、光纤连接器、配线产品、馈线电缆、数据线缆、架空裸导地线、光缆金具及附件等新一代信息技术产品。
+2.公司独资子公司成都傅立叶在卫星通信领域主要涉及地面终端（主要基于自主可控的天通卫星移动通信系统）、卫星解调设备、卫星态势感知系统等。</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>农药</t>
+          <t>光纤光缆, 商业航天</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>0.51</v>
+        <v>-1.06</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>据生意社及行业数据显示，关键化工品价格显著上涨，其中西南市场甲醇价格较2月底上涨约38.9%，溴素报价月内涨幅超50%，尿素、钾肥等化肥产品3月以来也普遍提价。</t>
+          <t>机构研报指出，特斯拉OptimusV3进入亮相发布时间窗口，并计划年内启动大规模量产，并且特斯拉已将弗里蒙特工厂的Model S/X产线改造为Optimus专用产线，中期规划年产能达100万台。</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>sh603585</t>
+          <t>sz301255</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>苏利股份</t>
+          <t>通力科技</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>22.81</v>
+        <v>29.76</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>农药|公司主营业务为农药、阻燃剂及其他精细化工产品的研发、生产和销售。农药类产品包括百菌清原药、嘧菌酯原药、农药制剂及其他农药类产品。</t>
+          <t>机器人|公司是一家专业从事减速机的研发、生产、销售及服务的高新技术企业。公司主要产品为自主品牌“通力”系列减速机，公司已形成R、K、S、F、H、B、P等减速机全系列产品。</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>农药</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>0.51</v>
+        <v>-1.06</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>据生意社及行业数据显示，关键化工品价格显著上涨，其中西南市场甲醇价格较2月底上涨约38.9%，溴素报价月内涨幅超50%，尿素、钾肥等化肥产品3月以来也普遍提价。</t>
+          <t>机构研报指出，特斯拉OptimusV3进入亮相发布时间窗口，并计划年内启动大规模量产，并且特斯拉已将弗里蒙特工厂的Model S/X产线改造为Optimus专用产线，中期规划年产能达100万台。</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>sz002810</t>
+          <t>sh600184</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>山东赫达</t>
+          <t>光电股份</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>22.9</v>
+        <v>18.41</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>化工|公司是国内第一、全球第四的纤维素醚供应商，具有自主研发、生产全系列建材级、医药级和食品级非离子型纤维素醚产品的能力。</t>
+          <t>光通信+机器人|1.子公司新华光自主研发的光通信核心材料GP，突破了批量生产工艺，已经送样给光通信领域多家企业测试使用。
+2.公司从光学设计源头导入终端应用，加大不同性能的高性能光学材料及先进元件的开发生产力度，以满足镜头、器件、模组等的使用要求，最终应用到下游车载镜头、消费电子、安防监控、投影成像，以及工业自动控制系统、工业机器人、机器人的光学成像、视觉传感系统中。</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>光通信, 机器人</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>业绩超预期</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>0.16</v>
+        <v>-1.97</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>机构指出，储能需求非线性增长推动下，锂电新周期愈发明确。</t>
+          <t>上市公司年报业绩预告进入密集披露阶段，市场驱动逻辑正转向对业绩增长与盈利改善的验证层面。</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>sz002850</t>
+          <t>sh600502</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>科达利</t>
+          <t>安徽建工</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>177.32</v>
+        <v>5.63</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I40" s="2" t="inlineStr"/>
+        <v>9.959999999999999</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>锂电池+机器人|1.公司为国内动力锂电池精密结构件龙头企业，也是国内最早从事动力锂电池精密结构件研发和生产的企业之一。
-2.公司基于人形机器人在未来的发展前景，通过谐波减速器等产品业务，拓展人形机器人关节部件领域，打开未来成长空间。</t>
+          <t>业绩+基建|公司2025年1-12月实现营业收入831.98亿元，同比下降13.79%；实现归母净利润15.26亿元，同比增长13.45%。报告显示，公司营收下降主要系建筑施工业务收入减少所致，但利润总额和归母净利润实现双增长。全年基建投资及工程业务新签合同金额1626.08亿元，同比增长4.86%。</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>锂电池, 机器人</t>
+          <t>业绩, 基建</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>业绩超预期</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>0.16</v>
+        <v>-1.97</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>机构指出，储能需求非线性增长推动下，锂电新周期愈发明确。</t>
+          <t>上市公司年报业绩预告进入密集披露阶段，市场驱动逻辑正转向对业绩增长与盈利改善的验证层面。</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>sh600135</t>
+          <t>sh600066</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>乐凯胶片</t>
+          <t>宇通客车</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>11.06</v>
+        <v>35.86</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>10.05</v>
+        <v>10</v>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>光伏+锂电池|2015年5月，公司向乐凯集团等对象定增募资6亿元投向高性能锂离子电池PE隔膜、锂电隔膜涂布、太阳能电池背板等五个项目，募集资金投入建设年产4000万平米的湿法分步双向拉伸的锂离子电池PE隔膜生产线、年产500万平方米陶瓷涂布型锂电隔膜的锂电隔膜涂布生产线、年产1200万平方米涂层改性隔膜成品的锂电隔膜涂布生产线和新增年产1500万平米太阳能电池背板生产能力。“高性能锂离子电池PE隔膜产业化建设项目”和“锂电隔膜涂布生产线一期项目”已于2018年12月竣工验收。</t>
+          <t>业绩|宇通客车披露年报，2025年实现营业收入414.26亿元，同比增长11.31%；归母净利润55.54亿元，同比增长34.94%；基本每股收益2.51元。公司拟每10股派发现金红利20元(含税)。</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>光伏, 锂电池</t>
+          <t>业绩</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>0.16</v>
+        <v>-2.62</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>机构指出，储能需求非线性增长推动下，锂电新周期愈发明确。</t>
+          <t>华泰证券指出，霍尔木兹海峡封锁强化化石能源价格易涨难跌预期，水、核、风、光、生物质等绿电板块有望充分受益。</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>sh603778</t>
+          <t>sz000037</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>国晟科技</t>
+          <t>深南电A</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>25.3</v>
+        <v>13.02</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I42" s="2" t="inlineStr"/>
+        <v>9.969999999999999</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>光伏+锂电池|1.公司目前从事大尺寸高效异质结光伏电池的研发、生产、销售，以及异质结、TOPCON、PERC等电池组件的生产与销售。控股孙公司恒立聚能涉及钙钛矿研究。
-2.国晟科技公告称，公司拟以2.406亿元的价格受让正豪科技、林琴合计持有的孚悦科技100%股权。交易完成后，公司将持有标的公司100%股权，标的公司将纳入公司合并报表。孚悦科技主要从事高精密度新型锂电池结构件的研发、生产和销售。</t>
+          <t>电力|公司主营业务为生产经营供电供热、从事发电厂（站）相关技术咨询和技术服务等，公司南山热电厂位于深圳市电力负荷中心区，是所在区域的调峰电源。</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>光伏, 锂电池</t>
+          <t>电力</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>农业种植</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>2.9</v>
+        <v>-2.62</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>高盛表示，化肥短缺可能导致因施肥延迟或不当而造成产量降低，同时一些农民可能转向化肥密集度较低的作物,进一步收紧谷物供应。</t>
+          <t>华泰证券指出，霍尔木兹海峡封锁强化化石能源价格易涨难跌预期，水、核、风、光、生物质等绿电板块有望充分受益。</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
@@ -2491,1468 +2484,740 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>sh600127</t>
+          <t>sh605162</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t xml:space="preserve">新中港  </t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>7.51</v>
+        <v>11.61</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>9.959999999999999</v>
+        <v>10.05</v>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>大米|公司以优质粮油、新型健康食品和药品的开发、生产、销售为主，主要产品有大米、面粉、面条、植物油、牛奶、药品、休闲食品等。</t>
+          <t>电力|公司采用热电联产的方式进行热力产品和电力产品的生产及供应。公司的热力业务主要面向工业用户供应所生产的蒸汽，主要满足工业园区内的造纸、印染、医药、化工、食品等150余家工业企业的热需求。公司生产的电力直接销售给国家电网公司。公司是嵊州市地区唯一一家集中供热的热电联产企业，具有150多家下游客户，区域优势和先发优势明显。</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>大米</t>
+          <t>电力</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>农业种植</t>
+          <t>智能电网</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>2.9</v>
+        <v>-1.95</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>高盛表示，化肥短缺可能导致因施肥延迟或不当而造成产量降低，同时一些农民可能转向化肥密集度较低的作物,进一步收紧谷物供应。</t>
+          <t>国家电投计划今年投资2000亿元，同比增长17%。其中，一季度要完成投资230亿元，实现同比增长35%。</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>sh600359</t>
+          <t>sz002560</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>新农开发</t>
+          <t>通达股份</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>7.65</v>
+        <v>10.79</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>10.07</v>
+        <v>9.99</v>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>农业种植|公司的最终控制人为新疆生产建设兵团第一师国有资产监督管理委员会。公司主营为棉纱、香梨、大米、甘草、棉浆粕、清弹棉、生态棉、细绒棉、长绒棉的生产。</t>
+          <t>电线电缆|公司从事的主要业务包括电线电缆生产、销售及航空零部件加工两大板块。</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>农业种植</t>
+          <t>电线电缆</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>业内机构LightCounting测算，当前光模块需求量已超供应量两倍以上，800G光模块需求将持续旺盛，1.6T光模块2026年将进入规模化放量阶段，海外大客户已上修2026年采购计划至2000万只。</t>
-        </is>
-      </c>
+        <v>-1.52</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>sz002980</t>
+          <t>sh603429</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>华盛昌</t>
+          <t xml:space="preserve">*ST集友 </t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>43.78</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I45" s="2" t="inlineStr"/>
+        <v>4.96</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>5天4板</t>
+        </is>
+      </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>并购重组+光通信|华盛昌公告称，公司拟以现金方式收购深圳市伽蓝特科技有限公司100%股权，整体估值暂定为4.6亿元。伽蓝特专注于仪器仪表测试测量行业中的光通信模块和光芯片测试领域。</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>并购重组, 光通信</t>
-        </is>
-      </c>
+          <t>ST股 | 子公司集新能源主要在固态电池方向系统地开展关键材料研究。</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>业内机构LightCounting测算，当前光模块需求量已超供应量两倍以上，800G光模块需求将持续旺盛，1.6T光模块2026年将进入规模化放量阶段，海外大客户已上修2026年采购计划至2000万只。</t>
-        </is>
-      </c>
+        <v>-1.52</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>sz002222</t>
+          <t>sz002168</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>*ST惠程</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>71.94</v>
+        <v>4.18</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I46" s="2" t="inlineStr"/>
+        <v>5.029999999999999</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>光通信+光刻机|1.公司部分精密光学元件产品应用于光通讯领域。
-2.公司曾通过欧洲代理向ASML提供及其少量光学元件。此外，华为是公司的客户，公司在业务范围内向其提供光学元件产品。</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>光通信, 光刻机</t>
-        </is>
-      </c>
+          <t>ST股 | 公司旗下控股子公司哆可梦以基于大数据精细化营销的流量经营业务和移动游戏的研发、发行及游戏平台的运营为主营业务</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>0.7000000000000001</v>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>福建省国资委印发《实施“五大行动”　推动所出资企业向新向优发展工作方案（2026—2028年）》，加快向新质生产力领域布局，向高质量效益转型。</t>
-        </is>
-      </c>
+        <v>-1.52</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr"/>
       <c r="D47" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>sz000592</t>
+          <t>sz002528</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>平潭发展</t>
+          <t>ST英飞拓</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>11.62</v>
+        <v>3.79</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>10.04</v>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>4.99</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>福建|公司在林木业务方面已基本形成“林板一体化”的发展产业链，拥有经营林区近90万亩，在福建省处于行业领先龙头地位。</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
+          <t>ST股 | 英飞拓推出5G多功能智慧灯杆，支持节能照明、视频监控、新能源充电、公共WIFI、环境监测、信息发布、应急报警、5G微基站等模块，实现多种类型的感知数据采集、分析、仿真预测，提升城市综合治理。</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>0.7000000000000001</v>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>福建省国资委印发《实施“五大行动”　推动所出资企业向新向优发展工作方案（2026—2028年）》，加快向新质生产力领域布局，向高质量效益转型。</t>
-        </is>
-      </c>
+        <v>-1.52</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr"/>
       <c r="D48" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>sz000753</t>
+          <t>sh600581</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>漳州发展</t>
+          <t xml:space="preserve">*ST八钢 </t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>7.21</v>
+        <v>2.79</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>4.89</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>福建+绿电|公司海上风电相关业务主要为全资子公司漳发新能源与南平电缆等公司共同在东山投建海底电缆项目，漳发新能源持有20%股权，业务覆盖福建及周边海上风电场。</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>福建, 绿电</t>
-        </is>
-      </c>
+          <t>ST股 | 新疆唯一的钢铁上市公司，拥有完整优质的炼铁、炼钢及轧钢生产系统，产品以高速线材、螺纹钢、热轧板卷、冷轧薄板、中厚板等建筑及工业用钢为主。</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>3月29日，上海人工智能实验室联合相关主体启动“超智融合算力”平台，为原始创新提供可统一调度的算力、可直接用于AI训练数据等底层支撑。</t>
-        </is>
-      </c>
+        <v>-1.52</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr"/>
       <c r="D49" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>sh600996</t>
+          <t>sh605199</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>贵广网络</t>
+          <t>ST葫芦娃</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>11.02</v>
+        <v>6.83</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>5.08</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>贵州+算力|据中国信通院消息，3月26日，中国算力平台（贵州）建设工作在贵阳启动。贵州广播电视台旗下上市公司。公司将致力于贵州与粤港澳、长三角、京津冀等地区大数据中心集群的算力资源对接，充分发挥贵州省作为南方数据中心示范基地优势，有效承接东部算力需求。</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>贵州, 算力</t>
-        </is>
-      </c>
+          <t>ST股 | 公司地处海南海口，聚焦儿童药研发、生产、销售于一体的创新型医药企业。</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>3月29日，上海人工智能实验室联合相关主体启动“超智融合算力”平台，为原始创新提供可统一调度的算力、可直接用于AI训练数据等底层支撑。</t>
-        </is>
-      </c>
+        <v>-1.52</v>
+      </c>
+      <c r="C50" s="2" t="inlineStr"/>
       <c r="D50" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>sh600602</t>
+          <t>sh603559</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>云赛智联</t>
+          <t xml:space="preserve">ST通脉  </t>
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>23.33</v>
+        <v>7.16</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>10</v>
+        <v>4.99</v>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>国资云|公司是上海国资委旗下上市公司，定位于中立第三方高端数据中心运营商。</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>国资云</t>
-        </is>
-      </c>
+          <t>ST股 | 公司是国内专业通信技术服务商，主营业务是为基础电信运营商和通信设备商提供涵盖核心网、传输网和接入网等全网络层次的通信网络工程建设和维护综合技术服务。</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="n">
-        <v>0.41</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C51" s="2" t="inlineStr"/>
       <c r="D51" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>sz000908</t>
+          <t>sz002263</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>ST景峰</t>
+          <t>大东南</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>8.16</v>
+        <v>4.51</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>5.02</v>
+        <v>10</v>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>18天14板</t>
+          <t>4天3板</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司专注医药健康产业，涉足药品研发、生产、销售等领域，产品涵盖了心脑血管、抗肿瘤、骨科、妇儿等用药领域。</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr"/>
+          <t>隔膜+复合铜箔|1.公司产品覆盖传统包装薄膜、锂电池隔膜、耐高温超薄电容膜、光学膜。
+2.公司复合铜箔用电容薄膜的研发已经完成，此项目使公司生产更超薄产品成为可能，且技术指标均达到或超过国家标准。</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>隔膜, 复合铜箔</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="n">
-        <v>0.41</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C52" s="2" t="inlineStr"/>
       <c r="D52" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>sz002620</t>
+          <t>sz000631</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>ST瑞和</t>
+          <t>顺发恒能</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>9.119999999999999</v>
+        <v>4.27</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>6天6板</t>
-        </is>
-      </c>
+        <v>10.05</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司主要从事政府机构、房地产开发商、大型企业、高档酒店、交通枢纽、园林绿化等综合性专业化装饰设计、工程施工业务以及光伏电站运营、光伏项目施工安装等。</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr"/>
+          <t>并购重组|顺发恒能公告称，为满足发展需要，公司拟以自有资金分别收购顺发德能49%股权和普星京兴100%股权，交易价格分别为1.13亿元和1.47亿元。交易完成后，顺发德能和普星京兴将成为公司全资子公司。本次交易构成关联交易，但不构成重大资产重组，已获公司董事会审议通过，尚需提交股东会审议。关联董事已回避表决。</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>并购重组</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="n">
-        <v>0.41</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C53" s="2" t="inlineStr"/>
       <c r="D53" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>sz002024</t>
+          <t>sz002454</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>ST易购</t>
+          <t>松芝股份</t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>1.47</v>
+        <v>9.24</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 已经形成零售、金融、物流三大业务单元协同发展。</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr"/>
+          <t>储能热管理|松芝股份聚焦储能领域的创新研发，自2016年即开始研发销售电池热管理液冷机组，目前产品市场保有量达5万余套，广泛应用于储能集装箱、储能电柜、客车、卡车、换电等领域。</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>储能热管理</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="n">
-        <v>0.41</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C54" s="2" t="inlineStr"/>
       <c r="D54" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>sz001270</t>
+          <t>sz300834</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>*ST铖昌</t>
+          <t>星辉环材</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>108.99</v>
+        <v>30.2</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>3天2板</t>
-        </is>
-      </c>
+        <v>19.98</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司主营业务为微波毫米波模拟相控阵T/R芯片的研发、生产、销售和技术服务，产品已应用于探测、遥感、通信、导航、电子对抗等领域。</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr"/>
+          <t>引入战略投资者|近日，星辉环材宣布引入战略投资者九识智能，九识智能2021年成立，截至2025年底，其运营全球最大RoboVan无人货运车队。</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>引入战略投资者</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="n">
-        <v>0.41</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C55" s="2" t="inlineStr"/>
       <c r="D55" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>sz002808</t>
+          <t>sz000863</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>*ST恒久</t>
+          <t>三湘印象</t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>4.94</v>
+        <v>5.71</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>3天2板</t>
-        </is>
-      </c>
+        <v>10.02</v>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司的控股子公司福建省闽保信息技术有限公司是一家从事信息安全领域软件开发及系统集成的高新技术企业。</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr"/>
+          <t>借壳预期|2025年10月28日，三湘印象股份有限公司发布公告，提名苏存颖女士为公司第八届董事会董事候选人。苏存颖的简历显示，其现任职务为荣芯半导体(中国)有限公司投融资部总监。此项任命已在2025年第二次临时股东会上获得通过。</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>借壳预期</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="n">
-        <v>0.41</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C56" s="2" t="inlineStr"/>
       <c r="D56" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>sz002713</t>
+          <t>sh603657</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>*ST东易</t>
+          <t>春光科技</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>12.36</v>
+        <v>27.94</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司基于数字化系统优势和业务场景优势，研发推出了行业内首个新一代AIGC技术和真家系统结合的全新设计工具“真家 AIGC”，同时打造出AI 创意大师、AI小白设计家两款智能应用设计工具。</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr"/>
+          <t>家电|公司主营业务为吸尘器零件、橡塑软管、塑料制品、小家电的研发、制造和销售及自营进出口业务。</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>家电</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="n">
-        <v>0.41</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C57" s="2" t="inlineStr"/>
       <c r="D57" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>sh603261</t>
+          <t>sz300992</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST立航 </t>
+          <t>泰福泵业</t>
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>34.49</v>
+        <v>41.88</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司是以飞机地面保障设备、航空器试验和检测设备、飞机工艺装备、飞机零件加工和飞机部件装配等专业研发、设计、制造、销售为一体的军民融合企业。</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr"/>
+          <t>实控人变更|泰福泵业公告称，实控人陈宜文、林慧夫妇及地久电子与诤远行共同签署《控制权收购协议》，协议约定，陈宜文、林慧拟以协议转让的方式向诤远行分别转让公司4.18%、1.05%股份。陈宜文、林慧拟以股权转让的方式将地久电子的100%股权向诤远行转让，转让完成后诤远行通过地久电子间接持有公司18.88%股份。本次转让完成后，诤远行直接和间接合计持有公司总股本的24.11%。公司控股股东变更为诤远行，孙凯将成为公司实际控制人。</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>实控人变更</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="n">
-        <v>0.41</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C58" s="2" t="inlineStr"/>
       <c r="D58" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>sz002424</t>
+          <t>sz002800</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>ST百灵</t>
+          <t>天顺股份</t>
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>5.07</v>
+        <v>22.91</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>4.97</v>
+        <v>9.99</v>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司是我国最大的苗药研发、生产企业之一,贵州中药行业的龙头企业，国内中药行业的知名企业。</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr"/>
+          <t>物流+一带一路|公司作为疆内第三方物流、供应链管理的龙头企业，国际铁路业务在2022年开行了莫斯科、杜伊斯堡、汉堡、梅杰乌、阿拉木图、热特苏、塔什干、格鲁吉亚、意大利、梅尔辛、马拉等中亚、中欧方向的班列。国际航班货源业务在2022年以乌鲁木齐为中心开通了格鲁吉亚第比利斯等全货机航线；在海口开设海口至莫斯科航线；在武汉开设了武汉至莫斯科航线。</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>物流, 一带一路</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="n">
-        <v>0.41</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C59" s="2" t="inlineStr"/>
       <c r="D59" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>sz000668</t>
+          <t>sh600250</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>*ST荣控</t>
+          <t>南京商旅</t>
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>14.7</v>
+        <v>14.05</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>5</v>
+        <v>10.02</v>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司主营业务为房地产开发，经营模式以自主开发销售为主，曾推出国内第一个小户型楼盘，第一家运动主题社区，在业内产生较大影响。</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr"/>
+          <t>旅游+零售|1.公司旅游业务主要在子公司秦淮风光开展，秦淮风光主要业务为向游客提供内秦淮河水域的水上游船观光游览服务，船票收入为主要收入来源。
+2.公司零售业务的核心企业是控股子公司南京南商商业运营管理有限责任公司，南商运营主要从事单店百货零售业务，拥有南京商厦20年经营权。南京商厦是南京城北地区主要商业综合体之一，是集购物、餐饮、娱乐于一体的现代化、多功能、综合性大型百货商场，在所处区域占有较高的市场地位。</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>旅游, 零售</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="n">
-        <v>0.41</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>sz000972</t>
+          <t>sz002580</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>*ST中基</t>
+          <t>圣阳股份</t>
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>3.99</v>
+        <v>17.61</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>5</v>
+        <v>9.99</v>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司依托新疆得天独厚的地域和自然优势，致力于发展番茄“红色产业”，产业规模居于前列，产品行销世界数十国家和地区，是全球主要食品企业长期、固定的原料供应商。</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="C61" s="2" t="inlineStr"/>
-      <c r="D61" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>sh603838</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">*ST四通 </t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="n">
-        <v>8.76</v>
-      </c>
-      <c r="H61" s="2" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 公司是一家集研发、设计、生产、销售于一体的新型家居生活陶瓷供应商，产品覆盖日用陶瓷、卫生陶瓷、艺术陶瓷、建筑装饰等全系列家居生活用瓷。</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="C62" s="2" t="inlineStr"/>
-      <c r="D62" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>sh603580</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">*ST艾艾 </t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>17.36</v>
-      </c>
-      <c r="H62" s="2" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 公司是专业从事为轻型输送带的研发、生产及销售，境外营业收入大于50%。</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="C63" s="2" t="inlineStr"/>
-      <c r="D63" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>sh600381</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">*ST春天 </t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H63" s="2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 在大健康业务方面，公司已基本完成了涵盖保健食品、药品等冬虫夏草高效利用产品的储备和战略布局。</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="C64" s="2" t="inlineStr"/>
-      <c r="D64" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>sz002168</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>*ST惠程</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="H64" s="2" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 公司旗下控股子公司哆可梦以基于大数据精细化营销的流量经营业务和移动游戏的研发、发行及游戏平台的运营为主营业务</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr"/>
-      <c r="D65" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>sh600539</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>狮头股份</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>15.63</v>
-      </c>
-      <c r="H65" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>5天4板</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>并购重组|2025年3月7日公告，公司拟以发行股份及支付现金方式向王旭龙琦等14名交易对方收购杭州利珀科技100%股权，同时向上市公司实控人旗下企业募集配套资金。本次交易预计构成重大资产重组。标的公司自成立以来一直致力于机器视觉相关技术产品的研发、生产与销售。</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>并购重组</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr"/>
-      <c r="D66" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>sh600502</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>安徽建工</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="n">
-        <v>5.12</v>
-      </c>
-      <c r="H66" s="2" t="n">
-        <v>10.11</v>
-      </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>基建|公司是一家国有控股上市公司，主营业务包括工程施工、房地产开发、水电投资建设与运营。</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>基建</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr"/>
-      <c r="D67" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>sz301008</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>宏昌科技</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="n">
-        <v>35.24</v>
-      </c>
-      <c r="H67" s="2" t="n">
-        <v>19.99</v>
-      </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>投资张雪机车|在3月28日进行的世界超级摩托车锦标赛（WSBK）中量级赛事（葡萄牙站）中，法国车手Valentin Debise驾驶张雪机车（编号53）820RR-RS车型，以领先近4秒的优势强势夺冠。宏昌科技通过旗下投资基金间接投资了张雪机车。</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>投资张雪机车</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr"/>
-      <c r="D68" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>sz002686</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>亿利达</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="n">
-        <v>7.89</v>
-      </c>
-      <c r="H68" s="2" t="n">
-        <v>10.04</v>
-      </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>数据中心风机|公司EC风机产品可以应用于数据中心冷却设备，与国内多家精密空调制造企业有合作。</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>数据中心风机</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr"/>
-      <c r="D69" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>sh688693</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">锴威特  </t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="n">
-        <v>54.9</v>
-      </c>
-      <c r="H69" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>并购重组|锴威特公告称，公司拟通过发行股份及支付现金方式向易坤、晶格共智、晶格共创、晶格共赢、晶格顶峰、晶格未来等26名交易对方购买其合计持有的晶艺半导体100.00%股份，并募集配套资金。截至预案签署日，相关审计、评估工作尚未完成，标的资产财务数据及评估结果将在重组报告书中披露。本次交易预计构成重大资产重组。</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>并购重组</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr"/>
-      <c r="D70" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>sh603016</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">新宏泰  </t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="n">
-        <v>45.02</v>
-      </c>
-      <c r="H70" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>电网设备|公司主营业务为断路器关键部件，低压断路器及刀熔开关的研发，生产与销售，公司实控人为无锡市人民政府国有资产监督管理委员会。</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>电网设备</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr"/>
-      <c r="D71" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>sz003036</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>泰坦股份</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="H71" s="2" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>机器人+固态电池|1.2026年2月2日公司在互动平台表示，公司纺织智能柔性操作机器人研发进展顺利，相关产品目前处于运行测试和进一步优化阶段。
-2.公司设立了控股子公司，主要从事固态电池锂硫磷氯电解质的研发和生产。</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>机器人, 固态电池</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr"/>
-      <c r="D72" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>sz300385</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>雪浪环境</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="n">
-        <v>19.82</v>
-      </c>
-      <c r="H72" s="2" t="n">
-        <v>19.98</v>
-      </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>重整|雪浪环境公告称，公司与上海氦星万联科技发展合伙企业(有限合伙)等四方及预重整引导人签署《重整投资协议》，并与上海氦星光曜科技发展合伙企业签署附属协议。根据协议，重整完成后氦星万联将成为公司控股股东。</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>重整</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr"/>
-      <c r="D73" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>sh603256</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>宏和科技</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="n">
-        <v>72.14</v>
-      </c>
-      <c r="H73" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>电子玻纤布|公司是全球领先的中高端电子级玻璃纤维布专业厂商，是全球少数具备极薄布生产能力的厂商之一。公司主要产品为中高端电子级玻璃纤维布系列产品，为制造电子产品核心铜箔基板的重要原料。</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>电子玻纤布</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr"/>
-      <c r="D74" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>sh603061</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">金海通  </t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="n">
-        <v>284.67</v>
-      </c>
-      <c r="H74" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>半导体设备|公司是一家从事研发、生产并销售半导体芯片测试设备的高新技术企业，深耕集成电路测试分选机（Test handler）领域，其UPH（单位小时产出）最大可达到13500颗，可测试芯片尺寸范围可涵盖2*2mm~100*100mm。</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>半导体设备</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr"/>
-      <c r="D75" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>sz002634</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>棒杰股份</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="n">
-        <v>8.130000000000001</v>
-      </c>
-      <c r="H75" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>重整+光伏|1.棒杰股份2月2日公告,公司及子公司扬州棒杰近日收到扬州经开区法院送达的《民事裁定书》,法院于1月30日裁定受理兴业银行苏州分行对扬州棒杰的重整申请。
-2.公司拟投资设立全资子公司棒杰新能源集团有限公司布局光伏产业，注册资本为5亿元。从而形成“无缝服装+光伏”双主业的业务结构。公司与江苏诺信就扬州经开区600MW地面光伏电站一期240MW农光互补项目建设等合作。</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>重整, 光伏</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr"/>
-      <c r="D76" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>sh600724</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>宁波富达</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="n">
-        <v>6.39</v>
-      </c>
-      <c r="H76" s="2" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>房地产|公司的最终控制人为宁波市人民政府国有资产监督管理委员会。公司主营商业地产的出租、自营联营及托管业务，其中包括物业管理 。</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>房地产</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr"/>
-      <c r="D77" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>sh603358</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>华达科技</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="H77" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>增持|华达科技公告称，基于对公司发展前景的信心和公司股票长期投资价值的认可，股东张耀坤计划6个月内以集中竞价或大宗交易方式增持公司A股股份，累计增持金额不低于2亿元且不超过3亿元，增持价格不超过70元/股。</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>增持</t>
+          <t>储能|公司聚焦网络能源、智慧储能和绿色动力应用领域，提供备用电源、储能电源、动力电源和新能源系统解决方案及运维服务等，主要产品包括锂离子电池及电源系统、铅蓄电池及系统、新能源储能系统集成产品及服务等。</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>储能</t>
         </is>
       </c>
     </row>
@@ -3967,7 +3232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3994,16 +3259,16 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sh603538</t>
+          <t>sz002361</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">美诺华  </t>
+          <t>神剑股份</t>
         </is>
       </c>
     </row>
@@ -4013,12 +3278,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sz002361</t>
+          <t>sh600488</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>神剑股份</t>
+          <t>津药药业</t>
         </is>
       </c>
     </row>
@@ -4028,12 +3293,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sh600996</t>
+          <t>sz000008</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>贵广网络</t>
+          <t>神州高铁</t>
         </is>
       </c>
     </row>
@@ -4043,12 +3308,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sh600539</t>
+          <t>sz002578</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>狮头股份</t>
+          <t>闽发铝业</t>
         </is>
       </c>
     </row>
@@ -4058,12 +3323,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sz002038</t>
+          <t>sh600502</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>双鹭药业</t>
+          <t>安徽建工</t>
         </is>
       </c>
     </row>
@@ -4073,12 +3338,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sh603585</t>
+          <t>sz000592</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>苏利股份</t>
+          <t>平潭发展</t>
         </is>
       </c>
     </row>
@@ -4088,12 +3353,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>sh600513</t>
+          <t>sz002634</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>联环药业</t>
+          <t>棒杰股份</t>
         </is>
       </c>
     </row>
@@ -4103,72 +3368,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>sh603618</t>
+          <t>sz301008</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>杭电股份</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>sz003042</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>中农联合</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>sz002432</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>九安医疗</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>sz000890</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>法尔胜</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>sh600488</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>津药药业</t>
+          <t>宏昌科技</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,19 +476,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K60"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="100" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="85" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="216" customWidth="1" min="10" max="10"/>
+    <col width="232" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -552,84 +552,84 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>高铁轨交</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.62</v>
+        <v>3.87</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>央视财经报道，长江入海口，“十五五”重大工程——沿江高铁的标志性项目正加紧施工，沿江高铁总投资超5000亿元。</t>
+          <t>美国癌症研究协会(AACR)年会将于2026年4月17-22日在美国圣地亚哥召开。据报道，今年共有超过100家中国药企亮相AACR，带来近400项研究成果。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>sz000927</t>
+          <t>sh600488</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>中国铁物</t>
+          <t>津药药业</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>3.34</v>
+        <v>5.76</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>9.869999999999999</v>
+        <v>9.92</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>5天3板</t>
+          <t>4天4板</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>高铁+物流|围绕路网安全和降本增效，公司开展了铁路专用检测设备研发、线路综合检测、钢轨道岔廓形设计、高铁轨道线路斜裂纹检测、高铁铁路轨道精调、钢轨焊接、大小机打磨集成服务、施工监测、道岔大修等线路综合运维集成服务，形成了完整的线路运维服务体系。</t>
+          <t>原料药|公司主要从事皮质激素类、氨基酸类原料药及制剂的研发、生产和销售，产品包括地塞米松系列、泼尼松系列、甲泼尼龙系列、倍他米松系列等40余个皮质激素原料药品种，23个氨基酸原料药品种，以及16个剂型药品。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>高铁, 物流</t>
+          <t>原料药</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>高铁轨交</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.62</v>
+        <v>3.87</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>央视财经报道，长江入海口，“十五五”重大工程——沿江高铁的标志性项目正加紧施工，沿江高铁总投资超5000亿元。</t>
+          <t>美国癌症研究协会(AACR)年会将于2026年4月17-22日在美国圣地亚哥召开。据报道，今年共有超过100家中国药企亮相AACR，带来近400项研究成果。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sz000008</t>
+          <t>sz002821</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>神州高铁</t>
+          <t>凯莱英</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>3.27</v>
+        <v>121.85</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -638,148 +638,150 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>高铁+机器人|1.公司提供轨道交通运营维护全产业链智能装备系统，并以此为依托，提供轨道交通运营及维保专业服务，是中国轨道交通运营维护领域首家涵盖全产业链装备及运营维保服务的上市公司。
-2.神州高铁在互动平台表示，近年来，公司积极加强智能化、数字化产品研发，动车组空心车轴超声检测机器人、动车组车轮超声检测机器人等智能产品已进入样机测试阶段。</t>
+          <t>业绩+CRO|1.凯莱英公告称，公司发布2025年年度报告，实现营业收入66.70亿元，同比增长14.91%；归属于上市公司股东的净利润11.33亿元，同比增长19.35%。公司拟向全体股东每10股派发现金红利13元(含税)，送红股0股，不以公积金转增股本。
+2.公司是一家全球领先、技术驱动型的医药外包服务一站式综合服务商，通过为国内外制药公司、生物技术公司提供药品全生命周期的一站式CMC服务、高效和高质量的研发与生产服务。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>高铁, 机器人</t>
+          <t>业绩, CRO</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>高铁轨交</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.62</v>
+        <v>3.87</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>央视财经报道，长江入海口，“十五五”重大工程——沿江高铁的标志性项目正加紧施工，沿江高铁总投资超5000亿元。</t>
+          <t>美国癌症研究协会(AACR)年会将于2026年4月17-22日在美国圣地亚哥召开。据报道，今年共有超过100家中国药企亮相AACR，带来近400项研究成果。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sz301048</t>
+          <t>sz002923</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>金鹰重工</t>
+          <t>润都股份</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>13.09</v>
+        <v>17.24</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>19.98</v>
+        <v>10.02</v>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>高铁|公司是国内领先的轨道工程装备产品供应商，是国铁集团系统内唯一取得相关产品型号合格证和制造许可并能够研制并生产轨道工程装备的企业。</t>
+          <t>创新药+电子烟|1.公司1类创新药盐酸去甲乌药碱注射液可作为心脏负荷试验药物用于核素心肌灌注显像，以辅助诊断和评估心肌缺血。
+2.子公司润都制药（荆门）有限公司生产的电子烟用烟碱品质获得客户普遍认可，并已形成商业化销售。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>高铁</t>
+          <t>创新药, 电子烟</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>高铁轨交</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.62</v>
+        <v>3.87</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>央视财经报道，长江入海口，“十五五”重大工程——沿江高铁的标志性项目正加紧施工，沿江高铁总投资超5000亿元。</t>
+          <t>美国癌症研究协会(AACR)年会将于2026年4月17-22日在美国圣地亚哥召开。据报道，今年共有超过100家中国药企亮相AACR，带来近400项研究成果。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sh600528</t>
+          <t>sz000534</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>中铁工业</t>
+          <t>万泽股份</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>9.17</v>
+        <v>38.98</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>9.950000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>高铁+盾构机|公司是中国中铁重组整合中铁山桥、中铁宝桥、中铁科工和中铁装备成立的专业从事隧道掘进设备、铁路道岔、钢桥梁、大型铁路施工机械以及新型轨道交通的研发设计、制造安装和技术服务的企业集团。</t>
+          <t>医药+燃气轮机|1.公司主要产品金双歧和定君生均为独家创新药，受集采降价影响较小。
+2.公司的高温合金产品主要用于航空发动机、燃气轮机（地面与船舶燃机、核电、机车动力等领域）、涡轮增压器等，主要客户即该领域公司。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>高铁, 盾构机</t>
+          <t>医药, 燃气轮机</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>高铁轨交</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.62</v>
+        <v>3.87</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>央视财经报道，长江入海口，“十五五”重大工程——沿江高铁的标志性项目正加紧施工，沿江高铁总投资超5000亿元。</t>
+          <t>美国癌症研究协会(AACR)年会将于2026年4月17-22日在美国圣地亚哥召开。据报道，今年共有超过100家中国药企亮相AACR，带来近400项研究成果。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sh600495</t>
+          <t>sz002940</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>晋西车轴</t>
+          <t>昂利康</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>4.93</v>
+        <v>34.88</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>10.04</v>
+        <v>10</v>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>高铁|公司控股股东是中国兵器工业集团旗下晋西工业集团，公司是国内外铁路装备行业车轴细分领域中最具影响力的供应商之一。</t>
+          <t>创新药|公司目前正在进行的创新药研发项目为注射用ALK-N001，该药物是一种创新的肿瘤微环境激活型的小分子偶联药物，已于2025年2月收到国家药品监督管理局签发的境内生产药品注册临床试验《受理通知书》。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>高铁</t>
+          <t>创新药</t>
         </is>
       </c>
     </row>
@@ -790,45 +792,41 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-0.6</v>
+        <v>3.87</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>据媒体报道，4月17日至22日，美国癌症研究协会（AACR）年会将在圣地亚哥举行，104家中国药企将携250余款创新药亮相。</t>
+          <t>美国癌症研究协会(AACR)年会将于2026年4月17-22日在美国圣地亚哥召开。据报道，今年共有超过100家中国药企亮相AACR，带来近400项研究成果。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sz002082</t>
+          <t>sz300149</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>万邦德</t>
+          <t>睿智医药</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>30.2</v>
+        <v>12.42</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6天4板</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">创新药+AI|在研发端，公司探索人工智能在创新药设计、筛选、实验设计等环节的应用，目前全球首个治疗胃轻瘫的中药1.1类新药“理中消痞颗粒”正在开展临床研究。 </t>
+          <t>CDMO|公司是一家拥有领先水平的生物药、化学药一站式医药研发及生产外包服务提供商，主营业务包含两大业务板块，分别为医药研发及生产服务（CRO/CDMO）、微生态营养与医疗。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>创新药, AI</t>
+          <t>CDMO</t>
         </is>
       </c>
     </row>
@@ -839,45 +837,41 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>-0.6</v>
+        <v>3.87</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>据媒体报道，4月17日至22日，美国癌症研究协会（AACR）年会将在圣地亚哥举行，104家中国药企将携250余款创新药亮相。</t>
+          <t>美国癌症研究协会(AACR)年会将于2026年4月17-22日在美国圣地亚哥召开。据报道，今年共有超过100家中国药企亮相AACR，带来近400项研究成果。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sh600488</t>
+          <t>sh600851</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>津药药业</t>
+          <t>海欣股份</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>5.24</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>9.950000000000001</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>原料药|公司主要从事皮质激素类、氨基酸类原料药及制剂的研发、生产和销售，产品包括地塞米松系列、泼尼松系列、甲泼尼龙系列、倍他米松系列等40余个皮质激素原料药品种，23个氨基酸原料药品种，以及16个剂型药品。</t>
+          <t>创新药|子公司上海海欣生物技术有限公司APDC项目主要用于结直肠癌治疗，目前海欣生物就APDC三期项目正多方面探索解决方案。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>原料药</t>
+          <t>创新药</t>
         </is>
       </c>
     </row>
@@ -888,42 +882,41 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-0.6</v>
+        <v>3.87</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>据媒体报道，4月17日至22日，美国癌症研究协会（AACR）年会将在圣地亚哥举行，104家中国药企将携250余款创新药亮相。</t>
+          <t>美国癌症研究协会(AACR)年会将于2026年4月17-22日在美国圣地亚哥召开。据报道，今年共有超过100家中国药企亮相AACR，带来近400项研究成果。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sz002821</t>
+          <t>sz000078</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>凯莱英</t>
+          <t>海王生物</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>110.77</v>
+        <v>3.45</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>10</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>业绩+CRO|1.凯莱英公告称，公司发布2025年年度报告，实现营业收入66.70亿元，同比增长14.91%；归属于上市公司股东的净利润11.33亿元，同比增长19.35%。公司拟向全体股东每10股派发现金红利13元(含税)，送红股0股，不以公积金转增股本。
-2.公司是一家全球领先、技术驱动型的医药外包服务一站式综合服务商，通过为国内外制药公司、生物技术公司提供药品全生命周期的一站式CMC服务、高效和高质量的研发与生产服务。</t>
+          <t>创新药|公司一直致力于创新药和仿制药的研究。公司在研发领域拥有国家认定企业技术中心、企业博士后科研工作站、广东省教育部产学研结合示范基地、深圳市海洋药物研究开发工程中心、广东省小分子抗肿瘤创新药物工程技术研究中心等技术创新平台，拥有60余项发明专利。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>业绩, CRO</t>
+          <t>创新药</t>
         </is>
       </c>
     </row>
@@ -934,36 +927,36 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-0.6</v>
+        <v>3.87</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>据媒体报道，4月17日至22日，美国癌症研究协会（AACR）年会将在圣地亚哥举行，104家中国药企将携250余款创新药亮相。</t>
+          <t>美国癌症研究协会(AACR)年会将于2026年4月17-22日在美国圣地亚哥召开。据报道，今年共有超过100家中国药企亮相AACR，带来近400项研究成果。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sh605116</t>
+          <t>sh600594</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">奥锐特  </t>
+          <t>益佰制药</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>29.39</v>
+        <v>4.36</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>9.99</v>
+        <v>10.1</v>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>创新药|参股源道医药聚焦慢病领域，致力于 FIRST-IN-CLASS 原创新药的自主研发；利用研究团队在人工智能药物设计方面特有的技术优势，通过精准药物设计高效地发现新药先导物，充分分析临床数据快速推进慢病个性化和精准化治疗药物的发现。</t>
+          <t>创新药|公司苗药相关研发工作有民族药珍珠滴丸Ⅲ期临床研究、苗药理气活血滴丸产业化应用研究等。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -979,401 +972,394 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>-0.6</v>
+        <v>3.87</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>据媒体报道，4月17日至22日，美国癌症研究协会（AACR）年会将在圣地亚哥举行，104家中国药企将携250余款创新药亮相。</t>
+          <t>美国癌症研究协会(AACR)年会将于2026年4月17-22日在美国圣地亚哥召开。据报道，今年共有超过100家中国药企亮相AACR，带来近400项研究成果。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sz002788</t>
+          <t>sz000788</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>鹭燕医药</t>
+          <t>北大医药</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>16.17</v>
+        <v>6.56</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>10</v>
+        <v>10.07</v>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>医药+福建|公司从事医药分销和零售，隶属于医药流通行业，系福建省最大的医药流通企业。</t>
+          <t>创新药|公司已建立起自主知识产权、仿创技术、技术创新为一体的技术核心体系，研发领 域聚焦于抗感染类、镇痛类、精神类、慢病类等创新药、高端仿制药和大市场品种，为企业发展提供持续优化的产品结技术中心可独立完成仿制药、一致性评价品种的研发全流程，也可开展创新药的药学部分研究工作。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>医药, 福建</t>
+          <t>创新药</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>商业航天</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>-0.8</v>
+        <v>3.87</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>据中科宇航消息，3月30日19时，力箭二号遥一运载火箭在东风商业航天创新试验区发射，将新征程01卫星、新征程02卫星和天视卫星01星精准送入预定轨道，发射任务取得圆满成功。</t>
+          <t>美国癌症研究协会(AACR)年会将于2026年4月17-22日在美国圣地亚哥召开。据报道，今年共有超过100家中国药企亮相AACR，带来近400项研究成果。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sz002361</t>
+          <t>sz300436</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>神剑股份</t>
+          <t>广生堂</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>16.5</v>
+        <v>119.03</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4天4板</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>商业航天|公司参与了星网项目建设，提供卫星上相关零部件。目前航天类产品有卫星天线、反射器及支撑塔等。</t>
+          <t>创新药|公司创新药控股子公司福建广生中霖生物科技有限公司的在研乙肝治疗一类创新药奈瑞可韦GST-HG141的III期临床试验，已于近日完成全部受试者入组，合计入组578例。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>商业航天</t>
+          <t>创新药</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>商业航天</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-0.8</v>
+        <v>3.87</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>据中科宇航消息，3月30日19时，力箭二号遥一运载火箭在东风商业航天创新试验区发射，将新征程01卫星、新征程02卫星和天视卫星01星精准送入预定轨道，发射任务取得圆满成功。</t>
+          <t>美国癌症研究协会(AACR)年会将于2026年4月17-22日在美国圣地亚哥召开。据报道，今年共有超过100家中国药企亮相AACR，带来近400项研究成果。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sz002565</t>
+          <t>sh688488</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>顺灏股份</t>
+          <t>艾迪药业</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>17.01</v>
+        <v>17.82</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>10.03</v>
+        <v>20</v>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>太空算力|公司2025年6月以1.1亿元人民币投资北京轨道辰光科技有限公司，持股比例为19.30%。轨道辰光的主要业务是通过将算力卫星发射至晨昏轨道，组建太空数据中心，为客户提供算力服务，其经营范围包括微小卫星生产制造、微小卫星科研试验、互联网信息服务等。轨道辰光首颗试验星算力规模预计25p。</t>
+          <t>创新药|公司是一家专注于医药领域，集药品研发、生产、销售于一体的高新技术企业，瞄准艾滋病、炎症以及恶性肿瘤等严重威胁人类健康的重大疾病领域。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>太空算力</t>
+          <t>创新药</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>商业航天</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>-0.8</v>
+        <v>2.44</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>据中科宇航消息，3月30日19时，力箭二号遥一运载火箭在东风商业航天创新试验区发射，将新征程01卫星、新征程02卫星和天视卫星01星精准送入预定轨道，发射任务取得圆满成功。</t>
+          <t>在智谱2025年业绩说明会上，智谱CEO张鹏对记者介绍，2026年一季度智谱的API调用定价提升83%，即便如此，市场依然呈现出供不应求的情况，调用量增长400%。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sh600894</t>
+          <t>sh600666</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>广日股份</t>
+          <t xml:space="preserve">奥瑞德  </t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>9.59</v>
+        <v>6.27</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="I14" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>11天6板</t>
+        </is>
+      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>参股中科宇航|公司参股的广州国资国企创新投资基金合伙企业(有限合伙)仅间接持有中科宇航技术股份有限公司约0.1%股权。</t>
+          <t>算力租赁|公司设立全资子公司北京智算力、深圳智算力，使用自有资金投资建设算力租赁一、二、三期项目。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>参股中科宇航</t>
+          <t>算力租赁</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>商业航天</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>-0.8</v>
+        <v>2.44</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>据中科宇航消息，3月30日19时，力箭二号遥一运载火箭在东风商业航天创新试验区发射，将新征程01卫星、新征程02卫星和天视卫星01星精准送入预定轨道，发射任务取得圆满成功。</t>
+          <t>在智谱2025年业绩说明会上，智谱CEO张鹏对记者介绍，2026年一季度智谱的API调用定价提升83%，即便如此，市场依然呈现出供不应求的情况，调用量增长400%。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sz002342</t>
+          <t>sz000815</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>巨力索具</t>
+          <t>美利云</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>14.4</v>
+        <v>20.7</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>10.01</v>
+        <v>9.99</v>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>商业航天|公司为神舟十九号发射任务提供了火箭转运索具、总装索具、火箭分离索具等。</t>
+          <t>国资云|公司是中国诚通控股集团旗下上市公司，数据中心位于宁夏中卫市，处于国家战略工程“东数西算”的双节点城市。美利云公告称，目前数据中心业务主要提供机架出租、网络接入及运维服务，暂未提供算力。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>商业航天</t>
+          <t>国资云</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>商业航天</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>-0.8</v>
+        <v>2.44</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>据中科宇航消息，3月30日19时，力箭二号遥一运载火箭在东风商业航天创新试验区发射，将新征程01卫星、新征程02卫星和天视卫星01星精准送入预定轨道，发射任务取得圆满成功。</t>
+          <t>在智谱2025年业绩说明会上，智谱CEO张鹏对记者介绍，2026年一季度智谱的API调用定价提升83%，即便如此，市场依然呈现出供不应求的情况，调用量增长400%。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sz301079</t>
+          <t>sh605289</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>邵阳液压</t>
+          <t>罗曼股份</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>44.76</v>
+        <v>104.16</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>机器人+商业航天|1.公司的深海机器人液压控制系统能够深潜1500米进行数据采集和故障诊断。
-2.公司主营业务为液压柱塞泵、液压缸、液压系统的设计、研发、生产、销售和液压产品专业技术服务，产品可以用于航空航天领域，西昌卫星发射中心、福建航空装备维修中心都是公司的重要客户。</t>
+          <t>AI应用+服务器|1.旗下Holovis是全球交互技术研发先行者，自主研发虚拟现实、无感交互等领域二十多项国际专有技术，将生成式AI大数据分析平台 Deep Smarts、基于AI视觉追踪的智能交互系统 HoloTrac 等核心技术融入个性化智能体验和运营，为行业发展注入强大创新引擎。
+2.参股上海武桐树高新技术有限公司主要从事AIDC算力服务器与集群综合解决方案服务业务。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>机器人, 商业航天</t>
+          <t>AI应用, 服务器</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>体育产业</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>0.59</v>
+        <v>2.44</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>当地时间3月28日，WSBK葡萄牙站SSP组别，法国车手瓦伦丁·德比斯夺冠，其所骑820RR-RS，来自中国摩托车制造商重庆张雪机车工业有限公司。</t>
+          <t>在智谱2025年业绩说明会上，智谱CEO张鹏对记者介绍，2026年一季度智谱的API调用定价提升83%，即便如此，市场依然呈现出供不应求的情况，调用量增长400%。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sh605299</t>
+          <t>sh603296</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>舒华体育</t>
+          <t>华勤技术</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>21.33</v>
+        <v>88.14</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>12天6板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>体育产业+福建|公司主营业务为健身器材和展示架产品的研发、生产和销售，其中健身器材包括室内健身器材、室外路径产品。</t>
+          <t>液冷+服务器|1.公司已于2021年取得液冷装置及设备的实用新型专利，并在散热方面取得了数据产品散热核心技术。目前在部分的人工智能服务器上使用液冷散热技术。
+2.公司服务器ODM业务主要为服务器品牌厂商提供通用型服务器、为云计算系统集成商提供定制型服务器。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>体育产业, 福建</t>
+          <t>液冷, 服务器</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>体育产业</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>0.59</v>
+        <v>2.44</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>当地时间3月28日，WSBK葡萄牙站SSP组别，法国车手瓦伦丁·德比斯夺冠，其所骑820RR-RS，来自中国摩托车制造商重庆张雪机车工业有限公司。</t>
+          <t>在智谱2025年业绩说明会上，智谱CEO张鹏对记者介绍，2026年一季度智谱的API调用定价提升83%，即便如此，市场依然呈现出供不应求的情况，调用量增长400%。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sz301008</t>
+          <t>sh603687</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>宏昌科技</t>
+          <t xml:space="preserve">大胜达  </t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>42.29</v>
+        <v>16.39</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>20.01</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>参股张雪机车|宏昌科技通过旗下投资基金间接投资了张雪机车。</t>
+          <t>并购重组+算力芯片|大胜达公告称，公司拟通过股权受让及增资方式合计投资5.5亿元取得芯瞳半导体技术（厦门）有限公司22.9831%的股权。其中，以2786万元受让2.7074%股权，以2214万元受让1.5961%股权，并以5亿元增资（分两次，第一次2.5亿元，第二次2.5亿元需满足流片成功条件）。同时，控股股东新胜达以5000万元同条件增资，取得1.9608%股权。芯瞳半导体成立于2019年，是国内专注于通用高性能图形处理器芯片设计研发与销售的先驱企业。</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>参股张雪机车</t>
+          <t>并购重组, 算力芯片</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>体育产业</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>0.59</v>
+        <v>2.44</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>当地时间3月28日，WSBK葡萄牙站SSP组别，法国车手瓦伦丁·德比斯夺冠，其所骑820RR-RS，来自中国摩托车制造商重庆张雪机车工业有限公司。</t>
+          <t>在智谱2025年业绩说明会上，智谱CEO张鹏对记者介绍，2026年一季度智谱的API调用定价提升83%，即便如此，市场依然呈现出供不应求的情况，调用量增长400%。</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sh600158</t>
+          <t>sh603985</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>中体产业</t>
+          <t>恒润股份</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>11.99</v>
+        <v>20.46</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>10</v>
@@ -1381,27 +1367,27 @@
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>体育产业|公司作为国家体育总局唯一一家A股上市公司，在赛事活动、体育传播、教育培训、体育彩票、体育空间平台、体育认证等业务领域已初步完成全国性布局。</t>
+          <t>算力租赁|子公司上海润六尺主要业务包括算法模型的建立、新型智算服务器的销售、智算中心的建设与运维、算力服务，以及为高校科研团队研究的垂直化模型提供咨询服务等，在手算力2500P，已与芜湖高新区管委会签订了《战略合作框架协议》，芜湖智算中心目标提供超40000P算力。</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>体育产业</t>
+          <t>算力租赁</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>体育产业</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>0.59</v>
+        <v>3.05</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>当地时间3月28日，WSBK葡萄牙站SSP组别，法国车手瓦伦丁·德比斯夺冠，其所骑820RR-RS，来自中国摩托车制造商重庆张雪机车工业有限公司。</t>
+          <t>国信证券表示，2026年迈入Agent元年，AI应用场景加速落地，算力基础设施需求刚性凸显。</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -1409,45 +1395,45 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sz000913</t>
+          <t>sz002902</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>钱江摩托</t>
+          <t>铭普光磁</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>16.67</v>
+        <v>28.78</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>10.03</v>
+        <v>10.02</v>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">摩托车+体育|1.公司致力于高性能摩托车核心技术研发、制造、销售及服务，拥有Benelli、QJMOTOR、钱江等燃油车品牌，排量覆盖50cc-1200cc，品类覆盖复古、街车、巡航、旅行、仿赛、越野等。
-2.钱江携赛800在欧洲参加2024赛季世界超级摩托车锦标赛WSBK，和世界各大知名品牌同场竞技。 </t>
+          <t>光模块+储能|1.铭普光磁在互动平台表示，公司持续开展光模块产品的研发与迭代，目前200G及以下速率光模块正常供货。800G LPO（线性驱动可插拔光模块）方案的ODM定制开发，已实现小批量出货，但整体订单量较小，产生的利润不足以实质性影响公司的整体业绩方向。
+2.2022年5月31日公司在互动平台表示，公司目前生产的用于光伏领域的主要有光伏逆变器用电抗器、高频变压器和电感器，及通信局站用光伏供电系统。</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>摩托车, 体育</t>
+          <t>光模块, 储能</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>-0.7799999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>福建省国资委印发《实施“五大行动”　推动所出资企业向新向优发展工作方案（2026—2028年）》，加快向新质生产力领域布局，向高质量效益转型。</t>
+          <t>国信证券表示，2026年迈入Agent元年，AI应用场景加速落地，算力基础设施需求刚性凸显。</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
@@ -1455,48 +1441,44 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>sz000592</t>
+          <t>sz301312</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>平潭发展</t>
+          <t>智立方</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>12.78</v>
+        <v>103.2</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>5天3板</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>林业+福建|公司在林木业务方面已基本形成“林板一体化”的发展产业链，拥有经营林区近90万亩，在福建省处于行业领先龙头地位。</t>
+          <t>光通信设备|公司在光通信CPO半导体领域推出了多款设备，包括光芯片排巴机、摆盘机、光芯片AOI设备、高精度固晶机等，设备已进入行业技术路线领先的硅光领域，逐步扩大市场份额。</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>林业, 福建</t>
+          <t>光通信设备</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>-0.7799999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>福建省国资委印发《实施“五大行动”　推动所出资企业向新向优发展工作方案（2026—2028年）》，加快向新质生产力领域布局，向高质量效益转型。</t>
+          <t>国信证券表示，2026年迈入Agent元年，AI应用场景加速落地，算力基础设施需求刚性凸显。</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
@@ -1504,48 +1486,44 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>sz002578</t>
+          <t>sh603803</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>闽发铝业</t>
+          <t>瑞斯康达</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>4.69</v>
+        <v>13.68</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>10.09</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.969999999999999</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>铝+福建|公司是国内行业中较早涉足工业型材领域的企业之一，主营业务和产品主要是建筑铝型材、工业铝型材和建筑铝模板的研发、生产、销售。</t>
+          <t>光模块|在高端光模块领域，公司联营企业易锐光电是中国少数产业链上下游关键层面具备完整核心技术和解决方案的高科技企业，新一代基于自主知识产权的25G/100G/超100G集成光收发芯片的光通信模块及光组件，用于电信网络城域网和大型数据中心网络。</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>铝, 福建</t>
+          <t>光模块</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>-0.7799999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>福建省国资委印发《实施“五大行动”　推动所出资企业向新向优发展工作方案（2026—2028年）》，加快向新质生产力领域布局，向高质量效益转型。</t>
+          <t>国信证券表示，2026年迈入Agent元年，AI应用场景加速落地，算力基础设施需求刚性凸显。</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
@@ -1553,44 +1531,45 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>sz000993</t>
+          <t>sh600105</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>永鼎股份</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>16.31</v>
+        <v>30.51</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>9.98</v>
+        <v>9.99</v>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>福建+电力|公司致力于清洁能源、新能源等领域的发展。发电业务是公司业务的核心业务，主要包括水力发电和风力发电。是电力产业链的发电环节，相对电网企业，处于弱势地位，由于水电、风电生产均属清洁能源，电调顺序靠前，与火电相比，来自电网的竞争压力相对较小。公司目前是宁德市唯一以经营清洁能源发电为主营业务的国有控股上市公司。</t>
+          <t>光芯片+光纤|1.公司产品涉及光芯片-光器件-光模块-系统设备的整体覆盖。芯片主要为波分滤波芯片、平面波导芯片、激光器芯片；光器件分为波分器件以及各类连接器件；模块主要有 5G 前传各类彩光模块、数据中心各类高速模块。
+2.公司的特种光纤广泛用于航天、航空、航海、工业制造技术及通信等国民经济的各个领域。</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>福建, 电力</t>
+          <t>光芯片, 光纤</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>-0.7799999999999999</v>
+        <v>1.85</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>福建省国资委印发《实施“五大行动”　推动所出资企业向新向优发展工作方案（2026—2028年）》，加快向新质生产力领域布局，向高质量效益转型。</t>
+          <t>据报道，由乐聚机器人和东方精工联合打造的国内万台级人形机器人自动化产线在广东正式启用，标志着人形机器人规模化量产能力取得重大突破。</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
@@ -1598,180 +1577,186 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>sh603826</t>
+          <t>sz002560</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>坤彩科技</t>
+          <t>通达股份</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>27.67</v>
+        <v>11.87</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
+        <v>10.01</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>化工+福建|公司是一家专业从事无机颜料研发、生产、销售的高新技术企业，经过多年的发展，现已成为全球珠光材料龙头企业。公司提供的珠光材料、二氧化钛、氧化铁、二氯氧钛、三氯化铁等系列产品同属于无机材料，可广泛应用于涂料、塑料、汽车、造纸、化妆品（日化）、油墨、陶瓷、建材、食品、纺织、光伏、新能源、环保等行业。</t>
+          <t>业绩+机器人|1.公司2025年1-12月实现营业收入79.99亿元，同比增长29.00%；归母净利润1.61亿元，同比增长533.17%。
+2.2025年5月9日公司在互动平台表示，公司已研发、试制机器人用电缆样品，目前正在进行第三方测试。</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>化工, 福建</t>
+          <t>业绩, 机器人</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>汽车零部件</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>-1.06</v>
+        <v>1.85</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>北京时间3月28日，世界超级摩托车锦标赛（WSBK）赛场上，中国摩托车品牌张雪机车以近4秒的绝对优势夺冠，一举打破了杜卡迪、雅马哈、川崎等国际豪强对该组别长达数十年的垄断。</t>
+          <t>据报道，由乐聚机器人和东方精工联合打造的国内万台级人形机器人自动化产线在广东正式启用，标志着人形机器人规模化量产能力取得重大突破。</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>sz003033</t>
+          <t>sz002645</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>征和工业</t>
+          <t>华宏科技</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>60.61</v>
+        <v>18.43</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>10</v>
+        <v>10.03</v>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>摩托车+机器人|1.公司作为国内链传动行业的领军企业，专注于各类链传动系统的研发、制造与销售，产品应用于摩托车、汽车、自行车等领域。
-2.2025年4月28日公司在调研中表示，公司研发的的微型链系统项目，重点攻关机器人灵巧手传动技术，尚处于早期技术探索与储备阶段。</t>
+          <t>稀土+机器人|1.公司旗下全资子公司鑫泰科技主营业务为稀土废料的综合利用，即通过钕铁硼废料、荧光粉废料生产高纯稀土氧化物，其全资子公司中杭新材从事稀土永磁材料生产业务。
+2.公司生产的高性能磁材产品已经应用于新能源汽车电机、工业机器人电机、3C电子等高科技领域。</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>摩托车, 机器人</t>
+          <t>稀土, 机器人</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>汽车零部件</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>-1.06</v>
+        <v>1.85</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>北京时间3月28日，世界超级摩托车锦标赛（WSBK）赛场上，中国摩托车品牌张雪机车以近4秒的绝对优势夺冠，一举打破了杜卡迪、雅马哈、川崎等国际豪强对该组别长达数十年的垄断。</t>
+          <t>据报道，由乐聚机器人和东方精工联合打造的国内万台级人形机器人自动化产线在广东正式启用，标志着人形机器人规模化量产能力取得重大突破。</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>sz000030</t>
+          <t>sh603121</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>富奥股份</t>
+          <t>华培动力</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>5.56</v>
+        <v>18.06</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>10.1</v>
+        <v>9.99</v>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>汽车零部件|公司为混合动力车型，如红旗EV、奥迪C8 PHEV配套的相关产品（如电动压缩机、电池冷却器、散热器）已经实现量产。</t>
+          <t>机器人+氢能|1.公司切入机器人传感器赛道，通过并购+自主研发等方式布局磁编码器、MEMS压力传感器、六维力矩传感器等多款传感器。此外，公司单独设立子公司承接人形机器人领域开展的相关业务，专注于人形机器人相关的传感器和芯片的研发和销售。
+2.在新能源汽车领域的氢燃料电池压力/温度、泄露传感器等多品类传感器领域持续研发。</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>汽车零部件</t>
+          <t>机器人, 氢能</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>汽车零部件</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>-1.06</v>
+        <v>1.85</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>北京时间3月28日，世界超级摩托车锦标赛（WSBK）赛场上，中国摩托车品牌张雪机车以近4秒的绝对优势夺冠，一举打破了杜卡迪、雅马哈、川崎等国际豪强对该组别长达数十年的垄断。</t>
+          <t>据报道，由乐聚机器人和东方精工联合打造的国内万台级人形机器人自动化产线在广东正式启用，标志着人形机器人规模化量产能力取得重大突破。</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>sz000678</t>
+          <t>sh603949</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>雪龙集团</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>12.64</v>
+        <v>18.49</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>10.01</v>
+        <v>9.99</v>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>摩托车零部件|公司专注于各类滚动轴承的研发、生产与销售，其产品覆盖汽车、摩托车、工程机械及家用电器等多个领域。</t>
+          <t>参股宇树科技|公司作为有限合伙人通过深创投中小企业发展基金（新疆）有限合伙企业间接持股杭州宇树科技有限公司。目前，深创投中小企业发展基金（新疆）有限合伙企业对杭州宇树科技有限公司的持股比例为1.3546%；公司对深创投中小企业发展基金（新疆）有限合伙企业的持股比例为0.7239%。</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>摩托车零部件</t>
+          <t>参股宇树科技</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>-1.16</v>
+        <v>3.67</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>国盛证券表示，Agent进入实际落地阶段，OpenClaw引领渗透加速。</t>
+          <t>光远新材已于3月31日宣布上调产品价格：电子纱价格上调800元/吨，7628布价格上调0.5元/米。</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
@@ -1779,48 +1764,44 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>sz002995</t>
+          <t>sh605006</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>天地在线</t>
+          <t>山东玻纤</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>24.66</v>
+        <v>9.67</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>3天2板</t>
-        </is>
-      </c>
+        <v>10.01</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>AI数字人|公司已推出AI数字人SAAS产品“星河AI数字人系统”以及帮助企业提高工作效率和协作能力的AI智能应用产品“AIbase” ，满足客户在营销及提升企业经营效能的不同需求。</t>
+          <t>玻纤电子纱|公司主要从事玻璃纤维及其制品的研发、生产与销售，其玻璃纤维电子纱产品可应用于PCB制造。</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>AI数字人</t>
+          <t>玻纤电子纱</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>-1.16</v>
+        <v>3.67</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>国盛证券表示，Agent进入实际落地阶段，OpenClaw引领渗透加速。</t>
+          <t>光远新材已于3月31日宣布上调产品价格：电子纱价格上调800元/吨，7628布价格上调0.5元/米。</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
@@ -1828,44 +1809,44 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>sh603039</t>
+          <t>sh600545</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>泛微网络</t>
+          <t>卓郎智能</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>43.45</v>
+        <v>4</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>10</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>AI智能体|泛微数智大脑Xiaoe.AI为组织每个用户提供了一位7*24工作的智能助理。有了Xiaoe.AI的支撑，办理事务无需摸索与学习多个系统，也不用填写大量的、重复的表单和信息，只要对着手机喊话就完成工作，让组织的业务运营更加敏捷。</t>
+          <t>玻纤捻线机|2025年6月28日公司官微透露，公司与国际复材签订了加捻事业部史上最大额玻璃纤维捻线机订单。玻纤凭借其低介电常数等特性，已成为制造高频高速PCB与高性能芯片封装材料的不二之选。</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>AI智能体</t>
+          <t>玻纤捻线机</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>-1.16</v>
+        <v>3.67</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>国盛证券表示，Agent进入实际落地阶段，OpenClaw引领渗透加速。</t>
+          <t>光远新材已于3月31日宣布上调产品价格：电子纱价格上调800元/吨，7628布价格上调0.5元/米。</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -1873,45 +1854,45 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>sh603660</t>
+          <t>sz002579</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>苏州科达</t>
+          <t>中京电子</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>9.74</v>
+        <v>12.29</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>10.06</v>
+        <v>10.03</v>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>AI+量子通信|1.2023年7月正式推出了KD-GPT大模型，包括多模态大模型、AIGC图像大模型和行业大模型已经初具雏形，并开始在实际项目中投入应用。
-2.苏州科达的量子网呈产品，是国内唯一支持量子通信技术的视频会议产品。</t>
+          <t>机器人+PCB|1.2022年8月2日公司在互动平台表示，消费及工业机器人均需较大量使用PCB（含FPC、RPC及R-F），公司已开始向相关客户提供应用产品服务。
+2.公司主营业务为印制电路板(PCB)的研发、生产、销售与服务，已获得AI PC的小批量订单。</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>AI, 量子通信</t>
+          <t>机器人, PCB</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>光伏</t>
+          <t>液冷IDC</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>-2.36</v>
+        <v>2.69</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>华金证券表示，商业航天产业趋势已来，关注太空光伏新技术方向。</t>
+          <t>业内预测，随着算力持续放量与数据中心建设提速，液冷技术已从“可选配置”变为“强制标配”，市场即将迎来前所未有的机遇期。</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
@@ -1919,49 +1900,44 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>sz002634</t>
+          <t>sh603912</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>棒杰股份</t>
+          <t xml:space="preserve">佳力图  </t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>8.94</v>
+        <v>10</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>9.959999999999999</v>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.01</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>重整+光伏|1.棒杰股份2月2日公告,公司及子公司扬州棒杰近日收到扬州经开区法院送达的《民事裁定书》,法院于1月30日裁定受理兴业银行苏州分行对扬州棒杰的重整申请。
-2.公司拟投资设立全资子公司棒杰新能源集团有限公司布局光伏产业，注册资本为5亿元。从而形成“无缝服装+光伏”双主业的业务结构。公司与江苏诺信就扬州经开区600MW地面光伏电站一期240MW农光互补项目建设等合作。</t>
+          <t>液冷IDC|公司拥有多项核心技术，包含带封闭式高效冷却循环的通信模块、数据中心冷冻站集中控制系统、机房空调VRF系统、CPU液冷技术、VRF技术在机房空调领域的初级应用等多项在研项目。</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>重整, 光伏</t>
+          <t>液冷IDC</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>光伏</t>
+          <t>液冷IDC</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>-2.36</v>
+        <v>2.69</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>华金证券表示，商业航天产业趋势已来，关注太空光伏新技术方向。</t>
+          <t>业内预测，随着算力持续放量与数据中心建设提速，液冷技术已从“可选配置”变为“强制标配”，市场即将迎来前所未有的机遇期。</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
@@ -1969,49 +1945,44 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>sh601908</t>
+          <t>sh603158</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">京运通  </t>
+          <t>腾龙股份</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>5.01</v>
+        <v>12.28</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>10.11</v>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>10.04</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>光伏+半导体|1.公司主营光伏设备（单晶硅生长炉、多晶硅铸锭炉）、多晶硅锭及硅片、光伏电站（地面光伏发电及分布式光伏发电）。
-2.公司半导体相关业务有区熔产品、碳化硅炉、金刚石炉等，金刚石炉目前实现小批量对外销售。</t>
+          <t>服务器液冷|公司电子水泵产品有向客户供货，间接应用于数据中心/服务器液冷领域。</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>光伏, 半导体</t>
+          <t>服务器液冷</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>光伏</t>
+          <t>液冷IDC</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>-2.36</v>
+        <v>2.69</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>华金证券表示，商业航天产业趋势已来，关注太空光伏新技术方向。</t>
+          <t>业内预测，随着算力持续放量与数据中心建设提速，液冷技术已从“可选配置”变为“强制标配”，市场即将迎来前所未有的机遇期。</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
@@ -2019,184 +1990,181 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>sz002218</t>
+          <t>sz002639</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>拓日新能</t>
+          <t>雪人集团</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>6.93</v>
+        <v>18.82</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>太空光伏|公司于2015年参与了东方红卫星“开拓一号”单晶硅太阳电池项目，具备成熟的卫星用光伏组件生产制造能力。</t>
+          <t>氢能+液冷|1.公司已为中科院合肥物质研究所、理化所等多所研究院提供氦气螺杆压缩机，分别应用于全超导托克马克核聚变实验装置、航天试验等大科学工程应用领域。
+2.公司制冷压缩机与机组可作为液冷服务器的配套冷源，为Facebook丹麦数据中心(液冷)提供第三代低充注的氨制冷技术。公司旗下杭州龙华承接了之江实验室新型算力中心环境基础设施升级改造工程的暖通空调项目、之江实验室智算中心机房提升工程(二期)项目。</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>太空光伏</t>
+          <t>氢能, 液冷</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>盾构机</t>
+          <t>锂电池</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>央视财经报道，长江入海口，“十五五”重大工程——沿江高铁的标志性项目正加紧施工，沿江高铁总投资超5000亿元。</t>
+          <t>根据机构测算，2026年全球锂电需求达到3065GWh，同比增长33.7%，对应电解液需求367万吨。</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>sz002542</t>
+          <t>sh603937</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>中化岩土</t>
+          <t>丽岛新材</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>3.28</v>
+        <v>15.27</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>10.07</v>
+        <v>10.01</v>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>盾构机|公司旗下上海力行主营业务为盾构机设备制造和租赁，主要服务对象为国内大型铁路、公路、城市轨道交通及市政等重点施工企业。上海力行盾构机设备既有适用于各地层的大型地铁盾构机，也有适用于水务、电力隧道和城市维修建设的小型盾构机。</t>
+          <t>铝+锂电池|1.公司的主要业务为铝材产品的研发、生产和销售，专注于以建筑工业彩涂铝材、食品包装彩涂铝材及精整切割铝材为主的铝材深加工业务。
+2.2022年5月18日公告，公司拟与安徽五河经济开发区管委会签订《投资合同》，在五河县建设新能源电池集流体材料项目，项目总投资10亿元。</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>盾构机</t>
+          <t>铝, 锂电池</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>盾构机</t>
+          <t>锂电池</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>央视财经报道，长江入海口，“十五五”重大工程——沿江高铁的标志性项目正加紧施工，沿江高铁总投资超5000亿元。</t>
+          <t>根据机构测算，2026年全球锂电需求达到3065GWh，同比增长33.7%，对应电解液需求367万吨。</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sz001239</t>
+          <t>sz002083</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>永达股份</t>
+          <t>孚日股份</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>15.86</v>
+        <v>12.95</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>9.99</v>
+        <v>10.03</v>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>盾构机+机器人|1.公司的隧道掘进及配套设备主要为盾构机的盾体、刀盘体、管片机以及与之配套的定制化支撑管片等金属结构产品。
-2.子公司江苏金源高端装备有限公司的主营业务为高速重载齿轮锻件的研发、生产和销售，产品部分应用于机器人领域。</t>
+          <t>电解液|子公司孚日新能源积极布局锂电池电解液添加剂产品，主要生产氯代碳酸乙烯酯（CEC）、碳酸亚乙烯酯（VC）粗品和电池级产品等动力锂电池上下游系列产品。</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>盾构机, 机器人</t>
+          <t>电解液</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>锂电池</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>-0.06</v>
+        <v>1.39</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>中信建投证券研报称，今年2月，我国出口光纤3779.9吨、金额7.9亿元，同比增长63.6%、126.8%。如果折算为公里数，2月我国出口光纤约2520万芯公里，占我国光纤月有效产量的65%左右。</t>
+          <t>根据机构测算，2026年全球锂电需求达到3065GWh，同比增长33.7%，对应电解液需求367万吨。</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sz000720</t>
+          <t>sh601515</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>新能泰山</t>
+          <t>衢州东峰</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>5.46</v>
+        <v>4.55</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>6天5板</t>
-        </is>
-      </c>
+        <v>9.9</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>电线电缆+光纤光缆|子公司曲阜电缆主要从事电线电缆、光纤光缆、电力光缆等产品的研发、制造与销售，曲阜电缆生产、 销售的电线电缆产品是公司重点发展的智慧供应链业务产品之一。</t>
+          <t>隔膜|公司布局半固态/固态电池隔膜及基膜等相关电池核心材料，投入多款产品的开发，包括复合铜箔/铝箔、泡沫铜、半固态电池功能膜材料、固态电池电解质复合膜和电解质涂布工艺、新能源车用涂料、CCS集成母排结构件等。</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>电线电缆, 光纤光缆</t>
+          <t>隔膜</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>航运</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>-0.06</v>
+        <v>2.65</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>中信建投证券研报称，今年2月，我国出口光纤3779.9吨、金额7.9亿元，同比增长63.6%、126.8%。如果折算为公里数，2月我国出口光纤约2520万芯公里，占我国光纤月有效产量的65%左右。</t>
+          <t>招商轮船在接受调研者提问时表示，近年来全球石油贸易和航运格局的演变，油轮硬资产属性或将日益凸显，在石油链条中日益成为供应链瓶颈，预期回报或有机会大幅提升。</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
@@ -2204,45 +2172,44 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sz000070</t>
+          <t>sh601083</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>特发信息</t>
+          <t>锦江航运</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>17.8</v>
+        <v>12.93</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>10.01</v>
+        <v>10.04</v>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆+商业航天|1.公司拥有一系列先进的纤缆生产及检测设备，组建了华南地区规模最大的光纤光缆研制、生产及检测基地，产品主要包括光纤、光缆、光纤连接器、配线产品、馈线电缆、数据线缆、架空裸导地线、光缆金具及附件等新一代信息技术产品。
-2.公司独资子公司成都傅立叶在卫星通信领域主要涉及地面终端（主要基于自主可控的天通卫星移动通信系统）、卫星解调设备、卫星态势感知系统等。</t>
+          <t>航运|公司是一家综合性航运公司，主要从事国际、国内海上集装箱运输业务，多年来持续深耕东北亚、东南亚和国内航线。</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆, 商业航天</t>
+          <t>航运</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>航运</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>-1.06</v>
+        <v>2.65</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>机构研报指出，特斯拉OptimusV3进入亮相发布时间窗口，并计划年内启动大规模量产，并且特斯拉已将弗里蒙特工厂的Model S/X产线改造为Optimus专用产线，中期规划年产能达100万台。</t>
+          <t>招商轮船在接受调研者提问时表示，近年来全球石油贸易和航运格局的演变，油轮硬资产属性或将日益凸显，在石油链条中日益成为供应链瓶颈，预期回报或有机会大幅提升。</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
@@ -2250,44 +2217,44 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>sz301255</t>
+          <t>sh601872</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>通力科技</t>
+          <t>招商轮船</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>29.76</v>
+        <v>18</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>20</v>
+        <v>10.02</v>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司是一家专业从事减速机的研发、生产、销售及服务的高新技术企业。公司主要产品为自主品牌“通力”系列减速机，公司已形成R、K、S、F、H、B、P等减速机全系列产品。</t>
+          <t>油运|公司主要从事国际原油运输、国际干散货运输业务，并通过持股50%的CLNG公司（另一持股50%的股东为中远海能下属的大连中远海运油品运输有限公司）投资经营国际LNG运输业务。</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>油运</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>-1.06</v>
+        <v>2.4</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>机构研报指出，特斯拉OptimusV3进入亮相发布时间窗口，并计划年内启动大规模量产，并且特斯拉已将弗里蒙特工厂的Model S/X产线改造为Optimus专用产线，中期规划年产能达100万台。</t>
+          <t>英伟达宣布，向美国半导体企业迈威尔科技（MRVL.US）投资20亿美元，将其纳入英伟达的AI生态体系。</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
@@ -2295,16 +2262,16 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>sh600184</t>
+          <t>sh601133</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>光电股份</t>
+          <t>柏诚股份</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>18.41</v>
+        <v>18.85</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>9.98</v>
@@ -2312,28 +2279,27 @@
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>光通信+机器人|1.子公司新华光自主研发的光通信核心材料GP，突破了批量生产工艺，已经送样给光通信领域多家企业测试使用。
-2.公司从光学设计源头导入终端应用，加大不同性能的高性能光学材料及先进元件的开发生产力度，以满足镜头、器件、模组等的使用要求，最终应用到下游车载镜头、消费电子、安防监控、投影成像，以及工业自动控制系统、工业机器人、机器人的光学成像、视觉传感系统中。</t>
+          <t>洁净室系统集成|公司主要专注于为高科技产业的建厂、技改等项目提供专业的洁净室系统集成整体解决方案，覆盖半导体及泛半导体、新型显示、生命科学、食品药品大健康等国家重点产业。</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>光通信, 机器人</t>
+          <t>洁净室系统集成</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>业绩超预期</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>-1.97</v>
+        <v>2.4</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>上市公司年报业绩预告进入密集披露阶段，市场驱动逻辑正转向对业绩增长与盈利改善的验证层面。</t>
+          <t>英伟达宣布，向美国半导体企业迈威尔科技（MRVL.US）投资20亿美元，将其纳入英伟达的AI生态体系。</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
@@ -2341,48 +2307,44 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>sh600502</t>
+          <t>sz301392</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>安徽建工</t>
+          <t>汇成真空</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>5.63</v>
+        <v>127.58</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>9.959999999999999</v>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>业绩+基建|公司2025年1-12月实现营业收入831.98亿元，同比下降13.79%；实现归母净利润15.26亿元，同比增长13.45%。报告显示，公司营收下降主要系建筑施工业务收入减少所致，但利润总额和归母净利润实现双增长。全年基建投资及工程业务新签合同金额1626.08亿元，同比增长4.86%。</t>
+          <t>半导体设备|公司真空镀膜设备可以应用于部分芯片加工制造，光刻掩膜版/铬板镀膜设备主要应用于集成电路、平板显示等领域。</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>业绩, 基建</t>
+          <t>半导体设备</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>业绩超预期</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>-1.97</v>
+        <v>2.16</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>上市公司年报业绩预告进入密集披露阶段，市场驱动逻辑正转向对业绩增长与盈利改善的验证层面。</t>
+          <t>中银证券指出，今年3月中国日均词元调用量已突破140万亿，两年增长超千倍。表明我国AI产业的发展重心正在从“卷模型”转向“卷应用”，AI应用正在深度融入社会经济活动。</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
@@ -2390,44 +2352,49 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>sh600066</t>
+          <t>sz002432</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>宇通客车</t>
+          <t>九安医疗</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>35.86</v>
+        <v>80.94</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>4天3板</t>
+        </is>
+      </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>业绩|宇通客车披露年报，2025年实现营业收入414.26亿元，同比增长11.31%；归母净利润55.54亿元，同比增长34.94%；基本每股收益2.51元。公司拟每10股派发现金红利20元(含税)。</t>
+          <t>医药+参股智谱|1.公司是一家在国内外具有影响力的个人健康管理产品供应商，主要从事家用医疗器械的研发、生产及销售。
+2.公司持有月之暗面、智谱AI等独角兽股权。</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>业绩</t>
+          <t>医药, 参股智谱</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>-2.62</v>
+        <v>2.16</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>华泰证券指出，霍尔木兹海峡封锁强化化石能源价格易涨难跌预期，水、核、风、光、生物质等绿电板块有望充分受益。</t>
+          <t>中银证券指出，今年3月中国日均词元调用量已突破140万亿，两年增长超千倍。表明我国AI产业的发展重心正在从“卷模型”转向“卷应用”，AI应用正在深度融入社会经济活动。</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
@@ -2435,48 +2402,44 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>sz000037</t>
+          <t>sh605287</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>深南电A</t>
+          <t>德才股份</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>13.02</v>
+        <v>45.08</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>9.969999999999999</v>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>电力|公司主营业务为生产经营供电供热、从事发电厂（站）相关技术咨询和技术服务等，公司南山热电厂位于深圳市电力负荷中心区，是所在区域的调峰电源。</t>
+          <t>AI漫剧|旗下奇想无限深耕“网文IP+AI漫剧”转化，与头部网文平台合作，将玄幻、甜宠等成熟IP快速落地，已产出多部爆款。</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>AI漫剧</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>游戏</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>-2.62</v>
+        <v>1.93</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>华泰证券指出，霍尔木兹海峡封锁强化化石能源价格易涨难跌预期，水、核、风、光、生物质等绿电板块有望充分受益。</t>
+          <t>完美世界旗下幻塔工作室研发的超自然都市开放世界RPG《异环》全平台公测定档4月23日，目前官网预约量已突破3000万。</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
@@ -2484,61 +2447,61 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>sh605162</t>
+          <t>sz002624</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">新中港  </t>
+          <t>完美世界</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>11.61</v>
+        <v>19.33</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>10.05</v>
+        <v>10.02</v>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>电力|公司采用热电联产的方式进行热力产品和电力产品的生产及供应。公司的热力业务主要面向工业用户供应所生产的蒸汽，主要满足工业园区内的造纸、印染、医药、化工、食品等150余家工业企业的热需求。公司生产的电力直接销售给国家电网公司。公司是嵊州市地区唯一一家集中供热的热电联产企业，具有150多家下游客户，区域优势和先发优势明显。</t>
+          <t>《异环》将上线|《异环》是公司基于虚幻5引擎开发的二次元都市题材开放世界游戏，2026.2.4国内开启删档计费测试（三测），反响热烈。</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>《异环》将上线</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>游戏</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>-1.95</v>
+        <v>1.93</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>国家电投计划今年投资2000亿元，同比增长17%。其中，一季度要完成投资230亿元，实现同比增长35%。</t>
+          <t>完美世界旗下幻塔工作室研发的超自然都市开放世界RPG《异环》全平台公测定档4月23日，目前官网预约量已突破3000万。</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>sz002560</t>
+          <t>sz002558</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>通达股份</t>
+          <t>巨人网络</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>10.79</v>
+        <v>34.69</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>9.99</v>
@@ -2546,96 +2509,109 @@
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>电线电缆|公司从事的主要业务包括电线电缆生产、销售及航空零部件加工两大板块。</t>
+          <t>游戏|公司主营业务是互联网游戏的研发和运营，最主要的两条产品线分别为“征途”系列和“球球大作战”。</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>电线电缆</t>
+          <t>游戏</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>日化用品</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>-1.52</v>
-      </c>
-      <c r="C45" s="2" t="inlineStr"/>
+        <v>2.84</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>2025年我国化妆品市场规模超万亿元，国货占比近六成。</t>
+        </is>
+      </c>
       <c r="D45" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>sh603429</t>
+          <t>sh603193</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST集友 </t>
+          <t>润本股份</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>9.949999999999999</v>
+        <v>24.46</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>5天4板</t>
-        </is>
-      </c>
+        <v>9.98</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 子公司集新能源主要在固态电池方向系统地开展关键材料研究。</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr"/>
+          <t>护理产品|公司主要从事驱蚊类、个人护理类产品的研发、生产和销售，目前已形成驱蚊产品、婴童护理产品、精油产品三大核心产品系列。</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>护理产品</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>光伏</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>-1.52</v>
-      </c>
-      <c r="C46" s="2" t="inlineStr"/>
+        <v>1.34</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>界面新闻独家获悉，国内光伏电池片核心工艺设备及解决方案提供商拉普拉斯于近日中标特斯拉光伏项目第二期，订单规模近百亿人民币。</t>
+        </is>
+      </c>
       <c r="D46" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>sz002168</t>
+          <t>sh603778</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>*ST惠程</t>
+          <t>国晟科技</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>4.18</v>
+        <v>27.5</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>5.029999999999999</v>
+        <v>10</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>3天2板</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司旗下控股子公司哆可梦以基于大数据精细化营销的流量经营业务和移动游戏的研发、发行及游戏平台的运营为主营业务</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
+          <t>光伏+锂电池|1.公司目前从事大尺寸高效异质结光伏电池的研发、生产、销售，以及异质结、TOPCON、PERC等电池组件的生产与销售。控股孙公司恒立聚能涉及钙钛矿研究。
+2.国晟科技公告称，公司拟以2.406亿元的价格受让正豪科技、林琴合计持有的孚悦科技100%股权。交易完成后，公司将持有标的公司100%股权，标的公司将纳入公司合并报表。孚悦科技主要从事高精密度新型锂电池结构件的研发、生产和销售。</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>光伏, 锂电池</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2644,32 +2620,36 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>-1.52</v>
+        <v>0.53</v>
       </c>
       <c r="C47" s="2" t="inlineStr"/>
       <c r="D47" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>sz002528</t>
+          <t>sh603429</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>ST英飞拓</t>
+          <t xml:space="preserve">*ST集友 </t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>3.79</v>
+        <v>10.45</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="I47" s="2" t="inlineStr"/>
+        <v>5.029999999999999</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>6天5板</t>
+        </is>
+      </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 英飞拓推出5G多功能智慧灯杆，支持节能照明、视频监控、新能源充电、公共WIFI、环境监测、信息发布、应急报警、5G微基站等模块，实现多种类型的感知数据采集、分析、仿真预测，提升城市综合治理。</t>
+          <t>ST股 | 子公司集新能源主要在固态电池方向系统地开展关键材料研究。</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
@@ -2681,32 +2661,36 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>-1.52</v>
+        <v>0.53</v>
       </c>
       <c r="C48" s="2" t="inlineStr"/>
       <c r="D48" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>sh600581</t>
+          <t>sz002528</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST八钢 </t>
+          <t>ST英飞拓</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>2.79</v>
+        <v>3.98</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
+        <v>5.01</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>7天4板</t>
+        </is>
+      </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 新疆唯一的钢铁上市公司，拥有完整优质的炼铁、炼钢及轧钢生产系统，产品以高速线材、螺纹钢、热轧板卷、冷轧薄板、中厚板等建筑及工业用钢为主。</t>
+          <t>ST股 | 英飞拓推出5G多功能智慧灯杆，支持节能照明、视频监控、新能源充电、公共WIFI、环境监测、信息发布、应急报警、5G微基站等模块，实现多种类型的感知数据采集、分析、仿真预测，提升城市综合治理。</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr"/>
@@ -2718,32 +2702,36 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>-1.52</v>
+        <v>0.53</v>
       </c>
       <c r="C49" s="2" t="inlineStr"/>
       <c r="D49" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>sh605199</t>
+          <t>sz002713</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>ST葫芦娃</t>
+          <t>*ST东易</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>6.83</v>
+        <v>12.45</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="I49" s="2" t="inlineStr"/>
+        <v>4.97</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>6天3板</t>
+        </is>
+      </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司地处海南海口，聚焦儿童药研发、生产、销售于一体的创新型医药企业。</t>
+          <t>ST股 | 公司基于数字化系统优势和业务场景优势，研发推出了行业内首个新一代AIGC技术和真家系统结合的全新设计工具“真家 AIGC”，同时打造出AI 创意大师、AI小白设计家两款智能应用设计工具。</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr"/>
@@ -2755,32 +2743,36 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>-1.52</v>
+        <v>0.53</v>
       </c>
       <c r="C50" s="2" t="inlineStr"/>
       <c r="D50" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>sh603559</t>
+          <t>sh600581</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST通脉  </t>
+          <t xml:space="preserve">*ST八钢 </t>
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>7.16</v>
+        <v>2.93</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="I50" s="2" t="inlineStr"/>
+        <v>5.02</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司是国内专业通信技术服务商，主营业务是为基础电信运营商和通信设备商提供涵盖核心网、传输网和接入网等全网络层次的通信网络工程建设和维护综合技术服务。</t>
+          <t>ST股 | 新疆唯一的钢铁上市公司，拥有完整优质的炼铁、炼钢及轧钢生产系统，产品以高速线材、螺纹钢、热轧板卷、冷轧薄板、中厚板等建筑及工业用钢为主。</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
@@ -2788,222 +2780,192 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>0.53</v>
       </c>
       <c r="C51" s="2" t="inlineStr"/>
       <c r="D51" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>sz002263</t>
+          <t>sh605199</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>大东南</t>
+          <t>ST葫芦娃</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>4.51</v>
+        <v>7.17</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>10</v>
+        <v>4.98</v>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>4天3板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>隔膜+复合铜箔|1.公司产品覆盖传统包装薄膜、锂电池隔膜、耐高温超薄电容膜、光学膜。
-2.公司复合铜箔用电容薄膜的研发已经完成，此项目使公司生产更超薄产品成为可能，且技术指标均达到或超过国家标准。</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>隔膜, 复合铜箔</t>
-        </is>
-      </c>
+          <t>ST股 | 公司地处海南海口，聚焦儿童药研发、生产、销售于一体的创新型医药企业。</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>0.53</v>
       </c>
       <c r="C52" s="2" t="inlineStr"/>
       <c r="D52" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>sz000631</t>
+          <t>sz002306</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>顺发恒能</t>
+          <t>*ST云网</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>4.27</v>
+        <v>2.38</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>10.05</v>
+        <v>4.850000000000001</v>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>并购重组|顺发恒能公告称，为满足发展需要，公司拟以自有资金分别收购顺发德能49%股权和普星京兴100%股权，交易价格分别为1.13亿元和1.47亿元。交易完成后，顺发德能和普星京兴将成为公司全资子公司。本次交易构成关联交易，但不构成重大资产重组，已获公司董事会审议通过，尚需提交股东会审议。关联董事已回避表决。</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>并购重组</t>
-        </is>
-      </c>
+          <t>ST股 | 1.“湘鄂情”品牌是全国仅有的几个中餐类“中国驰名商标”之一，为跻身于北京市专营连锁餐饮类企业前五名中的唯一民族品牌。
+2.公司拟分二期在超高效N型晶硅电池研发和生产。</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>0.53</v>
       </c>
       <c r="C53" s="2" t="inlineStr"/>
       <c r="D53" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>sz002454</t>
+          <t>sh603517</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>松芝股份</t>
+          <t xml:space="preserve">ST绝味  </t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>9.24</v>
+        <v>12.29</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>10</v>
+        <v>5.04</v>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>储能热管理|松芝股份聚焦储能领域的创新研发，自2016年即开始研发销售电池热管理液冷机组，目前产品市场保有量达5万余套，广泛应用于储能集装箱、储能电柜、客车、卡车、换电等领域。</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>储能热管理</t>
-        </is>
-      </c>
+          <t>ST股 | 休闲卤制品连锁龙头。生产基地覆盖全国重要省份和区域，并使用以销定产的营销模式，产能和物流效率最优，对于小型加盟商有天然推广优势，拥有较强的议价能力和存储原材料的能力。</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>0.53</v>
       </c>
       <c r="C54" s="2" t="inlineStr"/>
       <c r="D54" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>sz300834</t>
+          <t>sh603822</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>星辉环材</t>
+          <t xml:space="preserve">ST嘉澳  </t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>30.2</v>
+        <v>90.44</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>19.98</v>
+        <v>5</v>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>引入战略投资者|近日，星辉环材宣布引入战略投资者九识智能，九识智能2021年成立，截至2025年底，其运营全球最大RoboVan无人货运车队。</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>引入战略投资者</t>
-        </is>
-      </c>
+          <t>ST股 | 全资子公司东江能源专业从事餐厨垃圾、废油脂无害化、减量化、资源化处理和新能源开发，是目前国内规模较大的废弃油脂资源综合利用企业。</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>0.53</v>
       </c>
       <c r="C55" s="2" t="inlineStr"/>
       <c r="D55" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>sz000863</t>
+          <t>sh600107</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>三湘印象</t>
+          <t xml:space="preserve">ST尔雅  </t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>5.71</v>
+        <v>6.5</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>10.02</v>
+        <v>5.01</v>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>借壳预期|2025年10月28日，三湘印象股份有限公司发布公告，提名苏存颖女士为公司第八届董事会董事候选人。苏存颖的简历显示，其现任职务为荣芯半导体(中国)有限公司投融资部总监。此项任命已在2025年第二次临时股东会上获得通过。</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>借壳预期</t>
-        </is>
-      </c>
+          <t>ST股 | 公司的主营业务为服装、服饰和纺织品研发、设计、制造和销售。</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3018,33 +2980,37 @@
       </c>
       <c r="C56" s="2" t="inlineStr"/>
       <c r="D56" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>sh603657</t>
+          <t>sz300834</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>春光科技</t>
+          <t>星辉环材</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>27.94</v>
+        <v>36.24</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I56" s="2" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>家电|公司主营业务为吸尘器零件、橡塑软管、塑料制品、小家电的研发、制造和销售及自营进出口业务。</t>
+          <t>引入战略投资者|近日，星辉环材宣布引入战略投资者九识智能，九识智能2021年成立，截至2025年底，其运营全球最大RoboVan无人货运车队。</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>引入战略投资者</t>
         </is>
       </c>
     </row>
@@ -3061,33 +3027,37 @@
       </c>
       <c r="C57" s="2" t="inlineStr"/>
       <c r="D57" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>sz300992</t>
+          <t>sh605162</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>泰福泵业</t>
+          <t xml:space="preserve">新中港  </t>
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>41.88</v>
+        <v>12.77</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I57" s="2" t="inlineStr"/>
+        <v>9.99</v>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>实控人变更|泰福泵业公告称，实控人陈宜文、林慧夫妇及地久电子与诤远行共同签署《控制权收购协议》，协议约定，陈宜文、林慧拟以协议转让的方式向诤远行分别转让公司4.18%、1.05%股份。陈宜文、林慧拟以股权转让的方式将地久电子的100%股权向诤远行转让，转让完成后诤远行通过地久电子间接持有公司18.88%股份。本次转让完成后，诤远行直接和间接合计持有公司总股本的24.11%。公司控股股东变更为诤远行，孙凯将成为公司实际控制人。</t>
+          <t>电力|公司采用热电联产的方式进行热力产品和电力产品的生产及供应。公司的热力业务主要面向工业用户供应所生产的蒸汽，主要满足工业园区内的造纸、印染、医药、化工、食品等150余家工业企业的热需求。公司生产的电力直接销售给国家电网公司。公司是嵊州市地区唯一一家集中供热的热电联产企业，具有150多家下游客户，区域优势和先发优势明显。</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>实控人变更</t>
+          <t>电力</t>
         </is>
       </c>
     </row>
@@ -3104,33 +3074,37 @@
       </c>
       <c r="C58" s="2" t="inlineStr"/>
       <c r="D58" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>sz002800</t>
+          <t>sh600724</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>天顺股份</t>
+          <t>宁波富达</t>
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>22.91</v>
+        <v>6.66</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I58" s="2" t="inlineStr"/>
+        <v>10.08</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>物流+一带一路|公司作为疆内第三方物流、供应链管理的龙头企业，国际铁路业务在2022年开行了莫斯科、杜伊斯堡、汉堡、梅杰乌、阿拉木图、热特苏、塔什干、格鲁吉亚、意大利、梅尔辛、马拉等中亚、中欧方向的班列。国际航班货源业务在2022年以乌鲁木齐为中心开通了格鲁吉亚第比利斯等全货机航线；在海口开设海口至莫斯科航线；在武汉开设了武汉至莫斯科航线。</t>
+          <t>房地产|公司的最终控制人为宁波市人民政府国有资产监督管理委员会。公司主营商业地产的出租、自营联营及托管业务，其中包括物业管理 。</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>物流, 一带一路</t>
+          <t>房地产</t>
         </is>
       </c>
     </row>
@@ -3147,34 +3121,37 @@
       </c>
       <c r="C59" s="2" t="inlineStr"/>
       <c r="D59" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>sh600250</t>
+          <t>sh603248</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>南京商旅</t>
+          <t>锡华科技</t>
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>14.05</v>
+        <v>30.07</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I59" s="2" t="inlineStr"/>
+        <v>9.99</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>旅游+零售|1.公司旅游业务主要在子公司秦淮风光开展，秦淮风光主要业务为向游客提供内秦淮河水域的水上游船观光游览服务，船票收入为主要收入来源。
-2.公司零售业务的核心企业是控股子公司南京南商商业运营管理有限责任公司，南商运营主要从事单店百货零售业务，拥有南京商厦20年经营权。南京商厦是南京城北地区主要商业综合体之一，是集购物、餐饮、娱乐于一体的现代化、多功能、综合性大型百货商场，在所处区域占有较高的市场地位。</t>
+          <t>次新+风电|公司主要从事大型高端装备专用部件的研发、制造与销售，产品结构以风电齿轮箱专用部件为主、注塑机厚大专用部件为辅，是全球行业领先、质量可靠、技术卓越的大型高端装备专用部件制造商。</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>旅游, 零售</t>
+          <t>次新, 风电</t>
         </is>
       </c>
     </row>
@@ -3191,33 +3168,291 @@
       </c>
       <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>sz002580</t>
+          <t>sh600249</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>圣阳股份</t>
+          <t xml:space="preserve">两面针  </t>
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>17.61</v>
+        <v>7.01</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>9.99</v>
+        <v>10.05</v>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>储能|公司聚焦网络能源、智慧储能和绿色动力应用领域，提供备用电源、储能电源、动力电源和新能源系统解决方案及运维服务等，主要产品包括锂离子电池及电源系统、铅蓄电池及系统、新能源储能系统集成产品及服务等。</t>
+          <t>实控人变更|两面针公告称，公司控股股东广西柳州市产业投资发展集团有限公司及其一致行动人，于3月31日与广西国控资本运营集团有限责任公司签署《股份转让协议》，合计转让1.54亿股股份(占总股本28%)，转让总价约12.28亿元。交易完成后，公司控股股东将变更为广西国控，实际控制人将由柳州市国资委变更为广西壮族自治区国资委。公司股票将于4月1日复牌。</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>储能</t>
+          <t>实控人变更</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr"/>
+      <c r="D61" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>sz002269</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>美邦服饰</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>签订重大合同|美邦服饰公告称，公司第六届董事会审议通过关于签署日常经营重大合同暨关联交易的议案。公司或其子公司拟向关联方贵州美邦新能纺织服装科技有限公司采购货物，预计交易金额不超过10亿元。该合同为采购框架合同，有效期一年，采取成本加成定价方式。</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>签订重大合同</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr"/>
+      <c r="D62" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>sh600643</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>爱建集团</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>多元金融|公司致力于成为一家以金融业为主体、专注于提供财富管理和资产管理综合服务的成长性上市公司，下属爱建信托公司、爱建租赁公司、华瑞租赁公司、爱建资产公司、爱建产业公司、爱建资本公司、爱建基金销售公司、爱建香港公司、爱建保理公司等子公司围绕相应主业开展业务。</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr"/>
+      <c r="D63" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>sh601579</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">会稽山  </t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>业绩|公司2025年1-12月实现营业收入18.22亿元，同比增长11.68%；归母净利润2.45亿元，同比增长24.70%。</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>业绩</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr"/>
+      <c r="D64" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>sh603727</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">博迈科  </t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>20.89</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>油气|公司主要产品大类分为海洋油气开发模块、矿业开采模块、天然气液化模块等，产品具体涉及十多种子类别。公司为海洋油气开发、矿业开采和天然气液化领域中的国内外高端客户提供能源资源设施开发的专业分包服务。</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>油气</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr"/>
+      <c r="D65" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>sz002408</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>齐翔腾达</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>9.969999999999999</v>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>石油化工|公司目前已形成碳四丁烯组分综合利用产品线、异丁烯组分综合利用产品线和丁烷组分综合利用产品线三条产品线。</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>石油化工</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr"/>
+      <c r="D66" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>sz301188</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>力诺药包</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>药用玻璃|公司主要药用玻璃产品包括中硼硅药用玻璃瓶、低硼硅药用玻璃瓶和低硼硅药用玻璃管等，客户主要为国内知名制药企业，包括悦康药业、华润双鹤、新时代药业、齐鲁制药等。</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>药用玻璃</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3263,27 +3498,27 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sz002361</t>
+          <t>sh600488</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>神剑股份</t>
+          <t>津药药业</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sh600488</t>
+          <t>sz002821</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>津药药业</t>
+          <t>凯莱英</t>
         </is>
       </c>
     </row>
@@ -3293,12 +3528,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sz000008</t>
+          <t>sz002560</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>神州高铁</t>
+          <t>通达股份</t>
         </is>
       </c>
     </row>
@@ -3308,12 +3543,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sz002578</t>
+          <t>sz300834</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>闽发铝业</t>
+          <t>星辉环材</t>
         </is>
       </c>
     </row>
@@ -3323,57 +3558,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sh600502</t>
+          <t>sh605162</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>安徽建工</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>sz000592</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>平潭发展</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>sz002634</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>棒杰股份</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>sz301008</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>宏昌科技</t>
+          <t xml:space="preserve">新中港  </t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,19 +476,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="92" customWidth="1" min="3" max="3"/>
+    <col width="101" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="216" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="245" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -552,228 +552,214 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>医药生物</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.53</v>
+        <v>1.51</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>礼来公司当地时间周三宣布，美国食品药品监督管理局(FDA)已批准其GLP-1口服药物上市。此外，2026年4月14-16日第37届国际阿尔茨海默病协会全球大会在法国里昂举办。</t>
+          <t>4月2日，工信部发布关于开展普惠算力赋能中小企业发展专项行动的通知。提出推动全光交换等技术应用部署，降低算力应用终端到服务器的网络时延，提升应用交互体验。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>sh600488</t>
+          <t>sz002792</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>津药药业</t>
+          <t>通宇通讯</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>6.34</v>
+        <v>45.34</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10.07</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>5天5板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>创新药|公司于2024年成立创新研究院，负责创新药设计发现、研发以及引进孵化工作，JYSW003项目为津药生物科技（天津）有限公司委托公司创新研究院开展的创新药项目，适应症是银屑病，前期探索性研究结果初步显示药效明显、安全性优等特点。</t>
+          <t>光模块+商业航天|1.间接参股25.58%的深圳光为致力于各类光模块研发，目前已成功研发出了包括100G CFP2、400G QSFP-DD等系列在内的多个光模块产品类型。
+2.蓝箭鸿擎是国内唯三有万颗卫星发射计划的公司之一，拥有鸿鹄星座计划，申报了1万颗卫星。公司投资参股北京蓝箭鸿擎科技公司以强化协同效应。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>光模块, 商业航天</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>医药生物</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.53</v>
+        <v>1.51</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>礼来公司当地时间周三宣布，美国食品药品监督管理局(FDA)已批准其GLP-1口服药物上市。此外，2026年4月14-16日第37届国际阿尔茨海默病协会全球大会在法国里昂举办。</t>
+          <t>4月2日，工信部发布关于开展普惠算力赋能中小企业发展专项行动的通知。提出推动全光交换等技术应用部署，降低算力应用终端到服务器的网络时延，提升应用交互体验。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sz002038</t>
+          <t>sz002980</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>双鹭药业</t>
+          <t>华盛昌</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>8.550000000000001</v>
+        <v>46.09</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>10.04</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>7天4板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>创新药|公司目前具有较强竞争力的储备品种有包括即将上市的G-CSF长效制剂、人促卵泡激素长、短效制剂，GLP-1类似物长、短效和双靶点制剂，心脑血管领域开发的创新药和特色仿制药等。</t>
+          <t>并购重组+光通信|华盛昌公告称，公司拟以现金方式收购深圳市伽蓝特科技有限公司100%股权，整体估值暂定为4.6亿元。伽蓝特专注于仪器仪表测试测量行业中的光通信模块和光芯片测试领域。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>并购重组, 光通信</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>医药生物</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.53</v>
+        <v>1.51</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>礼来公司当地时间周三宣布，美国食品药品监督管理局(FDA)已批准其GLP-1口服药物上市。此外，2026年4月14-16日第37届国际阿尔茨海默病协会全球大会在法国里昂举办。</t>
+          <t>4月2日，工信部发布关于开展普惠算力赋能中小企业发展专项行动的通知。提出推动全光交换等技术应用部署，降低算力应用终端到服务器的网络时延，提升应用交互体验。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sz000788</t>
+          <t>sz300812</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>北大医药</t>
+          <t>易天股份</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>7.22</v>
+        <v>40.5</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>10.06</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>创新药|公司已建立起自主知识产权、仿创技术、技术创新为一体的技术核心体系，研发领 域聚焦于抗感染类、镇痛类、精神类、慢病类等创新药、高端仿制药和大市场品种，为企业发展提供持续优化的产品结技术中心可独立完成仿制药、一致性评价品种的研发全流程，也可开展创新药的药学部分研究工作。</t>
+          <t>光模块设备|2023年7月13日公司在互动平台表示，子公司微组半导体的微组装设备可应用于部分光模块的部分器件组装工序，设备精度已满足100G的精度。未来公司也将持续提升产品精度，在800G/1.6T的精度方向进一步研发。相关产品已获得客户订单。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>光模块设备</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>医药生物</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.53</v>
+        <v>1.51</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>礼来公司当地时间周三宣布，美国食品药品监督管理局(FDA)已批准其GLP-1口服药物上市。此外，2026年4月14-16日第37届国际阿尔茨海默病协会全球大会在法国里昂举办。</t>
+          <t>4月2日，工信部发布关于开展普惠算力赋能中小企业发展专项行动的通知。提出推动全光交换等技术应用部署，降低算力应用终端到服务器的网络时延，提升应用交互体验。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sh600594</t>
+          <t>sz002222</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>益佰制药</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>4.8</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>10.09</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>中药创新药|公司苗药相关研发工作有民族药珍珠滴丸Ⅲ期临床研究、苗药理气活血滴丸产业化应用研究等。</t>
+          <t>光通信+光刻机|1.公司部分精密光学元件产品应用于光通讯领域。
+2.公司曾通过欧洲代理向ASML提供及其少量光学元件。此外，华为是公司的客户，公司在业务范围内向其提供光学元件产品。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>中药创新药</t>
+          <t>光通信, 光刻机</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>医药生物</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.53</v>
+        <v>1.51</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>礼来公司当地时间周三宣布，美国食品药品监督管理局(FDA)已批准其GLP-1口服药物上市。此外，2026年4月14-16日第37届国际阿尔茨海默病协会全球大会在法国里昂举办。</t>
+          <t>4月2日，工信部发布关于开展普惠算力赋能中小企业发展专项行动的通知。提出推动全光交换等技术应用部署，降低算力应用终端到服务器的网络时延，提升应用交互体验。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sz000950</t>
+          <t>sz003031</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>重药控股</t>
+          <t>中瓷电子</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>6.49</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>10</v>
@@ -781,179 +767,180 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>创新药|2025年12月10日公告，参股子公司重庆药友制药有限责任公司与上海复星医药产业发展有限公司及辉瑞共同签订《Collaboration and License Agreement》，其中主要包括由药友制药就口服小分子胰高血糖素样肽-1受体（GLP-1R）激动剂（包括 YP05002）及含有该活性成分的产品授予辉瑞于许可区域（即全球范围）及领域（人类、动物所有适应症的治疗、诊断及预防）独家开发、使用、生产及商业化权利。</t>
+          <t>光通信+商业航天|1.在光通信领域，公司开发的光通信器件外壳包括Butterfly外壳、TOSA外壳、ROSA外壳、光接收组件外壳、光开关外壳等，传输速率覆盖2.5Gbps-800Gbps，产品种类可以覆盖全部光通信器件产品，电性能、可靠性达到国际水平，能够替代进口外壳。目前公司光通信领域器件产品已经进入多家世界知名光通信模块生产厂家，包括华为、新易盛、旭创、光迅科技等。
+2.子公司国联万众的GaN射频芯片可以应用到商业卫星的卫星通信模块中。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>光通信, 商业航天</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>医药生物</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.53</v>
+        <v>1.51</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>礼来公司当地时间周三宣布，美国食品药品监督管理局(FDA)已批准其GLP-1口服药物上市。此外，2026年4月14-16日第37届国际阿尔茨海默病协会全球大会在法国里昂举办。</t>
+          <t>4月2日，工信部发布关于开展普惠算力赋能中小企业发展专项行动的通知。提出推动全光交换等技术应用部署，降低算力应用终端到服务器的网络时延，提升应用交互体验。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sh603222</t>
+          <t>sz002796</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>济民健康</t>
+          <t>世嘉科技</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>10.15</v>
+        <v>50.59</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>9.969999999999999</v>
+        <v>10</v>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>创新药|公司主要研发项目包含DB006溶瘤病毒注射液等多个Ⅰ类创新药。</t>
+          <t>光通信|2025年8月4日公告，公司看好光通信细分行业的市场前景，认可光彩芯辰（浙江）科技有限公司在光通信领域内的前期投入、技术储备以及客户资源。公司拟通过增资扩股的方式取得光彩芯辰部分股权，并与光彩芯辰签署了《增资意向协议》。如交易顺利完成，公司将于交易完成后预计持有光彩芯辰不超过20%的股权。光彩芯辰主要从事100G—800G多系列光通信模块的研发制造，总部及生产基地均位于中新嘉善现代产业园。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>光通信</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>医药生物</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.53</v>
+        <v>1.51</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>礼来公司当地时间周三宣布，美国食品药品监督管理局(FDA)已批准其GLP-1口服药物上市。此外，2026年4月14-16日第37届国际阿尔茨海默病协会全球大会在法国里昂举办。</t>
+          <t>4月2日，工信部发布关于开展普惠算力赋能中小企业发展专项行动的通知。提出推动全光交换等技术应用部署，降低算力应用终端到服务器的网络时延，提升应用交互体验。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>920230.BJ</t>
+          <t>sh688226</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>欧康医药</t>
+          <t>威腾电气</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>14.61</v>
+        <v>50.28</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>29.98</v>
+        <v>20</v>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>医药|公司是专业从事植物提取物的研发、生产和销售的国家高新技术企业，属于医药制造业。公司自成立以来一直专注于槲皮素、芦丁、地奥司明、橙皮苷等天然维生素P类化合物的提纯、合成、纵深开发及运用，产品广泛应用于保健品、食品、药品、化妆品等大健康及相关产业，致力于“建立全球领先的天然维生素P类化合物技术运用中心”。</t>
+          <t>光模块|上海孛璞半导体技术有限公司负责向子公司威璞磐芯（上海）科技有限公司提供高速光模块/组的整体设计方案并转让全部已有相关技术成果的知识产权。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>光模块</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>石油石化</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>3.03</v>
+        <v>1.51</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>午后布伦特原油期货涨幅扩大至7%，报108.3美元/桶；WTI原油日内涨幅达6.5%，报106.66美元/桶。</t>
+          <t>4月2日，工信部发布关于开展普惠算力赋能中小企业发展专项行动的通知。提出推动全光交换等技术应用部署，降低算力应用终端到服务器的网络时延，提升应用交互体验。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sz300839</t>
+          <t>sh688205</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>博汇股份</t>
+          <t xml:space="preserve">德科立  </t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>16.69</v>
+        <v>247.21</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>19.99</v>
+        <v>20</v>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>石油石化|公司主营业务是采用自行研发的间歇式加工生产工艺,连续式生产工艺以及分子蒸馏和沉降等技术,对催化裂化后的燃料油即催化油浆进行深加工,研发,生产和销售作为化工原料的沥青助剂,橡胶助剂,润滑油助剂等重芳烃产品和更为纯净。</t>
+          <t>OCS|德科立发布股票交易异常波动公告称，近期，受AI算力需求推动，OCS（光交换）产品引发市场高度关注。公司始终密切关注相关技术发展，硅基OCS产品已获得海外样品订单，尚未获得海外大厂的批量订单。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>石油石化</t>
+          <t>OCS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>石油石化</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>3.03</v>
+        <v>-0.63</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>午后布伦特原油期货涨幅扩大至7%，报108.3美元/桶；WTI原油日内涨幅达6.5%，报106.66美元/桶。</t>
+          <t>韩国3月份半导体出口额同比猛增151.4%，首次突破300亿美元关口。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sh603353</t>
+          <t>sh605589</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>和顺石油</t>
+          <t>圣泉集团</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>36.5</v>
+        <v>32.43</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>10.01</v>
@@ -961,208 +948,208 @@
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>油气+半导体|1.公司是湖南省第一家获国家商务部批准取得成品油批发资质的民营石油企业，主营成品油批发零售，业务涵盖成品油采购、仓储、物流、批发、零售环节，在成品油流通领域形成完整产业链。
-2.2025年11月16日晚公告，公司拟以现金收购及增资方式取得上海奎芯集成电路设计有限公司不低于34%股权并通过表决权委托合计控制其51%表决权，交易完成后奎芯科技将纳入合并报表，布局高速接口IP及Chiplet解决方案。</t>
+          <t>光刻胶|公司产品包括光刻胶用电子级酚醛树脂。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>油气, 半导体</t>
+          <t>光刻胶</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>石油石化</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>3.03</v>
+        <v>-0.63</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>午后布伦特原油期货涨幅扩大至7%，报108.3美元/桶；WTI原油日内涨幅达6.5%，报106.66美元/桶。</t>
+          <t>韩国3月份半导体出口额同比猛增151.4%，首次突破300亿美元关口。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sz002828</t>
+          <t>sh688485</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>贝肯能源</t>
+          <t>九州一轨</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>13.79</v>
+        <v>31.3</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>9.969999999999999</v>
+        <v>20.02</v>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>油气|公司主要从事油气勘探和开发过程中的钻井工程技术服务及其他油田技术服务，具体包括钻井、固井、钻井液、定向井、欠平衡等，是国内规模较大的、能够提供一体化钻井工程技术服务的独立油田服务供应商。</t>
+          <t>半导体+高铁|1.2026年3月27日公告，公司拟与江苏通用半导体有限公司共同出资设立北京通用九州金刚石科技有限公司(暂定名)，注册资本2亿元，其中公司以现金出资8000万元，占40%。合资公司聚焦第四代半导体材料(金刚石)的研发、制造及在轨道交通、声纹传感等领域的产业化应用。
+2.公司主要面向城市轨道交通、市域/市郊铁路的减振降噪、TOD上盖开发噪声振动综合控制等领域提供钢弹簧浮置道床减振系统、预制钢弹簧浮置板、声屏障、隔离式高弹性减振垫、重型调频钢轨耗能装置等系列化产品和服务。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>油气</t>
+          <t>半导体, 高铁</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>石油石化</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>3.03</v>
+        <v>-0.63</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>午后布伦特原油期货涨幅扩大至7%，报108.3美元/桶；WTI原油日内涨幅达6.5%，报106.66美元/桶。</t>
+          <t>韩国3月份半导体出口额同比猛增151.4%，首次突破300亿美元关口。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sz000968</t>
+          <t>sh605303</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>蓝焰控股</t>
+          <t>园林股份</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>10.91</v>
+        <v>17.77</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>9.98</v>
+        <v>10.03</v>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>煤层气|公司主营业务为煤矿瓦斯治理及煤层气勘探、开发与利用业务。公司作为行业内的龙头企业，形成了煤层气勘探、抽采、输送、销售等完整产业链，掌握了具有独立自主知识产权且较为完善煤层气地面抽采技术。</t>
+          <t>存储芯片|参股华澜微是国内极少数拥有全系列数码存储控制器芯片的高科技公司，产品应用于存储卡、USB闪存盘、移动硬盘、固态硬盘、硬盘阵列以及大数据存储系统。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>煤层气</t>
+          <t>存储芯片</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>石油石化</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>3.03</v>
+        <v>-0.63</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>午后布伦特原油期货涨幅扩大至7%，报108.3美元/桶；WTI原油日内涨幅达6.5%，报106.66美元/桶。</t>
+          <t>韩国3月份半导体出口额同比猛增151.4%，首次突破300亿美元关口。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sh603798</t>
+          <t>sh688146</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">康普顿  </t>
+          <t>中船特气</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>15.62</v>
+        <v>51.22</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>10</v>
+        <v>20.01</v>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>润滑油|公司是专业的润滑油和汽车养护用品生产商和服务商。公司始终致力于产品研发和创新，在中国润滑油、车用养护品和汽车化学品市场上一直稳步发展。</t>
+          <t>光刻气|中船特气公告称，公司光刻气产品（Kr/Ne、Ar/Ne/Xe）通过日本GIGAPHOTON株式会社的合格供应商认证，证书有效期至2030年7月23日。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>润滑油</t>
+          <t>光刻气</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>石油石化</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>3.03</v>
+        <v>-1.03</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>午后布伦特原油期货涨幅扩大至7%，报108.3美元/桶；WTI原油日内涨幅达6.5%，报106.66美元/桶。</t>
+          <t>工信部首次明确提出，探索“算力银行”“算力超市”等创新业务，支持中小企业存入闲置算力资源，通过跨区域、跨周期调度实现灵活取用。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sh600339</t>
+          <t>sz300608</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>中油工程</t>
+          <t>思特奇</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>4.46</v>
+        <v>12.9</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>10.12</v>
+        <v>20</v>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>油气+基建|公司主要从事以油气田地面工程服务、储运工程服务、炼化工程服务、环境工程服务、项目管理服务为核心的石油工程设计、施工及总承包等相关石油工程建设业务，公司面向国内外石油化工工程市场提供全产业链的“一站式”综合服务。</t>
+          <t>算力调度|‌思特奇在国家“东数西算”的某关键枢纽节点，公司主导建设的算力调度与运营平台已成为行业典范，成功统一纳管调度了区域内的算力资源，形成了“区域算力一张网”。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>油气, 基建</t>
+          <t>算力调度</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0.8999999999999999</v>
+        <v>-1.03</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>据报道，英国伦敦大学学院科学家创下了现有商用光纤数据传输速度新纪录——每秒450太比特(Tb/s)。这一速度相当于现有商用网络的十倍。</t>
+          <t>工信部首次明确提出，探索“算力银行”“算力超市”等创新业务，支持中小企业存入闲置算力资源，通过跨区域、跨周期调度实现灵活取用。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
@@ -1170,48 +1157,44 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sz000720</t>
+          <t>sz003007</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>新能泰山</t>
+          <t>直真科技</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>5.4</v>
+        <v>44.06</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>8天6板</t>
-        </is>
-      </c>
+        <v>10.01</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>电线电缆+光纤光缆|子公司曲阜电缆主要从事电线电缆、光纤光缆、电力光缆等产品的研发、制造与销售，曲阜电缆生产、 销售的电线电缆产品是公司重点发展的智慧供应链业务产品之一。</t>
+          <t>算力调度|公司大力推进算力网络相关产品的定义和解决方案的推广，23年上半年，完成了网控制器、算控制器为核心的算网大脑产品的预研和部分开发工作，进行了基于网络和算力感知技术的算力、运力可视化、意图驱动的多因素运力、算力调度的探索与实践。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>电线电缆, 光纤光缆</t>
+          <t>算力调度</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>0.8999999999999999</v>
+        <v>-1.03</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>据报道，英国伦敦大学学院科学家创下了现有商用光纤数据传输速度新纪录——每秒450太比特(Tb/s)。这一速度相当于现有商用网络的十倍。</t>
+          <t>工信部首次明确提出，探索“算力银行”“算力超市”等创新业务，支持中小企业存入闲置算力资源，通过跨区域、跨周期调度实现灵活取用。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
@@ -1219,49 +1202,44 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sz002309</t>
+          <t>sh600654</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>中利集团</t>
+          <t xml:space="preserve">中安科  </t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>4.98</v>
+        <v>3.64</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10天6板</t>
-        </is>
-      </c>
+        <v>9.969999999999999</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>光伏+光纤光缆|1.公司的新能源光伏组件业务板块，包括单晶大尺寸高效光伏电池片和光伏组件的研发、生产和销售。公司拥有钙钛矿叠层电池及组件研发专利等技术储备6项。
-2.公司光通讯线缆板块已延伸到高分子材料、光纤、电缆的全产业链，作为华为核心战略供应商，为华为提供通信用电缆，包括5G用新品光电混合缆。</t>
+          <t>算力租赁|2024年7月25日公告，公司及全资子公司灵算智云（武汉）投资有限公司拟与宜兴兴阳产业投资有限公司签署投资合作协议，共建宜兴人工智能算力中心项目。本次合作项目计划总投资为3.75亿元。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>光伏, 光纤光缆</t>
+          <t>算力租赁</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>0.8999999999999999</v>
+        <v>-1.03</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>据报道，英国伦敦大学学院科学家创下了现有商用光纤数据传输速度新纪录——每秒450太比特(Tb/s)。这一速度相当于现有商用网络的十倍。</t>
+          <t>工信部首次明确提出，探索“算力银行”“算力超市”等创新业务，支持中小企业存入闲置算力资源，通过跨区域、跨周期调度实现灵活取用。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
@@ -1269,16 +1247,16 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sz000586</t>
+          <t>sh600602</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>汇源通信</t>
+          <t>云赛智联</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>17.15</v>
+        <v>24.39</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>10.01</v>
@@ -1286,27 +1264,27 @@
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>光缆光纤|公司是国内最早的全系列光缆供应商之一，光缆光纤业务主要生产、销售普通光缆、特种光缆、气吹微缆等，以及提供工程解决方案服务。公司旗下全资子公司汇源光通信是国内电力光缆的制造商、气吹微缆的供应商，同时也是高压输电线路在线检测产品的供应商。</t>
+          <t>算力租赁|公司是上海国资委旗下上市公司，定位于中立第三方高端数据中心运营商。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>光缆光纤</t>
+          <t>算力租赁</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>0.8999999999999999</v>
+        <v>-1.85</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>据报道，英国伦敦大学学院科学家创下了现有商用光纤数据传输速度新纪录——每秒450太比特(Tb/s)。这一速度相当于现有商用网络的十倍。</t>
+          <t>第十四届中国电子信息博览会（CITE 2026）将于2026年4月9日至11日在深圳会展中心（福田）举办。具身智能板块，宇树机器人、众擎机器人、智元机器人、越疆机器人、灵心巧手等明星企业将集体亮相。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
@@ -1314,690 +1292,973 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sh603042</t>
+          <t>sh605133</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>华脉科技</t>
+          <t>嵘泰股份</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>21.76</v>
+        <v>28.49</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>铜连接+光纤光缆|1.公司数据中心业务主要包括低压配电、铜缆综合布线、光综合布线、机柜及微模块及基础设施等业务。
-2.公司是一家信息通信网络基础设施解决方案提供商，主要产品包括光纤、光缆、光器件及光配线设施全场景有线传输链路解决方案及系列产品。</t>
+          <t>机器人|公司与润孚动力合资设立润泰机器人公司，布局应用于人形机器人和汽车底盘系统的行星滚柱丝杠、滚珠丝杠的研发、生产、销售业务。</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>铜连接, 光纤光缆</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>-1.6</v>
+        <v>-1.85</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>崔东树发文称，2026年1-2月锂电池出口达到142亿美元，增46%。</t>
+          <t>第十四届中国电子信息博览会（CITE 2026）将于2026年4月9日至11日在深圳会展中心（福田）举办。具身智能板块，宇树机器人、众擎机器人、智元机器人、越疆机器人、灵心巧手等明星企业将集体亮相。</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sz002263</t>
+          <t>sh603966</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>大东南</t>
+          <t>法兰泰克</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>4.73</v>
+        <v>13.68</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>6天4板</t>
-        </is>
-      </c>
+        <v>9.969999999999999</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>隔膜|1.公司产品覆盖传统包装薄膜、锂电池隔膜、耐高温超薄电容膜、光学膜。
-2.公司复合铜箔用电容薄膜的研发已经完成，此项目使公司生产更超薄产品成为可能，且技术指标均达到或超过国家标准。</t>
+          <t>机器人|2022年9月4日山西证券研报称，2022年上半年公司自主研发的智能酿酒机器人新增订单超2亿元，帮助下游客户实现从传统酿造向智能酿造的全面转型，降低了50%的场地需求，70%的人力需求， 54%的耗水量，实现单位面积产能的翻倍提升。</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>隔膜</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>-1.6</v>
+        <v>-1.85</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>崔东树发文称，2026年1-2月锂电池出口达到142亿美元，增46%。</t>
+          <t>第十四届中国电子信息博览会（CITE 2026）将于2026年4月9日至11日在深圳会展中心（福田）举办。具身智能板块，宇树机器人、众擎机器人、智元机器人、越疆机器人、灵心巧手等明星企业将集体亮相。</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sz000155</t>
+          <t>sz300626</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>川能动力</t>
+          <t>华瑞股份</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>16.97</v>
+        <v>24.59</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>9.98</v>
+        <v>20.01</v>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>锂矿|公司持有鼎盛锂业72%股权，鼎盛锂业主要从事电池级碳酸锂、氢氧化锂等锂盐产品生产、销售、研发。公司拟与亿纬锂能、蜂巢能源共同组建合资公司，投资建设3万吨/年锂盐项目。新设合资公司注册资本7.5亿元，公司持股比例51%。</t>
+          <t>机器人|公司换向器产品有少部分已应用于军用汽车、武器装备、航空航天等方面。人形机器人的部分电机会使用换向器产品。
+2025年11月10日公司在业绩说明会上表示，公司高度重视并积极投入到空心杯电机换向器项目的研发之中，目前已有部分产品试样中。</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>锂矿</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>-1.6</v>
+        <v>-1.85</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>崔东树发文称，2026年1-2月锂电池出口达到142亿美元，增46%。</t>
+          <t>第十四届中国电子信息博览会（CITE 2026）将于2026年4月9日至11日在深圳会展中心（福田）举办。具身智能板块，宇树机器人、众擎机器人、智元机器人、越疆机器人、灵心巧手等明星企业将集体亮相。</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>sz000762</t>
+          <t>sh600302</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>西藏矿业</t>
+          <t>标准股份</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>31.26</v>
+        <v>12.27</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>9.99</v>
+        <v>10.04</v>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>盐湖提锂|公司拥有独家开采权的西藏扎布耶盐湖是世界第三大、亚洲第一大锂矿盐湖，已探明的锂储量为184.10万吨，是富含锂、硼、钾固、液并存的特种综合性大型盐湖矿床。</t>
+          <t>机器人|2023年6月26日公司在互动平台表示，公司在自动化定制研发方面，围绕汽车内饰领域为客户提供智慧绿色的系统解决方案，目前所研发的机械臂3D机器人缝纫项目完成中控台装饰线迹试缝测试，基本具备整体交付能力。</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>盐湖提锂</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>医药生物</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>-1.62</v>
+        <v>-2.62</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>华泰证券指出，霍尔木兹海峡封锁强化化石能源价格易涨难跌预期，水、核、风、光、生物质等绿电板块有望充分受益。</t>
+          <t>美国癌症研究协会(AACR)年会将于2026年4月17-22日在美国圣地亚哥召开。据报道，今年共有超过100家中国药企亮相AACR，带来近400项研究成果。</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>sh605162</t>
+          <t>sh600488</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">新中港  </t>
+          <t>津药药业</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>14.05</v>
+        <v>6.97</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>10.02</v>
+        <v>9.94</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3天3板</t>
+          <t>6天6板</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>电力|公司采用热电联产的方式进行热力产品和电力产品的生产及供应。公司的热力业务主要面向工业用户供应所生产的蒸汽，主要满足工业园区内的造纸、印染、医药、化工、食品等150余家工业企业的热需求。公司生产的电力直接销售给国家电网公司。公司是嵊州市地区唯一一家集中供热的热电联产企业，具有150多家下游客户，区域优势和先发优势明显。</t>
+          <t>原料药|津药药业发布股票交易风险提示性公告称，公司关注到市场将公司列为创新药概念，公司目前研发以仿制药为主，无在研创新药项目。公司主营业务为甾体激素类、氨基酸类原料药及制剂的研发、生产和销售。</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>原料药</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>医药生物</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>-1.62</v>
+        <v>-2.62</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>华泰证券指出，霍尔木兹海峡封锁强化化石能源价格易涨难跌预期，水、核、风、光、生物质等绿电板块有望充分受益。</t>
+          <t>美国癌症研究协会(AACR)年会将于2026年4月17-22日在美国圣地亚哥召开。据报道，今年共有超过100家中国药企亮相AACR，带来近400项研究成果。</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>sh600644</t>
+          <t>sz000950</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>乐山电力</t>
+          <t>重药控股</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>12.64</v>
+        <v>7.14</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
+        <v>10.02</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>绿电|公司电力业务拥有水力发电站和独立的电力网络，公司电网供电区域主要分布在乐山市和眉山市的部分区县。</t>
+          <t>创新药|2025年12月10日公告，参股子公司重庆药友制药有限责任公司与上海复星医药产业发展有限公司及辉瑞共同签订《Collaboration and License Agreement》，其中主要包括由药友制药就口服小分子胰高血糖素样肽-1受体（GLP-1R）激动剂（包括 YP05002）及含有该活性成分的产品授予辉瑞于许可区域（即全球范围）及领域（人类、动物所有适应症的治疗、诊断及预防）独家开发、使用、生产及商业化权利。</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>绿电</t>
+          <t>创新药</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>商业航天</t>
+          <t>医药生物</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>-2.15</v>
+        <v>-2.62</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>当地时间4月1日傍晚，美国航空航天局新一代登月火箭“太空发射系统”从佛罗里达州肯尼迪航天中心发射升空，执行“阿耳忒弥斯2号”载人绕月任务。这是美国自1972年以来首次载人飞向月球。</t>
+          <t>美国癌症研究协会(AACR)年会将于2026年4月17-22日在美国圣地亚哥召开。据报道，今年共有超过100家中国药企亮相AACR，带来近400项研究成果。</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>sz002560</t>
+          <t>sh600056</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>通达股份</t>
+          <t>中国医药</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>13.06</v>
+        <v>11.59</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>9.959999999999999</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>业绩+商业航天|1.公司2025年1-12月实现营业收入79.99亿元，同比增长29.00%；归母净利润1.61亿元，同比增长533.17%。
-2.公司在研项目包括面向航天器装配的自动调平吊具设计及性能研究，项目产品可广泛应用于运载火箭、卫星、航天器舱段等各类航天产品的装配吊装环节，适配性强、通用性好，可大幅提升装配效率，目前已研发完成。</t>
+          <t>医药|公司已建立以国际贸易为引领、以医药工业为支撑、以医药商业为纽带的贸、工、技、服一体化产业格局，全面推动工商贸三大业务板块业务整合。</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>业绩, 商业航天</t>
+          <t>医药</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>医药生物</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>-1.61</v>
-      </c>
-      <c r="C25" s="2" t="inlineStr"/>
+        <v>-2.62</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>美国癌症研究协会(AACR)年会将于2026年4月17-22日在美国圣地亚哥召开。据报道，今年共有超过100家中国药企亮相AACR，带来近400项研究成果。</t>
+        </is>
+      </c>
       <c r="D25" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>sh600381</t>
+          <t>sz300006</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST春天 </t>
+          <t>莱美药业</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>3.22</v>
+        <v>6.52</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>20.07</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 在大健康业务方面，公司已基本完成了涵盖保健食品、药品等冬虫夏草高效利用产品的储备和战略布局。</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr"/>
+          <t>创新药|2025年4月30日公司在互动平台表示，子公司四川瀛瑞的纳米炭铁混悬注射液（CNSI-Fe）临床试验进展顺利；参股公司康德赛用于治疗晚期卵巢癌的个体化肿瘤疫苗项目（CUD002）、用于治疗中晚期肝硬化的巨噬细胞项目（CUD005）临床一期工作均在稳步推进中。</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>创新药</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>光纤光缆</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>-1.61</v>
-      </c>
-      <c r="C26" s="2" t="inlineStr"/>
+        <v>1.28</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>光纤行业迎来涨价潮，瑞银最新研报援引行业研究机构CRU数据，欧洲G652.D裸光纤价格在3月达到每光纤千米7.94欧元(约合9.1美元)，较1月环比上涨136%，同比上涨159%。</t>
+        </is>
+      </c>
       <c r="D26" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>sz002898</t>
+          <t>sz000720</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>*ST赛隆</t>
+          <t>新能泰山</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>12.13</v>
+        <v>5.94</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>9天7板</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司已建成集医药中间体、原料药、制剂的研发、生产、营销和技术服务为一体的医药全产业链的现代化制药企业。</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr"/>
+          <t>电线电缆+光纤光缆|子公司曲阜电缆主要从事电线电缆、光纤光缆、电力光缆等产品的研发、制造与销售，曲阜电缆生产、 销售的电线电缆产品是公司重点发展的智慧供应链业务产品之一。</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>电线电缆, 光纤光缆</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>光纤光缆</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>-1.61</v>
-      </c>
-      <c r="C27" s="2" t="inlineStr"/>
+        <v>1.28</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>光纤行业迎来涨价潮，瑞银最新研报援引行业研究机构CRU数据，欧洲G652.D裸光纤价格在3月达到每光纤千米7.94欧元(约合9.1美元)，较1月环比上涨136%，同比上涨159%。</t>
+        </is>
+      </c>
       <c r="D27" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>sh600608</t>
+          <t>sz000586</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST沪科 </t>
+          <t>汇源通信</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>3</v>
+        <v>18.87</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr"/>
+        <v>10.03</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司是一家信息技术行业公司，主要业务分为钢材制品加工制造及商品贸易业务两大板块。</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr"/>
+          <t>光缆光纤|公司是国内最早的全系列光缆供应商之一，光缆光纤业务主要生产、销售普通光缆、特种光缆、气吹微缆等，以及提供工程解决方案服务。公司旗下全资子公司汇源光通信是国内电力光缆的制造商、气吹微缆的供应商，同时也是高压输电线路在线检测产品的供应商。</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>光缆光纤</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>光纤光缆</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>-1.61</v>
-      </c>
-      <c r="C28" s="2" t="inlineStr"/>
+        <v>1.28</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>光纤行业迎来涨价潮，瑞银最新研报援引行业研究机构CRU数据，欧洲G652.D裸光纤价格在3月达到每光纤千米7.94欧元(约合9.1美元)，较1月环比上涨136%，同比上涨159%。</t>
+        </is>
+      </c>
       <c r="D28" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>sz000711</t>
+          <t>sh600869</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>ST京蓝</t>
+          <t>远东股份</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>3.93</v>
+        <v>15.61</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>5.08</v>
+        <v>10.01</v>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 主要业务包括流域水生态修复、灌区节水综合系统工程、污水治理、沿河生态景观工程、智慧水务等。</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr"/>
+          <t>光纤中标|远东股份公告称，公司收到子公司中标/签约千万元以上合同订单合计为人民币18.21亿元。其中，国家和地方电网类合同金额约1.67亿元；其他战略客户类合同金额约16.55亿元，涵盖智能线缆、储能系统、锂电池及智慧机场项目等，其中AIDC用光纤订单2319.77万元。</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>光纤中标</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr"/>
+          <t>化工</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>-2.68</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>财联社记者采访产业链多家企业获悉，今年以来，国内供给短缺叠加海外供应不畅，溴素价格进入上行通道。进入3月，溴素价格曲线变得极为陡峭，最新成交价已涨至7.8万元/吨，月涨幅高达90%。</t>
+        </is>
+      </c>
       <c r="D29" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>sz300834</t>
+          <t>sh603585</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>星辉环材</t>
+          <t>苏利股份</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>43.49</v>
+        <v>24.51</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>20.01</v>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>10.01</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>引入战略投资者|近日，星辉环材宣布引入战略投资者九识智能，九识智能2021年成立，截至2025年底，其运营全球最大RoboVan无人货运车队。</t>
+          <t>溴素|据2025年7月11日互动易，目前公司拥有回收溴素1.5万吨/年的产能，主要是回收溴系列阻燃剂生产过程中多余的溴素再回用。</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>引入战略投资者</t>
+          <t>溴素</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr"/>
+          <t>化工</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>-2.68</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>财联社记者采访产业链多家企业获悉，今年以来，国内供给短缺叠加海外供应不畅，溴素价格进入上行通道。进入3月，溴素价格曲线变得极为陡峭，最新成交价已涨至7.8万元/吨，月涨幅高达90%。</t>
+        </is>
+      </c>
       <c r="D30" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>sh603122</t>
+          <t>sh603067</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>合富中国</t>
+          <t>振华股份</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>18.69</v>
+        <v>34.68</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>9.99</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>医药商业+海峡两岸|1.公司系医疗流通领域的渠道商，具备与境内外试剂耗材和医疗设备原厂、各大代理商及医疗机构长期互惠、合作共赢的核心竞争力。
-2.公司为唯一一家海峡两岸市场“双上市”的医疗企业，其母公司合富医疗控股在台湾上市，公司实际控制人为台湾企业家王琼芝，在两岸医疗流通领域有深度合作。</t>
+          <t>铬+维生素|公司是全球规模最大的铬盐生产企业，维生素K3的生产能力位居全球前列。</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>医药商业, 海峡两岸</t>
+          <t>铬, 维生素</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr"/>
+          <t>化工</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>-2.68</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>财联社记者采访产业链多家企业获悉，今年以来，国内供给短缺叠加海外供应不畅，溴素价格进入上行通道。进入3月，溴素价格曲线变得极为陡峭，最新成交价已涨至7.8万元/吨，月涨幅高达90%。</t>
+        </is>
+      </c>
       <c r="D31" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>sh603863</t>
+          <t>sh603033</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>松炀资源</t>
+          <t>三维股份</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>17.25</v>
+        <v>10.78</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>造纸|公司主要从事环保再生纸的研发、生产和销售，是一家集废纸回收、环保造纸及涂布成型于一体，形成资源再生利用价值链的造纸企业。</t>
+          <t>化工|公司以精细化工新材料一体化产业链为主业，目前主要产品为BDO（电石完全自给）。未来公司将进一步向上游拓展兰炭等产品，实现原料供给一体化，向下游拓展高端聚醚材料PTMEG、可降解塑料PBAT、电子化学品NMP等产品，产品线涵盖精细化工基础原料、生物降解材料、化工新材料等。</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>造纸</t>
+          <t>化工</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr"/>
+          <t>AI应用</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>-2.24</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>中信建投研报称，AI应用行业方面，坚定看好产业趋势下的投资机会，回调后逐渐出现合适买点。</t>
+        </is>
+      </c>
       <c r="D32" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>sz002051</t>
+          <t>sh603189</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>中工国际</t>
+          <t>网达软件</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>9.91</v>
+        <v>18.03</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>9.99</v>
+        <v>10.01</v>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>一带一路+基建|公司是经中华人民共和国商务部批准，由国内著名的外贸公司、设计院、机械制造商和施工单位共同发起设立的股份有限公司。主营业务是国际工程总承包</t>
+          <t>AI应用+阿里云|1.公司以AI大模型赋能全媒体的内容生产、运营、分发为主要着力点，重构现有内容运营编辑系统、媒资管理系统，研发了系列智能化内容生产系统。
+2.公司是阿里云的核心合作伙伴，在广电融媒体端有广泛深入的技术合作。</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>一带一路, 基建</t>
+          <t>AI应用, 阿里云</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr"/>
+          <t>AI应用</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>-2.24</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>中信建投研报称，AI应用行业方面，坚定看好产业趋势下的投资机会，回调后逐渐出现合适买点。</t>
+        </is>
+      </c>
       <c r="D33" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>sh603477</t>
+          <t>sz002678</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>巨星农牧</t>
+          <t>珠江钢琴</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>17.03</v>
+        <v>6.07</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>10.01</v>
+        <v>9.959999999999999</v>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>生猪养殖|公司拥有生猪养殖行业较为完整的一体化产业链，是集种猪、饲料、商品猪生产于一体的农业产业化经营企业。</t>
+          <t>AI应用|公司以“平台+AI+生态”为目标，以“钢琴云学堂”为依托，不断扩展“AI+云计算”的技术能力。</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>生猪养殖</t>
+          <t>AI应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>sz002898</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>*ST赛隆</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>5.029999999999999</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司已建成集医药中间体、原料药、制剂的研发、生产、营销和技术服务为一体的医药全产业链的现代化制药企业。</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr"/>
+      <c r="D35" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>sz000669</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>ST金鸿</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 主营气源开发与输送、长输管网建设与管理、城市燃气经营与销售、车用加气站投资与运营、LNG点供、分布式能源项目开发与建设等。</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>sh603123</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>翠微股份</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>数字货币+跨境支付|1.全资子公司海科融通已积极参与央行数字货币研究所指定运营银行签署合作协议，进行系统对接，推进数字人民币受理的系统建设。
+2.子公司海科融通在国际业务方面聚焦卡组织合作，构建卡组交易生态，外卡收单业务落地，微信海外钱包上线，助力推广境内交易网络与人民币卡使用，并积极探索海外业务。</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>数字货币, 跨境支付</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr"/>
+      <c r="D37" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>sh600106</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>重庆路桥</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>基建|公司是一家集城市路桥经营、城市基础设施建设、投资及房地产综合开发为一体的股份制企业。</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>基建</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>sz002831</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>裕同科技</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>35.29</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>并购重组|裕同科技公告称，公司拟通过自有或自筹资金向观点投资收购其持有的华研科技51%股份，交易金额为4.49亿元。本次交易构成关联交易，公司实际控制人王华君、吴兰兰夫妇合计持有观点投资100%股权。交易完成后，华研科技将成为公司的控股子公司，并纳入公司合并报表范围。东莞市华研新材料科技有限公司成立于2016年，致力于为客户提供一站式精密金属及陶瓷零组件整体解决方案，一体化设计、研发、制造、组装整体解决方案的专精特新国家级“小巨人”高新技术企业。</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>并购重组</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr"/>
+      <c r="D39" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>sz002952</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>亚世光电</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>25.18</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>光电显示模组|公司下设全资子公司亚世光电(鞍山)有限公司。公司属于国内液晶领域领先企业，拥有2条国际领先水平的液晶显示屏生产线和8条光电显示模组生产线。</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>光电显示模组</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2039,7 +2300,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -2054,76 +2315,46 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sz002560</t>
+          <t>sz000586</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>通达股份</t>
+          <t>汇源通信</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sh605162</t>
+          <t>sz000720</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">新中港  </t>
+          <t>新能泰山</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sz300834</t>
+          <t>sz000950</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>星辉环材</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>sz000788</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>北大医药</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>sh600594</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>益佰制药</t>
+          <t>重药控股</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,19 +476,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="101" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="93" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="245" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="234" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -552,486 +552,486 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1.51</v>
+        <v>3.75</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>4月2日，工信部发布关于开展普惠算力赋能中小企业发展专项行动的通知。提出推动全光交换等技术应用部署，降低算力应用终端到服务器的网络时延，提升应用交互体验。</t>
+          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>sz002792</t>
+          <t>sz002408</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>通宇通讯</t>
+          <t>齐翔腾达</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>45.34</v>
+        <v>6.62</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr"/>
+        <v>9.969999999999999</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>光模块+商业航天|1.间接参股25.58%的深圳光为致力于各类光模块研发，目前已成功研发出了包括100G CFP2、400G QSFP-DD等系列在内的多个光模块产品类型。
-2.蓝箭鸿擎是国内唯三有万颗卫星发射计划的公司之一，拥有鸿鹄星座计划，申报了1万颗卫星。公司投资参股北京蓝箭鸿擎科技公司以强化协同效应。</t>
+          <t>石油化工|公司目前已形成碳四丁烯组分综合利用产品线、异丁烯组分综合利用产品线和丁烷组分综合利用产品线三条产品线。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>光模块, 商业航天</t>
+          <t>石油化工</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1.51</v>
+        <v>3.75</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>4月2日，工信部发布关于开展普惠算力赋能中小企业发展专项行动的通知。提出推动全光交换等技术应用部署，降低算力应用终端到服务器的网络时延，提升应用交互体验。</t>
+          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sz002980</t>
+          <t>sz002442</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>华盛昌</t>
+          <t>龙星科技</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46.09</v>
+        <v>6.02</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>10</v>
+        <v>10.05</v>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>并购重组+光通信|华盛昌公告称，公司拟以现金方式收购深圳市伽蓝特科技有限公司100%股权，整体估值暂定为4.6亿元。伽蓝特专注于仪器仪表测试测量行业中的光通信模块和光芯片测试领域。</t>
+          <t>化工+锂电|公司主要业务为炭黑、白炭黑及煤焦油制品的生产和销售。公司主要产品包括PVDF。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>并购重组, 光通信</t>
+          <t>化工, 锂电</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.51</v>
+        <v>3.75</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4月2日，工信部发布关于开展普惠算力赋能中小企业发展专项行动的通知。提出推动全光交换等技术应用部署，降低算力应用终端到服务器的网络时延，提升应用交互体验。</t>
+          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sz300812</t>
+          <t>sh600527</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>易天股份</t>
+          <t>江南高纤</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>40.5</v>
+        <v>2.5</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>20</v>
+        <v>10.13</v>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>光模块设备|2023年7月13日公司在互动平台表示，子公司微组半导体的微组装设备可应用于部分光模块的部分器件组装工序，设备精度已满足100G的精度。未来公司也将持续提升产品精度，在800G/1.6T的精度方向进一步研发。相关产品已获得客户订单。</t>
+          <t>化纤|国内涤纶毛条和复合纤维的龙头公司。公司产品主要包括涤纶毛条和复合短纤维。下游主要供给纸尿裤、卫生巾等一次性卫生材料。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>光模块设备</t>
+          <t>化纤</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1.51</v>
+        <v>3.75</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4月2日，工信部发布关于开展普惠算力赋能中小企业发展专项行动的通知。提出推动全光交换等技术应用部署，降低算力应用终端到服务器的网络时延，提升应用交互体验。</t>
+          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sz002222</t>
+          <t>sz000703</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>恒逸石化</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>75.45999999999999</v>
+        <v>14.16</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>10</v>
+        <v>10.02</v>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>光通信+光刻机|1.公司部分精密光学元件产品应用于光通讯领域。
-2.公司曾通过欧洲代理向ASML提供及其少量光学元件。此外，华为是公司的客户，公司在业务范围内向其提供光学元件产品。</t>
+          <t>石油化工|公司已发展成为全球领先的炼化、化纤的产业链一体化企业之一，主要产品包括汽油、柴油、煤油等成品油；对二甲苯（PX）、苯、精对苯二甲酸（PTA）、己内酰胺（CPL）等石化产品；涤纶预取向丝（POY）、涤纶牵伸丝（FDY）、涤纶加弹丝（DTY）以及涤纶短纤、聚酯（PET）切片、聚酯瓶片等产品。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>光通信, 光刻机</t>
+          <t>石油化工</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1.51</v>
+        <v>3.75</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4月2日，工信部发布关于开展普惠算力赋能中小企业发展专项行动的通知。提出推动全光交换等技术应用部署，降低算力应用终端到服务器的网络时延，提升应用交互体验。</t>
+          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sz003031</t>
+          <t>sz002427</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>中瓷电子</t>
+          <t>尤夫股份</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>88.56999999999999</v>
+        <v>6.23</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>10</v>
+        <v>10.07</v>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>光通信+商业航天|1.在光通信领域，公司开发的光通信器件外壳包括Butterfly外壳、TOSA外壳、ROSA外壳、光接收组件外壳、光开关外壳等，传输速率覆盖2.5Gbps-800Gbps，产品种类可以覆盖全部光通信器件产品，电性能、可靠性达到国际水平，能够替代进口外壳。目前公司光通信领域器件产品已经进入多家世界知名光通信模块生产厂家，包括华为、新易盛、旭创、光迅科技等。
-2.子公司国联万众的GaN射频芯片可以应用到商业卫星的卫星通信模块中。</t>
+          <t>化纤|公司开发的拒海水聚酯工业丝产品已广泛应用于船舶、海洋钻井、深海风电系泊缆绳，产品通过DNV、ABS船级社测试认证。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>光通信, 商业航天</t>
+          <t>化纤</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1.51</v>
+        <v>3.75</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4月2日，工信部发布关于开展普惠算力赋能中小企业发展专项行动的通知。提出推动全光交换等技术应用部署，降低算力应用终端到服务器的网络时延，提升应用交互体验。</t>
+          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sz002796</t>
+          <t>sh600370</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>世嘉科技</t>
+          <t xml:space="preserve">三房巷  </t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>50.59</v>
+        <v>2.52</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>10</v>
+        <v>10.04</v>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>光通信|2025年8月4日公告，公司看好光通信细分行业的市场前景，认可光彩芯辰（浙江）科技有限公司在光通信领域内的前期投入、技术储备以及客户资源。公司拟通过增资扩股的方式取得光彩芯辰部分股权，并与光彩芯辰签署了《增资意向协议》。如交易顺利完成，公司将于交易完成后预计持有光彩芯辰不超过20%的股权。光彩芯辰主要从事100G—800G多系列光通信模块的研发制造，总部及生产基地均位于中新嘉善现代产业园。</t>
+          <t>PTA|公司成为“PTA-瓶级聚酯切片”一体化布局的优势企业，PTA产品是郑州商品交易所PTA交割免检品牌，已开发出多种全系列的瓶级聚酯切片产品。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>PTA</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1.51</v>
+        <v>3.75</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4月2日，工信部发布关于开展普惠算力赋能中小企业发展专项行动的通知。提出推动全光交换等技术应用部署，降低算力应用终端到服务器的网络时延，提升应用交互体验。</t>
+          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sh688226</t>
+          <t>sz000990</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>威腾电气</t>
+          <t>诚志股份</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>50.28</v>
+        <v>10.24</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>20</v>
+        <v>9.99</v>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>光模块|上海孛璞半导体技术有限公司负责向子公司威璞磐芯（上海）科技有限公司提供高速光模块/组的整体设计方案并转让全部已有相关技术成果的知识产权。</t>
+          <t>化工|2022年8月，公司拟通过全资子公司青岛华青投资建设POE（聚烯烃弹性体）项目和超高分子量聚乙烯项目。公司在南京生产基地拥有两套烯烃生产工厂，乙烯、丙烯、丁二烯总产能接近100万吨/年。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>光模块</t>
+          <t>化工</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1.51</v>
+        <v>3.75</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4月2日，工信部发布关于开展普惠算力赋能中小企业发展专项行动的通知。提出推动全光交换等技术应用部署，降低算力应用终端到服务器的网络时延，提升应用交互体验。</t>
+          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sh688205</t>
+          <t>sh600810</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">德科立  </t>
+          <t>神马股份</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>247.21</v>
+        <v>8.99</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>20</v>
+        <v>10.04</v>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>OCS|德科立发布股票交易异常波动公告称，近期，受AI算力需求推动，OCS（光交换）产品引发市场高度关注。公司始终密切关注相关技术发展，硅基OCS产品已获得海外样品订单，尚未获得海外大厂的批量订单。</t>
+          <t>化纤|公司产业结构上横跨化工、化纤两大行业，通过实施一体化战略，形成了以尼龙66盐和尼龙66盐中间产品、尼龙66切片、工业丝、帘子布、尼龙6切片等主导产品为支柱、以原辅材料及相关产品为依托的新产业格局。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>OCS</t>
+          <t>化纤</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-0.63</v>
+        <v>3.75</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>韩国3月份半导体出口额同比猛增151.4%，首次突破300亿美元关口。</t>
+          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sh605589</t>
+          <t>sz002109</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>圣泉集团</t>
+          <t>兴化股份</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>32.43</v>
+        <v>4.46</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>10.01</v>
+        <v>10.12</v>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>光刻胶|公司产品包括光刻胶用电子级酚醛树脂。</t>
+          <t>煤化工|全资子公司兴化化工主营煤制甲醇，产能30万吨/年。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>光刻胶</t>
+          <t>煤化工</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>-0.63</v>
+        <v>3.75</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>韩国3月份半导体出口额同比猛增151.4%，首次突破300亿美元关口。</t>
+          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sh688485</t>
+          <t>sh600722</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>九州一轨</t>
+          <t>金牛化工</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>31.3</v>
+        <v>14.52</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>20.02</v>
+        <v>10</v>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>半导体+高铁|1.2026年3月27日公告，公司拟与江苏通用半导体有限公司共同出资设立北京通用九州金刚石科技有限公司(暂定名)，注册资本2亿元，其中公司以现金出资8000万元，占40%。合资公司聚焦第四代半导体材料(金刚石)的研发、制造及在轨道交通、声纹传感等领域的产业化应用。
-2.公司主要面向城市轨道交通、市域/市郊铁路的减振降噪、TOD上盖开发噪声振动综合控制等领域提供钢弹簧浮置道床减振系统、预制钢弹簧浮置板、声屏障、隔离式高弹性减振垫、重型调频钢轨耗能装置等系列化产品和服务。</t>
+          <t>甲醇|公司的主要业务为甲醇的生产和销售，产品方式为焦炉气制甲醇。公司的主要业务由持股50%的控股子公司金牛旭阳经营，金牛旭阳拥有的甲醇生产能力为20万吨/年。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>半导体, 高铁</t>
+          <t>甲醇</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>-0.63</v>
+        <v>3.75</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>韩国3月份半导体出口额同比猛增151.4%，首次突破300亿美元关口。</t>
+          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sh605303</t>
+          <t>sh600955</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>园林股份</t>
+          <t>维远股份</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>17.77</v>
+        <v>18.1</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>10.03</v>
@@ -1039,749 +1039,735 @@
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>存储芯片|参股华澜微是国内极少数拥有全系列数码存储控制器芯片的高科技公司，产品应用于存储卡、USB闪存盘、移动硬盘、固态硬盘、硬盘阵列以及大数据存储系统。</t>
+          <t>化工+锂电池|1.公司主营业务为“苯酚、丙酮—双酚A—聚碳酸酯”产业链有机化学新材料产品的研发、生产与销售，是目前国内唯一具备完整聚碳酸酯产业链的公司。
+2.2022年2月28日公告，公司与日本宇部兴产株式会社签署了《2万吨/年高纯碳酸二甲酯技术许可协议》，宇部将其拥有的通过碳酸二甲酯生产高纯碳酸二甲酯的技术许可给公司生产HPDMC；HPDMC主要应用于锂电池电解液。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>存储芯片</t>
+          <t>化工, 锂电池</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-0.63</v>
+        <v>3.75</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>韩国3月份半导体出口额同比猛增151.4%，首次突破300亿美元关口。</t>
+          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sh688146</t>
+          <t>sz003042</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>中船特气</t>
+          <t>中农联合</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>51.22</v>
+        <v>18.26</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>20.01</v>
+        <v>10</v>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>光刻气|中船特气公告称，公司光刻气产品（Kr/Ne、Ar/Ne/Xe）通过日本GIGAPHOTON株式会社的合格供应商认证，证书有效期至2030年7月23日。</t>
+          <t>农药|公司实控人为中华全国供销合作总社。公司是专业从事农药中间体、原药及制剂产品的研发、生产和销售的全产业链农药生产企业。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>光刻气</t>
+          <t>农药</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>-1.03</v>
+        <v>3.75</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>工信部首次明确提出，探索“算力银行”“算力超市”等创新业务，支持中小企业存入闲置算力资源，通过跨区域、跨周期调度实现灵活取用。</t>
+          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sz300608</t>
+          <t>sh600691</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>思特奇</t>
+          <t>潞化科技</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>12.9</v>
+        <v>3.34</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>20</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>算力调度|‌思特奇在国家“东数西算”的某关键枢纽节点，公司主导建设的算力调度与运营平台已成为行业典范，成功统一纳管调度了区域内的算力资源，形成了“区域算力一张网”。</t>
+          <t>煤化工|公司主要业务包括化工产品和化工机械设备的生产和销售，化工产品研发及工程总承包设计等，主要产品包括尿素、聚氯乙烯、烯烃、烧碱、双氧水、甲醇等。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>算力调度</t>
+          <t>煤化工</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>-1.03</v>
+        <v>3.75</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>工信部首次明确提出，探索“算力银行”“算力超市”等创新业务，支持中小企业存入闲置算力资源，通过跨区域、跨周期调度实现灵活取用。</t>
+          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sz003007</t>
+          <t>sh600227</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>直真科技</t>
+          <t xml:space="preserve">赤天化  </t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>44.06</v>
+        <v>3.82</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>10.01</v>
+        <v>10.09</v>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>算力调度|公司大力推进算力网络相关产品的定义和解决方案的推广，23年上半年，完成了网控制器、算控制器为核心的算网大脑产品的预研和部分开发工作，进行了基于网络和算力感知技术的算力、运力可视化、意图驱动的多因素运力、算力调度的探索与实践。</t>
+          <t>氮肥|公司是贵州省最大的氮肥生产企业，公司化肥化工生产基地分别是以天然气为原料生产的赤水化工分公司（年产63万吨尿素）和以煤为生产原料的公司全资子公司桐梓化工（年产52万吨尿素、30万吨甲醇）。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>算力调度</t>
+          <t>氮肥</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>-1.03</v>
+        <v>3.75</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>工信部首次明确提出，探索“算力银行”“算力超市”等创新业务，支持中小企业存入闲置算力资源，通过跨区域、跨周期调度实现灵活取用。</t>
+          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sh600654</t>
+          <t>sh603968</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">中安科  </t>
+          <t>醋化股份</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>3.64</v>
+        <v>14.19</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>9.969999999999999</v>
+        <v>10</v>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>算力租赁|2024年7月25日公告，公司及全资子公司灵算智云（武汉）投资有限公司拟与宜兴兴阳产业投资有限公司签署投资合作协议，共建宜兴人工智能算力中心项目。本次合作项目计划总投资为3.75亿元。</t>
+          <t>化工|公司主要从事以醋酸衍生物、吡啶衍生物为主体的高端专用精细化学品的研发、生产和销售。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>算力租赁</t>
+          <t>化工</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>-1.03</v>
+        <v>3.75</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>工信部首次明确提出，探索“算力银行”“算力超市”等创新业务，支持中小企业存入闲置算力资源，通过跨区域、跨周期调度实现灵活取用。</t>
+          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sh600602</t>
+          <t>sz002470</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>云赛智联</t>
+          <t>金正大</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>24.39</v>
+        <v>3</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>10.01</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>算力租赁|公司是上海国资委旗下上市公司，定位于中立第三方高端数据中心运营商。</t>
+          <t>化肥|公司的复合肥、缓控释肥、硝基复合肥、水溶肥及其他新型肥料在技术和市场占有率方面居国内领先地位，具有较强的竞争优势。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>算力租赁</t>
+          <t>化肥</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>-1.85</v>
+        <v>3.75</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>第十四届中国电子信息博览会（CITE 2026）将于2026年4月9日至11日在深圳会展中心（福田）举办。具身智能板块，宇树机器人、众擎机器人、智元机器人、越疆机器人、灵心巧手等明星企业将集体亮相。</t>
+          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sh605133</t>
+          <t>sh600423</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>嵘泰股份</t>
+          <t>柳化股份</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>28.49</v>
+        <v>3.61</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>10</v>
+        <v>10.06</v>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司与润孚动力合资设立润泰机器人公司，布局应用于人形机器人和汽车底盘系统的行星滚柱丝杠、滚珠丝杠的研发、生产、销售业务。</t>
+          <t>化工+半导体材料|1.公司主要从事27.5%双氧水的生产和销售，年设计产能为10万吨。公司采用蒽醌钯催化剂工艺，以外购氢气为主要原料生产双氧水。
+2.公司生产的电子级双氧水(G1/G2级30%-32%浓度)主要用于半导体硅晶片清洗剂，电镀液无机杂质去除，电子行业中铜、铜合金和镓、锗的处理，以及太阳能硅晶片的蚀刻和清洗等方面。</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>化工, 半导体材料</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>-1.85</v>
+        <v>3.75</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>第十四届中国电子信息博览会（CITE 2026）将于2026年4月9日至11日在深圳会展中心（福田）举办。具身智能板块，宇树机器人、众擎机器人、智元机器人、越疆机器人、灵心巧手等明星企业将集体亮相。</t>
+          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sh603966</t>
+          <t>sh603255</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>法兰泰克</t>
+          <t xml:space="preserve">鼎际得  </t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>13.68</v>
+        <v>29.4</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>9.969999999999999</v>
+        <v>9.99</v>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>机器人|2022年9月4日山西证券研报称，2022年上半年公司自主研发的智能酿酒机器人新增订单超2亿元，帮助下游客户实现从传统酿造向智能酿造的全面转型，降低了50%的场地需求，70%的人力需求， 54%的耗水量，实现单位面积产能的翻倍提升。</t>
+          <t>化工+光伏|1.公司是国内少数同时具备高分子材料高效能催化剂和化学助剂产品的专业提供商，形成了聚烯烃高效能催化剂和化学助剂的研发、生产和销售为一体的业务体系。
+2.公司聚烯陉催化剂产品对应的是下游产业烯陉聚合技术的核心产品POE粒子，N型电池的推广可以增加POE用量。</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>化工, 光伏</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>-1.85</v>
+        <v>3.75</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>第十四届中国电子信息博览会（CITE 2026）将于2026年4月9日至11日在深圳会展中心（福田）举办。具身智能板块，宇树机器人、众擎机器人、智元机器人、越疆机器人、灵心巧手等明星企业将集体亮相。</t>
+          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sz300626</t>
+          <t>sh600470</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>华瑞股份</t>
+          <t>六国化工</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>24.59</v>
+        <v>7.05</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>20.01</v>
+        <v>9.98</v>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司换向器产品有少部分已应用于军用汽车、武器装备、航空航天等方面。人形机器人的部分电机会使用换向器产品。
-2025年11月10日公司在业绩说明会上表示，公司高度重视并积极投入到空心杯电机换向器项目的研发之中，目前已有部分产品试样中。</t>
+          <t>化肥|公司是华东地区磷复肥和磷化工一体化专业制造的大型企业，主营业务为化肥(含氮肥、磷肥、钾肥)、肥料（含复合肥料、复混肥料、有机肥料及微生物肥料）、化学制品（含精制磷酸、磷酸盐）、化学原料的生产加工和销售。</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>化肥</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>-1.85</v>
+        <v>3.75</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>第十四届中国电子信息博览会（CITE 2026）将于2026年4月9日至11日在深圳会展中心（福田）举办。具身智能板块，宇树机器人、众擎机器人、智元机器人、越疆机器人、灵心巧手等明星企业将集体亮相。</t>
+          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>sh600302</t>
+          <t>sz300927</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>标准股份</t>
+          <t>江天化学</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>12.27</v>
+        <v>30.49</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>10.04</v>
+        <v>19.99</v>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>机器人|2023年6月26日公司在互动平台表示，公司在自动化定制研发方面，围绕汽车内饰领域为客户提供智慧绿色的系统解决方案，目前所研发的机械臂3D机器人缝纫项目完成中控台装饰线迹试缝测试，基本具备整体交付能力。</t>
+          <t>化工|公司专注于以甲醇下游深加工为产业链的高端专用精细化学品的研发、生产和销售，主要产品包括颗粒多聚甲醛、高浓度甲醛、超高纯氯甲烷及1,3,5-三丙烯酰基六氢-均三嗪等。</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>化工</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>医药生物</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>-2.62</v>
+        <v>3.75</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>美国癌症研究协会(AACR)年会将于2026年4月17-22日在美国圣地亚哥召开。据报道，今年共有超过100家中国药企亮相AACR，带来近400项研究成果。</t>
+          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>sh600488</t>
+          <t>sz000912</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>津药药业</t>
+          <t>泸天化</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>6.97</v>
+        <v>5.27</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>9.94</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>6天6板</t>
-        </is>
-      </c>
+        <v>10.02</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>原料药|津药药业发布股票交易风险提示性公告称，公司关注到市场将公司列为创新药概念，公司目前研发以仿制药为主，无在研创新药项目。公司主营业务为甾体激素类、氨基酸类原料药及制剂的研发、生产和销售。</t>
+          <t>化肥|公司的主营业务包括尿素、复合肥等化肥类产品，液氨、甲醇、二甲醚、稀硝酸系列、浓硝酸、液体硝酸铵以及四氧化二氮等化工类产品。</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>原料药</t>
+          <t>化肥</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>医药生物</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>-2.62</v>
+        <v>3.75</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>美国癌症研究协会(AACR)年会将于2026年4月17-22日在美国圣地亚哥召开。据报道，今年共有超过100家中国药企亮相AACR，带来近400项研究成果。</t>
+          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>sz000950</t>
+          <t>sz002637</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>重药控股</t>
+          <t>赞宇科技</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>7.14</v>
+        <v>12.28</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.04</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>创新药|2025年12月10日公告，参股子公司重庆药友制药有限责任公司与上海复星医药产业发展有限公司及辉瑞共同签订《Collaboration and License Agreement》，其中主要包括由药友制药就口服小分子胰高血糖素样肽-1受体（GLP-1R）激动剂（包括 YP05002）及含有该活性成分的产品授予辉瑞于许可区域（即全球范围）及领域（人类、动物所有适应症的治疗、诊断及预防）独家开发、使用、生产及商业化权利。</t>
+          <t>油脂化工|公司油脂化工业务主要由杭州油化、南通凯塔和杜库达三家控股子公司负责生产经营。油脂化工业务主要以棕榈油为原料，主要产品包括硬脂酸、脂肪酸、油酸、脂肪醇、脂肪胺、二聚酸、聚酰胺树脂、甘油及其他助剂等油脂化工产品。</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>油脂化工</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>医药生物</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>-2.62</v>
+        <v>3.75</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>美国癌症研究协会(AACR)年会将于2026年4月17-22日在美国圣地亚哥召开。据报道，今年共有超过100家中国药企亮相AACR，带来近400项研究成果。</t>
+          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>sh600056</t>
+          <t>sh603188</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>中国医药</t>
+          <t>亚邦股份</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>11.59</v>
+        <v>5.13</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>9.959999999999999</v>
+        <v>10.09</v>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>医药|公司已建立以国际贸易为引领、以医药工业为支撑、以医药商业为纽带的贸、工、技、服一体化产业格局，全面推动工商贸三大业务板块业务整合。</t>
+          <t>染料|公司主要从事染料及染料中间体的销售与服务，是国内蒽醌结构染料生产专家工厂。</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>染料</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>医药生物</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>-2.62</v>
+        <v>3.75</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>美国癌症研究协会(AACR)年会将于2026年4月17-22日在美国圣地亚哥召开。据报道，今年共有超过100家中国药企亮相AACR，带来近400项研究成果。</t>
+          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>sz300006</t>
+          <t>sh600623</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>莱美药业</t>
+          <t>华谊集团</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>6.52</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>20.07</v>
+        <v>10.01</v>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>创新药|2025年4月30日公司在互动平台表示，子公司四川瀛瑞的纳米炭铁混悬注射液（CNSI-Fe）临床试验进展顺利；参股公司康德赛用于治疗晚期卵巢癌的个体化肿瘤疫苗项目（CUD002）、用于治疗中晚期肝硬化的巨噬细胞项目（CUD005）临床一期工作均在稳步推进中。</t>
+          <t>化工|公司主要从事能源化工、绿色轮胎、先进材料、精细化工和化工服务五大核心业务，主要产品包括甲醇、醋酸及酯，工业气体，丙烯及下游产品，涂料及树脂，轮胎等。</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>化工</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>1.28</v>
+        <v>3.75</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>光纤行业迎来涨价潮，瑞银最新研报援引行业研究机构CRU数据，欧洲G652.D裸光纤价格在3月达到每光纤千米7.94欧元(约合9.1美元)，较1月环比上涨136%，同比上涨159%。</t>
+          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>sz000720</t>
+          <t>sz002274</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>新能泰山</t>
+          <t>华昌化工</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>5.94</v>
+        <v>6.5</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>9天7板</t>
-        </is>
-      </c>
+        <v>9.98</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>电线电缆+光纤光缆|子公司曲阜电缆主要从事电线电缆、光纤光缆、电力光缆等产品的研发、制造与销售，曲阜电缆生产、 销售的电线电缆产品是公司重点发展的智慧供应链业务产品之一。</t>
+          <t>煤化工|公司是一家以煤气化为产业链源头的综合性的化工企业，产业链总体分为三个部分：一是煤制合成气（主要成分COH2），生产合成氨、尿素、纯碱、氯化铵、硝酸等；二是使用煤化工生产的产品生产新型肥料；三是以合成气与丙烯为原料，实现无机化工与石油化工相结合研发、生产新型材料，后续产品为醇类、增塑剂、树脂、涂料等。另外，随着氢燃料电池技术及产业的发展，氢气将作为能源进行利用。</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>电线电缆, 光纤光缆</t>
+          <t>煤化工</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>1.28</v>
+        <v>3.75</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>光纤行业迎来涨价潮，瑞银最新研报援引行业研究机构CRU数据，欧洲G652.D裸光纤价格在3月达到每光纤千米7.94欧元(约合9.1美元)，较1月环比上涨136%，同比上涨159%。</t>
+          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>sz000586</t>
+          <t>sz002092</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>汇源通信</t>
+          <t>中泰化学</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>18.87</v>
+        <v>6.95</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.969999999999999</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>光缆光纤|公司是国内最早的全系列光缆供应商之一，光缆光纤业务主要生产、销售普通光缆、特种光缆、气吹微缆等，以及提供工程解决方案服务。公司旗下全资子公司汇源光通信是国内电力光缆的制造商、气吹微缆的供应商，同时也是高压输电线路在线检测产品的供应商。</t>
+          <t>化工|公司拥有完整的煤炭—热电—氯碱化工—粘胶纤维—粘胶纱上下游一体化的循环经济产业链，主营聚氯乙烯树脂（PVC）、离子膜烧碱、粘胶纤维、粘胶纱等四大产品。公司本部现有150万吨PVC产能。</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>光缆光纤</t>
+          <t>化工</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>1.28</v>
+        <v>3.75</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>光纤行业迎来涨价潮，瑞银最新研报援引行业研究机构CRU数据，欧洲G652.D裸光纤价格在3月达到每光纤千米7.94欧元(约合9.1美元)，较1月环比上涨136%，同比上涨159%。</t>
+          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>sh600869</t>
+          <t>sh600075</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>远东股份</t>
+          <t>新疆天业</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>15.61</v>
+        <v>6.8</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>10.01</v>
+        <v>10.03</v>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>光纤中标|远东股份公告称，公司收到子公司中标/签约千万元以上合同订单合计为人民币18.21亿元。其中，国家和地方电网类合同金额约1.67亿元；其他战略客户类合同金额约16.55亿元，涵盖智能线缆、储能系统、锂电池及智慧机场项目等，其中AIDC用光纤订单2319.77万元。</t>
+          <t>化工|公司通过资产重组、收购氯碱化工资产，已具备较为完整的“自备电力→电石→聚氯乙烯树脂及副产品→电石渣及其他废弃物制水泥”一体化产业联动式绿色环保型循环经济产业链，具有89万吨PVC产能（包括69万吨通用PVC、10万吨特种树脂、10万吨糊树脂）、65万吨离子膜烧碱产能、134万吨电石产能，同时拥有2×300MW、2×330MW自备热电站以及405万吨电石渣制水泥装置。</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>光纤中标</t>
+          <t>化工</t>
         </is>
       </c>
     </row>
@@ -1792,163 +1778,164 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>-2.68</v>
+        <v>3.75</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>财联社记者采访产业链多家企业获悉，今年以来，国内供给短缺叠加海外供应不畅，溴素价格进入上行通道。进入3月，溴素价格曲线变得极为陡峭，最新成交价已涨至7.8万元/吨，月涨幅高达90%。</t>
+          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>sh603585</t>
+          <t>sh600063</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>苏利股份</t>
+          <t>皖维高新</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>24.51</v>
+        <v>7.19</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>10.01</v>
+        <v>9.94</v>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>溴素|据2025年7月11日互动易，目前公司拥有回收溴素1.5万吨/年的产能，主要是回收溴系列阻燃剂生产过程中多余的溴素再回用。</t>
+          <t>化纤|公司主要从事聚乙烯醇（PVA）、高强高模PVA纤维、PVB树脂、PVA光学薄膜、可再分散性乳胶粉、醋酸乙烯、VAE乳液、酒精、聚酯切片、醋酸甲酯、电石渣制水泥熟料及环保水泥，以及其他PVA相关的衍生产品、中间产品和副产品等的研发、生产与销售。</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>溴素</t>
+          <t>化纤</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>体育产业</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>-2.68</v>
+        <v>2.7</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>财联社记者采访产业链多家企业获悉，今年以来，国内供给短缺叠加海外供应不畅，溴素价格进入上行通道。进入3月，溴素价格曲线变得极为陡峭，最新成交价已涨至7.8万元/吨，月涨幅高达90%。</t>
+          <t>顶流赛事“苏超”11日重燃战火，比首届提前一个月，广东、湖北、福建今年新办的联赛，以及山东的“齐鲁超赛”也将在这个月打响。</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>sh603067</t>
+          <t>sz002181</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>振华股份</t>
+          <t>粤 传 媒</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>34.68</v>
+        <v>11.81</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>9.99</v>
+        <v>9.959999999999999</v>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>铬+维生素|公司是全球规模最大的铬盐生产企业，维生素K3的生产能力位居全球前列。</t>
+          <t>AI应用+体育|1.公司在视频制作中应用AI技术，在美术插画、创意视效和智能剪辑等方面提升制作效率和品质，以更好地满足市场和用户需求。
+2.公司先锋报业经营《足球》报刊及足球+APP、劲球网、足球报微信公众号等新媒体矩阵。</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>铬, 维生素</t>
+          <t>AI应用, 体育</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>体育产业</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>-2.68</v>
+        <v>2.7</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>财联社记者采访产业链多家企业获悉，今年以来，国内供给短缺叠加海外供应不畅，溴素价格进入上行通道。进入3月，溴素价格曲线变得极为陡峭，最新成交价已涨至7.8万元/吨，月涨幅高达90%。</t>
+          <t>顶流赛事“苏超”11日重燃战火，比首届提前一个月，广东、湖北、福建今年新办的联赛，以及山东的“齐鲁超赛”也将在这个月打响。</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>sh603033</t>
+          <t>sz002431</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>三维股份</t>
+          <t>棕榈股份</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>10.78</v>
+        <v>2.77</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>10</v>
+        <v>9.92</v>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>化工|公司以精细化工新材料一体化产业链为主业，目前主要产品为BDO（电石完全自给）。未来公司将进一步向上游拓展兰炭等产品，实现原料供给一体化，向下游拓展高端聚醚材料PTMEG、可降解塑料PBAT、电子化学品NMP等产品，产品线涵盖精细化工基础原料、生物降解材料、化工新材料等。</t>
+          <t>基建+体育|参股成立的棕榈体育产业有限公司、参股英超西布罗姆维奇俱乐部。推进’生态城镇+体育’战略。</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>基建, 体育</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>体育产业</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>-2.24</v>
+        <v>2.7</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>中信建投研报称，AI应用行业方面，坚定看好产业趋势下的投资机会，回调后逐渐出现合适买点。</t>
+          <t>顶流赛事“苏超”11日重燃战火，比首届提前一个月，广东、湖北、福建今年新办的联赛，以及山东的“齐鲁超赛”也将在这个月打响。</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>sh603189</t>
+          <t>sh600158</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>网达软件</t>
+          <t>中体产业</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>18.03</v>
+        <v>11.87</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>10.01</v>
@@ -1956,309 +1943,3145 @@
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>AI应用+阿里云|1.公司以AI大模型赋能全媒体的内容生产、运营、分发为主要着力点，重构现有内容运营编辑系统、媒资管理系统，研发了系列智能化内容生产系统。
-2.公司是阿里云的核心合作伙伴，在广电融媒体端有广泛深入的技术合作。</t>
+          <t>体育|公司作为国家体育总局唯一一家A股上市公司，在赛事活动、体育传播、教育培训、体育彩票、体育空间平台、体育认证等业务领域已初步完成全国性布局。</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>AI应用, 阿里云</t>
+          <t>体育</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>体育产业</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>-2.24</v>
+        <v>2.7</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>中信建投研报称，AI应用行业方面，坚定看好产业趋势下的投资机会，回调后逐渐出现合适买点。</t>
+          <t>顶流赛事“苏超”11日重燃战火，比首届提前一个月，广东、湖北、福建今年新办的联赛，以及山东的“齐鲁超赛”也将在这个月打响。</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>sz002678</t>
+          <t>sh605099</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>珠江钢琴</t>
+          <t>共创草坪</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>6.07</v>
+        <v>41.15</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>9.959999999999999</v>
+        <v>10</v>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>AI应用|公司以“平台+AI+生态”为目标，以“钢琴云学堂”为依托，不断扩展“AI+云计算”的技术能力。</t>
+          <t>体育|公司是全球生产和销售规模最大的人造草坪企业，FIFA（国际足联）8家全球人造草坪优选供应商之一，WorldRugby（世界橄榄球运动联盟）8家全球人造草坪优选供应商之一、FIH（国际曲联）11家全球人造草坪优选供应商之一。</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>体育</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>体育产业</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="C34" s="2" t="inlineStr"/>
+        <v>2.7</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>顶流赛事“苏超”11日重燃战火，比首届提前一个月，广东、湖北、福建今年新办的联赛，以及山东的“齐鲁超赛”也将在这个月打响。</t>
+        </is>
+      </c>
       <c r="D34" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>sz002898</t>
+          <t>sz300651</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>*ST赛隆</t>
+          <t>金陵体育</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>12.74</v>
+        <v>32.4</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>5.029999999999999</v>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司已建成集医药中间体、原料药、制剂的研发、生产、营销和技术服务为一体的医药全产业链的现代化制药企业。</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr"/>
+          <t>体育|公司是行业领先的高端体育装备和体育文化设施系统集成服务商，以体育装备、场馆建设、全民健身、赛事保障为核心业务，主要经营产品包括球类器材、田径器材、场馆设施及赛事服务。</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>体育</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>体育产业</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="C35" s="2" t="inlineStr"/>
+        <v>2.7</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>顶流赛事“苏超”11日重燃战火，比首届提前一个月，广东、湖北、福建今年新办的联赛，以及山东的“齐鲁超赛”也将在这个月打响。</t>
+        </is>
+      </c>
       <c r="D35" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sz000669</t>
+          <t>sh605299</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>ST金鸿</t>
+          <t>舒华体育</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>5.07</v>
+        <v>23.06</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>4.97</v>
+        <v>10.02</v>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 主营气源开发与输送、长输管网建设与管理、城市燃气经营与销售、车用加气站投资与运营、LNG点供、分布式能源项目开发与建设等。</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr"/>
+          <t>体育|公司主营业务为健身器材和展示架产品的研发、生产和销售，其中健身器材包括室内健身器材、室外路径产品。</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>体育</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr"/>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>三星电子预计其第一季度营利将创历史新高，较去年同期增长逾八倍，营收预计同比增长68%，已与主要客户完成第二季度DRAM价格谈判并签署供货合同，价格较第一季度再上涨约30%。</t>
+        </is>
+      </c>
       <c r="D36" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>sh603687</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大胜达  </t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>16.38</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>14天7板</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>并购重组+算力芯片|大胜达公告称，公司拟通过股权受让及增资方式合计投资5.5亿元取得芯瞳半导体技术（厦门）有限公司22.9831%的股权。其中，以2786万元受让2.7074%股权，以2214万元受让1.5961%股权，并以5亿元增资（分两次，第一次2.5亿元，第二次2.5亿元需满足流片成功条件）。同时，控股股东新胜达以5000万元同条件增资，取得1.9608%股权。芯瞳半导体成立于2019年，是国内专注于通用高性能图形处理器芯片设计研发与销售的先驱企业。</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>并购重组, 算力芯片</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>三星电子预计其第一季度营利将创历史新高，较去年同期增长逾八倍，营收预计同比增长68%，已与主要客户完成第二季度DRAM价格谈判并签署供货合同，价格较第一季度再上涨约30%。</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>sh603353</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>和顺石油</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>40.47</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>油气+半导体|1.公司是湖南省第一家获国家商务部批准取得成品油批发资质的民营石油企业，主营成品油批发零售，业务涵盖成品油采购、仓储、物流、批发、零售环节，在成品油流通领域形成完整产业链。
+2.2025年11月16日晚公告，公司拟以现金收购及增资方式取得上海奎芯集成电路设计有限公司不低于34%股权并通过表决权委托合计控制其51%表决权，交易完成后奎芯科技将纳入合并报表，布局高速接口IP及Chiplet解决方案。</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>油气, 半导体</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>三星电子预计其第一季度营利将创历史新高，较去年同期增长逾八倍，营收预计同比增长68%，已与主要客户完成第二季度DRAM价格谈判并签署供货合同，价格较第一季度再上涨约30%。</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>sh601133</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>柏诚股份</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>洁净室系统集成|公司主要专注于为高科技产业的建厂、技改等项目提供专业的洁净室系统集成整体解决方案，覆盖半导体及泛半导体、新型显示、生命科学、食品药品大健康等国家重点产业。</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>洁净室系统集成</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>三星电子预计其第一季度营利将创历史新高，较去年同期增长逾八倍，营收预计同比增长68%，已与主要客户完成第二季度DRAM价格谈判并签署供货合同，价格较第一季度再上涨约30%。</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>sh603421</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>鼎信通讯</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>半导体+智能电网|1.鼎信通讯在互动平台表示，公司芯片开发采用平头哥的CK802 32位内核架构，平头哥与公司签订有全面技术授权协议。
+2.公司的主营业务为低压用电系统产品的研发、生产、销售及服务，主要产品包括低压电力线载波通信模块（含芯片）产品、采集终端设备、智能电能表和配电终端等，主要应用于国家智能电网的用电信息采集系统和配网自动化系统。</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>半导体, 智能电网</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>三星电子预计其第一季度营利将创历史新高，较去年同期增长逾八倍，营收预计同比增长68%，已与主要客户完成第二季度DRAM价格谈判并签署供货合同，价格较第一季度再上涨约30%。</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>sz000062</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>深圳华强</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>27.03</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>存储芯片分销|公司主营业务是电子元器件授权分销，是国内头部芯片设计公司的主要代理商之一。</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>存储芯片分销</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>三星电子预计其第一季度营利将创历史新高，较去年同期增长逾八倍，营收预计同比增长68%，已与主要客户完成第二季度DRAM价格谈判并签署供货合同，价格较第一季度再上涨约30%。</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>sz002119</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>康强电子</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>21.11</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>半导体封装|公司是一家专业从事各类半导体封装材料引线框架、键合丝等半导体封装材料的开发、生产、销售的高新技术企业，主要产品引线框架和键合丝国内市场规模处于领先地位，产品覆盖国内知名的半导体后封装企业。</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>半导体封装</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>英科医疗、蓝帆医疗、中红医疗等日前先后公告，因为中东问题导致原油价格飙升，化工成本大涨，一次性手套价格将面临大幅上涨。</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>sh600488</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>津药药业</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>7天7板</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>医药|津药药业发布股票交易风险提示性公告称，公司关注到市场将公司列为创新药概念，公司目前研发以仿制药为主，无在研创新药项目。公司主营业务为甾体激素类、氨基酸类原料药及制剂的研发、生产和销售。</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>英科医疗、蓝帆医疗、中红医疗等日前先后公告，因为中东问题导致原油价格飙升，化工成本大涨，一次性手套价格将面临大幅上涨。</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>sz002873</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>新天药业</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>中药创新药|公司目前主要从事现代中药创新药的研发、生产和销售，主要优势产品有和颜®坤泰胶囊、坤立舒®苦参凝胶、宁泌泰®宁泌泰胶囊、即瑞®夏枯草口服液等，产品主要应用于妇科类和泌尿系统疾病，同时覆盖清热类、补血类、口腔类、抗感冒类等领域疾病。</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>中药创新药</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>英科医疗、蓝帆医疗、中红医疗等日前先后公告，因为中东问题导致原油价格飙升，化工成本大涨，一次性手套价格将面临大幅上涨。</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>sz000919</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>金陵药业</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>医药|公司主要产品有：脉络宁注射液（主要用于血栓闭塞性脉管炎、动脉硬化性闭塞症、脑血栓形成及后遗症、多发性大动脉炎、四肢急性动脉栓塞症、糖尿病坏疽、静脉血栓形成及血栓性静脉炎等的治疗）、琥珀酸亚铁片（速力菲，主要用于缺铁性贫血的预防及治疗）、香菇多糖注射液（主要用于恶性肿瘤的辅助治疗）等。</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>英科医疗、蓝帆医疗、中红医疗等日前先后公告，因为中东问题导致原油价格飙升，化工成本大涨，一次性手套价格将面临大幅上涨。</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>sz002788</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>鹭燕医药</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>医药+福建|公司从事医药分销和零售，隶属于医药流通行业，系福建省最大的医药流通企业。</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>医药, 福建</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>英科医疗、蓝帆医疗、中红医疗等日前先后公告，因为中东问题导致原油价格飙升，化工成本大涨，一次性手套价格将面临大幅上涨。</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>sz000766</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>通化金马</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">创新药|公司主导研发的治疗轻、中度阿尔茨海默病的1.1类新药琥珀八氢氨吖啶片临床III期试验,目前处于相关临床试验稽查和纠偏阶段,同时为统计及揭盲会议做好筹开工作。
+</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>创新药</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>英科医疗、蓝帆医疗、中红医疗等日前先后公告，因为中东问题导致原油价格飙升，化工成本大涨，一次性手套价格将面临大幅上涨。</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>sh600664</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>哈药股份</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>医药|公司主要从事医药研发与制造、批发与零售业务，是集医药研发、制造、销售于一体的国内大型高新技术医药企业。</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>有机硅</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>东岳硅材公告，预计第一季度净利润同比增长397.02%～451.34%。公司表示自2025年12月份以来，有机硅行业主要产品价格上涨并回归合理区间。</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>sz300821</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>东岳硅材</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>业绩+有机硅|东岳硅材公告称，预计2026年第一季度归属于上市公司股东的净利润为1.83亿元-2.03亿元，比上年同期增长397.02%-451.34%。自2025年12月份以来，受市场环境及行业供需格局改善影响，有机硅行业主要产品价格上涨并回归合理区间，公司产品毛利率显著提升。</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>业绩, 有机硅</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>有机硅</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>东岳硅材公告，预计第一季度净利润同比增长397.02%～451.34%。公司表示自2025年12月份以来，有机硅行业主要产品价格上涨并回归合理区间。</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>sh600596</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>新安股份</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>有机硅|公司是我国第二大有机硅单体生产企业，围绕有机硅单体合成，完善从硅矿冶炼、硅粉加工、单体合成、下游制品加工的完整产业链，形成硅橡胶、硅油、硅树脂、硅烷偶联剂四大系列产品。公司有机硅单体总体规模提升至49万吨，折DMC产能约25万吨。</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>有机硅</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>有机硅</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>东岳硅材公告，预计第一季度净利润同比增长397.02%～451.34%。公司表示自2025年12月份以来，有机硅行业主要产品价格上涨并回归合理区间。</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>sh603260</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>合盛硅业</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>43.02</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>有机硅|公司是我国目前最大的工业硅生产企业，主要从事工业硅及有机硅等硅基新材料产品的研发、生产及销售，是我国硅基新材料行业中业务链最完整、生产规模最大的企业之一。</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>有机硅</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>有机硅</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>东岳硅材公告，预计第一季度净利润同比增长397.02%～451.34%。公司表示自2025年12月份以来，有机硅行业主要产品价格上涨并回归合理区间。</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>sz002132</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>恒星科技</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>有机硅|公司旗下子公司恒星化学投资21.07亿元建设“年产12万吨高性能有机硅聚合物项目”，一期投资18亿元，建设年产20万吨单体（10万吨环体）。</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>有机硅</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>有机硅</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>东岳硅材公告，预计第一季度净利润同比增长397.02%～451.34%。公司表示自2025年12月份以来，有机硅行业主要产品价格上涨并回归合理区间。</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>sz000830</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>鲁西化工</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>9.969999999999999</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>化肥+有机硅|1.公司主营业务为化工、化工新材料及化肥产品的生产销售。主要产品涵盖聚碳酸酯、己内酰胺、甲酸、尼龙6、多元醇、甲烷氯化物、氯化石蜡、氯化苄、有机硅、尿素、复合肥等百余种，产品应用领域广泛。
+2.2022年6月29日公告，拟投资建设100万吨/年有机硅项目一期工程40万吨/年有机硅项目。</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>化肥, 有机硅</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>4月3日，CCL龙头建滔积层板发函，板料及pp半固化片价格统一上调10%，主因是上游树脂、电子玻纤布等核心原材料“价格暴涨且供应紧张”。</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>sh603002</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>宏昌电子</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>PCB+半导体材料|1.公司主要从事电子级环氧树脂、覆铜板两大类产品的生产和销售，覆铜板主营产品为多层板用环氧玻璃布覆铜板、多层板用环氧玻璃布半固化片。
+2.2023年6月26日公告，全资子公司珠海宏昌与晶化科技签订《合作框架协议书》及《技术开发（委托）合同》，在先进封装过程中集成电路载板之增层膜新材料,或特定产品开展密切的研发及销售合作关系，该增层膜新材料产品应用于半导体FCBGA(倒装芯片球栅格数组)及FCCSP(倒装芯片级封装)先进封装制程使用之载板中。</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>PCB, 半导体材料</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>4月3日，CCL龙头建滔积层板发函，板料及pp半固化片价格统一上调10%，主因是上游树脂、电子玻纤布等核心原材料“价格暴涨且供应紧张”。</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>sz301630</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>同宇新材</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>211.92</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>PCB+光刻胶|1.公司主营业务系电子树脂的研发、生产和销售，主要应用于覆铜板生产。
+2.2025年12月17日公司在互动平台表示，公司在募投项目：江西同宇新材料有限公司年产20万吨电子树脂项目（一期）中包含可用于光刻胶油墨的邻甲酚醛环氧树脂（CNE），设计产能为10000吨。</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>PCB, 光刻胶</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>4月3日，CCL龙头建滔积层板发函，板料及pp半固化片价格统一上调10%，主因是上游树脂、电子玻纤布等核心原材料“价格暴涨且供应紧张”。</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>sz301373</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>凌玮科技</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>82.86</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>PCB+半导体材料|1.公司的主营业务是纳米二氧化硅新材料的研发、生产、销售，涂层助剂及其他材料的销售。
+2.公司产品已进入精密基材抛光液等新的应用领域。抛光液可用于半导体芯片的CMP抛光以及电子产品精密部件的抛光。</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>PCB, 半导体材料</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>4月3日，CCL龙头建滔积层板发函，板料及pp半固化片价格统一上调10%，主因是上游树脂、电子玻纤布等核心原材料“价格暴涨且供应紧张”。</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>sh600110</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>诺德股份</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>锂电铜箔+PCB|1.公司主要从事锂离子电池用电解铜箔的研发、生产和销售，产品主要应用于动力锂电池生产制造，是国内主要知名锂离子电池厂商的供应商。
+2.公司紧跟AI算力设备对高频材料的需求升级，新一代HVLP铜箔产品已通过部分客户认证，可满足高速覆铜板（CCL）对低损耗、高稳定性的要求。</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>锂电铜箔, PCB</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>光纤光缆</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>截至2026年4月6日，由AI数据中心建设与地缘需求驱动的全球光纤市场涨价潮进一步确认，最新数据显示中国市场G652.D光纤价格自去年低点涨超400%。</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>sz000720</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>新能泰山</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>10天8板</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>电线电缆+光纤光缆|子公司曲阜电缆主要从事电线电缆、光纤光缆、电力光缆等产品的研发、制造与销售，曲阜电缆生产、 销售的电线电缆产品是公司重点发展的智慧供应链业务产品之一。</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>电线电缆, 光纤光缆</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>光纤光缆</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>截至2026年4月6日，由AI数据中心建设与地缘需求驱动的全球光纤市场涨价潮进一步确认，最新数据显示中国市场G652.D光纤价格自去年低点涨超400%。</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>sz000586</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>汇源通信</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>20.76</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>光缆光纤|公司是国内最早的全系列光缆供应商之一，光缆光纤业务主要生产、销售普通光缆、特种光缆、气吹微缆等，以及提供工程解决方案服务。公司旗下全资子公司汇源光通信是国内电力光缆的制造商、气吹微缆的供应商，同时也是高压输电线路在线检测产品的供应商。</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>光缆光纤</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>光纤光缆</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>截至2026年4月6日，由AI数据中心建设与地缘需求驱动的全球光纤市场涨价潮进一步确认，最新数据显示中国市场G652.D光纤价格自去年低点涨超400%。</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>sh603042</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>华脉科技</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>22.81</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>铜缆+光缆光纤|1.公司数据中心业务主要包括低压配电、铜缆综合布线、光综合布线、机柜及微模块及基础设施等业务。
+2.公司是一家信息通信网络基础设施解决方案提供商，主要产品包括光纤、光缆、光器件及光配线设施全场景有线传输链路解决方案及系列产品。</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>铜缆, 光缆光纤</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>光纤光缆</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>截至2026年4月6日，由AI数据中心建设与地缘需求驱动的全球光纤市场涨价潮进一步确认，最新数据显示中国市场G652.D光纤价格自去年低点涨超400%。</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>sz002491</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>通鼎互联</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>光纤光缆|公司光电通信业务板块的产品和解决方案主要涵盖光电线缆和光通信设备两大领域，光电线缆领域的具体产品包括光纤预制棒、光纤、光缆、通信电缆、铁路信号缆、电力电缆等。</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>光纤光缆</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>储能</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>记者近日多方采访获悉，当前国内储能电芯产能已全面进入供不应求状态，已有头部企业储能电芯订单排期至2027年一季度末。</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>sz000695</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>滨海能源</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>9.969999999999999</v>
+      </c>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>锂电负极+储能|1.公司全面聚焦锂电负极材料业务，自建及协同控股股东石墨化产能已形成一定规模优势，于2023年7月底实现4万吨后端成品线投料试生产，并于11月底实现1.8万吨自有石墨化产品线投产调试。
+2.公司生产的负极材料可广泛应用于储能项目。</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>锂电负极, 储能</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>储能</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>记者近日多方采访获悉，当前国内储能电芯产能已全面进入供不应求状态，已有头部企业储能电芯订单排期至2027年一季度末。</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>sh688345</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">博力威  </t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>储能电池|公司储能电池主要用于家庭、旅途及户外活动应急供电，装有逆变器，具备将直流电转换为交流电的功能，具有临时备用等特点。</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>储能电池</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>储能</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>记者近日多方采访获悉，当前国内储能电芯产能已全面进入供不应求状态，已有头部企业储能电芯订单排期至2027年一季度末。</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>sh603988</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>中电电机</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>27.02</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>风光电储|2025年12月22日公告，董事会同意公司以自有资金或自筹资金6000万元在内蒙古投资设立全资子公司，开展风光电储新能源、金属矿产资源业务，并授权公司经营管理层负责具体办理与本次对外投资有关的一切事项，包括但不限于签署相关协议、办理成立新设公司的相关事项、申报相关审批手续、组织实施等。</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>风光电储</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>光通信</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>0.9900000000000001</v>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>台积电表示，旗下硅光整合平台COUPE预计今年进入量产，成为推动共封装光学（CPO）落地的关键里程碑，标志着AI光通信正式进入产业化倒数阶段。</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>sz002980</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>华盛昌</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>6天3板</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>并购重组+光通信|华盛昌公告称，公司拟以现金方式收购深圳市伽蓝特科技有限公司100%股权，整体估值暂定为4.6亿元。伽蓝特专注于仪器仪表测试测量行业中的光通信模块和光芯片测试领域。</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>并购重组, 光通信</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>光通信</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>0.9900000000000001</v>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>台积电表示，旗下硅光整合平台COUPE预计今年进入量产，成为推动共封装光学（CPO）落地的关键里程碑，标志着AI光通信正式进入产业化倒数阶段。</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>sz002025</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>航天电器</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>66.72</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>光通信|公司生产的光通信器件（光有源器件）包括各种激光器、探测器、光收发一体化组件和模块等系列产品，广泛应用于光通信、数据中心、视频安防监控、智能电网、物联网、医疗传感等众多领域。公司江苏奥雷新基建用光模块产业化项目的厂房基建工程已封顶，预计完工时间为2024年12月底，项目达产后，预计年产153万只光模块。</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>光通信</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>光通信</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>0.9900000000000001</v>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>台积电表示，旗下硅光整合平台COUPE预计今年进入量产，成为推动共封装光学（CPO）落地的关键里程碑，标志着AI光通信正式进入产业化倒数阶段。</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>sz002957</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>科瑞技术</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>33.68</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>光通信模组设备|公司已为国内外大客户批量交付光通信模组生产设备。</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>光通信模组设备</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>猪肉产业</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>国家发改委、商务部、财政部于4月1日宣布开展2026年第二批中央冻猪肉储备收储工作，并要求各地同步实施。</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>sz002840</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>华统股份</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>12.94</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>猪肉产业|公司主营业务为生猪养殖、生猪屠宰、肉制品深加工三大主要板块，此外还配套拥有饲料加工、家禽养殖及屠宰等业务。</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>猪肉产业</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>猪肉产业</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>国家发改委、商务部、财政部于4月1日宣布开展2026年第二批中央冻猪肉储备收储工作，并要求各地同步实施。</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>sh600195</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>中牧股份</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>猪用疫苗|公司是兽用疫苗生产企业中产品品种较全、生产能力和产量较大的企业，主要包括高致病性禽流感疫苗、口蹄疫类疫苗、鸡马立克系列产品、ST猪瘟疫苗、猪圆环病毒灭活疫苗、猪伪狂犬病活疫苗、牛结节性皮肤病灭活疫苗、狂犬病灭活疫苗、犬四联疫苗、猫三联灭活疫苗及其他各类常规兽用疫苗产品和诊断制剂。</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>猪用疫苗</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>钠电池</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>4月6日，中国科学院物理研究所胡勇胜团队在《自然·能源》发表重磅成果：该团队成功开发出一种具有自保护功能的可聚合不燃电解质（PNE），全球首次在安时级钠离子电池中实现彻底阻断热失控。</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>sh605589</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>圣泉集团</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>35.67</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>钠电池+光刻胶|1.公司已建成万吨级钠电硬碳负极材料产线。
+2.公司产品包括光刻胶用电子级酚醛树脂</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>钠电池, 光刻胶</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>钠电池</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>4月6日，中国科学院物理研究所胡勇胜团队在《自然·能源》发表重磅成果：该团队成功开发出一种具有自保护功能的可聚合不燃电解质（PNE），全球首次在安时级钠离子电池中实现彻底阻断热失控。</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>sz002348</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>高乐股份</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>9.969999999999999</v>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>钠电池|子公司高乐新能源与重庆尼古拉科技产业研究院有限公司于2024年1月28日签订了《纳米固态钠离子电池成套技术开发研究项目技术研发合作协议书》, 高乐新能源委托尼古拉研究院研究开发“纳米固态钠离子电池成套技术开发研究项目”，尼古拉研究院接受委托并进行此项研究开发工作。</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>钠电池</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>折叠屏</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>据中证金牛座，记者4月6日从产业链人士处获悉，富士康已在试产苹果折叠屏iPhone手机。</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>sh603327</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>福蓉科技</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>折叠屏|公司生产的铝制结构件材料已经应用于三星、谷歌等品牌折叠屏手机铰链上。</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>折叠屏</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>折叠屏</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>据中证金牛座，记者4月6日从产业链人士处获悉，富士康已在试产苹果折叠屏iPhone手机。</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>sz002631</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>德尔未来</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>锂电池+折叠屏|1.公司参股公司益舟新能源是一家专业从事锂离子电池功能材料的应用开发研究和产业化工作，为锂离子电池性能提升提供技术解决方案的高科技企业，目前主要生产销售高安全性功能隔膜及其关联材料、用于高功率密度电池的功能涂层电池箔及其关联浆料等。
+2.19年2月19日互动平台称，石墨烯透明导电薄膜可以作为柔性触控用于柔性屏手机，这方面公司控股子公司烯成石墨烯有相关技术和专利布局，柔性触控的技术2013年已经突破，并推出了相关样品。</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>锂电池, 折叠屏</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>瑞银财富管理投资总监办公室(CIO)发表机构观点，认为在政策支持、结构性需求增长和海外扩张的推动下，中国电力和资源板块有望步入多年增长周期。</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>sh605162</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新中港  </t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>5天4板</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>热电联产|公司采用热电联产的方式进行热力产品和电力产品的生产及供应。公司的热力业务主要面向工业用户供应所生产的蒸汽，主要满足工业园区内的造纸、印染、医药、化工、食品等150余家工业企业的热需求。公司生产的电力直接销售给国家电网公司。公司是嵊州市地区唯一一家集中供热的热电联产企业，具有150多家下游客户，区域优势和先发优势明显。</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>热电联产</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>瑞银财富管理投资总监办公室(CIO)发表机构观点，认为在政策支持、结构性需求增长和海外扩张的推动下，中国电力和资源板块有望步入多年增长周期。</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>sz002310</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>东方新能</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>并购重组+绿电|2025年12月15日公告，公司拟以现金支付方式购买海城锐海100%股权和电投瑞享80%股权。其中，海城锐海100%股权拟通过在天津产权交易中心摘牌方式购买。标的资产的审计和评估工作尚未完成，评估值及交易价格均尚未确定（海城锐海100%股权在天津产权交易所的挂牌转让底价为1410万元）。本次交易预计构成重大资产重组。通过本次交易，东方园林新增光伏电站、风电场的投资、开发、建设和运营等新能源业务。</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>并购重组, 绿电</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>跨境支付</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>跨境银行间支付清算有限责任公司的网站数据显示，人民币跨境支付系统日均交易额达9205亿元，创过去12个月以来最高，并且在4月2日，单日交易额进一步升至1.22万亿元。</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>sh603123</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>翠微股份</t>
         </is>
       </c>
-      <c r="G36" s="2" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="H36" s="2" t="n">
+      <c r="G75" s="2" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="H75" s="2" t="n">
         <v>10.03</v>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
         <is>
           <t>数字货币+跨境支付|1.全资子公司海科融通已积极参与央行数字货币研究所指定运营银行签署合作协议，进行系统对接，推进数字人民币受理的系统建设。
 2.子公司海科融通在国际业务方面聚焦卡组织合作，构建卡组交易生态，外卡收单业务落地，微信海外钱包上线，助力推广境内交易网络与人民币卡使用，并积极探索海外业务。</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="K75" s="2" t="inlineStr">
         <is>
           <t>数字货币, 跨境支付</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C76" s="2" t="inlineStr"/>
+      <c r="D76" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>sz002528</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>ST英飞拓</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>10天5板</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 英飞拓推出5G多功能智慧灯杆，支持节能照明、视频监控、新能源充电、公共WIFI、环境监测、信息发布、应急报警、5G微基站等模块，实现多种类型的感知数据采集、分析、仿真预测，提升城市综合治理。</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C77" s="2" t="inlineStr"/>
+      <c r="D77" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>sz002713</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>*ST东易</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>6天3板</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司基于数字化系统优势和业务场景优势，研发推出了行业内首个新一代AIGC技术和真家系统结合的全新设计工具“真家 AIGC”，同时打造出AI 创意大师、AI小白设计家两款智能应用设计工具。</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C78" s="2" t="inlineStr"/>
+      <c r="D78" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>sh603822</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST嘉澳  </t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 全资子公司东江能源专业从事餐厨垃圾、废油脂无害化、减量化、资源化处理和新能源开发，是目前国内规模较大的废弃油脂资源综合利用企业。</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C79" s="2" t="inlineStr"/>
+      <c r="D79" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>sh603813</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*ST原尚 </t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>22.81</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司参股公司广东原锋新能源科技的股东之一锋源是国内极少的集全套自主知识产权氢燃料电池电堆以及核心零部件膜电极、催化剂、金属双极板等研发、生产、销售一体的公司。</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C80" s="2" t="inlineStr"/>
+      <c r="D80" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>sz000909</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>*ST数源</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司旗下东软股份运营的东部软件园是科技部火炬中心认定的国家级科技企业孵化器，是浙江省首家企业化运作的科技园区。</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C81" s="2" t="inlineStr"/>
+      <c r="D81" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>sh603838</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*ST四通 </t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司是一家集研发、设计、生产、销售于一体的新型家居生活陶瓷供应商，产品覆盖日用陶瓷、卫生陶瓷、艺术陶瓷、建筑装饰等全系列家居生活用瓷。</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C82" s="2" t="inlineStr"/>
+      <c r="D82" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>sz002789</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>*ST建艺</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司是集施工、设计、资源矿产、科技工业园、高新技术建材产业、投融资为一体的规模化实体企业集团。</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C83" s="2" t="inlineStr"/>
+      <c r="D83" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>sz002650</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>ST加加</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 主营业务涉及酱油、植物油、食醋、味精、鸡精、蚝油等的生产及销售。</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr"/>
-      <c r="D37" s="2" t="n">
+      <c r="C84" s="2" t="inlineStr"/>
+      <c r="D84" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>sh603778</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>国晟科技</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>6天3板</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>光伏+锂电池|1.公司目前从事大尺寸高效异质结光伏电池的研发、生产、销售，以及异质结、TOPCON、PERC等电池组件的生产与销售。控股孙公司恒立聚能涉及钙钛矿研究。
+2.国晟科技公告称，公司拟以2.406亿元的价格受让正豪科技、林琴合计持有的孚悦科技100%股权。交易完成后，公司将持有标的公司100%股权，标的公司将纳入公司合并报表。孚悦科技主要从事高精密度新型锂电池结构件的研发、生产和销售。</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>光伏, 锂电池</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr"/>
+      <c r="D85" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>sh600654</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中安科  </t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>sh600106</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>重庆路桥</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>基建|公司是一家集城市路桥经营、城市基础设施建设、投资及房地产综合开发为一体的股份制企业。</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>基建</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="H85" s="2" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>算力租赁|2024年7月25日公告，公司及全资子公司灵算智云（武汉）投资有限公司拟与宜兴兴阳产业投资有限公司签署投资合作协议，共建宜兴人工智能算力中心项目。本次合作项目计划总投资为3.75亿元。</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>算力租赁</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>sz002831</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>裕同科技</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>35.29</v>
-      </c>
-      <c r="H38" s="2" t="n">
+      <c r="C86" s="2" t="inlineStr"/>
+      <c r="D86" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>sz002051</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>中工国际</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>9.969999999999999</v>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>一带一路+基建|公司是经中华人民共和国商务部批准，由国内著名的外贸公司、设计院、机械制造商和施工单位共同发起设立的股份有限公司。主营业务是国际工程总承包</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>一带一路, 基建</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr"/>
+      <c r="D87" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>sh603637</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>镇海股份</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>股份转让|镇海股份公告称，公司控股股东舜通集团及实际控制人余姚市国资中心拟通过公开征集受让方的方式协议转让公司部分股份。舜通集团拟转让其持有的35,802,881股股份，占公司总股本的15%。转让完成后，舜通集团及其一致行动人舜建集团合计持股比例降至6.22%，该事项可能导致公司控股股东及实际控制人发生变更。</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>股份转让</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr"/>
+      <c r="D88" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>sz000890</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>法尔胜</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>17.61</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>主营不涉及光纤|1.法尔胜公告称，公司澄清主营业务不涉及“光纤”、“特种光纤”，不存在“重组”或“被借壳”情形，控股股东下属子公司与上市公司无股权关系及业务往来。
+2.公司主营业务为金属制品及环保业务。</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>主营不涉及光纤</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr"/>
+      <c r="D89" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>sz000652</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>泰达股份</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>9.950000000000001</v>
+      </c>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>转让泰达能源股权|泰达股份公告称，公司拟向泰达供应链转让其持有的泰达能源51%股权（对应出资额12,850万元）。本次交易完成后，上市公司不再持有泰达能源股权。交易价格1.87亿元。本次交易构成重大资产重组。</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>转让泰达能源股权</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr"/>
+      <c r="D90" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>sz002193</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>如意集团</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>纺织|毛纺行业龙头。海外并购不断，收购标的的业务范围涵盖上游原材料、纺织制造、品牌服饰，标的运营的国家包括日本、澳大利亚、韩国、印度、英国、澳大利亚、新西兰、德国和法国等。</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>纺织</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr"/>
+      <c r="D91" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>sz000019</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>深粮控股</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>9.959999999999999</v>
+      </c>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>农业种植|老牌国企，专注于茶产业,已建立从茶叶种植、茶叶初制/精制、茶提取、精品茶销售、茶文化体验、电子商务、茶叶交易服务平台、茶叶金融等较为完善的茶产业链体系。</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>农业种植</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr"/>
+      <c r="D92" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>sh603090</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>宏盛股份</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>63.83</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>锂电池+液冷IDC|1.公司锂电池PACK产品应用于工业储能、动力储能以及家用储能市场。
+2.公司掌握液冷散热技术，能够为多种场景提供解决方案，同时，公司与苏州和信精密科技股份有限公司合资成立了无锡和宏智散热科技有限公司，和信精密是行业内领先的数据中心设备供应商，双方通过设立合资公司的形式，拓展数据中心环境温度控制业务。</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>锂电池, 液冷IDC</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr"/>
+      <c r="D93" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>sz002663</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>普邦股份</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>9.950000000000001</v>
+      </c>
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>园林景观|公司的园林景观业务包括住宅景观、度假景观以及市政景观业务。子公司深蓝环保是国内污水处理、一般工业固废处理处置等领域最具综合实力的环保企业之一。</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>园林景观</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr"/>
+      <c r="D94" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>sh601388</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>怡球资源</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>再生铝|公司的主营业务是利用所回收的来源于废旧汽车、建材、电器、机械、包装、设备等及生产过程中产生的铝渣、边角料等各方面的废铝资源，进行分选、熔炼、浇注等生产工序，制造出替代原铝的再生铝产品。</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>再生铝</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr"/>
+      <c r="D95" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>sz300165</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>天瑞仪器</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>19.96</v>
+      </c>
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>摘帽|ST天瑞公告称，公司股票将于3月27日停牌一天，3月30日开市起复牌并撤销其他风险警示，证券简称由“ST天瑞”变更为“天瑞仪器”，证券代码不变，仍为300165，日涨跌幅限制仍为20%。</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>摘帽</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr"/>
+      <c r="D96" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>sz002037</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>保利联合</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>9.969999999999999</v>
+      </c>
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>民爆|公司已形成贵州、河南、甘肃、西藏、山东、河北、新疆等全国布局的生产基地，可为用户提供品种齐全、规格配套的工业炸药、工业雷管、工业导爆索（管）以及根据用户特殊需求订制的个性化民爆产品，产品广泛应用于矿山开采、水利水电、基础设施建设、城市改造及国防建设等领域。</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>民爆</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr"/>
+      <c r="D97" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>sh600250</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>南京商旅</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>旅游+零售|1.公司旅游业务主要在子公司秦淮风光开展，秦淮风光主要业务为向游客提供内秦淮河水域的水上游船观光游览服务，船票收入为主要收入来源。
+2.公司零售业务的核心企业是控股子公司南京南商商业运营管理有限责任公司，南商运营主要从事单店百货零售业务，拥有南京商厦20年经营权。南京商厦是南京城北地区主要商业综合体之一，是集购物、餐饮、娱乐于一体的现代化、多功能、综合性大型百货商场，在所处区域占有较高的市场地位。</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>旅游, 零售</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr"/>
+      <c r="D98" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>sh600743</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>华远控股</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>房地产|2025年4月，公司完成了重大资产重组，已将持有的房地产开发业务相关资产及负债转让至公司控股股东华远集团，实现了从重资产开发商向轻资产服务商的价值重构。</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>房地产</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr"/>
+      <c r="D99" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>sh600259</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>中稀有色</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>86.95999999999999</v>
+      </c>
+      <c r="H99" s="2" t="n">
         <v>10.01</v>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>并购重组|裕同科技公告称，公司拟通过自有或自筹资金向观点投资收购其持有的华研科技51%股份，交易金额为4.49亿元。本次交易构成关联交易，公司实际控制人王华君、吴兰兰夫妇合计持有观点投资100%股权。交易完成后，华研科技将成为公司的控股子公司，并纳入公司合并报表范围。东莞市华研新材料科技有限公司成立于2016年，致力于为客户提供一站式精密金属及陶瓷零组件整体解决方案，一体化设计、研发、制造、组装整体解决方案的专精特新国家级“小巨人”高新技术企业。</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>并购重组</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>稀土+钨|广东省稀土龙头，在粤北地区控股及参股5个钨矿山。</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>稀土, 钨</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr"/>
-      <c r="D39" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>sz002952</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>亚世光电</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>25.18</v>
-      </c>
-      <c r="H39" s="2" t="n">
+      <c r="C100" s="2" t="inlineStr"/>
+      <c r="D100" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>sh603348</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>文灿股份</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>21.47</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>汽车|公司已批量为特斯拉（TESLA）供应铝合金车身结构件，2017年特斯拉是公司的第五大客户。</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>汽车</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr"/>
+      <c r="D101" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>sh600791</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>京能置业</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>11.79</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>房地产|公司主营房地产开发与经营，拥有十余年的房地产开发经验，拥有一套较为完善的房地产开发和管理模式。</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>房地产</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr"/>
+      <c r="D102" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>sh605018</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>长华集团</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="H102" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>光电显示模组|公司下设全资子公司亚世光电(鞍山)有限公司。公司属于国内液晶领域领先企业，拥有2条国际领先水平的液晶显示屏生产线和8条光电显示模组生产线。</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>光电显示模组</t>
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>机器人|在轻量化方面，公司生产工艺采用级进模快速生产、3D视觉自动识别上料、全自动压铆及在线检测、机器人自动堆垛。</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
         </is>
       </c>
     </row>
@@ -2273,7 +5096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2300,7 +5123,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -2315,7 +5138,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
@@ -2330,7 +5153,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -2349,12 +5172,57 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sz000950</t>
+          <t>sz002980</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>重药控股</t>
+          <t>华盛昌</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>sh600654</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中安科  </t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>sh605589</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>圣泉集团</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>sh603123</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>翠微股份</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,19 +476,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:K136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="93" customWidth="1" min="3" max="3"/>
+    <col width="111" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="234" customWidth="1" min="10" max="10"/>
+    <col width="282" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -552,532 +552,531 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>3.75</v>
+        <v>6.329999999999999</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
+          <t>根据OpenRouter数据，过去一年周度消耗Token数量从2.1T上升至24.5T，2026年以来周度Token消耗增加280%。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>sz002408</t>
+          <t>sh600126</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>齐翔腾达</t>
+          <t>杭钢股份</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>6.62</v>
+        <v>9.31</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>9.969999999999999</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>10.05</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>石油化工|公司目前已形成碳四丁烯组分综合利用产品线、异丁烯组分综合利用产品线和丁烷组分综合利用产品线三条产品线。</t>
+          <t>算力租赁|公司与浙江天猫合作建设浙江云计算数据中心项目，由浙江天猫承租数据中心机柜资源。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>石油化工</t>
+          <t>算力租赁</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>3.75</v>
+        <v>6.329999999999999</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
+          <t>根据OpenRouter数据，过去一年周度消耗Token数量从2.1T上升至24.5T，2026年以来周度Token消耗增加280%。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sz002442</t>
+          <t>sh600666</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>龙星科技</t>
+          <t xml:space="preserve">奥瑞德  </t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>6.02</v>
+        <v>6.5</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>10.05</v>
+        <v>9.98</v>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>化工+锂电|公司主要业务为炭黑、白炭黑及煤焦油制品的生产和销售。公司主要产品包括PVDF。</t>
+          <t>算力租赁|公司设立全资子公司北京智算力、深圳智算力，使用自有资金投资建设算力租赁一、二、三期项目。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>化工, 锂电</t>
+          <t>算力租赁</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3.75</v>
+        <v>6.329999999999999</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
+          <t>根据OpenRouter数据，过去一年周度消耗Token数量从2.1T上升至24.5T，2026年以来周度Token消耗增加280%。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sh600527</t>
+          <t>sz300209</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>江南高纤</t>
+          <t>行云科技</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>2.5</v>
+        <v>11.69</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>10.13</v>
+        <v>20.02</v>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>化纤|国内涤纶毛条和复合纤维的龙头公司。公司产品主要包括涤纶毛条和复合短纤维。下游主要供给纸尿裤、卫生巾等一次性卫生材料。</t>
+          <t>算力租赁|2026年3月30日公告，公司拟出资1020万元与蔚莱投资（深圳）有限公司等主体共同设立合资公司行云存算（深圳）科技有限公司，公司持股34%，该合资公司将纳入行云科技合并报表范围。行云存算将专注于数字化研发与AI解决方案，秉持AI技术驱动创新理念，依托国产及全球优势GPU算力资源，搭配自研高速企业级SSD，为各行业企业搭建专属智算中心。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>化纤</t>
+          <t>算力租赁</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>3.75</v>
+        <v>6.329999999999999</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
+          <t>根据OpenRouter数据，过去一年周度消耗Token数量从2.1T上升至24.5T，2026年以来周度Token消耗增加280%。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sz000703</t>
+          <t>sz002042</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>恒逸石化</t>
+          <t>华孚时尚</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>14.16</v>
+        <v>4.53</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>10.02</v>
+        <v>9.950000000000001</v>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>石油化工|公司已发展成为全球领先的炼化、化纤的产业链一体化企业之一，主要产品包括汽油、柴油、煤油等成品油；对二甲苯（PX）、苯、精对苯二甲酸（PTA）、己内酰胺（CPL）等石化产品；涤纶预取向丝（POY）、涤纶牵伸丝（FDY）、涤纶加弹丝（DTY）以及涤纶短纤、聚酯（PET）切片、聚酯瓶片等产品。</t>
+          <t>算力租赁|2024年1月2日公告，公司全资子公司浙江华孚计划投资“上虞华尚数智中心AIGC智算中心项目”，项目规划建设规模3000PFLOPS AI算力。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>石油化工</t>
+          <t>算力租赁</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>3.75</v>
+        <v>6.329999999999999</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
+          <t>根据OpenRouter数据，过去一年周度消耗Token数量从2.1T上升至24.5T，2026年以来周度Token消耗增加280%。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sz002427</t>
+          <t>sh600186</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>尤夫股份</t>
+          <t>莲花控股</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>6.23</v>
+        <v>7.63</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>10.07</v>
+        <v>9.94</v>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>化纤|公司开发的拒海水聚酯工业丝产品已广泛应用于船舶、海洋钻井、深海风电系泊缆绳，产品通过DNV、ABS船级社测试认证。</t>
+          <t>味精+算力租赁|1.拥有全国性营销网络的味精企业，主要业务为生产销售味精、鸡精、面粉、谷朊粉等。
+2.2023年9月，新华三集团与公司举行战略合作签约仪式，携手莲花健康共建国内领先、国际一流的智能算力中心，满足通用大模型、自动驾驶、机器人、元宇宙、游戏、传媒等应用行业在内的算力需求。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>化纤</t>
+          <t>味精, 算力租赁</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>3.75</v>
+        <v>6.329999999999999</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
+          <t>根据OpenRouter数据，过去一年周度消耗Token数量从2.1T上升至24.5T，2026年以来周度Token消耗增加280%。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sh600370</t>
+          <t>sh600589</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">三房巷  </t>
+          <t>大位科技</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>2.52</v>
+        <v>10.87</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>10.04</v>
+        <v>10.02</v>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>PTA|公司成为“PTA-瓶级聚酯切片”一体化布局的优势企业，PTA产品是郑州商品交易所PTA交割免检品牌，已开发出多种全系列的瓶级聚酯切片产品。</t>
+          <t>算力租赁|公司聚焦主业完成由数据中心、云计算中心向算力中心的业务转型，张北算力中心项目位于国家八大算力枢纽之一的张家口算力集群。公司将在算力基础设施建设运营的基础上，向客户提供垂直算力服务，并基于国家八大算力枢纽建设主算力节点，结合边缘算力开展云网一体化垂直算力服务。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>PTA</t>
+          <t>算力租赁</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>3.75</v>
+        <v>6.329999999999999</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
+          <t>根据OpenRouter数据，过去一年周度消耗Token数量从2.1T上升至24.5T，2026年以来周度Token消耗增加280%。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sz000990</t>
+          <t>sz000889</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>诚志股份</t>
+          <t>中嘉博创</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>10.24</v>
+        <v>3.59</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>9.99</v>
+        <v>10.12</v>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>化工|2022年8月，公司拟通过全资子公司青岛华青投资建设POE（聚烯烃弹性体）项目和超高分子量聚乙烯项目。公司在南京生产基地拥有两套烯烃生产工厂，乙烯、丙烯、丁二烯总产能接近100万吨/年。</t>
+          <t>算力租赁|公司于2021年4月28日在互动平台表示，公司2020年正式开展离岸运算服务，并计划从2021年二季度开始从算力运营服务向算力设备采购进一步延伸拓展，直接提供算力输出。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>算力租赁</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>3.75</v>
+        <v>6.329999999999999</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
+          <t>根据OpenRouter数据，过去一年周度消耗Token数量从2.1T上升至24.5T，2026年以来周度Token消耗增加280%。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sh600810</t>
+          <t>sh603315</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>神马股份</t>
+          <t>福鞍股份</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>8.99</v>
+        <v>14.53</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>10.04</v>
+        <v>9.99</v>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>化纤|公司产业结构上横跨化工、化纤两大行业，通过实施一体化战略，形成了以尼龙66盐和尼龙66盐中间产品、尼龙66切片、工业丝、帘子布、尼龙6切片等主导产品为支柱、以原辅材料及相关产品为依托的新产业格局。</t>
+          <t xml:space="preserve">算力租赁|2024年5月13日公告，公司拟与上海集铁网络科技有限公司共同以现金出资的方式，设立合资公司，共同开拓AI算力租赁服务业务。公司拟持有合资公司71%的股权，集铁网络拟持有合资公司29%的股权，合资公司拟对AI算力租赁服务业务预计投入资金约3.5亿元人民币，按照出资比例计算，公司拟对外投资约2.485亿元人民币。
+</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>化纤</t>
+          <t>算力租赁</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>3.75</v>
+        <v>6.329999999999999</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
+          <t>根据OpenRouter数据，过去一年周度消耗Token数量从2.1T上升至24.5T，2026年以来周度Token消耗增加280%。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sz002109</t>
+          <t>sh600986</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>兴化股份</t>
+          <t>浙文互联</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>4.46</v>
+        <v>10.1</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>10.12</v>
+        <v>10.02</v>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>煤化工|全资子公司兴化化工主营煤制甲醇，产能30万吨/年。</t>
+          <t>AI应用+算力租赁|1.据浙文互联官微1月20日消息，公司AI程序化广告工具“派智”数字人2025年累计消耗量已突破2.5亿元，同比实现5倍增长。
+2.2024年12月25日公告，公司拟参投国资股东浙江省文投集团旗下浙江自贸区海城融资租赁有限公司，强化算力运营服务布局，形成从资金支持到服务保障产业链闭环，提升公司在算力服务领域的市场竞争力。此前，浙文互联已与GPU算力云服务提供商蓝耘科技合资成立浙文蓝耘智算科技有限公司，深化在算力运营、技术服务及综合解决方案等合作。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>煤化工</t>
+          <t>AI应用, 算力租赁</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>3.75</v>
+        <v>6.329999999999999</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
+          <t>根据OpenRouter数据，过去一年周度消耗Token数量从2.1T上升至24.5T，2026年以来周度Token消耗增加280%。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sh600722</t>
+          <t>sz300571</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>金牛化工</t>
+          <t>平治信息</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>14.52</v>
+        <v>36.61</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>10</v>
+        <v>19.99</v>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>甲醇|公司的主要业务为甲醇的生产和销售，产品方式为焦炉气制甲醇。公司的主要业务由持股50%的控股子公司金牛旭阳经营，金牛旭阳拥有的甲醇生产能力为20万吨/年。</t>
+          <t>光模块+算力租赁|1.参股25%的武汉飞沃科技主要产品包括光模块、无源波分以及半有源波分产品等，为通信运营商提供5G/4G前传、城域网、数据中心等光器件解决方案，是国内通信运营商主要的5G前传产品和光模块产品供应商之一。
+2.2024年5月26日公告，公司于近期收到浙江算力科技有限公司算力服务采购项目《成交通知书》，平治信息成为浙江算力科技有限公司算力服务采购项目成交供应商。该项目将搭建千卡算力集群，以供大模型训练所需的智能算力服务，同时支持后续平滑扩容到万卡集群，该项目将对公司发展算力业务产生积极的影响。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>甲醇</t>
+          <t>光模块, 算力租赁</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>3.75</v>
+        <v>6.329999999999999</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
+          <t>根据OpenRouter数据，过去一年周度消耗Token数量从2.1T上升至24.5T，2026年以来周度Token消耗增加280%。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sh600955</t>
+          <t>sz002217</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>维远股份</t>
+          <t>合力泰</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>18.1</v>
+        <v>2.46</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>10.03</v>
+        <v>9.82</v>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>化工+锂电池|1.公司主营业务为“苯酚、丙酮—双酚A—聚碳酸酯”产业链有机化学新材料产品的研发、生产与销售，是目前国内唯一具备完整聚碳酸酯产业链的公司。
-2.2022年2月28日公告，公司与日本宇部兴产株式会社签署了《2万吨/年高纯碳酸二甲酯技术许可协议》，宇部将其拥有的通过碳酸二甲酯生产高纯碳酸二甲酯的技术许可给公司生产HPDMC；HPDMC主要应用于锂电池电解液。</t>
+          <t>算力租赁|公司与重整投资人杭州骋风而来共设合资公司智泰驰骋，致力于开发算力底座、算力平台运营及算力应用服务等业务。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>化工, 锂电池</t>
+          <t>算力租赁</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>3.75</v>
+        <v>6.329999999999999</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
+          <t>根据OpenRouter数据，过去一年周度消耗Token数量从2.1T上升至24.5T，2026年以来周度Token消耗增加280%。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sz003042</t>
+          <t>sh603629</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>中农联合</t>
+          <t>利通电子</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>18.26</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>10</v>
@@ -1085,134 +1084,134 @@
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>农药|公司实控人为中华全国供销合作总社。公司是专业从事农药中间体、原药及制剂产品的研发、生产和销售的全产业链农药生产企业。</t>
+          <t>算力租赁|公司AI算力业务主要是以云交付方式为客户提供AI算力产品，具体业务形态包括AI设备经销、算力优化、并机集群、算力云输出与持续运维支持与技术服务。公司2025年中报披露，可调度的算力资源用于客户算力云服务的规模逾29000P。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>农药</t>
+          <t>算力租赁</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>3.75</v>
+        <v>6.329999999999999</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
+          <t>根据OpenRouter数据，过去一年周度消耗Token数量从2.1T上升至24.5T，2026年以来周度Token消耗增加280%。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sh600691</t>
+          <t>sh603881</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>潞化科技</t>
+          <t xml:space="preserve">数据港  </t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>3.34</v>
+        <v>39.25</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>9.869999999999999</v>
+        <v>10.01</v>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>煤化工|公司主要业务包括化工产品和化工机械设备的生产和销售，化工产品研发及工程总承包设计等，主要产品包括尿素、聚氯乙烯、烯烃、烧碱、双氧水、甲醇等。</t>
+          <t>算力租赁|公司作为国内第三方数据中心服务商的代表性企业，长期为阿里云提供数据中心基础设施服务，为阿里云的业务运行提供物理支撑和算力支持。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>煤化工</t>
+          <t>算力租赁</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>3.75</v>
+        <v>6.329999999999999</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
+          <t>根据OpenRouter数据，过去一年周度消耗Token数量从2.1T上升至24.5T，2026年以来周度Token消耗增加280%。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sh600227</t>
+          <t>sz002929</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">赤天化  </t>
+          <t>润建股份</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>3.82</v>
+        <v>52.16</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>10.09</v>
+        <v>10</v>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>氮肥|公司是贵州省最大的氮肥生产企业，公司化肥化工生产基地分别是以天然气为原料生产的赤水化工分公司（年产63万吨尿素）和以煤为生产原料的公司全资子公司桐梓化工（年产52万吨尿素、30万吨甲醇）。</t>
+          <t>阿里+算力|公司在原有IDC服务业务全链条布局基础上，进一步深化算力服务，为算力中心及IDC提供全生命周期一站式服务，以提高算力中心及IDC运行效率为核心指标，提供全栈式的算力运维服务，包括咨询设计、建设、运维、节能改造、优化、运营以及算力调优、调度等服务，已经形成以基础电信运营商为核心客户，以云厂商、政企机构为主要客户的市场格局。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>氮肥</t>
+          <t>阿里, 算力</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>3.75</v>
+        <v>6.329999999999999</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
+          <t>根据OpenRouter数据，过去一年周度消耗Token数量从2.1T上升至24.5T，2026年以来周度Token消耗增加280%。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sh603968</t>
+          <t>sh605289</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>醋化股份</t>
+          <t>罗曼股份</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>14.19</v>
+        <v>109.41</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>10</v>
@@ -1220,1096 +1219,1090 @@
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>化工|公司主要从事以醋酸衍生物、吡啶衍生物为主体的高端专用精细化学品的研发、生产和销售。</t>
+          <t>算力+AI应用|1.旗下Holovis是全球交互技术研发先行者，自主研发虚拟现实、无感交互等领域二十多项国际专有技术，将生成式AI大数据分析平台 Deep Smarts、基于AI视觉追踪的智能交互系统 HoloTrac 等核心技术融入个性化智能体验和运营，为行业发展注入强大创新引擎。
+2.参股上海武桐树高新技术有限公司主要从事AIDC算力服务器与集群综合解决方案服务业务。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>算力, AI应用</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>3.75</v>
+        <v>6.329999999999999</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
+          <t>根据OpenRouter数据，过去一年周度消耗Token数量从2.1T上升至24.5T，2026年以来周度Token消耗增加280%。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sz002470</t>
+          <t>sz002484</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>金正大</t>
+          <t>江海股份</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>3</v>
+        <v>30.97</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>9.890000000000001</v>
+        <v>10.02</v>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>化肥|公司的复合肥、缓控释肥、硝基复合肥、水溶肥及其他新型肥料在技术和市场占有率方面居国内领先地位，具有较强的竞争优势。</t>
+          <t xml:space="preserve">服务器材料|2024年11月19日公告，公司近日在第二十九届慕尼黑电子展上推出基于高性能N型导电聚合物的MLPC新产品。该产品采用原位聚合与氧化还原掺杂相结合的一步法合成技术，具备超高电导率、高稳定性和高温耐久性等优点。MLPC广泛应用于服务器中高功耗芯片的供电滤波场景，特别是CPU和GPU的核心电压供电，进一步提升了服务器的可靠性。
+</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>化肥</t>
+          <t>服务器材料</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>3.75</v>
+        <v>5.43</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
+          <t>长江证券指出，近期AI资本化加速，AI产业共识再发酵。随着AI应用商业化加速，参考美国AI演绎，资本开支领先于商业化一年左右，AI应用也即将在26年迎来商业化拐点。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sh600423</t>
+          <t>sz002181</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>柳化股份</t>
+          <t>粤 传 媒</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>3.61</v>
+        <v>12.99</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>10.06</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
+        <v>9.99</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>化工+半导体材料|1.公司主要从事27.5%双氧水的生产和销售，年设计产能为10万吨。公司采用蒽醌钯催化剂工艺，以外购氢气为主要原料生产双氧水。
-2.公司生产的电子级双氧水(G1/G2级30%-32%浓度)主要用于半导体硅晶片清洗剂，电镀液无机杂质去除，电子行业中铜、铜合金和镓、锗的处理，以及太阳能硅晶片的蚀刻和清洗等方面。</t>
+          <t>AI应用+体育|1.公司在视频制作中应用AI技术，在美术插画、创意视效和智能剪辑等方面提升制作效率和品质，以更好地满足市场和用户需求。
+2.公司先锋报业经营《足球》报刊及足球+APP、劲球网、足球报微信公众号等新媒体矩阵。</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>化工, 半导体材料</t>
+          <t>AI应用, 体育</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>3.75</v>
+        <v>5.43</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
+          <t>长江证券指出，近期AI资本化加速，AI产业共识再发酵。随着AI应用商业化加速，参考美国AI演绎，资本开支领先于商业化一年左右，AI应用也即将在26年迎来商业化拐点。</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sh603255</t>
+          <t>sz002421</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">鼎际得  </t>
+          <t>达实智能</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>29.4</v>
+        <v>2.73</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>9.99</v>
+        <v>10.08</v>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>化工+光伏|1.公司是国内少数同时具备高分子材料高效能催化剂和化学助剂产品的专业提供商，形成了聚烯烃高效能催化剂和化学助剂的研发、生产和销售为一体的业务体系。
-2.公司聚烯陉催化剂产品对应的是下游产业烯陉聚合技术的核心产品POE粒子，N型电池的推广可以增加POE用量。</t>
+          <t>AI医疗|公司智慧医疗事业部孵化的达实旗云是国内领先的健康医疗大数据服务企业，通过应用AI、大数据引擎等技术，拥有文本+影像的全量大数据能力。</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>化工, 光伏</t>
+          <t>AI医疗</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>3.75</v>
+        <v>5.43</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
+          <t>长江证券指出，近期AI资本化加速，AI产业共识再发酵。随着AI应用商业化加速，参考美国AI演绎，资本开支领先于商业化一年左右，AI应用也即将在26年迎来商业化拐点。</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sh600470</t>
+          <t>sz000727</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>六国化工</t>
+          <t>冠捷科技</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>7.05</v>
+        <v>2.82</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>9.98</v>
+        <v>10.16</v>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>化肥|公司是华东地区磷复肥和磷化工一体化专业制造的大型企业，主营业务为化肥(含氮肥、磷肥、钾肥)、肥料（含复合肥料、复混肥料、有机肥料及微生物肥料）、化学制品（含精制磷酸、磷酸盐）、化学原料的生产加工和销售。</t>
+          <t>AI应用|冠捷科技11月10日在投资者互动平台表示，公司旗下AOC推出的AI新品包括AIGC拍照机、AI数字人售货终端、AI数字人、AI字幕音响屏等，但目前业务在整体业务中占比较小，请注意投资风险。</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>化肥</t>
+          <t>AI应用</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>3.75</v>
+        <v>5.43</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
+          <t>长江证券指出，近期AI资本化加速，AI产业共识再发酵。随着AI应用商业化加速，参考美国AI演绎，资本开支领先于商业化一年左右，AI应用也即将在26年迎来商业化拐点。</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>sz300927</t>
+          <t>sz002131</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>江天化学</t>
+          <t>利欧股份</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>30.49</v>
+        <v>7.95</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>19.99</v>
+        <v>9.959999999999999</v>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>化工|公司专注于以甲醇下游深加工为产业链的高端专用精细化学品的研发、生产和销售，主要产品包括颗粒多聚甲醛、高浓度甲醛、超高纯氯甲烷及1,3,5-三丙烯酰基六氢-均三嗪等。</t>
+          <t>AI智能体+液冷|1.公司以利欧数字全链条业务场景为基础，实现从策略制定、创意生产到用户运营等全环节智能化升级，打造营销各环节专属智能体，包括策略智能体、创意智能体、投放智能体、运营智能体等。
+2.公司在数据中心布局了全场景智慧冷却方案，涉及一次侧和二次侧的高效液冷用泵和健康检测系统，已对接国内主流液冷系统方案供应商。</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>AI智能体, 液冷</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>3.75</v>
+        <v>5.43</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
+          <t>长江证券指出，近期AI资本化加速，AI产业共识再发酵。随着AI应用商业化加速，参考美国AI演绎，资本开支领先于商业化一年左右，AI应用也即将在26年迎来商业化拐点。</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>sz000912</t>
+          <t>sh605287</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>泸天化</t>
+          <t>德才股份</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>5.27</v>
+        <v>42.53</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>10.02</v>
+        <v>10.01</v>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>化肥|公司的主营业务包括尿素、复合肥等化肥类产品，液氨、甲醇、二甲醚、稀硝酸系列、浓硝酸、液体硝酸铵以及四氧化二氮等化工类产品。</t>
+          <t>AI漫剧|旗下奇想无限深耕“网文IP+AI漫剧”转化，与头部网文平台合作，将玄幻、甜宠等成熟IP快速落地，已产出多部爆款。</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>化肥</t>
+          <t>AI漫剧</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>3.75</v>
+        <v>5.43</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
+          <t>长江证券指出，近期AI资本化加速，AI产业共识再发酵。随着AI应用商业化加速，参考美国AI演绎，资本开支领先于商业化一年左右，AI应用也即将在26年迎来商业化拐点。</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>sz002637</t>
+          <t>sz002995</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>赞宇科技</t>
+          <t>天地在线</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>12.28</v>
+        <v>24.76</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>10.04</v>
+        <v>10</v>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>油脂化工|公司油脂化工业务主要由杭州油化、南通凯塔和杜库达三家控股子公司负责生产经营。油脂化工业务主要以棕榈油为原料，主要产品包括硬脂酸、脂肪酸、油酸、脂肪醇、脂肪胺、二聚酸、聚酰胺树脂、甘油及其他助剂等油脂化工产品。</t>
+          <t>AI应用|公司已推出AI数字人SAAS产品“星河AI数字人系统”以及帮助企业提高工作效率和协作能力的AI智能应用产品“AIbase” ，满足客户在营销及提升企业经营效能的不同需求。</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>油脂化工</t>
+          <t>AI应用</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>3.75</v>
+        <v>5.43</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
+          <t>长江证券指出，近期AI资本化加速，AI产业共识再发酵。随着AI应用商业化加速，参考美国AI演绎，资本开支领先于商业化一年左右，AI应用也即将在26年迎来商业化拐点。</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>sh603188</t>
+          <t>920171.BJ</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>亚邦股份</t>
+          <t>志晟信息</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>5.13</v>
+        <v>21.09</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>10.09</v>
+        <v>29.94</v>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>染料|公司主要从事染料及染料中间体的销售与服务，是国内蒽醌结构染料生产专家工厂。</t>
+          <t>AI应用|2025年2月初，公司为邯郸下属县域金融服务平台迭代搭载AI信贷顾问，可提供“7×24”小时多轮对话解读金融政策的智能问答服务，为中小企业提供贷款对接、融资担保、政策咨询等提供 “一站式”、“保姆式”高效服务。</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>染料</t>
+          <t>AI应用</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>3.75</v>
+        <v>5.43</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
+          <t>长江证券指出，近期AI资本化加速，AI产业共识再发酵。随着AI应用商业化加速，参考美国AI演绎，资本开支领先于商业化一年左右，AI应用也即将在26年迎来商业化拐点。</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>sh600623</t>
+          <t>sz300058</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>华谊集团</t>
+          <t>蓝色光标</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>9.779999999999999</v>
+        <v>16.31</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>10.01</v>
+        <v>20.01</v>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>化工|公司主要从事能源化工、绿色轮胎、先进材料、精细化工和化工服务五大核心业务，主要产品包括甲醇、醋酸及酯，工业气体，丙烯及下游产品，涂料及树脂，轮胎等。</t>
+          <t>AI智能体|公司宣布与火山引擎达成深度合作，双方将基于火山方舟、豆包·视频生成模型、扣子专业版智能体开发平台，在视频生成、视频服务解决方案以及营销行业智能体应用等领域展开深入合作，共同推动AI与营销体系的深度整合、加速营销行业AI化进程。</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>AI智能体</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>3.75</v>
+        <v>5.43</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
+          <t>长江证券指出，近期AI资本化加速，AI产业共识再发酵。随着AI应用商业化加速，参考美国AI演绎，资本开支领先于商业化一年左右，AI应用也即将在26年迎来商业化拐点。</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>sz002274</t>
+          <t>sz000892</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>华昌化工</t>
+          <t>欢瑞世纪</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>6.5</v>
+        <v>6.68</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>9.98</v>
+        <v>10.05</v>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>煤化工|公司是一家以煤气化为产业链源头的综合性的化工企业，产业链总体分为三个部分：一是煤制合成气（主要成分COH2），生产合成氨、尿素、纯碱、氯化铵、硝酸等；二是使用煤化工生产的产品生产新型肥料；三是以合成气与丙烯为原料，实现无机化工与石油化工相结合研发、生产新型材料，后续产品为醇类、增塑剂、树脂、涂料等。另外，随着氢燃料电池技术及产业的发展，氢气将作为能源进行利用。</t>
+          <t>AI应用|公司与上海阶跃星辰智能科技有限公司已达成战略合作，双方共建“麟跃”AI联合实验室，合作方向为短剧Agent产品，双方将合力打造短剧Agent产品，深化探索AI技术在相关影视应用、短剧管理与投流产品等方向的应用。</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>煤化工</t>
+          <t>AI应用</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>3.75</v>
+        <v>5.43</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
+          <t>长江证券指出，近期AI资本化加速，AI产业共识再发酵。随着AI应用商业化加速，参考美国AI演绎，资本开支领先于商业化一年左右，AI应用也即将在26年迎来商业化拐点。</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>sz002092</t>
+          <t>sh603598</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>中泰化学</t>
+          <t>引力传媒</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>6.95</v>
+        <v>21.25</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>9.969999999999999</v>
+        <v>9.99</v>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>化工|公司拥有完整的煤炭—热电—氯碱化工—粘胶纤维—粘胶纱上下游一体化的循环经济产业链，主营聚氯乙烯树脂（PVC）、离子膜烧碱、粘胶纤维、粘胶纱等四大产品。公司本部现有150万吨PVC产能。</t>
+          <t>AI智能体+短剧|1.公司已推出自有营销电商行业模型并推出三大智能体（Agent）-感知智能体、决策智能体、内容智能体，用以增强营销决策、创意素材、视频混剪等环节内容产出的精准性与稳定性。
+2.公司依托全链路整合能力，均衡发力于平台精品短剧、达人定制剧、小程序剧等多个细分领域。</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>AI智能体, 短剧</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>3.75</v>
+        <v>5.43</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
+          <t>长江证券指出，近期AI资本化加速，AI产业共识再发酵。随着AI应用商业化加速，参考美国AI演绎，资本开支领先于商业化一年左右，AI应用也即将在26年迎来商业化拐点。</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>sh600075</t>
+          <t>sh603138</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>新疆天业</t>
+          <t>海量数据</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>6.8</v>
+        <v>19.91</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>10.03</v>
+        <v>10</v>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>化工|公司通过资产重组、收购氯碱化工资产，已具备较为完整的“自备电力→电石→聚氯乙烯树脂及副产品→电石渣及其他废弃物制水泥”一体化产业联动式绿色环保型循环经济产业链，具有89万吨PVC产能（包括69万吨通用PVC、10万吨特种树脂、10万吨糊树脂）、65万吨离子膜烧碱产能、134万吨电石产能，同时拥有2×300MW、2×330MW自备热电站以及405万吨电石渣制水泥装置。</t>
+          <t>AI大数据|公司发布的企业级大数据应用平台提供AI驱动的增强分析功能，如时序预测分析、关联分析、根因分析等，助力数据驱动决策。</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>AI大数据</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>3.75</v>
+        <v>5.43</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>中东地缘紧张局势的影响，正从能源领域向化工与高端制造产业链逐步扩散。3月份全球多家化工企业接连宣布涨价计划。</t>
+          <t>长江证券指出，近期AI资本化加速，AI产业共识再发酵。随着AI应用商业化加速，参考美国AI演绎，资本开支领先于商业化一年左右，AI应用也即将在26年迎来商业化拐点。</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>sh600063</t>
+          <t>sh605318</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>皖维高新</t>
+          <t xml:space="preserve">法狮龙  </t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>7.19</v>
+        <v>84.7</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>9.94</v>
+        <v>10</v>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>化纤|公司主要从事聚乙烯醇（PVA）、高强高模PVA纤维、PVB树脂、PVA光学薄膜、可再分散性乳胶粉、醋酸乙烯、VAE乳液、酒精、聚酯切片、醋酸甲酯、电石渣制水泥熟料及环保水泥，以及其他PVA相关的衍生产品、中间产品和副产品等的研发、生产与销售。</t>
+          <t>AI应用|旗下北宸星穹（北京）科技经营范围包括：人工智能应用软件开发；人工智能行业应用系统集成服务；人工智能基础软件开发；人工智能公共服务平台技术咨询服务等。</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>化纤</t>
+          <t>AI应用</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>体育产业</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>2.7</v>
+        <v>5.43</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>顶流赛事“苏超”11日重燃战火，比首届提前一个月，广东、湖北、福建今年新办的联赛，以及山东的“齐鲁超赛”也将在这个月打响。</t>
+          <t>长江证券指出，近期AI资本化加速，AI产业共识再发酵。随着AI应用商业化加速，参考美国AI演绎，资本开支领先于商业化一年左右，AI应用也即将在26年迎来商业化拐点。</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>sz002181</t>
+          <t>sz002400</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>粤 传 媒</t>
+          <t>省广集团</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>11.81</v>
+        <v>8.76</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>9.959999999999999</v>
+        <v>10.05</v>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>AI应用+体育|1.公司在视频制作中应用AI技术，在美术插画、创意视效和智能剪辑等方面提升制作效率和品质，以更好地满足市场和用户需求。
-2.公司先锋报业经营《足球》报刊及足球+APP、劲球网、足球报微信公众号等新媒体矩阵。</t>
+          <t>AI应用|公司掌握国内外各主流的综合媒体平台，以及创新媒体的优质资源，洞察品牌合作最佳契合点，打造包括GIMC 云、灵犀AI 在内的数智产品矩阵，以大数据为依托精准触达目标消费者，为各品类客户提供包括数字营销策略、数字媒介购买执行、数字媒介创新合作、品牌互动策划与创意执行、互动类技术支持以及 SEO/SEM 营销在内的整合数字营销服务。</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>AI应用, 体育</t>
+          <t>AI应用</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>体育产业</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>2.7</v>
+        <v>4.88</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>顶流赛事“苏超”11日重燃战火，比首届提前一个月，广东、湖北、福建今年新办的联赛，以及山东的“齐鲁超赛”也将在这个月打响。</t>
+          <t>现货黄金站上4850美元/盎司，日内涨3.19%。此外中国央行公布数据显示，中国3月末黄金储备报7438万盎司，环比增加16万盎司，为连续第17个月增持黄金。</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>sz002431</t>
+          <t>sh601069</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>棕榈股份</t>
+          <t>西部黄金</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>2.77</v>
+        <v>33.2</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>9.92</v>
+        <v>10.01</v>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>基建+体育|参股成立的棕榈体育产业有限公司、参股英超西布罗姆维奇俱乐部。推进’生态城镇+体育’战略。</t>
+          <t>黄金+业绩|西部黄金公告称，预计2026年第一季度实现归属于上市公司股东的净利润4.5亿元-5.6亿元，与上年同期（法定披露数据）相比，同比增加1161.38%-1469.71%；与上年同期（追溯调整后）相比，同比增加1797.16%-2260.91%。业绩预增主要原因为黄金产品销量较上年同期增加、销售价格较上年同期上升以及电解锰的销售价格较上年同期上升。</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>基建, 体育</t>
+          <t>黄金, 业绩</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>体育产业</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>2.7</v>
+        <v>4.88</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>顶流赛事“苏超”11日重燃战火，比首届提前一个月，广东、湖北、福建今年新办的联赛，以及山东的“齐鲁超赛”也将在这个月打响。</t>
+          <t>现货黄金站上4850美元/盎司，日内涨3.19%。此外中国央行公布数据显示，中国3月末黄金储备报7438万盎司，环比增加16万盎司，为连续第17个月增持黄金。</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>sh600158</t>
+          <t>sz000426</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>中体产业</t>
+          <t>兴业银锡</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>11.87</v>
+        <v>43.56</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>体育|公司作为国家体育总局唯一一家A股上市公司，在赛事活动、体育传播、教育培训、体育彩票、体育空间平台、体育认证等业务领域已初步完成全国性布局。</t>
+          <t>银锡+锑|公司的主营业务为有色金属及贵金属采选与冶炼，主要矿产品保有金属储量包括锑金属24.44万吨，同时具有年采选锑金属1000吨的生产能力。</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>体育</t>
+          <t>银锡, 锑</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>体育产业</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>2.7</v>
+        <v>4.88</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>顶流赛事“苏超”11日重燃战火，比首届提前一个月，广东、湖北、福建今年新办的联赛，以及山东的“齐鲁超赛”也将在这个月打响。</t>
+          <t>现货黄金站上4850美元/盎司，日内涨3.19%。此外中国央行公布数据显示，中国3月末黄金储备报7438万盎司，环比增加16万盎司，为连续第17个月增持黄金。</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>sh605099</t>
+          <t>sz000506</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>共创草坪</t>
+          <t>招金黄金</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>41.15</v>
+        <v>18.71</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>体育|公司是全球生产和销售规模最大的人造草坪企业，FIFA（国际足联）8家全球人造草坪优选供应商之一，WorldRugby（世界橄榄球运动联盟）8家全球人造草坪优选供应商之一、FIH（国际曲联）11家全球人造草坪优选供应商之一。</t>
+          <t>黄金|公司主要业务包括以黄金为主要品种的矿业开采，子公司斐济瓦图科拉金矿有限公司所拥有的斐济瓦图科拉金矿已有90年的开采历史，已采出黄金240多吨，是全球少有的长寿大型矿山，地质勘探潜力较大。</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>体育</t>
+          <t>黄金</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>体育产业</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>2.7</v>
+        <v>4.88</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>顶流赛事“苏超”11日重燃战火，比首届提前一个月，广东、湖北、福建今年新办的联赛，以及山东的“齐鲁超赛”也将在这个月打响。</t>
+          <t>现货黄金站上4850美元/盎司，日内涨3.19%。此外中国央行公布数据显示，中国3月末黄金储备报7438万盎司，环比增加16万盎司，为连续第17个月增持黄金。</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>sz300651</t>
+          <t>sz002716</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>金陵体育</t>
+          <t>湖南白银</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>32.4</v>
+        <v>12.49</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>20</v>
+        <v>10.04</v>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>体育|公司是行业领先的高端体育装备和体育文化设施系统集成服务商，以体育装备、场馆建设、全民健身、赛事保障为核心业务，主要经营产品包括球类器材、田径器材、场馆设施及赛事服务。</t>
+          <t>贵金属+铅锌|1.公司主要产品为白银、电铅、黄金及其他综合回收产品。
+2.旗下西藏俊龙矿业有限公司在拉萨地区拥有优质铅锌矿产资源。</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>体育</t>
+          <t>贵金属, 铅锌</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>体育产业</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>2.7</v>
+        <v>4.88</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>顶流赛事“苏超”11日重燃战火，比首届提前一个月，广东、湖北、福建今年新办的联赛，以及山东的“齐鲁超赛”也将在这个月打响。</t>
+          <t>现货黄金站上4850美元/盎司，日内涨3.19%。此外中国央行公布数据显示，中国3月末黄金储备报7438万盎司，环比增加16万盎司，为连续第17个月增持黄金。</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sh605299</t>
+          <t>sz000962</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>舒华体育</t>
+          <t>东方钽业</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>23.06</v>
+        <v>44.51</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>10.02</v>
+        <v>10.01</v>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>体育|公司主营业务为健身器材和展示架产品的研发、生产和销售，其中健身器材包括室内健身器材、室外路径产品。</t>
+          <t>小金属|公司主要从事稀有金属钽、铌、铍及合金等的研发、生产、销售和进出口业务，已形成钽金属及合金制品、铌金属及合金制品等系列产品。上述产品被广泛应用于电子、通讯、航空、航天、冶金、石油、化工、照明、原子能、太阳能等领域。</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>体育</t>
+          <t>小金属</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>1.45</v>
+        <v>4.88</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>三星电子预计其第一季度营利将创历史新高，较去年同期增长逾八倍，营收预计同比增长68%，已与主要客户完成第二季度DRAM价格谈判并签署供货合同，价格较第一季度再上涨约30%。</t>
+          <t>现货黄金站上4850美元/盎司，日内涨3.19%。此外中国央行公布数据显示，中国3月末黄金储备报7438万盎司，环比增加16万盎司，为连续第17个月增持黄金。</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sh603687</t>
+          <t>sz001337</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">大胜达  </t>
+          <t>四川黄金</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>16.38</v>
+        <v>51.32</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>10.01</v>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>14天7板</t>
-        </is>
-      </c>
+      <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>并购重组+算力芯片|大胜达公告称，公司拟通过股权受让及增资方式合计投资5.5亿元取得芯瞳半导体技术（厦门）有限公司22.9831%的股权。其中，以2786万元受让2.7074%股权，以2214万元受让1.5961%股权，并以5亿元增资（分两次，第一次2.5亿元，第二次2.5亿元需满足流片成功条件）。同时，控股股东新胜达以5000万元同条件增资，取得1.9608%股权。芯瞳半导体成立于2019年，是国内专注于通用高性能图形处理器芯片设计研发与销售的先驱企业。</t>
+          <t xml:space="preserve">黄金|公司是一家长期专注于金矿资源开发及综合利用的企业，主要从事金矿的采选及销售，产品为金精矿和合质金，已成为国内主要的金矿采选企业之一。公司拥有梭罗沟金矿采矿权和梭罗-挖金沟详查金矿探矿权，梭罗沟金矿矿区采矿许可证范围内保有资源储量为金金属量44862kg，梭罗沟金矿区挖金沟矿段查明资源储量为金金属量1332kg。
+</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>并购重组, 算力芯片</t>
+          <t>黄金</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>1.45</v>
+        <v>4.88</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>三星电子预计其第一季度营利将创历史新高，较去年同期增长逾八倍，营收预计同比增长68%，已与主要客户完成第二季度DRAM价格谈判并签署供货合同，价格较第一季度再上涨约30%。</t>
+          <t>现货黄金站上4850美元/盎司，日内涨3.19%。此外中国央行公布数据显示，中国3月末黄金储备报7438万盎司，环比增加16万盎司，为连续第17个月增持黄金。</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sh603353</t>
+          <t>sh603045</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>和顺石油</t>
+          <t>福达合金</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>40.47</v>
+        <v>31.35</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>3天2板</t>
-        </is>
-      </c>
+      <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>油气+半导体|1.公司是湖南省第一家获国家商务部批准取得成品油批发资质的民营石油企业，主营成品油批发零售，业务涵盖成品油采购、仓储、物流、批发、零售环节，在成品油流通领域形成完整产业链。
-2.2025年11月16日晚公告，公司拟以现金收购及增资方式取得上海奎芯集成电路设计有限公司不低于34%股权并通过表决权委托合计控制其51%表决权，交易完成后奎芯科技将纳入合并报表，布局高速接口IP及Chiplet解决方案。</t>
+          <t>电接触材料|公司重点进行电接触材料产品研究开发，公司主导产品电接触材料的主要原材料为白银，所掌握的先进的贵金属提取回收技术和工艺，能实现提取高纯度银锭及铜等贵金属资源的循环利用，已建成了年回收800吨银锭的专用厂房和高标准的“三废”处理环保设施并投入量产。</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>油气, 半导体</t>
+          <t>电接触材料</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>1.45</v>
+        <v>4.88</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>三星电子预计其第一季度营利将创历史新高，较去年同期增长逾八倍，营收预计同比增长68%，已与主要客户完成第二季度DRAM价格谈判并签署供货合同，价格较第一季度再上涨约30%。</t>
+          <t>现货黄金站上4850美元/盎司，日内涨3.19%。此外中国央行公布数据显示，中国3月末黄金储备报7438万盎司，环比增加16万盎司，为连续第17个月增持黄金。</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>sh601133</t>
+          <t>sz002155</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>柏诚股份</t>
+          <t>湖南黄金</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>21.43</v>
+        <v>32.07</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>10.02</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>洁净室系统集成|公司主要专注于为高科技产业的建厂、技改等项目提供专业的洁净室系统集成整体解决方案，覆盖半导体及泛半导体、新型显示、生命科学、食品药品大健康等国家重点产业。</t>
+          <t>锑金属|公司拥有规模化的生产线，拥有3万吨/年精锑冶炼生产线、3.2万吨/年多品种氧化锑生产线。截止2019年末，公司锑金属储量25.75万吨。</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>洁净室系统集成</t>
+          <t>锑金属</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>1.45</v>
+        <v>4.88</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>三星电子预计其第一季度营利将创历史新高，较去年同期增长逾八倍，营收预计同比增长68%，已与主要客户完成第二季度DRAM价格谈判并签署供货合同，价格较第一季度再上涨约30%。</t>
+          <t>现货黄金站上4850美元/盎司，日内涨3.19%。此外中国央行公布数据显示，中国3月末黄金储备报7438万盎司，环比增加16万盎司，为连续第17个月增持黄金。</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>sh603421</t>
+          <t>sh600301</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>鼎信通讯</t>
+          <t>华锡有色</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>8.91</v>
+        <v>52.53</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>半导体+智能电网|1.鼎信通讯在互动平台表示，公司芯片开发采用平头哥的CK802 32位内核架构，平头哥与公司签订有全面技术授权协议。
-2.公司的主营业务为低压用电系统产品的研发、生产、销售及服务，主要产品包括低压电力线载波通信模块（含芯片）产品、采集终端设备、智能电能表和配电终端等，主要应用于国家智能电网的用电信息采集系统和配网自动化系统。</t>
+          <t>有色金属|公司是亚洲最大的锡多金属矿选矿基地、国内唯一的铟锡锑资源综合利用示范基地，拥有的多项关键战略性资源储量位居全球前列，主要金属矿产资源包括锡、锑、铟、锌、铅、银等，是国内主要的锡、锑金属生产企业之一。</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>半导体, 智能电网</t>
+          <t>有色金属</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>有色金属概念</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>1.45</v>
+        <v>4.88</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>三星电子预计其第一季度营利将创历史新高，较去年同期增长逾八倍，营收预计同比增长68%，已与主要客户完成第二季度DRAM价格谈判并签署供货合同，价格较第一季度再上涨约30%。</t>
+          <t>现货黄金站上4850美元/盎司，日内涨3.19%。此外中国央行公布数据显示，中国3月末黄金储备报7438万盎司，环比增加16万盎司，为连续第17个月增持黄金。</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>sz000062</t>
+          <t>sh601137</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>深圳华强</t>
+          <t>博威合金</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>27.03</v>
+        <v>19.56</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>10.01</v>
@@ -2317,44 +2310,44 @@
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>存储芯片分销|公司主营业务是电子元器件授权分销，是国内头部芯片设计公司的主要代理商之一。</t>
+          <t>铜合金|国内铜合金棒材行业龙头之一，铜合金线研发实力和产量居国内前三强。</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>存储芯片分销</t>
+          <t>铜合金</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>1.45</v>
+        <v>6.19</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>三星电子预计其第一季度营利将创历史新高，较去年同期增长逾八倍，营收预计同比增长68%，已与主要客户完成第二季度DRAM价格谈判并签署供货合同，价格较第一季度再上涨约30%。</t>
+          <t>4月3日，CCL龙头建滔积层板发函，板料及pp半固化片价格统一上调10%，主因是上游树脂、电子玻纤布等核心原材料“价格暴涨且供应紧张”。</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>sz002119</t>
+          <t>sh603920</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>康强电子</t>
+          <t>世运电路</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>21.11</v>
+        <v>54.08</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>10.01</v>
@@ -2362,1013 +2355,991 @@
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>半导体封装|公司是一家专业从事各类半导体封装材料引线框架、键合丝等半导体封装材料的开发、生产、销售的高新技术企业，主要产品引线框架和键合丝国内市场规模处于领先地位，产品覆盖国内知名的半导体后封装企业。</t>
+          <t>PCB|公司主营业务为各类印制电路板（PCB）的研发、生产与销售，产品涉及高多层硬板，高精密互连HDI，软板（FPC）、软硬结合板（含HDI）和金属基板四大类。</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>半导体封装</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>0.79</v>
+        <v>6.19</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>英科医疗、蓝帆医疗、中红医疗等日前先后公告，因为中东问题导致原油价格飙升，化工成本大涨，一次性手套价格将面临大幅上涨。</t>
+          <t>4月3日，CCL龙头建滔积层板发函，板料及pp半固化片价格统一上调10%，主因是上游树脂、电子玻纤布等核心原材料“价格暴涨且供应紧张”。</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>sh600488</t>
+          <t>sh603175</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>津药药业</t>
+          <t>超颖电子</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>7.67</v>
+        <v>84.02</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>10.04</v>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>7天7板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>医药|津药药业发布股票交易风险提示性公告称，公司关注到市场将公司列为创新药概念，公司目前研发以仿制药为主，无在研创新药项目。公司主营业务为甾体激素类、氨基酸类原料药及制剂的研发、生产和销售。</t>
+          <t>PCB+存储|1.公司主营业务是印制电路板的研发、生产和销售，拥有HDI板、厚铜板、金属基板、高频板、高速板等特殊材料、特殊工艺产品的生产能力，产品广泛应用于汽车电子、显示、储存、消费电子、通信等领域，并积极布局AR/VR、航天卫星等领域。
+2.在储存领域，公司产品主要应用于机械硬盘、固态硬盘、内存条等，与全球机械硬盘制造商龙头希捷、西部数据及全球知名固态硬盘制造商海力士等建立了稳定合作。</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>PCB, 存储</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>0.79</v>
+        <v>6.19</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>英科医疗、蓝帆医疗、中红医疗等日前先后公告，因为中东问题导致原油价格飙升，化工成本大涨，一次性手套价格将面临大幅上涨。</t>
+          <t>4月3日，CCL龙头建滔积层板发函，板料及pp半固化片价格统一上调10%，主因是上游树脂、电子玻纤布等核心原材料“价格暴涨且供应紧张”。</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>sz002873</t>
+          <t>sz001389</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>新天药业</t>
+          <t>广合科技</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>11.9</v>
+        <v>125.62</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>中药创新药|公司目前主要从事现代中药创新药的研发、生产和销售，主要优势产品有和颜®坤泰胶囊、坤立舒®苦参凝胶、宁泌泰®宁泌泰胶囊、即瑞®夏枯草口服液等，产品主要应用于妇科类和泌尿系统疾病，同时覆盖清热类、补血类、口腔类、抗感冒类等领域疾病。</t>
+          <t>PCB|公司主营业务是印制电路板的研发、生产和销售，公司5G产品广泛应用于通讯基站 、无线射频微波、有线局域网、通讯交换等领域。公司5.5G低轨卫星产品开始批量供货。</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>中药创新药</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>0.79</v>
+        <v>6.19</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>英科医疗、蓝帆医疗、中红医疗等日前先后公告，因为中东问题导致原油价格飙升，化工成本大涨，一次性手套价格将面临大幅上涨。</t>
+          <t>4月3日，CCL龙头建滔积层板发函，板料及pp半固化片价格统一上调10%，主因是上游树脂、电子玻纤布等核心原材料“价格暴涨且供应紧张”。</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>sz000919</t>
+          <t>sh688655</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>金陵药业</t>
+          <t xml:space="preserve">迅捷兴  </t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>8.1</v>
+        <v>29.04</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>10.05</v>
+        <v>20</v>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>医药|公司主要产品有：脉络宁注射液（主要用于血栓闭塞性脉管炎、动脉硬化性闭塞症、脑血栓形成及后遗症、多发性大动脉炎、四肢急性动脉栓塞症、糖尿病坏疽、静脉血栓形成及血栓性静脉炎等的治疗）、琥珀酸亚铁片（速力菲，主要用于缺铁性贫血的预防及治疗）、香菇多糖注射液（主要用于恶性肿瘤的辅助治疗）等。</t>
+          <t>PCB|公司主营业务为印制电路板（PCB）的研发、生产与销售，公司在光模块领域已积累了相关产品经验和客户，目前已可批量接单。</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>0.79</v>
+        <v>6.19</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>英科医疗、蓝帆医疗、中红医疗等日前先后公告，因为中东问题导致原油价格飙升，化工成本大涨，一次性手套价格将面临大幅上涨。</t>
+          <t>4月3日，CCL龙头建滔积层板发函，板料及pp半固化片价格统一上调10%，主因是上游树脂、电子玻纤布等核心原材料“价格暴涨且供应紧张”。</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>sz002788</t>
+          <t>sh605258</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>鹭燕医药</t>
+          <t>协和电子</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>19.44</v>
+        <v>37.26</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>10.02</v>
+        <v>10.01</v>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>医药+福建|公司从事医药分销和零售，隶属于医药流通行业，系福建省最大的医药流通企业。</t>
+          <t>PCB|公司主要从事印制电路板的研发、生产、销售以及SMT业务，PCB产品主要应用在汽车电子和高频通讯领域。</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>医药, 福建</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>0.79</v>
+        <v>6.19</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>英科医疗、蓝帆医疗、中红医疗等日前先后公告，因为中东问题导致原油价格飙升，化工成本大涨，一次性手套价格将面临大幅上涨。</t>
+          <t>4月3日，CCL龙头建滔积层板发函，板料及pp半固化片价格统一上调10%，主因是上游树脂、电子玻纤布等核心原材料“价格暴涨且供应紧张”。</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>sz000766</t>
+          <t>sz002916</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>通化金马</t>
+          <t>深南电路</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>21.02</v>
+        <v>237.51</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">创新药|公司主导研发的治疗轻、中度阿尔茨海默病的1.1类新药琥珀八氢氨吖啶片临床III期试验,目前处于相关临床试验稽查和纠偏阶段,同时为统计及揭盲会议做好筹开工作。
-</t>
+          <t>PCB|公司已成为全球领先的无线基站射频功放PCB供应商、内资最大的封装基板供应商、国内领先的处理器芯片封装基板供应商、电子装联制造的特色企业。</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>0.79</v>
+        <v>6.19</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>英科医疗、蓝帆医疗、中红医疗等日前先后公告，因为中东问题导致原油价格飙升，化工成本大涨，一次性手套价格将面临大幅上涨。</t>
+          <t>4月3日，CCL龙头建滔积层板发函，板料及pp半固化片价格统一上调10%，主因是上游树脂、电子玻纤布等核心原材料“价格暴涨且供应紧张”。</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>sh600664</t>
+          <t>sz002463</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>沪电股份</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>3.87</v>
+        <v>84.06999999999999</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>9.94</v>
+        <v>10</v>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>医药|公司主要从事医药研发与制造、批发与零售业务，是集医药研发、制造、销售于一体的国内大型高新技术医药企业。</t>
+          <t>PCB|公司已成为PCB行业内的重要品牌之一，以通信通讯设备、数据中心基础设施、汽车电子为核心应用领域，主导产品为14-28层企业通讯市场板、中高阶汽车板。</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>有机硅</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>5.38</v>
+        <v>6.19</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>东岳硅材公告，预计第一季度净利润同比增长397.02%～451.34%。公司表示自2025年12月份以来，有机硅行业主要产品价格上涨并回归合理区间。</t>
+          <t>4月3日，CCL龙头建滔积层板发函，板料及pp半固化片价格统一上调10%，主因是上游树脂、电子玻纤布等核心原材料“价格暴涨且供应紧张”。</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>sz300821</t>
+          <t>sz002008</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>东岳硅材</t>
+          <t>大族激光</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>13.39</v>
+        <v>70.8</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>19.98</v>
+        <v>10.01</v>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>业绩+有机硅|东岳硅材公告称，预计2026年第一季度归属于上市公司股东的净利润为1.83亿元-2.03亿元，比上年同期增长397.02%-451.34%。自2025年12月份以来，受市场环境及行业供需格局改善影响，有机硅行业主要产品价格上涨并回归合理区间，公司产品毛利率显著提升。</t>
+          <t>PCB设备|公司构建了覆盖多层板、HDI板、IC封装基板、挠性板及刚挠结合板等不同细分PCB市场及层压、钻孔、曝光、成型、检测等关键工序的立体化产品矩阵，为PCB不同细分领域的客户提供差异化的一站式工序解决方案。</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>业绩, 有机硅</t>
+          <t>PCB设备</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>有机硅</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>5.38</v>
+        <v>6.19</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>东岳硅材公告，预计第一季度净利润同比增长397.02%～451.34%。公司表示自2025年12月份以来，有机硅行业主要产品价格上涨并回归合理区间。</t>
+          <t>4月3日，CCL龙头建滔积层板发函，板料及pp半固化片价格统一上调10%，主因是上游树脂、电子玻纤布等核心原材料“价格暴涨且供应紧张”。</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>sh600596</t>
+          <t>sh603328</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>新安股份</t>
+          <t>依顿电子</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>11.5</v>
+        <v>12.28</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>10.05</v>
+        <v>10.04</v>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>有机硅|公司是我国第二大有机硅单体生产企业，围绕有机硅单体合成，完善从硅矿冶炼、硅粉加工、单体合成、下游制品加工的完整产业链，形成硅橡胶、硅油、硅树脂、硅烷偶联剂四大系列产品。公司有机硅单体总体规模提升至49万吨，折DMC产能约25万吨。</t>
+          <t>PCB|公司专注于高精度、高密度双层及多层印制电路板的研发、生产和销售业务，作为首批进入国际大厂汽车PCB核心供应链的PCB厂商，公司PCB产品供货覆盖传统汽车零部件。</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>有机硅</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>有机硅</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>5.38</v>
+        <v>6.19</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>东岳硅材公告，预计第一季度净利润同比增长397.02%～451.34%。公司表示自2025年12月份以来，有机硅行业主要产品价格上涨并回归合理区间。</t>
+          <t>4月3日，CCL龙头建滔积层板发函，板料及pp半固化片价格统一上调10%，主因是上游树脂、电子玻纤布等核心原材料“价格暴涨且供应紧张”。</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>sh603260</t>
+          <t>sh688630</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>合盛硅业</t>
+          <t>芯碁微装</t>
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>43.02</v>
+        <v>240</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>有机硅|公司是我国目前最大的工业硅生产企业，主要从事工业硅及有机硅等硅基新材料产品的研发、生产及销售，是我国硅基新材料行业中业务链最完整、生产规模最大的企业之一。</t>
+          <t>PCB设备|公司是PCB光刻直写设备国产龙头，提供全制程高速量产型的直接成像设备，最小线宽涵盖8μm-75μm范围，主要应用于PCB制造过程中的线路层及阻焊层曝光环节，是PCB制造中的关键设备之一。</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>有机硅</t>
+          <t>PCB设备</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>有机硅</t>
+          <t>发电机概念</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>5.38</v>
+        <v>6.56</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>东岳硅材公告，预计第一季度净利润同比增长397.02%～451.34%。公司表示自2025年12月份以来，有机硅行业主要产品价格上涨并回归合理区间。</t>
+          <t>全球能源监测组织（GEM）和多家市场研究机构数据显示，2025年全球燃气轮机新增装机60.4GW，市场规模在240亿美元至250亿美元之间。</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>sz002132</t>
+          <t>sz000534</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>恒星科技</t>
+          <t>万泽股份</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>4.07</v>
+        <v>39.33</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>有机硅|公司旗下子公司恒星化学投资21.07亿元建设“年产12万吨高性能有机硅聚合物项目”，一期投资18亿元，建设年产20万吨单体（10万吨环体）。</t>
+          <t>创新药+燃气轮机|1.公司主要产品金双歧和定君生均为独家创新药，受集采降价影响较小。
+2.公司的高温合金产品主要用于航空发动机、燃气轮机（地面与船舶燃机、核电、机车动力等领域）、涡轮增压器等，主要客户即该领域公司。</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>有机硅</t>
+          <t>创新药, 燃气轮机</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>有机硅</t>
+          <t>发电机概念</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>5.38</v>
+        <v>6.56</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>东岳硅材公告，预计第一季度净利润同比增长397.02%～451.34%。公司表示自2025年12月份以来，有机硅行业主要产品价格上涨并回归合理区间。</t>
+          <t>全球能源监测组织（GEM）和多家市场研究机构数据显示，2025年全球燃气轮机新增装机60.4GW，市场规模在240亿美元至250亿美元之间。</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>sz000830</t>
+          <t>sh605060</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>鲁西化工</t>
+          <t>联德股份</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>16.87</v>
+        <v>52.98</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>9.969999999999999</v>
+        <v>10.01</v>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>化肥+有机硅|1.公司主营业务为化工、化工新材料及化肥产品的生产销售。主要产品涵盖聚碳酸酯、己内酰胺、甲酸、尼龙6、多元醇、甲烷氯化物、氯化石蜡、氯化苄、有机硅、尿素、复合肥等百余种，产品应用领域广泛。
-2.2022年6月29日公告，拟投资建设100万吨/年有机硅项目一期工程40万吨/年有机硅项目。</t>
+          <t>燃气轮机|公司已实现内燃机缸体和零部件产品的批量化供应，并开始给客户提供燃气轮机零部件产品，预期在燃气轮机领域将实现批量化供应。</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>化肥, 有机硅</t>
+          <t>燃气轮机</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>发电机概念</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>2.68</v>
+        <v>6.56</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>4月3日，CCL龙头建滔积层板发函，板料及pp半固化片价格统一上调10%，主因是上游树脂、电子玻纤布等核心原材料“价格暴涨且供应紧张”。</t>
+          <t>全球能源监测组织（GEM）和多家市场研究机构数据显示，2025年全球燃气轮机新增装机60.4GW，市场规模在240亿美元至250亿美元之间。</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>sh603002</t>
+          <t>sz002478</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>宏昌电子</t>
+          <t>常宝股份</t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>10.67</v>
+        <v>11.06</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>10</v>
+        <v>10.05</v>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>PCB+半导体材料|1.公司主要从事电子级环氧树脂、覆铜板两大类产品的生产和销售，覆铜板主营产品为多层板用环氧玻璃布覆铜板、多层板用环氧玻璃布半固化片。
-2.2023年6月26日公告，全资子公司珠海宏昌与晶化科技签订《合作框架协议书》及《技术开发（委托）合同》，在先进封装过程中集成电路载板之增层膜新材料,或特定产品开展密切的研发及销售合作关系，该增层膜新材料产品应用于半导体FCBGA(倒装芯片球栅格数组)及FCCSP(倒装芯片级封装)先进封装制程使用之载板中。</t>
+          <t>燃气轮机|HRSG产品为公司特色价值产品，主要应用于燃气轮机余热锅炉发电领域。</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>PCB, 半导体材料</t>
+          <t>燃气轮机</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>发电机概念</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>2.68</v>
+        <v>6.56</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>4月3日，CCL龙头建滔积层板发函，板料及pp半固化片价格统一上调10%，主因是上游树脂、电子玻纤布等核心原材料“价格暴涨且供应紧张”。</t>
+          <t>全球能源监测组织（GEM）和多家市场研究机构数据显示，2025年全球燃气轮机新增装机60.4GW，市场规模在240亿美元至250亿美元之间。</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>sz301630</t>
+          <t>sh600841</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>同宇新材</t>
+          <t>动力新科</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>211.92</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>PCB+光刻胶|1.公司主营业务系电子树脂的研发、生产和销售，主要应用于覆铜板生产。
-2.2025年12月17日公司在互动平台表示，公司在募投项目：江西同宇新材料有限公司年产20万吨电子树脂项目（一期）中包含可用于光刻胶油墨的邻甲酚醛环氧树脂（CNE），设计产能为10000吨。</t>
+          <t>柴油发电机|公司生产制造的柴油发动机主要为国内商用车企业、工程机械企业以及船舶和发电机组等制造企业配套，产品具有大马力、大扭矩、高可靠、低油耗、低排放、低噪声和高性价比等优点，广泛用于商用车、工程机械、农用机械、船舶、移动式电站等领域。</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>PCB, 光刻胶</t>
+          <t>柴油发电机</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>发电机概念</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>2.68</v>
+        <v>6.56</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>4月3日，CCL龙头建滔积层板发函，板料及pp半固化片价格统一上调10%，主因是上游树脂、电子玻纤布等核心原材料“价格暴涨且供应紧张”。</t>
+          <t>全球能源监测组织（GEM）和多家市场研究机构数据显示，2025年全球燃气轮机新增装机60.4GW，市场规模在240亿美元至250亿美元之间。</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>sz301373</t>
+          <t>sz002380</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>凌玮科技</t>
+          <t>科远智慧</t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>82.86</v>
+        <v>33.19</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>20</v>
+        <v>10.01</v>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>PCB+半导体材料|1.公司的主营业务是纳米二氧化硅新材料的研发、生产、销售，涂层助剂及其他材料的销售。
-2.公司产品已进入精密基材抛光液等新的应用领域。抛光液可用于半导体芯片的CMP抛光以及电子产品精密部件的抛光。</t>
+          <t>燃气轮机|公司与中国重燃、东南大学三方联合成立“智能化燃气轮机控制系统协同创新中心”，共同推动国产重型燃气轮机智能控制系统研发、推广和应用，成功交付我国自主重型燃气轮机首套国产化控制系统。</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>PCB, 半导体材料</t>
+          <t>燃气轮机</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>发电机概念</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>2.68</v>
+        <v>6.56</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>4月3日，CCL龙头建滔积层板发函，板料及pp半固化片价格统一上调10%，主因是上游树脂、电子玻纤布等核心原材料“价格暴涨且供应紧张”。</t>
+          <t>全球能源监测组织（GEM）和多家市场研究机构数据显示，2025年全球燃气轮机新增装机60.4GW，市场规模在240亿美元至250亿美元之间。</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>sh600110</t>
+          <t>sz002353</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>诺德股份</t>
+          <t>杰瑞股份</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>9.630000000000001</v>
+        <v>111.83</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>10.06</v>
+        <v>10</v>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>锂电铜箔+PCB|1.公司主要从事锂离子电池用电解铜箔的研发、生产和销售，产品主要应用于动力锂电池生产制造，是国内主要知名锂离子电池厂商的供应商。
-2.公司紧跟AI算力设备对高频材料的需求升级，新一代HVLP铜箔产品已通过部分客户认证，可满足高速覆铜板（CCL）对低损耗、高稳定性的要求。</t>
+          <t>燃气轮机|公司自主研制的燃气轮机发电机组设备能够为客户提供多种稳定、可靠的供电解决方案，目前已在海外成功开展设备销售和发电服务两种业务模式，主要用于石油、天然气开发以及调峰发电、应急发电等领域。</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>锂电铜箔, PCB</t>
+          <t>燃气轮机</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>发电机概念</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>2.09</v>
+        <v>6.56</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>截至2026年4月6日，由AI数据中心建设与地缘需求驱动的全球光纤市场涨价潮进一步确认，最新数据显示中国市场G652.D光纤价格自去年低点涨超400%。</t>
+          <t>全球能源监测组织（GEM）和多家市场研究机构数据显示，2025年全球燃气轮机新增装机60.4GW，市场规模在240亿美元至250亿美元之间。</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>sz000720</t>
+          <t>sh603308</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>新能泰山</t>
+          <t>应流股份</t>
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>6.53</v>
+        <v>67</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>10天8板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>电线电缆+光纤光缆|子公司曲阜电缆主要从事电线电缆、光纤光缆、电力光缆等产品的研发、制造与销售，曲阜电缆生产、 销售的电线电缆产品是公司重点发展的智慧供应链业务产品之一。</t>
+          <t>燃气轮机|公司高温合金产品及精密铸钢件产品主要为使用硅溶胶精铸、消失模精铸、复合模精铸等精密铸造工艺的铸件产品，主要为应用在航空发动机、燃气轮机、核能核电、油气钻采等设备中的精密零部件，包括航空发动机及燃气轮机高温合金部件、核一级导叶、叶轮、油气钻采零部件、水处理泵等。</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>电线电缆, 光纤光缆</t>
+          <t>燃气轮机</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>发电机概念</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>2.09</v>
+        <v>6.56</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>截至2026年4月6日，由AI数据中心建设与地缘需求驱动的全球光纤市场涨价潮进一步确认，最新数据显示中国市场G652.D光纤价格自去年低点涨超400%。</t>
+          <t>全球能源监测组织（GEM）和多家市场研究机构数据显示，2025年全球燃气轮机新增装机60.4GW，市场规模在240亿美元至250亿美元之间。</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>sz000586</t>
+          <t>sh600875</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>汇源通信</t>
+          <t>东方电气</t>
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>20.76</v>
+        <v>38.3</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>9.99</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>光缆光纤|公司是国内最早的全系列光缆供应商之一，光缆光纤业务主要生产、销售普通光缆、特种光缆、气吹微缆等，以及提供工程解决方案服务。公司旗下全资子公司汇源光通信是国内电力光缆的制造商、气吹微缆的供应商，同时也是高压输电线路在线检测产品的供应商。</t>
+          <t>燃气轮机|公司在2025世界清洁能源装备大会上发布了自主研发的首款15兆瓦纯氢燃气轮机。</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>光缆光纤</t>
+          <t>燃气轮机</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>发电机概念</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>2.09</v>
+        <v>6.56</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>截至2026年4月6日，由AI数据中心建设与地缘需求驱动的全球光纤市场涨价潮进一步确认，最新数据显示中国市场G652.D光纤价格自去年低点涨超400%。</t>
+          <t>全球能源监测组织（GEM）和多家市场研究机构数据显示，2025年全球燃气轮机新增装机60.4GW，市场规模在240亿美元至250亿美元之间。</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>sh603042</t>
+          <t>sz301232</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>华脉科技</t>
+          <t>飞沃科技</t>
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>22.81</v>
+        <v>184.74</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>3天2板</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>铜缆+光缆光纤|1.公司数据中心业务主要包括低压配电、铜缆综合布线、光综合布线、机柜及微模块及基础设施等业务。
-2.公司是一家信息通信网络基础设施解决方案提供商，主要产品包括光纤、光缆、光器件及光配线设施全场景有线传输链路解决方案及系列产品。</t>
+          <t>燃气轮机|公司持续积极拓展非风电业务板块，如航空航天、燃气轮机、石油装备等高端零部件领域，降低公司对单一风电行业的依赖度，提升综合竞争力，将非风电业务打造成公司新的业绩增长点。</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>铜缆, 光缆光纤</t>
+          <t>燃气轮机</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>2.09</v>
+        <v>5.53</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>截至2026年4月6日，由AI数据中心建设与地缘需求驱动的全球光纤市场涨价潮进一步确认，最新数据显示中国市场G652.D光纤价格自去年低点涨超400%。</t>
+          <t>三星电子在今一季度将DRAM合约价上涨了100%之后，二季度的DRAM合约价将再度环比上涨30%。</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>sz002491</t>
+          <t>sz002213</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>通鼎互联</t>
+          <t>大为股份</t>
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>13.82</v>
+        <v>29.55</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>10.03</v>
+        <v>10.01</v>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆|公司光电通信业务板块的产品和解决方案主要涵盖光电线缆和光通信设备两大领域，光电线缆领域的具体产品包括光纤预制棒、光纤、光缆、通信电缆、铁路信号缆、电力电缆等。</t>
+          <t>存储芯片|公司旗下大为创芯主要产品有NAND、DRAM存储两大系列，覆盖DDR3、DDR4、LPDDR4X商规/宽温级别产品，已有eMMC工业级产品线。</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>存储芯片</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>储能</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>1.24</v>
+        <v>5.53</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>记者近日多方采访获悉，当前国内储能电芯产能已全面进入供不应求状态，已有头部企业储能电芯订单排期至2027年一季度末。</t>
+          <t>三星电子在今一季度将DRAM合约价上涨了100%之后，二季度的DRAM合约价将再度环比上涨30%。</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>sz000695</t>
+          <t>sz002449</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>滨海能源</t>
+          <t>国星光电</t>
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>12.9</v>
+        <v>8.33</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>9.969999999999999</v>
+        <v>10.04</v>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>锂电负极+储能|1.公司全面聚焦锂电负极材料业务，自建及协同控股股东石墨化产能已形成一定规模优势，于2023年7月底实现4万吨后端成品线投料试生产，并于11月底实现1.8万吨自有石墨化产品线投产调试。
-2.公司生产的负极材料可广泛应用于储能项目。</t>
+          <t>半导体芯片|公司芯片子公司国星半导体以RGB 芯片、倒装芯片、紫光芯片等利基型产品为主，同时研发布局Mini 和Micro 领域，形成了Mini 背光和Mini显示两大系列的芯片产品，在保障对中游封装的供给份额的同时保持独立开发市场能力。</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>锂电负极, 储能</t>
+          <t>半导体芯片</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>储能</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>1.24</v>
+        <v>5.53</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>记者近日多方采访获悉，当前国内储能电芯产能已全面进入供不应求状态，已有头部企业储能电芯订单排期至2027年一季度末。</t>
+          <t>三星电子在今一季度将DRAM合约价上涨了100%之后，二季度的DRAM合约价将再度环比上涨30%。</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>sh688345</t>
+          <t>sz001287</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">博力威  </t>
+          <t>中电港</t>
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>51.6</v>
+        <v>25.26</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>20</v>
+        <v>10.02</v>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>储能电池|公司储能电池主要用于家庭、旅途及户外活动应急供电，装有逆变器，具备将直流电转换为交流电的功能，具有临时备用等特点。</t>
+          <t>存储芯片分销|公司授权代理的上游产品线资源丰富，分销产品类别完备，包括处理器、存储器、模拟器件、传感器等各类电子元器件，覆盖电子信息行业主要芯片企业。</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>储能电池</t>
+          <t>存储芯片分销</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>储能</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>1.24</v>
+        <v>5.53</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>记者近日多方采访获悉，当前国内储能电芯产能已全面进入供不应求状态，已有头部企业储能电芯订单排期至2027年一季度末。</t>
+          <t>三星电子在今一季度将DRAM合约价上涨了100%之后，二季度的DRAM合约价将再度环比上涨30%。</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>sh603988</t>
+          <t>sh600641</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>中电电机</t>
+          <t>先导基电</t>
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>27.02</v>
+        <v>21.09</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>10.02</v>
@@ -3376,1699 +3347,1785 @@
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>风光电储|2025年12月22日公告，董事会同意公司以自有资金或自筹资金6000万元在内蒙古投资设立全资子公司，开展风光电储新能源、金属矿产资源业务，并授权公司经营管理层负责具体办理与本次对外投资有关的一切事项，包括但不限于签署相关协议、办理成立新设公司的相关事项、申报相关审批手续、组织实施等。</t>
+          <t>半导体设备|公司旗下全资子公司凯世通主营离子注入机，在集成电路离子注入机领域，凯世通定位在适用于16纳米及以下制程的FinFET集成电路以及3D存储器的离子注入设备市场。</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>风光电储</t>
+          <t>半导体设备</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>0.9900000000000001</v>
+        <v>5.53</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>台积电表示，旗下硅光整合平台COUPE预计今年进入量产，成为推动共封装光学（CPO）落地的关键里程碑，标志着AI光通信正式进入产业化倒数阶段。</t>
+          <t>三星电子在今一季度将DRAM合约价上涨了100%之后，二季度的DRAM合约价将再度环比上涨30%。</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>sz002980</t>
+          <t>sz300475</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>华盛昌</t>
+          <t>香农芯创</t>
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>50.7</v>
+        <v>148.18</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>6天3板</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>并购重组+光通信|华盛昌公告称，公司拟以现金方式收购深圳市伽蓝特科技有限公司100%股权，整体估值暂定为4.6亿元。伽蓝特专注于仪器仪表测试测量行业中的光通信模块和光芯片测试领域。</t>
+          <t>存储芯片+业绩|公司预计2026年1-3月实现归母净利润114000万元至148000万元，同比增长6714.72%至8747.18%。在生成式人工智能应用需求蓬勃增长的强劲驱动下，行业景气度持续上行，企业级存储产品价格持续上涨，公司盈利能力持续改善，利润水平大幅提高。</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>并购重组, 光通信</t>
+          <t>存储芯片, 业绩</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>0.9900000000000001</v>
+        <v>5.53</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>台积电表示，旗下硅光整合平台COUPE预计今年进入量产，成为推动共封装光学（CPO）落地的关键里程碑，标志着AI光通信正式进入产业化倒数阶段。</t>
+          <t>三星电子在今一季度将DRAM合约价上涨了100%之后，二季度的DRAM合约价将再度环比上涨30%。</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>sz002025</t>
+          <t>sh688693</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>航天电器</t>
+          <t xml:space="preserve">锴威特  </t>
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>66.72</v>
+        <v>66.92</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>10.01</v>
+        <v>19.99</v>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>光通信|公司生产的光通信器件（光有源器件）包括各种激光器、探测器、光收发一体化组件和模块等系列产品，广泛应用于光通信、数据中心、视频安防监控、智能电网、物联网、医疗传感等众多领域。公司江苏奥雷新基建用光模块产业化项目的厂房基建工程已封顶，预计完工时间为2024年12月底，项目达产后，预计年产153万只光模块。</t>
+          <t>并购重组+半导体|2026年3月27日公告，公司拟通过发行股份及支付现金方式向易坤、晶格共智、晶格共创、晶格共赢、晶格顶峰、晶格未来等26名交易对方购买其合计持有的晶艺半导体100.00%股份，并募集配套资金。</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>并购重组, 半导体</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>0.9900000000000001</v>
+        <v>5.53</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>台积电表示，旗下硅光整合平台COUPE预计今年进入量产，成为推动共封装光学（CPO）落地的关键里程碑，标志着AI光通信正式进入产业化倒数阶段。</t>
+          <t>三星电子在今一季度将DRAM合约价上涨了100%之后，二季度的DRAM合约价将再度环比上涨30%。</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>sz002957</t>
+          <t>sh603306</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>科瑞技术</t>
+          <t>华懋科技</t>
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>33.68</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>光通信模组设备|公司已为国内外大客户批量交付光通信模组生产设备。</t>
+          <t>光刻胶|参股徐州博康是国内少有能打通光刻胶上游材料的全产业链公司，已成功开发出10+个高端光刻胶产品系列，包括多种电子束胶，193nm ArF干法光刻胶，248nm KrF正负型光刻胶，365nm I线正负型光刻胶及GHI超厚负胶。光刻胶单体占全球市场份额5%，已储备全球80%的光刻胶单体产品技术。</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>光通信模组设备</t>
+          <t>光刻胶</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>猪肉产业</t>
+          <t>液冷IDC</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>3.02</v>
+        <v>6.239999999999999</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>国家发改委、商务部、财政部于4月1日宣布开展2026年第二批中央冻猪肉储备收储工作，并要求各地同步实施。</t>
+          <t>业内预测，随着算力持续放量与数据中心建设提速，液冷技术已从“可选配置”变为“强制标配”，市场即将迎来前所未有的机遇期。</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>sz002840</t>
+          <t>sz002536</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>华统股份</t>
+          <t>飞龙股份</t>
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>12.94</v>
+        <v>30.51</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>10.03</v>
+        <v>9.99</v>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>猪肉产业|公司主营业务为生猪养殖、生猪屠宰、肉制品深加工三大主要板块，此外还配套拥有饲料加工、家禽养殖及屠宰等业务。</t>
+          <t xml:space="preserve">服务器液冷|公司电子泵及温控阀系列产品可以应用在服务器液冷领域。
+</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>猪肉产业</t>
+          <t>服务器液冷</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>猪肉产业</t>
+          <t>液冷IDC</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>3.02</v>
+        <v>6.239999999999999</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>国家发改委、商务部、财政部于4月1日宣布开展2026年第二批中央冻猪肉储备收储工作，并要求各地同步实施。</t>
+          <t>业内预测，随着算力持续放量与数据中心建设提速，液冷技术已从“可选配置”变为“强制标配”，市场即将迎来前所未有的机遇期。</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>sh600195</t>
+          <t>sz002975</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>中牧股份</t>
+          <t>博杰股份</t>
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>8.640000000000001</v>
+        <v>79</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>10.06</v>
+        <v>10</v>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>猪用疫苗|公司是兽用疫苗生产企业中产品品种较全、生产能力和产量较大的企业，主要包括高致病性禽流感疫苗、口蹄疫类疫苗、鸡马立克系列产品、ST猪瘟疫苗、猪圆环病毒灭活疫苗、猪伪狂犬病活疫苗、牛结节性皮肤病灭活疫苗、狂犬病灭活疫苗、犬四联疫苗、猫三联灭活疫苗及其他各类常规兽用疫苗产品和诊断制剂。</t>
+          <t>服务器液冷|公司持续为海外大客户提供AI服务器测试设备，在测试设备中已植入自研液冷散热方案，并积累了相关技术储备和解决方案。</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>猪用疫苗</t>
+          <t>服务器液冷</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>钠电池</t>
+          <t>液冷IDC</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>2.15</v>
+        <v>6.239999999999999</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>4月6日，中国科学院物理研究所胡勇胜团队在《自然·能源》发表重磅成果：该团队成功开发出一种具有自保护功能的可聚合不燃电解质（PNE），全球首次在安时级钠离子电池中实现彻底阻断热失控。</t>
+          <t>业内预测，随着算力持续放量与数据中心建设提速，液冷技术已从“可选配置”变为“强制标配”，市场即将迎来前所未有的机遇期。</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>sh605589</t>
+          <t>sh603757</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>圣泉集团</t>
+          <t>大元泵业</t>
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>35.67</v>
+        <v>49.24</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.01</v>
+      </c>
+      <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>钠电池+光刻胶|1.公司已建成万吨级钠电硬碳负极材料产线。
-2.公司产品包括光刻胶用电子级酚醛树脂</t>
+          <t>液冷|公司高压电子水泵及相关屏蔽泵产品能够应用在IDC温控领域，下游客户包括维谛技术、英维克、中兴通讯、曙光数创、同飞股份等。</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>钠电池, 光刻胶</t>
+          <t>液冷</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>钠电池</t>
+          <t>液冷IDC</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>2.15</v>
+        <v>6.239999999999999</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>4月6日，中国科学院物理研究所胡勇胜团队在《自然·能源》发表重磅成果：该团队成功开发出一种具有自保护功能的可聚合不燃电解质（PNE），全球首次在安时级钠离子电池中实现彻底阻断热失控。</t>
+          <t>业内预测，随着算力持续放量与数据中心建设提速，液冷技术已从“可选配置”变为“强制标配”，市场即将迎来前所未有的机遇期。</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>sz002348</t>
+          <t>sh603516</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>高乐股份</t>
+          <t>淳中科技</t>
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>8.050000000000001</v>
+        <v>141.68</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>9.969999999999999</v>
+        <v>10</v>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>钠电池|子公司高乐新能源与重庆尼古拉科技产业研究院有限公司于2024年1月28日签订了《纳米固态钠离子电池成套技术开发研究项目技术研发合作协议书》, 高乐新能源委托尼古拉研究院研究开发“纳米固态钠离子电池成套技术开发研究项目”，尼古拉研究院接受委托并进行此项研究开发工作。</t>
+          <t>液冷|公司与N公司对接的业务主要是各类产品的测试与检测平台，目前正在对接的产品包括：液冷测试平台、基于AI的检测平台、各种测试板卡等。</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>钠电池</t>
+          <t>液冷</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>折叠屏</t>
+          <t>液冷IDC</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>1.28</v>
+        <v>6.239999999999999</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>据中证金牛座，记者4月6日从产业链人士处获悉，富士康已在试产苹果折叠屏iPhone手机。</t>
+          <t>业内预测，随着算力持续放量与数据中心建设提速，液冷技术已从“可选配置”变为“强制标配”，市场即将迎来前所未有的机遇期。</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>sh603327</t>
+          <t>sz000811</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>福蓉科技</t>
+          <t>冰轮环境</t>
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>9.77</v>
+        <v>18.43</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>10.02</v>
+        <v>10.03</v>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>折叠屏|公司生产的铝制结构件材料已经应用于三星、谷歌等品牌折叠屏手机铰链上。</t>
+          <t>液冷|公司可以为液冷业务提供冷源装备和换热装置，公司风冷螺杆机组和变频离心式冷水机组入选工信部《绿色数据中心先进适用技术产品目录》。</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>折叠屏</t>
+          <t>液冷</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>折叠屏</t>
+          <t>液冷IDC</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>1.28</v>
+        <v>6.239999999999999</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>据中证金牛座，记者4月6日从产业链人士处获悉，富士康已在试产苹果折叠屏iPhone手机。</t>
+          <t>业内预测，随着算力持续放量与数据中心建设提速，液冷技术已从“可选配置”变为“强制标配”，市场即将迎来前所未有的机遇期。</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>sz002631</t>
+          <t>sh603203</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>德尔未来</t>
+          <t>快克智能</t>
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>6.83</v>
+        <v>42.1</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>9.98</v>
+        <v>10.01</v>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>锂电池+折叠屏|1.公司参股公司益舟新能源是一家专业从事锂离子电池功能材料的应用开发研究和产业化工作，为锂离子电池性能提升提供技术解决方案的高科技企业，目前主要生产销售高安全性功能隔膜及其关联材料、用于高功率密度电池的功能涂层电池箔及其关联浆料等。
-2.19年2月19日互动平台称，石墨烯透明导电薄膜可以作为柔性触控用于柔性屏手机，这方面公司控股子公司烯成石墨烯有相关技术和专利布局，柔性触控的技术2013年已经突破，并推出了相关样品。</t>
+          <t>液冷|公司为飞龙股份定制散热水泵生产线涉及英伟达AI服务器液冷产品。</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>锂电池, 折叠屏</t>
+          <t>液冷</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>液冷IDC</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>0.95</v>
+        <v>6.239999999999999</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>瑞银财富管理投资总监办公室(CIO)发表机构观点，认为在政策支持、结构性需求增长和海外扩张的推动下，中国电力和资源板块有望步入多年增长周期。</t>
+          <t>业内预测，随着算力持续放量与数据中心建设提速，液冷技术已从“可选配置”变为“强制标配”，市场即将迎来前所未有的机遇期。</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>sh605162</t>
+          <t>sh603890</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">新中港  </t>
+          <t>春秋电子</t>
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>14.07</v>
+        <v>15.61</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>10.01</v>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>5天4板</t>
-        </is>
-      </c>
+      <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>热电联产|公司采用热电联产的方式进行热力产品和电力产品的生产及供应。公司的热力业务主要面向工业用户供应所生产的蒸汽，主要满足工业园区内的造纸、印染、医药、化工、食品等150余家工业企业的热需求。公司生产的电力直接销售给国家电网公司。公司是嵊州市地区唯一一家集中供热的热电联产企业，具有150多家下游客户，区域优势和先发优势明显。</t>
+          <t>服务器液冷|2025年11月25日公告，公司拟通过在新加坡设立的全资控股子公司CQXA作为要约人，向在纳斯达克哥本哈根交易所上市公司Asetek A/S全体股东发起自愿性全面要约，以现金方式收购标的公司全部股份。本次交易对标的公司的要约价格为1.72丹麦克朗/股，对应总要约对价不超过5.73亿丹麦克朗。Asetek作为台式电脑液冷散热技术领域的领先企业，长期为戴尔外星人、华硕、NZXT等全球主流PC品牌商、配件商提供高性能散热解决方案。结合公司制造优势及Asetek技术积累与客户资源，开拓服务器液冷市场。</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>热电联产</t>
+          <t>服务器液冷</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>0.95</v>
+        <v>5.98</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>瑞银财富管理投资总监办公室(CIO)发表机构观点，认为在政策支持、结构性需求增长和海外扩张的推动下，中国电力和资源板块有望步入多年增长周期。</t>
+          <t>西部证券指出，CPO在行业龙头等推动下加速商用，未来三年是CPO行业渗透率快速提升、供应链格局和产业链价值分工逐步构建的核心观察窗口期。</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>sz002310</t>
+          <t>sz002957</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>东方新能</t>
+          <t>科瑞技术</t>
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>3.11</v>
+        <v>37.05</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>9.890000000000001</v>
-      </c>
-      <c r="I74" s="2" t="inlineStr"/>
+        <v>10.01</v>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>并购重组+绿电|2025年12月15日公告，公司拟以现金支付方式购买海城锐海100%股权和电投瑞享80%股权。其中，海城锐海100%股权拟通过在天津产权交易中心摘牌方式购买。标的资产的审计和评估工作尚未完成，评估值及交易价格均尚未确定（海城锐海100%股权在天津产权交易所的挂牌转让底价为1410万元）。本次交易预计构成重大资产重组。通过本次交易，东方园林新增光伏电站、风电场的投资、开发、建设和运营等新能源业务。</t>
+          <t>光通信模组设备|公司已为国内外大客户批量交付光通信模组生产设备。</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>并购重组, 绿电</t>
+          <t>光通信模组设备</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>跨境支付</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>2.38</v>
+        <v>5.98</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>跨境银行间支付清算有限责任公司的网站数据显示，人民币跨境支付系统日均交易额达9205亿元，创过去12个月以来最高，并且在4月2日，单日交易额进一步升至1.22万亿元。</t>
+          <t>西部证券指出，CPO在行业龙头等推动下加速商用，未来三年是CPO行业渗透率快速提升、供应链格局和产业链价值分工逐步构建的核心观察窗口期。</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>sh603123</t>
+          <t>sz002384</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>翠微股份</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>13.16</v>
+        <v>119.91</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>数字货币+跨境支付|1.全资子公司海科融通已积极参与央行数字货币研究所指定运营银行签署合作协议，进行系统对接，推进数字人民币受理的系统建设。
-2.子公司海科融通在国际业务方面聚焦卡组织合作，构建卡组交易生态，外卡收单业务落地，微信海外钱包上线，助力推广境内交易网络与人民币卡使用，并积极探索海外业务。</t>
+          <t>光模块+业绩|东山精密公告称，预计2026年第一季度归属于上市公司股东的净利润为10亿元-11.5亿元，比上年同期增长119.36%-152.27%。AI算力需求强劲驱动了AI基础设施的加速投资，索尔思的光模块产品不断导入新的大客户，成为了公司新的核心利润增长点。</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>数字货币, 跨境支付</t>
+          <t>光模块, 业绩</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="C76" s="2" t="inlineStr"/>
+        <v>5.98</v>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>西部证券指出，CPO在行业龙头等推动下加速商用，未来三年是CPO行业渗透率快速提升、供应链格局和产业链价值分工逐步构建的核心观察窗口期。</t>
+        </is>
+      </c>
       <c r="D76" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>sz002528</t>
+          <t>sz002902</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>ST英飞拓</t>
+          <t>铭普光磁</t>
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>4.19</v>
+        <v>29.37</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>10天5板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 英飞拓推出5G多功能智慧灯杆，支持节能照明、视频监控、新能源充电、公共WIFI、环境监测、信息发布、应急报警、5G微基站等模块，实现多种类型的感知数据采集、分析、仿真预测，提升城市综合治理。</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr"/>
+          <t>光模块+储能|1.铭普光磁在互动平台表示，公司持续开展光模块产品的研发与迭代，目前200G及以下速率光模块正常供货。800G LPO（线性驱动可插拔光模块）方案的ODM定制开发，已实现小批量出货，但整体订单量较小，产生的利润不足以实质性影响公司的整体业绩方向。
+2.2022年5月31日公司在互动平台表示，公司目前生产的用于光伏领域的主要有光伏逆变器用电抗器、高频变压器和电感器，及通信局站用光伏供电系统。</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>光模块, 储能</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="C77" s="2" t="inlineStr"/>
+        <v>5.98</v>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>西部证券指出，CPO在行业龙头等推动下加速商用，未来三年是CPO行业渗透率快速提升、供应链格局和产业链价值分工逐步构建的核心观察窗口期。</t>
+        </is>
+      </c>
       <c r="D77" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>sz002713</t>
+          <t>sh603083</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>*ST东易</t>
+          <t>剑桥科技</t>
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>12.68</v>
+        <v>111.55</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>6天3板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司基于数字化系统优势和业务场景优势，研发推出了行业内首个新一代AIGC技术和真家系统结合的全新设计工具“真家 AIGC”，同时打造出AI 创意大师、AI小白设计家两款智能应用设计工具。</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr"/>
+          <t>光模块|公司系全球高速光组件和光模块技术领先企业，2019年通过收购美国Lumentum公司旗下的Oclaro日本公司的部分资产及技术转移，加上在上海和美国培养发展的两个光电子研发中心，公司又进一步在高速光模块，特别是基于最新PAM4调制技术的400G和800G以及硅光技术的光模块、400G和800G LPO线性直驱光模块领域成为领先公司之一。</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>光模块</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="C78" s="2" t="inlineStr"/>
+        <v>5.98</v>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>西部证券指出，CPO在行业龙头等推动下加速商用，未来三年是CPO行业渗透率快速提升、供应链格局和产业链价值分工逐步构建的核心观察窗口期。</t>
+        </is>
+      </c>
       <c r="D78" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>sh603822</t>
+          <t>sz001267</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST嘉澳  </t>
+          <t>汇绿生态</t>
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>88</v>
+        <v>44.3</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>10.01</v>
+      </c>
+      <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 全资子公司东江能源专业从事餐厨垃圾、废油脂无害化、减量化、资源化处理和新能源开发，是目前国内规模较大的废弃油脂资源综合利用企业。</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr"/>
+          <t>光通信|公司旗下钧恒科技是专业从事高端光通信产品的研制、生产及推广的高新技术企业，拥有从光学组件，光电转换模块，光端机及子系统的行业垂直整合能力，能够为客户提供各种特定应用的定制化产品，包括PLCC、Mini SFF、Micro Pod等各种形态及各种复合协议的光端机及波分复用子系统。
+2025年4月22日公告，子公司武汉钧恒拟投资在湖北省鄂州市临空经济区建设生产厂房、研发中心、办公设施及配套设施的建设，以及高端光通信设备的购置和安装。项目达产后，将主要生产400G及以上速率光模块，满足市场对高速率、大容量光通信模块的需求。本项目投资总额预计约为2亿元。</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>光通信</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="C79" s="2" t="inlineStr"/>
+        <v>5.98</v>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>西部证券指出，CPO在行业龙头等推动下加速商用，未来三年是CPO行业渗透率快速提升、供应链格局和产业链价值分工逐步构建的核心观察窗口期。</t>
+        </is>
+      </c>
       <c r="D79" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>sh603813</t>
+          <t>sz300679</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST原尚 </t>
+          <t>电连技术</t>
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>22.81</v>
+        <v>40.16</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>5.02</v>
+        <v>19.99</v>
       </c>
       <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司参股公司广东原锋新能源科技的股东之一锋源是国内极少的集全套自主知识产权氢燃料电池电堆以及核心零部件膜电极、催化剂、金属双极板等研发、生产、销售一体的公司。</t>
-        </is>
-      </c>
-      <c r="K79" s="2" t="inlineStr"/>
+          <t>高速连接线缆|公司的高速线缆产品在服务器上的应用主要是用于服务器主板到背板的高速连接、主板到加速卡的高速连接以及数据中心设备互联，对英伟达有部分产品的研发送样。</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>高速连接线缆</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>商业航天</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="C80" s="2" t="inlineStr"/>
+        <v>5.4</v>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>7日21时32分，长征八号运载火箭在海南商业航天发射场以“一箭十八星”方式，将千帆星座第7批组网卫星送入预定轨道，发射任务获得圆满成功。</t>
+        </is>
+      </c>
       <c r="D80" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>sz000909</t>
+          <t>sz000551</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>*ST数源</t>
+          <t>创元科技</t>
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>5.99</v>
+        <v>13.94</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>5.09</v>
+        <v>10.02</v>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司旗下东软股份运营的东部软件园是科技部火炬中心认定的国家级科技企业孵化器，是浙江省首家企业化运作的科技园区。</t>
-        </is>
-      </c>
-      <c r="K80" s="2" t="inlineStr"/>
+          <t>商业航天|子公司苏州轴承目前在商业航天领域配套的产品主要是滚针轴承系列产品。</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>商业航天</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>商业航天</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="C81" s="2" t="inlineStr"/>
+        <v>5.4</v>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>7日21时32分，长征八号运载火箭在海南商业航天发射场以“一箭十八星”方式，将千帆星座第7批组网卫星送入预定轨道，发射任务获得圆满成功。</t>
+        </is>
+      </c>
       <c r="D81" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>sh603838</t>
+          <t>sz002361</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST四通 </t>
+          <t>神剑股份</t>
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>8.99</v>
+        <v>16.78</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>5.02</v>
+        <v>10.03</v>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司是一家集研发、设计、生产、销售于一体的新型家居生活陶瓷供应商，产品覆盖日用陶瓷、卫生陶瓷、艺术陶瓷、建筑装饰等全系列家居生活用瓷。</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr"/>
+          <t>商业航天|公司参与了星网项目建设，提供卫星上相关零部件。目前航天类产品有卫星天线、反射器及支撑塔等。</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>商业航天</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>商业航天</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="C82" s="2" t="inlineStr"/>
+        <v>5.4</v>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>7日21时32分，长征八号运载火箭在海南商业航天发射场以“一箭十八星”方式，将千帆星座第7批组网卫星送入预定轨道，发射任务获得圆满成功。</t>
+        </is>
+      </c>
       <c r="D82" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>sz002789</t>
+          <t>sh603211</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>*ST建艺</t>
+          <t>晋拓股份</t>
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>11.73</v>
+        <v>26.09</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>5.01</v>
+        <v>9.99</v>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司是集施工、设计、资源矿产、科技工业园、高新技术建材产业、投融资为一体的规模化实体企业集团。</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr"/>
+          <t>机器人+商业航天|1.公司与施耐德、UR机器人等合作，向其供应伺服马达、感应器、机器关节所需要的零部件。
+2.卫星通信零部件是公司业务板块之一，公司高度关注商业航天的发展。</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>机器人, 商业航天</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>商业航天</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="C83" s="2" t="inlineStr"/>
+        <v>5.4</v>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>7日21时32分，长征八号运载火箭在海南商业航天发射场以“一箭十八星”方式，将千帆星座第7批组网卫星送入预定轨道，发射任务获得圆满成功。</t>
+        </is>
+      </c>
       <c r="D83" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>sz002650</t>
+          <t>sz002046</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>ST加加</t>
+          <t>国机精工</t>
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>7.23</v>
+        <v>45.97</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>4.93</v>
+        <v>10</v>
       </c>
       <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 主营业务涉及酱油、植物油、食醋、味精、鸡精、蚝油等的生产及销售。</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr"/>
+          <t>商业航天|公司在航天领域所使用的轴承市场中份额较高，重点产品配套率90%以上，在卫星、空间站、运载火箭等均有公司的产品。公司旗下洛阳轴承研究所是我国神舟系列载人飞船专用轴承的重要供应商。</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>商业航天</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr"/>
+          <t>商业航天</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>7日21时32分，长征八号运载火箭在海南商业航天发射场以“一箭十八星”方式，将千帆星座第7批组网卫星送入预定轨道，发射任务获得圆满成功。</t>
+        </is>
+      </c>
       <c r="D84" s="2" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>sh603778</t>
+          <t>sz002342</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>国晟科技</t>
+          <t>巨力索具</t>
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>31.55</v>
+        <v>14.17</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>6天3板</t>
-        </is>
-      </c>
+        <v>10.02</v>
+      </c>
+      <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>光伏+锂电池|1.公司目前从事大尺寸高效异质结光伏电池的研发、生产、销售，以及异质结、TOPCON、PERC等电池组件的生产与销售。控股孙公司恒立聚能涉及钙钛矿研究。
-2.国晟科技公告称，公司拟以2.406亿元的价格受让正豪科技、林琴合计持有的孚悦科技100%股权。交易完成后，公司将持有标的公司100%股权，标的公司将纳入公司合并报表。孚悦科技主要从事高精密度新型锂电池结构件的研发、生产和销售。</t>
+          <t>商业航天|公司为神舟十九号发射任务提供了火箭转运索具、总装索具、火箭分离索具等。</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>光伏, 锂电池</t>
+          <t>商业航天</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr"/>
+          <t>商业航天</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>7日21时32分，长征八号运载火箭在海南商业航天发射场以“一箭十八星”方式，将千帆星座第7批组网卫星送入预定轨道，发射任务获得圆满成功。</t>
+        </is>
+      </c>
       <c r="D85" s="2" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>sh600654</t>
+          <t>sz000917</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">中安科  </t>
+          <t>电广传媒</t>
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>4</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>9.890000000000001</v>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.04</v>
+      </c>
+      <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>算力租赁|2024年7月25日公告，公司及全资子公司灵算智云（武汉）投资有限公司拟与宜兴兴阳产业投资有限公司签署投资合作协议，共建宜兴人工智能算力中心项目。本次合作项目计划总投资为3.75亿元。</t>
+          <t>参股北斗院|旗下达晨财智管理基金参股北斗院专注于卫星导航、航天测控两大领域的技术与产品的研发、生产与销售，客户涵盖国防军工、低空安全、商业航天、能源、交通、教育等多个行业。</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>算力租赁</t>
+          <t>参股北斗院</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr"/>
+          <t>光纤光缆</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>截至2026年4月6日，由AI数据中心建设与地缘需求驱动的全球光纤市场涨价潮进一步确认，最新数据显示中国市场G652.D光纤价格自去年低点涨超400%。</t>
+        </is>
+      </c>
       <c r="D86" s="2" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>sz002051</t>
+          <t>sz000586</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>中工国际</t>
+          <t>汇源通信</t>
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>10.48</v>
+        <v>22.84</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>9.969999999999999</v>
+        <v>10.02</v>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>3天2板</t>
+          <t>4天4板</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>一带一路+基建|公司是经中华人民共和国商务部批准，由国内著名的外贸公司、设计院、机械制造商和施工单位共同发起设立的股份有限公司。主营业务是国际工程总承包</t>
+          <t>光缆光纤|公司是国内最早的全系列光缆供应商之一，光缆光纤业务主要生产、销售普通光缆、特种光缆、气吹微缆等，以及提供工程解决方案服务。公司旗下全资子公司汇源光通信是国内电力光缆的制造商、气吹微缆的供应商，同时也是高压输电线路在线检测产品的供应商。</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>一带一路, 基建</t>
+          <t>光缆光纤</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr"/>
+          <t>光纤光缆</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>截至2026年4月6日，由AI数据中心建设与地缘需求驱动的全球光纤市场涨价潮进一步确认，最新数据显示中国市场G652.D光纤价格自去年低点涨超400%。</t>
+        </is>
+      </c>
       <c r="D87" s="2" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>sh603637</t>
+          <t>sz002491</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>镇海股份</t>
+          <t>通鼎互联</t>
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>12.73</v>
+        <v>15.2</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="I87" s="2" t="inlineStr"/>
+        <v>9.99</v>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>股份转让|镇海股份公告称，公司控股股东舜通集团及实际控制人余姚市国资中心拟通过公开征集受让方的方式协议转让公司部分股份。舜通集团拟转让其持有的35,802,881股股份，占公司总股本的15%。转让完成后，舜通集团及其一致行动人舜建集团合计持股比例降至6.22%，该事项可能导致公司控股股东及实际控制人发生变更。</t>
+          <t>光纤光缆|公司光电通信业务板块的产品和解决方案主要涵盖光电线缆和光通信设备两大领域，光电线缆领域的具体产品包括光纤预制棒、光纤、光缆、通信电缆、铁路信号缆、电力电缆等。</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>股份转让</t>
+          <t>光纤光缆</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr"/>
+          <t>光纤光缆</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>截至2026年4月6日，由AI数据中心建设与地缘需求驱动的全球光纤市场涨价潮进一步确认，最新数据显示中国市场G652.D光纤价格自去年低点涨超400%。</t>
+        </is>
+      </c>
       <c r="D88" s="2" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>sz000890</t>
+          <t>sh600869</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>法尔胜</t>
+          <t>远东股份</t>
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>17.61</v>
+        <v>15.83</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I88" s="2" t="inlineStr"/>
+        <v>10.01</v>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>主营不涉及光纤|1.法尔胜公告称，公司澄清主营业务不涉及“光纤”、“特种光纤”，不存在“重组”或“被借壳”情形，控股股东下属子公司与上市公司无股权关系及业务往来。
-2.公司主营业务为金属制品及环保业务。</t>
+          <t>光纤|公司在通信前沿领域加速多模光纤（OM3/OM4/OM5）项目实施批量投产，推进落实空芯光纤等前沿技术。</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>主营不涉及光纤</t>
+          <t>光纤</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr"/>
+          <t>光纤光缆</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>截至2026年4月6日，由AI数据中心建设与地缘需求驱动的全球光纤市场涨价潮进一步确认，最新数据显示中国市场G652.D光纤价格自去年低点涨超400%。</t>
+        </is>
+      </c>
       <c r="D89" s="2" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>sz000652</t>
+          <t>sh600105</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>泰达股份</t>
+          <t>永鼎股份</t>
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>4.2</v>
+        <v>33.23</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>9.950000000000001</v>
+        <v>10</v>
       </c>
       <c r="I89" s="2" t="inlineStr"/>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>转让泰达能源股权|泰达股份公告称，公司拟向泰达供应链转让其持有的泰达能源51%股权（对应出资额12,850万元）。本次交易完成后，上市公司不再持有泰达能源股权。交易价格1.87亿元。本次交易构成重大资产重组。</t>
+          <t>光纤|公司主要产品为光纤预制棒、通信光纤、通信光缆、特种光缆、室内光缆、蝶形光缆、光电复合缆、通信电缆、数据电缆。</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>转让泰达能源股权</t>
+          <t>光纤</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr"/>
+          <t>医药生物</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>4月7日，北京市医保局等10部门联合发布《北京市支持创新医药高质量发展若干措施（2026年）》，推出32条新举措。</t>
+        </is>
+      </c>
       <c r="D90" s="2" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>sz002193</t>
+          <t>sz000919</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>如意集团</t>
+          <t>金陵药业</t>
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>5.93</v>
+        <v>8.91</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I90" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>纺织|毛纺行业龙头。海外并购不断，收购标的的业务范围涵盖上游原材料、纺织制造、品牌服饰，标的运营的国家包括日本、澳大利亚、韩国、印度、英国、澳大利亚、新西兰、德国和法国等。</t>
+          <t>创新药|公司目前已披露的创新药产品有琥珀酸亚铁片、复方磺胺甲噁唑注射液、硫酸镁注射液、术苓健脾胶囊、碳酸司维拉姆干混悬剂、噁拉戈利片。</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>纺织</t>
+          <t>创新药</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr"/>
+          <t>医药生物</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>4月7日，北京市医保局等10部门联合发布《北京市支持创新医药高质量发展若干措施（2026年）》，推出32条新举措。</t>
+        </is>
+      </c>
       <c r="D91" s="2" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>sz000019</t>
+          <t>sh600721</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>深粮控股</t>
+          <t>百花医药</t>
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>7.84</v>
+        <v>11.2</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>9.959999999999999</v>
+        <v>10.02</v>
       </c>
       <c r="I91" s="2" t="inlineStr"/>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>农业种植|老牌国企，专注于茶产业,已建立从茶叶种植、茶叶初制/精制、茶提取、精品茶销售、茶文化体验、电子商务、茶叶交易服务平台、茶叶金融等较为完善的茶产业链体系。</t>
+          <t>CRO|公司主营业务为药物发现、研究、技术服务，提供从药物发现、CMC、临床CRO、药品注册、CMO/API供应等新药开发全流程的服务及一体化的解决方案。</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>农业种植</t>
+          <t>CRO</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr"/>
+          <t>医药生物</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>4月7日，北京市医保局等10部门联合发布《北京市支持创新医药高质量发展若干措施（2026年）》，推出32条新举措。</t>
+        </is>
+      </c>
       <c r="D92" s="2" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>sh603090</t>
+          <t>sh603538</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>宏盛股份</t>
+          <t xml:space="preserve">美诺华  </t>
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>63.83</v>
+        <v>43.24</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="I92" s="2" t="inlineStr"/>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>锂电池+液冷IDC|1.公司锂电池PACK产品应用于工业储能、动力储能以及家用储能市场。
-2.公司掌握液冷散热技术，能够为多种场景提供解决方案，同时，公司与苏州和信精密科技股份有限公司合资成立了无锡和宏智散热科技有限公司，和信精密是行业内领先的数据中心设备供应商，双方通过设立合资公司的形式，拓展数据中心环境温度控制业务。</t>
+          <t>减肥药|2026年3月19日公司在官微公布益生菌（JH389）胶囊产品临床数据，结果显示，服用该产品8周可显著改善受试者体重、体脂及肥胖相关指标，有助于全面提升生活质量、有助于正向调节肠道菌群结构，同时对糖脂代谢及各项安全性指标无不良影响。</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>锂电池, 液冷IDC</t>
+          <t>减肥药</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-      